--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -45,7 +45,7 @@
     <t xml:space="preserve">1.  Set your starting point</t>
   </si>
   <si>
-    <t xml:space="preserve">On the 'Cash Flow' tab, type your Beginning Balance in E5 and your start date in E6 (use a Monday). Everything below it flows from those two cells.</t>
+    <t xml:space="preserve">On the 'Cash Flow' tab, type your Beginning Balance in E5 and your start date in E6 (use a Friday). Everything below it flows from those two cells. Weeks run Friday through Thursday, so your Friday paycheck arrives on day one.</t>
   </si>
   <si>
     <t xml:space="preserve">2.  Check your recurring transactions</t>
@@ -300,7 +300,7 @@
     <t xml:space="preserve">Beginning Balance  (cash on hand at the start date)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cash Flow Start Date  (use a Monday)</t>
+    <t xml:space="preserve">Cash Flow Start Date  (use a Friday — weeks run Fri to Thu)</t>
   </si>
   <si>
     <t xml:space="preserve">Minimum Cash Cushion  (warn me below this)</t>
@@ -309,7 +309,7 @@
     <t xml:space="preserve">Today</t>
   </si>
   <si>
-    <t xml:space="preserve">This sheet projects 13 weeks from the start date. Week 1 begins on the start date.</t>
+    <t xml:space="preserve">This sheet projects 13 weeks from the start date. Week 1 begins on the start date and each week runs Friday through Thursday.</t>
   </si>
   <si>
     <t xml:space="preserve">Blue = you type it.  Black/green = formulas, leave them alone.  A yellow 'Amount Paid' cell means that transaction is due or overdue and still unrecorded.</t>
@@ -817,6 +817,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -839,10 +843,6 @@
     </xf>
     <xf numFmtId="167" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2404,7 +2404,11 @@
         <v>89</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>46237</v>
+        <v>46234</v>
+      </c>
+      <c r="G6" s="26" t="str">
+        <f aca="false">IF($E$6="","",IF(WEEKDAY($E$6,2)=5,"","! That is a "&amp;TEXT($E$6,"dddd")&amp;". Weeks run Friday to Thursday — use the Friday on or before the date you want to start."))</f>
+        <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2416,12 +2420,12 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="28" t="n">
         <f aca="true">TODAY()</f>
-        <v>46236</v>
+        <v>46240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2435,24 +2439,24 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="str">
+      <c r="B13" s="29" t="str">
         <f aca="false">"WEEK 1     "&amp;TEXT($E$6+0,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+0+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 1     Mon, Aug 3   through   Sun, Aug 9, 2026</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="30" t="s">
+        <v>WEEK 1     Fri, Jul 31   through   Thu, Aug 6, 2026</v>
+      </c>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="31" t="n">
+      <c r="H13" s="30"/>
+      <c r="I13" s="32" t="n">
         <f aca="false">$E$5</f>
         <v>1250</v>
       </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="32" t="str">
+      <c r="J13" s="30"/>
+      <c r="K13" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,1)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,1)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -2518,7 +2522,7 @@
       </c>
       <c r="J15" s="38" t="str">
         <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2553,7 +2557,7 @@
       </c>
       <c r="J16" s="38" t="str">
         <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2588,7 +2592,7 @@
       </c>
       <c r="J17" s="38" t="str">
         <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2623,112 +2627,112 @@
       </c>
       <c r="J18" s="38" t="str">
         <f aca="true">IF($B18="","",IF($F18&lt;&gt;"","PAID",IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
-      </c>
-      <c r="C19" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="34" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$G$4:$G$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v/>
       </c>
       <c r="D19" s="35" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$D$4:$D$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
-      </c>
-      <c r="E19" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="36" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$E$4:$E$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v/>
       </c>
       <c r="F19" s="16"/>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="36" t="str">
         <f aca="false">IF($B19="","",IF($F19&lt;&gt;"",$F19,$E19))</f>
-        <v>790</v>
+        <v/>
       </c>
       <c r="H19" s="36" t="n">
         <f aca="false">IF($B19="",0,IF($D19="Income",$G19,-$G19))</f>
-        <v>790</v>
-      </c>
-      <c r="I19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="37" t="str">
         <f aca="false">IF($B19="","",$I$13+SUM($H$15:$H19))</f>
-        <v>2078.9</v>
+        <v/>
       </c>
       <c r="J19" s="38" t="str">
         <f aca="true">IF($B19="","",IF($F19&lt;&gt;"","PAID",IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
-      </c>
-      <c r="C20" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="34" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$G$4:$G$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v/>
       </c>
       <c r="D20" s="35" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$D$4:$D$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E20" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="36" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$E$4:$E$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v/>
       </c>
       <c r="F20" s="16"/>
-      <c r="G20" s="36" t="n">
+      <c r="G20" s="36" t="str">
         <f aca="false">IF($B20="","",IF($F20&lt;&gt;"",$F20,$E20))</f>
-        <v>4.99</v>
+        <v/>
       </c>
       <c r="H20" s="36" t="n">
         <f aca="false">IF($B20="",0,IF($D20="Income",$G20,-$G20))</f>
-        <v>-4.99</v>
-      </c>
-      <c r="I20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="37" t="str">
         <f aca="false">IF($B20="","",$I$13+SUM($H$15:$H20))</f>
-        <v>2073.91</v>
+        <v/>
       </c>
       <c r="J20" s="38" t="str">
         <f aca="true">IF($B20="","",IF($F20&lt;&gt;"","PAID",IF($C20&lt;TODAY(),"PAST DUE",IF($C20&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
-      </c>
-      <c r="C21" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C21" s="34" t="str">
         <f aca="false">IF($B21="","",INDEX(Schedule!$G$4:$G$483,MATCH(1007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v/>
       </c>
       <c r="D21" s="35" t="str">
         <f aca="false">IF($B21="","",INDEX(Schedule!$D$4:$D$483,MATCH(1007,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E21" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E21" s="36" t="str">
         <f aca="false">IF($B21="","",INDEX(Schedule!$E$4:$E$483,MATCH(1007,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v/>
       </c>
       <c r="F21" s="16"/>
-      <c r="G21" s="36" t="n">
+      <c r="G21" s="36" t="str">
         <f aca="false">IF($B21="","",IF($F21&lt;&gt;"",$F21,$E21))</f>
-        <v>500</v>
+        <v/>
       </c>
       <c r="H21" s="36" t="n">
         <f aca="false">IF($B21="",0,IF($D21="Income",$G21,-$G21))</f>
-        <v>-500</v>
-      </c>
-      <c r="I21" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="37" t="str">
         <f aca="false">IF($B21="","",$I$13+SUM($H$15:$H21))</f>
-        <v>1573.91</v>
+        <v/>
       </c>
       <c r="J21" s="38" t="str">
         <f aca="true">IF($B21="","",IF($F21&lt;&gt;"","PAID",IF($C21&lt;TODAY(),"PAST DUE",IF($C21&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2872,7 +2876,7 @@
       </c>
       <c r="I26" s="37" t="n">
         <f aca="false">IF($B26="","",$I$13+SUM($H$15:$H26))</f>
-        <v>1453.91</v>
+        <v>1168.9</v>
       </c>
       <c r="J26" s="8"/>
     </row>
@@ -2899,7 +2903,7 @@
       </c>
       <c r="I27" s="37" t="n">
         <f aca="false">IF($B27="","",$I$13+SUM($H$15:$H27))</f>
-        <v>1393.91</v>
+        <v>1108.9</v>
       </c>
       <c r="J27" s="8"/>
     </row>
@@ -2926,7 +2930,7 @@
       </c>
       <c r="I28" s="37" t="n">
         <f aca="false">IF($B28="","",$I$13+SUM($H$15:$H28))</f>
-        <v>1358.91</v>
+        <v>1073.9</v>
       </c>
       <c r="J28" s="8"/>
     </row>
@@ -3007,7 +3011,7 @@
       <c r="D32" s="42"/>
       <c r="E32" s="43" t="n">
         <f aca="false">SUM($E$15:$E$31)</f>
-        <v>1651.09</v>
+        <v>356.1</v>
       </c>
       <c r="F32" s="43" t="n">
         <f aca="false">SUM($F$15:$F$24)</f>
@@ -3015,15 +3019,15 @@
       </c>
       <c r="G32" s="43" t="n">
         <f aca="false">SUM($G$15:$G$31)</f>
-        <v>1651.09</v>
+        <v>356.1</v>
       </c>
       <c r="H32" s="43" t="n">
         <f aca="false">SUM($H$15:$H$31)</f>
-        <v>108.91</v>
+        <v>-176.1</v>
       </c>
       <c r="I32" s="44" t="n">
         <f aca="false">$I$13+SUM($H$15:$H$31)</f>
-        <v>1358.91</v>
+        <v>1073.9</v>
       </c>
       <c r="J32" s="45" t="str">
         <f aca="false">IF($I$32&lt;0,"SHORTFALL",IF($I$32&lt;$E$7,"TIGHT","OK"))</f>
@@ -3031,28 +3035,28 @@
       </c>
       <c r="K32" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$15:$D$31,"Income",$G$15:$G$31),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$15:$D$31,"Expense",$G$15:$G$31),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$32,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $771.09   =  net $108.91</v>
+        <v>Income $90.00   less expenses $266.10   =  net -$176.10</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="28" t="str">
+      <c r="B34" s="29" t="str">
         <f aca="false">"WEEK 2     "&amp;TEXT($E$6+7,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+7+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 2     Mon, Aug 10   through   Sun, Aug 16, 2026</v>
-      </c>
-      <c r="C34" s="29"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="30" t="s">
+        <v>WEEK 2     Fri, Aug 7   through   Thu, Aug 13, 2026</v>
+      </c>
+      <c r="C34" s="30"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="30"/>
+      <c r="F34" s="30"/>
+      <c r="G34" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H34" s="29"/>
-      <c r="I34" s="31" t="n">
+      <c r="H34" s="30"/>
+      <c r="I34" s="32" t="n">
         <f aca="false">$I$32</f>
-        <v>1358.91</v>
-      </c>
-      <c r="J34" s="29"/>
-      <c r="K34" s="32" t="str">
+        <v>1073.9</v>
+      </c>
+      <c r="J34" s="30"/>
+      <c r="K34" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,2)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,2)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -3089,81 +3093,81 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C36" s="34" t="n">
         <f aca="false">IF($B36="","",INDEX(Schedule!$G$4:$G$483,MATCH(2001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="D36" s="35" t="str">
         <f aca="false">IF($B36="","",INDEX(Schedule!$D$4:$D$483,MATCH(2001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E36" s="36" t="n">
         <f aca="false">IF($B36="","",INDEX(Schedule!$E$4:$E$483,MATCH(2001,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>790</v>
       </c>
       <c r="F36" s="16"/>
       <c r="G36" s="36" t="n">
         <f aca="false">IF($B36="","",IF($F36&lt;&gt;"",$F36,$E36))</f>
-        <v>163.5</v>
+        <v>790</v>
       </c>
       <c r="H36" s="36" t="n">
         <f aca="false">IF($B36="",0,IF($D36="Income",$G36,-$G36))</f>
-        <v>-163.5</v>
+        <v>790</v>
       </c>
       <c r="I36" s="37" t="n">
         <f aca="false">IF($B36="","",$I$34+SUM($H$36:$H36))</f>
-        <v>1195.41</v>
+        <v>1863.9</v>
       </c>
       <c r="J36" s="38" t="str">
         <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Google One</v>
       </c>
       <c r="C37" s="34" t="n">
         <f aca="false">IF($B37="","",INDEX(Schedule!$G$4:$G$483,MATCH(2002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="D37" s="35" t="str">
         <f aca="false">IF($B37="","",INDEX(Schedule!$D$4:$D$483,MATCH(2002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E37" s="36" t="n">
         <f aca="false">IF($B37="","",INDEX(Schedule!$E$4:$E$483,MATCH(2002,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>4.99</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="36" t="n">
         <f aca="false">IF($B37="","",IF($F37&lt;&gt;"",$F37,$E37))</f>
-        <v>90</v>
+        <v>4.99</v>
       </c>
       <c r="H37" s="36" t="n">
         <f aca="false">IF($B37="",0,IF($D37="Income",$G37,-$G37))</f>
-        <v>90</v>
+        <v>-4.99</v>
       </c>
       <c r="I37" s="37" t="n">
         <f aca="false">IF($B37="","",$I$34+SUM($H$36:$H37))</f>
-        <v>1285.41</v>
+        <v>1858.91</v>
       </c>
       <c r="J37" s="38" t="str">
         <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>Upstart (loan)</v>
       </c>
       <c r="C38" s="34" t="n">
         <f aca="false">IF($B38="","",INDEX(Schedule!$G$4:$G$483,MATCH(2003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="D38" s="35" t="str">
         <f aca="false">IF($B38="","",INDEX(Schedule!$D$4:$D$483,MATCH(2003,Schedule!$K$4:$K$483,0)))</f>
@@ -3171,104 +3175,104 @@
       </c>
       <c r="E38" s="36" t="n">
         <f aca="false">IF($B38="","",INDEX(Schedule!$E$4:$E$483,MATCH(2003,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>500</v>
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="36" t="n">
         <f aca="false">IF($B38="","",IF($F38&lt;&gt;"",$F38,$E38))</f>
-        <v>2.99</v>
+        <v>500</v>
       </c>
       <c r="H38" s="36" t="n">
         <f aca="false">IF($B38="",0,IF($D38="Income",$G38,-$G38))</f>
-        <v>-2.99</v>
+        <v>-500</v>
       </c>
       <c r="I38" s="37" t="n">
         <f aca="false">IF($B38="","",$I$34+SUM($H$36:$H38))</f>
-        <v>1282.42</v>
+        <v>1358.91</v>
       </c>
       <c r="J38" s="38" t="str">
         <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Central Maine Power Co.</v>
       </c>
       <c r="C39" s="34" t="n">
         <f aca="false">IF($B39="","",INDEX(Schedule!$G$4:$G$483,MATCH(2004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46248</v>
+        <v>46244</v>
       </c>
       <c r="D39" s="35" t="str">
         <f aca="false">IF($B39="","",INDEX(Schedule!$D$4:$D$483,MATCH(2004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E39" s="36" t="n">
         <f aca="false">IF($B39="","",INDEX(Schedule!$E$4:$E$483,MATCH(2004,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>163.5</v>
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="36" t="n">
         <f aca="false">IF($B39="","",IF($F39&lt;&gt;"",$F39,$E39))</f>
-        <v>790</v>
+        <v>163.5</v>
       </c>
       <c r="H39" s="36" t="n">
         <f aca="false">IF($B39="",0,IF($D39="Income",$G39,-$G39))</f>
-        <v>790</v>
+        <v>-163.5</v>
       </c>
       <c r="I39" s="37" t="n">
         <f aca="false">IF($B39="","",$I$34+SUM($H$36:$H39))</f>
-        <v>2072.42</v>
+        <v>1195.41</v>
       </c>
       <c r="J39" s="38" t="str">
         <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C40" s="34" t="n">
         <f aca="false">IF($B40="","",INDEX(Schedule!$G$4:$G$483,MATCH(2005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="D40" s="35" t="str">
         <f aca="false">IF($B40="","",INDEX(Schedule!$D$4:$D$483,MATCH(2005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E40" s="36" t="n">
         <f aca="false">IF($B40="","",INDEX(Schedule!$E$4:$E$483,MATCH(2005,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="F40" s="16"/>
       <c r="G40" s="36" t="n">
         <f aca="false">IF($B40="","",IF($F40&lt;&gt;"",$F40,$E40))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="H40" s="36" t="n">
         <f aca="false">IF($B40="",0,IF($D40="Income",$G40,-$G40))</f>
-        <v>-350</v>
+        <v>90</v>
       </c>
       <c r="I40" s="37" t="n">
         <f aca="false">IF($B40="","",$I$34+SUM($H$36:$H40))</f>
-        <v>1722.42</v>
+        <v>1285.41</v>
       </c>
       <c r="J40" s="38" t="str">
         <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Spectrum</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C41" s="34" t="n">
         <f aca="false">IF($B41="","",INDEX(Schedule!$G$4:$G$483,MATCH(2006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46250</v>
+        <v>46247</v>
       </c>
       <c r="D41" s="35" t="str">
         <f aca="false">IF($B41="","",INDEX(Schedule!$D$4:$D$483,MATCH(2006,Schedule!$K$4:$K$483,0)))</f>
@@ -3276,59 +3280,59 @@
       </c>
       <c r="E41" s="36" t="n">
         <f aca="false">IF($B41="","",INDEX(Schedule!$E$4:$E$483,MATCH(2006,Schedule!$K$4:$K$483,0)))</f>
-        <v>171.1</v>
+        <v>2.99</v>
       </c>
       <c r="F41" s="16"/>
       <c r="G41" s="36" t="n">
         <f aca="false">IF($B41="","",IF($F41&lt;&gt;"",$F41,$E41))</f>
-        <v>171.1</v>
+        <v>2.99</v>
       </c>
       <c r="H41" s="36" t="n">
         <f aca="false">IF($B41="",0,IF($D41="Income",$G41,-$G41))</f>
-        <v>-171.1</v>
+        <v>-2.99</v>
       </c>
       <c r="I41" s="37" t="n">
         <f aca="false">IF($B41="","",$I$34+SUM($H$36:$H41))</f>
-        <v>1551.32</v>
+        <v>1282.42</v>
       </c>
       <c r="J41" s="38" t="str">
         <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services</v>
-      </c>
-      <c r="C42" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="34" t="str">
         <f aca="false">IF($B42="","",INDEX(Schedule!$G$4:$G$483,MATCH(2007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46250</v>
+        <v/>
       </c>
       <c r="D42" s="35" t="str">
         <f aca="false">IF($B42="","",INDEX(Schedule!$D$4:$D$483,MATCH(2007,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E42" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E42" s="36" t="str">
         <f aca="false">IF($B42="","",INDEX(Schedule!$E$4:$E$483,MATCH(2007,Schedule!$K$4:$K$483,0)))</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="F42" s="16"/>
-      <c r="G42" s="36" t="n">
+      <c r="G42" s="36" t="str">
         <f aca="false">IF($B42="","",IF($F42&lt;&gt;"",$F42,$E42))</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="H42" s="36" t="n">
         <f aca="false">IF($B42="",0,IF($D42="Income",$G42,-$G42))</f>
-        <v>-45</v>
-      </c>
-      <c r="I42" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="37" t="str">
         <f aca="false">IF($B42="","",$I$34+SUM($H$36:$H42))</f>
-        <v>1506.32</v>
+        <v/>
       </c>
       <c r="J42" s="38" t="str">
         <f aca="true">IF($B42="","",IF($F42&lt;&gt;"","PAID",IF($C42&lt;TODAY(),"PAST DUE",IF($C42&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3595,7 +3599,7 @@
       <c r="D53" s="42"/>
       <c r="E53" s="43" t="n">
         <f aca="false">SUM($E$36:$E$52)</f>
-        <v>1612.59</v>
+        <v>1551.48</v>
       </c>
       <c r="F53" s="43" t="n">
         <f aca="false">SUM($F$36:$F$45)</f>
@@ -3603,15 +3607,15 @@
       </c>
       <c r="G53" s="43" t="n">
         <f aca="false">SUM($G$36:$G$52)</f>
-        <v>1612.59</v>
+        <v>1551.48</v>
       </c>
       <c r="H53" s="43" t="n">
         <f aca="false">SUM($H$36:$H$52)</f>
-        <v>147.41</v>
+        <v>208.52</v>
       </c>
       <c r="I53" s="44" t="n">
         <f aca="false">$I$34+SUM($H$36:$H$52)</f>
-        <v>1506.32</v>
+        <v>1282.42</v>
       </c>
       <c r="J53" s="45" t="str">
         <f aca="false">IF($I$53&lt;0,"SHORTFALL",IF($I$53&lt;$E$7,"TIGHT","OK"))</f>
@@ -3619,28 +3623,28 @@
       </c>
       <c r="K53" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$36:$D$52,"Income",$G$36:$G$52),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$36:$D$52,"Expense",$G$36:$G$52),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$53,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $732.59   =  net $147.41</v>
+        <v>Income $880.00   less expenses $671.48   =  net $208.52</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="28" t="str">
+      <c r="B55" s="29" t="str">
         <f aca="false">"WEEK 3     "&amp;TEXT($E$6+14,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+14+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 3     Mon, Aug 17   through   Sun, Aug 23, 2026</v>
-      </c>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="30" t="s">
+        <v>WEEK 3     Fri, Aug 14   through   Thu, Aug 20, 2026</v>
+      </c>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H55" s="29"/>
-      <c r="I55" s="31" t="n">
+      <c r="H55" s="30"/>
+      <c r="I55" s="32" t="n">
         <f aca="false">$I$53</f>
-        <v>1506.32</v>
-      </c>
-      <c r="J55" s="29"/>
-      <c r="K55" s="32" t="str">
+        <v>1282.42</v>
+      </c>
+      <c r="J55" s="30"/>
+      <c r="K55" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,3)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,3)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -3677,32 +3681,32 @@
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Metal Copy</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C57" s="34" t="n">
         <f aca="false">IF($B57="","",INDEX(Schedule!$G$4:$G$483,MATCH(3001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="D57" s="35" t="str">
         <f aca="false">IF($B57="","",INDEX(Schedule!$D$4:$D$483,MATCH(3001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E57" s="36" t="n">
         <f aca="false">IF($B57="","",INDEX(Schedule!$E$4:$E$483,MATCH(3001,Schedule!$K$4:$K$483,0)))</f>
-        <v>16.99</v>
+        <v>790</v>
       </c>
       <c r="F57" s="16"/>
       <c r="G57" s="36" t="n">
         <f aca="false">IF($B57="","",IF($F57&lt;&gt;"",$F57,$E57))</f>
-        <v>16.99</v>
+        <v>790</v>
       </c>
       <c r="H57" s="36" t="n">
         <f aca="false">IF($B57="",0,IF($D57="Income",$G57,-$G57))</f>
-        <v>-16.99</v>
+        <v>790</v>
       </c>
       <c r="I57" s="37" t="n">
         <f aca="false">IF($B57="","",$I$55+SUM($H$57:$H57))</f>
-        <v>1489.33</v>
+        <v>2072.42</v>
       </c>
       <c r="J57" s="38" t="str">
         <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3712,32 +3716,32 @@
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C58" s="34" t="n">
         <f aca="false">IF($B58="","",INDEX(Schedule!$G$4:$G$483,MATCH(3002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="D58" s="35" t="str">
         <f aca="false">IF($B58="","",INDEX(Schedule!$D$4:$D$483,MATCH(3002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E58" s="36" t="n">
         <f aca="false">IF($B58="","",INDEX(Schedule!$E$4:$E$483,MATCH(3002,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="36" t="n">
         <f aca="false">IF($B58="","",IF($F58&lt;&gt;"",$F58,$E58))</f>
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="H58" s="36" t="n">
         <f aca="false">IF($B58="",0,IF($D58="Income",$G58,-$G58))</f>
-        <v>90</v>
+        <v>-350</v>
       </c>
       <c r="I58" s="37" t="n">
         <f aca="false">IF($B58="","",$I$55+SUM($H$57:$H58))</f>
-        <v>1579.33</v>
+        <v>1722.42</v>
       </c>
       <c r="J58" s="38" t="str">
         <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3747,32 +3751,32 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Spectrum</v>
       </c>
       <c r="C59" s="34" t="n">
         <f aca="false">IF($B59="","",INDEX(Schedule!$G$4:$G$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46255</v>
+        <v>46250</v>
       </c>
       <c r="D59" s="35" t="str">
         <f aca="false">IF($B59="","",INDEX(Schedule!$D$4:$D$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E59" s="36" t="n">
         <f aca="false">IF($B59="","",INDEX(Schedule!$E$4:$E$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>171.1</v>
       </c>
       <c r="F59" s="16"/>
       <c r="G59" s="36" t="n">
         <f aca="false">IF($B59="","",IF($F59&lt;&gt;"",$F59,$E59))</f>
-        <v>790</v>
+        <v>171.1</v>
       </c>
       <c r="H59" s="36" t="n">
         <f aca="false">IF($B59="",0,IF($D59="Income",$G59,-$G59))</f>
-        <v>790</v>
+        <v>-171.1</v>
       </c>
       <c r="I59" s="37" t="n">
         <f aca="false">IF($B59="","",$I$55+SUM($H$57:$H59))</f>
-        <v>2369.33</v>
+        <v>1551.32</v>
       </c>
       <c r="J59" s="38" t="str">
         <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3782,106 +3786,106 @@
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="34" t="str">
+        <v>Maine Revenue Services</v>
+      </c>
+      <c r="C60" s="34" t="n">
         <f aca="false">IF($B60="","",INDEX(Schedule!$G$4:$G$483,MATCH(3004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46250</v>
       </c>
       <c r="D60" s="35" t="str">
         <f aca="false">IF($B60="","",INDEX(Schedule!$D$4:$D$483,MATCH(3004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E60" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E60" s="36" t="n">
         <f aca="false">IF($B60="","",INDEX(Schedule!$E$4:$E$483,MATCH(3004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="F60" s="16"/>
-      <c r="G60" s="36" t="str">
+      <c r="G60" s="36" t="n">
         <f aca="false">IF($B60="","",IF($F60&lt;&gt;"",$F60,$E60))</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="H60" s="36" t="n">
         <f aca="false">IF($B60="",0,IF($D60="Income",$G60,-$G60))</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="37" t="str">
+        <v>-45</v>
+      </c>
+      <c r="I60" s="37" t="n">
         <f aca="false">IF($B60="","",$I$55+SUM($H$57:$H60))</f>
-        <v/>
+        <v>1506.32</v>
       </c>
       <c r="J60" s="38" t="str">
         <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C61" s="34" t="str">
+        <v>Metal Copy</v>
+      </c>
+      <c r="C61" s="34" t="n">
         <f aca="false">IF($B61="","",INDEX(Schedule!$G$4:$G$483,MATCH(3005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46252</v>
       </c>
       <c r="D61" s="35" t="str">
         <f aca="false">IF($B61="","",INDEX(Schedule!$D$4:$D$483,MATCH(3005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E61" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E61" s="36" t="n">
         <f aca="false">IF($B61="","",INDEX(Schedule!$E$4:$E$483,MATCH(3005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>16.99</v>
       </c>
       <c r="F61" s="16"/>
-      <c r="G61" s="36" t="str">
+      <c r="G61" s="36" t="n">
         <f aca="false">IF($B61="","",IF($F61&lt;&gt;"",$F61,$E61))</f>
-        <v/>
+        <v>16.99</v>
       </c>
       <c r="H61" s="36" t="n">
         <f aca="false">IF($B61="",0,IF($D61="Income",$G61,-$G61))</f>
-        <v>0</v>
-      </c>
-      <c r="I61" s="37" t="str">
+        <v>-16.99</v>
+      </c>
+      <c r="I61" s="37" t="n">
         <f aca="false">IF($B61="","",$I$55+SUM($H$57:$H61))</f>
-        <v/>
+        <v>1489.33</v>
       </c>
       <c r="J61" s="38" t="str">
         <f aca="true">IF($B61="","",IF($F61&lt;&gt;"","PAID",IF($C61&lt;TODAY(),"PAST DUE",IF($C61&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C62" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C62" s="34" t="n">
         <f aca="false">IF($B62="","",INDEX(Schedule!$G$4:$G$483,MATCH(3006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46253</v>
       </c>
       <c r="D62" s="35" t="str">
         <f aca="false">IF($B62="","",INDEX(Schedule!$D$4:$D$483,MATCH(3006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E62" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E62" s="36" t="n">
         <f aca="false">IF($B62="","",INDEX(Schedule!$E$4:$E$483,MATCH(3006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F62" s="16"/>
-      <c r="G62" s="36" t="str">
+      <c r="G62" s="36" t="n">
         <f aca="false">IF($B62="","",IF($F62&lt;&gt;"",$F62,$E62))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H62" s="36" t="n">
         <f aca="false">IF($B62="",0,IF($D62="Income",$G62,-$G62))</f>
-        <v>0</v>
-      </c>
-      <c r="I62" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I62" s="37" t="n">
         <f aca="false">IF($B62="","",$I$55+SUM($H$57:$H62))</f>
-        <v/>
+        <v>1579.33</v>
       </c>
       <c r="J62" s="38" t="str">
         <f aca="true">IF($B62="","",IF($F62&lt;&gt;"","PAID",IF($C62&lt;TODAY(),"PAST DUE",IF($C62&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4183,7 +4187,7 @@
       <c r="D74" s="42"/>
       <c r="E74" s="43" t="n">
         <f aca="false">SUM($E$57:$E$73)</f>
-        <v>896.99</v>
+        <v>1463.09</v>
       </c>
       <c r="F74" s="43" t="n">
         <f aca="false">SUM($F$57:$F$66)</f>
@@ -4191,15 +4195,15 @@
       </c>
       <c r="G74" s="43" t="n">
         <f aca="false">SUM($G$57:$G$73)</f>
-        <v>896.99</v>
+        <v>1463.09</v>
       </c>
       <c r="H74" s="43" t="n">
         <f aca="false">SUM($H$57:$H$73)</f>
-        <v>863.01</v>
+        <v>296.91</v>
       </c>
       <c r="I74" s="44" t="n">
         <f aca="false">$I$55+SUM($H$57:$H$73)</f>
-        <v>2369.33</v>
+        <v>1579.33</v>
       </c>
       <c r="J74" s="45" t="str">
         <f aca="false">IF($I$74&lt;0,"SHORTFALL",IF($I$74&lt;$E$7,"TIGHT","OK"))</f>
@@ -4207,28 +4211,28 @@
       </c>
       <c r="K74" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$57:$D$73,"Income",$G$57:$G$73),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$57:$D$73,"Expense",$G$57:$G$73),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$74,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $16.99   =  net $863.01</v>
+        <v>Income $880.00   less expenses $583.09   =  net $296.91</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B76" s="28" t="str">
+      <c r="B76" s="29" t="str">
         <f aca="false">"WEEK 4     "&amp;TEXT($E$6+21,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+21+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 4     Mon, Aug 24   through   Sun, Aug 30, 2026</v>
-      </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="30" t="s">
+        <v>WEEK 4     Fri, Aug 21   through   Thu, Aug 27, 2026</v>
+      </c>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H76" s="29"/>
-      <c r="I76" s="31" t="n">
+      <c r="H76" s="30"/>
+      <c r="I76" s="32" t="n">
         <f aca="false">$I$74</f>
-        <v>2369.33</v>
-      </c>
-      <c r="J76" s="29"/>
-      <c r="K76" s="32" t="str">
+        <v>1579.33</v>
+      </c>
+      <c r="J76" s="30"/>
+      <c r="K76" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,4)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,4)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -4265,32 +4269,32 @@
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Microsoft</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C78" s="34" t="n">
         <f aca="false">IF($B78="","",INDEX(Schedule!$G$4:$G$483,MATCH(4001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="D78" s="35" t="str">
         <f aca="false">IF($B78="","",INDEX(Schedule!$D$4:$D$483,MATCH(4001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E78" s="36" t="n">
         <f aca="false">IF($B78="","",INDEX(Schedule!$E$4:$E$483,MATCH(4001,Schedule!$K$4:$K$483,0)))</f>
-        <v>13.7</v>
+        <v>790</v>
       </c>
       <c r="F78" s="16"/>
       <c r="G78" s="36" t="n">
         <f aca="false">IF($B78="","",IF($F78&lt;&gt;"",$F78,$E78))</f>
-        <v>13.7</v>
+        <v>790</v>
       </c>
       <c r="H78" s="36" t="n">
         <f aca="false">IF($B78="",0,IF($D78="Income",$G78,-$G78))</f>
-        <v>-13.7</v>
+        <v>790</v>
       </c>
       <c r="I78" s="37" t="n">
         <f aca="false">IF($B78="","",$I$76+SUM($H$78:$H78))</f>
-        <v>2355.63</v>
+        <v>2369.33</v>
       </c>
       <c r="J78" s="38" t="str">
         <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4300,7 +4304,7 @@
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Microsoft</v>
       </c>
       <c r="C79" s="34" t="n">
         <f aca="false">IF($B79="","",INDEX(Schedule!$G$4:$G$483,MATCH(4002,Schedule!$K$4:$K$483,0)))</f>
@@ -4312,20 +4316,20 @@
       </c>
       <c r="E79" s="36" t="n">
         <f aca="false">IF($B79="","",INDEX(Schedule!$E$4:$E$483,MATCH(4002,Schedule!$K$4:$K$483,0)))</f>
-        <v>43.87</v>
+        <v>13.7</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="36" t="n">
         <f aca="false">IF($B79="","",IF($F79&lt;&gt;"",$F79,$E79))</f>
-        <v>43.87</v>
+        <v>13.7</v>
       </c>
       <c r="H79" s="36" t="n">
         <f aca="false">IF($B79="",0,IF($D79="Income",$G79,-$G79))</f>
-        <v>-43.87</v>
+        <v>-13.7</v>
       </c>
       <c r="I79" s="37" t="n">
         <f aca="false">IF($B79="","",$I$76+SUM($H$78:$H79))</f>
-        <v>2311.76</v>
+        <v>2355.63</v>
       </c>
       <c r="J79" s="38" t="str">
         <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4335,32 +4339,32 @@
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Central Maine Power: Property</v>
       </c>
       <c r="C80" s="34" t="n">
         <f aca="false">IF($B80="","",INDEX(Schedule!$G$4:$G$483,MATCH(4003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="D80" s="35" t="str">
         <f aca="false">IF($B80="","",INDEX(Schedule!$D$4:$D$483,MATCH(4003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E80" s="36" t="n">
         <f aca="false">IF($B80="","",INDEX(Schedule!$E$4:$E$483,MATCH(4003,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>43.87</v>
       </c>
       <c r="F80" s="16"/>
       <c r="G80" s="36" t="n">
         <f aca="false">IF($B80="","",IF($F80&lt;&gt;"",$F80,$E80))</f>
-        <v>90</v>
+        <v>43.87</v>
       </c>
       <c r="H80" s="36" t="n">
         <f aca="false">IF($B80="",0,IF($D80="Income",$G80,-$G80))</f>
-        <v>90</v>
+        <v>-43.87</v>
       </c>
       <c r="I80" s="37" t="n">
         <f aca="false">IF($B80="","",$I$76+SUM($H$78:$H80))</f>
-        <v>2401.76</v>
+        <v>2311.76</v>
       </c>
       <c r="J80" s="38" t="str">
         <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4370,11 +4374,11 @@
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C81" s="34" t="n">
         <f aca="false">IF($B81="","",INDEX(Schedule!$G$4:$G$483,MATCH(4004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46262</v>
+        <v>46260</v>
       </c>
       <c r="D81" s="35" t="str">
         <f aca="false">IF($B81="","",INDEX(Schedule!$D$4:$D$483,MATCH(4004,Schedule!$K$4:$K$483,0)))</f>
@@ -4382,20 +4386,20 @@
       </c>
       <c r="E81" s="36" t="n">
         <f aca="false">IF($B81="","",INDEX(Schedule!$E$4:$E$483,MATCH(4004,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>90</v>
       </c>
       <c r="F81" s="16"/>
       <c r="G81" s="36" t="n">
         <f aca="false">IF($B81="","",IF($F81&lt;&gt;"",$F81,$E81))</f>
-        <v>790</v>
+        <v>90</v>
       </c>
       <c r="H81" s="36" t="n">
         <f aca="false">IF($B81="",0,IF($D81="Income",$G81,-$G81))</f>
-        <v>790</v>
+        <v>90</v>
       </c>
       <c r="I81" s="37" t="n">
         <f aca="false">IF($B81="","",$I$76+SUM($H$78:$H81))</f>
-        <v>3191.76</v>
+        <v>2401.76</v>
       </c>
       <c r="J81" s="38" t="str">
         <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4405,36 +4409,36 @@
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services (2)</v>
-      </c>
-      <c r="C82" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C82" s="34" t="str">
         <f aca="false">IF($B82="","",INDEX(Schedule!$G$4:$G$483,MATCH(4005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46264</v>
+        <v/>
       </c>
       <c r="D82" s="35" t="str">
         <f aca="false">IF($B82="","",INDEX(Schedule!$D$4:$D$483,MATCH(4005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E82" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E82" s="36" t="str">
         <f aca="false">IF($B82="","",INDEX(Schedule!$E$4:$E$483,MATCH(4005,Schedule!$K$4:$K$483,0)))</f>
-        <v>150</v>
+        <v/>
       </c>
       <c r="F82" s="16"/>
-      <c r="G82" s="36" t="n">
+      <c r="G82" s="36" t="str">
         <f aca="false">IF($B82="","",IF($F82&lt;&gt;"",$F82,$E82))</f>
-        <v>150</v>
+        <v/>
       </c>
       <c r="H82" s="36" t="n">
         <f aca="false">IF($B82="",0,IF($D82="Income",$G82,-$G82))</f>
-        <v>-150</v>
-      </c>
-      <c r="I82" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="37" t="str">
         <f aca="false">IF($B82="","",$I$76+SUM($H$78:$H82))</f>
-        <v>3041.76</v>
+        <v/>
       </c>
       <c r="J82" s="38" t="str">
         <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4771,7 +4775,7 @@
       <c r="D95" s="42"/>
       <c r="E95" s="43" t="n">
         <f aca="false">SUM($E$78:$E$94)</f>
-        <v>1087.57</v>
+        <v>937.57</v>
       </c>
       <c r="F95" s="43" t="n">
         <f aca="false">SUM($F$78:$F$87)</f>
@@ -4779,15 +4783,15 @@
       </c>
       <c r="G95" s="43" t="n">
         <f aca="false">SUM($G$78:$G$94)</f>
-        <v>1087.57</v>
+        <v>937.57</v>
       </c>
       <c r="H95" s="43" t="n">
         <f aca="false">SUM($H$78:$H$94)</f>
-        <v>672.43</v>
+        <v>822.43</v>
       </c>
       <c r="I95" s="44" t="n">
         <f aca="false">$I$76+SUM($H$78:$H$94)</f>
-        <v>3041.76</v>
+        <v>2401.76</v>
       </c>
       <c r="J95" s="45" t="str">
         <f aca="false">IF($I$95&lt;0,"SHORTFALL",IF($I$95&lt;$E$7,"TIGHT","OK"))</f>
@@ -4795,28 +4799,28 @@
       </c>
       <c r="K95" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$78:$D$94,"Income",$G$78:$G$94),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$78:$D$94,"Expense",$G$78:$G$94),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$95,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $207.57   =  net $672.43</v>
+        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B97" s="28" t="str">
+      <c r="B97" s="29" t="str">
         <f aca="false">"WEEK 5     "&amp;TEXT($E$6+28,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+28+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 5     Mon, Aug 31   through   Sun, Sep 6, 2026</v>
-      </c>
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="30" t="s">
+        <v>WEEK 5     Fri, Aug 28   through   Thu, Sep 3, 2026</v>
+      </c>
+      <c r="C97" s="30"/>
+      <c r="D97" s="30"/>
+      <c r="E97" s="30"/>
+      <c r="F97" s="30"/>
+      <c r="G97" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H97" s="29"/>
-      <c r="I97" s="31" t="n">
+      <c r="H97" s="30"/>
+      <c r="I97" s="32" t="n">
         <f aca="false">$I$95</f>
-        <v>3041.76</v>
-      </c>
-      <c r="J97" s="29"/>
-      <c r="K97" s="32" t="str">
+        <v>2401.76</v>
+      </c>
+      <c r="J97" s="30"/>
+      <c r="K97" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,5)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,5)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -4853,32 +4857,32 @@
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C99" s="34" t="n">
         <f aca="false">IF($B99="","",INDEX(Schedule!$G$4:$G$483,MATCH(5001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="D99" s="35" t="str">
         <f aca="false">IF($B99="","",INDEX(Schedule!$D$4:$D$483,MATCH(5001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E99" s="36" t="n">
         <f aca="false">IF($B99="","",INDEX(Schedule!$E$4:$E$483,MATCH(5001,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>790</v>
       </c>
       <c r="F99" s="16"/>
       <c r="G99" s="36" t="n">
         <f aca="false">IF($B99="","",IF($F99&lt;&gt;"",$F99,$E99))</f>
-        <v>350</v>
+        <v>790</v>
       </c>
       <c r="H99" s="36" t="n">
         <f aca="false">IF($B99="",0,IF($D99="Income",$G99,-$G99))</f>
-        <v>-350</v>
+        <v>790</v>
       </c>
       <c r="I99" s="37" t="n">
         <f aca="false">IF($B99="","",$I$97+SUM($H$99:$H99))</f>
-        <v>2691.76</v>
+        <v>3191.76</v>
       </c>
       <c r="J99" s="38" t="str">
         <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4888,11 +4892,11 @@
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Progressive Insurance</v>
+        <v>Maine Revenue Services (2)</v>
       </c>
       <c r="C100" s="34" t="n">
         <f aca="false">IF($B100="","",INDEX(Schedule!$G$4:$G$483,MATCH(5002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="D100" s="35" t="str">
         <f aca="false">IF($B100="","",INDEX(Schedule!$D$4:$D$483,MATCH(5002,Schedule!$K$4:$K$483,0)))</f>
@@ -4900,20 +4904,20 @@
       </c>
       <c r="E100" s="36" t="n">
         <f aca="false">IF($B100="","",INDEX(Schedule!$E$4:$E$483,MATCH(5002,Schedule!$K$4:$K$483,0)))</f>
-        <v>143.37</v>
+        <v>150</v>
       </c>
       <c r="F100" s="16"/>
       <c r="G100" s="36" t="n">
         <f aca="false">IF($B100="","",IF($F100&lt;&gt;"",$F100,$E100))</f>
-        <v>143.37</v>
+        <v>150</v>
       </c>
       <c r="H100" s="36" t="n">
         <f aca="false">IF($B100="",0,IF($D100="Income",$G100,-$G100))</f>
-        <v>-143.37</v>
+        <v>-150</v>
       </c>
       <c r="I100" s="37" t="n">
         <f aca="false">IF($B100="","",$I$97+SUM($H$99:$H100))</f>
-        <v>2548.39</v>
+        <v>3041.76</v>
       </c>
       <c r="J100" s="38" t="str">
         <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4923,32 +4927,32 @@
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C101" s="34" t="n">
         <f aca="false">IF($B101="","",INDEX(Schedule!$G$4:$G$483,MATCH(5003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46267</v>
+        <v>46265</v>
       </c>
       <c r="D101" s="35" t="str">
         <f aca="false">IF($B101="","",INDEX(Schedule!$D$4:$D$483,MATCH(5003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E101" s="36" t="n">
         <f aca="false">IF($B101="","",INDEX(Schedule!$E$4:$E$483,MATCH(5003,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="F101" s="16"/>
       <c r="G101" s="36" t="n">
         <f aca="false">IF($B101="","",IF($F101&lt;&gt;"",$F101,$E101))</f>
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="H101" s="36" t="n">
         <f aca="false">IF($B101="",0,IF($D101="Income",$G101,-$G101))</f>
-        <v>90</v>
+        <v>-350</v>
       </c>
       <c r="I101" s="37" t="n">
         <f aca="false">IF($B101="","",$I$97+SUM($H$99:$H101))</f>
-        <v>2638.39</v>
+        <v>2691.76</v>
       </c>
       <c r="J101" s="38" t="str">
         <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4958,32 +4962,32 @@
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Progressive Insurance</v>
       </c>
       <c r="C102" s="34" t="n">
         <f aca="false">IF($B102="","",INDEX(Schedule!$G$4:$G$483,MATCH(5004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="D102" s="35" t="str">
         <f aca="false">IF($B102="","",INDEX(Schedule!$D$4:$D$483,MATCH(5004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E102" s="36" t="n">
         <f aca="false">IF($B102="","",INDEX(Schedule!$E$4:$E$483,MATCH(5004,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>143.37</v>
       </c>
       <c r="F102" s="16"/>
       <c r="G102" s="36" t="n">
         <f aca="false">IF($B102="","",IF($F102&lt;&gt;"",$F102,$E102))</f>
-        <v>790</v>
+        <v>143.37</v>
       </c>
       <c r="H102" s="36" t="n">
         <f aca="false">IF($B102="",0,IF($D102="Income",$G102,-$G102))</f>
-        <v>790</v>
+        <v>-143.37</v>
       </c>
       <c r="I102" s="37" t="n">
         <f aca="false">IF($B102="","",$I$97+SUM($H$99:$H102))</f>
-        <v>3428.39</v>
+        <v>2548.39</v>
       </c>
       <c r="J102" s="38" t="str">
         <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4993,32 +4997,32 @@
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: Claude</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C103" s="34" t="n">
         <f aca="false">IF($B103="","",INDEX(Schedule!$G$4:$G$483,MATCH(5005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="D103" s="35" t="str">
         <f aca="false">IF($B103="","",INDEX(Schedule!$D$4:$D$483,MATCH(5005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E103" s="36" t="n">
         <f aca="false">IF($B103="","",INDEX(Schedule!$E$4:$E$483,MATCH(5005,Schedule!$K$4:$K$483,0)))</f>
-        <v>21.1</v>
+        <v>90</v>
       </c>
       <c r="F103" s="16"/>
       <c r="G103" s="36" t="n">
         <f aca="false">IF($B103="","",IF($F103&lt;&gt;"",$F103,$E103))</f>
-        <v>21.1</v>
+        <v>90</v>
       </c>
       <c r="H103" s="36" t="n">
         <f aca="false">IF($B103="",0,IF($D103="Income",$G103,-$G103))</f>
-        <v>-21.1</v>
+        <v>90</v>
       </c>
       <c r="I103" s="37" t="n">
         <f aca="false">IF($B103="","",$I$97+SUM($H$99:$H103))</f>
-        <v>3407.29</v>
+        <v>2638.39</v>
       </c>
       <c r="J103" s="38" t="str">
         <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5028,71 +5032,71 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>OpenAI</v>
-      </c>
-      <c r="C104" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C104" s="34" t="str">
         <f aca="false">IF($B104="","",INDEX(Schedule!$G$4:$G$483,MATCH(5006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46270</v>
+        <v/>
       </c>
       <c r="D104" s="35" t="str">
         <f aca="false">IF($B104="","",INDEX(Schedule!$D$4:$D$483,MATCH(5006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E104" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E104" s="36" t="str">
         <f aca="false">IF($B104="","",INDEX(Schedule!$E$4:$E$483,MATCH(5006,Schedule!$K$4:$K$483,0)))</f>
-        <v>20</v>
+        <v/>
       </c>
       <c r="F104" s="16"/>
-      <c r="G104" s="36" t="n">
+      <c r="G104" s="36" t="str">
         <f aca="false">IF($B104="","",IF($F104&lt;&gt;"",$F104,$E104))</f>
-        <v>20</v>
+        <v/>
       </c>
       <c r="H104" s="36" t="n">
         <f aca="false">IF($B104="",0,IF($D104="Income",$G104,-$G104))</f>
-        <v>-20</v>
-      </c>
-      <c r="I104" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="37" t="str">
         <f aca="false">IF($B104="","",$I$97+SUM($H$99:$H104))</f>
-        <v>3387.29</v>
+        <v/>
       </c>
       <c r="J104" s="38" t="str">
         <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Obsidian</v>
-      </c>
-      <c r="C105" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C105" s="34" t="str">
         <f aca="false">IF($B105="","",INDEX(Schedule!$G$4:$G$483,MATCH(5007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46270</v>
+        <v/>
       </c>
       <c r="D105" s="35" t="str">
         <f aca="false">IF($B105="","",INDEX(Schedule!$D$4:$D$483,MATCH(5007,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E105" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E105" s="36" t="str">
         <f aca="false">IF($B105="","",INDEX(Schedule!$E$4:$E$483,MATCH(5007,Schedule!$K$4:$K$483,0)))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="F105" s="16"/>
-      <c r="G105" s="36" t="n">
+      <c r="G105" s="36" t="str">
         <f aca="false">IF($B105="","",IF($F105&lt;&gt;"",$F105,$E105))</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="H105" s="36" t="n">
         <f aca="false">IF($B105="",0,IF($D105="Income",$G105,-$G105))</f>
-        <v>-10</v>
-      </c>
-      <c r="I105" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="37" t="str">
         <f aca="false">IF($B105="","",$I$97+SUM($H$99:$H105))</f>
-        <v>3377.29</v>
+        <v/>
       </c>
       <c r="J105" s="38" t="str">
         <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5359,7 +5363,7 @@
       <c r="D116" s="42"/>
       <c r="E116" s="43" t="n">
         <f aca="false">SUM($E$99:$E$115)</f>
-        <v>1424.47</v>
+        <v>1523.37</v>
       </c>
       <c r="F116" s="43" t="n">
         <f aca="false">SUM($F$99:$F$108)</f>
@@ -5367,15 +5371,15 @@
       </c>
       <c r="G116" s="43" t="n">
         <f aca="false">SUM($G$99:$G$115)</f>
-        <v>1424.47</v>
+        <v>1523.37</v>
       </c>
       <c r="H116" s="43" t="n">
         <f aca="false">SUM($H$99:$H$115)</f>
-        <v>335.53</v>
+        <v>236.63</v>
       </c>
       <c r="I116" s="44" t="n">
         <f aca="false">$I$97+SUM($H$99:$H$115)</f>
-        <v>3377.29</v>
+        <v>2638.39</v>
       </c>
       <c r="J116" s="45" t="str">
         <f aca="false">IF($I$116&lt;0,"SHORTFALL",IF($I$116&lt;$E$7,"TIGHT","OK"))</f>
@@ -5383,28 +5387,28 @@
       </c>
       <c r="K116" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$99:$D$115,"Income",$G$99:$G$115),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$99:$D$115,"Expense",$G$99:$G$115),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$116,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $544.47   =  net $335.53</v>
+        <v>Income $880.00   less expenses $643.37   =  net $236.63</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B118" s="28" t="str">
+      <c r="B118" s="29" t="str">
         <f aca="false">"WEEK 6     "&amp;TEXT($E$6+35,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+35+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 6     Mon, Sep 7   through   Sun, Sep 13, 2026</v>
-      </c>
-      <c r="C118" s="29"/>
-      <c r="D118" s="29"/>
-      <c r="E118" s="29"/>
-      <c r="F118" s="29"/>
-      <c r="G118" s="30" t="s">
+        <v>WEEK 6     Fri, Sep 4   through   Thu, Sep 10, 2026</v>
+      </c>
+      <c r="C118" s="30"/>
+      <c r="D118" s="30"/>
+      <c r="E118" s="30"/>
+      <c r="F118" s="30"/>
+      <c r="G118" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H118" s="29"/>
-      <c r="I118" s="31" t="n">
+      <c r="H118" s="30"/>
+      <c r="I118" s="32" t="n">
         <f aca="false">$I$116</f>
-        <v>3377.29</v>
-      </c>
-      <c r="J118" s="29"/>
-      <c r="K118" s="32" t="str">
+        <v>2638.39</v>
+      </c>
+      <c r="J118" s="30"/>
+      <c r="K118" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,6)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,6)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -5441,32 +5445,32 @@
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C120" s="34" t="n">
         <f aca="false">IF($B120="","",INDEX(Schedule!$G$4:$G$483,MATCH(6001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="D120" s="35" t="str">
         <f aca="false">IF($B120="","",INDEX(Schedule!$D$4:$D$483,MATCH(6001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E120" s="36" t="n">
         <f aca="false">IF($B120="","",INDEX(Schedule!$E$4:$E$483,MATCH(6001,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v>790</v>
       </c>
       <c r="F120" s="16"/>
       <c r="G120" s="36" t="n">
         <f aca="false">IF($B120="","",IF($F120&lt;&gt;"",$F120,$E120))</f>
-        <v>4.99</v>
+        <v>790</v>
       </c>
       <c r="H120" s="36" t="n">
         <f aca="false">IF($B120="",0,IF($D120="Income",$G120,-$G120))</f>
-        <v>-4.99</v>
+        <v>790</v>
       </c>
       <c r="I120" s="37" t="n">
         <f aca="false">IF($B120="","",$I$118+SUM($H$120:$H120))</f>
-        <v>3372.3</v>
+        <v>3428.39</v>
       </c>
       <c r="J120" s="38" t="str">
         <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5476,11 +5480,11 @@
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
+        <v>Apple: Claude</v>
       </c>
       <c r="C121" s="34" t="n">
         <f aca="false">IF($B121="","",INDEX(Schedule!$G$4:$G$483,MATCH(6002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="D121" s="35" t="str">
         <f aca="false">IF($B121="","",INDEX(Schedule!$D$4:$D$483,MATCH(6002,Schedule!$K$4:$K$483,0)))</f>
@@ -5488,20 +5492,20 @@
       </c>
       <c r="E121" s="36" t="n">
         <f aca="false">IF($B121="","",INDEX(Schedule!$E$4:$E$483,MATCH(6002,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v>21.1</v>
       </c>
       <c r="F121" s="16"/>
       <c r="G121" s="36" t="n">
         <f aca="false">IF($B121="","",IF($F121&lt;&gt;"",$F121,$E121))</f>
-        <v>500</v>
+        <v>21.1</v>
       </c>
       <c r="H121" s="36" t="n">
         <f aca="false">IF($B121="",0,IF($D121="Income",$G121,-$G121))</f>
-        <v>-500</v>
+        <v>-21.1</v>
       </c>
       <c r="I121" s="37" t="n">
         <f aca="false">IF($B121="","",$I$118+SUM($H$120:$H121))</f>
-        <v>2872.3</v>
+        <v>3407.29</v>
       </c>
       <c r="J121" s="38" t="str">
         <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5511,32 +5515,32 @@
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>OpenAI</v>
       </c>
       <c r="C122" s="34" t="n">
         <f aca="false">IF($B122="","",INDEX(Schedule!$G$4:$G$483,MATCH(6003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46274</v>
+        <v>46270</v>
       </c>
       <c r="D122" s="35" t="str">
         <f aca="false">IF($B122="","",INDEX(Schedule!$D$4:$D$483,MATCH(6003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E122" s="36" t="n">
         <f aca="false">IF($B122="","",INDEX(Schedule!$E$4:$E$483,MATCH(6003,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F122" s="16"/>
       <c r="G122" s="36" t="n">
         <f aca="false">IF($B122="","",IF($F122&lt;&gt;"",$F122,$E122))</f>
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="H122" s="36" t="n">
         <f aca="false">IF($B122="",0,IF($D122="Income",$G122,-$G122))</f>
-        <v>90</v>
+        <v>-20</v>
       </c>
       <c r="I122" s="37" t="n">
         <f aca="false">IF($B122="","",$I$118+SUM($H$120:$H122))</f>
-        <v>2962.3</v>
+        <v>3387.29</v>
       </c>
       <c r="J122" s="38" t="str">
         <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5546,11 +5550,11 @@
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Obsidian</v>
       </c>
       <c r="C123" s="34" t="n">
         <f aca="false">IF($B123="","",INDEX(Schedule!$G$4:$G$483,MATCH(6004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46275</v>
+        <v>46270</v>
       </c>
       <c r="D123" s="35" t="str">
         <f aca="false">IF($B123="","",INDEX(Schedule!$D$4:$D$483,MATCH(6004,Schedule!$K$4:$K$483,0)))</f>
@@ -5558,20 +5562,20 @@
       </c>
       <c r="E123" s="36" t="n">
         <f aca="false">IF($B123="","",INDEX(Schedule!$E$4:$E$483,MATCH(6004,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>10</v>
       </c>
       <c r="F123" s="16"/>
       <c r="G123" s="36" t="n">
         <f aca="false">IF($B123="","",IF($F123&lt;&gt;"",$F123,$E123))</f>
-        <v>163.5</v>
+        <v>10</v>
       </c>
       <c r="H123" s="36" t="n">
         <f aca="false">IF($B123="",0,IF($D123="Income",$G123,-$G123))</f>
-        <v>-163.5</v>
+        <v>-10</v>
       </c>
       <c r="I123" s="37" t="n">
         <f aca="false">IF($B123="","",$I$118+SUM($H$120:$H123))</f>
-        <v>2798.8</v>
+        <v>3377.29</v>
       </c>
       <c r="J123" s="38" t="str">
         <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5581,32 +5585,32 @@
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Google One</v>
       </c>
       <c r="C124" s="34" t="n">
         <f aca="false">IF($B124="","",INDEX(Schedule!$G$4:$G$483,MATCH(6005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46276</v>
+        <v>46272</v>
       </c>
       <c r="D124" s="35" t="str">
         <f aca="false">IF($B124="","",INDEX(Schedule!$D$4:$D$483,MATCH(6005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E124" s="36" t="n">
         <f aca="false">IF($B124="","",INDEX(Schedule!$E$4:$E$483,MATCH(6005,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>4.99</v>
       </c>
       <c r="F124" s="16"/>
       <c r="G124" s="36" t="n">
         <f aca="false">IF($B124="","",IF($F124&lt;&gt;"",$F124,$E124))</f>
-        <v>790</v>
+        <v>4.99</v>
       </c>
       <c r="H124" s="36" t="n">
         <f aca="false">IF($B124="",0,IF($D124="Income",$G124,-$G124))</f>
-        <v>790</v>
+        <v>-4.99</v>
       </c>
       <c r="I124" s="37" t="n">
         <f aca="false">IF($B124="","",$I$118+SUM($H$120:$H124))</f>
-        <v>3588.8</v>
+        <v>3372.3</v>
       </c>
       <c r="J124" s="38" t="str">
         <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5616,11 +5620,11 @@
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>Upstart (loan)</v>
       </c>
       <c r="C125" s="34" t="n">
         <f aca="false">IF($B125="","",INDEX(Schedule!$G$4:$G$483,MATCH(6006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46278</v>
+        <v>46272</v>
       </c>
       <c r="D125" s="35" t="str">
         <f aca="false">IF($B125="","",INDEX(Schedule!$D$4:$D$483,MATCH(6006,Schedule!$K$4:$K$483,0)))</f>
@@ -5628,20 +5632,20 @@
       </c>
       <c r="E125" s="36" t="n">
         <f aca="false">IF($B125="","",INDEX(Schedule!$E$4:$E$483,MATCH(6006,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>500</v>
       </c>
       <c r="F125" s="16"/>
       <c r="G125" s="36" t="n">
         <f aca="false">IF($B125="","",IF($F125&lt;&gt;"",$F125,$E125))</f>
-        <v>2.99</v>
+        <v>500</v>
       </c>
       <c r="H125" s="36" t="n">
         <f aca="false">IF($B125="",0,IF($D125="Income",$G125,-$G125))</f>
-        <v>-2.99</v>
+        <v>-500</v>
       </c>
       <c r="I125" s="37" t="n">
         <f aca="false">IF($B125="","",$I$118+SUM($H$120:$H125))</f>
-        <v>3585.81</v>
+        <v>2872.3</v>
       </c>
       <c r="J125" s="38" t="str">
         <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5651,71 +5655,71 @@
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C126" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C126" s="34" t="n">
         <f aca="false">IF($B126="","",INDEX(Schedule!$G$4:$G$483,MATCH(6007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46274</v>
       </c>
       <c r="D126" s="35" t="str">
         <f aca="false">IF($B126="","",INDEX(Schedule!$D$4:$D$483,MATCH(6007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E126" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E126" s="36" t="n">
         <f aca="false">IF($B126="","",INDEX(Schedule!$E$4:$E$483,MATCH(6007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F126" s="16"/>
-      <c r="G126" s="36" t="str">
+      <c r="G126" s="36" t="n">
         <f aca="false">IF($B126="","",IF($F126&lt;&gt;"",$F126,$E126))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H126" s="36" t="n">
         <f aca="false">IF($B126="",0,IF($D126="Income",$G126,-$G126))</f>
-        <v>0</v>
-      </c>
-      <c r="I126" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I126" s="37" t="n">
         <f aca="false">IF($B126="","",$I$118+SUM($H$120:$H126))</f>
-        <v/>
+        <v>2962.3</v>
       </c>
       <c r="J126" s="38" t="str">
         <f aca="true">IF($B126="","",IF($F126&lt;&gt;"","PAID",IF($C126&lt;TODAY(),"PAST DUE",IF($C126&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6008,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C127" s="34" t="str">
+        <v>Central Maine Power Co.</v>
+      </c>
+      <c r="C127" s="34" t="n">
         <f aca="false">IF($B127="","",INDEX(Schedule!$G$4:$G$483,MATCH(6008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46275</v>
       </c>
       <c r="D127" s="35" t="str">
         <f aca="false">IF($B127="","",INDEX(Schedule!$D$4:$D$483,MATCH(6008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E127" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E127" s="36" t="n">
         <f aca="false">IF($B127="","",INDEX(Schedule!$E$4:$E$483,MATCH(6008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>163.5</v>
       </c>
       <c r="F127" s="16"/>
-      <c r="G127" s="36" t="str">
+      <c r="G127" s="36" t="n">
         <f aca="false">IF($B127="","",IF($F127&lt;&gt;"",$F127,$E127))</f>
-        <v/>
+        <v>163.5</v>
       </c>
       <c r="H127" s="36" t="n">
         <f aca="false">IF($B127="",0,IF($D127="Income",$G127,-$G127))</f>
-        <v>0</v>
-      </c>
-      <c r="I127" s="37" t="str">
+        <v>-163.5</v>
+      </c>
+      <c r="I127" s="37" t="n">
         <f aca="false">IF($B127="","",$I$118+SUM($H$120:$H127))</f>
-        <v/>
+        <v>2798.8</v>
       </c>
       <c r="J127" s="38" t="str">
         <f aca="true">IF($B127="","",IF($F127&lt;&gt;"","PAID",IF($C127&lt;TODAY(),"PAST DUE",IF($C127&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5947,7 +5951,7 @@
       <c r="D137" s="42"/>
       <c r="E137" s="43" t="n">
         <f aca="false">SUM($E$120:$E$136)</f>
-        <v>1551.48</v>
+        <v>1599.59</v>
       </c>
       <c r="F137" s="43" t="n">
         <f aca="false">SUM($F$120:$F$129)</f>
@@ -5955,15 +5959,15 @@
       </c>
       <c r="G137" s="43" t="n">
         <f aca="false">SUM($G$120:$G$136)</f>
-        <v>1551.48</v>
+        <v>1599.59</v>
       </c>
       <c r="H137" s="43" t="n">
         <f aca="false">SUM($H$120:$H$136)</f>
-        <v>208.52</v>
+        <v>160.41</v>
       </c>
       <c r="I137" s="44" t="n">
         <f aca="false">$I$118+SUM($H$120:$H$136)</f>
-        <v>3585.81</v>
+        <v>2798.8</v>
       </c>
       <c r="J137" s="45" t="str">
         <f aca="false">IF($I$137&lt;0,"SHORTFALL",IF($I$137&lt;$E$7,"TIGHT","OK"))</f>
@@ -5971,28 +5975,28 @@
       </c>
       <c r="K137" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$120:$D$136,"Income",$G$120:$G$136),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$120:$D$136,"Expense",$G$120:$G$136),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$137,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $671.48   =  net $208.52</v>
+        <v>Income $880.00   less expenses $719.59   =  net $160.41</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B139" s="28" t="str">
+      <c r="B139" s="29" t="str">
         <f aca="false">"WEEK 7     "&amp;TEXT($E$6+42,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+42+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 7     Mon, Sep 14   through   Sun, Sep 20, 2026</v>
-      </c>
-      <c r="C139" s="29"/>
-      <c r="D139" s="29"/>
-      <c r="E139" s="29"/>
-      <c r="F139" s="29"/>
-      <c r="G139" s="30" t="s">
+        <v>WEEK 7     Fri, Sep 11   through   Thu, Sep 17, 2026</v>
+      </c>
+      <c r="C139" s="30"/>
+      <c r="D139" s="30"/>
+      <c r="E139" s="30"/>
+      <c r="F139" s="30"/>
+      <c r="G139" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H139" s="29"/>
-      <c r="I139" s="31" t="n">
+      <c r="H139" s="30"/>
+      <c r="I139" s="32" t="n">
         <f aca="false">$I$137</f>
-        <v>3585.81</v>
-      </c>
-      <c r="J139" s="29"/>
-      <c r="K139" s="32" t="str">
+        <v>2798.8</v>
+      </c>
+      <c r="J139" s="30"/>
+      <c r="K139" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,7)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,7)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -6029,32 +6033,32 @@
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B141" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C141" s="34" t="n">
         <f aca="false">IF($B141="","",INDEX(Schedule!$G$4:$G$483,MATCH(7001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="D141" s="35" t="str">
         <f aca="false">IF($B141="","",INDEX(Schedule!$D$4:$D$483,MATCH(7001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E141" s="36" t="n">
         <f aca="false">IF($B141="","",INDEX(Schedule!$E$4:$E$483,MATCH(7001,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>790</v>
       </c>
       <c r="F141" s="16"/>
       <c r="G141" s="36" t="n">
         <f aca="false">IF($B141="","",IF($F141&lt;&gt;"",$F141,$E141))</f>
-        <v>350</v>
+        <v>790</v>
       </c>
       <c r="H141" s="36" t="n">
         <f aca="false">IF($B141="",0,IF($D141="Income",$G141,-$G141))</f>
-        <v>-350</v>
+        <v>790</v>
       </c>
       <c r="I141" s="37" t="n">
         <f aca="false">IF($B141="","",$I$139+SUM($H$141:$H141))</f>
-        <v>3235.81</v>
+        <v>3588.8</v>
       </c>
       <c r="J141" s="38" t="str">
         <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6064,32 +6068,32 @@
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C142" s="34" t="n">
         <f aca="false">IF($B142="","",INDEX(Schedule!$G$4:$G$483,MATCH(7002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46281</v>
+        <v>46278</v>
       </c>
       <c r="D142" s="35" t="str">
         <f aca="false">IF($B142="","",INDEX(Schedule!$D$4:$D$483,MATCH(7002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E142" s="36" t="n">
         <f aca="false">IF($B142="","",INDEX(Schedule!$E$4:$E$483,MATCH(7002,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>2.99</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="36" t="n">
         <f aca="false">IF($B142="","",IF($F142&lt;&gt;"",$F142,$E142))</f>
-        <v>90</v>
+        <v>2.99</v>
       </c>
       <c r="H142" s="36" t="n">
         <f aca="false">IF($B142="",0,IF($D142="Income",$G142,-$G142))</f>
-        <v>90</v>
+        <v>-2.99</v>
       </c>
       <c r="I142" s="37" t="n">
         <f aca="false">IF($B142="","",$I$139+SUM($H$141:$H142))</f>
-        <v>3325.81</v>
+        <v>3585.81</v>
       </c>
       <c r="J142" s="38" t="str">
         <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6099,11 +6103,11 @@
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Spectrum</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C143" s="34" t="n">
         <f aca="false">IF($B143="","",INDEX(Schedule!$G$4:$G$483,MATCH(7003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46281</v>
+        <v>46280</v>
       </c>
       <c r="D143" s="35" t="str">
         <f aca="false">IF($B143="","",INDEX(Schedule!$D$4:$D$483,MATCH(7003,Schedule!$K$4:$K$483,0)))</f>
@@ -6111,20 +6115,20 @@
       </c>
       <c r="E143" s="36" t="n">
         <f aca="false">IF($B143="","",INDEX(Schedule!$E$4:$E$483,MATCH(7003,Schedule!$K$4:$K$483,0)))</f>
-        <v>171.1</v>
+        <v>350</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="36" t="n">
         <f aca="false">IF($B143="","",IF($F143&lt;&gt;"",$F143,$E143))</f>
-        <v>171.1</v>
+        <v>350</v>
       </c>
       <c r="H143" s="36" t="n">
         <f aca="false">IF($B143="",0,IF($D143="Income",$G143,-$G143))</f>
-        <v>-171.1</v>
+        <v>-350</v>
       </c>
       <c r="I143" s="37" t="n">
         <f aca="false">IF($B143="","",$I$139+SUM($H$141:$H143))</f>
-        <v>3154.71</v>
+        <v>3235.81</v>
       </c>
       <c r="J143" s="38" t="str">
         <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6134,7 +6138,7 @@
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C144" s="34" t="n">
         <f aca="false">IF($B144="","",INDEX(Schedule!$G$4:$G$483,MATCH(7004,Schedule!$K$4:$K$483,0)))</f>
@@ -6142,24 +6146,24 @@
       </c>
       <c r="D144" s="35" t="str">
         <f aca="false">IF($B144="","",INDEX(Schedule!$D$4:$D$483,MATCH(7004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E144" s="36" t="n">
         <f aca="false">IF($B144="","",INDEX(Schedule!$E$4:$E$483,MATCH(7004,Schedule!$K$4:$K$483,0)))</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F144" s="16"/>
       <c r="G144" s="36" t="n">
         <f aca="false">IF($B144="","",IF($F144&lt;&gt;"",$F144,$E144))</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H144" s="36" t="n">
         <f aca="false">IF($B144="",0,IF($D144="Income",$G144,-$G144))</f>
-        <v>-45</v>
+        <v>90</v>
       </c>
       <c r="I144" s="37" t="n">
         <f aca="false">IF($B144="","",$I$139+SUM($H$141:$H144))</f>
-        <v>3109.71</v>
+        <v>3325.81</v>
       </c>
       <c r="J144" s="38" t="str">
         <f aca="true">IF($B144="","",IF($F144&lt;&gt;"","PAID",IF($C144&lt;TODAY(),"PAST DUE",IF($C144&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6169,32 +6173,32 @@
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Spectrum</v>
       </c>
       <c r="C145" s="34" t="n">
         <f aca="false">IF($B145="","",INDEX(Schedule!$G$4:$G$483,MATCH(7005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="D145" s="35" t="str">
         <f aca="false">IF($B145="","",INDEX(Schedule!$D$4:$D$483,MATCH(7005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E145" s="36" t="n">
         <f aca="false">IF($B145="","",INDEX(Schedule!$E$4:$E$483,MATCH(7005,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>171.1</v>
       </c>
       <c r="F145" s="16"/>
       <c r="G145" s="36" t="n">
         <f aca="false">IF($B145="","",IF($F145&lt;&gt;"",$F145,$E145))</f>
-        <v>790</v>
+        <v>171.1</v>
       </c>
       <c r="H145" s="36" t="n">
         <f aca="false">IF($B145="",0,IF($D145="Income",$G145,-$G145))</f>
-        <v>790</v>
+        <v>-171.1</v>
       </c>
       <c r="I145" s="37" t="n">
         <f aca="false">IF($B145="","",$I$139+SUM($H$141:$H145))</f>
-        <v>3899.71</v>
+        <v>3154.71</v>
       </c>
       <c r="J145" s="38" t="str">
         <f aca="true">IF($B145="","",IF($F145&lt;&gt;"","PAID",IF($C145&lt;TODAY(),"PAST DUE",IF($C145&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6204,11 +6208,11 @@
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Metal Copy</v>
+        <v>Maine Revenue Services</v>
       </c>
       <c r="C146" s="34" t="n">
         <f aca="false">IF($B146="","",INDEX(Schedule!$G$4:$G$483,MATCH(7006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="D146" s="35" t="str">
         <f aca="false">IF($B146="","",INDEX(Schedule!$D$4:$D$483,MATCH(7006,Schedule!$K$4:$K$483,0)))</f>
@@ -6216,20 +6220,20 @@
       </c>
       <c r="E146" s="36" t="n">
         <f aca="false">IF($B146="","",INDEX(Schedule!$E$4:$E$483,MATCH(7006,Schedule!$K$4:$K$483,0)))</f>
-        <v>16.99</v>
+        <v>45</v>
       </c>
       <c r="F146" s="16"/>
       <c r="G146" s="36" t="n">
         <f aca="false">IF($B146="","",IF($F146&lt;&gt;"",$F146,$E146))</f>
-        <v>16.99</v>
+        <v>45</v>
       </c>
       <c r="H146" s="36" t="n">
         <f aca="false">IF($B146="",0,IF($D146="Income",$G146,-$G146))</f>
-        <v>-16.99</v>
+        <v>-45</v>
       </c>
       <c r="I146" s="37" t="n">
         <f aca="false">IF($B146="","",$I$139+SUM($H$141:$H146))</f>
-        <v>3882.72</v>
+        <v>3109.71</v>
       </c>
       <c r="J146" s="38" t="str">
         <f aca="true">IF($B146="","",IF($F146&lt;&gt;"","PAID",IF($C146&lt;TODAY(),"PAST DUE",IF($C146&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6535,7 +6539,7 @@
       <c r="D158" s="42"/>
       <c r="E158" s="43" t="n">
         <f aca="false">SUM($E$141:$E$157)</f>
-        <v>1463.09</v>
+        <v>1449.09</v>
       </c>
       <c r="F158" s="43" t="n">
         <f aca="false">SUM($F$141:$F$150)</f>
@@ -6543,15 +6547,15 @@
       </c>
       <c r="G158" s="43" t="n">
         <f aca="false">SUM($G$141:$G$157)</f>
-        <v>1463.09</v>
+        <v>1449.09</v>
       </c>
       <c r="H158" s="43" t="n">
         <f aca="false">SUM($H$141:$H$157)</f>
-        <v>296.91</v>
+        <v>310.91</v>
       </c>
       <c r="I158" s="44" t="n">
         <f aca="false">$I$139+SUM($H$141:$H$157)</f>
-        <v>3882.72</v>
+        <v>3109.71</v>
       </c>
       <c r="J158" s="45" t="str">
         <f aca="false">IF($I$158&lt;0,"SHORTFALL",IF($I$158&lt;$E$7,"TIGHT","OK"))</f>
@@ -6559,28 +6563,28 @@
       </c>
       <c r="K158" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$141:$D$157,"Income",$G$141:$G$157),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$141:$D$157,"Expense",$G$141:$G$157),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$158,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $583.09   =  net $296.91</v>
+        <v>Income $880.00   less expenses $569.09   =  net $310.91</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B160" s="28" t="str">
+      <c r="B160" s="29" t="str">
         <f aca="false">"WEEK 8     "&amp;TEXT($E$6+49,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+49+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 8     Mon, Sep 21   through   Sun, Sep 27, 2026</v>
-      </c>
-      <c r="C160" s="29"/>
-      <c r="D160" s="29"/>
-      <c r="E160" s="29"/>
-      <c r="F160" s="29"/>
-      <c r="G160" s="30" t="s">
+        <v>WEEK 8     Fri, Sep 18   through   Thu, Sep 24, 2026</v>
+      </c>
+      <c r="C160" s="30"/>
+      <c r="D160" s="30"/>
+      <c r="E160" s="30"/>
+      <c r="F160" s="30"/>
+      <c r="G160" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H160" s="29"/>
-      <c r="I160" s="31" t="n">
+      <c r="H160" s="30"/>
+      <c r="I160" s="32" t="n">
         <f aca="false">$I$158</f>
-        <v>3882.72</v>
-      </c>
-      <c r="J160" s="29"/>
-      <c r="K160" s="32" t="str">
+        <v>3109.71</v>
+      </c>
+      <c r="J160" s="30"/>
+      <c r="K160" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,8)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,8)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -6617,11 +6621,11 @@
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B162" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C162" s="34" t="n">
         <f aca="false">IF($B162="","",INDEX(Schedule!$G$4:$G$483,MATCH(8001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46288</v>
+        <v>46283</v>
       </c>
       <c r="D162" s="35" t="str">
         <f aca="false">IF($B162="","",INDEX(Schedule!$D$4:$D$483,MATCH(8001,Schedule!$K$4:$K$483,0)))</f>
@@ -6629,20 +6633,20 @@
       </c>
       <c r="E162" s="36" t="n">
         <f aca="false">IF($B162="","",INDEX(Schedule!$E$4:$E$483,MATCH(8001,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="F162" s="16"/>
       <c r="G162" s="36" t="n">
         <f aca="false">IF($B162="","",IF($F162&lt;&gt;"",$F162,$E162))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="H162" s="36" t="n">
         <f aca="false">IF($B162="",0,IF($D162="Income",$G162,-$G162))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="I162" s="37" t="n">
         <f aca="false">IF($B162="","",$I$160+SUM($H$162:$H162))</f>
-        <v>3972.72</v>
+        <v>3899.71</v>
       </c>
       <c r="J162" s="38" t="str">
         <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6652,32 +6656,32 @@
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Metal Copy</v>
       </c>
       <c r="C163" s="34" t="n">
         <f aca="false">IF($B163="","",INDEX(Schedule!$G$4:$G$483,MATCH(8002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46290</v>
+        <v>46283</v>
       </c>
       <c r="D163" s="35" t="str">
         <f aca="false">IF($B163="","",INDEX(Schedule!$D$4:$D$483,MATCH(8002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E163" s="36" t="n">
         <f aca="false">IF($B163="","",INDEX(Schedule!$E$4:$E$483,MATCH(8002,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>16.99</v>
       </c>
       <c r="F163" s="16"/>
       <c r="G163" s="36" t="n">
         <f aca="false">IF($B163="","",IF($F163&lt;&gt;"",$F163,$E163))</f>
-        <v>790</v>
+        <v>16.99</v>
       </c>
       <c r="H163" s="36" t="n">
         <f aca="false">IF($B163="",0,IF($D163="Income",$G163,-$G163))</f>
-        <v>790</v>
+        <v>-16.99</v>
       </c>
       <c r="I163" s="37" t="n">
         <f aca="false">IF($B163="","",$I$160+SUM($H$162:$H163))</f>
-        <v>4762.72</v>
+        <v>3882.72</v>
       </c>
       <c r="J163" s="38" t="str">
         <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6687,32 +6691,32 @@
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Microsoft</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C164" s="34" t="n">
         <f aca="false">IF($B164="","",INDEX(Schedule!$G$4:$G$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46290</v>
+        <v>46288</v>
       </c>
       <c r="D164" s="35" t="str">
         <f aca="false">IF($B164="","",INDEX(Schedule!$D$4:$D$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E164" s="36" t="n">
         <f aca="false">IF($B164="","",INDEX(Schedule!$E$4:$E$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
-        <v>13.7</v>
+        <v>90</v>
       </c>
       <c r="F164" s="16"/>
       <c r="G164" s="36" t="n">
         <f aca="false">IF($B164="","",IF($F164&lt;&gt;"",$F164,$E164))</f>
-        <v>13.7</v>
+        <v>90</v>
       </c>
       <c r="H164" s="36" t="n">
         <f aca="false">IF($B164="",0,IF($D164="Income",$G164,-$G164))</f>
-        <v>-13.7</v>
+        <v>90</v>
       </c>
       <c r="I164" s="37" t="n">
         <f aca="false">IF($B164="","",$I$160+SUM($H$162:$H164))</f>
-        <v>4749.02</v>
+        <v>3972.72</v>
       </c>
       <c r="J164" s="38" t="str">
         <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6722,36 +6726,36 @@
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
-      </c>
-      <c r="C165" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C165" s="34" t="str">
         <f aca="false">IF($B165="","",INDEX(Schedule!$G$4:$G$483,MATCH(8004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46290</v>
+        <v/>
       </c>
       <c r="D165" s="35" t="str">
         <f aca="false">IF($B165="","",INDEX(Schedule!$D$4:$D$483,MATCH(8004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E165" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E165" s="36" t="str">
         <f aca="false">IF($B165="","",INDEX(Schedule!$E$4:$E$483,MATCH(8004,Schedule!$K$4:$K$483,0)))</f>
-        <v>43.87</v>
+        <v/>
       </c>
       <c r="F165" s="16"/>
-      <c r="G165" s="36" t="n">
+      <c r="G165" s="36" t="str">
         <f aca="false">IF($B165="","",IF($F165&lt;&gt;"",$F165,$E165))</f>
-        <v>43.87</v>
+        <v/>
       </c>
       <c r="H165" s="36" t="n">
         <f aca="false">IF($B165="",0,IF($D165="Income",$G165,-$G165))</f>
-        <v>-43.87</v>
-      </c>
-      <c r="I165" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="37" t="str">
         <f aca="false">IF($B165="","",$I$160+SUM($H$162:$H165))</f>
-        <v>4705.15</v>
+        <v/>
       </c>
       <c r="J165" s="38" t="str">
         <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7123,7 +7127,7 @@
       <c r="D179" s="42"/>
       <c r="E179" s="43" t="n">
         <f aca="false">SUM($E$162:$E$178)</f>
-        <v>937.57</v>
+        <v>896.99</v>
       </c>
       <c r="F179" s="43" t="n">
         <f aca="false">SUM($F$162:$F$171)</f>
@@ -7131,15 +7135,15 @@
       </c>
       <c r="G179" s="43" t="n">
         <f aca="false">SUM($G$162:$G$178)</f>
-        <v>937.57</v>
+        <v>896.99</v>
       </c>
       <c r="H179" s="43" t="n">
         <f aca="false">SUM($H$162:$H$178)</f>
-        <v>822.43</v>
+        <v>863.01</v>
       </c>
       <c r="I179" s="44" t="n">
         <f aca="false">$I$160+SUM($H$162:$H$178)</f>
-        <v>4705.15</v>
+        <v>3972.72</v>
       </c>
       <c r="J179" s="45" t="str">
         <f aca="false">IF($I$179&lt;0,"SHORTFALL",IF($I$179&lt;$E$7,"TIGHT","OK"))</f>
@@ -7147,28 +7151,28 @@
       </c>
       <c r="K179" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$162:$D$178,"Income",$G$162:$G$178),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$162:$D$178,"Expense",$G$162:$G$178),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$179,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
+        <v>Income $880.00   less expenses $16.99   =  net $863.01</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B181" s="28" t="str">
+      <c r="B181" s="29" t="str">
         <f aca="false">"WEEK 9     "&amp;TEXT($E$6+56,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+56+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 9     Mon, Sep 28   through   Sun, Oct 4, 2026</v>
-      </c>
-      <c r="C181" s="29"/>
-      <c r="D181" s="29"/>
-      <c r="E181" s="29"/>
-      <c r="F181" s="29"/>
-      <c r="G181" s="30" t="s">
+        <v>WEEK 9     Fri, Sep 25   through   Thu, Oct 1, 2026</v>
+      </c>
+      <c r="C181" s="30"/>
+      <c r="D181" s="30"/>
+      <c r="E181" s="30"/>
+      <c r="F181" s="30"/>
+      <c r="G181" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H181" s="29"/>
-      <c r="I181" s="31" t="n">
+      <c r="H181" s="30"/>
+      <c r="I181" s="32" t="n">
         <f aca="false">$I$179</f>
-        <v>4705.15</v>
-      </c>
-      <c r="J181" s="29"/>
-      <c r="K181" s="32" t="str">
+        <v>3972.72</v>
+      </c>
+      <c r="J181" s="30"/>
+      <c r="K181" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,9)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,9)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -7205,11 +7209,11 @@
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B183" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C183" s="34" t="n">
         <f aca="false">IF($B183="","",INDEX(Schedule!$G$4:$G$483,MATCH(9001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="D183" s="35" t="str">
         <f aca="false">IF($B183="","",INDEX(Schedule!$D$4:$D$483,MATCH(9001,Schedule!$K$4:$K$483,0)))</f>
@@ -7217,20 +7221,20 @@
       </c>
       <c r="E183" s="36" t="n">
         <f aca="false">IF($B183="","",INDEX(Schedule!$E$4:$E$483,MATCH(9001,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="F183" s="16"/>
       <c r="G183" s="36" t="n">
         <f aca="false">IF($B183="","",IF($F183&lt;&gt;"",$F183,$E183))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="H183" s="36" t="n">
         <f aca="false">IF($B183="",0,IF($D183="Income",$G183,-$G183))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="I183" s="37" t="n">
         <f aca="false">IF($B183="","",$I$181+SUM($H$183:$H183))</f>
-        <v>4795.15</v>
+        <v>4762.72</v>
       </c>
       <c r="J183" s="38" t="str">
         <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7240,11 +7244,11 @@
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B184" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Microsoft</v>
       </c>
       <c r="C184" s="34" t="n">
         <f aca="false">IF($B184="","",INDEX(Schedule!$G$4:$G$483,MATCH(9002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="D184" s="35" t="str">
         <f aca="false">IF($B184="","",INDEX(Schedule!$D$4:$D$483,MATCH(9002,Schedule!$K$4:$K$483,0)))</f>
@@ -7252,20 +7256,20 @@
       </c>
       <c r="E184" s="36" t="n">
         <f aca="false">IF($B184="","",INDEX(Schedule!$E$4:$E$483,MATCH(9002,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>13.7</v>
       </c>
       <c r="F184" s="16"/>
       <c r="G184" s="36" t="n">
         <f aca="false">IF($B184="","",IF($F184&lt;&gt;"",$F184,$E184))</f>
-        <v>350</v>
+        <v>13.7</v>
       </c>
       <c r="H184" s="36" t="n">
         <f aca="false">IF($B184="",0,IF($D184="Income",$G184,-$G184))</f>
-        <v>-350</v>
+        <v>-13.7</v>
       </c>
       <c r="I184" s="37" t="n">
         <f aca="false">IF($B184="","",$I$181+SUM($H$183:$H184))</f>
-        <v>4445.15</v>
+        <v>4749.02</v>
       </c>
       <c r="J184" s="38" t="str">
         <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7275,11 +7279,11 @@
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B185" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services (2)</v>
+        <v>Central Maine Power: Property</v>
       </c>
       <c r="C185" s="34" t="n">
         <f aca="false">IF($B185="","",INDEX(Schedule!$G$4:$G$483,MATCH(9003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="D185" s="35" t="str">
         <f aca="false">IF($B185="","",INDEX(Schedule!$D$4:$D$483,MATCH(9003,Schedule!$K$4:$K$483,0)))</f>
@@ -7287,20 +7291,20 @@
       </c>
       <c r="E185" s="36" t="n">
         <f aca="false">IF($B185="","",INDEX(Schedule!$E$4:$E$483,MATCH(9003,Schedule!$K$4:$K$483,0)))</f>
-        <v>150</v>
+        <v>43.87</v>
       </c>
       <c r="F185" s="16"/>
       <c r="G185" s="36" t="n">
         <f aca="false">IF($B185="","",IF($F185&lt;&gt;"",$F185,$E185))</f>
-        <v>150</v>
+        <v>43.87</v>
       </c>
       <c r="H185" s="36" t="n">
         <f aca="false">IF($B185="",0,IF($D185="Income",$G185,-$G185))</f>
-        <v>-150</v>
+        <v>-43.87</v>
       </c>
       <c r="I185" s="37" t="n">
         <f aca="false">IF($B185="","",$I$181+SUM($H$183:$H185))</f>
-        <v>4295.15</v>
+        <v>4705.15</v>
       </c>
       <c r="J185" s="38" t="str">
         <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7310,7 +7314,7 @@
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B186" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Progressive Insurance</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C186" s="34" t="n">
         <f aca="false">IF($B186="","",INDEX(Schedule!$G$4:$G$483,MATCH(9004,Schedule!$K$4:$K$483,0)))</f>
@@ -7318,24 +7322,24 @@
       </c>
       <c r="D186" s="35" t="str">
         <f aca="false">IF($B186="","",INDEX(Schedule!$D$4:$D$483,MATCH(9004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E186" s="36" t="n">
         <f aca="false">IF($B186="","",INDEX(Schedule!$E$4:$E$483,MATCH(9004,Schedule!$K$4:$K$483,0)))</f>
-        <v>143.37</v>
+        <v>90</v>
       </c>
       <c r="F186" s="16"/>
       <c r="G186" s="36" t="n">
         <f aca="false">IF($B186="","",IF($F186&lt;&gt;"",$F186,$E186))</f>
-        <v>143.37</v>
+        <v>90</v>
       </c>
       <c r="H186" s="36" t="n">
         <f aca="false">IF($B186="",0,IF($D186="Income",$G186,-$G186))</f>
-        <v>-143.37</v>
+        <v>90</v>
       </c>
       <c r="I186" s="37" t="n">
         <f aca="false">IF($B186="","",$I$181+SUM($H$183:$H186))</f>
-        <v>4151.78</v>
+        <v>4795.15</v>
       </c>
       <c r="J186" s="38" t="str">
         <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7345,32 +7349,32 @@
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B187" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C187" s="34" t="n">
         <f aca="false">IF($B187="","",INDEX(Schedule!$G$4:$G$483,MATCH(9005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="D187" s="35" t="str">
         <f aca="false">IF($B187="","",INDEX(Schedule!$D$4:$D$483,MATCH(9005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E187" s="36" t="n">
         <f aca="false">IF($B187="","",INDEX(Schedule!$E$4:$E$483,MATCH(9005,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>350</v>
       </c>
       <c r="F187" s="16"/>
       <c r="G187" s="36" t="n">
         <f aca="false">IF($B187="","",IF($F187&lt;&gt;"",$F187,$E187))</f>
-        <v>790</v>
+        <v>350</v>
       </c>
       <c r="H187" s="36" t="n">
         <f aca="false">IF($B187="",0,IF($D187="Income",$G187,-$G187))</f>
-        <v>790</v>
+        <v>-350</v>
       </c>
       <c r="I187" s="37" t="n">
         <f aca="false">IF($B187="","",$I$181+SUM($H$183:$H187))</f>
-        <v>4941.78</v>
+        <v>4445.15</v>
       </c>
       <c r="J187" s="38" t="str">
         <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7380,11 +7384,11 @@
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B188" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: Claude</v>
+        <v>Maine Revenue Services (2)</v>
       </c>
       <c r="C188" s="34" t="n">
         <f aca="false">IF($B188="","",INDEX(Schedule!$G$4:$G$483,MATCH(9006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46299</v>
+        <v>46295</v>
       </c>
       <c r="D188" s="35" t="str">
         <f aca="false">IF($B188="","",INDEX(Schedule!$D$4:$D$483,MATCH(9006,Schedule!$K$4:$K$483,0)))</f>
@@ -7392,20 +7396,20 @@
       </c>
       <c r="E188" s="36" t="n">
         <f aca="false">IF($B188="","",INDEX(Schedule!$E$4:$E$483,MATCH(9006,Schedule!$K$4:$K$483,0)))</f>
-        <v>21.1</v>
+        <v>150</v>
       </c>
       <c r="F188" s="16"/>
       <c r="G188" s="36" t="n">
         <f aca="false">IF($B188="","",IF($F188&lt;&gt;"",$F188,$E188))</f>
-        <v>21.1</v>
+        <v>150</v>
       </c>
       <c r="H188" s="36" t="n">
         <f aca="false">IF($B188="",0,IF($D188="Income",$G188,-$G188))</f>
-        <v>-21.1</v>
+        <v>-150</v>
       </c>
       <c r="I188" s="37" t="n">
         <f aca="false">IF($B188="","",$I$181+SUM($H$183:$H188))</f>
-        <v>4920.68</v>
+        <v>4295.15</v>
       </c>
       <c r="J188" s="38" t="str">
         <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7415,36 +7419,36 @@
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B189" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C189" s="34" t="str">
+        <v>Progressive Insurance</v>
+      </c>
+      <c r="C189" s="34" t="n">
         <f aca="false">IF($B189="","",INDEX(Schedule!$G$4:$G$483,MATCH(9007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46295</v>
       </c>
       <c r="D189" s="35" t="str">
         <f aca="false">IF($B189="","",INDEX(Schedule!$D$4:$D$483,MATCH(9007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E189" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E189" s="36" t="n">
         <f aca="false">IF($B189="","",INDEX(Schedule!$E$4:$E$483,MATCH(9007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>143.37</v>
       </c>
       <c r="F189" s="16"/>
-      <c r="G189" s="36" t="str">
+      <c r="G189" s="36" t="n">
         <f aca="false">IF($B189="","",IF($F189&lt;&gt;"",$F189,$E189))</f>
-        <v/>
+        <v>143.37</v>
       </c>
       <c r="H189" s="36" t="n">
         <f aca="false">IF($B189="",0,IF($D189="Income",$G189,-$G189))</f>
-        <v>0</v>
-      </c>
-      <c r="I189" s="37" t="str">
+        <v>-143.37</v>
+      </c>
+      <c r="I189" s="37" t="n">
         <f aca="false">IF($B189="","",$I$181+SUM($H$183:$H189))</f>
-        <v/>
+        <v>4151.78</v>
       </c>
       <c r="J189" s="38" t="str">
         <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7711,7 +7715,7 @@
       <c r="D200" s="42"/>
       <c r="E200" s="43" t="n">
         <f aca="false">SUM($E$183:$E$199)</f>
-        <v>1544.47</v>
+        <v>1580.94</v>
       </c>
       <c r="F200" s="43" t="n">
         <f aca="false">SUM($F$183:$F$192)</f>
@@ -7719,15 +7723,15 @@
       </c>
       <c r="G200" s="43" t="n">
         <f aca="false">SUM($G$183:$G$199)</f>
-        <v>1544.47</v>
+        <v>1580.94</v>
       </c>
       <c r="H200" s="43" t="n">
         <f aca="false">SUM($H$183:$H$199)</f>
-        <v>215.53</v>
+        <v>179.06</v>
       </c>
       <c r="I200" s="44" t="n">
         <f aca="false">$I$181+SUM($H$183:$H$199)</f>
-        <v>4920.68</v>
+        <v>4151.78</v>
       </c>
       <c r="J200" s="45" t="str">
         <f aca="false">IF($I$200&lt;0,"SHORTFALL",IF($I$200&lt;$E$7,"TIGHT","OK"))</f>
@@ -7735,28 +7739,28 @@
       </c>
       <c r="K200" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$183:$D$199,"Income",$G$183:$G$199),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$183:$D$199,"Expense",$G$183:$G$199),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$200,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $664.47   =  net $215.53</v>
+        <v>Income $880.00   less expenses $700.94   =  net $179.06</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B202" s="28" t="str">
+      <c r="B202" s="29" t="str">
         <f aca="false">"WEEK 10     "&amp;TEXT($E$6+63,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+63+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 10     Mon, Oct 5   through   Sun, Oct 11, 2026</v>
-      </c>
-      <c r="C202" s="29"/>
-      <c r="D202" s="29"/>
-      <c r="E202" s="29"/>
-      <c r="F202" s="29"/>
-      <c r="G202" s="30" t="s">
+        <v>WEEK 10     Fri, Oct 2   through   Thu, Oct 8, 2026</v>
+      </c>
+      <c r="C202" s="30"/>
+      <c r="D202" s="30"/>
+      <c r="E202" s="30"/>
+      <c r="F202" s="30"/>
+      <c r="G202" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H202" s="29"/>
-      <c r="I202" s="31" t="n">
+      <c r="H202" s="30"/>
+      <c r="I202" s="32" t="n">
         <f aca="false">$I$200</f>
-        <v>4920.68</v>
-      </c>
-      <c r="J202" s="29"/>
-      <c r="K202" s="32" t="str">
+        <v>4151.78</v>
+      </c>
+      <c r="J202" s="30"/>
+      <c r="K202" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,10)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,10)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -7793,32 +7797,32 @@
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B204" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>OpenAI</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C204" s="34" t="n">
         <f aca="false">IF($B204="","",INDEX(Schedule!$G$4:$G$483,MATCH(10001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="D204" s="35" t="str">
         <f aca="false">IF($B204="","",INDEX(Schedule!$D$4:$D$483,MATCH(10001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E204" s="36" t="n">
         <f aca="false">IF($B204="","",INDEX(Schedule!$E$4:$E$483,MATCH(10001,Schedule!$K$4:$K$483,0)))</f>
-        <v>20</v>
+        <v>790</v>
       </c>
       <c r="F204" s="16"/>
       <c r="G204" s="36" t="n">
         <f aca="false">IF($B204="","",IF($F204&lt;&gt;"",$F204,$E204))</f>
-        <v>20</v>
+        <v>790</v>
       </c>
       <c r="H204" s="36" t="n">
         <f aca="false">IF($B204="",0,IF($D204="Income",$G204,-$G204))</f>
-        <v>-20</v>
+        <v>790</v>
       </c>
       <c r="I204" s="37" t="n">
         <f aca="false">IF($B204="","",$I$202+SUM($H$204:$H204))</f>
-        <v>4900.68</v>
+        <v>4941.78</v>
       </c>
       <c r="J204" s="38" t="str">
         <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7828,11 +7832,11 @@
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B205" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Obsidian</v>
+        <v>Apple: Claude</v>
       </c>
       <c r="C205" s="34" t="n">
         <f aca="false">IF($B205="","",INDEX(Schedule!$G$4:$G$483,MATCH(10002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46300</v>
+        <v>46299</v>
       </c>
       <c r="D205" s="35" t="str">
         <f aca="false">IF($B205="","",INDEX(Schedule!$D$4:$D$483,MATCH(10002,Schedule!$K$4:$K$483,0)))</f>
@@ -7840,20 +7844,20 @@
       </c>
       <c r="E205" s="36" t="n">
         <f aca="false">IF($B205="","",INDEX(Schedule!$E$4:$E$483,MATCH(10002,Schedule!$K$4:$K$483,0)))</f>
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="F205" s="16"/>
       <c r="G205" s="36" t="n">
         <f aca="false">IF($B205="","",IF($F205&lt;&gt;"",$F205,$E205))</f>
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="H205" s="36" t="n">
         <f aca="false">IF($B205="",0,IF($D205="Income",$G205,-$G205))</f>
-        <v>-10</v>
+        <v>-21.1</v>
       </c>
       <c r="I205" s="37" t="n">
         <f aca="false">IF($B205="","",$I$202+SUM($H$204:$H205))</f>
-        <v>4890.68</v>
+        <v>4920.68</v>
       </c>
       <c r="J205" s="38" t="str">
         <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7863,32 +7867,32 @@
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B206" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>OpenAI</v>
       </c>
       <c r="C206" s="34" t="n">
         <f aca="false">IF($B206="","",INDEX(Schedule!$G$4:$G$483,MATCH(10003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="D206" s="35" t="str">
         <f aca="false">IF($B206="","",INDEX(Schedule!$D$4:$D$483,MATCH(10003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E206" s="36" t="n">
         <f aca="false">IF($B206="","",INDEX(Schedule!$E$4:$E$483,MATCH(10003,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="F206" s="16"/>
       <c r="G206" s="36" t="n">
         <f aca="false">IF($B206="","",IF($F206&lt;&gt;"",$F206,$E206))</f>
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="H206" s="36" t="n">
         <f aca="false">IF($B206="",0,IF($D206="Income",$G206,-$G206))</f>
-        <v>90</v>
+        <v>-20</v>
       </c>
       <c r="I206" s="37" t="n">
         <f aca="false">IF($B206="","",$I$202+SUM($H$204:$H206))</f>
-        <v>4980.68</v>
+        <v>4900.68</v>
       </c>
       <c r="J206" s="38" t="str">
         <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7898,11 +7902,11 @@
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B207" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
+        <v>Obsidian</v>
       </c>
       <c r="C207" s="34" t="n">
         <f aca="false">IF($B207="","",INDEX(Schedule!$G$4:$G$483,MATCH(10004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46302</v>
+        <v>46300</v>
       </c>
       <c r="D207" s="35" t="str">
         <f aca="false">IF($B207="","",INDEX(Schedule!$D$4:$D$483,MATCH(10004,Schedule!$K$4:$K$483,0)))</f>
@@ -7910,20 +7914,20 @@
       </c>
       <c r="E207" s="36" t="n">
         <f aca="false">IF($B207="","",INDEX(Schedule!$E$4:$E$483,MATCH(10004,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v>10</v>
       </c>
       <c r="F207" s="16"/>
       <c r="G207" s="36" t="n">
         <f aca="false">IF($B207="","",IF($F207&lt;&gt;"",$F207,$E207))</f>
-        <v>4.99</v>
+        <v>10</v>
       </c>
       <c r="H207" s="36" t="n">
         <f aca="false">IF($B207="",0,IF($D207="Income",$G207,-$G207))</f>
-        <v>-4.99</v>
+        <v>-10</v>
       </c>
       <c r="I207" s="37" t="n">
         <f aca="false">IF($B207="","",$I$202+SUM($H$204:$H207))</f>
-        <v>4975.69</v>
+        <v>4890.68</v>
       </c>
       <c r="J207" s="38" t="str">
         <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7933,7 +7937,7 @@
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B208" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C208" s="34" t="n">
         <f aca="false">IF($B208="","",INDEX(Schedule!$G$4:$G$483,MATCH(10005,Schedule!$K$4:$K$483,0)))</f>
@@ -7941,24 +7945,24 @@
       </c>
       <c r="D208" s="35" t="str">
         <f aca="false">IF($B208="","",INDEX(Schedule!$D$4:$D$483,MATCH(10005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E208" s="36" t="n">
         <f aca="false">IF($B208="","",INDEX(Schedule!$E$4:$E$483,MATCH(10005,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="F208" s="16"/>
       <c r="G208" s="36" t="n">
         <f aca="false">IF($B208="","",IF($F208&lt;&gt;"",$F208,$E208))</f>
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="H208" s="36" t="n">
         <f aca="false">IF($B208="",0,IF($D208="Income",$G208,-$G208))</f>
-        <v>-500</v>
+        <v>90</v>
       </c>
       <c r="I208" s="37" t="n">
         <f aca="false">IF($B208="","",$I$202+SUM($H$204:$H208))</f>
-        <v>4475.69</v>
+        <v>4980.68</v>
       </c>
       <c r="J208" s="38" t="str">
         <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7968,32 +7972,32 @@
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B209" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Google One</v>
       </c>
       <c r="C209" s="34" t="n">
         <f aca="false">IF($B209="","",INDEX(Schedule!$G$4:$G$483,MATCH(10006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="D209" s="35" t="str">
         <f aca="false">IF($B209="","",INDEX(Schedule!$D$4:$D$483,MATCH(10006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E209" s="36" t="n">
         <f aca="false">IF($B209="","",INDEX(Schedule!$E$4:$E$483,MATCH(10006,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>4.99</v>
       </c>
       <c r="F209" s="16"/>
       <c r="G209" s="36" t="n">
         <f aca="false">IF($B209="","",IF($F209&lt;&gt;"",$F209,$E209))</f>
-        <v>790</v>
+        <v>4.99</v>
       </c>
       <c r="H209" s="36" t="n">
         <f aca="false">IF($B209="",0,IF($D209="Income",$G209,-$G209))</f>
-        <v>790</v>
+        <v>-4.99</v>
       </c>
       <c r="I209" s="37" t="n">
         <f aca="false">IF($B209="","",$I$202+SUM($H$204:$H209))</f>
-        <v>5265.69</v>
+        <v>4975.69</v>
       </c>
       <c r="J209" s="38" t="str">
         <f aca="true">IF($B209="","",IF($F209&lt;&gt;"","PAID",IF($C209&lt;TODAY(),"PAST DUE",IF($C209&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8003,11 +8007,11 @@
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B210" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Upstart (loan)</v>
       </c>
       <c r="C210" s="34" t="n">
         <f aca="false">IF($B210="","",INDEX(Schedule!$G$4:$G$483,MATCH(10007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46305</v>
+        <v>46302</v>
       </c>
       <c r="D210" s="35" t="str">
         <f aca="false">IF($B210="","",INDEX(Schedule!$D$4:$D$483,MATCH(10007,Schedule!$K$4:$K$483,0)))</f>
@@ -8015,20 +8019,20 @@
       </c>
       <c r="E210" s="36" t="n">
         <f aca="false">IF($B210="","",INDEX(Schedule!$E$4:$E$483,MATCH(10007,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>500</v>
       </c>
       <c r="F210" s="16"/>
       <c r="G210" s="36" t="n">
         <f aca="false">IF($B210="","",IF($F210&lt;&gt;"",$F210,$E210))</f>
-        <v>163.5</v>
+        <v>500</v>
       </c>
       <c r="H210" s="36" t="n">
         <f aca="false">IF($B210="",0,IF($D210="Income",$G210,-$G210))</f>
-        <v>-163.5</v>
+        <v>-500</v>
       </c>
       <c r="I210" s="37" t="n">
         <f aca="false">IF($B210="","",$I$202+SUM($H$204:$H210))</f>
-        <v>5102.19</v>
+        <v>4475.69</v>
       </c>
       <c r="J210" s="38" t="str">
         <f aca="true">IF($B210="","",IF($F210&lt;&gt;"","PAID",IF($C210&lt;TODAY(),"PAST DUE",IF($C210&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8299,7 +8303,7 @@
       <c r="D221" s="42"/>
       <c r="E221" s="43" t="n">
         <f aca="false">SUM($E$204:$E$220)</f>
-        <v>1578.49</v>
+        <v>1436.09</v>
       </c>
       <c r="F221" s="43" t="n">
         <f aca="false">SUM($F$204:$F$213)</f>
@@ -8307,15 +8311,15 @@
       </c>
       <c r="G221" s="43" t="n">
         <f aca="false">SUM($G$204:$G$220)</f>
-        <v>1578.49</v>
+        <v>1436.09</v>
       </c>
       <c r="H221" s="43" t="n">
         <f aca="false">SUM($H$204:$H$220)</f>
-        <v>181.51</v>
+        <v>323.91</v>
       </c>
       <c r="I221" s="44" t="n">
         <f aca="false">$I$202+SUM($H$204:$H$220)</f>
-        <v>5102.19</v>
+        <v>4475.69</v>
       </c>
       <c r="J221" s="45" t="str">
         <f aca="false">IF($I$221&lt;0,"SHORTFALL",IF($I$221&lt;$E$7,"TIGHT","OK"))</f>
@@ -8323,28 +8327,28 @@
       </c>
       <c r="K221" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$204:$D$220,"Income",$G$204:$G$220),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$204:$D$220,"Expense",$G$204:$G$220),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$221,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $698.49   =  net $181.51</v>
+        <v>Income $880.00   less expenses $556.09   =  net $323.91</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B223" s="28" t="str">
+      <c r="B223" s="29" t="str">
         <f aca="false">"WEEK 11     "&amp;TEXT($E$6+70,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+70+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 11     Mon, Oct 12   through   Sun, Oct 18, 2026</v>
-      </c>
-      <c r="C223" s="29"/>
-      <c r="D223" s="29"/>
-      <c r="E223" s="29"/>
-      <c r="F223" s="29"/>
-      <c r="G223" s="30" t="s">
+        <v>WEEK 11     Fri, Oct 9   through   Thu, Oct 15, 2026</v>
+      </c>
+      <c r="C223" s="30"/>
+      <c r="D223" s="30"/>
+      <c r="E223" s="30"/>
+      <c r="F223" s="30"/>
+      <c r="G223" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H223" s="29"/>
-      <c r="I223" s="31" t="n">
+      <c r="H223" s="30"/>
+      <c r="I223" s="32" t="n">
         <f aca="false">$I$221</f>
-        <v>5102.19</v>
-      </c>
-      <c r="J223" s="29"/>
-      <c r="K223" s="32" t="str">
+        <v>4475.69</v>
+      </c>
+      <c r="J223" s="30"/>
+      <c r="K223" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,11)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,11)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -8381,32 +8385,32 @@
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B225" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C225" s="34" t="n">
         <f aca="false">IF($B225="","",INDEX(Schedule!$G$4:$G$483,MATCH(11001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="D225" s="35" t="str">
         <f aca="false">IF($B225="","",INDEX(Schedule!$D$4:$D$483,MATCH(11001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E225" s="36" t="n">
         <f aca="false">IF($B225="","",INDEX(Schedule!$E$4:$E$483,MATCH(11001,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>790</v>
       </c>
       <c r="F225" s="16"/>
       <c r="G225" s="36" t="n">
         <f aca="false">IF($B225="","",IF($F225&lt;&gt;"",$F225,$E225))</f>
-        <v>2.99</v>
+        <v>790</v>
       </c>
       <c r="H225" s="36" t="n">
         <f aca="false">IF($B225="",0,IF($D225="Income",$G225,-$G225))</f>
-        <v>-2.99</v>
+        <v>790</v>
       </c>
       <c r="I225" s="37" t="n">
         <f aca="false">IF($B225="","",$I$223+SUM($H$225:$H225))</f>
-        <v>5099.2</v>
+        <v>5265.69</v>
       </c>
       <c r="J225" s="38" t="str">
         <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8416,32 +8420,32 @@
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B226" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Central Maine Power Co.</v>
       </c>
       <c r="C226" s="34" t="n">
         <f aca="false">IF($B226="","",INDEX(Schedule!$G$4:$G$483,MATCH(11002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46309</v>
+        <v>46305</v>
       </c>
       <c r="D226" s="35" t="str">
         <f aca="false">IF($B226="","",INDEX(Schedule!$D$4:$D$483,MATCH(11002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E226" s="36" t="n">
         <f aca="false">IF($B226="","",INDEX(Schedule!$E$4:$E$483,MATCH(11002,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>163.5</v>
       </c>
       <c r="F226" s="16"/>
       <c r="G226" s="36" t="n">
         <f aca="false">IF($B226="","",IF($F226&lt;&gt;"",$F226,$E226))</f>
-        <v>90</v>
+        <v>163.5</v>
       </c>
       <c r="H226" s="36" t="n">
         <f aca="false">IF($B226="",0,IF($D226="Income",$G226,-$G226))</f>
-        <v>90</v>
+        <v>-163.5</v>
       </c>
       <c r="I226" s="37" t="n">
         <f aca="false">IF($B226="","",$I$223+SUM($H$225:$H226))</f>
-        <v>5189.2</v>
+        <v>5102.19</v>
       </c>
       <c r="J226" s="38" t="str">
         <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8451,11 +8455,11 @@
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B227" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C227" s="34" t="n">
         <f aca="false">IF($B227="","",INDEX(Schedule!$G$4:$G$483,MATCH(11003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46310</v>
+        <v>46308</v>
       </c>
       <c r="D227" s="35" t="str">
         <f aca="false">IF($B227="","",INDEX(Schedule!$D$4:$D$483,MATCH(11003,Schedule!$K$4:$K$483,0)))</f>
@@ -8463,20 +8467,20 @@
       </c>
       <c r="E227" s="36" t="n">
         <f aca="false">IF($B227="","",INDEX(Schedule!$E$4:$E$483,MATCH(11003,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>2.99</v>
       </c>
       <c r="F227" s="16"/>
       <c r="G227" s="36" t="n">
         <f aca="false">IF($B227="","",IF($F227&lt;&gt;"",$F227,$E227))</f>
-        <v>350</v>
+        <v>2.99</v>
       </c>
       <c r="H227" s="36" t="n">
         <f aca="false">IF($B227="",0,IF($D227="Income",$G227,-$G227))</f>
-        <v>-350</v>
+        <v>-2.99</v>
       </c>
       <c r="I227" s="37" t="n">
         <f aca="false">IF($B227="","",$I$223+SUM($H$225:$H227))</f>
-        <v>4839.2</v>
+        <v>5099.2</v>
       </c>
       <c r="J227" s="38" t="str">
         <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8486,11 +8490,11 @@
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C228" s="34" t="n">
         <f aca="false">IF($B228="","",INDEX(Schedule!$G$4:$G$483,MATCH(11004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="D228" s="35" t="str">
         <f aca="false">IF($B228="","",INDEX(Schedule!$D$4:$D$483,MATCH(11004,Schedule!$K$4:$K$483,0)))</f>
@@ -8498,20 +8502,20 @@
       </c>
       <c r="E228" s="36" t="n">
         <f aca="false">IF($B228="","",INDEX(Schedule!$E$4:$E$483,MATCH(11004,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>90</v>
       </c>
       <c r="F228" s="16"/>
       <c r="G228" s="36" t="n">
         <f aca="false">IF($B228="","",IF($F228&lt;&gt;"",$F228,$E228))</f>
-        <v>790</v>
+        <v>90</v>
       </c>
       <c r="H228" s="36" t="n">
         <f aca="false">IF($B228="",0,IF($D228="Income",$G228,-$G228))</f>
-        <v>790</v>
+        <v>90</v>
       </c>
       <c r="I228" s="37" t="n">
         <f aca="false">IF($B228="","",$I$223+SUM($H$225:$H228))</f>
-        <v>5629.2</v>
+        <v>5189.2</v>
       </c>
       <c r="J228" s="38" t="str">
         <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8521,11 +8525,11 @@
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B229" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Spectrum</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C229" s="34" t="n">
         <f aca="false">IF($B229="","",INDEX(Schedule!$G$4:$G$483,MATCH(11005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46311</v>
+        <v>46310</v>
       </c>
       <c r="D229" s="35" t="str">
         <f aca="false">IF($B229="","",INDEX(Schedule!$D$4:$D$483,MATCH(11005,Schedule!$K$4:$K$483,0)))</f>
@@ -8533,20 +8537,20 @@
       </c>
       <c r="E229" s="36" t="n">
         <f aca="false">IF($B229="","",INDEX(Schedule!$E$4:$E$483,MATCH(11005,Schedule!$K$4:$K$483,0)))</f>
-        <v>171.1</v>
+        <v>350</v>
       </c>
       <c r="F229" s="16"/>
       <c r="G229" s="36" t="n">
         <f aca="false">IF($B229="","",IF($F229&lt;&gt;"",$F229,$E229))</f>
-        <v>171.1</v>
+        <v>350</v>
       </c>
       <c r="H229" s="36" t="n">
         <f aca="false">IF($B229="",0,IF($D229="Income",$G229,-$G229))</f>
-        <v>-171.1</v>
+        <v>-350</v>
       </c>
       <c r="I229" s="37" t="n">
         <f aca="false">IF($B229="","",$I$223+SUM($H$225:$H229))</f>
-        <v>5458.1</v>
+        <v>4839.2</v>
       </c>
       <c r="J229" s="38" t="str">
         <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8556,71 +8560,71 @@
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B230" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services</v>
-      </c>
-      <c r="C230" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C230" s="34" t="str">
         <f aca="false">IF($B230="","",INDEX(Schedule!$G$4:$G$483,MATCH(11006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46311</v>
+        <v/>
       </c>
       <c r="D230" s="35" t="str">
         <f aca="false">IF($B230="","",INDEX(Schedule!$D$4:$D$483,MATCH(11006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E230" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E230" s="36" t="str">
         <f aca="false">IF($B230="","",INDEX(Schedule!$E$4:$E$483,MATCH(11006,Schedule!$K$4:$K$483,0)))</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="F230" s="16"/>
-      <c r="G230" s="36" t="n">
+      <c r="G230" s="36" t="str">
         <f aca="false">IF($B230="","",IF($F230&lt;&gt;"",$F230,$E230))</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="H230" s="36" t="n">
         <f aca="false">IF($B230="",0,IF($D230="Income",$G230,-$G230))</f>
-        <v>-45</v>
-      </c>
-      <c r="I230" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" s="37" t="str">
         <f aca="false">IF($B230="","",$I$223+SUM($H$225:$H230))</f>
-        <v>5413.1</v>
+        <v/>
       </c>
       <c r="J230" s="38" t="str">
         <f aca="true">IF($B230="","",IF($F230&lt;&gt;"","PAID",IF($C230&lt;TODAY(),"PAST DUE",IF($C230&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B231" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Metal Copy</v>
-      </c>
-      <c r="C231" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C231" s="34" t="str">
         <f aca="false">IF($B231="","",INDEX(Schedule!$G$4:$G$483,MATCH(11007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46313</v>
+        <v/>
       </c>
       <c r="D231" s="35" t="str">
         <f aca="false">IF($B231="","",INDEX(Schedule!$D$4:$D$483,MATCH(11007,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E231" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E231" s="36" t="str">
         <f aca="false">IF($B231="","",INDEX(Schedule!$E$4:$E$483,MATCH(11007,Schedule!$K$4:$K$483,0)))</f>
-        <v>16.99</v>
+        <v/>
       </c>
       <c r="F231" s="16"/>
-      <c r="G231" s="36" t="n">
+      <c r="G231" s="36" t="str">
         <f aca="false">IF($B231="","",IF($F231&lt;&gt;"",$F231,$E231))</f>
-        <v>16.99</v>
+        <v/>
       </c>
       <c r="H231" s="36" t="n">
         <f aca="false">IF($B231="",0,IF($D231="Income",$G231,-$G231))</f>
-        <v>-16.99</v>
-      </c>
-      <c r="I231" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I231" s="37" t="str">
         <f aca="false">IF($B231="","",$I$223+SUM($H$225:$H231))</f>
-        <v>5396.11</v>
+        <v/>
       </c>
       <c r="J231" s="38" t="str">
         <f aca="true">IF($B231="","",IF($F231&lt;&gt;"","PAID",IF($C231&lt;TODAY(),"PAST DUE",IF($C231&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8887,7 +8891,7 @@
       <c r="D242" s="42"/>
       <c r="E242" s="43" t="n">
         <f aca="false">SUM($E$225:$E$241)</f>
-        <v>1466.08</v>
+        <v>1396.49</v>
       </c>
       <c r="F242" s="43" t="n">
         <f aca="false">SUM($F$225:$F$234)</f>
@@ -8895,15 +8899,15 @@
       </c>
       <c r="G242" s="43" t="n">
         <f aca="false">SUM($G$225:$G$241)</f>
-        <v>1466.08</v>
+        <v>1396.49</v>
       </c>
       <c r="H242" s="43" t="n">
         <f aca="false">SUM($H$225:$H$241)</f>
-        <v>293.92</v>
+        <v>363.51</v>
       </c>
       <c r="I242" s="44" t="n">
         <f aca="false">$I$223+SUM($H$225:$H$241)</f>
-        <v>5396.11</v>
+        <v>4839.2</v>
       </c>
       <c r="J242" s="45" t="str">
         <f aca="false">IF($I$242&lt;0,"SHORTFALL",IF($I$242&lt;$E$7,"TIGHT","OK"))</f>
@@ -8911,28 +8915,28 @@
       </c>
       <c r="K242" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$225:$D$241,"Income",$G$225:$G$241),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$225:$D$241,"Expense",$G$225:$G$241),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$242,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $586.08   =  net $293.92</v>
+        <v>Income $880.00   less expenses $516.49   =  net $363.51</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B244" s="28" t="str">
+      <c r="B244" s="29" t="str">
         <f aca="false">"WEEK 12     "&amp;TEXT($E$6+77,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+77+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 12     Mon, Oct 19   through   Sun, Oct 25, 2026</v>
-      </c>
-      <c r="C244" s="29"/>
-      <c r="D244" s="29"/>
-      <c r="E244" s="29"/>
-      <c r="F244" s="29"/>
-      <c r="G244" s="30" t="s">
+        <v>WEEK 12     Fri, Oct 16   through   Thu, Oct 22, 2026</v>
+      </c>
+      <c r="C244" s="30"/>
+      <c r="D244" s="30"/>
+      <c r="E244" s="30"/>
+      <c r="F244" s="30"/>
+      <c r="G244" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H244" s="29"/>
-      <c r="I244" s="31" t="n">
+      <c r="H244" s="30"/>
+      <c r="I244" s="32" t="n">
         <f aca="false">$I$242</f>
-        <v>5396.11</v>
-      </c>
-      <c r="J244" s="29"/>
-      <c r="K244" s="32" t="str">
+        <v>4839.2</v>
+      </c>
+      <c r="J244" s="30"/>
+      <c r="K244" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,12)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,12)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -8969,11 +8973,11 @@
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B246" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C246" s="34" t="n">
         <f aca="false">IF($B246="","",INDEX(Schedule!$G$4:$G$483,MATCH(12001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="D246" s="35" t="str">
         <f aca="false">IF($B246="","",INDEX(Schedule!$D$4:$D$483,MATCH(12001,Schedule!$K$4:$K$483,0)))</f>
@@ -8981,20 +8985,20 @@
       </c>
       <c r="E246" s="36" t="n">
         <f aca="false">IF($B246="","",INDEX(Schedule!$E$4:$E$483,MATCH(12001,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="F246" s="16"/>
       <c r="G246" s="36" t="n">
         <f aca="false">IF($B246="","",IF($F246&lt;&gt;"",$F246,$E246))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="H246" s="36" t="n">
         <f aca="false">IF($B246="",0,IF($D246="Income",$G246,-$G246))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="I246" s="37" t="n">
         <f aca="false">IF($B246="","",$I$244+SUM($H$246:$H246))</f>
-        <v>5486.11</v>
+        <v>5629.2</v>
       </c>
       <c r="J246" s="38" t="str">
         <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9004,32 +9008,32 @@
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B247" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Spectrum</v>
       </c>
       <c r="C247" s="34" t="n">
         <f aca="false">IF($B247="","",INDEX(Schedule!$G$4:$G$483,MATCH(12002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="D247" s="35" t="str">
         <f aca="false">IF($B247="","",INDEX(Schedule!$D$4:$D$483,MATCH(12002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E247" s="36" t="n">
         <f aca="false">IF($B247="","",INDEX(Schedule!$E$4:$E$483,MATCH(12002,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>171.1</v>
       </c>
       <c r="F247" s="16"/>
       <c r="G247" s="36" t="n">
         <f aca="false">IF($B247="","",IF($F247&lt;&gt;"",$F247,$E247))</f>
-        <v>790</v>
+        <v>171.1</v>
       </c>
       <c r="H247" s="36" t="n">
         <f aca="false">IF($B247="",0,IF($D247="Income",$G247,-$G247))</f>
-        <v>790</v>
+        <v>-171.1</v>
       </c>
       <c r="I247" s="37" t="n">
         <f aca="false">IF($B247="","",$I$244+SUM($H$246:$H247))</f>
-        <v>6276.11</v>
+        <v>5458.1</v>
       </c>
       <c r="J247" s="38" t="str">
         <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9039,11 +9043,11 @@
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B248" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Microsoft</v>
+        <v>Maine Revenue Services</v>
       </c>
       <c r="C248" s="34" t="n">
         <f aca="false">IF($B248="","",INDEX(Schedule!$G$4:$G$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46320</v>
+        <v>46311</v>
       </c>
       <c r="D248" s="35" t="str">
         <f aca="false">IF($B248="","",INDEX(Schedule!$D$4:$D$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
@@ -9051,20 +9055,20 @@
       </c>
       <c r="E248" s="36" t="n">
         <f aca="false">IF($B248="","",INDEX(Schedule!$E$4:$E$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
-        <v>13.7</v>
+        <v>45</v>
       </c>
       <c r="F248" s="16"/>
       <c r="G248" s="36" t="n">
         <f aca="false">IF($B248="","",IF($F248&lt;&gt;"",$F248,$E248))</f>
-        <v>13.7</v>
+        <v>45</v>
       </c>
       <c r="H248" s="36" t="n">
         <f aca="false">IF($B248="",0,IF($D248="Income",$G248,-$G248))</f>
-        <v>-13.7</v>
+        <v>-45</v>
       </c>
       <c r="I248" s="37" t="n">
         <f aca="false">IF($B248="","",$I$244+SUM($H$246:$H248))</f>
-        <v>6262.41</v>
+        <v>5413.1</v>
       </c>
       <c r="J248" s="38" t="str">
         <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9074,11 +9078,11 @@
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B249" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Metal Copy</v>
       </c>
       <c r="C249" s="34" t="n">
         <f aca="false">IF($B249="","",INDEX(Schedule!$G$4:$G$483,MATCH(12004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46320</v>
+        <v>46313</v>
       </c>
       <c r="D249" s="35" t="str">
         <f aca="false">IF($B249="","",INDEX(Schedule!$D$4:$D$483,MATCH(12004,Schedule!$K$4:$K$483,0)))</f>
@@ -9086,20 +9090,20 @@
       </c>
       <c r="E249" s="36" t="n">
         <f aca="false">IF($B249="","",INDEX(Schedule!$E$4:$E$483,MATCH(12004,Schedule!$K$4:$K$483,0)))</f>
-        <v>43.87</v>
+        <v>16.99</v>
       </c>
       <c r="F249" s="16"/>
       <c r="G249" s="36" t="n">
         <f aca="false">IF($B249="","",IF($F249&lt;&gt;"",$F249,$E249))</f>
-        <v>43.87</v>
+        <v>16.99</v>
       </c>
       <c r="H249" s="36" t="n">
         <f aca="false">IF($B249="",0,IF($D249="Income",$G249,-$G249))</f>
-        <v>-43.87</v>
+        <v>-16.99</v>
       </c>
       <c r="I249" s="37" t="n">
         <f aca="false">IF($B249="","",$I$244+SUM($H$246:$H249))</f>
-        <v>6218.54</v>
+        <v>5396.11</v>
       </c>
       <c r="J249" s="38" t="str">
         <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9109,36 +9113,36 @@
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B250" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C250" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C250" s="34" t="n">
         <f aca="false">IF($B250="","",INDEX(Schedule!$G$4:$G$483,MATCH(12005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46316</v>
       </c>
       <c r="D250" s="35" t="str">
         <f aca="false">IF($B250="","",INDEX(Schedule!$D$4:$D$483,MATCH(12005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E250" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E250" s="36" t="n">
         <f aca="false">IF($B250="","",INDEX(Schedule!$E$4:$E$483,MATCH(12005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F250" s="16"/>
-      <c r="G250" s="36" t="str">
+      <c r="G250" s="36" t="n">
         <f aca="false">IF($B250="","",IF($F250&lt;&gt;"",$F250,$E250))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H250" s="36" t="n">
         <f aca="false">IF($B250="",0,IF($D250="Income",$G250,-$G250))</f>
-        <v>0</v>
-      </c>
-      <c r="I250" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I250" s="37" t="n">
         <f aca="false">IF($B250="","",$I$244+SUM($H$246:$H250))</f>
-        <v/>
+        <v>5486.11</v>
       </c>
       <c r="J250" s="38" t="str">
         <f aca="true">IF($B250="","",IF($F250&lt;&gt;"","PAID",IF($C250&lt;TODAY(),"PAST DUE",IF($C250&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9475,7 +9479,7 @@
       <c r="D263" s="42"/>
       <c r="E263" s="43" t="n">
         <f aca="false">SUM($E$246:$E$262)</f>
-        <v>937.57</v>
+        <v>1113.09</v>
       </c>
       <c r="F263" s="43" t="n">
         <f aca="false">SUM($F$246:$F$255)</f>
@@ -9483,15 +9487,15 @@
       </c>
       <c r="G263" s="43" t="n">
         <f aca="false">SUM($G$246:$G$262)</f>
-        <v>937.57</v>
+        <v>1113.09</v>
       </c>
       <c r="H263" s="43" t="n">
         <f aca="false">SUM($H$246:$H$262)</f>
-        <v>822.43</v>
+        <v>646.91</v>
       </c>
       <c r="I263" s="44" t="n">
         <f aca="false">$I$244+SUM($H$246:$H$262)</f>
-        <v>6218.54</v>
+        <v>5486.11</v>
       </c>
       <c r="J263" s="45" t="str">
         <f aca="false">IF($I$263&lt;0,"SHORTFALL",IF($I$263&lt;$E$7,"TIGHT","OK"))</f>
@@ -9499,28 +9503,28 @@
       </c>
       <c r="K263" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$246:$D$262,"Income",$G$246:$G$262),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$246:$D$262,"Expense",$G$246:$G$262),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$263,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
+        <v>Income $880.00   less expenses $233.09   =  net $646.91</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B265" s="28" t="str">
+      <c r="B265" s="29" t="str">
         <f aca="false">"WEEK 13     "&amp;TEXT($E$6+84,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+84+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 13     Mon, Oct 26   through   Sun, Nov 1, 2026</v>
-      </c>
-      <c r="C265" s="29"/>
-      <c r="D265" s="29"/>
-      <c r="E265" s="29"/>
-      <c r="F265" s="29"/>
-      <c r="G265" s="30" t="s">
+        <v>WEEK 13     Fri, Oct 23   through   Thu, Oct 29, 2026</v>
+      </c>
+      <c r="C265" s="30"/>
+      <c r="D265" s="30"/>
+      <c r="E265" s="30"/>
+      <c r="F265" s="30"/>
+      <c r="G265" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="H265" s="29"/>
-      <c r="I265" s="31" t="n">
+      <c r="H265" s="30"/>
+      <c r="I265" s="32" t="n">
         <f aca="false">$I$263</f>
-        <v>6218.54</v>
-      </c>
-      <c r="J265" s="29"/>
-      <c r="K265" s="32" t="str">
+        <v>5486.11</v>
+      </c>
+      <c r="J265" s="30"/>
+      <c r="K265" s="26" t="str">
         <f aca="false">IF(COUNTIF(Schedule!$I$4:$I$483,13)&gt;10,"! "&amp;COUNTIF(Schedule!$I$4:$I$483,13)-10&amp;" more transaction(s) fall in this week than there are rows to show them.","")</f>
         <v/>
       </c>
@@ -9557,11 +9561,11 @@
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B267" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C267" s="34" t="n">
         <f aca="false">IF($B267="","",INDEX(Schedule!$G$4:$G$483,MATCH(13001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46323</v>
+        <v>46318</v>
       </c>
       <c r="D267" s="35" t="str">
         <f aca="false">IF($B267="","",INDEX(Schedule!$D$4:$D$483,MATCH(13001,Schedule!$K$4:$K$483,0)))</f>
@@ -9569,20 +9573,20 @@
       </c>
       <c r="E267" s="36" t="n">
         <f aca="false">IF($B267="","",INDEX(Schedule!$E$4:$E$483,MATCH(13001,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="F267" s="16"/>
       <c r="G267" s="36" t="n">
         <f aca="false">IF($B267="","",IF($F267&lt;&gt;"",$F267,$E267))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="H267" s="36" t="n">
         <f aca="false">IF($B267="",0,IF($D267="Income",$G267,-$G267))</f>
-        <v>90</v>
+        <v>790</v>
       </c>
       <c r="I267" s="37" t="n">
         <f aca="false">IF($B267="","",$I$265+SUM($H$267:$H267))</f>
-        <v>6308.54</v>
+        <v>6276.11</v>
       </c>
       <c r="J267" s="38" t="str">
         <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9592,32 +9596,32 @@
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B268" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Microsoft</v>
       </c>
       <c r="C268" s="34" t="n">
         <f aca="false">IF($B268="","",INDEX(Schedule!$G$4:$G$483,MATCH(13002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="D268" s="35" t="str">
         <f aca="false">IF($B268="","",INDEX(Schedule!$D$4:$D$483,MATCH(13002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E268" s="36" t="n">
         <f aca="false">IF($B268="","",INDEX(Schedule!$E$4:$E$483,MATCH(13002,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>13.7</v>
       </c>
       <c r="F268" s="16"/>
       <c r="G268" s="36" t="n">
         <f aca="false">IF($B268="","",IF($F268&lt;&gt;"",$F268,$E268))</f>
-        <v>790</v>
+        <v>13.7</v>
       </c>
       <c r="H268" s="36" t="n">
         <f aca="false">IF($B268="",0,IF($D268="Income",$G268,-$G268))</f>
-        <v>790</v>
+        <v>-13.7</v>
       </c>
       <c r="I268" s="37" t="n">
         <f aca="false">IF($B268="","",$I$265+SUM($H$267:$H268))</f>
-        <v>7098.54</v>
+        <v>6262.41</v>
       </c>
       <c r="J268" s="38" t="str">
         <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9627,11 +9631,11 @@
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B269" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Central Maine Power: Property</v>
       </c>
       <c r="C269" s="34" t="n">
         <f aca="false">IF($B269="","",INDEX(Schedule!$G$4:$G$483,MATCH(13003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46325</v>
+        <v>46320</v>
       </c>
       <c r="D269" s="35" t="str">
         <f aca="false">IF($B269="","",INDEX(Schedule!$D$4:$D$483,MATCH(13003,Schedule!$K$4:$K$483,0)))</f>
@@ -9639,20 +9643,20 @@
       </c>
       <c r="E269" s="36" t="n">
         <f aca="false">IF($B269="","",INDEX(Schedule!$E$4:$E$483,MATCH(13003,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>43.87</v>
       </c>
       <c r="F269" s="16"/>
       <c r="G269" s="36" t="n">
         <f aca="false">IF($B269="","",IF($F269&lt;&gt;"",$F269,$E269))</f>
-        <v>350</v>
+        <v>43.87</v>
       </c>
       <c r="H269" s="36" t="n">
         <f aca="false">IF($B269="",0,IF($D269="Income",$G269,-$G269))</f>
-        <v>-350</v>
+        <v>-43.87</v>
       </c>
       <c r="I269" s="37" t="n">
         <f aca="false">IF($B269="","",$I$265+SUM($H$267:$H269))</f>
-        <v>6748.54</v>
+        <v>6218.54</v>
       </c>
       <c r="J269" s="38" t="str">
         <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9662,32 +9666,32 @@
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B270" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services (2)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C270" s="34" t="n">
         <f aca="false">IF($B270="","",INDEX(Schedule!$G$4:$G$483,MATCH(13004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46325</v>
+        <v>46323</v>
       </c>
       <c r="D270" s="35" t="str">
         <f aca="false">IF($B270="","",INDEX(Schedule!$D$4:$D$483,MATCH(13004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E270" s="36" t="n">
         <f aca="false">IF($B270="","",INDEX(Schedule!$E$4:$E$483,MATCH(13004,Schedule!$K$4:$K$483,0)))</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="F270" s="16"/>
       <c r="G270" s="36" t="n">
         <f aca="false">IF($B270="","",IF($F270&lt;&gt;"",$F270,$E270))</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="H270" s="36" t="n">
         <f aca="false">IF($B270="",0,IF($D270="Income",$G270,-$G270))</f>
-        <v>-150</v>
+        <v>90</v>
       </c>
       <c r="I270" s="37" t="n">
         <f aca="false">IF($B270="","",$I$265+SUM($H$267:$H270))</f>
-        <v>6598.54</v>
+        <v>6308.54</v>
       </c>
       <c r="J270" s="38" t="str">
         <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9697,36 +9701,36 @@
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B271" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Progressive Insurance</v>
-      </c>
-      <c r="C271" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C271" s="34" t="str">
         <f aca="false">IF($B271="","",INDEX(Schedule!$G$4:$G$483,MATCH(13005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46326</v>
+        <v/>
       </c>
       <c r="D271" s="35" t="str">
         <f aca="false">IF($B271="","",INDEX(Schedule!$D$4:$D$483,MATCH(13005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E271" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E271" s="36" t="str">
         <f aca="false">IF($B271="","",INDEX(Schedule!$E$4:$E$483,MATCH(13005,Schedule!$K$4:$K$483,0)))</f>
-        <v>143.37</v>
+        <v/>
       </c>
       <c r="F271" s="16"/>
-      <c r="G271" s="36" t="n">
+      <c r="G271" s="36" t="str">
         <f aca="false">IF($B271="","",IF($F271&lt;&gt;"",$F271,$E271))</f>
-        <v>143.37</v>
+        <v/>
       </c>
       <c r="H271" s="36" t="n">
         <f aca="false">IF($B271="",0,IF($D271="Income",$G271,-$G271))</f>
-        <v>-143.37</v>
-      </c>
-      <c r="I271" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" s="37" t="str">
         <f aca="false">IF($B271="","",$I$265+SUM($H$267:$H271))</f>
-        <v>6455.17</v>
+        <v/>
       </c>
       <c r="J271" s="38" t="str">
         <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10063,7 +10067,7 @@
       <c r="D284" s="42"/>
       <c r="E284" s="43" t="n">
         <f aca="false">SUM($E$267:$E$283)</f>
-        <v>1523.37</v>
+        <v>937.57</v>
       </c>
       <c r="F284" s="43" t="n">
         <f aca="false">SUM($F$267:$F$276)</f>
@@ -10071,15 +10075,15 @@
       </c>
       <c r="G284" s="43" t="n">
         <f aca="false">SUM($G$267:$G$283)</f>
-        <v>1523.37</v>
+        <v>937.57</v>
       </c>
       <c r="H284" s="43" t="n">
         <f aca="false">SUM($H$267:$H$283)</f>
-        <v>236.63</v>
+        <v>822.43</v>
       </c>
       <c r="I284" s="44" t="n">
         <f aca="false">$I$265+SUM($H$267:$H$283)</f>
-        <v>6455.17</v>
+        <v>6308.54</v>
       </c>
       <c r="J284" s="45" t="str">
         <f aca="false">IF($I$284&lt;0,"SHORTFALL",IF($I$284&lt;$E$7,"TIGHT","OK"))</f>
@@ -10087,7 +10091,7 @@
       </c>
       <c r="K284" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$267:$D$283,"Income",$G$267:$G$283),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$267:$D$283,"Expense",$G$267:$G$283),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$284,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $643.37   =  net $236.63</v>
+        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
       </c>
     </row>
   </sheetData>
@@ -10160,7 +10164,7 @@
       <c r="D4" s="46"/>
       <c r="E4" s="47" t="n">
         <f aca="false">MIN($I$13:$I$25)</f>
-        <v>1358.91</v>
+        <v>1073.9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10171,7 +10175,7 @@
       <c r="D5" s="46"/>
       <c r="E5" s="48" t="str">
         <f aca="false">"Week "&amp;INDEX($B$13:$B$25,MATCH(MIN($I$13:$I$25),$I$13:$I$25,0))&amp;", beginning "&amp;TEXT(INDEX($C$13:$C$25,MATCH(MIN($I$13:$I$25),$I$13:$I$25,0)),"mmm d, yyyy")</f>
-        <v>Week 1, beginning Aug 3, 2026</v>
+        <v>Week 1, beginning Jul 31, 2026</v>
       </c>
       <c r="F5" s="48"/>
       <c r="G5" s="48"/>
@@ -10201,7 +10205,7 @@
       <c r="D7" s="46"/>
       <c r="E7" s="49" t="n">
         <f aca="false">SUM($E$13:$E$25)</f>
-        <v>11440</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10212,7 +10216,7 @@
       <c r="D8" s="46"/>
       <c r="E8" s="49" t="n">
         <f aca="false">SUM($F$13:$F$25)+SUM($G$13:$G$25)</f>
-        <v>6234.83</v>
+        <v>5591.46</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10223,7 +10227,7 @@
       <c r="D9" s="46"/>
       <c r="E9" s="47" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5205.17</v>
+        <v>5058.54</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10234,7 +10238,7 @@
       <c r="D10" s="46"/>
       <c r="E10" s="47" t="n">
         <f aca="false">$I$25</f>
-        <v>6455.17</v>
+        <v>6308.54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10275,7 +10279,7 @@
       </c>
       <c r="C13" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+0</f>
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="D13" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$13</f>
@@ -10283,11 +10287,11 @@
       </c>
       <c r="E13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Income",'Cash Flow'!$G$15:$G$24)</f>
-        <v>880</v>
+        <v>90</v>
       </c>
       <c r="F13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Expense",'Cash Flow'!$G$15:$G$24)</f>
-        <v>556.09</v>
+        <v>51.1</v>
       </c>
       <c r="G13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$26:$D$31,"Expense",'Cash Flow'!$G$26:$G$31)</f>
@@ -10295,17 +10299,17 @@
       </c>
       <c r="H13" s="53" t="n">
         <f aca="false">$E13-$F13-$G13</f>
-        <v>108.91</v>
+        <v>-176.1</v>
       </c>
       <c r="I13" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$32</f>
-        <v>1358.91</v>
+        <v>1073.9</v>
       </c>
       <c r="J13" s="54" t="str">
         <f aca="false">IF($I13&lt;0,"SHORTFALL",IF($I13&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K13" s="26" t="n">
+      <c r="K13" s="27" t="n">
         <f aca="false">IF($I13&lt;0,$B13,999)</f>
         <v>999</v>
       </c>
@@ -10316,11 +10320,11 @@
       </c>
       <c r="C14" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+7</f>
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="D14" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$34</f>
-        <v>1358.91</v>
+        <v>1073.9</v>
       </c>
       <c r="E14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$36:$D$45,"Income",'Cash Flow'!$G$36:$G$45)</f>
@@ -10328,7 +10332,7 @@
       </c>
       <c r="F14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$36:$D$45,"Expense",'Cash Flow'!$G$36:$G$45)</f>
-        <v>732.59</v>
+        <v>671.48</v>
       </c>
       <c r="G14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$47:$D$52,"Expense",'Cash Flow'!$G$47:$G$52)</f>
@@ -10336,17 +10340,17 @@
       </c>
       <c r="H14" s="58" t="n">
         <f aca="false">$E14-$F14-$G14</f>
-        <v>147.41</v>
+        <v>208.52</v>
       </c>
       <c r="I14" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$53</f>
-        <v>1506.32</v>
+        <v>1282.42</v>
       </c>
       <c r="J14" s="59" t="str">
         <f aca="false">IF($I14&lt;0,"SHORTFALL",IF($I14&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K14" s="26" t="n">
+      <c r="K14" s="27" t="n">
         <f aca="false">IF($I14&lt;0,$B14,999)</f>
         <v>999</v>
       </c>
@@ -10357,11 +10361,11 @@
       </c>
       <c r="C15" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+14</f>
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$55</f>
-        <v>1506.32</v>
+        <v>1282.42</v>
       </c>
       <c r="E15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$57:$D$66,"Income",'Cash Flow'!$G$57:$G$66)</f>
@@ -10369,7 +10373,7 @@
       </c>
       <c r="F15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$57:$D$66,"Expense",'Cash Flow'!$G$57:$G$66)</f>
-        <v>16.99</v>
+        <v>583.09</v>
       </c>
       <c r="G15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$68:$D$73,"Expense",'Cash Flow'!$G$68:$G$73)</f>
@@ -10377,17 +10381,17 @@
       </c>
       <c r="H15" s="53" t="n">
         <f aca="false">$E15-$F15-$G15</f>
-        <v>863.01</v>
+        <v>296.91</v>
       </c>
       <c r="I15" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$74</f>
-        <v>2369.33</v>
+        <v>1579.33</v>
       </c>
       <c r="J15" s="54" t="str">
         <f aca="false">IF($I15&lt;0,"SHORTFALL",IF($I15&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K15" s="26" t="n">
+      <c r="K15" s="27" t="n">
         <f aca="false">IF($I15&lt;0,$B15,999)</f>
         <v>999</v>
       </c>
@@ -10398,11 +10402,11 @@
       </c>
       <c r="C16" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+21</f>
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="D16" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$76</f>
-        <v>2369.33</v>
+        <v>1579.33</v>
       </c>
       <c r="E16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$78:$D$87,"Income",'Cash Flow'!$G$78:$G$87)</f>
@@ -10410,7 +10414,7 @@
       </c>
       <c r="F16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$78:$D$87,"Expense",'Cash Flow'!$G$78:$G$87)</f>
-        <v>207.57</v>
+        <v>57.57</v>
       </c>
       <c r="G16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$89:$D$94,"Expense",'Cash Flow'!$G$89:$G$94)</f>
@@ -10418,17 +10422,17 @@
       </c>
       <c r="H16" s="58" t="n">
         <f aca="false">$E16-$F16-$G16</f>
-        <v>672.43</v>
+        <v>822.43</v>
       </c>
       <c r="I16" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$95</f>
-        <v>3041.76</v>
+        <v>2401.76</v>
       </c>
       <c r="J16" s="59" t="str">
         <f aca="false">IF($I16&lt;0,"SHORTFALL",IF($I16&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K16" s="26" t="n">
+      <c r="K16" s="27" t="n">
         <f aca="false">IF($I16&lt;0,$B16,999)</f>
         <v>999</v>
       </c>
@@ -10439,11 +10443,11 @@
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+28</f>
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$97</f>
-        <v>3041.76</v>
+        <v>2401.76</v>
       </c>
       <c r="E17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$99:$D$108,"Income",'Cash Flow'!$G$99:$G$108)</f>
@@ -10451,7 +10455,7 @@
       </c>
       <c r="F17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$99:$D$108,"Expense",'Cash Flow'!$G$99:$G$108)</f>
-        <v>544.47</v>
+        <v>643.37</v>
       </c>
       <c r="G17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$110:$D$115,"Expense",'Cash Flow'!$G$110:$G$115)</f>
@@ -10459,17 +10463,17 @@
       </c>
       <c r="H17" s="53" t="n">
         <f aca="false">$E17-$F17-$G17</f>
-        <v>335.53</v>
+        <v>236.63</v>
       </c>
       <c r="I17" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$116</f>
-        <v>3377.29</v>
+        <v>2638.39</v>
       </c>
       <c r="J17" s="54" t="str">
         <f aca="false">IF($I17&lt;0,"SHORTFALL",IF($I17&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K17" s="26" t="n">
+      <c r="K17" s="27" t="n">
         <f aca="false">IF($I17&lt;0,$B17,999)</f>
         <v>999</v>
       </c>
@@ -10480,11 +10484,11 @@
       </c>
       <c r="C18" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+35</f>
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="D18" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$118</f>
-        <v>3377.29</v>
+        <v>2638.39</v>
       </c>
       <c r="E18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$120:$D$129,"Income",'Cash Flow'!$G$120:$G$129)</f>
@@ -10492,7 +10496,7 @@
       </c>
       <c r="F18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$120:$D$129,"Expense",'Cash Flow'!$G$120:$G$129)</f>
-        <v>671.48</v>
+        <v>719.59</v>
       </c>
       <c r="G18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$131:$D$136,"Expense",'Cash Flow'!$G$131:$G$136)</f>
@@ -10500,17 +10504,17 @@
       </c>
       <c r="H18" s="58" t="n">
         <f aca="false">$E18-$F18-$G18</f>
-        <v>208.52</v>
+        <v>160.41</v>
       </c>
       <c r="I18" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$137</f>
-        <v>3585.81</v>
+        <v>2798.8</v>
       </c>
       <c r="J18" s="59" t="str">
         <f aca="false">IF($I18&lt;0,"SHORTFALL",IF($I18&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K18" s="26" t="n">
+      <c r="K18" s="27" t="n">
         <f aca="false">IF($I18&lt;0,$B18,999)</f>
         <v>999</v>
       </c>
@@ -10521,11 +10525,11 @@
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+42</f>
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$139</f>
-        <v>3585.81</v>
+        <v>2798.8</v>
       </c>
       <c r="E19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$141:$D$150,"Income",'Cash Flow'!$G$141:$G$150)</f>
@@ -10533,7 +10537,7 @@
       </c>
       <c r="F19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$141:$D$150,"Expense",'Cash Flow'!$G$141:$G$150)</f>
-        <v>583.09</v>
+        <v>569.09</v>
       </c>
       <c r="G19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$152:$D$157,"Expense",'Cash Flow'!$G$152:$G$157)</f>
@@ -10541,17 +10545,17 @@
       </c>
       <c r="H19" s="53" t="n">
         <f aca="false">$E19-$F19-$G19</f>
-        <v>296.91</v>
+        <v>310.91</v>
       </c>
       <c r="I19" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$158</f>
-        <v>3882.72</v>
+        <v>3109.71</v>
       </c>
       <c r="J19" s="54" t="str">
         <f aca="false">IF($I19&lt;0,"SHORTFALL",IF($I19&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K19" s="26" t="n">
+      <c r="K19" s="27" t="n">
         <f aca="false">IF($I19&lt;0,$B19,999)</f>
         <v>999</v>
       </c>
@@ -10562,11 +10566,11 @@
       </c>
       <c r="C20" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+49</f>
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="D20" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$160</f>
-        <v>3882.72</v>
+        <v>3109.71</v>
       </c>
       <c r="E20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$162:$D$171,"Income",'Cash Flow'!$G$162:$G$171)</f>
@@ -10574,7 +10578,7 @@
       </c>
       <c r="F20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$162:$D$171,"Expense",'Cash Flow'!$G$162:$G$171)</f>
-        <v>57.57</v>
+        <v>16.99</v>
       </c>
       <c r="G20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$173:$D$178,"Expense",'Cash Flow'!$G$173:$G$178)</f>
@@ -10582,17 +10586,17 @@
       </c>
       <c r="H20" s="58" t="n">
         <f aca="false">$E20-$F20-$G20</f>
-        <v>822.43</v>
+        <v>863.01</v>
       </c>
       <c r="I20" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$179</f>
-        <v>4705.15</v>
+        <v>3972.72</v>
       </c>
       <c r="J20" s="59" t="str">
         <f aca="false">IF($I20&lt;0,"SHORTFALL",IF($I20&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K20" s="26" t="n">
+      <c r="K20" s="27" t="n">
         <f aca="false">IF($I20&lt;0,$B20,999)</f>
         <v>999</v>
       </c>
@@ -10603,11 +10607,11 @@
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+56</f>
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$181</f>
-        <v>4705.15</v>
+        <v>3972.72</v>
       </c>
       <c r="E21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$183:$D$192,"Income",'Cash Flow'!$G$183:$G$192)</f>
@@ -10615,7 +10619,7 @@
       </c>
       <c r="F21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$183:$D$192,"Expense",'Cash Flow'!$G$183:$G$192)</f>
-        <v>664.47</v>
+        <v>700.94</v>
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$194:$D$199,"Expense",'Cash Flow'!$G$194:$G$199)</f>
@@ -10623,17 +10627,17 @@
       </c>
       <c r="H21" s="53" t="n">
         <f aca="false">$E21-$F21-$G21</f>
-        <v>215.53</v>
+        <v>179.06</v>
       </c>
       <c r="I21" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$200</f>
-        <v>4920.68</v>
+        <v>4151.78</v>
       </c>
       <c r="J21" s="54" t="str">
         <f aca="false">IF($I21&lt;0,"SHORTFALL",IF($I21&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K21" s="26" t="n">
+      <c r="K21" s="27" t="n">
         <f aca="false">IF($I21&lt;0,$B21,999)</f>
         <v>999</v>
       </c>
@@ -10644,11 +10648,11 @@
       </c>
       <c r="C22" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+63</f>
-        <v>46300</v>
+        <v>46297</v>
       </c>
       <c r="D22" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$202</f>
-        <v>4920.68</v>
+        <v>4151.78</v>
       </c>
       <c r="E22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$204:$D$213,"Income",'Cash Flow'!$G$204:$G$213)</f>
@@ -10656,7 +10660,7 @@
       </c>
       <c r="F22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$204:$D$213,"Expense",'Cash Flow'!$G$204:$G$213)</f>
-        <v>698.49</v>
+        <v>556.09</v>
       </c>
       <c r="G22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$215:$D$220,"Expense",'Cash Flow'!$G$215:$G$220)</f>
@@ -10664,17 +10668,17 @@
       </c>
       <c r="H22" s="58" t="n">
         <f aca="false">$E22-$F22-$G22</f>
-        <v>181.51</v>
+        <v>323.91</v>
       </c>
       <c r="I22" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$221</f>
-        <v>5102.19</v>
+        <v>4475.69</v>
       </c>
       <c r="J22" s="59" t="str">
         <f aca="false">IF($I22&lt;0,"SHORTFALL",IF($I22&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K22" s="26" t="n">
+      <c r="K22" s="27" t="n">
         <f aca="false">IF($I22&lt;0,$B22,999)</f>
         <v>999</v>
       </c>
@@ -10685,11 +10689,11 @@
       </c>
       <c r="C23" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+70</f>
-        <v>46307</v>
+        <v>46304</v>
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$223</f>
-        <v>5102.19</v>
+        <v>4475.69</v>
       </c>
       <c r="E23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$225:$D$234,"Income",'Cash Flow'!$G$225:$G$234)</f>
@@ -10697,7 +10701,7 @@
       </c>
       <c r="F23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$225:$D$234,"Expense",'Cash Flow'!$G$225:$G$234)</f>
-        <v>586.08</v>
+        <v>516.49</v>
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$236:$D$241,"Expense",'Cash Flow'!$G$236:$G$241)</f>
@@ -10705,17 +10709,17 @@
       </c>
       <c r="H23" s="53" t="n">
         <f aca="false">$E23-$F23-$G23</f>
-        <v>293.92</v>
+        <v>363.51</v>
       </c>
       <c r="I23" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$242</f>
-        <v>5396.11</v>
+        <v>4839.2</v>
       </c>
       <c r="J23" s="54" t="str">
         <f aca="false">IF($I23&lt;0,"SHORTFALL",IF($I23&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K23" s="26" t="n">
+      <c r="K23" s="27" t="n">
         <f aca="false">IF($I23&lt;0,$B23,999)</f>
         <v>999</v>
       </c>
@@ -10726,11 +10730,11 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+77</f>
-        <v>46314</v>
+        <v>46311</v>
       </c>
       <c r="D24" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$244</f>
-        <v>5396.11</v>
+        <v>4839.2</v>
       </c>
       <c r="E24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$246:$D$255,"Income",'Cash Flow'!$G$246:$G$255)</f>
@@ -10738,7 +10742,7 @@
       </c>
       <c r="F24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$246:$D$255,"Expense",'Cash Flow'!$G$246:$G$255)</f>
-        <v>57.57</v>
+        <v>233.09</v>
       </c>
       <c r="G24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$257:$D$262,"Expense",'Cash Flow'!$G$257:$G$262)</f>
@@ -10746,17 +10750,17 @@
       </c>
       <c r="H24" s="58" t="n">
         <f aca="false">$E24-$F24-$G24</f>
-        <v>822.43</v>
+        <v>646.91</v>
       </c>
       <c r="I24" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$263</f>
-        <v>6218.54</v>
+        <v>5486.11</v>
       </c>
       <c r="J24" s="59" t="str">
         <f aca="false">IF($I24&lt;0,"SHORTFALL",IF($I24&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K24" s="26" t="n">
+      <c r="K24" s="27" t="n">
         <f aca="false">IF($I24&lt;0,$B24,999)</f>
         <v>999</v>
       </c>
@@ -10767,11 +10771,11 @@
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+84</f>
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$265</f>
-        <v>6218.54</v>
+        <v>5486.11</v>
       </c>
       <c r="E25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$267:$D$276,"Income",'Cash Flow'!$G$267:$G$276)</f>
@@ -10779,7 +10783,7 @@
       </c>
       <c r="F25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$267:$D$276,"Expense",'Cash Flow'!$G$267:$G$276)</f>
-        <v>643.37</v>
+        <v>57.57</v>
       </c>
       <c r="G25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$278:$D$283,"Expense",'Cash Flow'!$G$278:$G$283)</f>
@@ -10787,17 +10791,17 @@
       </c>
       <c r="H25" s="53" t="n">
         <f aca="false">$E25-$F25-$G25</f>
-        <v>236.63</v>
+        <v>822.43</v>
       </c>
       <c r="I25" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$284</f>
-        <v>6455.17</v>
+        <v>6308.54</v>
       </c>
       <c r="J25" s="54" t="str">
         <f aca="false">IF($I25&lt;0,"SHORTFALL",IF($I25&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
         <v>OK</v>
       </c>
-      <c r="K25" s="26" t="n">
+      <c r="K25" s="27" t="n">
         <f aca="false">IF($I25&lt;0,$B25,999)</f>
         <v>999</v>
       </c>
@@ -10815,11 +10819,11 @@
       </c>
       <c r="E26" s="43" t="n">
         <f aca="false">SUM($E$13:$E$25)</f>
-        <v>11440</v>
+        <v>10650</v>
       </c>
       <c r="F26" s="43" t="n">
         <f aca="false">SUM($F$13:$F$25)</f>
-        <v>6019.83</v>
+        <v>5376.46</v>
       </c>
       <c r="G26" s="43" t="n">
         <f aca="false">SUM($G$13:$G$25)</f>
@@ -10827,11 +10831,11 @@
       </c>
       <c r="H26" s="61" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5205.17</v>
+        <v>5058.54</v>
       </c>
       <c r="I26" s="61" t="n">
         <f aca="false">$I$25</f>
-        <v>6455.17</v>
+        <v>6308.54</v>
       </c>
       <c r="J26" s="42"/>
     </row>
@@ -11035,7 +11039,7 @@
       </c>
       <c r="K5" s="66" t="n">
         <f aca="false">IF($H5=1,$I5*1000+COUNTIFS($I$4:$I$483,$I5,$J$4:$J$483,"&lt;"&amp;$J5)+1,"")</f>
-        <v>2002</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11079,7 +11083,7 @@
       </c>
       <c r="K6" s="66" t="n">
         <f aca="false">IF($H6=1,$I6*1000+COUNTIFS($I$4:$I$483,$I6,$J$4:$J$483,"&lt;"&amp;$J6)+1,"")</f>
-        <v>3002</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11123,7 +11127,7 @@
       </c>
       <c r="K7" s="66" t="n">
         <f aca="false">IF($H7=1,$I7*1000+COUNTIFS($I$4:$I$483,$I7,$J$4:$J$483,"&lt;"&amp;$J7)+1,"")</f>
-        <v>4003</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11167,7 +11171,7 @@
       </c>
       <c r="K8" s="66" t="n">
         <f aca="false">IF($H8=1,$I8*1000+COUNTIFS($I$4:$I$483,$I8,$J$4:$J$483,"&lt;"&amp;$J8)+1,"")</f>
-        <v>5003</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11211,7 +11215,7 @@
       </c>
       <c r="K9" s="66" t="n">
         <f aca="false">IF($H9=1,$I9*1000+COUNTIFS($I$4:$I$483,$I9,$J$4:$J$483,"&lt;"&amp;$J9)+1,"")</f>
-        <v>6003</v>
+        <v>6007</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11255,7 +11259,7 @@
       </c>
       <c r="K10" s="66" t="n">
         <f aca="false">IF($H10=1,$I10*1000+COUNTIFS($I$4:$I$483,$I10,$J$4:$J$483,"&lt;"&amp;$J10)+1,"")</f>
-        <v>7002</v>
+        <v>7004</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11299,7 +11303,7 @@
       </c>
       <c r="K11" s="66" t="n">
         <f aca="false">IF($H11=1,$I11*1000+COUNTIFS($I$4:$I$483,$I11,$J$4:$J$483,"&lt;"&amp;$J11)+1,"")</f>
-        <v>8001</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11343,7 +11347,7 @@
       </c>
       <c r="K12" s="66" t="n">
         <f aca="false">IF($H12=1,$I12*1000+COUNTIFS($I$4:$I$483,$I12,$J$4:$J$483,"&lt;"&amp;$J12)+1,"")</f>
-        <v>9001</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11387,7 +11391,7 @@
       </c>
       <c r="K13" s="66" t="n">
         <f aca="false">IF($H13=1,$I13*1000+COUNTIFS($I$4:$I$483,$I13,$J$4:$J$483,"&lt;"&amp;$J13)+1,"")</f>
-        <v>10003</v>
+        <v>10005</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11431,7 +11435,7 @@
       </c>
       <c r="K14" s="66" t="n">
         <f aca="false">IF($H14=1,$I14*1000+COUNTIFS($I$4:$I$483,$I14,$J$4:$J$483,"&lt;"&amp;$J14)+1,"")</f>
-        <v>11002</v>
+        <v>11004</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11475,7 +11479,7 @@
       </c>
       <c r="K15" s="66" t="n">
         <f aca="false">IF($H15=1,$I15*1000+COUNTIFS($I$4:$I$483,$I15,$J$4:$J$483,"&lt;"&amp;$J15)+1,"")</f>
-        <v>12001</v>
+        <v>12005</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11519,7 +11523,7 @@
       </c>
       <c r="K16" s="66" t="n">
         <f aca="false">IF($H16=1,$I16*1000+COUNTIFS($I$4:$I$483,$I16,$J$4:$J$483,"&lt;"&amp;$J16)+1,"")</f>
-        <v>13001</v>
+        <v>13004</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11687,7 +11691,7 @@
       </c>
       <c r="I20" s="69" t="n">
         <f aca="false">IF($H20=1,INT(($G20-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="66" t="n">
         <f aca="false">IF($H20=1,$G20*10000+ROW(),"")</f>
@@ -11695,7 +11699,7 @@
       </c>
       <c r="K20" s="66" t="n">
         <f aca="false">IF($H20=1,$I20*1000+COUNTIFS($I$4:$I$483,$I20,$J$4:$J$483,"&lt;"&amp;$J20)+1,"")</f>
-        <v>1005</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11731,7 +11735,7 @@
       </c>
       <c r="I21" s="69" t="n">
         <f aca="false">IF($H21=1,INT(($G21-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="66" t="n">
         <f aca="false">IF($H21=1,$G21*10000+ROW(),"")</f>
@@ -11739,7 +11743,7 @@
       </c>
       <c r="K21" s="66" t="n">
         <f aca="false">IF($H21=1,$I21*1000+COUNTIFS($I$4:$I$483,$I21,$J$4:$J$483,"&lt;"&amp;$J21)+1,"")</f>
-        <v>2004</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11775,7 +11779,7 @@
       </c>
       <c r="I22" s="69" t="n">
         <f aca="false">IF($H22=1,INT(($G22-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="66" t="n">
         <f aca="false">IF($H22=1,$G22*10000+ROW(),"")</f>
@@ -11783,7 +11787,7 @@
       </c>
       <c r="K22" s="66" t="n">
         <f aca="false">IF($H22=1,$I22*1000+COUNTIFS($I$4:$I$483,$I22,$J$4:$J$483,"&lt;"&amp;$J22)+1,"")</f>
-        <v>3003</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11819,7 +11823,7 @@
       </c>
       <c r="I23" s="69" t="n">
         <f aca="false">IF($H23=1,INT(($G23-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="66" t="n">
         <f aca="false">IF($H23=1,$G23*10000+ROW(),"")</f>
@@ -11827,7 +11831,7 @@
       </c>
       <c r="K23" s="66" t="n">
         <f aca="false">IF($H23=1,$I23*1000+COUNTIFS($I$4:$I$483,$I23,$J$4:$J$483,"&lt;"&amp;$J23)+1,"")</f>
-        <v>4004</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11863,7 +11867,7 @@
       </c>
       <c r="I24" s="69" t="n">
         <f aca="false">IF($H24=1,INT(($G24-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" s="66" t="n">
         <f aca="false">IF($H24=1,$G24*10000+ROW(),"")</f>
@@ -11871,7 +11875,7 @@
       </c>
       <c r="K24" s="66" t="n">
         <f aca="false">IF($H24=1,$I24*1000+COUNTIFS($I$4:$I$483,$I24,$J$4:$J$483,"&lt;"&amp;$J24)+1,"")</f>
-        <v>5004</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11907,7 +11911,7 @@
       </c>
       <c r="I25" s="69" t="n">
         <f aca="false">IF($H25=1,INT(($G25-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J25" s="66" t="n">
         <f aca="false">IF($H25=1,$G25*10000+ROW(),"")</f>
@@ -11915,7 +11919,7 @@
       </c>
       <c r="K25" s="66" t="n">
         <f aca="false">IF($H25=1,$I25*1000+COUNTIFS($I$4:$I$483,$I25,$J$4:$J$483,"&lt;"&amp;$J25)+1,"")</f>
-        <v>6005</v>
+        <v>7001</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11951,7 +11955,7 @@
       </c>
       <c r="I26" s="69" t="n">
         <f aca="false">IF($H26=1,INT(($G26-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="66" t="n">
         <f aca="false">IF($H26=1,$G26*10000+ROW(),"")</f>
@@ -11959,7 +11963,7 @@
       </c>
       <c r="K26" s="66" t="n">
         <f aca="false">IF($H26=1,$I26*1000+COUNTIFS($I$4:$I$483,$I26,$J$4:$J$483,"&lt;"&amp;$J26)+1,"")</f>
-        <v>7005</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11995,7 +11999,7 @@
       </c>
       <c r="I27" s="69" t="n">
         <f aca="false">IF($H27=1,INT(($G27-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="66" t="n">
         <f aca="false">IF($H27=1,$G27*10000+ROW(),"")</f>
@@ -12003,7 +12007,7 @@
       </c>
       <c r="K27" s="66" t="n">
         <f aca="false">IF($H27=1,$I27*1000+COUNTIFS($I$4:$I$483,$I27,$J$4:$J$483,"&lt;"&amp;$J27)+1,"")</f>
-        <v>8002</v>
+        <v>9001</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12039,7 +12043,7 @@
       </c>
       <c r="I28" s="69" t="n">
         <f aca="false">IF($H28=1,INT(($G28-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="66" t="n">
         <f aca="false">IF($H28=1,$G28*10000+ROW(),"")</f>
@@ -12047,7 +12051,7 @@
       </c>
       <c r="K28" s="66" t="n">
         <f aca="false">IF($H28=1,$I28*1000+COUNTIFS($I$4:$I$483,$I28,$J$4:$J$483,"&lt;"&amp;$J28)+1,"")</f>
-        <v>9005</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12083,7 +12087,7 @@
       </c>
       <c r="I29" s="69" t="n">
         <f aca="false">IF($H29=1,INT(($G29-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="66" t="n">
         <f aca="false">IF($H29=1,$G29*10000+ROW(),"")</f>
@@ -12091,7 +12095,7 @@
       </c>
       <c r="K29" s="66" t="n">
         <f aca="false">IF($H29=1,$I29*1000+COUNTIFS($I$4:$I$483,$I29,$J$4:$J$483,"&lt;"&amp;$J29)+1,"")</f>
-        <v>10006</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12127,7 +12131,7 @@
       </c>
       <c r="I30" s="69" t="n">
         <f aca="false">IF($H30=1,INT(($G30-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="66" t="n">
         <f aca="false">IF($H30=1,$G30*10000+ROW(),"")</f>
@@ -12135,7 +12139,7 @@
       </c>
       <c r="K30" s="66" t="n">
         <f aca="false">IF($H30=1,$I30*1000+COUNTIFS($I$4:$I$483,$I30,$J$4:$J$483,"&lt;"&amp;$J30)+1,"")</f>
-        <v>11004</v>
+        <v>12001</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12171,7 +12175,7 @@
       </c>
       <c r="I31" s="69" t="n">
         <f aca="false">IF($H31=1,INT(($G31-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="66" t="n">
         <f aca="false">IF($H31=1,$G31*10000+ROW(),"")</f>
@@ -12179,7 +12183,7 @@
       </c>
       <c r="K31" s="66" t="n">
         <f aca="false">IF($H31=1,$I31*1000+COUNTIFS($I$4:$I$483,$I31,$J$4:$J$483,"&lt;"&amp;$J31)+1,"")</f>
-        <v>12002</v>
+        <v>13001</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12211,19 +12215,19 @@
       </c>
       <c r="H32" s="69" t="n">
         <f aca="false">IF($G32="",0,IF(AND($G32&gt;='Cash Flow'!$E$6,$G32&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="69" t="str">
         <f aca="false">IF($H32=1,INT(($G32-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J32" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="66" t="str">
         <f aca="false">IF($H32=1,$G32*10000+ROW(),"")</f>
-        <v>463250032</v>
-      </c>
-      <c r="K32" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K32" s="66" t="str">
         <f aca="false">IF($H32=1,$I32*1000+COUNTIFS($I$4:$I$483,$I32,$J$4:$J$483,"&lt;"&amp;$J32)+1,"")</f>
-        <v>13002</v>
+        <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12435,7 +12439,7 @@
       </c>
       <c r="I37" s="69" t="n">
         <f aca="false">IF($H37=1,INT(($G37-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J37" s="66" t="n">
         <f aca="false">IF($H37=1,$G37*10000+ROW(),"")</f>
@@ -12443,7 +12447,7 @@
       </c>
       <c r="K37" s="66" t="n">
         <f aca="false">IF($H37=1,$I37*1000+COUNTIFS($I$4:$I$483,$I37,$J$4:$J$483,"&lt;"&amp;$J37)+1,"")</f>
-        <v>5005</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12479,7 +12483,7 @@
       </c>
       <c r="I38" s="69" t="n">
         <f aca="false">IF($H38=1,INT(($G38-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J38" s="66" t="n">
         <f aca="false">IF($H38=1,$G38*10000+ROW(),"")</f>
@@ -12487,7 +12491,7 @@
       </c>
       <c r="K38" s="66" t="n">
         <f aca="false">IF($H38=1,$I38*1000+COUNTIFS($I$4:$I$483,$I38,$J$4:$J$483,"&lt;"&amp;$J38)+1,"")</f>
-        <v>9006</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13139,7 +13143,7 @@
       </c>
       <c r="I53" s="69" t="n">
         <f aca="false">IF($H53=1,INT(($G53-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J53" s="66" t="n">
         <f aca="false">IF($H53=1,$G53*10000+ROW(),"")</f>
@@ -13147,7 +13151,7 @@
       </c>
       <c r="K53" s="66" t="n">
         <f aca="false">IF($H53=1,$I53*1000+COUNTIFS($I$4:$I$483,$I53,$J$4:$J$483,"&lt;"&amp;$J53)+1,"")</f>
-        <v>5006</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13191,7 +13195,7 @@
       </c>
       <c r="K54" s="66" t="n">
         <f aca="false">IF($H54=1,$I54*1000+COUNTIFS($I$4:$I$483,$I54,$J$4:$J$483,"&lt;"&amp;$J54)+1,"")</f>
-        <v>10001</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13843,7 +13847,7 @@
       </c>
       <c r="I69" s="69" t="n">
         <f aca="false">IF($H69=1,INT(($G69-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J69" s="66" t="n">
         <f aca="false">IF($H69=1,$G69*10000+ROW(),"")</f>
@@ -13851,7 +13855,7 @@
       </c>
       <c r="K69" s="66" t="n">
         <f aca="false">IF($H69=1,$I69*1000+COUNTIFS($I$4:$I$483,$I69,$J$4:$J$483,"&lt;"&amp;$J69)+1,"")</f>
-        <v>5007</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13895,7 +13899,7 @@
       </c>
       <c r="K70" s="66" t="n">
         <f aca="false">IF($H70=1,$I70*1000+COUNTIFS($I$4:$I$483,$I70,$J$4:$J$483,"&lt;"&amp;$J70)+1,"")</f>
-        <v>10002</v>
+        <v>10004</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14503,7 +14507,7 @@
       </c>
       <c r="I84" s="69" t="n">
         <f aca="false">IF($H84=1,INT(($G84-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J84" s="66" t="n">
         <f aca="false">IF($H84=1,$G84*10000+ROW(),"")</f>
@@ -14511,7 +14515,7 @@
       </c>
       <c r="K84" s="66" t="n">
         <f aca="false">IF($H84=1,$I84*1000+COUNTIFS($I$4:$I$483,$I84,$J$4:$J$483,"&lt;"&amp;$J84)+1,"")</f>
-        <v>1006</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14555,7 +14559,7 @@
       </c>
       <c r="K85" s="66" t="n">
         <f aca="false">IF($H85=1,$I85*1000+COUNTIFS($I$4:$I$483,$I85,$J$4:$J$483,"&lt;"&amp;$J85)+1,"")</f>
-        <v>6001</v>
+        <v>6005</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14599,7 +14603,7 @@
       </c>
       <c r="K86" s="66" t="n">
         <f aca="false">IF($H86=1,$I86*1000+COUNTIFS($I$4:$I$483,$I86,$J$4:$J$483,"&lt;"&amp;$J86)+1,"")</f>
-        <v>10004</v>
+        <v>10006</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15207,7 +15211,7 @@
       </c>
       <c r="I100" s="69" t="n">
         <f aca="false">IF($H100=1,INT(($G100-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J100" s="66" t="n">
         <f aca="false">IF($H100=1,$G100*10000+ROW(),"")</f>
@@ -15215,7 +15219,7 @@
       </c>
       <c r="K100" s="66" t="n">
         <f aca="false">IF($H100=1,$I100*1000+COUNTIFS($I$4:$I$483,$I100,$J$4:$J$483,"&lt;"&amp;$J100)+1,"")</f>
-        <v>1007</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15259,7 +15263,7 @@
       </c>
       <c r="K101" s="66" t="n">
         <f aca="false">IF($H101=1,$I101*1000+COUNTIFS($I$4:$I$483,$I101,$J$4:$J$483,"&lt;"&amp;$J101)+1,"")</f>
-        <v>6002</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15303,7 +15307,7 @@
       </c>
       <c r="K102" s="66" t="n">
         <f aca="false">IF($H102=1,$I102*1000+COUNTIFS($I$4:$I$483,$I102,$J$4:$J$483,"&lt;"&amp;$J102)+1,"")</f>
-        <v>10005</v>
+        <v>10007</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15919,7 +15923,7 @@
       </c>
       <c r="K116" s="66" t="n">
         <f aca="false">IF($H116=1,$I116*1000+COUNTIFS($I$4:$I$483,$I116,$J$4:$J$483,"&lt;"&amp;$J116)+1,"")</f>
-        <v>2001</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15963,7 +15967,7 @@
       </c>
       <c r="K117" s="66" t="n">
         <f aca="false">IF($H117=1,$I117*1000+COUNTIFS($I$4:$I$483,$I117,$J$4:$J$483,"&lt;"&amp;$J117)+1,"")</f>
-        <v>6004</v>
+        <v>6008</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15999,7 +16003,7 @@
       </c>
       <c r="I118" s="69" t="n">
         <f aca="false">IF($H118=1,INT(($G118-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J118" s="66" t="n">
         <f aca="false">IF($H118=1,$G118*10000+ROW(),"")</f>
@@ -16007,7 +16011,7 @@
       </c>
       <c r="K118" s="66" t="n">
         <f aca="false">IF($H118=1,$I118*1000+COUNTIFS($I$4:$I$483,$I118,$J$4:$J$483,"&lt;"&amp;$J118)+1,"")</f>
-        <v>10007</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16623,7 +16627,7 @@
       </c>
       <c r="K132" s="66" t="n">
         <f aca="false">IF($H132=1,$I132*1000+COUNTIFS($I$4:$I$483,$I132,$J$4:$J$483,"&lt;"&amp;$J132)+1,"")</f>
-        <v>2003</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16659,7 +16663,7 @@
       </c>
       <c r="I133" s="69" t="n">
         <f aca="false">IF($H133=1,INT(($G133-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J133" s="66" t="n">
         <f aca="false">IF($H133=1,$G133*10000+ROW(),"")</f>
@@ -16667,7 +16671,7 @@
       </c>
       <c r="K133" s="66" t="n">
         <f aca="false">IF($H133=1,$I133*1000+COUNTIFS($I$4:$I$483,$I133,$J$4:$J$483,"&lt;"&amp;$J133)+1,"")</f>
-        <v>6006</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16711,7 +16715,7 @@
       </c>
       <c r="K134" s="66" t="n">
         <f aca="false">IF($H134=1,$I134*1000+COUNTIFS($I$4:$I$483,$I134,$J$4:$J$483,"&lt;"&amp;$J134)+1,"")</f>
-        <v>11001</v>
+        <v>11003</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17319,7 +17323,7 @@
       </c>
       <c r="I148" s="69" t="n">
         <f aca="false">IF($H148=1,INT(($G148-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J148" s="66" t="n">
         <f aca="false">IF($H148=1,$G148*10000+ROW(),"")</f>
@@ -17327,7 +17331,7 @@
       </c>
       <c r="K148" s="66" t="n">
         <f aca="false">IF($H148=1,$I148*1000+COUNTIFS($I$4:$I$483,$I148,$J$4:$J$483,"&lt;"&amp;$J148)+1,"")</f>
-        <v>2005</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17371,7 +17375,7 @@
       </c>
       <c r="K149" s="66" t="n">
         <f aca="false">IF($H149=1,$I149*1000+COUNTIFS($I$4:$I$483,$I149,$J$4:$J$483,"&lt;"&amp;$J149)+1,"")</f>
-        <v>5001</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17415,7 +17419,7 @@
       </c>
       <c r="K150" s="66" t="n">
         <f aca="false">IF($H150=1,$I150*1000+COUNTIFS($I$4:$I$483,$I150,$J$4:$J$483,"&lt;"&amp;$J150)+1,"")</f>
-        <v>7001</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17459,7 +17463,7 @@
       </c>
       <c r="K151" s="66" t="n">
         <f aca="false">IF($H151=1,$I151*1000+COUNTIFS($I$4:$I$483,$I151,$J$4:$J$483,"&lt;"&amp;$J151)+1,"")</f>
-        <v>9002</v>
+        <v>9005</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17503,7 +17507,7 @@
       </c>
       <c r="K152" s="66" t="n">
         <f aca="false">IF($H152=1,$I152*1000+COUNTIFS($I$4:$I$483,$I152,$J$4:$J$483,"&lt;"&amp;$J152)+1,"")</f>
-        <v>11003</v>
+        <v>11005</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17535,19 +17539,19 @@
       </c>
       <c r="H153" s="69" t="n">
         <f aca="false">IF($G153="",0,IF(AND($G153&gt;='Cash Flow'!$E$6,$G153&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I153" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="69" t="str">
         <f aca="false">IF($H153=1,INT(($G153-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J153" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J153" s="66" t="str">
         <f aca="false">IF($H153=1,$G153*10000+ROW(),"")</f>
-        <v>463250153</v>
-      </c>
-      <c r="K153" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K153" s="66" t="str">
         <f aca="false">IF($H153=1,$I153*1000+COUNTIFS($I$4:$I$483,$I153,$J$4:$J$483,"&lt;"&amp;$J153)+1,"")</f>
-        <v>13003</v>
+        <v/>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18023,7 +18027,7 @@
       </c>
       <c r="I164" s="69" t="n">
         <f aca="false">IF($H164=1,INT(($G164-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J164" s="66" t="n">
         <f aca="false">IF($H164=1,$G164*10000+ROW(),"")</f>
@@ -18031,7 +18035,7 @@
       </c>
       <c r="K164" s="66" t="n">
         <f aca="false">IF($H164=1,$I164*1000+COUNTIFS($I$4:$I$483,$I164,$J$4:$J$483,"&lt;"&amp;$J164)+1,"")</f>
-        <v>2006</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18075,7 +18079,7 @@
       </c>
       <c r="K165" s="66" t="n">
         <f aca="false">IF($H165=1,$I165*1000+COUNTIFS($I$4:$I$483,$I165,$J$4:$J$483,"&lt;"&amp;$J165)+1,"")</f>
-        <v>7003</v>
+        <v>7005</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18111,7 +18115,7 @@
       </c>
       <c r="I166" s="69" t="n">
         <f aca="false">IF($H166=1,INT(($G166-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J166" s="66" t="n">
         <f aca="false">IF($H166=1,$G166*10000+ROW(),"")</f>
@@ -18119,7 +18123,7 @@
       </c>
       <c r="K166" s="66" t="n">
         <f aca="false">IF($H166=1,$I166*1000+COUNTIFS($I$4:$I$483,$I166,$J$4:$J$483,"&lt;"&amp;$J166)+1,"")</f>
-        <v>11005</v>
+        <v>12002</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18727,7 +18731,7 @@
       </c>
       <c r="I180" s="69" t="n">
         <f aca="false">IF($H180=1,INT(($G180-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J180" s="66" t="n">
         <f aca="false">IF($H180=1,$G180*10000+ROW(),"")</f>
@@ -18735,7 +18739,7 @@
       </c>
       <c r="K180" s="66" t="n">
         <f aca="false">IF($H180=1,$I180*1000+COUNTIFS($I$4:$I$483,$I180,$J$4:$J$483,"&lt;"&amp;$J180)+1,"")</f>
-        <v>2007</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18779,7 +18783,7 @@
       </c>
       <c r="K181" s="66" t="n">
         <f aca="false">IF($H181=1,$I181*1000+COUNTIFS($I$4:$I$483,$I181,$J$4:$J$483,"&lt;"&amp;$J181)+1,"")</f>
-        <v>7004</v>
+        <v>7006</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18815,7 +18819,7 @@
       </c>
       <c r="I182" s="69" t="n">
         <f aca="false">IF($H182=1,INT(($G182-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J182" s="66" t="n">
         <f aca="false">IF($H182=1,$G182*10000+ROW(),"")</f>
@@ -18823,7 +18827,7 @@
       </c>
       <c r="K182" s="66" t="n">
         <f aca="false">IF($H182=1,$I182*1000+COUNTIFS($I$4:$I$483,$I182,$J$4:$J$483,"&lt;"&amp;$J182)+1,"")</f>
-        <v>11006</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19439,7 +19443,7 @@
       </c>
       <c r="K196" s="66" t="n">
         <f aca="false">IF($H196=1,$I196*1000+COUNTIFS($I$4:$I$483,$I196,$J$4:$J$483,"&lt;"&amp;$J196)+1,"")</f>
-        <v>3001</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19475,7 +19479,7 @@
       </c>
       <c r="I197" s="69" t="n">
         <f aca="false">IF($H197=1,INT(($G197-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J197" s="66" t="n">
         <f aca="false">IF($H197=1,$G197*10000+ROW(),"")</f>
@@ -19483,7 +19487,7 @@
       </c>
       <c r="K197" s="66" t="n">
         <f aca="false">IF($H197=1,$I197*1000+COUNTIFS($I$4:$I$483,$I197,$J$4:$J$483,"&lt;"&amp;$J197)+1,"")</f>
-        <v>7006</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19519,7 +19523,7 @@
       </c>
       <c r="I198" s="69" t="n">
         <f aca="false">IF($H198=1,INT(($G198-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J198" s="66" t="n">
         <f aca="false">IF($H198=1,$G198*10000+ROW(),"")</f>
@@ -19527,7 +19531,7 @@
       </c>
       <c r="K198" s="66" t="n">
         <f aca="false">IF($H198=1,$I198*1000+COUNTIFS($I$4:$I$483,$I198,$J$4:$J$483,"&lt;"&amp;$J198)+1,"")</f>
-        <v>11007</v>
+        <v>12004</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20143,7 +20147,7 @@
       </c>
       <c r="K212" s="66" t="n">
         <f aca="false">IF($H212=1,$I212*1000+COUNTIFS($I$4:$I$483,$I212,$J$4:$J$483,"&lt;"&amp;$J212)+1,"")</f>
-        <v>4001</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20179,7 +20183,7 @@
       </c>
       <c r="I213" s="69" t="n">
         <f aca="false">IF($H213=1,INT(($G213-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J213" s="66" t="n">
         <f aca="false">IF($H213=1,$G213*10000+ROW(),"")</f>
@@ -20187,7 +20191,7 @@
       </c>
       <c r="K213" s="66" t="n">
         <f aca="false">IF($H213=1,$I213*1000+COUNTIFS($I$4:$I$483,$I213,$J$4:$J$483,"&lt;"&amp;$J213)+1,"")</f>
-        <v>8003</v>
+        <v>9002</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20223,7 +20227,7 @@
       </c>
       <c r="I214" s="69" t="n">
         <f aca="false">IF($H214=1,INT(($G214-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J214" s="66" t="n">
         <f aca="false">IF($H214=1,$G214*10000+ROW(),"")</f>
@@ -20231,7 +20235,7 @@
       </c>
       <c r="K214" s="66" t="n">
         <f aca="false">IF($H214=1,$I214*1000+COUNTIFS($I$4:$I$483,$I214,$J$4:$J$483,"&lt;"&amp;$J214)+1,"")</f>
-        <v>12003</v>
+        <v>13002</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20847,7 +20851,7 @@
       </c>
       <c r="K228" s="66" t="n">
         <f aca="false">IF($H228=1,$I228*1000+COUNTIFS($I$4:$I$483,$I228,$J$4:$J$483,"&lt;"&amp;$J228)+1,"")</f>
-        <v>4002</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20883,7 +20887,7 @@
       </c>
       <c r="I229" s="69" t="n">
         <f aca="false">IF($H229=1,INT(($G229-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J229" s="66" t="n">
         <f aca="false">IF($H229=1,$G229*10000+ROW(),"")</f>
@@ -20891,7 +20895,7 @@
       </c>
       <c r="K229" s="66" t="n">
         <f aca="false">IF($H229=1,$I229*1000+COUNTIFS($I$4:$I$483,$I229,$J$4:$J$483,"&lt;"&amp;$J229)+1,"")</f>
-        <v>8004</v>
+        <v>9003</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20927,7 +20931,7 @@
       </c>
       <c r="I230" s="69" t="n">
         <f aca="false">IF($H230=1,INT(($G230-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J230" s="66" t="n">
         <f aca="false">IF($H230=1,$G230*10000+ROW(),"")</f>
@@ -20935,7 +20939,7 @@
       </c>
       <c r="K230" s="66" t="n">
         <f aca="false">IF($H230=1,$I230*1000+COUNTIFS($I$4:$I$483,$I230,$J$4:$J$483,"&lt;"&amp;$J230)+1,"")</f>
-        <v>12004</v>
+        <v>13003</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21543,7 +21547,7 @@
       </c>
       <c r="I244" s="69" t="n">
         <f aca="false">IF($H244=1,INT(($G244-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J244" s="66" t="n">
         <f aca="false">IF($H244=1,$G244*10000+ROW(),"")</f>
@@ -21551,7 +21555,7 @@
       </c>
       <c r="K244" s="66" t="n">
         <f aca="false">IF($H244=1,$I244*1000+COUNTIFS($I$4:$I$483,$I244,$J$4:$J$483,"&lt;"&amp;$J244)+1,"")</f>
-        <v>4005</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21595,7 +21599,7 @@
       </c>
       <c r="K245" s="66" t="n">
         <f aca="false">IF($H245=1,$I245*1000+COUNTIFS($I$4:$I$483,$I245,$J$4:$J$483,"&lt;"&amp;$J245)+1,"")</f>
-        <v>9003</v>
+        <v>9006</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21627,19 +21631,19 @@
       </c>
       <c r="H246" s="69" t="n">
         <f aca="false">IF($G246="",0,IF(AND($G246&gt;='Cash Flow'!$E$6,$G246&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I246" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I246" s="69" t="str">
         <f aca="false">IF($H246=1,INT(($G246-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J246" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J246" s="66" t="str">
         <f aca="false">IF($H246=1,$G246*10000+ROW(),"")</f>
-        <v>463250246</v>
-      </c>
-      <c r="K246" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K246" s="66" t="str">
         <f aca="false">IF($H246=1,$I246*1000+COUNTIFS($I$4:$I$483,$I246,$J$4:$J$483,"&lt;"&amp;$J246)+1,"")</f>
-        <v>13004</v>
+        <v/>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22255,7 +22259,7 @@
       </c>
       <c r="K260" s="66" t="n">
         <f aca="false">IF($H260=1,$I260*1000+COUNTIFS($I$4:$I$483,$I260,$J$4:$J$483,"&lt;"&amp;$J260)+1,"")</f>
-        <v>5002</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22299,7 +22303,7 @@
       </c>
       <c r="K261" s="66" t="n">
         <f aca="false">IF($H261=1,$I261*1000+COUNTIFS($I$4:$I$483,$I261,$J$4:$J$483,"&lt;"&amp;$J261)+1,"")</f>
-        <v>9004</v>
+        <v>9007</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22331,19 +22335,19 @@
       </c>
       <c r="H262" s="69" t="n">
         <f aca="false">IF($G262="",0,IF(AND($G262&gt;='Cash Flow'!$E$6,$G262&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I262" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" s="69" t="str">
         <f aca="false">IF($H262=1,INT(($G262-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J262" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J262" s="66" t="str">
         <f aca="false">IF($H262=1,$G262*10000+ROW(),"")</f>
-        <v>463260262</v>
-      </c>
-      <c r="K262" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K262" s="66" t="str">
         <f aca="false">IF($H262=1,$I262*1000+COUNTIFS($I$4:$I$483,$I262,$J$4:$J$483,"&lt;"&amp;$J262)+1,"")</f>
-        <v>13005</v>
+        <v/>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Cash Flow'!$A$1:$K$284</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$32</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$40</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Recurring!$A$1:$J$38</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Recurring!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$J$28</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="160">
   <si>
     <t xml:space="preserve">WEEKLY CASH FLOW SURVIVAL WORKSHEET</t>
   </si>
@@ -90,13 +90,52 @@
     <t xml:space="preserve">Black text</t>
   </si>
   <si>
-    <t xml:space="preserve">A formula. Do not overwrite it or the model stops updating.</t>
+    <t xml:space="preserve">A formula that does the arithmetic — running balances, week totals, the Summary. Leave these alone.</t>
   </si>
   <si>
     <t xml:space="preserve">Green text</t>
   </si>
   <si>
-    <t xml:space="preserve">A formula that pulls from another tab.</t>
+    <t xml:space="preserve">A formula that pulls a transaction in from the Recurring tab. You CAN type straight over these — see below.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WHEN A FORMULA IS IN YOUR WAY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type over it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The green cells in the week blocks — Description, Scheduled Date, Type, Scheduled Amount — are safe to overwrite. Type a real date or a different amount straight into the cell. The running balance, the week totals and the Summary all keep working, because they read the cell rather than the formula behind it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What you give up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That one row stops following the Recurring tab. Edit the transaction later and this row will not move with it. Everything else on the sheet is unaffected.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To skip a bill this week</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clear the Description cell. The row empties out and drops from the week's totals, leaving the rest of the week intact.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To add a one-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type a description, date, Income or Expense, and an amount into any blank row in a week block. Nothing needs to exist on the Recurring tab first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To pay part of a bill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leave the scheduled row alone and put what you actually paid in Amount Paid. That column is yours already and always wins over the scheduled figure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To get the formula back</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Undo, or copy the same cell from the row above or below and let Excel adjust it.</t>
   </si>
   <si>
     <t xml:space="preserve">FREQUENCIES THE SHEET UNDERSTANDS</t>
@@ -312,7 +351,7 @@
     <t xml:space="preserve">This sheet projects 13 weeks from the start date. Week 1 begins on the start date and each week runs Friday through Thursday.</t>
   </si>
   <si>
-    <t xml:space="preserve">Blue = you type it.  Black/green = formulas, leave them alone.  A yellow 'Amount Paid' cell means that transaction is due or overdue and still unrecorded.</t>
+    <t xml:space="preserve">A yellow 'Amount Paid' cell means that transaction is due or overdue and still unrecorded.  The green transaction cells are safe to type straight over when a date or amount is wrong — the balances keep working.  See the Instructions tab.</t>
   </si>
   <si>
     <t xml:space="preserve">Starting balance:</t>
@@ -343,15 +382,6 @@
   </si>
   <si>
     <t xml:space="preserve">WEEKLY VARIABLE EXPENSES — type what you spend this week (groceries, gas, eating out, anything)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Groceries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gas / fuel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eating out</t>
   </si>
   <si>
     <t xml:space="preserve">WEEK 1 TOTALS</t>
@@ -1331,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:C32"/>
+  <dimension ref="B2:C40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1416,7 +1446,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="8" t="s">
         <v>18</v>
       </c>
@@ -1424,7 +1454,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="s">
         <v>20</v>
       </c>
@@ -1437,7 +1467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
         <v>23</v>
       </c>
@@ -1445,7 +1475,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="10" t="s">
         <v>25</v>
       </c>
@@ -1453,7 +1483,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="10" t="s">
         <v>27</v>
       </c>
@@ -1461,7 +1491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="10" t="s">
         <v>29</v>
       </c>
@@ -1469,7 +1499,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="10" t="s">
         <v>31</v>
       </c>
@@ -1477,65 +1507,118 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
+    <row r="24" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="10" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11" t="s">
+      <c r="C24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="12" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C27" s="12" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="C27" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" s="12" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="10" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="C28" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" s="12" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="10" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C32" s="12" t="s">
+      <c r="C29" s="5" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1571,44 +1654,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1616,28 +1699,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>90</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>46239</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -1646,28 +1729,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>790</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F6" s="22" t="n">
         <v>46241</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="J6" s="19"/>
     </row>
@@ -1676,28 +1759,28 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>21.1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>46238</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -1706,28 +1789,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D8" s="21" t="n">
         <v>20</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F8" s="22" t="n">
         <v>46239</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J8" s="19"/>
     </row>
@@ -1736,28 +1819,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>10</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F9" s="17" t="n">
         <v>46239</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1766,28 +1849,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D10" s="21" t="n">
         <v>4.99</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F10" s="22" t="n">
         <v>46241</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J10" s="19"/>
     </row>
@@ -1796,28 +1879,28 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>500</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>46241</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -1826,28 +1909,28 @@
         <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D12" s="21" t="n">
         <v>163.5</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F12" s="22" t="n">
         <v>46244</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J12" s="19"/>
     </row>
@@ -1856,28 +1939,28 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>2.99</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>46247</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -1886,28 +1969,28 @@
         <v>10</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D14" s="21" t="n">
         <v>350</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>46248</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J14" s="19"/>
     </row>
@@ -1916,28 +1999,28 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>74</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>61</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>171.1</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F15" s="17" t="n">
         <v>46250</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -1946,28 +2029,28 @@
         <v>12</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>45</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F16" s="22" t="n">
         <v>46250</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J16" s="19"/>
     </row>
@@ -1976,28 +2059,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>16.99</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F17" s="17" t="n">
         <v>46252</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2006,28 +2089,28 @@
         <v>14</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>13.7</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F18" s="22" t="n">
         <v>46259</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="J18" s="19"/>
     </row>
@@ -2036,28 +2119,28 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>43.87</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F19" s="17" t="n">
         <v>46259</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -2066,28 +2149,28 @@
         <v>16</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D20" s="21" t="n">
         <v>150</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F20" s="22" t="n">
         <v>46264</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="J20" s="19"/>
     </row>
@@ -2096,28 +2179,28 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>143.37</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F21" s="17" t="n">
         <v>46265</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J21" s="6"/>
     </row>
@@ -2305,17 +2388,17 @@
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="12" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="12" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="23" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -2330,19 +2413,19 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation allowBlank="true" error="Pick one of the listed values." errorStyle="stop" errorTitle="Not a valid entry" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C34" type="list">
+    <dataValidation allowBlank="true" error="The Schedule tab only recognises the listed values, so anything else will not generate dates. Choose Yes to enter it anyway." errorStyle="warning" errorTitle="Not one of the listed values" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5:C34" type="list">
       <formula1>"Income,Expense"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick one of the listed values." errorStyle="stop" errorTitle="Not a valid entry" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E34" type="list">
+    <dataValidation allowBlank="true" error="The Schedule tab only recognises the listed values, so anything else will not generate dates. Choose Yes to enter it anyway." errorStyle="warning" errorTitle="Not one of the listed values" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E5:E34" type="list">
       <formula1>"Weekly,Every 2 Weeks,Monthly,Twice a Month,One Time"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick one of the listed values." errorStyle="stop" errorTitle="Not a valid entry" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G34" type="list">
+    <dataValidation allowBlank="true" error="The Schedule tab only recognises the listed values, so anything else will not generate dates. Choose Yes to enter it anyway." errorStyle="warning" errorTitle="Not one of the listed values" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G34" type="list">
       <formula1>"None,Move Before,Move After"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Pick one of the listed values." errorStyle="stop" errorTitle="Not a valid entry" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H34" type="list">
+    <dataValidation allowBlank="true" error="The Schedule tab only recognises the listed values, so anything else will not generate dates. Choose Yes to enter it anyway." errorStyle="warning" errorTitle="Not one of the listed values" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H34" type="list">
       <formula1>"Yes,No"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -2383,28 +2466,28 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>1250</v>
+        <v>71.17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="E6" s="25" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="G6" s="26" t="str">
         <f aca="false">IF($E$6="","",IF(WEEKDAY($E$6,2)=5,"","! That is a "&amp;TEXT($E$6,"dddd")&amp;". Weeks run Friday to Thursday — use the Friday on or before the date you want to start."))</f>
@@ -2413,7 +2496,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E7" s="24" t="n">
         <v>200</v>
@@ -2421,39 +2504,39 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="27" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="true">TODAY()</f>
-        <v>46240</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="23" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="23" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="29" t="str">
         <f aca="false">"WEEK 1     "&amp;TEXT($E$6+0,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+0+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 1     Fri, Jul 31   through   Thu, Aug 6, 2026</v>
+        <v>WEEK 1     Fri, Aug 7   through   Thu, Aug 13, 2026</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
       <c r="G13" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="32" t="n">
         <f aca="false">$E$5</f>
-        <v>1250</v>
+        <v>71.17</v>
       </c>
       <c r="J13" s="30"/>
       <c r="K13" s="26" t="str">
@@ -2463,111 +2546,111 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: Claude</v>
+        <v>Compunnel Software (paycheck)</v>
       </c>
       <c r="C15" s="34" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$G$4:$G$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="D15" s="35" t="str">
         <f aca="false">IF($B15="","",INDEX(Schedule!$D$4:$D$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$E$4:$E$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>21.1</v>
+        <v>790</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="36" t="n">
         <f aca="false">IF($B15="","",IF($F15&lt;&gt;"",$F15,$E15))</f>
-        <v>21.1</v>
+        <v>790</v>
       </c>
       <c r="H15" s="36" t="n">
         <f aca="false">IF($B15="",0,IF($D15="Income",$G15,-$G15))</f>
-        <v>-21.1</v>
+        <v>790</v>
       </c>
       <c r="I15" s="37" t="n">
         <f aca="false">IF($B15="","",$I$13+SUM($H$15:$H15))</f>
-        <v>1228.9</v>
+        <v>861.17</v>
       </c>
       <c r="J15" s="38" t="str">
         <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>PAST DUE</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Google One</v>
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$G$4:$G$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="D16" s="35" t="str">
         <f aca="false">IF($B16="","",INDEX(Schedule!$D$4:$D$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$E$4:$E$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>4.99</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="36" t="n">
         <f aca="false">IF($B16="","",IF($F16&lt;&gt;"",$F16,$E16))</f>
-        <v>90</v>
+        <v>4.99</v>
       </c>
       <c r="H16" s="36" t="n">
         <f aca="false">IF($B16="",0,IF($D16="Income",$G16,-$G16))</f>
-        <v>90</v>
+        <v>-4.99</v>
       </c>
       <c r="I16" s="37" t="n">
         <f aca="false">IF($B16="","",$I$13+SUM($H$15:$H16))</f>
-        <v>1318.9</v>
+        <v>856.18</v>
       </c>
       <c r="J16" s="38" t="str">
         <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>PAST DUE</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>OpenAI</v>
+        <v>Upstart (loan)</v>
       </c>
       <c r="C17" s="34" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$G$4:$G$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="D17" s="35" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$D$4:$D$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
@@ -2575,34 +2658,34 @@
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$E$4:$E$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="36" t="n">
         <f aca="false">IF($B17="","",IF($F17&lt;&gt;"",$F17,$E17))</f>
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="H17" s="36" t="n">
         <f aca="false">IF($B17="",0,IF($D17="Income",$G17,-$G17))</f>
-        <v>-20</v>
+        <v>-500</v>
       </c>
       <c r="I17" s="37" t="n">
         <f aca="false">IF($B17="","",$I$13+SUM($H$15:$H17))</f>
-        <v>1298.9</v>
+        <v>356.18</v>
       </c>
       <c r="J17" s="38" t="str">
         <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>PAST DUE</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Obsidian</v>
+        <v>Central Maine Power Co.</v>
       </c>
       <c r="C18" s="34" t="n">
         <f aca="false">IF($B18="","",INDEX(Schedule!$G$4:$G$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="D18" s="35" t="str">
         <f aca="false">IF($B18="","",INDEX(Schedule!$D$4:$D$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
@@ -2610,94 +2693,94 @@
       </c>
       <c r="E18" s="36" t="n">
         <f aca="false">IF($B18="","",INDEX(Schedule!$E$4:$E$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>10</v>
+        <v>163.5</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="36" t="n">
         <f aca="false">IF($B18="","",IF($F18&lt;&gt;"",$F18,$E18))</f>
-        <v>10</v>
+        <v>163.5</v>
       </c>
       <c r="H18" s="36" t="n">
         <f aca="false">IF($B18="",0,IF($D18="Income",$G18,-$G18))</f>
-        <v>-10</v>
+        <v>-163.5</v>
       </c>
       <c r="I18" s="37" t="n">
         <f aca="false">IF($B18="","",$I$13+SUM($H$15:$H18))</f>
-        <v>1288.9</v>
+        <v>192.68</v>
       </c>
       <c r="J18" s="38" t="str">
         <f aca="true">IF($B18="","",IF($F18&lt;&gt;"","PAID",IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>PAST DUE</v>
+        <v>DUE</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C19" s="34" t="n">
         <f aca="false">IF($B19="","",INDEX(Schedule!$G$4:$G$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46246</v>
       </c>
       <c r="D19" s="35" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$D$4:$D$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E19" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E19" s="36" t="n">
         <f aca="false">IF($B19="","",INDEX(Schedule!$E$4:$E$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F19" s="16"/>
-      <c r="G19" s="36" t="str">
+      <c r="G19" s="36" t="n">
         <f aca="false">IF($B19="","",IF($F19&lt;&gt;"",$F19,$E19))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H19" s="36" t="n">
         <f aca="false">IF($B19="",0,IF($D19="Income",$G19,-$G19))</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I19" s="37" t="n">
         <f aca="false">IF($B19="","",$I$13+SUM($H$15:$H19))</f>
-        <v/>
+        <v>282.68</v>
       </c>
       <c r="J19" s="38" t="str">
         <f aca="true">IF($B19="","",IF($F19&lt;&gt;"","PAID",IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>DUE</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C20" s="34" t="str">
+        <v>Apple: iCloud</v>
+      </c>
+      <c r="C20" s="34" t="n">
         <f aca="false">IF($B20="","",INDEX(Schedule!$G$4:$G$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46247</v>
       </c>
       <c r="D20" s="35" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$D$4:$D$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E20" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E20" s="36" t="n">
         <f aca="false">IF($B20="","",INDEX(Schedule!$E$4:$E$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>2.99</v>
       </c>
       <c r="F20" s="16"/>
-      <c r="G20" s="36" t="str">
+      <c r="G20" s="36" t="n">
         <f aca="false">IF($B20="","",IF($F20&lt;&gt;"",$F20,$E20))</f>
-        <v/>
+        <v>2.99</v>
       </c>
       <c r="H20" s="36" t="n">
         <f aca="false">IF($B20="",0,IF($D20="Income",$G20,-$G20))</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="37" t="str">
+        <v>-2.99</v>
+      </c>
+      <c r="I20" s="37" t="n">
         <f aca="false">IF($B20="","",$I$13+SUM($H$15:$H20))</f>
-        <v/>
+        <v>279.69</v>
       </c>
       <c r="J20" s="38" t="str">
         <f aca="true">IF($B20="","",IF($F20&lt;&gt;"","PAID",IF($C20&lt;TODAY(),"PAST DUE",IF($C20&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>DUE</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2842,7 +2925,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="40"/>
@@ -2854,83 +2937,71 @@
       <c r="J25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="6" t="s">
-        <v>104</v>
-      </c>
+      <c r="B26" s="6"/>
       <c r="C26" s="8"/>
       <c r="D26" s="38" t="str">
         <f aca="false">IF($B26="","","Expense")</f>
-        <v>Expense</v>
-      </c>
-      <c r="E26" s="16" t="n">
-        <v>120</v>
-      </c>
+        <v/>
+      </c>
+      <c r="E26" s="16"/>
       <c r="F26" s="8"/>
-      <c r="G26" s="36" t="n">
+      <c r="G26" s="36" t="str">
         <f aca="false">IF($B26="","",N($E26))</f>
-        <v>120</v>
+        <v/>
       </c>
       <c r="H26" s="36" t="n">
         <f aca="false">IF($B26="",0,-N($E26))</f>
-        <v>-120</v>
-      </c>
-      <c r="I26" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="37" t="str">
         <f aca="false">IF($B26="","",$I$13+SUM($H$15:$H26))</f>
-        <v>1168.9</v>
+        <v/>
       </c>
       <c r="J26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="6" t="s">
-        <v>105</v>
-      </c>
+      <c r="B27" s="6"/>
       <c r="C27" s="8"/>
       <c r="D27" s="38" t="str">
         <f aca="false">IF($B27="","","Expense")</f>
-        <v>Expense</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>60</v>
-      </c>
+        <v/>
+      </c>
+      <c r="E27" s="16"/>
       <c r="F27" s="8"/>
-      <c r="G27" s="36" t="n">
+      <c r="G27" s="36" t="str">
         <f aca="false">IF($B27="","",N($E27))</f>
-        <v>60</v>
+        <v/>
       </c>
       <c r="H27" s="36" t="n">
         <f aca="false">IF($B27="",0,-N($E27))</f>
-        <v>-60</v>
-      </c>
-      <c r="I27" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="37" t="str">
         <f aca="false">IF($B27="","",$I$13+SUM($H$15:$H27))</f>
-        <v>1108.9</v>
+        <v/>
       </c>
       <c r="J27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="6" t="s">
-        <v>106</v>
-      </c>
+      <c r="B28" s="6"/>
       <c r="C28" s="8"/>
       <c r="D28" s="38" t="str">
         <f aca="false">IF($B28="","","Expense")</f>
-        <v>Expense</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>35</v>
-      </c>
+        <v/>
+      </c>
+      <c r="E28" s="16"/>
       <c r="F28" s="8"/>
-      <c r="G28" s="36" t="n">
+      <c r="G28" s="36" t="str">
         <f aca="false">IF($B28="","",N($E28))</f>
-        <v>35</v>
+        <v/>
       </c>
       <c r="H28" s="36" t="n">
         <f aca="false">IF($B28="",0,-N($E28))</f>
-        <v>-35</v>
-      </c>
-      <c r="I28" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="37" t="str">
         <f aca="false">IF($B28="","",$I$13+SUM($H$15:$H28))</f>
-        <v>1073.9</v>
+        <v/>
       </c>
       <c r="J28" s="8"/>
     </row>
@@ -3005,13 +3076,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="41" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
       <c r="E32" s="43" t="n">
         <f aca="false">SUM($E$15:$E$31)</f>
-        <v>356.1</v>
+        <v>1551.48</v>
       </c>
       <c r="F32" s="43" t="n">
         <f aca="false">SUM($F$15:$F$24)</f>
@@ -3019,15 +3090,15 @@
       </c>
       <c r="G32" s="43" t="n">
         <f aca="false">SUM($G$15:$G$31)</f>
-        <v>356.1</v>
+        <v>1551.48</v>
       </c>
       <c r="H32" s="43" t="n">
         <f aca="false">SUM($H$15:$H$31)</f>
-        <v>-176.1</v>
+        <v>208.52</v>
       </c>
       <c r="I32" s="44" t="n">
         <f aca="false">$I$13+SUM($H$15:$H$31)</f>
-        <v>1073.9</v>
+        <v>279.69</v>
       </c>
       <c r="J32" s="45" t="str">
         <f aca="false">IF($I$32&lt;0,"SHORTFALL",IF($I$32&lt;$E$7,"TIGHT","OK"))</f>
@@ -3035,25 +3106,25 @@
       </c>
       <c r="K32" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$15:$D$31,"Income",$G$15:$G$31),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$15:$D$31,"Expense",$G$15:$G$31),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$32,"$#,##0.00")</f>
-        <v>Income $90.00   less expenses $266.10   =  net -$176.10</v>
+        <v>Income $880.00   less expenses $671.48   =  net $208.52</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="29" t="str">
         <f aca="false">"WEEK 2     "&amp;TEXT($E$6+7,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+7+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 2     Fri, Aug 7   through   Thu, Aug 13, 2026</v>
+        <v>WEEK 2     Fri, Aug 14   through   Thu, Aug 20, 2026</v>
       </c>
       <c r="C34" s="30"/>
       <c r="D34" s="30"/>
       <c r="E34" s="30"/>
       <c r="F34" s="30"/>
       <c r="G34" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H34" s="30"/>
       <c r="I34" s="32" t="n">
         <f aca="false">$I$32</f>
-        <v>1073.9</v>
+        <v>279.69</v>
       </c>
       <c r="J34" s="30"/>
       <c r="K34" s="26" t="str">
@@ -3063,31 +3134,31 @@
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H35" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I35" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3097,7 +3168,7 @@
       </c>
       <c r="C36" s="34" t="n">
         <f aca="false">IF($B36="","",INDEX(Schedule!$G$4:$G$483,MATCH(2001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="D36" s="35" t="str">
         <f aca="false">IF($B36="","",INDEX(Schedule!$D$4:$D$483,MATCH(2001,Schedule!$K$4:$K$483,0)))</f>
@@ -3118,7 +3189,7 @@
       </c>
       <c r="I36" s="37" t="n">
         <f aca="false">IF($B36="","",$I$34+SUM($H$36:$H36))</f>
-        <v>1863.9</v>
+        <v>1069.69</v>
       </c>
       <c r="J36" s="38" t="str">
         <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3128,11 +3199,11 @@
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C37" s="34" t="n">
         <f aca="false">IF($B37="","",INDEX(Schedule!$G$4:$G$483,MATCH(2002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="D37" s="35" t="str">
         <f aca="false">IF($B37="","",INDEX(Schedule!$D$4:$D$483,MATCH(2002,Schedule!$K$4:$K$483,0)))</f>
@@ -3140,20 +3211,20 @@
       </c>
       <c r="E37" s="36" t="n">
         <f aca="false">IF($B37="","",INDEX(Schedule!$E$4:$E$483,MATCH(2002,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v>350</v>
       </c>
       <c r="F37" s="16"/>
       <c r="G37" s="36" t="n">
         <f aca="false">IF($B37="","",IF($F37&lt;&gt;"",$F37,$E37))</f>
-        <v>4.99</v>
+        <v>350</v>
       </c>
       <c r="H37" s="36" t="n">
         <f aca="false">IF($B37="",0,IF($D37="Income",$G37,-$G37))</f>
-        <v>-4.99</v>
+        <v>-350</v>
       </c>
       <c r="I37" s="37" t="n">
         <f aca="false">IF($B37="","",$I$34+SUM($H$36:$H37))</f>
-        <v>1858.91</v>
+        <v>719.69</v>
       </c>
       <c r="J37" s="38" t="str">
         <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3163,11 +3234,11 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
+        <v>Spectrum</v>
       </c>
       <c r="C38" s="34" t="n">
         <f aca="false">IF($B38="","",INDEX(Schedule!$G$4:$G$483,MATCH(2003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v>46250</v>
       </c>
       <c r="D38" s="35" t="str">
         <f aca="false">IF($B38="","",INDEX(Schedule!$D$4:$D$483,MATCH(2003,Schedule!$K$4:$K$483,0)))</f>
@@ -3175,34 +3246,34 @@
       </c>
       <c r="E38" s="36" t="n">
         <f aca="false">IF($B38="","",INDEX(Schedule!$E$4:$E$483,MATCH(2003,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v>171.1</v>
       </c>
       <c r="F38" s="16"/>
       <c r="G38" s="36" t="n">
         <f aca="false">IF($B38="","",IF($F38&lt;&gt;"",$F38,$E38))</f>
-        <v>500</v>
+        <v>171.1</v>
       </c>
       <c r="H38" s="36" t="n">
         <f aca="false">IF($B38="",0,IF($D38="Income",$G38,-$G38))</f>
-        <v>-500</v>
+        <v>-171.1</v>
       </c>
       <c r="I38" s="37" t="n">
         <f aca="false">IF($B38="","",$I$34+SUM($H$36:$H38))</f>
-        <v>1358.91</v>
+        <v>548.59</v>
       </c>
       <c r="J38" s="38" t="str">
         <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Maine Revenue Services</v>
       </c>
       <c r="C39" s="34" t="n">
         <f aca="false">IF($B39="","",INDEX(Schedule!$G$4:$G$483,MATCH(2004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="D39" s="35" t="str">
         <f aca="false">IF($B39="","",INDEX(Schedule!$D$4:$D$483,MATCH(2004,Schedule!$K$4:$K$483,0)))</f>
@@ -3210,94 +3281,94 @@
       </c>
       <c r="E39" s="36" t="n">
         <f aca="false">IF($B39="","",INDEX(Schedule!$E$4:$E$483,MATCH(2004,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>45</v>
       </c>
       <c r="F39" s="16"/>
       <c r="G39" s="36" t="n">
         <f aca="false">IF($B39="","",IF($F39&lt;&gt;"",$F39,$E39))</f>
-        <v>163.5</v>
+        <v>45</v>
       </c>
       <c r="H39" s="36" t="n">
         <f aca="false">IF($B39="",0,IF($D39="Income",$G39,-$G39))</f>
-        <v>-163.5</v>
+        <v>-45</v>
       </c>
       <c r="I39" s="37" t="n">
         <f aca="false">IF($B39="","",$I$34+SUM($H$36:$H39))</f>
-        <v>1195.41</v>
+        <v>503.59</v>
       </c>
       <c r="J39" s="38" t="str">
         <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Metal Copy</v>
       </c>
       <c r="C40" s="34" t="n">
         <f aca="false">IF($B40="","",INDEX(Schedule!$G$4:$G$483,MATCH(2005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46246</v>
+        <v>46252</v>
       </c>
       <c r="D40" s="35" t="str">
         <f aca="false">IF($B40="","",INDEX(Schedule!$D$4:$D$483,MATCH(2005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E40" s="36" t="n">
         <f aca="false">IF($B40="","",INDEX(Schedule!$E$4:$E$483,MATCH(2005,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>16.99</v>
       </c>
       <c r="F40" s="16"/>
       <c r="G40" s="36" t="n">
         <f aca="false">IF($B40="","",IF($F40&lt;&gt;"",$F40,$E40))</f>
-        <v>90</v>
+        <v>16.99</v>
       </c>
       <c r="H40" s="36" t="n">
         <f aca="false">IF($B40="",0,IF($D40="Income",$G40,-$G40))</f>
-        <v>90</v>
+        <v>-16.99</v>
       </c>
       <c r="I40" s="37" t="n">
         <f aca="false">IF($B40="","",$I$34+SUM($H$36:$H40))</f>
-        <v>1285.41</v>
+        <v>486.6</v>
       </c>
       <c r="J40" s="38" t="str">
         <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(2006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C41" s="34" t="n">
         <f aca="false">IF($B41="","",INDEX(Schedule!$G$4:$G$483,MATCH(2006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46247</v>
+        <v>46253</v>
       </c>
       <c r="D41" s="35" t="str">
         <f aca="false">IF($B41="","",INDEX(Schedule!$D$4:$D$483,MATCH(2006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E41" s="36" t="n">
         <f aca="false">IF($B41="","",INDEX(Schedule!$E$4:$E$483,MATCH(2006,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>90</v>
       </c>
       <c r="F41" s="16"/>
       <c r="G41" s="36" t="n">
         <f aca="false">IF($B41="","",IF($F41&lt;&gt;"",$F41,$E41))</f>
-        <v>2.99</v>
+        <v>90</v>
       </c>
       <c r="H41" s="36" t="n">
         <f aca="false">IF($B41="",0,IF($D41="Income",$G41,-$G41))</f>
-        <v>-2.99</v>
+        <v>90</v>
       </c>
       <c r="I41" s="37" t="n">
         <f aca="false">IF($B41="","",$I$34+SUM($H$36:$H41))</f>
-        <v>1282.42</v>
+        <v>576.6</v>
       </c>
       <c r="J41" s="38" t="str">
         <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3442,7 +3513,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -3593,13 +3664,13 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="41" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="C53" s="42"/>
       <c r="D53" s="42"/>
       <c r="E53" s="43" t="n">
         <f aca="false">SUM($E$36:$E$52)</f>
-        <v>1551.48</v>
+        <v>1463.09</v>
       </c>
       <c r="F53" s="43" t="n">
         <f aca="false">SUM($F$36:$F$45)</f>
@@ -3607,15 +3678,15 @@
       </c>
       <c r="G53" s="43" t="n">
         <f aca="false">SUM($G$36:$G$52)</f>
-        <v>1551.48</v>
+        <v>1463.09</v>
       </c>
       <c r="H53" s="43" t="n">
         <f aca="false">SUM($H$36:$H$52)</f>
-        <v>208.52</v>
+        <v>296.91</v>
       </c>
       <c r="I53" s="44" t="n">
         <f aca="false">$I$34+SUM($H$36:$H$52)</f>
-        <v>1282.42</v>
+        <v>576.6</v>
       </c>
       <c r="J53" s="45" t="str">
         <f aca="false">IF($I$53&lt;0,"SHORTFALL",IF($I$53&lt;$E$7,"TIGHT","OK"))</f>
@@ -3623,25 +3694,25 @@
       </c>
       <c r="K53" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$36:$D$52,"Income",$G$36:$G$52),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$36:$D$52,"Expense",$G$36:$G$52),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$53,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $671.48   =  net $208.52</v>
+        <v>Income $880.00   less expenses $583.09   =  net $296.91</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="29" t="str">
         <f aca="false">"WEEK 3     "&amp;TEXT($E$6+14,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+14+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 3     Fri, Aug 14   through   Thu, Aug 20, 2026</v>
+        <v>WEEK 3     Fri, Aug 21   through   Thu, Aug 27, 2026</v>
       </c>
       <c r="C55" s="30"/>
       <c r="D55" s="30"/>
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
       <c r="G55" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H55" s="30"/>
       <c r="I55" s="32" t="n">
         <f aca="false">$I$53</f>
-        <v>1282.42</v>
+        <v>576.6</v>
       </c>
       <c r="J55" s="30"/>
       <c r="K55" s="26" t="str">
@@ -3651,31 +3722,31 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G56" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H56" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J56" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3685,7 +3756,7 @@
       </c>
       <c r="C57" s="34" t="n">
         <f aca="false">IF($B57="","",INDEX(Schedule!$G$4:$G$483,MATCH(3001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="D57" s="35" t="str">
         <f aca="false">IF($B57="","",INDEX(Schedule!$D$4:$D$483,MATCH(3001,Schedule!$K$4:$K$483,0)))</f>
@@ -3706,7 +3777,7 @@
       </c>
       <c r="I57" s="37" t="n">
         <f aca="false">IF($B57="","",$I$55+SUM($H$57:$H57))</f>
-        <v>2072.42</v>
+        <v>1366.6</v>
       </c>
       <c r="J57" s="38" t="str">
         <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3716,11 +3787,11 @@
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Microsoft</v>
       </c>
       <c r="C58" s="34" t="n">
         <f aca="false">IF($B58="","",INDEX(Schedule!$G$4:$G$483,MATCH(3002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46248</v>
+        <v>46259</v>
       </c>
       <c r="D58" s="35" t="str">
         <f aca="false">IF($B58="","",INDEX(Schedule!$D$4:$D$483,MATCH(3002,Schedule!$K$4:$K$483,0)))</f>
@@ -3728,20 +3799,20 @@
       </c>
       <c r="E58" s="36" t="n">
         <f aca="false">IF($B58="","",INDEX(Schedule!$E$4:$E$483,MATCH(3002,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>13.7</v>
       </c>
       <c r="F58" s="16"/>
       <c r="G58" s="36" t="n">
         <f aca="false">IF($B58="","",IF($F58&lt;&gt;"",$F58,$E58))</f>
-        <v>350</v>
+        <v>13.7</v>
       </c>
       <c r="H58" s="36" t="n">
         <f aca="false">IF($B58="",0,IF($D58="Income",$G58,-$G58))</f>
-        <v>-350</v>
+        <v>-13.7</v>
       </c>
       <c r="I58" s="37" t="n">
         <f aca="false">IF($B58="","",$I$55+SUM($H$57:$H58))</f>
-        <v>1722.42</v>
+        <v>1352.9</v>
       </c>
       <c r="J58" s="38" t="str">
         <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3751,11 +3822,11 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Spectrum</v>
+        <v>Central Maine Power: Property</v>
       </c>
       <c r="C59" s="34" t="n">
         <f aca="false">IF($B59="","",INDEX(Schedule!$G$4:$G$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="D59" s="35" t="str">
         <f aca="false">IF($B59="","",INDEX(Schedule!$D$4:$D$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
@@ -3763,20 +3834,20 @@
       </c>
       <c r="E59" s="36" t="n">
         <f aca="false">IF($B59="","",INDEX(Schedule!$E$4:$E$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
-        <v>171.1</v>
+        <v>43.87</v>
       </c>
       <c r="F59" s="16"/>
       <c r="G59" s="36" t="n">
         <f aca="false">IF($B59="","",IF($F59&lt;&gt;"",$F59,$E59))</f>
-        <v>171.1</v>
+        <v>43.87</v>
       </c>
       <c r="H59" s="36" t="n">
         <f aca="false">IF($B59="",0,IF($D59="Income",$G59,-$G59))</f>
-        <v>-171.1</v>
+        <v>-43.87</v>
       </c>
       <c r="I59" s="37" t="n">
         <f aca="false">IF($B59="","",$I$55+SUM($H$57:$H59))</f>
-        <v>1551.32</v>
+        <v>1309.03</v>
       </c>
       <c r="J59" s="38" t="str">
         <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3786,32 +3857,32 @@
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C60" s="34" t="n">
         <f aca="false">IF($B60="","",INDEX(Schedule!$G$4:$G$483,MATCH(3004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46250</v>
+        <v>46260</v>
       </c>
       <c r="D60" s="35" t="str">
         <f aca="false">IF($B60="","",INDEX(Schedule!$D$4:$D$483,MATCH(3004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E60" s="36" t="n">
         <f aca="false">IF($B60="","",INDEX(Schedule!$E$4:$E$483,MATCH(3004,Schedule!$K$4:$K$483,0)))</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="F60" s="16"/>
       <c r="G60" s="36" t="n">
         <f aca="false">IF($B60="","",IF($F60&lt;&gt;"",$F60,$E60))</f>
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="H60" s="36" t="n">
         <f aca="false">IF($B60="",0,IF($D60="Income",$G60,-$G60))</f>
-        <v>-45</v>
+        <v>90</v>
       </c>
       <c r="I60" s="37" t="n">
         <f aca="false">IF($B60="","",$I$55+SUM($H$57:$H60))</f>
-        <v>1506.32</v>
+        <v>1399.03</v>
       </c>
       <c r="J60" s="38" t="str">
         <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3821,71 +3892,71 @@
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Metal Copy</v>
-      </c>
-      <c r="C61" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="34" t="str">
         <f aca="false">IF($B61="","",INDEX(Schedule!$G$4:$G$483,MATCH(3005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46252</v>
+        <v/>
       </c>
       <c r="D61" s="35" t="str">
         <f aca="false">IF($B61="","",INDEX(Schedule!$D$4:$D$483,MATCH(3005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E61" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E61" s="36" t="str">
         <f aca="false">IF($B61="","",INDEX(Schedule!$E$4:$E$483,MATCH(3005,Schedule!$K$4:$K$483,0)))</f>
-        <v>16.99</v>
+        <v/>
       </c>
       <c r="F61" s="16"/>
-      <c r="G61" s="36" t="n">
+      <c r="G61" s="36" t="str">
         <f aca="false">IF($B61="","",IF($F61&lt;&gt;"",$F61,$E61))</f>
-        <v>16.99</v>
+        <v/>
       </c>
       <c r="H61" s="36" t="n">
         <f aca="false">IF($B61="",0,IF($D61="Income",$G61,-$G61))</f>
-        <v>-16.99</v>
-      </c>
-      <c r="I61" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="37" t="str">
         <f aca="false">IF($B61="","",$I$55+SUM($H$57:$H61))</f>
-        <v>1489.33</v>
+        <v/>
       </c>
       <c r="J61" s="38" t="str">
         <f aca="true">IF($B61="","",IF($F61&lt;&gt;"","PAID",IF($C61&lt;TODAY(),"PAST DUE",IF($C61&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
-      </c>
-      <c r="C62" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="34" t="str">
         <f aca="false">IF($B62="","",INDEX(Schedule!$G$4:$G$483,MATCH(3006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46253</v>
+        <v/>
       </c>
       <c r="D62" s="35" t="str">
         <f aca="false">IF($B62="","",INDEX(Schedule!$D$4:$D$483,MATCH(3006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
-      </c>
-      <c r="E62" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E62" s="36" t="str">
         <f aca="false">IF($B62="","",INDEX(Schedule!$E$4:$E$483,MATCH(3006,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="F62" s="16"/>
-      <c r="G62" s="36" t="n">
+      <c r="G62" s="36" t="str">
         <f aca="false">IF($B62="","",IF($F62&lt;&gt;"",$F62,$E62))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="H62" s="36" t="n">
         <f aca="false">IF($B62="",0,IF($D62="Income",$G62,-$G62))</f>
-        <v>90</v>
-      </c>
-      <c r="I62" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="37" t="str">
         <f aca="false">IF($B62="","",$I$55+SUM($H$57:$H62))</f>
-        <v>1579.33</v>
+        <v/>
       </c>
       <c r="J62" s="38" t="str">
         <f aca="true">IF($B62="","",IF($F62&lt;&gt;"","PAID",IF($C62&lt;TODAY(),"PAST DUE",IF($C62&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4030,7 +4101,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C67" s="40"/>
       <c r="D67" s="40"/>
@@ -4181,13 +4252,13 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="41" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="C74" s="42"/>
       <c r="D74" s="42"/>
       <c r="E74" s="43" t="n">
         <f aca="false">SUM($E$57:$E$73)</f>
-        <v>1463.09</v>
+        <v>937.57</v>
       </c>
       <c r="F74" s="43" t="n">
         <f aca="false">SUM($F$57:$F$66)</f>
@@ -4195,15 +4266,15 @@
       </c>
       <c r="G74" s="43" t="n">
         <f aca="false">SUM($G$57:$G$73)</f>
-        <v>1463.09</v>
+        <v>937.57</v>
       </c>
       <c r="H74" s="43" t="n">
         <f aca="false">SUM($H$57:$H$73)</f>
-        <v>296.91</v>
+        <v>822.43</v>
       </c>
       <c r="I74" s="44" t="n">
         <f aca="false">$I$55+SUM($H$57:$H$73)</f>
-        <v>1579.33</v>
+        <v>1399.03</v>
       </c>
       <c r="J74" s="45" t="str">
         <f aca="false">IF($I$74&lt;0,"SHORTFALL",IF($I$74&lt;$E$7,"TIGHT","OK"))</f>
@@ -4211,25 +4282,25 @@
       </c>
       <c r="K74" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$57:$D$73,"Income",$G$57:$G$73),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$57:$D$73,"Expense",$G$57:$G$73),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$74,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $583.09   =  net $296.91</v>
+        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="29" t="str">
         <f aca="false">"WEEK 4     "&amp;TEXT($E$6+21,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+21+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 4     Fri, Aug 21   through   Thu, Aug 27, 2026</v>
+        <v>WEEK 4     Fri, Aug 28   through   Thu, Sep 3, 2026</v>
       </c>
       <c r="C76" s="30"/>
       <c r="D76" s="30"/>
       <c r="E76" s="30"/>
       <c r="F76" s="30"/>
       <c r="G76" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H76" s="30"/>
       <c r="I76" s="32" t="n">
         <f aca="false">$I$74</f>
-        <v>1579.33</v>
+        <v>1399.03</v>
       </c>
       <c r="J76" s="30"/>
       <c r="K76" s="26" t="str">
@@ -4239,31 +4310,31 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H77" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I77" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J77" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4273,7 +4344,7 @@
       </c>
       <c r="C78" s="34" t="n">
         <f aca="false">IF($B78="","",INDEX(Schedule!$G$4:$G$483,MATCH(4001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="D78" s="35" t="str">
         <f aca="false">IF($B78="","",INDEX(Schedule!$D$4:$D$483,MATCH(4001,Schedule!$K$4:$K$483,0)))</f>
@@ -4294,7 +4365,7 @@
       </c>
       <c r="I78" s="37" t="n">
         <f aca="false">IF($B78="","",$I$76+SUM($H$78:$H78))</f>
-        <v>2369.33</v>
+        <v>2189.03</v>
       </c>
       <c r="J78" s="38" t="str">
         <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4304,11 +4375,11 @@
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Microsoft</v>
+        <v>Maine Revenue Services (2)</v>
       </c>
       <c r="C79" s="34" t="n">
         <f aca="false">IF($B79="","",INDEX(Schedule!$G$4:$G$483,MATCH(4002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46259</v>
+        <v>46264</v>
       </c>
       <c r="D79" s="35" t="str">
         <f aca="false">IF($B79="","",INDEX(Schedule!$D$4:$D$483,MATCH(4002,Schedule!$K$4:$K$483,0)))</f>
@@ -4316,20 +4387,20 @@
       </c>
       <c r="E79" s="36" t="n">
         <f aca="false">IF($B79="","",INDEX(Schedule!$E$4:$E$483,MATCH(4002,Schedule!$K$4:$K$483,0)))</f>
-        <v>13.7</v>
+        <v>150</v>
       </c>
       <c r="F79" s="16"/>
       <c r="G79" s="36" t="n">
         <f aca="false">IF($B79="","",IF($F79&lt;&gt;"",$F79,$E79))</f>
-        <v>13.7</v>
+        <v>150</v>
       </c>
       <c r="H79" s="36" t="n">
         <f aca="false">IF($B79="",0,IF($D79="Income",$G79,-$G79))</f>
-        <v>-13.7</v>
+        <v>-150</v>
       </c>
       <c r="I79" s="37" t="n">
         <f aca="false">IF($B79="","",$I$76+SUM($H$78:$H79))</f>
-        <v>2355.63</v>
+        <v>2039.03</v>
       </c>
       <c r="J79" s="38" t="str">
         <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4339,11 +4410,11 @@
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C80" s="34" t="n">
         <f aca="false">IF($B80="","",INDEX(Schedule!$G$4:$G$483,MATCH(4003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46259</v>
+        <v>46265</v>
       </c>
       <c r="D80" s="35" t="str">
         <f aca="false">IF($B80="","",INDEX(Schedule!$D$4:$D$483,MATCH(4003,Schedule!$K$4:$K$483,0)))</f>
@@ -4351,20 +4422,20 @@
       </c>
       <c r="E80" s="36" t="n">
         <f aca="false">IF($B80="","",INDEX(Schedule!$E$4:$E$483,MATCH(4003,Schedule!$K$4:$K$483,0)))</f>
-        <v>43.87</v>
+        <v>350</v>
       </c>
       <c r="F80" s="16"/>
       <c r="G80" s="36" t="n">
         <f aca="false">IF($B80="","",IF($F80&lt;&gt;"",$F80,$E80))</f>
-        <v>43.87</v>
+        <v>350</v>
       </c>
       <c r="H80" s="36" t="n">
         <f aca="false">IF($B80="",0,IF($D80="Income",$G80,-$G80))</f>
-        <v>-43.87</v>
+        <v>-350</v>
       </c>
       <c r="I80" s="37" t="n">
         <f aca="false">IF($B80="","",$I$76+SUM($H$78:$H80))</f>
-        <v>2311.76</v>
+        <v>1689.03</v>
       </c>
       <c r="J80" s="38" t="str">
         <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4374,32 +4445,32 @@
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Progressive Insurance</v>
       </c>
       <c r="C81" s="34" t="n">
         <f aca="false">IF($B81="","",INDEX(Schedule!$G$4:$G$483,MATCH(4004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="D81" s="35" t="str">
         <f aca="false">IF($B81="","",INDEX(Schedule!$D$4:$D$483,MATCH(4004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E81" s="36" t="n">
         <f aca="false">IF($B81="","",INDEX(Schedule!$E$4:$E$483,MATCH(4004,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>143.37</v>
       </c>
       <c r="F81" s="16"/>
       <c r="G81" s="36" t="n">
         <f aca="false">IF($B81="","",IF($F81&lt;&gt;"",$F81,$E81))</f>
-        <v>90</v>
+        <v>143.37</v>
       </c>
       <c r="H81" s="36" t="n">
         <f aca="false">IF($B81="",0,IF($D81="Income",$G81,-$G81))</f>
-        <v>90</v>
+        <v>-143.37</v>
       </c>
       <c r="I81" s="37" t="n">
         <f aca="false">IF($B81="","",$I$76+SUM($H$78:$H81))</f>
-        <v>2401.76</v>
+        <v>1545.66</v>
       </c>
       <c r="J81" s="38" t="str">
         <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4409,36 +4480,36 @@
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(4005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C82" s="34" t="n">
         <f aca="false">IF($B82="","",INDEX(Schedule!$G$4:$G$483,MATCH(4005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="D82" s="35" t="str">
         <f aca="false">IF($B82="","",INDEX(Schedule!$D$4:$D$483,MATCH(4005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E82" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E82" s="36" t="n">
         <f aca="false">IF($B82="","",INDEX(Schedule!$E$4:$E$483,MATCH(4005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F82" s="16"/>
-      <c r="G82" s="36" t="str">
+      <c r="G82" s="36" t="n">
         <f aca="false">IF($B82="","",IF($F82&lt;&gt;"",$F82,$E82))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H82" s="36" t="n">
         <f aca="false">IF($B82="",0,IF($D82="Income",$G82,-$G82))</f>
-        <v>0</v>
-      </c>
-      <c r="I82" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I82" s="37" t="n">
         <f aca="false">IF($B82="","",$I$76+SUM($H$78:$H82))</f>
-        <v/>
+        <v>1635.66</v>
       </c>
       <c r="J82" s="38" t="str">
         <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4618,7 +4689,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C88" s="40"/>
       <c r="D88" s="40"/>
@@ -4769,13 +4840,13 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="41" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="C95" s="42"/>
       <c r="D95" s="42"/>
       <c r="E95" s="43" t="n">
         <f aca="false">SUM($E$78:$E$94)</f>
-        <v>937.57</v>
+        <v>1523.37</v>
       </c>
       <c r="F95" s="43" t="n">
         <f aca="false">SUM($F$78:$F$87)</f>
@@ -4783,15 +4854,15 @@
       </c>
       <c r="G95" s="43" t="n">
         <f aca="false">SUM($G$78:$G$94)</f>
-        <v>937.57</v>
+        <v>1523.37</v>
       </c>
       <c r="H95" s="43" t="n">
         <f aca="false">SUM($H$78:$H$94)</f>
-        <v>822.43</v>
+        <v>236.63</v>
       </c>
       <c r="I95" s="44" t="n">
         <f aca="false">$I$76+SUM($H$78:$H$94)</f>
-        <v>2401.76</v>
+        <v>1635.66</v>
       </c>
       <c r="J95" s="45" t="str">
         <f aca="false">IF($I$95&lt;0,"SHORTFALL",IF($I$95&lt;$E$7,"TIGHT","OK"))</f>
@@ -4799,25 +4870,25 @@
       </c>
       <c r="K95" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$78:$D$94,"Income",$G$78:$G$94),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$78:$D$94,"Expense",$G$78:$G$94),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$95,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
+        <v>Income $880.00   less expenses $643.37   =  net $236.63</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B97" s="29" t="str">
         <f aca="false">"WEEK 5     "&amp;TEXT($E$6+28,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+28+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 5     Fri, Aug 28   through   Thu, Sep 3, 2026</v>
+        <v>WEEK 5     Fri, Sep 4   through   Thu, Sep 10, 2026</v>
       </c>
       <c r="C97" s="30"/>
       <c r="D97" s="30"/>
       <c r="E97" s="30"/>
       <c r="F97" s="30"/>
       <c r="G97" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H97" s="30"/>
       <c r="I97" s="32" t="n">
         <f aca="false">$I$95</f>
-        <v>2401.76</v>
+        <v>1635.66</v>
       </c>
       <c r="J97" s="30"/>
       <c r="K97" s="26" t="str">
@@ -4827,31 +4898,31 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F98" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G98" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H98" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I98" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J98" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4861,7 +4932,7 @@
       </c>
       <c r="C99" s="34" t="n">
         <f aca="false">IF($B99="","",INDEX(Schedule!$G$4:$G$483,MATCH(5001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="D99" s="35" t="str">
         <f aca="false">IF($B99="","",INDEX(Schedule!$D$4:$D$483,MATCH(5001,Schedule!$K$4:$K$483,0)))</f>
@@ -4882,7 +4953,7 @@
       </c>
       <c r="I99" s="37" t="n">
         <f aca="false">IF($B99="","",$I$97+SUM($H$99:$H99))</f>
-        <v>3191.76</v>
+        <v>2425.66</v>
       </c>
       <c r="J99" s="38" t="str">
         <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4892,11 +4963,11 @@
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services (2)</v>
+        <v>Apple: Claude</v>
       </c>
       <c r="C100" s="34" t="n">
         <f aca="false">IF($B100="","",INDEX(Schedule!$G$4:$G$483,MATCH(5002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46264</v>
+        <v>46269</v>
       </c>
       <c r="D100" s="35" t="str">
         <f aca="false">IF($B100="","",INDEX(Schedule!$D$4:$D$483,MATCH(5002,Schedule!$K$4:$K$483,0)))</f>
@@ -4904,20 +4975,20 @@
       </c>
       <c r="E100" s="36" t="n">
         <f aca="false">IF($B100="","",INDEX(Schedule!$E$4:$E$483,MATCH(5002,Schedule!$K$4:$K$483,0)))</f>
-        <v>150</v>
+        <v>21.1</v>
       </c>
       <c r="F100" s="16"/>
       <c r="G100" s="36" t="n">
         <f aca="false">IF($B100="","",IF($F100&lt;&gt;"",$F100,$E100))</f>
-        <v>150</v>
+        <v>21.1</v>
       </c>
       <c r="H100" s="36" t="n">
         <f aca="false">IF($B100="",0,IF($D100="Income",$G100,-$G100))</f>
-        <v>-150</v>
+        <v>-21.1</v>
       </c>
       <c r="I100" s="37" t="n">
         <f aca="false">IF($B100="","",$I$97+SUM($H$99:$H100))</f>
-        <v>3041.76</v>
+        <v>2404.56</v>
       </c>
       <c r="J100" s="38" t="str">
         <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4927,11 +4998,11 @@
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>OpenAI</v>
       </c>
       <c r="C101" s="34" t="n">
         <f aca="false">IF($B101="","",INDEX(Schedule!$G$4:$G$483,MATCH(5003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="D101" s="35" t="str">
         <f aca="false">IF($B101="","",INDEX(Schedule!$D$4:$D$483,MATCH(5003,Schedule!$K$4:$K$483,0)))</f>
@@ -4939,20 +5010,20 @@
       </c>
       <c r="E101" s="36" t="n">
         <f aca="false">IF($B101="","",INDEX(Schedule!$E$4:$E$483,MATCH(5003,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="F101" s="16"/>
       <c r="G101" s="36" t="n">
         <f aca="false">IF($B101="","",IF($F101&lt;&gt;"",$F101,$E101))</f>
-        <v>350</v>
+        <v>20</v>
       </c>
       <c r="H101" s="36" t="n">
         <f aca="false">IF($B101="",0,IF($D101="Income",$G101,-$G101))</f>
-        <v>-350</v>
+        <v>-20</v>
       </c>
       <c r="I101" s="37" t="n">
         <f aca="false">IF($B101="","",$I$97+SUM($H$99:$H101))</f>
-        <v>2691.76</v>
+        <v>2384.56</v>
       </c>
       <c r="J101" s="38" t="str">
         <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4962,11 +5033,11 @@
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Progressive Insurance</v>
+        <v>Obsidian</v>
       </c>
       <c r="C102" s="34" t="n">
         <f aca="false">IF($B102="","",INDEX(Schedule!$G$4:$G$483,MATCH(5004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46265</v>
+        <v>46270</v>
       </c>
       <c r="D102" s="35" t="str">
         <f aca="false">IF($B102="","",INDEX(Schedule!$D$4:$D$483,MATCH(5004,Schedule!$K$4:$K$483,0)))</f>
@@ -4974,20 +5045,20 @@
       </c>
       <c r="E102" s="36" t="n">
         <f aca="false">IF($B102="","",INDEX(Schedule!$E$4:$E$483,MATCH(5004,Schedule!$K$4:$K$483,0)))</f>
-        <v>143.37</v>
+        <v>10</v>
       </c>
       <c r="F102" s="16"/>
       <c r="G102" s="36" t="n">
         <f aca="false">IF($B102="","",IF($F102&lt;&gt;"",$F102,$E102))</f>
-        <v>143.37</v>
+        <v>10</v>
       </c>
       <c r="H102" s="36" t="n">
         <f aca="false">IF($B102="",0,IF($D102="Income",$G102,-$G102))</f>
-        <v>-143.37</v>
+        <v>-10</v>
       </c>
       <c r="I102" s="37" t="n">
         <f aca="false">IF($B102="","",$I$97+SUM($H$99:$H102))</f>
-        <v>2548.39</v>
+        <v>2374.56</v>
       </c>
       <c r="J102" s="38" t="str">
         <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4997,32 +5068,32 @@
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Google One</v>
       </c>
       <c r="C103" s="34" t="n">
         <f aca="false">IF($B103="","",INDEX(Schedule!$G$4:$G$483,MATCH(5005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="D103" s="35" t="str">
         <f aca="false">IF($B103="","",INDEX(Schedule!$D$4:$D$483,MATCH(5005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E103" s="36" t="n">
         <f aca="false">IF($B103="","",INDEX(Schedule!$E$4:$E$483,MATCH(5005,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>4.99</v>
       </c>
       <c r="F103" s="16"/>
       <c r="G103" s="36" t="n">
         <f aca="false">IF($B103="","",IF($F103&lt;&gt;"",$F103,$E103))</f>
-        <v>90</v>
+        <v>4.99</v>
       </c>
       <c r="H103" s="36" t="n">
         <f aca="false">IF($B103="",0,IF($D103="Income",$G103,-$G103))</f>
-        <v>90</v>
+        <v>-4.99</v>
       </c>
       <c r="I103" s="37" t="n">
         <f aca="false">IF($B103="","",$I$97+SUM($H$99:$H103))</f>
-        <v>2638.39</v>
+        <v>2369.57</v>
       </c>
       <c r="J103" s="38" t="str">
         <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5032,106 +5103,106 @@
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C104" s="34" t="str">
+        <v>Upstart (loan)</v>
+      </c>
+      <c r="C104" s="34" t="n">
         <f aca="false">IF($B104="","",INDEX(Schedule!$G$4:$G$483,MATCH(5006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46272</v>
       </c>
       <c r="D104" s="35" t="str">
         <f aca="false">IF($B104="","",INDEX(Schedule!$D$4:$D$483,MATCH(5006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E104" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E104" s="36" t="n">
         <f aca="false">IF($B104="","",INDEX(Schedule!$E$4:$E$483,MATCH(5006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="F104" s="16"/>
-      <c r="G104" s="36" t="str">
+      <c r="G104" s="36" t="n">
         <f aca="false">IF($B104="","",IF($F104&lt;&gt;"",$F104,$E104))</f>
-        <v/>
+        <v>500</v>
       </c>
       <c r="H104" s="36" t="n">
         <f aca="false">IF($B104="",0,IF($D104="Income",$G104,-$G104))</f>
-        <v>0</v>
-      </c>
-      <c r="I104" s="37" t="str">
+        <v>-500</v>
+      </c>
+      <c r="I104" s="37" t="n">
         <f aca="false">IF($B104="","",$I$97+SUM($H$99:$H104))</f>
-        <v/>
+        <v>1869.57</v>
       </c>
       <c r="J104" s="38" t="str">
         <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C105" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C105" s="34" t="n">
         <f aca="false">IF($B105="","",INDEX(Schedule!$G$4:$G$483,MATCH(5007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46274</v>
       </c>
       <c r="D105" s="35" t="str">
         <f aca="false">IF($B105="","",INDEX(Schedule!$D$4:$D$483,MATCH(5007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E105" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E105" s="36" t="n">
         <f aca="false">IF($B105="","",INDEX(Schedule!$E$4:$E$483,MATCH(5007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F105" s="16"/>
-      <c r="G105" s="36" t="str">
+      <c r="G105" s="36" t="n">
         <f aca="false">IF($B105="","",IF($F105&lt;&gt;"",$F105,$E105))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H105" s="36" t="n">
         <f aca="false">IF($B105="",0,IF($D105="Income",$G105,-$G105))</f>
-        <v>0</v>
-      </c>
-      <c r="I105" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I105" s="37" t="n">
         <f aca="false">IF($B105="","",$I$97+SUM($H$99:$H105))</f>
-        <v/>
+        <v>1959.57</v>
       </c>
       <c r="J105" s="38" t="str">
         <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(5008,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C106" s="34" t="str">
+        <v>Central Maine Power Co.</v>
+      </c>
+      <c r="C106" s="34" t="n">
         <f aca="false">IF($B106="","",INDEX(Schedule!$G$4:$G$483,MATCH(5008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46275</v>
       </c>
       <c r="D106" s="35" t="str">
         <f aca="false">IF($B106="","",INDEX(Schedule!$D$4:$D$483,MATCH(5008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E106" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E106" s="36" t="n">
         <f aca="false">IF($B106="","",INDEX(Schedule!$E$4:$E$483,MATCH(5008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>163.5</v>
       </c>
       <c r="F106" s="16"/>
-      <c r="G106" s="36" t="str">
+      <c r="G106" s="36" t="n">
         <f aca="false">IF($B106="","",IF($F106&lt;&gt;"",$F106,$E106))</f>
-        <v/>
+        <v>163.5</v>
       </c>
       <c r="H106" s="36" t="n">
         <f aca="false">IF($B106="",0,IF($D106="Income",$G106,-$G106))</f>
-        <v>0</v>
-      </c>
-      <c r="I106" s="37" t="str">
+        <v>-163.5</v>
+      </c>
+      <c r="I106" s="37" t="n">
         <f aca="false">IF($B106="","",$I$97+SUM($H$99:$H106))</f>
-        <v/>
+        <v>1796.07</v>
       </c>
       <c r="J106" s="38" t="str">
         <f aca="true">IF($B106="","",IF($F106&lt;&gt;"","PAID",IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5206,7 +5277,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C109" s="40"/>
       <c r="D109" s="40"/>
@@ -5357,13 +5428,13 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="41" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="C116" s="42"/>
       <c r="D116" s="42"/>
       <c r="E116" s="43" t="n">
         <f aca="false">SUM($E$99:$E$115)</f>
-        <v>1523.37</v>
+        <v>1599.59</v>
       </c>
       <c r="F116" s="43" t="n">
         <f aca="false">SUM($F$99:$F$108)</f>
@@ -5371,15 +5442,15 @@
       </c>
       <c r="G116" s="43" t="n">
         <f aca="false">SUM($G$99:$G$115)</f>
-        <v>1523.37</v>
+        <v>1599.59</v>
       </c>
       <c r="H116" s="43" t="n">
         <f aca="false">SUM($H$99:$H$115)</f>
-        <v>236.63</v>
+        <v>160.41</v>
       </c>
       <c r="I116" s="44" t="n">
         <f aca="false">$I$97+SUM($H$99:$H$115)</f>
-        <v>2638.39</v>
+        <v>1796.07</v>
       </c>
       <c r="J116" s="45" t="str">
         <f aca="false">IF($I$116&lt;0,"SHORTFALL",IF($I$116&lt;$E$7,"TIGHT","OK"))</f>
@@ -5387,25 +5458,25 @@
       </c>
       <c r="K116" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$99:$D$115,"Income",$G$99:$G$115),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$99:$D$115,"Expense",$G$99:$G$115),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$116,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $643.37   =  net $236.63</v>
+        <v>Income $880.00   less expenses $719.59   =  net $160.41</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B118" s="29" t="str">
         <f aca="false">"WEEK 6     "&amp;TEXT($E$6+35,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+35+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 6     Fri, Sep 4   through   Thu, Sep 10, 2026</v>
+        <v>WEEK 6     Fri, Sep 11   through   Thu, Sep 17, 2026</v>
       </c>
       <c r="C118" s="30"/>
       <c r="D118" s="30"/>
       <c r="E118" s="30"/>
       <c r="F118" s="30"/>
       <c r="G118" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H118" s="30"/>
       <c r="I118" s="32" t="n">
         <f aca="false">$I$116</f>
-        <v>2638.39</v>
+        <v>1796.07</v>
       </c>
       <c r="J118" s="30"/>
       <c r="K118" s="26" t="str">
@@ -5415,31 +5486,31 @@
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C119" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D119" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F119" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G119" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H119" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I119" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J119" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5449,7 +5520,7 @@
       </c>
       <c r="C120" s="34" t="n">
         <f aca="false">IF($B120="","",INDEX(Schedule!$G$4:$G$483,MATCH(6001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="D120" s="35" t="str">
         <f aca="false">IF($B120="","",INDEX(Schedule!$D$4:$D$483,MATCH(6001,Schedule!$K$4:$K$483,0)))</f>
@@ -5470,7 +5541,7 @@
       </c>
       <c r="I120" s="37" t="n">
         <f aca="false">IF($B120="","",$I$118+SUM($H$120:$H120))</f>
-        <v>3428.39</v>
+        <v>2586.07</v>
       </c>
       <c r="J120" s="38" t="str">
         <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5480,11 +5551,11 @@
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: Claude</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C121" s="34" t="n">
         <f aca="false">IF($B121="","",INDEX(Schedule!$G$4:$G$483,MATCH(6002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="D121" s="35" t="str">
         <f aca="false">IF($B121="","",INDEX(Schedule!$D$4:$D$483,MATCH(6002,Schedule!$K$4:$K$483,0)))</f>
@@ -5492,20 +5563,20 @@
       </c>
       <c r="E121" s="36" t="n">
         <f aca="false">IF($B121="","",INDEX(Schedule!$E$4:$E$483,MATCH(6002,Schedule!$K$4:$K$483,0)))</f>
-        <v>21.1</v>
+        <v>2.99</v>
       </c>
       <c r="F121" s="16"/>
       <c r="G121" s="36" t="n">
         <f aca="false">IF($B121="","",IF($F121&lt;&gt;"",$F121,$E121))</f>
-        <v>21.1</v>
+        <v>2.99</v>
       </c>
       <c r="H121" s="36" t="n">
         <f aca="false">IF($B121="",0,IF($D121="Income",$G121,-$G121))</f>
-        <v>-21.1</v>
+        <v>-2.99</v>
       </c>
       <c r="I121" s="37" t="n">
         <f aca="false">IF($B121="","",$I$118+SUM($H$120:$H121))</f>
-        <v>3407.29</v>
+        <v>2583.08</v>
       </c>
       <c r="J121" s="38" t="str">
         <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5515,11 +5586,11 @@
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>OpenAI</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C122" s="34" t="n">
         <f aca="false">IF($B122="","",INDEX(Schedule!$G$4:$G$483,MATCH(6003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46270</v>
+        <v>46280</v>
       </c>
       <c r="D122" s="35" t="str">
         <f aca="false">IF($B122="","",INDEX(Schedule!$D$4:$D$483,MATCH(6003,Schedule!$K$4:$K$483,0)))</f>
@@ -5527,20 +5598,20 @@
       </c>
       <c r="E122" s="36" t="n">
         <f aca="false">IF($B122="","",INDEX(Schedule!$E$4:$E$483,MATCH(6003,Schedule!$K$4:$K$483,0)))</f>
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="F122" s="16"/>
       <c r="G122" s="36" t="n">
         <f aca="false">IF($B122="","",IF($F122&lt;&gt;"",$F122,$E122))</f>
-        <v>20</v>
+        <v>350</v>
       </c>
       <c r="H122" s="36" t="n">
         <f aca="false">IF($B122="",0,IF($D122="Income",$G122,-$G122))</f>
-        <v>-20</v>
+        <v>-350</v>
       </c>
       <c r="I122" s="37" t="n">
         <f aca="false">IF($B122="","",$I$118+SUM($H$120:$H122))</f>
-        <v>3387.29</v>
+        <v>2233.08</v>
       </c>
       <c r="J122" s="38" t="str">
         <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5550,32 +5621,32 @@
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Obsidian</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C123" s="34" t="n">
         <f aca="false">IF($B123="","",INDEX(Schedule!$G$4:$G$483,MATCH(6004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46270</v>
+        <v>46281</v>
       </c>
       <c r="D123" s="35" t="str">
         <f aca="false">IF($B123="","",INDEX(Schedule!$D$4:$D$483,MATCH(6004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E123" s="36" t="n">
         <f aca="false">IF($B123="","",INDEX(Schedule!$E$4:$E$483,MATCH(6004,Schedule!$K$4:$K$483,0)))</f>
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F123" s="16"/>
       <c r="G123" s="36" t="n">
         <f aca="false">IF($B123="","",IF($F123&lt;&gt;"",$F123,$E123))</f>
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H123" s="36" t="n">
         <f aca="false">IF($B123="",0,IF($D123="Income",$G123,-$G123))</f>
-        <v>-10</v>
+        <v>90</v>
       </c>
       <c r="I123" s="37" t="n">
         <f aca="false">IF($B123="","",$I$118+SUM($H$120:$H123))</f>
-        <v>3377.29</v>
+        <v>2323.08</v>
       </c>
       <c r="J123" s="38" t="str">
         <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5585,11 +5656,11 @@
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
+        <v>Spectrum</v>
       </c>
       <c r="C124" s="34" t="n">
         <f aca="false">IF($B124="","",INDEX(Schedule!$G$4:$G$483,MATCH(6005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="D124" s="35" t="str">
         <f aca="false">IF($B124="","",INDEX(Schedule!$D$4:$D$483,MATCH(6005,Schedule!$K$4:$K$483,0)))</f>
@@ -5597,20 +5668,20 @@
       </c>
       <c r="E124" s="36" t="n">
         <f aca="false">IF($B124="","",INDEX(Schedule!$E$4:$E$483,MATCH(6005,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v>171.1</v>
       </c>
       <c r="F124" s="16"/>
       <c r="G124" s="36" t="n">
         <f aca="false">IF($B124="","",IF($F124&lt;&gt;"",$F124,$E124))</f>
-        <v>4.99</v>
+        <v>171.1</v>
       </c>
       <c r="H124" s="36" t="n">
         <f aca="false">IF($B124="",0,IF($D124="Income",$G124,-$G124))</f>
-        <v>-4.99</v>
+        <v>-171.1</v>
       </c>
       <c r="I124" s="37" t="n">
         <f aca="false">IF($B124="","",$I$118+SUM($H$120:$H124))</f>
-        <v>3372.3</v>
+        <v>2151.98</v>
       </c>
       <c r="J124" s="38" t="str">
         <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5620,11 +5691,11 @@
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
+        <v>Maine Revenue Services</v>
       </c>
       <c r="C125" s="34" t="n">
         <f aca="false">IF($B125="","",INDEX(Schedule!$G$4:$G$483,MATCH(6006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="D125" s="35" t="str">
         <f aca="false">IF($B125="","",INDEX(Schedule!$D$4:$D$483,MATCH(6006,Schedule!$K$4:$K$483,0)))</f>
@@ -5632,20 +5703,20 @@
       </c>
       <c r="E125" s="36" t="n">
         <f aca="false">IF($B125="","",INDEX(Schedule!$E$4:$E$483,MATCH(6006,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v>45</v>
       </c>
       <c r="F125" s="16"/>
       <c r="G125" s="36" t="n">
         <f aca="false">IF($B125="","",IF($F125&lt;&gt;"",$F125,$E125))</f>
-        <v>500</v>
+        <v>45</v>
       </c>
       <c r="H125" s="36" t="n">
         <f aca="false">IF($B125="",0,IF($D125="Income",$G125,-$G125))</f>
-        <v>-500</v>
+        <v>-45</v>
       </c>
       <c r="I125" s="37" t="n">
         <f aca="false">IF($B125="","",$I$118+SUM($H$120:$H125))</f>
-        <v>2872.3</v>
+        <v>2106.98</v>
       </c>
       <c r="J125" s="38" t="str">
         <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5655,71 +5726,71 @@
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
-      </c>
-      <c r="C126" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C126" s="34" t="str">
         <f aca="false">IF($B126="","",INDEX(Schedule!$G$4:$G$483,MATCH(6007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46274</v>
+        <v/>
       </c>
       <c r="D126" s="35" t="str">
         <f aca="false">IF($B126="","",INDEX(Schedule!$D$4:$D$483,MATCH(6007,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
-      </c>
-      <c r="E126" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E126" s="36" t="str">
         <f aca="false">IF($B126="","",INDEX(Schedule!$E$4:$E$483,MATCH(6007,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="F126" s="16"/>
-      <c r="G126" s="36" t="n">
+      <c r="G126" s="36" t="str">
         <f aca="false">IF($B126="","",IF($F126&lt;&gt;"",$F126,$E126))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="H126" s="36" t="n">
         <f aca="false">IF($B126="",0,IF($D126="Income",$G126,-$G126))</f>
-        <v>90</v>
-      </c>
-      <c r="I126" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="37" t="str">
         <f aca="false">IF($B126="","",$I$118+SUM($H$120:$H126))</f>
-        <v>2962.3</v>
+        <v/>
       </c>
       <c r="J126" s="38" t="str">
         <f aca="true">IF($B126="","",IF($F126&lt;&gt;"","PAID",IF($C126&lt;TODAY(),"PAST DUE",IF($C126&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(6008,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
-      </c>
-      <c r="C127" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C127" s="34" t="str">
         <f aca="false">IF($B127="","",INDEX(Schedule!$G$4:$G$483,MATCH(6008,Schedule!$K$4:$K$483,0)))</f>
-        <v>46275</v>
+        <v/>
       </c>
       <c r="D127" s="35" t="str">
         <f aca="false">IF($B127="","",INDEX(Schedule!$D$4:$D$483,MATCH(6008,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E127" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E127" s="36" t="str">
         <f aca="false">IF($B127="","",INDEX(Schedule!$E$4:$E$483,MATCH(6008,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v/>
       </c>
       <c r="F127" s="16"/>
-      <c r="G127" s="36" t="n">
+      <c r="G127" s="36" t="str">
         <f aca="false">IF($B127="","",IF($F127&lt;&gt;"",$F127,$E127))</f>
-        <v>163.5</v>
+        <v/>
       </c>
       <c r="H127" s="36" t="n">
         <f aca="false">IF($B127="",0,IF($D127="Income",$G127,-$G127))</f>
-        <v>-163.5</v>
-      </c>
-      <c r="I127" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="37" t="str">
         <f aca="false">IF($B127="","",$I$118+SUM($H$120:$H127))</f>
-        <v>2798.8</v>
+        <v/>
       </c>
       <c r="J127" s="38" t="str">
         <f aca="true">IF($B127="","",IF($F127&lt;&gt;"","PAID",IF($C127&lt;TODAY(),"PAST DUE",IF($C127&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5794,7 +5865,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C130" s="40"/>
       <c r="D130" s="40"/>
@@ -5945,13 +6016,13 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="41" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="C137" s="42"/>
       <c r="D137" s="42"/>
       <c r="E137" s="43" t="n">
         <f aca="false">SUM($E$120:$E$136)</f>
-        <v>1599.59</v>
+        <v>1449.09</v>
       </c>
       <c r="F137" s="43" t="n">
         <f aca="false">SUM($F$120:$F$129)</f>
@@ -5959,15 +6030,15 @@
       </c>
       <c r="G137" s="43" t="n">
         <f aca="false">SUM($G$120:$G$136)</f>
-        <v>1599.59</v>
+        <v>1449.09</v>
       </c>
       <c r="H137" s="43" t="n">
         <f aca="false">SUM($H$120:$H$136)</f>
-        <v>160.41</v>
+        <v>310.91</v>
       </c>
       <c r="I137" s="44" t="n">
         <f aca="false">$I$118+SUM($H$120:$H$136)</f>
-        <v>2798.8</v>
+        <v>2106.98</v>
       </c>
       <c r="J137" s="45" t="str">
         <f aca="false">IF($I$137&lt;0,"SHORTFALL",IF($I$137&lt;$E$7,"TIGHT","OK"))</f>
@@ -5975,25 +6046,25 @@
       </c>
       <c r="K137" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$120:$D$136,"Income",$G$120:$G$136),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$120:$D$136,"Expense",$G$120:$G$136),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$137,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $719.59   =  net $160.41</v>
+        <v>Income $880.00   less expenses $569.09   =  net $310.91</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B139" s="29" t="str">
         <f aca="false">"WEEK 7     "&amp;TEXT($E$6+42,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+42+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 7     Fri, Sep 11   through   Thu, Sep 17, 2026</v>
+        <v>WEEK 7     Fri, Sep 18   through   Thu, Sep 24, 2026</v>
       </c>
       <c r="C139" s="30"/>
       <c r="D139" s="30"/>
       <c r="E139" s="30"/>
       <c r="F139" s="30"/>
       <c r="G139" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H139" s="30"/>
       <c r="I139" s="32" t="n">
         <f aca="false">$I$137</f>
-        <v>2798.8</v>
+        <v>2106.98</v>
       </c>
       <c r="J139" s="30"/>
       <c r="K139" s="26" t="str">
@@ -6003,31 +6074,31 @@
     </row>
     <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C140" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D140" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E140" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F140" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G140" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H140" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I140" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J140" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6037,7 +6108,7 @@
       </c>
       <c r="C141" s="34" t="n">
         <f aca="false">IF($B141="","",INDEX(Schedule!$G$4:$G$483,MATCH(7001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="D141" s="35" t="str">
         <f aca="false">IF($B141="","",INDEX(Schedule!$D$4:$D$483,MATCH(7001,Schedule!$K$4:$K$483,0)))</f>
@@ -6058,7 +6129,7 @@
       </c>
       <c r="I141" s="37" t="n">
         <f aca="false">IF($B141="","",$I$139+SUM($H$141:$H141))</f>
-        <v>3588.8</v>
+        <v>2896.98</v>
       </c>
       <c r="J141" s="38" t="str">
         <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6068,11 +6139,11 @@
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B142" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>Metal Copy</v>
       </c>
       <c r="C142" s="34" t="n">
         <f aca="false">IF($B142="","",INDEX(Schedule!$G$4:$G$483,MATCH(7002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="D142" s="35" t="str">
         <f aca="false">IF($B142="","",INDEX(Schedule!$D$4:$D$483,MATCH(7002,Schedule!$K$4:$K$483,0)))</f>
@@ -6080,20 +6151,20 @@
       </c>
       <c r="E142" s="36" t="n">
         <f aca="false">IF($B142="","",INDEX(Schedule!$E$4:$E$483,MATCH(7002,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>16.99</v>
       </c>
       <c r="F142" s="16"/>
       <c r="G142" s="36" t="n">
         <f aca="false">IF($B142="","",IF($F142&lt;&gt;"",$F142,$E142))</f>
-        <v>2.99</v>
+        <v>16.99</v>
       </c>
       <c r="H142" s="36" t="n">
         <f aca="false">IF($B142="",0,IF($D142="Income",$G142,-$G142))</f>
-        <v>-2.99</v>
+        <v>-16.99</v>
       </c>
       <c r="I142" s="37" t="n">
         <f aca="false">IF($B142="","",$I$139+SUM($H$141:$H142))</f>
-        <v>3585.81</v>
+        <v>2879.99</v>
       </c>
       <c r="J142" s="38" t="str">
         <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6103,32 +6174,32 @@
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B143" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C143" s="34" t="n">
         <f aca="false">IF($B143="","",INDEX(Schedule!$G$4:$G$483,MATCH(7003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46280</v>
+        <v>46288</v>
       </c>
       <c r="D143" s="35" t="str">
         <f aca="false">IF($B143="","",INDEX(Schedule!$D$4:$D$483,MATCH(7003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E143" s="36" t="n">
         <f aca="false">IF($B143="","",INDEX(Schedule!$E$4:$E$483,MATCH(7003,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="F143" s="16"/>
       <c r="G143" s="36" t="n">
         <f aca="false">IF($B143="","",IF($F143&lt;&gt;"",$F143,$E143))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="H143" s="36" t="n">
         <f aca="false">IF($B143="",0,IF($D143="Income",$G143,-$G143))</f>
-        <v>-350</v>
+        <v>90</v>
       </c>
       <c r="I143" s="37" t="n">
         <f aca="false">IF($B143="","",$I$139+SUM($H$141:$H143))</f>
-        <v>3235.81</v>
+        <v>2969.99</v>
       </c>
       <c r="J143" s="38" t="str">
         <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6138,106 +6209,106 @@
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B144" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
-      </c>
-      <c r="C144" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C144" s="34" t="str">
         <f aca="false">IF($B144="","",INDEX(Schedule!$G$4:$G$483,MATCH(7004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46281</v>
+        <v/>
       </c>
       <c r="D144" s="35" t="str">
         <f aca="false">IF($B144="","",INDEX(Schedule!$D$4:$D$483,MATCH(7004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
-      </c>
-      <c r="E144" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E144" s="36" t="str">
         <f aca="false">IF($B144="","",INDEX(Schedule!$E$4:$E$483,MATCH(7004,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="F144" s="16"/>
-      <c r="G144" s="36" t="n">
+      <c r="G144" s="36" t="str">
         <f aca="false">IF($B144="","",IF($F144&lt;&gt;"",$F144,$E144))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="H144" s="36" t="n">
         <f aca="false">IF($B144="",0,IF($D144="Income",$G144,-$G144))</f>
-        <v>90</v>
-      </c>
-      <c r="I144" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="37" t="str">
         <f aca="false">IF($B144="","",$I$139+SUM($H$141:$H144))</f>
-        <v>3325.81</v>
+        <v/>
       </c>
       <c r="J144" s="38" t="str">
         <f aca="true">IF($B144="","",IF($F144&lt;&gt;"","PAID",IF($C144&lt;TODAY(),"PAST DUE",IF($C144&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B145" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Spectrum</v>
-      </c>
-      <c r="C145" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C145" s="34" t="str">
         <f aca="false">IF($B145="","",INDEX(Schedule!$G$4:$G$483,MATCH(7005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46281</v>
+        <v/>
       </c>
       <c r="D145" s="35" t="str">
         <f aca="false">IF($B145="","",INDEX(Schedule!$D$4:$D$483,MATCH(7005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E145" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E145" s="36" t="str">
         <f aca="false">IF($B145="","",INDEX(Schedule!$E$4:$E$483,MATCH(7005,Schedule!$K$4:$K$483,0)))</f>
-        <v>171.1</v>
+        <v/>
       </c>
       <c r="F145" s="16"/>
-      <c r="G145" s="36" t="n">
+      <c r="G145" s="36" t="str">
         <f aca="false">IF($B145="","",IF($F145&lt;&gt;"",$F145,$E145))</f>
-        <v>171.1</v>
+        <v/>
       </c>
       <c r="H145" s="36" t="n">
         <f aca="false">IF($B145="",0,IF($D145="Income",$G145,-$G145))</f>
-        <v>-171.1</v>
-      </c>
-      <c r="I145" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="37" t="str">
         <f aca="false">IF($B145="","",$I$139+SUM($H$141:$H145))</f>
-        <v>3154.71</v>
+        <v/>
       </c>
       <c r="J145" s="38" t="str">
         <f aca="true">IF($B145="","",IF($F145&lt;&gt;"","PAID",IF($C145&lt;TODAY(),"PAST DUE",IF($C145&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B146" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(7006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services</v>
-      </c>
-      <c r="C146" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C146" s="34" t="str">
         <f aca="false">IF($B146="","",INDEX(Schedule!$G$4:$G$483,MATCH(7006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46281</v>
+        <v/>
       </c>
       <c r="D146" s="35" t="str">
         <f aca="false">IF($B146="","",INDEX(Schedule!$D$4:$D$483,MATCH(7006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E146" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E146" s="36" t="str">
         <f aca="false">IF($B146="","",INDEX(Schedule!$E$4:$E$483,MATCH(7006,Schedule!$K$4:$K$483,0)))</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="F146" s="16"/>
-      <c r="G146" s="36" t="n">
+      <c r="G146" s="36" t="str">
         <f aca="false">IF($B146="","",IF($F146&lt;&gt;"",$F146,$E146))</f>
-        <v>45</v>
+        <v/>
       </c>
       <c r="H146" s="36" t="n">
         <f aca="false">IF($B146="",0,IF($D146="Income",$G146,-$G146))</f>
-        <v>-45</v>
-      </c>
-      <c r="I146" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="37" t="str">
         <f aca="false">IF($B146="","",$I$139+SUM($H$141:$H146))</f>
-        <v>3109.71</v>
+        <v/>
       </c>
       <c r="J146" s="38" t="str">
         <f aca="true">IF($B146="","",IF($F146&lt;&gt;"","PAID",IF($C146&lt;TODAY(),"PAST DUE",IF($C146&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6382,7 +6453,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C151" s="40"/>
       <c r="D151" s="40"/>
@@ -6533,13 +6604,13 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="41" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="C158" s="42"/>
       <c r="D158" s="42"/>
       <c r="E158" s="43" t="n">
         <f aca="false">SUM($E$141:$E$157)</f>
-        <v>1449.09</v>
+        <v>896.99</v>
       </c>
       <c r="F158" s="43" t="n">
         <f aca="false">SUM($F$141:$F$150)</f>
@@ -6547,15 +6618,15 @@
       </c>
       <c r="G158" s="43" t="n">
         <f aca="false">SUM($G$141:$G$157)</f>
-        <v>1449.09</v>
+        <v>896.99</v>
       </c>
       <c r="H158" s="43" t="n">
         <f aca="false">SUM($H$141:$H$157)</f>
-        <v>310.91</v>
+        <v>863.01</v>
       </c>
       <c r="I158" s="44" t="n">
         <f aca="false">$I$139+SUM($H$141:$H$157)</f>
-        <v>3109.71</v>
+        <v>2969.99</v>
       </c>
       <c r="J158" s="45" t="str">
         <f aca="false">IF($I$158&lt;0,"SHORTFALL",IF($I$158&lt;$E$7,"TIGHT","OK"))</f>
@@ -6563,25 +6634,25 @@
       </c>
       <c r="K158" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$141:$D$157,"Income",$G$141:$G$157),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$141:$D$157,"Expense",$G$141:$G$157),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$158,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $569.09   =  net $310.91</v>
+        <v>Income $880.00   less expenses $16.99   =  net $863.01</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B160" s="29" t="str">
         <f aca="false">"WEEK 8     "&amp;TEXT($E$6+49,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+49+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 8     Fri, Sep 18   through   Thu, Sep 24, 2026</v>
+        <v>WEEK 8     Fri, Sep 25   through   Thu, Oct 1, 2026</v>
       </c>
       <c r="C160" s="30"/>
       <c r="D160" s="30"/>
       <c r="E160" s="30"/>
       <c r="F160" s="30"/>
       <c r="G160" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H160" s="30"/>
       <c r="I160" s="32" t="n">
         <f aca="false">$I$158</f>
-        <v>3109.71</v>
+        <v>2969.99</v>
       </c>
       <c r="J160" s="30"/>
       <c r="K160" s="26" t="str">
@@ -6591,31 +6662,31 @@
     </row>
     <row r="161" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E161" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F161" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G161" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H161" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I161" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J161" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6625,7 +6696,7 @@
       </c>
       <c r="C162" s="34" t="n">
         <f aca="false">IF($B162="","",INDEX(Schedule!$G$4:$G$483,MATCH(8001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="D162" s="35" t="str">
         <f aca="false">IF($B162="","",INDEX(Schedule!$D$4:$D$483,MATCH(8001,Schedule!$K$4:$K$483,0)))</f>
@@ -6646,7 +6717,7 @@
       </c>
       <c r="I162" s="37" t="n">
         <f aca="false">IF($B162="","",$I$160+SUM($H$162:$H162))</f>
-        <v>3899.71</v>
+        <v>3759.99</v>
       </c>
       <c r="J162" s="38" t="str">
         <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6656,11 +6727,11 @@
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B163" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Metal Copy</v>
+        <v>Microsoft</v>
       </c>
       <c r="C163" s="34" t="n">
         <f aca="false">IF($B163="","",INDEX(Schedule!$G$4:$G$483,MATCH(8002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="D163" s="35" t="str">
         <f aca="false">IF($B163="","",INDEX(Schedule!$D$4:$D$483,MATCH(8002,Schedule!$K$4:$K$483,0)))</f>
@@ -6668,20 +6739,20 @@
       </c>
       <c r="E163" s="36" t="n">
         <f aca="false">IF($B163="","",INDEX(Schedule!$E$4:$E$483,MATCH(8002,Schedule!$K$4:$K$483,0)))</f>
-        <v>16.99</v>
+        <v>13.7</v>
       </c>
       <c r="F163" s="16"/>
       <c r="G163" s="36" t="n">
         <f aca="false">IF($B163="","",IF($F163&lt;&gt;"",$F163,$E163))</f>
-        <v>16.99</v>
+        <v>13.7</v>
       </c>
       <c r="H163" s="36" t="n">
         <f aca="false">IF($B163="",0,IF($D163="Income",$G163,-$G163))</f>
-        <v>-16.99</v>
+        <v>-13.7</v>
       </c>
       <c r="I163" s="37" t="n">
         <f aca="false">IF($B163="","",$I$160+SUM($H$162:$H163))</f>
-        <v>3882.72</v>
+        <v>3746.29</v>
       </c>
       <c r="J163" s="38" t="str">
         <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6691,32 +6762,32 @@
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Central Maine Power: Property</v>
       </c>
       <c r="C164" s="34" t="n">
         <f aca="false">IF($B164="","",INDEX(Schedule!$G$4:$G$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="D164" s="35" t="str">
         <f aca="false">IF($B164="","",INDEX(Schedule!$D$4:$D$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E164" s="36" t="n">
         <f aca="false">IF($B164="","",INDEX(Schedule!$E$4:$E$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>43.87</v>
       </c>
       <c r="F164" s="16"/>
       <c r="G164" s="36" t="n">
         <f aca="false">IF($B164="","",IF($F164&lt;&gt;"",$F164,$E164))</f>
-        <v>90</v>
+        <v>43.87</v>
       </c>
       <c r="H164" s="36" t="n">
         <f aca="false">IF($B164="",0,IF($D164="Income",$G164,-$G164))</f>
-        <v>90</v>
+        <v>-43.87</v>
       </c>
       <c r="I164" s="37" t="n">
         <f aca="false">IF($B164="","",$I$160+SUM($H$162:$H164))</f>
-        <v>3972.72</v>
+        <v>3702.42</v>
       </c>
       <c r="J164" s="38" t="str">
         <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6726,141 +6797,141 @@
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B165" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C165" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C165" s="34" t="n">
         <f aca="false">IF($B165="","",INDEX(Schedule!$G$4:$G$483,MATCH(8004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46295</v>
       </c>
       <c r="D165" s="35" t="str">
         <f aca="false">IF($B165="","",INDEX(Schedule!$D$4:$D$483,MATCH(8004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E165" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E165" s="36" t="n">
         <f aca="false">IF($B165="","",INDEX(Schedule!$E$4:$E$483,MATCH(8004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F165" s="16"/>
-      <c r="G165" s="36" t="str">
+      <c r="G165" s="36" t="n">
         <f aca="false">IF($B165="","",IF($F165&lt;&gt;"",$F165,$E165))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H165" s="36" t="n">
         <f aca="false">IF($B165="",0,IF($D165="Income",$G165,-$G165))</f>
-        <v>0</v>
-      </c>
-      <c r="I165" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I165" s="37" t="n">
         <f aca="false">IF($B165="","",$I$160+SUM($H$162:$H165))</f>
-        <v/>
+        <v>3792.42</v>
       </c>
       <c r="J165" s="38" t="str">
         <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B166" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C166" s="34" t="str">
+        <v>Patrick Rombalski (rent)</v>
+      </c>
+      <c r="C166" s="34" t="n">
         <f aca="false">IF($B166="","",INDEX(Schedule!$G$4:$G$483,MATCH(8005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46295</v>
       </c>
       <c r="D166" s="35" t="str">
         <f aca="false">IF($B166="","",INDEX(Schedule!$D$4:$D$483,MATCH(8005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E166" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E166" s="36" t="n">
         <f aca="false">IF($B166="","",INDEX(Schedule!$E$4:$E$483,MATCH(8005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="F166" s="16"/>
-      <c r="G166" s="36" t="str">
+      <c r="G166" s="36" t="n">
         <f aca="false">IF($B166="","",IF($F166&lt;&gt;"",$F166,$E166))</f>
-        <v/>
+        <v>350</v>
       </c>
       <c r="H166" s="36" t="n">
         <f aca="false">IF($B166="",0,IF($D166="Income",$G166,-$G166))</f>
-        <v>0</v>
-      </c>
-      <c r="I166" s="37" t="str">
+        <v>-350</v>
+      </c>
+      <c r="I166" s="37" t="n">
         <f aca="false">IF($B166="","",$I$160+SUM($H$162:$H166))</f>
-        <v/>
+        <v>3442.42</v>
       </c>
       <c r="J166" s="38" t="str">
         <f aca="true">IF($B166="","",IF($F166&lt;&gt;"","PAID",IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B167" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C167" s="34" t="str">
+        <v>Maine Revenue Services (2)</v>
+      </c>
+      <c r="C167" s="34" t="n">
         <f aca="false">IF($B167="","",INDEX(Schedule!$G$4:$G$483,MATCH(8006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46295</v>
       </c>
       <c r="D167" s="35" t="str">
         <f aca="false">IF($B167="","",INDEX(Schedule!$D$4:$D$483,MATCH(8006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E167" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E167" s="36" t="n">
         <f aca="false">IF($B167="","",INDEX(Schedule!$E$4:$E$483,MATCH(8006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="F167" s="16"/>
-      <c r="G167" s="36" t="str">
+      <c r="G167" s="36" t="n">
         <f aca="false">IF($B167="","",IF($F167&lt;&gt;"",$F167,$E167))</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="H167" s="36" t="n">
         <f aca="false">IF($B167="",0,IF($D167="Income",$G167,-$G167))</f>
-        <v>0</v>
-      </c>
-      <c r="I167" s="37" t="str">
+        <v>-150</v>
+      </c>
+      <c r="I167" s="37" t="n">
         <f aca="false">IF($B167="","",$I$160+SUM($H$162:$H167))</f>
-        <v/>
+        <v>3292.42</v>
       </c>
       <c r="J167" s="38" t="str">
         <f aca="true">IF($B167="","",IF($F167&lt;&gt;"","PAID",IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B168" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C168" s="34" t="str">
+        <v>Progressive Insurance</v>
+      </c>
+      <c r="C168" s="34" t="n">
         <f aca="false">IF($B168="","",INDEX(Schedule!$G$4:$G$483,MATCH(8007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46295</v>
       </c>
       <c r="D168" s="35" t="str">
         <f aca="false">IF($B168="","",INDEX(Schedule!$D$4:$D$483,MATCH(8007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E168" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E168" s="36" t="n">
         <f aca="false">IF($B168="","",INDEX(Schedule!$E$4:$E$483,MATCH(8007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>143.37</v>
       </c>
       <c r="F168" s="16"/>
-      <c r="G168" s="36" t="str">
+      <c r="G168" s="36" t="n">
         <f aca="false">IF($B168="","",IF($F168&lt;&gt;"",$F168,$E168))</f>
-        <v/>
+        <v>143.37</v>
       </c>
       <c r="H168" s="36" t="n">
         <f aca="false">IF($B168="",0,IF($D168="Income",$G168,-$G168))</f>
-        <v>0</v>
-      </c>
-      <c r="I168" s="37" t="str">
+        <v>-143.37</v>
+      </c>
+      <c r="I168" s="37" t="n">
         <f aca="false">IF($B168="","",$I$160+SUM($H$162:$H168))</f>
-        <v/>
+        <v>3149.05</v>
       </c>
       <c r="J168" s="38" t="str">
         <f aca="true">IF($B168="","",IF($F168&lt;&gt;"","PAID",IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6970,7 +7041,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C172" s="40"/>
       <c r="D172" s="40"/>
@@ -7121,13 +7192,13 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="41" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C179" s="42"/>
       <c r="D179" s="42"/>
       <c r="E179" s="43" t="n">
         <f aca="false">SUM($E$162:$E$178)</f>
-        <v>896.99</v>
+        <v>1580.94</v>
       </c>
       <c r="F179" s="43" t="n">
         <f aca="false">SUM($F$162:$F$171)</f>
@@ -7135,15 +7206,15 @@
       </c>
       <c r="G179" s="43" t="n">
         <f aca="false">SUM($G$162:$G$178)</f>
-        <v>896.99</v>
+        <v>1580.94</v>
       </c>
       <c r="H179" s="43" t="n">
         <f aca="false">SUM($H$162:$H$178)</f>
-        <v>863.01</v>
+        <v>179.06</v>
       </c>
       <c r="I179" s="44" t="n">
         <f aca="false">$I$160+SUM($H$162:$H$178)</f>
-        <v>3972.72</v>
+        <v>3149.05</v>
       </c>
       <c r="J179" s="45" t="str">
         <f aca="false">IF($I$179&lt;0,"SHORTFALL",IF($I$179&lt;$E$7,"TIGHT","OK"))</f>
@@ -7151,25 +7222,25 @@
       </c>
       <c r="K179" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$162:$D$178,"Income",$G$162:$G$178),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$162:$D$178,"Expense",$G$162:$G$178),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$179,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $16.99   =  net $863.01</v>
+        <v>Income $880.00   less expenses $700.94   =  net $179.06</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B181" s="29" t="str">
         <f aca="false">"WEEK 9     "&amp;TEXT($E$6+56,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+56+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 9     Fri, Sep 25   through   Thu, Oct 1, 2026</v>
+        <v>WEEK 9     Fri, Oct 2   through   Thu, Oct 8, 2026</v>
       </c>
       <c r="C181" s="30"/>
       <c r="D181" s="30"/>
       <c r="E181" s="30"/>
       <c r="F181" s="30"/>
       <c r="G181" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H181" s="30"/>
       <c r="I181" s="32" t="n">
         <f aca="false">$I$179</f>
-        <v>3972.72</v>
+        <v>3149.05</v>
       </c>
       <c r="J181" s="30"/>
       <c r="K181" s="26" t="str">
@@ -7179,31 +7250,31 @@
     </row>
     <row r="182" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D182" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E182" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F182" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G182" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H182" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I182" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J182" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7213,7 +7284,7 @@
       </c>
       <c r="C183" s="34" t="n">
         <f aca="false">IF($B183="","",INDEX(Schedule!$G$4:$G$483,MATCH(9001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="D183" s="35" t="str">
         <f aca="false">IF($B183="","",INDEX(Schedule!$D$4:$D$483,MATCH(9001,Schedule!$K$4:$K$483,0)))</f>
@@ -7234,7 +7305,7 @@
       </c>
       <c r="I183" s="37" t="n">
         <f aca="false">IF($B183="","",$I$181+SUM($H$183:$H183))</f>
-        <v>4762.72</v>
+        <v>3939.05</v>
       </c>
       <c r="J183" s="38" t="str">
         <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7244,11 +7315,11 @@
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B184" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Microsoft</v>
+        <v>Apple: Claude</v>
       </c>
       <c r="C184" s="34" t="n">
         <f aca="false">IF($B184="","",INDEX(Schedule!$G$4:$G$483,MATCH(9002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46290</v>
+        <v>46299</v>
       </c>
       <c r="D184" s="35" t="str">
         <f aca="false">IF($B184="","",INDEX(Schedule!$D$4:$D$483,MATCH(9002,Schedule!$K$4:$K$483,0)))</f>
@@ -7256,20 +7327,20 @@
       </c>
       <c r="E184" s="36" t="n">
         <f aca="false">IF($B184="","",INDEX(Schedule!$E$4:$E$483,MATCH(9002,Schedule!$K$4:$K$483,0)))</f>
-        <v>13.7</v>
+        <v>21.1</v>
       </c>
       <c r="F184" s="16"/>
       <c r="G184" s="36" t="n">
         <f aca="false">IF($B184="","",IF($F184&lt;&gt;"",$F184,$E184))</f>
-        <v>13.7</v>
+        <v>21.1</v>
       </c>
       <c r="H184" s="36" t="n">
         <f aca="false">IF($B184="",0,IF($D184="Income",$G184,-$G184))</f>
-        <v>-13.7</v>
+        <v>-21.1</v>
       </c>
       <c r="I184" s="37" t="n">
         <f aca="false">IF($B184="","",$I$181+SUM($H$183:$H184))</f>
-        <v>4749.02</v>
+        <v>3917.95</v>
       </c>
       <c r="J184" s="38" t="str">
         <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7279,11 +7350,11 @@
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B185" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>OpenAI</v>
       </c>
       <c r="C185" s="34" t="n">
         <f aca="false">IF($B185="","",INDEX(Schedule!$G$4:$G$483,MATCH(9003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46290</v>
+        <v>46300</v>
       </c>
       <c r="D185" s="35" t="str">
         <f aca="false">IF($B185="","",INDEX(Schedule!$D$4:$D$483,MATCH(9003,Schedule!$K$4:$K$483,0)))</f>
@@ -7291,20 +7362,20 @@
       </c>
       <c r="E185" s="36" t="n">
         <f aca="false">IF($B185="","",INDEX(Schedule!$E$4:$E$483,MATCH(9003,Schedule!$K$4:$K$483,0)))</f>
-        <v>43.87</v>
+        <v>20</v>
       </c>
       <c r="F185" s="16"/>
       <c r="G185" s="36" t="n">
         <f aca="false">IF($B185="","",IF($F185&lt;&gt;"",$F185,$E185))</f>
-        <v>43.87</v>
+        <v>20</v>
       </c>
       <c r="H185" s="36" t="n">
         <f aca="false">IF($B185="",0,IF($D185="Income",$G185,-$G185))</f>
-        <v>-43.87</v>
+        <v>-20</v>
       </c>
       <c r="I185" s="37" t="n">
         <f aca="false">IF($B185="","",$I$181+SUM($H$183:$H185))</f>
-        <v>4705.15</v>
+        <v>3897.95</v>
       </c>
       <c r="J185" s="38" t="str">
         <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7314,32 +7385,32 @@
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B186" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Obsidian</v>
       </c>
       <c r="C186" s="34" t="n">
         <f aca="false">IF($B186="","",INDEX(Schedule!$G$4:$G$483,MATCH(9004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46300</v>
       </c>
       <c r="D186" s="35" t="str">
         <f aca="false">IF($B186="","",INDEX(Schedule!$D$4:$D$483,MATCH(9004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E186" s="36" t="n">
         <f aca="false">IF($B186="","",INDEX(Schedule!$E$4:$E$483,MATCH(9004,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="F186" s="16"/>
       <c r="G186" s="36" t="n">
         <f aca="false">IF($B186="","",IF($F186&lt;&gt;"",$F186,$E186))</f>
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="H186" s="36" t="n">
         <f aca="false">IF($B186="",0,IF($D186="Income",$G186,-$G186))</f>
-        <v>90</v>
+        <v>-10</v>
       </c>
       <c r="I186" s="37" t="n">
         <f aca="false">IF($B186="","",$I$181+SUM($H$183:$H186))</f>
-        <v>4795.15</v>
+        <v>3887.95</v>
       </c>
       <c r="J186" s="38" t="str">
         <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7349,32 +7420,32 @@
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B187" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C187" s="34" t="n">
         <f aca="false">IF($B187="","",INDEX(Schedule!$G$4:$G$483,MATCH(9005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="D187" s="35" t="str">
         <f aca="false">IF($B187="","",INDEX(Schedule!$D$4:$D$483,MATCH(9005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E187" s="36" t="n">
         <f aca="false">IF($B187="","",INDEX(Schedule!$E$4:$E$483,MATCH(9005,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="F187" s="16"/>
       <c r="G187" s="36" t="n">
         <f aca="false">IF($B187="","",IF($F187&lt;&gt;"",$F187,$E187))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="H187" s="36" t="n">
         <f aca="false">IF($B187="",0,IF($D187="Income",$G187,-$G187))</f>
-        <v>-350</v>
+        <v>90</v>
       </c>
       <c r="I187" s="37" t="n">
         <f aca="false">IF($B187="","",$I$181+SUM($H$183:$H187))</f>
-        <v>4445.15</v>
+        <v>3977.95</v>
       </c>
       <c r="J187" s="38" t="str">
         <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7384,11 +7455,11 @@
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B188" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services (2)</v>
+        <v>Google One</v>
       </c>
       <c r="C188" s="34" t="n">
         <f aca="false">IF($B188="","",INDEX(Schedule!$G$4:$G$483,MATCH(9006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="D188" s="35" t="str">
         <f aca="false">IF($B188="","",INDEX(Schedule!$D$4:$D$483,MATCH(9006,Schedule!$K$4:$K$483,0)))</f>
@@ -7396,20 +7467,20 @@
       </c>
       <c r="E188" s="36" t="n">
         <f aca="false">IF($B188="","",INDEX(Schedule!$E$4:$E$483,MATCH(9006,Schedule!$K$4:$K$483,0)))</f>
-        <v>150</v>
+        <v>4.99</v>
       </c>
       <c r="F188" s="16"/>
       <c r="G188" s="36" t="n">
         <f aca="false">IF($B188="","",IF($F188&lt;&gt;"",$F188,$E188))</f>
-        <v>150</v>
+        <v>4.99</v>
       </c>
       <c r="H188" s="36" t="n">
         <f aca="false">IF($B188="",0,IF($D188="Income",$G188,-$G188))</f>
-        <v>-150</v>
+        <v>-4.99</v>
       </c>
       <c r="I188" s="37" t="n">
         <f aca="false">IF($B188="","",$I$181+SUM($H$183:$H188))</f>
-        <v>4295.15</v>
+        <v>3972.96</v>
       </c>
       <c r="J188" s="38" t="str">
         <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7419,11 +7490,11 @@
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B189" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(9007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Progressive Insurance</v>
+        <v>Upstart (loan)</v>
       </c>
       <c r="C189" s="34" t="n">
         <f aca="false">IF($B189="","",INDEX(Schedule!$G$4:$G$483,MATCH(9007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="D189" s="35" t="str">
         <f aca="false">IF($B189="","",INDEX(Schedule!$D$4:$D$483,MATCH(9007,Schedule!$K$4:$K$483,0)))</f>
@@ -7431,20 +7502,20 @@
       </c>
       <c r="E189" s="36" t="n">
         <f aca="false">IF($B189="","",INDEX(Schedule!$E$4:$E$483,MATCH(9007,Schedule!$K$4:$K$483,0)))</f>
-        <v>143.37</v>
+        <v>500</v>
       </c>
       <c r="F189" s="16"/>
       <c r="G189" s="36" t="n">
         <f aca="false">IF($B189="","",IF($F189&lt;&gt;"",$F189,$E189))</f>
-        <v>143.37</v>
+        <v>500</v>
       </c>
       <c r="H189" s="36" t="n">
         <f aca="false">IF($B189="",0,IF($D189="Income",$G189,-$G189))</f>
-        <v>-143.37</v>
+        <v>-500</v>
       </c>
       <c r="I189" s="37" t="n">
         <f aca="false">IF($B189="","",$I$181+SUM($H$183:$H189))</f>
-        <v>4151.78</v>
+        <v>3472.96</v>
       </c>
       <c r="J189" s="38" t="str">
         <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7558,7 +7629,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B193" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C193" s="40"/>
       <c r="D193" s="40"/>
@@ -7709,13 +7780,13 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B200" s="41" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="C200" s="42"/>
       <c r="D200" s="42"/>
       <c r="E200" s="43" t="n">
         <f aca="false">SUM($E$183:$E$199)</f>
-        <v>1580.94</v>
+        <v>1436.09</v>
       </c>
       <c r="F200" s="43" t="n">
         <f aca="false">SUM($F$183:$F$192)</f>
@@ -7723,15 +7794,15 @@
       </c>
       <c r="G200" s="43" t="n">
         <f aca="false">SUM($G$183:$G$199)</f>
-        <v>1580.94</v>
+        <v>1436.09</v>
       </c>
       <c r="H200" s="43" t="n">
         <f aca="false">SUM($H$183:$H$199)</f>
-        <v>179.06</v>
+        <v>323.91</v>
       </c>
       <c r="I200" s="44" t="n">
         <f aca="false">$I$181+SUM($H$183:$H$199)</f>
-        <v>4151.78</v>
+        <v>3472.96</v>
       </c>
       <c r="J200" s="45" t="str">
         <f aca="false">IF($I$200&lt;0,"SHORTFALL",IF($I$200&lt;$E$7,"TIGHT","OK"))</f>
@@ -7739,25 +7810,25 @@
       </c>
       <c r="K200" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$183:$D$199,"Income",$G$183:$G$199),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$183:$D$199,"Expense",$G$183:$G$199),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$200,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $700.94   =  net $179.06</v>
+        <v>Income $880.00   less expenses $556.09   =  net $323.91</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B202" s="29" t="str">
         <f aca="false">"WEEK 10     "&amp;TEXT($E$6+63,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+63+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 10     Fri, Oct 2   through   Thu, Oct 8, 2026</v>
+        <v>WEEK 10     Fri, Oct 9   through   Thu, Oct 15, 2026</v>
       </c>
       <c r="C202" s="30"/>
       <c r="D202" s="30"/>
       <c r="E202" s="30"/>
       <c r="F202" s="30"/>
       <c r="G202" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H202" s="30"/>
       <c r="I202" s="32" t="n">
         <f aca="false">$I$200</f>
-        <v>4151.78</v>
+        <v>3472.96</v>
       </c>
       <c r="J202" s="30"/>
       <c r="K202" s="26" t="str">
@@ -7767,31 +7838,31 @@
     </row>
     <row r="203" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C203" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D203" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E203" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F203" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G203" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H203" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I203" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J203" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7801,7 +7872,7 @@
       </c>
       <c r="C204" s="34" t="n">
         <f aca="false">IF($B204="","",INDEX(Schedule!$G$4:$G$483,MATCH(10001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="D204" s="35" t="str">
         <f aca="false">IF($B204="","",INDEX(Schedule!$D$4:$D$483,MATCH(10001,Schedule!$K$4:$K$483,0)))</f>
@@ -7822,7 +7893,7 @@
       </c>
       <c r="I204" s="37" t="n">
         <f aca="false">IF($B204="","",$I$202+SUM($H$204:$H204))</f>
-        <v>4941.78</v>
+        <v>4262.96</v>
       </c>
       <c r="J204" s="38" t="str">
         <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7832,11 +7903,11 @@
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B205" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: Claude</v>
+        <v>Central Maine Power Co.</v>
       </c>
       <c r="C205" s="34" t="n">
         <f aca="false">IF($B205="","",INDEX(Schedule!$G$4:$G$483,MATCH(10002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46299</v>
+        <v>46305</v>
       </c>
       <c r="D205" s="35" t="str">
         <f aca="false">IF($B205="","",INDEX(Schedule!$D$4:$D$483,MATCH(10002,Schedule!$K$4:$K$483,0)))</f>
@@ -7844,20 +7915,20 @@
       </c>
       <c r="E205" s="36" t="n">
         <f aca="false">IF($B205="","",INDEX(Schedule!$E$4:$E$483,MATCH(10002,Schedule!$K$4:$K$483,0)))</f>
-        <v>21.1</v>
+        <v>163.5</v>
       </c>
       <c r="F205" s="16"/>
       <c r="G205" s="36" t="n">
         <f aca="false">IF($B205="","",IF($F205&lt;&gt;"",$F205,$E205))</f>
-        <v>21.1</v>
+        <v>163.5</v>
       </c>
       <c r="H205" s="36" t="n">
         <f aca="false">IF($B205="",0,IF($D205="Income",$G205,-$G205))</f>
-        <v>-21.1</v>
+        <v>-163.5</v>
       </c>
       <c r="I205" s="37" t="n">
         <f aca="false">IF($B205="","",$I$202+SUM($H$204:$H205))</f>
-        <v>4920.68</v>
+        <v>4099.46</v>
       </c>
       <c r="J205" s="38" t="str">
         <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7867,11 +7938,11 @@
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B206" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>OpenAI</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C206" s="34" t="n">
         <f aca="false">IF($B206="","",INDEX(Schedule!$G$4:$G$483,MATCH(10003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46300</v>
+        <v>46308</v>
       </c>
       <c r="D206" s="35" t="str">
         <f aca="false">IF($B206="","",INDEX(Schedule!$D$4:$D$483,MATCH(10003,Schedule!$K$4:$K$483,0)))</f>
@@ -7879,20 +7950,20 @@
       </c>
       <c r="E206" s="36" t="n">
         <f aca="false">IF($B206="","",INDEX(Schedule!$E$4:$E$483,MATCH(10003,Schedule!$K$4:$K$483,0)))</f>
-        <v>20</v>
+        <v>2.99</v>
       </c>
       <c r="F206" s="16"/>
       <c r="G206" s="36" t="n">
         <f aca="false">IF($B206="","",IF($F206&lt;&gt;"",$F206,$E206))</f>
-        <v>20</v>
+        <v>2.99</v>
       </c>
       <c r="H206" s="36" t="n">
         <f aca="false">IF($B206="",0,IF($D206="Income",$G206,-$G206))</f>
-        <v>-20</v>
+        <v>-2.99</v>
       </c>
       <c r="I206" s="37" t="n">
         <f aca="false">IF($B206="","",$I$202+SUM($H$204:$H206))</f>
-        <v>4900.68</v>
+        <v>4096.47</v>
       </c>
       <c r="J206" s="38" t="str">
         <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7902,32 +7973,32 @@
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B207" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Obsidian</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C207" s="34" t="n">
         <f aca="false">IF($B207="","",INDEX(Schedule!$G$4:$G$483,MATCH(10004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46300</v>
+        <v>46309</v>
       </c>
       <c r="D207" s="35" t="str">
         <f aca="false">IF($B207="","",INDEX(Schedule!$D$4:$D$483,MATCH(10004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E207" s="36" t="n">
         <f aca="false">IF($B207="","",INDEX(Schedule!$E$4:$E$483,MATCH(10004,Schedule!$K$4:$K$483,0)))</f>
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="F207" s="16"/>
       <c r="G207" s="36" t="n">
         <f aca="false">IF($B207="","",IF($F207&lt;&gt;"",$F207,$E207))</f>
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="H207" s="36" t="n">
         <f aca="false">IF($B207="",0,IF($D207="Income",$G207,-$G207))</f>
-        <v>-10</v>
+        <v>90</v>
       </c>
       <c r="I207" s="37" t="n">
         <f aca="false">IF($B207="","",$I$202+SUM($H$204:$H207))</f>
-        <v>4890.68</v>
+        <v>4186.47</v>
       </c>
       <c r="J207" s="38" t="str">
         <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7937,32 +8008,32 @@
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B208" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C208" s="34" t="n">
         <f aca="false">IF($B208="","",INDEX(Schedule!$G$4:$G$483,MATCH(10005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46302</v>
+        <v>46310</v>
       </c>
       <c r="D208" s="35" t="str">
         <f aca="false">IF($B208="","",INDEX(Schedule!$D$4:$D$483,MATCH(10005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E208" s="36" t="n">
         <f aca="false">IF($B208="","",INDEX(Schedule!$E$4:$E$483,MATCH(10005,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="F208" s="16"/>
       <c r="G208" s="36" t="n">
         <f aca="false">IF($B208="","",IF($F208&lt;&gt;"",$F208,$E208))</f>
-        <v>90</v>
+        <v>350</v>
       </c>
       <c r="H208" s="36" t="n">
         <f aca="false">IF($B208="",0,IF($D208="Income",$G208,-$G208))</f>
-        <v>90</v>
+        <v>-350</v>
       </c>
       <c r="I208" s="37" t="n">
         <f aca="false">IF($B208="","",$I$202+SUM($H$204:$H208))</f>
-        <v>4980.68</v>
+        <v>3836.47</v>
       </c>
       <c r="J208" s="38" t="str">
         <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7972,71 +8043,71 @@
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B209" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
-      </c>
-      <c r="C209" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C209" s="34" t="str">
         <f aca="false">IF($B209="","",INDEX(Schedule!$G$4:$G$483,MATCH(10006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46302</v>
+        <v/>
       </c>
       <c r="D209" s="35" t="str">
         <f aca="false">IF($B209="","",INDEX(Schedule!$D$4:$D$483,MATCH(10006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E209" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E209" s="36" t="str">
         <f aca="false">IF($B209="","",INDEX(Schedule!$E$4:$E$483,MATCH(10006,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v/>
       </c>
       <c r="F209" s="16"/>
-      <c r="G209" s="36" t="n">
+      <c r="G209" s="36" t="str">
         <f aca="false">IF($B209="","",IF($F209&lt;&gt;"",$F209,$E209))</f>
-        <v>4.99</v>
+        <v/>
       </c>
       <c r="H209" s="36" t="n">
         <f aca="false">IF($B209="",0,IF($D209="Income",$G209,-$G209))</f>
-        <v>-4.99</v>
-      </c>
-      <c r="I209" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" s="37" t="str">
         <f aca="false">IF($B209="","",$I$202+SUM($H$204:$H209))</f>
-        <v>4975.69</v>
+        <v/>
       </c>
       <c r="J209" s="38" t="str">
         <f aca="true">IF($B209="","",IF($F209&lt;&gt;"","PAID",IF($C209&lt;TODAY(),"PAST DUE",IF($C209&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B210" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(10007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
-      </c>
-      <c r="C210" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C210" s="34" t="str">
         <f aca="false">IF($B210="","",INDEX(Schedule!$G$4:$G$483,MATCH(10007,Schedule!$K$4:$K$483,0)))</f>
-        <v>46302</v>
+        <v/>
       </c>
       <c r="D210" s="35" t="str">
         <f aca="false">IF($B210="","",INDEX(Schedule!$D$4:$D$483,MATCH(10007,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E210" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E210" s="36" t="str">
         <f aca="false">IF($B210="","",INDEX(Schedule!$E$4:$E$483,MATCH(10007,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v/>
       </c>
       <c r="F210" s="16"/>
-      <c r="G210" s="36" t="n">
+      <c r="G210" s="36" t="str">
         <f aca="false">IF($B210="","",IF($F210&lt;&gt;"",$F210,$E210))</f>
-        <v>500</v>
+        <v/>
       </c>
       <c r="H210" s="36" t="n">
         <f aca="false">IF($B210="",0,IF($D210="Income",$G210,-$G210))</f>
-        <v>-500</v>
-      </c>
-      <c r="I210" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I210" s="37" t="str">
         <f aca="false">IF($B210="","",$I$202+SUM($H$204:$H210))</f>
-        <v>4475.69</v>
+        <v/>
       </c>
       <c r="J210" s="38" t="str">
         <f aca="true">IF($B210="","",IF($F210&lt;&gt;"","PAID",IF($C210&lt;TODAY(),"PAST DUE",IF($C210&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8146,7 +8217,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C214" s="40"/>
       <c r="D214" s="40"/>
@@ -8297,13 +8368,13 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B221" s="41" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="C221" s="42"/>
       <c r="D221" s="42"/>
       <c r="E221" s="43" t="n">
         <f aca="false">SUM($E$204:$E$220)</f>
-        <v>1436.09</v>
+        <v>1396.49</v>
       </c>
       <c r="F221" s="43" t="n">
         <f aca="false">SUM($F$204:$F$213)</f>
@@ -8311,15 +8382,15 @@
       </c>
       <c r="G221" s="43" t="n">
         <f aca="false">SUM($G$204:$G$220)</f>
-        <v>1436.09</v>
+        <v>1396.49</v>
       </c>
       <c r="H221" s="43" t="n">
         <f aca="false">SUM($H$204:$H$220)</f>
-        <v>323.91</v>
+        <v>363.51</v>
       </c>
       <c r="I221" s="44" t="n">
         <f aca="false">$I$202+SUM($H$204:$H$220)</f>
-        <v>4475.69</v>
+        <v>3836.47</v>
       </c>
       <c r="J221" s="45" t="str">
         <f aca="false">IF($I$221&lt;0,"SHORTFALL",IF($I$221&lt;$E$7,"TIGHT","OK"))</f>
@@ -8327,25 +8398,25 @@
       </c>
       <c r="K221" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$204:$D$220,"Income",$G$204:$G$220),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$204:$D$220,"Expense",$G$204:$G$220),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$221,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $556.09   =  net $323.91</v>
+        <v>Income $880.00   less expenses $516.49   =  net $363.51</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B223" s="29" t="str">
         <f aca="false">"WEEK 11     "&amp;TEXT($E$6+70,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+70+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 11     Fri, Oct 9   through   Thu, Oct 15, 2026</v>
+        <v>WEEK 11     Fri, Oct 16   through   Thu, Oct 22, 2026</v>
       </c>
       <c r="C223" s="30"/>
       <c r="D223" s="30"/>
       <c r="E223" s="30"/>
       <c r="F223" s="30"/>
       <c r="G223" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H223" s="30"/>
       <c r="I223" s="32" t="n">
         <f aca="false">$I$221</f>
-        <v>4475.69</v>
+        <v>3836.47</v>
       </c>
       <c r="J223" s="30"/>
       <c r="K223" s="26" t="str">
@@ -8355,31 +8426,31 @@
     </row>
     <row r="224" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B224" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C224" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D224" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E224" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F224" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G224" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H224" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I224" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J224" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8389,7 +8460,7 @@
       </c>
       <c r="C225" s="34" t="n">
         <f aca="false">IF($B225="","",INDEX(Schedule!$G$4:$G$483,MATCH(11001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="D225" s="35" t="str">
         <f aca="false">IF($B225="","",INDEX(Schedule!$D$4:$D$483,MATCH(11001,Schedule!$K$4:$K$483,0)))</f>
@@ -8410,7 +8481,7 @@
       </c>
       <c r="I225" s="37" t="n">
         <f aca="false">IF($B225="","",$I$223+SUM($H$225:$H225))</f>
-        <v>5265.69</v>
+        <v>4626.47</v>
       </c>
       <c r="J225" s="38" t="str">
         <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8420,11 +8491,11 @@
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B226" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Spectrum</v>
       </c>
       <c r="C226" s="34" t="n">
         <f aca="false">IF($B226="","",INDEX(Schedule!$G$4:$G$483,MATCH(11002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46305</v>
+        <v>46311</v>
       </c>
       <c r="D226" s="35" t="str">
         <f aca="false">IF($B226="","",INDEX(Schedule!$D$4:$D$483,MATCH(11002,Schedule!$K$4:$K$483,0)))</f>
@@ -8432,20 +8503,20 @@
       </c>
       <c r="E226" s="36" t="n">
         <f aca="false">IF($B226="","",INDEX(Schedule!$E$4:$E$483,MATCH(11002,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>171.1</v>
       </c>
       <c r="F226" s="16"/>
       <c r="G226" s="36" t="n">
         <f aca="false">IF($B226="","",IF($F226&lt;&gt;"",$F226,$E226))</f>
-        <v>163.5</v>
+        <v>171.1</v>
       </c>
       <c r="H226" s="36" t="n">
         <f aca="false">IF($B226="",0,IF($D226="Income",$G226,-$G226))</f>
-        <v>-163.5</v>
+        <v>-171.1</v>
       </c>
       <c r="I226" s="37" t="n">
         <f aca="false">IF($B226="","",$I$223+SUM($H$225:$H226))</f>
-        <v>5102.19</v>
+        <v>4455.37</v>
       </c>
       <c r="J226" s="38" t="str">
         <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8455,11 +8526,11 @@
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B227" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>Maine Revenue Services</v>
       </c>
       <c r="C227" s="34" t="n">
         <f aca="false">IF($B227="","",INDEX(Schedule!$G$4:$G$483,MATCH(11003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46308</v>
+        <v>46311</v>
       </c>
       <c r="D227" s="35" t="str">
         <f aca="false">IF($B227="","",INDEX(Schedule!$D$4:$D$483,MATCH(11003,Schedule!$K$4:$K$483,0)))</f>
@@ -8467,20 +8538,20 @@
       </c>
       <c r="E227" s="36" t="n">
         <f aca="false">IF($B227="","",INDEX(Schedule!$E$4:$E$483,MATCH(11003,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>45</v>
       </c>
       <c r="F227" s="16"/>
       <c r="G227" s="36" t="n">
         <f aca="false">IF($B227="","",IF($F227&lt;&gt;"",$F227,$E227))</f>
-        <v>2.99</v>
+        <v>45</v>
       </c>
       <c r="H227" s="36" t="n">
         <f aca="false">IF($B227="",0,IF($D227="Income",$G227,-$G227))</f>
-        <v>-2.99</v>
+        <v>-45</v>
       </c>
       <c r="I227" s="37" t="n">
         <f aca="false">IF($B227="","",$I$223+SUM($H$225:$H227))</f>
-        <v>5099.2</v>
+        <v>4410.37</v>
       </c>
       <c r="J227" s="38" t="str">
         <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8490,32 +8561,32 @@
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B228" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Metal Copy</v>
       </c>
       <c r="C228" s="34" t="n">
         <f aca="false">IF($B228="","",INDEX(Schedule!$G$4:$G$483,MATCH(11004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46309</v>
+        <v>46313</v>
       </c>
       <c r="D228" s="35" t="str">
         <f aca="false">IF($B228="","",INDEX(Schedule!$D$4:$D$483,MATCH(11004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E228" s="36" t="n">
         <f aca="false">IF($B228="","",INDEX(Schedule!$E$4:$E$483,MATCH(11004,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>16.99</v>
       </c>
       <c r="F228" s="16"/>
       <c r="G228" s="36" t="n">
         <f aca="false">IF($B228="","",IF($F228&lt;&gt;"",$F228,$E228))</f>
-        <v>90</v>
+        <v>16.99</v>
       </c>
       <c r="H228" s="36" t="n">
         <f aca="false">IF($B228="",0,IF($D228="Income",$G228,-$G228))</f>
-        <v>90</v>
+        <v>-16.99</v>
       </c>
       <c r="I228" s="37" t="n">
         <f aca="false">IF($B228="","",$I$223+SUM($H$225:$H228))</f>
-        <v>5189.2</v>
+        <v>4393.38</v>
       </c>
       <c r="J228" s="38" t="str">
         <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8525,32 +8596,32 @@
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B229" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(11005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Patrick Rombalski (rent)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C229" s="34" t="n">
         <f aca="false">IF($B229="","",INDEX(Schedule!$G$4:$G$483,MATCH(11005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46310</v>
+        <v>46316</v>
       </c>
       <c r="D229" s="35" t="str">
         <f aca="false">IF($B229="","",INDEX(Schedule!$D$4:$D$483,MATCH(11005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E229" s="36" t="n">
         <f aca="false">IF($B229="","",INDEX(Schedule!$E$4:$E$483,MATCH(11005,Schedule!$K$4:$K$483,0)))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="F229" s="16"/>
       <c r="G229" s="36" t="n">
         <f aca="false">IF($B229="","",IF($F229&lt;&gt;"",$F229,$E229))</f>
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="H229" s="36" t="n">
         <f aca="false">IF($B229="",0,IF($D229="Income",$G229,-$G229))</f>
-        <v>-350</v>
+        <v>90</v>
       </c>
       <c r="I229" s="37" t="n">
         <f aca="false">IF($B229="","",$I$223+SUM($H$225:$H229))</f>
-        <v>4839.2</v>
+        <v>4483.38</v>
       </c>
       <c r="J229" s="38" t="str">
         <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8734,7 +8805,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C235" s="40"/>
       <c r="D235" s="40"/>
@@ -8885,13 +8956,13 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="41" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C242" s="42"/>
       <c r="D242" s="42"/>
       <c r="E242" s="43" t="n">
         <f aca="false">SUM($E$225:$E$241)</f>
-        <v>1396.49</v>
+        <v>1113.09</v>
       </c>
       <c r="F242" s="43" t="n">
         <f aca="false">SUM($F$225:$F$234)</f>
@@ -8899,15 +8970,15 @@
       </c>
       <c r="G242" s="43" t="n">
         <f aca="false">SUM($G$225:$G$241)</f>
-        <v>1396.49</v>
+        <v>1113.09</v>
       </c>
       <c r="H242" s="43" t="n">
         <f aca="false">SUM($H$225:$H$241)</f>
-        <v>363.51</v>
+        <v>646.91</v>
       </c>
       <c r="I242" s="44" t="n">
         <f aca="false">$I$223+SUM($H$225:$H$241)</f>
-        <v>4839.2</v>
+        <v>4483.38</v>
       </c>
       <c r="J242" s="45" t="str">
         <f aca="false">IF($I$242&lt;0,"SHORTFALL",IF($I$242&lt;$E$7,"TIGHT","OK"))</f>
@@ -8915,25 +8986,25 @@
       </c>
       <c r="K242" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$225:$D$241,"Income",$G$225:$G$241),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$225:$D$241,"Expense",$G$225:$G$241),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$242,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $516.49   =  net $363.51</v>
+        <v>Income $880.00   less expenses $233.09   =  net $646.91</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B244" s="29" t="str">
         <f aca="false">"WEEK 12     "&amp;TEXT($E$6+77,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+77+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 12     Fri, Oct 16   through   Thu, Oct 22, 2026</v>
+        <v>WEEK 12     Fri, Oct 23   through   Thu, Oct 29, 2026</v>
       </c>
       <c r="C244" s="30"/>
       <c r="D244" s="30"/>
       <c r="E244" s="30"/>
       <c r="F244" s="30"/>
       <c r="G244" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H244" s="30"/>
       <c r="I244" s="32" t="n">
         <f aca="false">$I$242</f>
-        <v>4839.2</v>
+        <v>4483.38</v>
       </c>
       <c r="J244" s="30"/>
       <c r="K244" s="26" t="str">
@@ -8943,31 +9014,31 @@
     </row>
     <row r="245" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B245" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E245" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F245" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G245" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H245" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I245" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J245" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8977,7 +9048,7 @@
       </c>
       <c r="C246" s="34" t="n">
         <f aca="false">IF($B246="","",INDEX(Schedule!$G$4:$G$483,MATCH(12001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="D246" s="35" t="str">
         <f aca="false">IF($B246="","",INDEX(Schedule!$D$4:$D$483,MATCH(12001,Schedule!$K$4:$K$483,0)))</f>
@@ -8998,7 +9069,7 @@
       </c>
       <c r="I246" s="37" t="n">
         <f aca="false">IF($B246="","",$I$244+SUM($H$246:$H246))</f>
-        <v>5629.2</v>
+        <v>5273.38</v>
       </c>
       <c r="J246" s="38" t="str">
         <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9008,11 +9079,11 @@
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B247" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Spectrum</v>
+        <v>Microsoft</v>
       </c>
       <c r="C247" s="34" t="n">
         <f aca="false">IF($B247="","",INDEX(Schedule!$G$4:$G$483,MATCH(12002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46311</v>
+        <v>46320</v>
       </c>
       <c r="D247" s="35" t="str">
         <f aca="false">IF($B247="","",INDEX(Schedule!$D$4:$D$483,MATCH(12002,Schedule!$K$4:$K$483,0)))</f>
@@ -9020,20 +9091,20 @@
       </c>
       <c r="E247" s="36" t="n">
         <f aca="false">IF($B247="","",INDEX(Schedule!$E$4:$E$483,MATCH(12002,Schedule!$K$4:$K$483,0)))</f>
-        <v>171.1</v>
+        <v>13.7</v>
       </c>
       <c r="F247" s="16"/>
       <c r="G247" s="36" t="n">
         <f aca="false">IF($B247="","",IF($F247&lt;&gt;"",$F247,$E247))</f>
-        <v>171.1</v>
+        <v>13.7</v>
       </c>
       <c r="H247" s="36" t="n">
         <f aca="false">IF($B247="",0,IF($D247="Income",$G247,-$G247))</f>
-        <v>-171.1</v>
+        <v>-13.7</v>
       </c>
       <c r="I247" s="37" t="n">
         <f aca="false">IF($B247="","",$I$244+SUM($H$246:$H247))</f>
-        <v>5458.1</v>
+        <v>5259.68</v>
       </c>
       <c r="J247" s="38" t="str">
         <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9043,11 +9114,11 @@
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B248" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Maine Revenue Services</v>
+        <v>Central Maine Power: Property</v>
       </c>
       <c r="C248" s="34" t="n">
         <f aca="false">IF($B248="","",INDEX(Schedule!$G$4:$G$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46311</v>
+        <v>46320</v>
       </c>
       <c r="D248" s="35" t="str">
         <f aca="false">IF($B248="","",INDEX(Schedule!$D$4:$D$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
@@ -9055,20 +9126,20 @@
       </c>
       <c r="E248" s="36" t="n">
         <f aca="false">IF($B248="","",INDEX(Schedule!$E$4:$E$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
-        <v>45</v>
+        <v>43.87</v>
       </c>
       <c r="F248" s="16"/>
       <c r="G248" s="36" t="n">
         <f aca="false">IF($B248="","",IF($F248&lt;&gt;"",$F248,$E248))</f>
-        <v>45</v>
+        <v>43.87</v>
       </c>
       <c r="H248" s="36" t="n">
         <f aca="false">IF($B248="",0,IF($D248="Income",$G248,-$G248))</f>
-        <v>-45</v>
+        <v>-43.87</v>
       </c>
       <c r="I248" s="37" t="n">
         <f aca="false">IF($B248="","",$I$244+SUM($H$246:$H248))</f>
-        <v>5413.1</v>
+        <v>5215.81</v>
       </c>
       <c r="J248" s="38" t="str">
         <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9078,32 +9149,32 @@
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B249" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Metal Copy</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C249" s="34" t="n">
         <f aca="false">IF($B249="","",INDEX(Schedule!$G$4:$G$483,MATCH(12004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46313</v>
+        <v>46323</v>
       </c>
       <c r="D249" s="35" t="str">
         <f aca="false">IF($B249="","",INDEX(Schedule!$D$4:$D$483,MATCH(12004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E249" s="36" t="n">
         <f aca="false">IF($B249="","",INDEX(Schedule!$E$4:$E$483,MATCH(12004,Schedule!$K$4:$K$483,0)))</f>
-        <v>16.99</v>
+        <v>90</v>
       </c>
       <c r="F249" s="16"/>
       <c r="G249" s="36" t="n">
         <f aca="false">IF($B249="","",IF($F249&lt;&gt;"",$F249,$E249))</f>
-        <v>16.99</v>
+        <v>90</v>
       </c>
       <c r="H249" s="36" t="n">
         <f aca="false">IF($B249="",0,IF($D249="Income",$G249,-$G249))</f>
-        <v>-16.99</v>
+        <v>90</v>
       </c>
       <c r="I249" s="37" t="n">
         <f aca="false">IF($B249="","",$I$244+SUM($H$246:$H249))</f>
-        <v>5396.11</v>
+        <v>5305.81</v>
       </c>
       <c r="J249" s="38" t="str">
         <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9113,36 +9184,36 @@
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B250" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
-      </c>
-      <c r="C250" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C250" s="34" t="str">
         <f aca="false">IF($B250="","",INDEX(Schedule!$G$4:$G$483,MATCH(12005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46316</v>
+        <v/>
       </c>
       <c r="D250" s="35" t="str">
         <f aca="false">IF($B250="","",INDEX(Schedule!$D$4:$D$483,MATCH(12005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
-      </c>
-      <c r="E250" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E250" s="36" t="str">
         <f aca="false">IF($B250="","",INDEX(Schedule!$E$4:$E$483,MATCH(12005,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="F250" s="16"/>
-      <c r="G250" s="36" t="n">
+      <c r="G250" s="36" t="str">
         <f aca="false">IF($B250="","",IF($F250&lt;&gt;"",$F250,$E250))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="H250" s="36" t="n">
         <f aca="false">IF($B250="",0,IF($D250="Income",$G250,-$G250))</f>
-        <v>90</v>
-      </c>
-      <c r="I250" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I250" s="37" t="str">
         <f aca="false">IF($B250="","",$I$244+SUM($H$246:$H250))</f>
-        <v>5486.11</v>
+        <v/>
       </c>
       <c r="J250" s="38" t="str">
         <f aca="true">IF($B250="","",IF($F250&lt;&gt;"","PAID",IF($C250&lt;TODAY(),"PAST DUE",IF($C250&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>Upcoming</v>
+        <v/>
       </c>
     </row>
     <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9322,7 +9393,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B256" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C256" s="40"/>
       <c r="D256" s="40"/>
@@ -9473,13 +9544,13 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B263" s="41" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="C263" s="42"/>
       <c r="D263" s="42"/>
       <c r="E263" s="43" t="n">
         <f aca="false">SUM($E$246:$E$262)</f>
-        <v>1113.09</v>
+        <v>937.57</v>
       </c>
       <c r="F263" s="43" t="n">
         <f aca="false">SUM($F$246:$F$255)</f>
@@ -9487,15 +9558,15 @@
       </c>
       <c r="G263" s="43" t="n">
         <f aca="false">SUM($G$246:$G$262)</f>
-        <v>1113.09</v>
+        <v>937.57</v>
       </c>
       <c r="H263" s="43" t="n">
         <f aca="false">SUM($H$246:$H$262)</f>
-        <v>646.91</v>
+        <v>822.43</v>
       </c>
       <c r="I263" s="44" t="n">
         <f aca="false">$I$244+SUM($H$246:$H$262)</f>
-        <v>5486.11</v>
+        <v>5305.81</v>
       </c>
       <c r="J263" s="45" t="str">
         <f aca="false">IF($I$263&lt;0,"SHORTFALL",IF($I$263&lt;$E$7,"TIGHT","OK"))</f>
@@ -9503,25 +9574,25 @@
       </c>
       <c r="K263" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$246:$D$262,"Income",$G$246:$G$262),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$246:$D$262,"Expense",$G$246:$G$262),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$263,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $233.09   =  net $646.91</v>
+        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
       </c>
     </row>
     <row r="265" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B265" s="29" t="str">
         <f aca="false">"WEEK 13     "&amp;TEXT($E$6+84,"ddd, mmm d")&amp;"   through   "&amp;TEXT($E$6+84+6,"ddd, mmm d, yyyy")</f>
-        <v>WEEK 13     Fri, Oct 23   through   Thu, Oct 29, 2026</v>
+        <v>WEEK 13     Fri, Oct 30   through   Thu, Nov 5, 2026</v>
       </c>
       <c r="C265" s="30"/>
       <c r="D265" s="30"/>
       <c r="E265" s="30"/>
       <c r="F265" s="30"/>
       <c r="G265" s="31" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H265" s="30"/>
       <c r="I265" s="32" t="n">
         <f aca="false">$I$263</f>
-        <v>5486.11</v>
+        <v>5305.81</v>
       </c>
       <c r="J265" s="30"/>
       <c r="K265" s="26" t="str">
@@ -9531,31 +9602,31 @@
     </row>
     <row r="266" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="33" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="C266" s="33" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="D266" s="33" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E266" s="33" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="F266" s="33" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="G266" s="33" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="H266" s="33" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="I266" s="33" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="J266" s="33" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9565,7 +9636,7 @@
       </c>
       <c r="C267" s="34" t="n">
         <f aca="false">IF($B267="","",INDEX(Schedule!$G$4:$G$483,MATCH(13001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="D267" s="35" t="str">
         <f aca="false">IF($B267="","",INDEX(Schedule!$D$4:$D$483,MATCH(13001,Schedule!$K$4:$K$483,0)))</f>
@@ -9586,7 +9657,7 @@
       </c>
       <c r="I267" s="37" t="n">
         <f aca="false">IF($B267="","",$I$265+SUM($H$267:$H267))</f>
-        <v>6276.11</v>
+        <v>6095.81</v>
       </c>
       <c r="J267" s="38" t="str">
         <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9596,11 +9667,11 @@
     <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B268" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Microsoft</v>
+        <v>Patrick Rombalski (rent)</v>
       </c>
       <c r="C268" s="34" t="n">
         <f aca="false">IF($B268="","",INDEX(Schedule!$G$4:$G$483,MATCH(13002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="D268" s="35" t="str">
         <f aca="false">IF($B268="","",INDEX(Schedule!$D$4:$D$483,MATCH(13002,Schedule!$K$4:$K$483,0)))</f>
@@ -9608,20 +9679,20 @@
       </c>
       <c r="E268" s="36" t="n">
         <f aca="false">IF($B268="","",INDEX(Schedule!$E$4:$E$483,MATCH(13002,Schedule!$K$4:$K$483,0)))</f>
-        <v>13.7</v>
+        <v>350</v>
       </c>
       <c r="F268" s="16"/>
       <c r="G268" s="36" t="n">
         <f aca="false">IF($B268="","",IF($F268&lt;&gt;"",$F268,$E268))</f>
-        <v>13.7</v>
+        <v>350</v>
       </c>
       <c r="H268" s="36" t="n">
         <f aca="false">IF($B268="",0,IF($D268="Income",$G268,-$G268))</f>
-        <v>-13.7</v>
+        <v>-350</v>
       </c>
       <c r="I268" s="37" t="n">
         <f aca="false">IF($B268="","",$I$265+SUM($H$267:$H268))</f>
-        <v>6262.41</v>
+        <v>5745.81</v>
       </c>
       <c r="J268" s="38" t="str">
         <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9631,11 +9702,11 @@
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B269" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Maine Revenue Services (2)</v>
       </c>
       <c r="C269" s="34" t="n">
         <f aca="false">IF($B269="","",INDEX(Schedule!$G$4:$G$483,MATCH(13003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46320</v>
+        <v>46325</v>
       </c>
       <c r="D269" s="35" t="str">
         <f aca="false">IF($B269="","",INDEX(Schedule!$D$4:$D$483,MATCH(13003,Schedule!$K$4:$K$483,0)))</f>
@@ -9643,20 +9714,20 @@
       </c>
       <c r="E269" s="36" t="n">
         <f aca="false">IF($B269="","",INDEX(Schedule!$E$4:$E$483,MATCH(13003,Schedule!$K$4:$K$483,0)))</f>
-        <v>43.87</v>
+        <v>150</v>
       </c>
       <c r="F269" s="16"/>
       <c r="G269" s="36" t="n">
         <f aca="false">IF($B269="","",IF($F269&lt;&gt;"",$F269,$E269))</f>
-        <v>43.87</v>
+        <v>150</v>
       </c>
       <c r="H269" s="36" t="n">
         <f aca="false">IF($B269="",0,IF($D269="Income",$G269,-$G269))</f>
-        <v>-43.87</v>
+        <v>-150</v>
       </c>
       <c r="I269" s="37" t="n">
         <f aca="false">IF($B269="","",$I$265+SUM($H$267:$H269))</f>
-        <v>6218.54</v>
+        <v>5595.81</v>
       </c>
       <c r="J269" s="38" t="str">
         <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9666,32 +9737,32 @@
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B270" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Progressive Insurance</v>
       </c>
       <c r="C270" s="34" t="n">
         <f aca="false">IF($B270="","",INDEX(Schedule!$G$4:$G$483,MATCH(13004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46323</v>
+        <v>46326</v>
       </c>
       <c r="D270" s="35" t="str">
         <f aca="false">IF($B270="","",INDEX(Schedule!$D$4:$D$483,MATCH(13004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E270" s="36" t="n">
         <f aca="false">IF($B270="","",INDEX(Schedule!$E$4:$E$483,MATCH(13004,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>143.37</v>
       </c>
       <c r="F270" s="16"/>
       <c r="G270" s="36" t="n">
         <f aca="false">IF($B270="","",IF($F270&lt;&gt;"",$F270,$E270))</f>
-        <v>90</v>
+        <v>143.37</v>
       </c>
       <c r="H270" s="36" t="n">
         <f aca="false">IF($B270="",0,IF($D270="Income",$G270,-$G270))</f>
-        <v>90</v>
+        <v>-143.37</v>
       </c>
       <c r="I270" s="37" t="n">
         <f aca="false">IF($B270="","",$I$265+SUM($H$267:$H270))</f>
-        <v>6308.54</v>
+        <v>5452.44</v>
       </c>
       <c r="J270" s="38" t="str">
         <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9701,141 +9772,141 @@
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B271" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C271" s="34" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C271" s="34" t="n">
         <f aca="false">IF($B271="","",INDEX(Schedule!$G$4:$G$483,MATCH(13005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="D271" s="35" t="str">
         <f aca="false">IF($B271="","",INDEX(Schedule!$D$4:$D$483,MATCH(13005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E271" s="36" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E271" s="36" t="n">
         <f aca="false">IF($B271="","",INDEX(Schedule!$E$4:$E$483,MATCH(13005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F271" s="16"/>
-      <c r="G271" s="36" t="str">
+      <c r="G271" s="36" t="n">
         <f aca="false">IF($B271="","",IF($F271&lt;&gt;"",$F271,$E271))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H271" s="36" t="n">
         <f aca="false">IF($B271="",0,IF($D271="Income",$G271,-$G271))</f>
-        <v>0</v>
-      </c>
-      <c r="I271" s="37" t="str">
+        <v>90</v>
+      </c>
+      <c r="I271" s="37" t="n">
         <f aca="false">IF($B271="","",$I$265+SUM($H$267:$H271))</f>
-        <v/>
+        <v>5542.44</v>
       </c>
       <c r="J271" s="38" t="str">
         <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B272" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C272" s="34" t="str">
+        <v>Apple: Claude</v>
+      </c>
+      <c r="C272" s="34" t="n">
         <f aca="false">IF($B272="","",INDEX(Schedule!$G$4:$G$483,MATCH(13006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46330</v>
       </c>
       <c r="D272" s="35" t="str">
         <f aca="false">IF($B272="","",INDEX(Schedule!$D$4:$D$483,MATCH(13006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E272" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E272" s="36" t="n">
         <f aca="false">IF($B272="","",INDEX(Schedule!$E$4:$E$483,MATCH(13006,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>21.1</v>
       </c>
       <c r="F272" s="16"/>
-      <c r="G272" s="36" t="str">
+      <c r="G272" s="36" t="n">
         <f aca="false">IF($B272="","",IF($F272&lt;&gt;"",$F272,$E272))</f>
-        <v/>
+        <v>21.1</v>
       </c>
       <c r="H272" s="36" t="n">
         <f aca="false">IF($B272="",0,IF($D272="Income",$G272,-$G272))</f>
-        <v>0</v>
-      </c>
-      <c r="I272" s="37" t="str">
+        <v>-21.1</v>
+      </c>
+      <c r="I272" s="37" t="n">
         <f aca="false">IF($B272="","",$I$265+SUM($H$267:$H272))</f>
-        <v/>
+        <v>5521.34</v>
       </c>
       <c r="J272" s="38" t="str">
         <f aca="true">IF($B272="","",IF($F272&lt;&gt;"","PAID",IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B273" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13007,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C273" s="34" t="str">
+        <v>OpenAI</v>
+      </c>
+      <c r="C273" s="34" t="n">
         <f aca="false">IF($B273="","",INDEX(Schedule!$G$4:$G$483,MATCH(13007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="D273" s="35" t="str">
         <f aca="false">IF($B273="","",INDEX(Schedule!$D$4:$D$483,MATCH(13007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E273" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E273" s="36" t="n">
         <f aca="false">IF($B273="","",INDEX(Schedule!$E$4:$E$483,MATCH(13007,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="F273" s="16"/>
-      <c r="G273" s="36" t="str">
+      <c r="G273" s="36" t="n">
         <f aca="false">IF($B273="","",IF($F273&lt;&gt;"",$F273,$E273))</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="H273" s="36" t="n">
         <f aca="false">IF($B273="",0,IF($D273="Income",$G273,-$G273))</f>
-        <v>0</v>
-      </c>
-      <c r="I273" s="37" t="str">
+        <v>-20</v>
+      </c>
+      <c r="I273" s="37" t="n">
         <f aca="false">IF($B273="","",$I$265+SUM($H$267:$H273))</f>
-        <v/>
+        <v>5501.34</v>
       </c>
       <c r="J273" s="38" t="str">
         <f aca="true">IF($B273="","",IF($F273&lt;&gt;"","PAID",IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B274" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(13008,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C274" s="34" t="str">
+        <v>Obsidian</v>
+      </c>
+      <c r="C274" s="34" t="n">
         <f aca="false">IF($B274="","",INDEX(Schedule!$G$4:$G$483,MATCH(13008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46331</v>
       </c>
       <c r="D274" s="35" t="str">
         <f aca="false">IF($B274="","",INDEX(Schedule!$D$4:$D$483,MATCH(13008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E274" s="36" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E274" s="36" t="n">
         <f aca="false">IF($B274="","",INDEX(Schedule!$E$4:$E$483,MATCH(13008,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F274" s="16"/>
-      <c r="G274" s="36" t="str">
+      <c r="G274" s="36" t="n">
         <f aca="false">IF($B274="","",IF($F274&lt;&gt;"",$F274,$E274))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="H274" s="36" t="n">
         <f aca="false">IF($B274="",0,IF($D274="Income",$G274,-$G274))</f>
-        <v>0</v>
-      </c>
-      <c r="I274" s="37" t="str">
+        <v>-10</v>
+      </c>
+      <c r="I274" s="37" t="n">
         <f aca="false">IF($B274="","",$I$265+SUM($H$267:$H274))</f>
-        <v/>
+        <v>5491.34</v>
       </c>
       <c r="J274" s="38" t="str">
         <f aca="true">IF($B274="","",IF($F274&lt;&gt;"","PAID",IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>Upcoming</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9910,7 +9981,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="39" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C277" s="40"/>
       <c r="D277" s="40"/>
@@ -10061,13 +10132,13 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B284" s="41" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="C284" s="42"/>
       <c r="D284" s="42"/>
       <c r="E284" s="43" t="n">
         <f aca="false">SUM($E$267:$E$283)</f>
-        <v>937.57</v>
+        <v>1574.47</v>
       </c>
       <c r="F284" s="43" t="n">
         <f aca="false">SUM($F$267:$F$276)</f>
@@ -10075,15 +10146,15 @@
       </c>
       <c r="G284" s="43" t="n">
         <f aca="false">SUM($G$267:$G$283)</f>
-        <v>937.57</v>
+        <v>1574.47</v>
       </c>
       <c r="H284" s="43" t="n">
         <f aca="false">SUM($H$267:$H$283)</f>
-        <v>822.43</v>
+        <v>185.53</v>
       </c>
       <c r="I284" s="44" t="n">
         <f aca="false">$I$265+SUM($H$267:$H$283)</f>
-        <v>6308.54</v>
+        <v>5491.34</v>
       </c>
       <c r="J284" s="45" t="str">
         <f aca="false">IF($I$284&lt;0,"SHORTFALL",IF($I$284&lt;$E$7,"TIGHT","OK"))</f>
@@ -10091,7 +10162,7 @@
       </c>
       <c r="K284" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$267:$D$283,"Income",$G$267:$G$283),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$267:$D$283,"Expense",$G$267:$G$283),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$284,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $57.57   =  net $822.43</v>
+        <v>Income $880.00   less expenses $694.47   =  net $185.53</v>
       </c>
     </row>
   </sheetData>
@@ -10148,34 +10219,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="46" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47" t="n">
         <f aca="false">MIN($I$13:$I$25)</f>
-        <v>1073.9</v>
+        <v>279.69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="46" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C5" s="46"/>
       <c r="D5" s="46"/>
       <c r="E5" s="48" t="str">
         <f aca="false">"Week "&amp;INDEX($B$13:$B$25,MATCH(MIN($I$13:$I$25),$I$13:$I$25,0))&amp;", beginning "&amp;TEXT(INDEX($C$13:$C$25,MATCH(MIN($I$13:$I$25),$I$13:$I$25,0)),"mmm d, yyyy")</f>
-        <v>Week 1, beginning Jul 31, 2026</v>
+        <v>Week 1, beginning Aug 7, 2026</v>
       </c>
       <c r="F5" s="48"/>
       <c r="G5" s="48"/>
@@ -10184,7 +10255,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="46" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C6" s="46"/>
       <c r="D6" s="46"/>
@@ -10199,78 +10270,78 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="46" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="C7" s="46"/>
       <c r="D7" s="46"/>
       <c r="E7" s="49" t="n">
         <f aca="false">SUM($E$13:$E$25)</f>
-        <v>10650</v>
+        <v>11440</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="46" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="C8" s="46"/>
       <c r="D8" s="46"/>
       <c r="E8" s="49" t="n">
         <f aca="false">SUM($F$13:$F$25)+SUM($G$13:$G$25)</f>
-        <v>5591.46</v>
+        <v>6019.83</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="46" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="46"/>
       <c r="E9" s="47" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5058.54</v>
+        <v>5420.17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="46" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C10" s="46"/>
       <c r="D10" s="46"/>
       <c r="E10" s="47" t="n">
         <f aca="false">$I$25</f>
-        <v>6308.54</v>
+        <v>5491.34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10279,31 +10350,31 @@
       </c>
       <c r="C13" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+0</f>
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="D13" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$13</f>
-        <v>1250</v>
+        <v>71.17</v>
       </c>
       <c r="E13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Income",'Cash Flow'!$G$15:$G$24)</f>
-        <v>90</v>
+        <v>880</v>
       </c>
       <c r="F13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Expense",'Cash Flow'!$G$15:$G$24)</f>
-        <v>51.1</v>
+        <v>671.48</v>
       </c>
       <c r="G13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$26:$D$31,"Expense",'Cash Flow'!$G$26:$G$31)</f>
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H13" s="53" t="n">
         <f aca="false">$E13-$F13-$G13</f>
-        <v>-176.1</v>
+        <v>208.52</v>
       </c>
       <c r="I13" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$32</f>
-        <v>1073.9</v>
+        <v>279.69</v>
       </c>
       <c r="J13" s="54" t="str">
         <f aca="false">IF($I13&lt;0,"SHORTFALL",IF($I13&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10320,11 +10391,11 @@
       </c>
       <c r="C14" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+7</f>
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="D14" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$34</f>
-        <v>1073.9</v>
+        <v>279.69</v>
       </c>
       <c r="E14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$36:$D$45,"Income",'Cash Flow'!$G$36:$G$45)</f>
@@ -10332,7 +10403,7 @@
       </c>
       <c r="F14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$36:$D$45,"Expense",'Cash Flow'!$G$36:$G$45)</f>
-        <v>671.48</v>
+        <v>583.09</v>
       </c>
       <c r="G14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$47:$D$52,"Expense",'Cash Flow'!$G$47:$G$52)</f>
@@ -10340,11 +10411,11 @@
       </c>
       <c r="H14" s="58" t="n">
         <f aca="false">$E14-$F14-$G14</f>
-        <v>208.52</v>
+        <v>296.91</v>
       </c>
       <c r="I14" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$53</f>
-        <v>1282.42</v>
+        <v>576.6</v>
       </c>
       <c r="J14" s="59" t="str">
         <f aca="false">IF($I14&lt;0,"SHORTFALL",IF($I14&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10361,11 +10432,11 @@
       </c>
       <c r="C15" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+14</f>
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$55</f>
-        <v>1282.42</v>
+        <v>576.6</v>
       </c>
       <c r="E15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$57:$D$66,"Income",'Cash Flow'!$G$57:$G$66)</f>
@@ -10373,7 +10444,7 @@
       </c>
       <c r="F15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$57:$D$66,"Expense",'Cash Flow'!$G$57:$G$66)</f>
-        <v>583.09</v>
+        <v>57.57</v>
       </c>
       <c r="G15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$68:$D$73,"Expense",'Cash Flow'!$G$68:$G$73)</f>
@@ -10381,11 +10452,11 @@
       </c>
       <c r="H15" s="53" t="n">
         <f aca="false">$E15-$F15-$G15</f>
-        <v>296.91</v>
+        <v>822.43</v>
       </c>
       <c r="I15" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$74</f>
-        <v>1579.33</v>
+        <v>1399.03</v>
       </c>
       <c r="J15" s="54" t="str">
         <f aca="false">IF($I15&lt;0,"SHORTFALL",IF($I15&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10402,11 +10473,11 @@
       </c>
       <c r="C16" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+21</f>
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="D16" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$76</f>
-        <v>1579.33</v>
+        <v>1399.03</v>
       </c>
       <c r="E16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$78:$D$87,"Income",'Cash Flow'!$G$78:$G$87)</f>
@@ -10414,7 +10485,7 @@
       </c>
       <c r="F16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$78:$D$87,"Expense",'Cash Flow'!$G$78:$G$87)</f>
-        <v>57.57</v>
+        <v>643.37</v>
       </c>
       <c r="G16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$89:$D$94,"Expense",'Cash Flow'!$G$89:$G$94)</f>
@@ -10422,11 +10493,11 @@
       </c>
       <c r="H16" s="58" t="n">
         <f aca="false">$E16-$F16-$G16</f>
-        <v>822.43</v>
+        <v>236.63</v>
       </c>
       <c r="I16" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$95</f>
-        <v>2401.76</v>
+        <v>1635.66</v>
       </c>
       <c r="J16" s="59" t="str">
         <f aca="false">IF($I16&lt;0,"SHORTFALL",IF($I16&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10443,11 +10514,11 @@
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+28</f>
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$97</f>
-        <v>2401.76</v>
+        <v>1635.66</v>
       </c>
       <c r="E17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$99:$D$108,"Income",'Cash Flow'!$G$99:$G$108)</f>
@@ -10455,7 +10526,7 @@
       </c>
       <c r="F17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$99:$D$108,"Expense",'Cash Flow'!$G$99:$G$108)</f>
-        <v>643.37</v>
+        <v>719.59</v>
       </c>
       <c r="G17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$110:$D$115,"Expense",'Cash Flow'!$G$110:$G$115)</f>
@@ -10463,11 +10534,11 @@
       </c>
       <c r="H17" s="53" t="n">
         <f aca="false">$E17-$F17-$G17</f>
-        <v>236.63</v>
+        <v>160.41</v>
       </c>
       <c r="I17" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$116</f>
-        <v>2638.39</v>
+        <v>1796.07</v>
       </c>
       <c r="J17" s="54" t="str">
         <f aca="false">IF($I17&lt;0,"SHORTFALL",IF($I17&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10484,11 +10555,11 @@
       </c>
       <c r="C18" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+35</f>
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="D18" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$118</f>
-        <v>2638.39</v>
+        <v>1796.07</v>
       </c>
       <c r="E18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$120:$D$129,"Income",'Cash Flow'!$G$120:$G$129)</f>
@@ -10496,7 +10567,7 @@
       </c>
       <c r="F18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$120:$D$129,"Expense",'Cash Flow'!$G$120:$G$129)</f>
-        <v>719.59</v>
+        <v>569.09</v>
       </c>
       <c r="G18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$131:$D$136,"Expense",'Cash Flow'!$G$131:$G$136)</f>
@@ -10504,11 +10575,11 @@
       </c>
       <c r="H18" s="58" t="n">
         <f aca="false">$E18-$F18-$G18</f>
-        <v>160.41</v>
+        <v>310.91</v>
       </c>
       <c r="I18" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$137</f>
-        <v>2798.8</v>
+        <v>2106.98</v>
       </c>
       <c r="J18" s="59" t="str">
         <f aca="false">IF($I18&lt;0,"SHORTFALL",IF($I18&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10525,11 +10596,11 @@
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+42</f>
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$139</f>
-        <v>2798.8</v>
+        <v>2106.98</v>
       </c>
       <c r="E19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$141:$D$150,"Income",'Cash Flow'!$G$141:$G$150)</f>
@@ -10537,7 +10608,7 @@
       </c>
       <c r="F19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$141:$D$150,"Expense",'Cash Flow'!$G$141:$G$150)</f>
-        <v>569.09</v>
+        <v>16.99</v>
       </c>
       <c r="G19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$152:$D$157,"Expense",'Cash Flow'!$G$152:$G$157)</f>
@@ -10545,11 +10616,11 @@
       </c>
       <c r="H19" s="53" t="n">
         <f aca="false">$E19-$F19-$G19</f>
-        <v>310.91</v>
+        <v>863.01</v>
       </c>
       <c r="I19" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$158</f>
-        <v>3109.71</v>
+        <v>2969.99</v>
       </c>
       <c r="J19" s="54" t="str">
         <f aca="false">IF($I19&lt;0,"SHORTFALL",IF($I19&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10566,11 +10637,11 @@
       </c>
       <c r="C20" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+49</f>
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="D20" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$160</f>
-        <v>3109.71</v>
+        <v>2969.99</v>
       </c>
       <c r="E20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$162:$D$171,"Income",'Cash Flow'!$G$162:$G$171)</f>
@@ -10578,7 +10649,7 @@
       </c>
       <c r="F20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$162:$D$171,"Expense",'Cash Flow'!$G$162:$G$171)</f>
-        <v>16.99</v>
+        <v>700.94</v>
       </c>
       <c r="G20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$173:$D$178,"Expense",'Cash Flow'!$G$173:$G$178)</f>
@@ -10586,11 +10657,11 @@
       </c>
       <c r="H20" s="58" t="n">
         <f aca="false">$E20-$F20-$G20</f>
-        <v>863.01</v>
+        <v>179.06</v>
       </c>
       <c r="I20" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$179</f>
-        <v>3972.72</v>
+        <v>3149.05</v>
       </c>
       <c r="J20" s="59" t="str">
         <f aca="false">IF($I20&lt;0,"SHORTFALL",IF($I20&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10607,11 +10678,11 @@
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+56</f>
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$181</f>
-        <v>3972.72</v>
+        <v>3149.05</v>
       </c>
       <c r="E21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$183:$D$192,"Income",'Cash Flow'!$G$183:$G$192)</f>
@@ -10619,7 +10690,7 @@
       </c>
       <c r="F21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$183:$D$192,"Expense",'Cash Flow'!$G$183:$G$192)</f>
-        <v>700.94</v>
+        <v>556.09</v>
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$194:$D$199,"Expense",'Cash Flow'!$G$194:$G$199)</f>
@@ -10627,11 +10698,11 @@
       </c>
       <c r="H21" s="53" t="n">
         <f aca="false">$E21-$F21-$G21</f>
-        <v>179.06</v>
+        <v>323.91</v>
       </c>
       <c r="I21" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$200</f>
-        <v>4151.78</v>
+        <v>3472.96</v>
       </c>
       <c r="J21" s="54" t="str">
         <f aca="false">IF($I21&lt;0,"SHORTFALL",IF($I21&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10648,11 +10719,11 @@
       </c>
       <c r="C22" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+63</f>
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="D22" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$202</f>
-        <v>4151.78</v>
+        <v>3472.96</v>
       </c>
       <c r="E22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$204:$D$213,"Income",'Cash Flow'!$G$204:$G$213)</f>
@@ -10660,7 +10731,7 @@
       </c>
       <c r="F22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$204:$D$213,"Expense",'Cash Flow'!$G$204:$G$213)</f>
-        <v>556.09</v>
+        <v>516.49</v>
       </c>
       <c r="G22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$215:$D$220,"Expense",'Cash Flow'!$G$215:$G$220)</f>
@@ -10668,11 +10739,11 @@
       </c>
       <c r="H22" s="58" t="n">
         <f aca="false">$E22-$F22-$G22</f>
-        <v>323.91</v>
+        <v>363.51</v>
       </c>
       <c r="I22" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$221</f>
-        <v>4475.69</v>
+        <v>3836.47</v>
       </c>
       <c r="J22" s="59" t="str">
         <f aca="false">IF($I22&lt;0,"SHORTFALL",IF($I22&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10689,11 +10760,11 @@
       </c>
       <c r="C23" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+70</f>
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$223</f>
-        <v>4475.69</v>
+        <v>3836.47</v>
       </c>
       <c r="E23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$225:$D$234,"Income",'Cash Flow'!$G$225:$G$234)</f>
@@ -10701,7 +10772,7 @@
       </c>
       <c r="F23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$225:$D$234,"Expense",'Cash Flow'!$G$225:$G$234)</f>
-        <v>516.49</v>
+        <v>233.09</v>
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$236:$D$241,"Expense",'Cash Flow'!$G$236:$G$241)</f>
@@ -10709,11 +10780,11 @@
       </c>
       <c r="H23" s="53" t="n">
         <f aca="false">$E23-$F23-$G23</f>
-        <v>363.51</v>
+        <v>646.91</v>
       </c>
       <c r="I23" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$242</f>
-        <v>4839.2</v>
+        <v>4483.38</v>
       </c>
       <c r="J23" s="54" t="str">
         <f aca="false">IF($I23&lt;0,"SHORTFALL",IF($I23&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10730,11 +10801,11 @@
       </c>
       <c r="C24" s="55" t="n">
         <f aca="false">'Cash Flow'!$E$6+77</f>
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="D24" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$244</f>
-        <v>4839.2</v>
+        <v>4483.38</v>
       </c>
       <c r="E24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$246:$D$255,"Income",'Cash Flow'!$G$246:$G$255)</f>
@@ -10742,7 +10813,7 @@
       </c>
       <c r="F24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$246:$D$255,"Expense",'Cash Flow'!$G$246:$G$255)</f>
-        <v>233.09</v>
+        <v>57.57</v>
       </c>
       <c r="G24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$257:$D$262,"Expense",'Cash Flow'!$G$257:$G$262)</f>
@@ -10750,11 +10821,11 @@
       </c>
       <c r="H24" s="58" t="n">
         <f aca="false">$E24-$F24-$G24</f>
-        <v>646.91</v>
+        <v>822.43</v>
       </c>
       <c r="I24" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$263</f>
-        <v>5486.11</v>
+        <v>5305.81</v>
       </c>
       <c r="J24" s="59" t="str">
         <f aca="false">IF($I24&lt;0,"SHORTFALL",IF($I24&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10771,11 +10842,11 @@
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">'Cash Flow'!$E$6+84</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$265</f>
-        <v>5486.11</v>
+        <v>5305.81</v>
       </c>
       <c r="E25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$267:$D$276,"Income",'Cash Flow'!$G$267:$G$276)</f>
@@ -10783,7 +10854,7 @@
       </c>
       <c r="F25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$267:$D$276,"Expense",'Cash Flow'!$G$267:$G$276)</f>
-        <v>57.57</v>
+        <v>694.47</v>
       </c>
       <c r="G25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$278:$D$283,"Expense",'Cash Flow'!$G$278:$G$283)</f>
@@ -10791,11 +10862,11 @@
       </c>
       <c r="H25" s="53" t="n">
         <f aca="false">$E25-$F25-$G25</f>
-        <v>822.43</v>
+        <v>185.53</v>
       </c>
       <c r="I25" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$284</f>
-        <v>6308.54</v>
+        <v>5491.34</v>
       </c>
       <c r="J25" s="54" t="str">
         <f aca="false">IF($I25&lt;0,"SHORTFALL",IF($I25&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10808,40 +10879,40 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="45" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D26" s="61" t="n">
         <f aca="false">$D$13</f>
-        <v>1250</v>
+        <v>71.17</v>
       </c>
       <c r="E26" s="43" t="n">
         <f aca="false">SUM($E$13:$E$25)</f>
-        <v>10650</v>
+        <v>11440</v>
       </c>
       <c r="F26" s="43" t="n">
         <f aca="false">SUM($F$13:$F$25)</f>
-        <v>5376.46</v>
+        <v>6019.83</v>
       </c>
       <c r="G26" s="43" t="n">
         <f aca="false">SUM($G$13:$G$25)</f>
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H26" s="61" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5058.54</v>
+        <v>5420.17</v>
       </c>
       <c r="I26" s="61" t="n">
         <f aca="false">$I$25</f>
-        <v>6308.54</v>
+        <v>5491.34</v>
       </c>
       <c r="J26" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="62" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="C28" s="62"/>
       <c r="D28" s="62"/>
@@ -10911,47 +10982,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="63" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="64" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E3" s="64" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="G3" s="64" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="H3" s="64" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I3" s="64" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="J3" s="64" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="K3" s="64" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10983,19 +11054,19 @@
       </c>
       <c r="H4" s="69" t="n">
         <f aca="false">IF($G4="",0,IF(AND($G4&gt;='Cash Flow'!$E$6,$G4&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I4" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="69" t="str">
         <f aca="false">IF($H4=1,INT(($G4-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="66" t="str">
         <f aca="false">IF($H4=1,$G4*10000+ROW(),"")</f>
-        <v>462390004</v>
-      </c>
-      <c r="K4" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K4" s="66" t="str">
         <f aca="false">IF($H4=1,$I4*1000+COUNTIFS($I$4:$I$483,$I4,$J$4:$J$483,"&lt;"&amp;$J4)+1,"")</f>
-        <v>1002</v>
+        <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11031,7 +11102,7 @@
       </c>
       <c r="I5" s="69" t="n">
         <f aca="false">IF($H5=1,INT(($G5-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J5" s="66" t="n">
         <f aca="false">IF($H5=1,$G5*10000+ROW(),"")</f>
@@ -11039,7 +11110,7 @@
       </c>
       <c r="K5" s="66" t="n">
         <f aca="false">IF($H5=1,$I5*1000+COUNTIFS($I$4:$I$483,$I5,$J$4:$J$483,"&lt;"&amp;$J5)+1,"")</f>
-        <v>2005</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11075,7 +11146,7 @@
       </c>
       <c r="I6" s="69" t="n">
         <f aca="false">IF($H6=1,INT(($G6-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="66" t="n">
         <f aca="false">IF($H6=1,$G6*10000+ROW(),"")</f>
@@ -11083,7 +11154,7 @@
       </c>
       <c r="K6" s="66" t="n">
         <f aca="false">IF($H6=1,$I6*1000+COUNTIFS($I$4:$I$483,$I6,$J$4:$J$483,"&lt;"&amp;$J6)+1,"")</f>
-        <v>3006</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11119,7 +11190,7 @@
       </c>
       <c r="I7" s="69" t="n">
         <f aca="false">IF($H7=1,INT(($G7-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="66" t="n">
         <f aca="false">IF($H7=1,$G7*10000+ROW(),"")</f>
@@ -11127,7 +11198,7 @@
       </c>
       <c r="K7" s="66" t="n">
         <f aca="false">IF($H7=1,$I7*1000+COUNTIFS($I$4:$I$483,$I7,$J$4:$J$483,"&lt;"&amp;$J7)+1,"")</f>
-        <v>4004</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11163,7 +11234,7 @@
       </c>
       <c r="I8" s="69" t="n">
         <f aca="false">IF($H8=1,INT(($G8-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="66" t="n">
         <f aca="false">IF($H8=1,$G8*10000+ROW(),"")</f>
@@ -11171,7 +11242,7 @@
       </c>
       <c r="K8" s="66" t="n">
         <f aca="false">IF($H8=1,$I8*1000+COUNTIFS($I$4:$I$483,$I8,$J$4:$J$483,"&lt;"&amp;$J8)+1,"")</f>
-        <v>5005</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11207,7 +11278,7 @@
       </c>
       <c r="I9" s="69" t="n">
         <f aca="false">IF($H9=1,INT(($G9-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="66" t="n">
         <f aca="false">IF($H9=1,$G9*10000+ROW(),"")</f>
@@ -11215,7 +11286,7 @@
       </c>
       <c r="K9" s="66" t="n">
         <f aca="false">IF($H9=1,$I9*1000+COUNTIFS($I$4:$I$483,$I9,$J$4:$J$483,"&lt;"&amp;$J9)+1,"")</f>
-        <v>6007</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11251,7 +11322,7 @@
       </c>
       <c r="I10" s="69" t="n">
         <f aca="false">IF($H10=1,INT(($G10-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" s="66" t="n">
         <f aca="false">IF($H10=1,$G10*10000+ROW(),"")</f>
@@ -11259,7 +11330,7 @@
       </c>
       <c r="K10" s="66" t="n">
         <f aca="false">IF($H10=1,$I10*1000+COUNTIFS($I$4:$I$483,$I10,$J$4:$J$483,"&lt;"&amp;$J10)+1,"")</f>
-        <v>7004</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11295,7 +11366,7 @@
       </c>
       <c r="I11" s="69" t="n">
         <f aca="false">IF($H11=1,INT(($G11-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J11" s="66" t="n">
         <f aca="false">IF($H11=1,$G11*10000+ROW(),"")</f>
@@ -11303,7 +11374,7 @@
       </c>
       <c r="K11" s="66" t="n">
         <f aca="false">IF($H11=1,$I11*1000+COUNTIFS($I$4:$I$483,$I11,$J$4:$J$483,"&lt;"&amp;$J11)+1,"")</f>
-        <v>8003</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11339,7 +11410,7 @@
       </c>
       <c r="I12" s="69" t="n">
         <f aca="false">IF($H12=1,INT(($G12-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J12" s="66" t="n">
         <f aca="false">IF($H12=1,$G12*10000+ROW(),"")</f>
@@ -11347,7 +11418,7 @@
       </c>
       <c r="K12" s="66" t="n">
         <f aca="false">IF($H12=1,$I12*1000+COUNTIFS($I$4:$I$483,$I12,$J$4:$J$483,"&lt;"&amp;$J12)+1,"")</f>
-        <v>9004</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11383,7 +11454,7 @@
       </c>
       <c r="I13" s="69" t="n">
         <f aca="false">IF($H13=1,INT(($G13-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J13" s="66" t="n">
         <f aca="false">IF($H13=1,$G13*10000+ROW(),"")</f>
@@ -11391,7 +11462,7 @@
       </c>
       <c r="K13" s="66" t="n">
         <f aca="false">IF($H13=1,$I13*1000+COUNTIFS($I$4:$I$483,$I13,$J$4:$J$483,"&lt;"&amp;$J13)+1,"")</f>
-        <v>10005</v>
+        <v>9005</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11427,7 +11498,7 @@
       </c>
       <c r="I14" s="69" t="n">
         <f aca="false">IF($H14=1,INT(($G14-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J14" s="66" t="n">
         <f aca="false">IF($H14=1,$G14*10000+ROW(),"")</f>
@@ -11435,7 +11506,7 @@
       </c>
       <c r="K14" s="66" t="n">
         <f aca="false">IF($H14=1,$I14*1000+COUNTIFS($I$4:$I$483,$I14,$J$4:$J$483,"&lt;"&amp;$J14)+1,"")</f>
-        <v>11004</v>
+        <v>10004</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11471,7 +11542,7 @@
       </c>
       <c r="I15" s="69" t="n">
         <f aca="false">IF($H15=1,INT(($G15-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J15" s="66" t="n">
         <f aca="false">IF($H15=1,$G15*10000+ROW(),"")</f>
@@ -11479,7 +11550,7 @@
       </c>
       <c r="K15" s="66" t="n">
         <f aca="false">IF($H15=1,$I15*1000+COUNTIFS($I$4:$I$483,$I15,$J$4:$J$483,"&lt;"&amp;$J15)+1,"")</f>
-        <v>12005</v>
+        <v>11005</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11515,7 +11586,7 @@
       </c>
       <c r="I16" s="69" t="n">
         <f aca="false">IF($H16=1,INT(($G16-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J16" s="66" t="n">
         <f aca="false">IF($H16=1,$G16*10000+ROW(),"")</f>
@@ -11523,7 +11594,7 @@
       </c>
       <c r="K16" s="66" t="n">
         <f aca="false">IF($H16=1,$I16*1000+COUNTIFS($I$4:$I$483,$I16,$J$4:$J$483,"&lt;"&amp;$J16)+1,"")</f>
-        <v>13004</v>
+        <v>12004</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11555,19 +11626,19 @@
       </c>
       <c r="H17" s="69" t="n">
         <f aca="false">IF($G17="",0,IF(AND($G17&gt;='Cash Flow'!$E$6,$G17&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I17" s="69" t="n">
         <f aca="false">IF($H17=1,INT(($G17-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J17" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J17" s="66" t="n">
         <f aca="false">IF($H17=1,$G17*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K17" s="66" t="str">
+        <v>463300017</v>
+      </c>
+      <c r="K17" s="66" t="n">
         <f aca="false">IF($H17=1,$I17*1000+COUNTIFS($I$4:$I$483,$I17,$J$4:$J$483,"&lt;"&amp;$J17)+1,"")</f>
-        <v/>
+        <v>13005</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11691,7 +11762,7 @@
       </c>
       <c r="I20" s="69" t="n">
         <f aca="false">IF($H20=1,INT(($G20-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J20" s="66" t="n">
         <f aca="false">IF($H20=1,$G20*10000+ROW(),"")</f>
@@ -11699,7 +11770,7 @@
       </c>
       <c r="K20" s="66" t="n">
         <f aca="false">IF($H20=1,$I20*1000+COUNTIFS($I$4:$I$483,$I20,$J$4:$J$483,"&lt;"&amp;$J20)+1,"")</f>
-        <v>2001</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11735,7 +11806,7 @@
       </c>
       <c r="I21" s="69" t="n">
         <f aca="false">IF($H21=1,INT(($G21-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" s="66" t="n">
         <f aca="false">IF($H21=1,$G21*10000+ROW(),"")</f>
@@ -11743,7 +11814,7 @@
       </c>
       <c r="K21" s="66" t="n">
         <f aca="false">IF($H21=1,$I21*1000+COUNTIFS($I$4:$I$483,$I21,$J$4:$J$483,"&lt;"&amp;$J21)+1,"")</f>
-        <v>3001</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11779,7 +11850,7 @@
       </c>
       <c r="I22" s="69" t="n">
         <f aca="false">IF($H22=1,INT(($G22-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J22" s="66" t="n">
         <f aca="false">IF($H22=1,$G22*10000+ROW(),"")</f>
@@ -11787,7 +11858,7 @@
       </c>
       <c r="K22" s="66" t="n">
         <f aca="false">IF($H22=1,$I22*1000+COUNTIFS($I$4:$I$483,$I22,$J$4:$J$483,"&lt;"&amp;$J22)+1,"")</f>
-        <v>4001</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11823,7 +11894,7 @@
       </c>
       <c r="I23" s="69" t="n">
         <f aca="false">IF($H23=1,INT(($G23-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J23" s="66" t="n">
         <f aca="false">IF($H23=1,$G23*10000+ROW(),"")</f>
@@ -11831,7 +11902,7 @@
       </c>
       <c r="K23" s="66" t="n">
         <f aca="false">IF($H23=1,$I23*1000+COUNTIFS($I$4:$I$483,$I23,$J$4:$J$483,"&lt;"&amp;$J23)+1,"")</f>
-        <v>5001</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11867,7 +11938,7 @@
       </c>
       <c r="I24" s="69" t="n">
         <f aca="false">IF($H24=1,INT(($G24-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J24" s="66" t="n">
         <f aca="false">IF($H24=1,$G24*10000+ROW(),"")</f>
@@ -11875,7 +11946,7 @@
       </c>
       <c r="K24" s="66" t="n">
         <f aca="false">IF($H24=1,$I24*1000+COUNTIFS($I$4:$I$483,$I24,$J$4:$J$483,"&lt;"&amp;$J24)+1,"")</f>
-        <v>6001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11911,7 +11982,7 @@
       </c>
       <c r="I25" s="69" t="n">
         <f aca="false">IF($H25=1,INT(($G25-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J25" s="66" t="n">
         <f aca="false">IF($H25=1,$G25*10000+ROW(),"")</f>
@@ -11919,7 +11990,7 @@
       </c>
       <c r="K25" s="66" t="n">
         <f aca="false">IF($H25=1,$I25*1000+COUNTIFS($I$4:$I$483,$I25,$J$4:$J$483,"&lt;"&amp;$J25)+1,"")</f>
-        <v>7001</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11955,7 +12026,7 @@
       </c>
       <c r="I26" s="69" t="n">
         <f aca="false">IF($H26=1,INT(($G26-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J26" s="66" t="n">
         <f aca="false">IF($H26=1,$G26*10000+ROW(),"")</f>
@@ -11963,7 +12034,7 @@
       </c>
       <c r="K26" s="66" t="n">
         <f aca="false">IF($H26=1,$I26*1000+COUNTIFS($I$4:$I$483,$I26,$J$4:$J$483,"&lt;"&amp;$J26)+1,"")</f>
-        <v>8001</v>
+        <v>7001</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11999,7 +12070,7 @@
       </c>
       <c r="I27" s="69" t="n">
         <f aca="false">IF($H27=1,INT(($G27-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J27" s="66" t="n">
         <f aca="false">IF($H27=1,$G27*10000+ROW(),"")</f>
@@ -12007,7 +12078,7 @@
       </c>
       <c r="K27" s="66" t="n">
         <f aca="false">IF($H27=1,$I27*1000+COUNTIFS($I$4:$I$483,$I27,$J$4:$J$483,"&lt;"&amp;$J27)+1,"")</f>
-        <v>9001</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12043,7 +12114,7 @@
       </c>
       <c r="I28" s="69" t="n">
         <f aca="false">IF($H28=1,INT(($G28-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" s="66" t="n">
         <f aca="false">IF($H28=1,$G28*10000+ROW(),"")</f>
@@ -12051,7 +12122,7 @@
       </c>
       <c r="K28" s="66" t="n">
         <f aca="false">IF($H28=1,$I28*1000+COUNTIFS($I$4:$I$483,$I28,$J$4:$J$483,"&lt;"&amp;$J28)+1,"")</f>
-        <v>10001</v>
+        <v>9001</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12087,7 +12158,7 @@
       </c>
       <c r="I29" s="69" t="n">
         <f aca="false">IF($H29=1,INT(($G29-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" s="66" t="n">
         <f aca="false">IF($H29=1,$G29*10000+ROW(),"")</f>
@@ -12095,7 +12166,7 @@
       </c>
       <c r="K29" s="66" t="n">
         <f aca="false">IF($H29=1,$I29*1000+COUNTIFS($I$4:$I$483,$I29,$J$4:$J$483,"&lt;"&amp;$J29)+1,"")</f>
-        <v>11001</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12131,7 +12202,7 @@
       </c>
       <c r="I30" s="69" t="n">
         <f aca="false">IF($H30=1,INT(($G30-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J30" s="66" t="n">
         <f aca="false">IF($H30=1,$G30*10000+ROW(),"")</f>
@@ -12139,7 +12210,7 @@
       </c>
       <c r="K30" s="66" t="n">
         <f aca="false">IF($H30=1,$I30*1000+COUNTIFS($I$4:$I$483,$I30,$J$4:$J$483,"&lt;"&amp;$J30)+1,"")</f>
-        <v>12001</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12175,7 +12246,7 @@
       </c>
       <c r="I31" s="69" t="n">
         <f aca="false">IF($H31=1,INT(($G31-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J31" s="66" t="n">
         <f aca="false">IF($H31=1,$G31*10000+ROW(),"")</f>
@@ -12183,7 +12254,7 @@
       </c>
       <c r="K31" s="66" t="n">
         <f aca="false">IF($H31=1,$I31*1000+COUNTIFS($I$4:$I$483,$I31,$J$4:$J$483,"&lt;"&amp;$J31)+1,"")</f>
-        <v>13001</v>
+        <v>12001</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12215,19 +12286,19 @@
       </c>
       <c r="H32" s="69" t="n">
         <f aca="false">IF($G32="",0,IF(AND($G32&gt;='Cash Flow'!$E$6,$G32&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I32" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I32" s="69" t="n">
         <f aca="false">IF($H32=1,INT(($G32-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J32" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J32" s="66" t="n">
         <f aca="false">IF($H32=1,$G32*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K32" s="66" t="str">
+        <v>463250032</v>
+      </c>
+      <c r="K32" s="66" t="n">
         <f aca="false">IF($H32=1,$I32*1000+COUNTIFS($I$4:$I$483,$I32,$J$4:$J$483,"&lt;"&amp;$J32)+1,"")</f>
-        <v/>
+        <v>13001</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12391,19 +12462,19 @@
       </c>
       <c r="H36" s="69" t="n">
         <f aca="false">IF($G36="",0,IF(AND($G36&gt;='Cash Flow'!$E$6,$G36&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I36" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="69" t="str">
         <f aca="false">IF($H36=1,INT(($G36-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J36" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="66" t="str">
         <f aca="false">IF($H36=1,$G36*10000+ROW(),"")</f>
-        <v>462380036</v>
-      </c>
-      <c r="K36" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K36" s="66" t="str">
         <f aca="false">IF($H36=1,$I36*1000+COUNTIFS($I$4:$I$483,$I36,$J$4:$J$483,"&lt;"&amp;$J36)+1,"")</f>
-        <v>1001</v>
+        <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12439,7 +12510,7 @@
       </c>
       <c r="I37" s="69" t="n">
         <f aca="false">IF($H37=1,INT(($G37-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J37" s="66" t="n">
         <f aca="false">IF($H37=1,$G37*10000+ROW(),"")</f>
@@ -12447,7 +12518,7 @@
       </c>
       <c r="K37" s="66" t="n">
         <f aca="false">IF($H37=1,$I37*1000+COUNTIFS($I$4:$I$483,$I37,$J$4:$J$483,"&lt;"&amp;$J37)+1,"")</f>
-        <v>6002</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12483,7 +12554,7 @@
       </c>
       <c r="I38" s="69" t="n">
         <f aca="false">IF($H38=1,INT(($G38-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J38" s="66" t="n">
         <f aca="false">IF($H38=1,$G38*10000+ROW(),"")</f>
@@ -12491,7 +12562,7 @@
       </c>
       <c r="K38" s="66" t="n">
         <f aca="false">IF($H38=1,$I38*1000+COUNTIFS($I$4:$I$483,$I38,$J$4:$J$483,"&lt;"&amp;$J38)+1,"")</f>
-        <v>10002</v>
+        <v>9002</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12523,19 +12594,19 @@
       </c>
       <c r="H39" s="69" t="n">
         <f aca="false">IF($G39="",0,IF(AND($G39&gt;='Cash Flow'!$E$6,$G39&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I39" s="69" t="n">
         <f aca="false">IF($H39=1,INT(($G39-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J39" s="66" t="n">
         <f aca="false">IF($H39=1,$G39*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="66" t="str">
+        <v>463300039</v>
+      </c>
+      <c r="K39" s="66" t="n">
         <f aca="false">IF($H39=1,$I39*1000+COUNTIFS($I$4:$I$483,$I39,$J$4:$J$483,"&lt;"&amp;$J39)+1,"")</f>
-        <v/>
+        <v>13006</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13095,19 +13166,19 @@
       </c>
       <c r="H52" s="69" t="n">
         <f aca="false">IF($G52="",0,IF(AND($G52&gt;='Cash Flow'!$E$6,$G52&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I52" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="69" t="str">
         <f aca="false">IF($H52=1,INT(($G52-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J52" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J52" s="66" t="str">
         <f aca="false">IF($H52=1,$G52*10000+ROW(),"")</f>
-        <v>462390052</v>
-      </c>
-      <c r="K52" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K52" s="66" t="str">
         <f aca="false">IF($H52=1,$I52*1000+COUNTIFS($I$4:$I$483,$I52,$J$4:$J$483,"&lt;"&amp;$J52)+1,"")</f>
-        <v>1003</v>
+        <v/>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13143,7 +13214,7 @@
       </c>
       <c r="I53" s="69" t="n">
         <f aca="false">IF($H53=1,INT(($G53-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J53" s="66" t="n">
         <f aca="false">IF($H53=1,$G53*10000+ROW(),"")</f>
@@ -13151,7 +13222,7 @@
       </c>
       <c r="K53" s="66" t="n">
         <f aca="false">IF($H53=1,$I53*1000+COUNTIFS($I$4:$I$483,$I53,$J$4:$J$483,"&lt;"&amp;$J53)+1,"")</f>
-        <v>6003</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13187,7 +13258,7 @@
       </c>
       <c r="I54" s="69" t="n">
         <f aca="false">IF($H54=1,INT(($G54-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J54" s="66" t="n">
         <f aca="false">IF($H54=1,$G54*10000+ROW(),"")</f>
@@ -13195,7 +13266,7 @@
       </c>
       <c r="K54" s="66" t="n">
         <f aca="false">IF($H54=1,$I54*1000+COUNTIFS($I$4:$I$483,$I54,$J$4:$J$483,"&lt;"&amp;$J54)+1,"")</f>
-        <v>10003</v>
+        <v>9003</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13227,19 +13298,19 @@
       </c>
       <c r="H55" s="69" t="n">
         <f aca="false">IF($G55="",0,IF(AND($G55&gt;='Cash Flow'!$E$6,$G55&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I55" s="69" t="n">
         <f aca="false">IF($H55=1,INT(($G55-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J55" s="66" t="n">
         <f aca="false">IF($H55=1,$G55*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K55" s="66" t="str">
+        <v>463310055</v>
+      </c>
+      <c r="K55" s="66" t="n">
         <f aca="false">IF($H55=1,$I55*1000+COUNTIFS($I$4:$I$483,$I55,$J$4:$J$483,"&lt;"&amp;$J55)+1,"")</f>
-        <v/>
+        <v>13007</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13799,19 +13870,19 @@
       </c>
       <c r="H68" s="69" t="n">
         <f aca="false">IF($G68="",0,IF(AND($G68&gt;='Cash Flow'!$E$6,$G68&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I68" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="69" t="str">
         <f aca="false">IF($H68=1,INT(($G68-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
-      </c>
-      <c r="J68" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J68" s="66" t="str">
         <f aca="false">IF($H68=1,$G68*10000+ROW(),"")</f>
-        <v>462390068</v>
-      </c>
-      <c r="K68" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K68" s="66" t="str">
         <f aca="false">IF($H68=1,$I68*1000+COUNTIFS($I$4:$I$483,$I68,$J$4:$J$483,"&lt;"&amp;$J68)+1,"")</f>
-        <v>1004</v>
+        <v/>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13847,7 +13918,7 @@
       </c>
       <c r="I69" s="69" t="n">
         <f aca="false">IF($H69=1,INT(($G69-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69" s="66" t="n">
         <f aca="false">IF($H69=1,$G69*10000+ROW(),"")</f>
@@ -13855,7 +13926,7 @@
       </c>
       <c r="K69" s="66" t="n">
         <f aca="false">IF($H69=1,$I69*1000+COUNTIFS($I$4:$I$483,$I69,$J$4:$J$483,"&lt;"&amp;$J69)+1,"")</f>
-        <v>6004</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13891,7 +13962,7 @@
       </c>
       <c r="I70" s="69" t="n">
         <f aca="false">IF($H70=1,INT(($G70-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J70" s="66" t="n">
         <f aca="false">IF($H70=1,$G70*10000+ROW(),"")</f>
@@ -13899,7 +13970,7 @@
       </c>
       <c r="K70" s="66" t="n">
         <f aca="false">IF($H70=1,$I70*1000+COUNTIFS($I$4:$I$483,$I70,$J$4:$J$483,"&lt;"&amp;$J70)+1,"")</f>
-        <v>10004</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13931,19 +14002,19 @@
       </c>
       <c r="H71" s="69" t="n">
         <f aca="false">IF($G71="",0,IF(AND($G71&gt;='Cash Flow'!$E$6,$G71&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I71" s="69" t="n">
         <f aca="false">IF($H71=1,INT(($G71-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J71" s="66" t="n">
         <f aca="false">IF($H71=1,$G71*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K71" s="66" t="str">
+        <v>463310071</v>
+      </c>
+      <c r="K71" s="66" t="n">
         <f aca="false">IF($H71=1,$I71*1000+COUNTIFS($I$4:$I$483,$I71,$J$4:$J$483,"&lt;"&amp;$J71)+1,"")</f>
-        <v/>
+        <v>13008</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14507,7 +14578,7 @@
       </c>
       <c r="I84" s="69" t="n">
         <f aca="false">IF($H84=1,INT(($G84-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J84" s="66" t="n">
         <f aca="false">IF($H84=1,$G84*10000+ROW(),"")</f>
@@ -14515,7 +14586,7 @@
       </c>
       <c r="K84" s="66" t="n">
         <f aca="false">IF($H84=1,$I84*1000+COUNTIFS($I$4:$I$483,$I84,$J$4:$J$483,"&lt;"&amp;$J84)+1,"")</f>
-        <v>2002</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14551,7 +14622,7 @@
       </c>
       <c r="I85" s="69" t="n">
         <f aca="false">IF($H85=1,INT(($G85-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J85" s="66" t="n">
         <f aca="false">IF($H85=1,$G85*10000+ROW(),"")</f>
@@ -14559,7 +14630,7 @@
       </c>
       <c r="K85" s="66" t="n">
         <f aca="false">IF($H85=1,$I85*1000+COUNTIFS($I$4:$I$483,$I85,$J$4:$J$483,"&lt;"&amp;$J85)+1,"")</f>
-        <v>6005</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14595,7 +14666,7 @@
       </c>
       <c r="I86" s="69" t="n">
         <f aca="false">IF($H86=1,INT(($G86-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J86" s="66" t="n">
         <f aca="false">IF($H86=1,$G86*10000+ROW(),"")</f>
@@ -14603,7 +14674,7 @@
       </c>
       <c r="K86" s="66" t="n">
         <f aca="false">IF($H86=1,$I86*1000+COUNTIFS($I$4:$I$483,$I86,$J$4:$J$483,"&lt;"&amp;$J86)+1,"")</f>
-        <v>10006</v>
+        <v>9006</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15211,7 +15282,7 @@
       </c>
       <c r="I100" s="69" t="n">
         <f aca="false">IF($H100=1,INT(($G100-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J100" s="66" t="n">
         <f aca="false">IF($H100=1,$G100*10000+ROW(),"")</f>
@@ -15219,7 +15290,7 @@
       </c>
       <c r="K100" s="66" t="n">
         <f aca="false">IF($H100=1,$I100*1000+COUNTIFS($I$4:$I$483,$I100,$J$4:$J$483,"&lt;"&amp;$J100)+1,"")</f>
-        <v>2003</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15255,7 +15326,7 @@
       </c>
       <c r="I101" s="69" t="n">
         <f aca="false">IF($H101=1,INT(($G101-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J101" s="66" t="n">
         <f aca="false">IF($H101=1,$G101*10000+ROW(),"")</f>
@@ -15263,7 +15334,7 @@
       </c>
       <c r="K101" s="66" t="n">
         <f aca="false">IF($H101=1,$I101*1000+COUNTIFS($I$4:$I$483,$I101,$J$4:$J$483,"&lt;"&amp;$J101)+1,"")</f>
-        <v>6006</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15299,7 +15370,7 @@
       </c>
       <c r="I102" s="69" t="n">
         <f aca="false">IF($H102=1,INT(($G102-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J102" s="66" t="n">
         <f aca="false">IF($H102=1,$G102*10000+ROW(),"")</f>
@@ -15307,7 +15378,7 @@
       </c>
       <c r="K102" s="66" t="n">
         <f aca="false">IF($H102=1,$I102*1000+COUNTIFS($I$4:$I$483,$I102,$J$4:$J$483,"&lt;"&amp;$J102)+1,"")</f>
-        <v>10007</v>
+        <v>9007</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15915,7 +15986,7 @@
       </c>
       <c r="I116" s="69" t="n">
         <f aca="false">IF($H116=1,INT(($G116-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J116" s="66" t="n">
         <f aca="false">IF($H116=1,$G116*10000+ROW(),"")</f>
@@ -15923,7 +15994,7 @@
       </c>
       <c r="K116" s="66" t="n">
         <f aca="false">IF($H116=1,$I116*1000+COUNTIFS($I$4:$I$483,$I116,$J$4:$J$483,"&lt;"&amp;$J116)+1,"")</f>
-        <v>2004</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15959,7 +16030,7 @@
       </c>
       <c r="I117" s="69" t="n">
         <f aca="false">IF($H117=1,INT(($G117-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J117" s="66" t="n">
         <f aca="false">IF($H117=1,$G117*10000+ROW(),"")</f>
@@ -15967,7 +16038,7 @@
       </c>
       <c r="K117" s="66" t="n">
         <f aca="false">IF($H117=1,$I117*1000+COUNTIFS($I$4:$I$483,$I117,$J$4:$J$483,"&lt;"&amp;$J117)+1,"")</f>
-        <v>6008</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16003,7 +16074,7 @@
       </c>
       <c r="I118" s="69" t="n">
         <f aca="false">IF($H118=1,INT(($G118-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J118" s="66" t="n">
         <f aca="false">IF($H118=1,$G118*10000+ROW(),"")</f>
@@ -16011,7 +16082,7 @@
       </c>
       <c r="K118" s="66" t="n">
         <f aca="false">IF($H118=1,$I118*1000+COUNTIFS($I$4:$I$483,$I118,$J$4:$J$483,"&lt;"&amp;$J118)+1,"")</f>
-        <v>11002</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16619,7 +16690,7 @@
       </c>
       <c r="I132" s="69" t="n">
         <f aca="false">IF($H132=1,INT(($G132-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J132" s="66" t="n">
         <f aca="false">IF($H132=1,$G132*10000+ROW(),"")</f>
@@ -16627,7 +16698,7 @@
       </c>
       <c r="K132" s="66" t="n">
         <f aca="false">IF($H132=1,$I132*1000+COUNTIFS($I$4:$I$483,$I132,$J$4:$J$483,"&lt;"&amp;$J132)+1,"")</f>
-        <v>2006</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16663,7 +16734,7 @@
       </c>
       <c r="I133" s="69" t="n">
         <f aca="false">IF($H133=1,INT(($G133-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J133" s="66" t="n">
         <f aca="false">IF($H133=1,$G133*10000+ROW(),"")</f>
@@ -16671,7 +16742,7 @@
       </c>
       <c r="K133" s="66" t="n">
         <f aca="false">IF($H133=1,$I133*1000+COUNTIFS($I$4:$I$483,$I133,$J$4:$J$483,"&lt;"&amp;$J133)+1,"")</f>
-        <v>7002</v>
+        <v>6002</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16707,7 +16778,7 @@
       </c>
       <c r="I134" s="69" t="n">
         <f aca="false">IF($H134=1,INT(($G134-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J134" s="66" t="n">
         <f aca="false">IF($H134=1,$G134*10000+ROW(),"")</f>
@@ -16715,7 +16786,7 @@
       </c>
       <c r="K134" s="66" t="n">
         <f aca="false">IF($H134=1,$I134*1000+COUNTIFS($I$4:$I$483,$I134,$J$4:$J$483,"&lt;"&amp;$J134)+1,"")</f>
-        <v>11003</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17323,7 +17394,7 @@
       </c>
       <c r="I148" s="69" t="n">
         <f aca="false">IF($H148=1,INT(($G148-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J148" s="66" t="n">
         <f aca="false">IF($H148=1,$G148*10000+ROW(),"")</f>
@@ -17331,7 +17402,7 @@
       </c>
       <c r="K148" s="66" t="n">
         <f aca="false">IF($H148=1,$I148*1000+COUNTIFS($I$4:$I$483,$I148,$J$4:$J$483,"&lt;"&amp;$J148)+1,"")</f>
-        <v>3002</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17367,7 +17438,7 @@
       </c>
       <c r="I149" s="69" t="n">
         <f aca="false">IF($H149=1,INT(($G149-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J149" s="66" t="n">
         <f aca="false">IF($H149=1,$G149*10000+ROW(),"")</f>
@@ -17375,7 +17446,7 @@
       </c>
       <c r="K149" s="66" t="n">
         <f aca="false">IF($H149=1,$I149*1000+COUNTIFS($I$4:$I$483,$I149,$J$4:$J$483,"&lt;"&amp;$J149)+1,"")</f>
-        <v>5003</v>
+        <v>4003</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17411,7 +17482,7 @@
       </c>
       <c r="I150" s="69" t="n">
         <f aca="false">IF($H150=1,INT(($G150-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J150" s="66" t="n">
         <f aca="false">IF($H150=1,$G150*10000+ROW(),"")</f>
@@ -17419,7 +17490,7 @@
       </c>
       <c r="K150" s="66" t="n">
         <f aca="false">IF($H150=1,$I150*1000+COUNTIFS($I$4:$I$483,$I150,$J$4:$J$483,"&lt;"&amp;$J150)+1,"")</f>
-        <v>7003</v>
+        <v>6003</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17455,7 +17526,7 @@
       </c>
       <c r="I151" s="69" t="n">
         <f aca="false">IF($H151=1,INT(($G151-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J151" s="66" t="n">
         <f aca="false">IF($H151=1,$G151*10000+ROW(),"")</f>
@@ -17463,7 +17534,7 @@
       </c>
       <c r="K151" s="66" t="n">
         <f aca="false">IF($H151=1,$I151*1000+COUNTIFS($I$4:$I$483,$I151,$J$4:$J$483,"&lt;"&amp;$J151)+1,"")</f>
-        <v>9005</v>
+        <v>8005</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17499,7 +17570,7 @@
       </c>
       <c r="I152" s="69" t="n">
         <f aca="false">IF($H152=1,INT(($G152-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J152" s="66" t="n">
         <f aca="false">IF($H152=1,$G152*10000+ROW(),"")</f>
@@ -17507,7 +17578,7 @@
       </c>
       <c r="K152" s="66" t="n">
         <f aca="false">IF($H152=1,$I152*1000+COUNTIFS($I$4:$I$483,$I152,$J$4:$J$483,"&lt;"&amp;$J152)+1,"")</f>
-        <v>11005</v>
+        <v>10005</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17539,19 +17610,19 @@
       </c>
       <c r="H153" s="69" t="n">
         <f aca="false">IF($G153="",0,IF(AND($G153&gt;='Cash Flow'!$E$6,$G153&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I153" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I153" s="69" t="n">
         <f aca="false">IF($H153=1,INT(($G153-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J153" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J153" s="66" t="n">
         <f aca="false">IF($H153=1,$G153*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K153" s="66" t="str">
+        <v>463250153</v>
+      </c>
+      <c r="K153" s="66" t="n">
         <f aca="false">IF($H153=1,$I153*1000+COUNTIFS($I$4:$I$483,$I153,$J$4:$J$483,"&lt;"&amp;$J153)+1,"")</f>
-        <v/>
+        <v>13002</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18027,7 +18098,7 @@
       </c>
       <c r="I164" s="69" t="n">
         <f aca="false">IF($H164=1,INT(($G164-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J164" s="66" t="n">
         <f aca="false">IF($H164=1,$G164*10000+ROW(),"")</f>
@@ -18035,7 +18106,7 @@
       </c>
       <c r="K164" s="66" t="n">
         <f aca="false">IF($H164=1,$I164*1000+COUNTIFS($I$4:$I$483,$I164,$J$4:$J$483,"&lt;"&amp;$J164)+1,"")</f>
-        <v>3003</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18071,7 +18142,7 @@
       </c>
       <c r="I165" s="69" t="n">
         <f aca="false">IF($H165=1,INT(($G165-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J165" s="66" t="n">
         <f aca="false">IF($H165=1,$G165*10000+ROW(),"")</f>
@@ -18079,7 +18150,7 @@
       </c>
       <c r="K165" s="66" t="n">
         <f aca="false">IF($H165=1,$I165*1000+COUNTIFS($I$4:$I$483,$I165,$J$4:$J$483,"&lt;"&amp;$J165)+1,"")</f>
-        <v>7005</v>
+        <v>6005</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18115,7 +18186,7 @@
       </c>
       <c r="I166" s="69" t="n">
         <f aca="false">IF($H166=1,INT(($G166-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J166" s="66" t="n">
         <f aca="false">IF($H166=1,$G166*10000+ROW(),"")</f>
@@ -18123,7 +18194,7 @@
       </c>
       <c r="K166" s="66" t="n">
         <f aca="false">IF($H166=1,$I166*1000+COUNTIFS($I$4:$I$483,$I166,$J$4:$J$483,"&lt;"&amp;$J166)+1,"")</f>
-        <v>12002</v>
+        <v>11002</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18731,7 +18802,7 @@
       </c>
       <c r="I180" s="69" t="n">
         <f aca="false">IF($H180=1,INT(($G180-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J180" s="66" t="n">
         <f aca="false">IF($H180=1,$G180*10000+ROW(),"")</f>
@@ -18739,7 +18810,7 @@
       </c>
       <c r="K180" s="66" t="n">
         <f aca="false">IF($H180=1,$I180*1000+COUNTIFS($I$4:$I$483,$I180,$J$4:$J$483,"&lt;"&amp;$J180)+1,"")</f>
-        <v>3004</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18775,7 +18846,7 @@
       </c>
       <c r="I181" s="69" t="n">
         <f aca="false">IF($H181=1,INT(($G181-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J181" s="66" t="n">
         <f aca="false">IF($H181=1,$G181*10000+ROW(),"")</f>
@@ -18783,7 +18854,7 @@
       </c>
       <c r="K181" s="66" t="n">
         <f aca="false">IF($H181=1,$I181*1000+COUNTIFS($I$4:$I$483,$I181,$J$4:$J$483,"&lt;"&amp;$J181)+1,"")</f>
-        <v>7006</v>
+        <v>6006</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18819,7 +18890,7 @@
       </c>
       <c r="I182" s="69" t="n">
         <f aca="false">IF($H182=1,INT(($G182-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J182" s="66" t="n">
         <f aca="false">IF($H182=1,$G182*10000+ROW(),"")</f>
@@ -18827,7 +18898,7 @@
       </c>
       <c r="K182" s="66" t="n">
         <f aca="false">IF($H182=1,$I182*1000+COUNTIFS($I$4:$I$483,$I182,$J$4:$J$483,"&lt;"&amp;$J182)+1,"")</f>
-        <v>12003</v>
+        <v>11003</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19435,7 +19506,7 @@
       </c>
       <c r="I196" s="69" t="n">
         <f aca="false">IF($H196=1,INT(($G196-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J196" s="66" t="n">
         <f aca="false">IF($H196=1,$G196*10000+ROW(),"")</f>
@@ -19443,7 +19514,7 @@
       </c>
       <c r="K196" s="66" t="n">
         <f aca="false">IF($H196=1,$I196*1000+COUNTIFS($I$4:$I$483,$I196,$J$4:$J$483,"&lt;"&amp;$J196)+1,"")</f>
-        <v>3005</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19479,7 +19550,7 @@
       </c>
       <c r="I197" s="69" t="n">
         <f aca="false">IF($H197=1,INT(($G197-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J197" s="66" t="n">
         <f aca="false">IF($H197=1,$G197*10000+ROW(),"")</f>
@@ -19487,7 +19558,7 @@
       </c>
       <c r="K197" s="66" t="n">
         <f aca="false">IF($H197=1,$I197*1000+COUNTIFS($I$4:$I$483,$I197,$J$4:$J$483,"&lt;"&amp;$J197)+1,"")</f>
-        <v>8002</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19523,7 +19594,7 @@
       </c>
       <c r="I198" s="69" t="n">
         <f aca="false">IF($H198=1,INT(($G198-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J198" s="66" t="n">
         <f aca="false">IF($H198=1,$G198*10000+ROW(),"")</f>
@@ -19531,7 +19602,7 @@
       </c>
       <c r="K198" s="66" t="n">
         <f aca="false">IF($H198=1,$I198*1000+COUNTIFS($I$4:$I$483,$I198,$J$4:$J$483,"&lt;"&amp;$J198)+1,"")</f>
-        <v>12004</v>
+        <v>11004</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20139,7 +20210,7 @@
       </c>
       <c r="I212" s="69" t="n">
         <f aca="false">IF($H212=1,INT(($G212-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J212" s="66" t="n">
         <f aca="false">IF($H212=1,$G212*10000+ROW(),"")</f>
@@ -20147,7 +20218,7 @@
       </c>
       <c r="K212" s="66" t="n">
         <f aca="false">IF($H212=1,$I212*1000+COUNTIFS($I$4:$I$483,$I212,$J$4:$J$483,"&lt;"&amp;$J212)+1,"")</f>
-        <v>4002</v>
+        <v>3002</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20183,7 +20254,7 @@
       </c>
       <c r="I213" s="69" t="n">
         <f aca="false">IF($H213=1,INT(($G213-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J213" s="66" t="n">
         <f aca="false">IF($H213=1,$G213*10000+ROW(),"")</f>
@@ -20191,7 +20262,7 @@
       </c>
       <c r="K213" s="66" t="n">
         <f aca="false">IF($H213=1,$I213*1000+COUNTIFS($I$4:$I$483,$I213,$J$4:$J$483,"&lt;"&amp;$J213)+1,"")</f>
-        <v>9002</v>
+        <v>8002</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20227,7 +20298,7 @@
       </c>
       <c r="I214" s="69" t="n">
         <f aca="false">IF($H214=1,INT(($G214-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J214" s="66" t="n">
         <f aca="false">IF($H214=1,$G214*10000+ROW(),"")</f>
@@ -20235,7 +20306,7 @@
       </c>
       <c r="K214" s="66" t="n">
         <f aca="false">IF($H214=1,$I214*1000+COUNTIFS($I$4:$I$483,$I214,$J$4:$J$483,"&lt;"&amp;$J214)+1,"")</f>
-        <v>13002</v>
+        <v>12002</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20843,7 +20914,7 @@
       </c>
       <c r="I228" s="69" t="n">
         <f aca="false">IF($H228=1,INT(($G228-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J228" s="66" t="n">
         <f aca="false">IF($H228=1,$G228*10000+ROW(),"")</f>
@@ -20851,7 +20922,7 @@
       </c>
       <c r="K228" s="66" t="n">
         <f aca="false">IF($H228=1,$I228*1000+COUNTIFS($I$4:$I$483,$I228,$J$4:$J$483,"&lt;"&amp;$J228)+1,"")</f>
-        <v>4003</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20887,7 +20958,7 @@
       </c>
       <c r="I229" s="69" t="n">
         <f aca="false">IF($H229=1,INT(($G229-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J229" s="66" t="n">
         <f aca="false">IF($H229=1,$G229*10000+ROW(),"")</f>
@@ -20895,7 +20966,7 @@
       </c>
       <c r="K229" s="66" t="n">
         <f aca="false">IF($H229=1,$I229*1000+COUNTIFS($I$4:$I$483,$I229,$J$4:$J$483,"&lt;"&amp;$J229)+1,"")</f>
-        <v>9003</v>
+        <v>8003</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20931,7 +21002,7 @@
       </c>
       <c r="I230" s="69" t="n">
         <f aca="false">IF($H230=1,INT(($G230-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J230" s="66" t="n">
         <f aca="false">IF($H230=1,$G230*10000+ROW(),"")</f>
@@ -20939,7 +21010,7 @@
       </c>
       <c r="K230" s="66" t="n">
         <f aca="false">IF($H230=1,$I230*1000+COUNTIFS($I$4:$I$483,$I230,$J$4:$J$483,"&lt;"&amp;$J230)+1,"")</f>
-        <v>13003</v>
+        <v>12003</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21547,7 +21618,7 @@
       </c>
       <c r="I244" s="69" t="n">
         <f aca="false">IF($H244=1,INT(($G244-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J244" s="66" t="n">
         <f aca="false">IF($H244=1,$G244*10000+ROW(),"")</f>
@@ -21555,7 +21626,7 @@
       </c>
       <c r="K244" s="66" t="n">
         <f aca="false">IF($H244=1,$I244*1000+COUNTIFS($I$4:$I$483,$I244,$J$4:$J$483,"&lt;"&amp;$J244)+1,"")</f>
-        <v>5002</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21591,7 +21662,7 @@
       </c>
       <c r="I245" s="69" t="n">
         <f aca="false">IF($H245=1,INT(($G245-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J245" s="66" t="n">
         <f aca="false">IF($H245=1,$G245*10000+ROW(),"")</f>
@@ -21599,7 +21670,7 @@
       </c>
       <c r="K245" s="66" t="n">
         <f aca="false">IF($H245=1,$I245*1000+COUNTIFS($I$4:$I$483,$I245,$J$4:$J$483,"&lt;"&amp;$J245)+1,"")</f>
-        <v>9006</v>
+        <v>8006</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21631,19 +21702,19 @@
       </c>
       <c r="H246" s="69" t="n">
         <f aca="false">IF($G246="",0,IF(AND($G246&gt;='Cash Flow'!$E$6,$G246&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I246" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I246" s="69" t="n">
         <f aca="false">IF($H246=1,INT(($G246-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J246" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J246" s="66" t="n">
         <f aca="false">IF($H246=1,$G246*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K246" s="66" t="str">
+        <v>463250246</v>
+      </c>
+      <c r="K246" s="66" t="n">
         <f aca="false">IF($H246=1,$I246*1000+COUNTIFS($I$4:$I$483,$I246,$J$4:$J$483,"&lt;"&amp;$J246)+1,"")</f>
-        <v/>
+        <v>13003</v>
       </c>
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22251,7 +22322,7 @@
       </c>
       <c r="I260" s="69" t="n">
         <f aca="false">IF($H260=1,INT(($G260-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J260" s="66" t="n">
         <f aca="false">IF($H260=1,$G260*10000+ROW(),"")</f>
@@ -22259,7 +22330,7 @@
       </c>
       <c r="K260" s="66" t="n">
         <f aca="false">IF($H260=1,$I260*1000+COUNTIFS($I$4:$I$483,$I260,$J$4:$J$483,"&lt;"&amp;$J260)+1,"")</f>
-        <v>5004</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22295,7 +22366,7 @@
       </c>
       <c r="I261" s="69" t="n">
         <f aca="false">IF($H261=1,INT(($G261-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J261" s="66" t="n">
         <f aca="false">IF($H261=1,$G261*10000+ROW(),"")</f>
@@ -22303,7 +22374,7 @@
       </c>
       <c r="K261" s="66" t="n">
         <f aca="false">IF($H261=1,$I261*1000+COUNTIFS($I$4:$I$483,$I261,$J$4:$J$483,"&lt;"&amp;$J261)+1,"")</f>
-        <v>9007</v>
+        <v>8007</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22335,19 +22406,19 @@
       </c>
       <c r="H262" s="69" t="n">
         <f aca="false">IF($G262="",0,IF(AND($G262&gt;='Cash Flow'!$E$6,$G262&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I262" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I262" s="69" t="n">
         <f aca="false">IF($H262=1,INT(($G262-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J262" s="66" t="str">
+        <v>13</v>
+      </c>
+      <c r="J262" s="66" t="n">
         <f aca="false">IF($H262=1,$G262*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K262" s="66" t="str">
+        <v>463260262</v>
+      </c>
+      <c r="K262" s="66" t="n">
         <f aca="false">IF($H262=1,$I262*1000+COUNTIFS($I$4:$I$483,$I262,$J$4:$J$483,"&lt;"&amp;$J262)+1,"")</f>
-        <v/>
+        <v>13004</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Cash Flow'!$A$1:$K$284</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$40</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$42</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Recurring!$A$1:$J$38</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Recurring!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$J$28</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="163">
   <si>
     <t xml:space="preserve">WEEKLY CASH FLOW SURVIVAL WORKSHEET</t>
   </si>
@@ -138,6 +138,12 @@
     <t xml:space="preserve">Undo, or copy the same cell from the row above or below and let Excel adjust it.</t>
   </si>
   <si>
+    <t xml:space="preserve">Already paid or already received</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Do NOT zero out the row. Go to the Recurring tab and move that transaction's Next Due Date forward to its following occurrence — that is a blue cell you are meant to edit, with no formula anywhere near it. The occurrence disappears from the cash flow and every later one still lands correctly. Your beginning balance already contains the money, so counting it again would overstate the whole 13 weeks.</t>
+  </si>
+  <si>
     <t xml:space="preserve">FREQUENCIES THE SHEET UNDERSTANDS</t>
   </si>
   <si>
@@ -181,6 +187,9 @@
   </si>
   <si>
     <t xml:space="preserve">Amounts are entered as positive numbers. The Type column (Income or Expense) decides the sign, so a $90 paycheck is Type = Income, amount 90.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sheet opens on Fri Aug 7, 2026 with $71.17 already in hand. The Aug 7 Compunnel paycheck had already landed by then, so its Next Due Date is Aug 14 — the first one still to come. Bruno's, Apple: Claude, OpenAI and Obsidian were rolled forward for the same reason. Google One ($4.99) and Upstart ($500) are still shown as due on Aug 7; if those already came out of the account, roll them forward to Sep 7 too.</t>
   </si>
   <si>
     <t xml:space="preserve">Progressive Insurance ($143.37) was cut off at the bottom of the third screenshot, so its due date is set to Aug 31, 2026. Correct it on the Recurring tab if that is wrong.</t>
@@ -1361,7 +1370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:C40"/>
+  <dimension ref="B2:C42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1515,16 +1524,16 @@
         <v>34</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="3" t="s">
+    <row r="25" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="10" t="s">
         <v>35</v>
       </c>
+      <c r="C25" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1560,65 +1569,81 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="10" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="11" t="s">
+      <c r="C32" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="12" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="3" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1654,44 +1679,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1699,28 +1724,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D5" s="16" t="n">
         <v>90</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -1729,28 +1754,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D6" s="21" t="n">
         <v>790</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="G6" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J6" s="19"/>
     </row>
@@ -1759,28 +1784,28 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D7" s="16" t="n">
         <v>21.1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>46238</v>
+        <v>46269</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -1789,28 +1814,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D8" s="21" t="n">
         <v>20</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J8" s="19"/>
     </row>
@@ -1819,28 +1844,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>77</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>74</v>
       </c>
       <c r="D9" s="16" t="n">
         <v>10</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1849,28 +1874,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D10" s="21" t="n">
         <v>4.99</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" s="22" t="n">
         <v>46241</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I10" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J10" s="19"/>
     </row>
@@ -1879,28 +1904,28 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D11" s="16" t="n">
         <v>500</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F11" s="17" t="n">
         <v>46241</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -1909,28 +1934,28 @@
         <v>8</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D12" s="21" t="n">
         <v>163.5</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F12" s="22" t="n">
         <v>46244</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J12" s="19"/>
     </row>
@@ -1939,28 +1964,28 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D13" s="16" t="n">
         <v>2.99</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F13" s="17" t="n">
         <v>46247</v>
       </c>
       <c r="G13" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -1969,28 +1994,28 @@
         <v>10</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" s="21" t="n">
         <v>350</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F14" s="22" t="n">
         <v>46248</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I14" s="19" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="J14" s="19"/>
     </row>
@@ -1999,28 +2024,28 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D15" s="16" t="n">
         <v>171.1</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F15" s="17" t="n">
         <v>46250</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -2029,28 +2054,28 @@
         <v>12</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D16" s="21" t="n">
         <v>45</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F16" s="22" t="n">
         <v>46250</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J16" s="19"/>
     </row>
@@ -2059,28 +2084,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D17" s="16" t="n">
         <v>16.99</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F17" s="17" t="n">
         <v>46252</v>
       </c>
       <c r="G17" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H17" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2089,28 +2114,28 @@
         <v>14</v>
       </c>
       <c r="B18" s="19" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D18" s="21" t="n">
         <v>13.7</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F18" s="22" t="n">
         <v>46259</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I18" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="J18" s="19"/>
     </row>
@@ -2119,28 +2144,28 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>43.87</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F19" s="17" t="n">
         <v>46259</v>
       </c>
       <c r="G19" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H19" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -2149,28 +2174,28 @@
         <v>16</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D20" s="21" t="n">
         <v>150</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F20" s="22" t="n">
         <v>46264</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I20" s="19" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J20" s="19"/>
     </row>
@@ -2179,28 +2204,28 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D21" s="16" t="n">
         <v>143.37</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F21" s="17" t="n">
         <v>46265</v>
       </c>
       <c r="G21" s="15" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H21" s="15" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J21" s="6"/>
     </row>
@@ -2388,17 +2413,17 @@
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="12" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="12" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="23" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -2466,17 +2491,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>71.17</v>
@@ -2484,7 +2509,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E6" s="25" t="n">
         <v>46241</v>
@@ -2496,7 +2521,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7" s="24" t="n">
         <v>200</v>
@@ -2504,7 +2529,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="27" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E8" s="28" t="n">
         <f aca="true">TODAY()</f>
@@ -2513,12 +2538,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="23" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2531,7 +2556,7 @@
       <c r="E13" s="30"/>
       <c r="F13" s="30"/>
       <c r="G13" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H13" s="30"/>
       <c r="I13" s="32" t="n">
@@ -2546,37 +2571,37 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C14" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G14" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H14" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J14" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Compunnel Software (paycheck)</v>
+        <v>Google One</v>
       </c>
       <c r="C15" s="34" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$G$4:$G$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
@@ -2584,24 +2609,24 @@
       </c>
       <c r="D15" s="35" t="str">
         <f aca="false">IF($B15="","",INDEX(Schedule!$D$4:$D$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$E$4:$E$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>790</v>
+        <v>4.99</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="36" t="n">
         <f aca="false">IF($B15="","",IF($F15&lt;&gt;"",$F15,$E15))</f>
-        <v>790</v>
+        <v>4.99</v>
       </c>
       <c r="H15" s="36" t="n">
         <f aca="false">IF($B15="",0,IF($D15="Income",$G15,-$G15))</f>
-        <v>790</v>
+        <v>-4.99</v>
       </c>
       <c r="I15" s="37" t="n">
         <f aca="false">IF($B15="","",$I$13+SUM($H$15:$H15))</f>
-        <v>861.17</v>
+        <v>66.18</v>
       </c>
       <c r="J15" s="38" t="str">
         <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2611,7 +2636,7 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
+        <v>Upstart (loan)</v>
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$G$4:$G$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
@@ -2623,20 +2648,20 @@
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$E$4:$E$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v>500</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="36" t="n">
         <f aca="false">IF($B16="","",IF($F16&lt;&gt;"",$F16,$E16))</f>
-        <v>4.99</v>
+        <v>500</v>
       </c>
       <c r="H16" s="36" t="n">
         <f aca="false">IF($B16="",0,IF($D16="Income",$G16,-$G16))</f>
-        <v>-4.99</v>
+        <v>-500</v>
       </c>
       <c r="I16" s="37" t="n">
         <f aca="false">IF($B16="","",$I$13+SUM($H$15:$H16))</f>
-        <v>856.18</v>
+        <v>-433.82</v>
       </c>
       <c r="J16" s="38" t="str">
         <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2646,11 +2671,11 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
+        <v>Central Maine Power Co.</v>
       </c>
       <c r="C17" s="34" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$G$4:$G$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="D17" s="35" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$D$4:$D$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
@@ -2658,20 +2683,20 @@
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$E$4:$E$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v>163.5</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="36" t="n">
         <f aca="false">IF($B17="","",IF($F17&lt;&gt;"",$F17,$E17))</f>
-        <v>500</v>
+        <v>163.5</v>
       </c>
       <c r="H17" s="36" t="n">
         <f aca="false">IF($B17="",0,IF($D17="Income",$G17,-$G17))</f>
-        <v>-500</v>
+        <v>-163.5</v>
       </c>
       <c r="I17" s="37" t="n">
         <f aca="false">IF($B17="","",$I$13+SUM($H$15:$H17))</f>
-        <v>356.18</v>
+        <v>-597.32</v>
       </c>
       <c r="J17" s="38" t="str">
         <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2681,32 +2706,32 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C18" s="34" t="n">
         <f aca="false">IF($B18="","",INDEX(Schedule!$G$4:$G$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="D18" s="35" t="str">
         <f aca="false">IF($B18="","",INDEX(Schedule!$D$4:$D$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E18" s="36" t="n">
         <f aca="false">IF($B18="","",INDEX(Schedule!$E$4:$E$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>90</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="36" t="n">
         <f aca="false">IF($B18="","",IF($F18&lt;&gt;"",$F18,$E18))</f>
-        <v>163.5</v>
+        <v>90</v>
       </c>
       <c r="H18" s="36" t="n">
         <f aca="false">IF($B18="",0,IF($D18="Income",$G18,-$G18))</f>
-        <v>-163.5</v>
+        <v>90</v>
       </c>
       <c r="I18" s="37" t="n">
         <f aca="false">IF($B18="","",$I$13+SUM($H$15:$H18))</f>
-        <v>192.68</v>
+        <v>-507.32</v>
       </c>
       <c r="J18" s="38" t="str">
         <f aca="true">IF($B18="","",IF($F18&lt;&gt;"","PAID",IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2716,32 +2741,32 @@
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C19" s="34" t="n">
         <f aca="false">IF($B19="","",INDEX(Schedule!$G$4:$G$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D19" s="35" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$D$4:$D$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E19" s="36" t="n">
         <f aca="false">IF($B19="","",INDEX(Schedule!$E$4:$E$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>2.99</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="36" t="n">
         <f aca="false">IF($B19="","",IF($F19&lt;&gt;"",$F19,$E19))</f>
-        <v>90</v>
+        <v>2.99</v>
       </c>
       <c r="H19" s="36" t="n">
         <f aca="false">IF($B19="",0,IF($D19="Income",$G19,-$G19))</f>
-        <v>90</v>
+        <v>-2.99</v>
       </c>
       <c r="I19" s="37" t="n">
         <f aca="false">IF($B19="","",$I$13+SUM($H$15:$H19))</f>
-        <v>282.68</v>
+        <v>-510.31</v>
       </c>
       <c r="J19" s="38" t="str">
         <f aca="true">IF($B19="","",IF($F19&lt;&gt;"","PAID",IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2751,36 +2776,36 @@
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1006,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
-      </c>
-      <c r="C20" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C20" s="34" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$G$4:$G$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v>46247</v>
+        <v/>
       </c>
       <c r="D20" s="35" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$D$4:$D$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E20" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="36" t="str">
         <f aca="false">IF($B20="","",INDEX(Schedule!$E$4:$E$483,MATCH(1006,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="F20" s="16"/>
-      <c r="G20" s="36" t="n">
+      <c r="G20" s="36" t="str">
         <f aca="false">IF($B20="","",IF($F20&lt;&gt;"",$F20,$E20))</f>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="H20" s="36" t="n">
         <f aca="false">IF($B20="",0,IF($D20="Income",$G20,-$G20))</f>
-        <v>-2.99</v>
-      </c>
-      <c r="I20" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="37" t="str">
         <f aca="false">IF($B20="","",$I$13+SUM($H$15:$H20))</f>
-        <v>279.69</v>
+        <v/>
       </c>
       <c r="J20" s="38" t="str">
         <f aca="true">IF($B20="","",IF($F20&lt;&gt;"","PAID",IF($C20&lt;TODAY(),"PAST DUE",IF($C20&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2925,7 +2950,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C25" s="40"/>
       <c r="D25" s="40"/>
@@ -3076,13 +3101,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="41" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C32" s="42"/>
       <c r="D32" s="42"/>
       <c r="E32" s="43" t="n">
         <f aca="false">SUM($E$15:$E$31)</f>
-        <v>1551.48</v>
+        <v>761.48</v>
       </c>
       <c r="F32" s="43" t="n">
         <f aca="false">SUM($F$15:$F$24)</f>
@@ -3090,23 +3115,23 @@
       </c>
       <c r="G32" s="43" t="n">
         <f aca="false">SUM($G$15:$G$31)</f>
-        <v>1551.48</v>
+        <v>761.48</v>
       </c>
       <c r="H32" s="43" t="n">
         <f aca="false">SUM($H$15:$H$31)</f>
-        <v>208.52</v>
+        <v>-581.48</v>
       </c>
       <c r="I32" s="44" t="n">
         <f aca="false">$I$13+SUM($H$15:$H$31)</f>
-        <v>279.69</v>
+        <v>-510.31</v>
       </c>
       <c r="J32" s="45" t="str">
         <f aca="false">IF($I$32&lt;0,"SHORTFALL",IF($I$32&lt;$E$7,"TIGHT","OK"))</f>
-        <v>OK</v>
+        <v>SHORTFALL</v>
       </c>
       <c r="K32" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$15:$D$31,"Income",$G$15:$G$31),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$15:$D$31,"Expense",$G$15:$G$31),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$32,"$#,##0.00")</f>
-        <v>Income $880.00   less expenses $671.48   =  net $208.52</v>
+        <v>Income $90.00   less expenses $671.48   =  net -$581.48</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3119,12 +3144,12 @@
       <c r="E34" s="30"/>
       <c r="F34" s="30"/>
       <c r="G34" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H34" s="30"/>
       <c r="I34" s="32" t="n">
         <f aca="false">$I$32</f>
-        <v>279.69</v>
+        <v>-510.31</v>
       </c>
       <c r="J34" s="30"/>
       <c r="K34" s="26" t="str">
@@ -3134,31 +3159,31 @@
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F35" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G35" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H35" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I35" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3189,7 +3214,7 @@
       </c>
       <c r="I36" s="37" t="n">
         <f aca="false">IF($B36="","",$I$34+SUM($H$36:$H36))</f>
-        <v>1069.69</v>
+        <v>279.69</v>
       </c>
       <c r="J36" s="38" t="str">
         <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3224,7 +3249,7 @@
       </c>
       <c r="I37" s="37" t="n">
         <f aca="false">IF($B37="","",$I$34+SUM($H$36:$H37))</f>
-        <v>719.69</v>
+        <v>-70.31</v>
       </c>
       <c r="J37" s="38" t="str">
         <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3259,7 +3284,7 @@
       </c>
       <c r="I38" s="37" t="n">
         <f aca="false">IF($B38="","",$I$34+SUM($H$36:$H38))</f>
-        <v>548.59</v>
+        <v>-241.41</v>
       </c>
       <c r="J38" s="38" t="str">
         <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3294,7 +3319,7 @@
       </c>
       <c r="I39" s="37" t="n">
         <f aca="false">IF($B39="","",$I$34+SUM($H$36:$H39))</f>
-        <v>503.59</v>
+        <v>-286.41</v>
       </c>
       <c r="J39" s="38" t="str">
         <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3329,7 +3354,7 @@
       </c>
       <c r="I40" s="37" t="n">
         <f aca="false">IF($B40="","",$I$34+SUM($H$36:$H40))</f>
-        <v>486.6</v>
+        <v>-303.4</v>
       </c>
       <c r="J40" s="38" t="str">
         <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3364,7 +3389,7 @@
       </c>
       <c r="I41" s="37" t="n">
         <f aca="false">IF($B41="","",$I$34+SUM($H$36:$H41))</f>
-        <v>576.6</v>
+        <v>-213.4</v>
       </c>
       <c r="J41" s="38" t="str">
         <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3513,7 +3538,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C46" s="40"/>
       <c r="D46" s="40"/>
@@ -3664,7 +3689,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="41" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C53" s="42"/>
       <c r="D53" s="42"/>
@@ -3686,11 +3711,11 @@
       </c>
       <c r="I53" s="44" t="n">
         <f aca="false">$I$34+SUM($H$36:$H$52)</f>
-        <v>576.6</v>
+        <v>-213.4</v>
       </c>
       <c r="J53" s="45" t="str">
         <f aca="false">IF($I$53&lt;0,"SHORTFALL",IF($I$53&lt;$E$7,"TIGHT","OK"))</f>
-        <v>OK</v>
+        <v>SHORTFALL</v>
       </c>
       <c r="K53" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$36:$D$52,"Income",$G$36:$G$52),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$36:$D$52,"Expense",$G$36:$G$52),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$53,"$#,##0.00")</f>
@@ -3707,12 +3732,12 @@
       <c r="E55" s="30"/>
       <c r="F55" s="30"/>
       <c r="G55" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H55" s="30"/>
       <c r="I55" s="32" t="n">
         <f aca="false">$I$53</f>
-        <v>576.6</v>
+        <v>-213.4</v>
       </c>
       <c r="J55" s="30"/>
       <c r="K55" s="26" t="str">
@@ -3722,31 +3747,31 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C56" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D56" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F56" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G56" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H56" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J56" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3777,7 +3802,7 @@
       </c>
       <c r="I57" s="37" t="n">
         <f aca="false">IF($B57="","",$I$55+SUM($H$57:$H57))</f>
-        <v>1366.6</v>
+        <v>576.6</v>
       </c>
       <c r="J57" s="38" t="str">
         <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3812,7 +3837,7 @@
       </c>
       <c r="I58" s="37" t="n">
         <f aca="false">IF($B58="","",$I$55+SUM($H$57:$H58))</f>
-        <v>1352.9</v>
+        <v>562.9</v>
       </c>
       <c r="J58" s="38" t="str">
         <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3847,7 +3872,7 @@
       </c>
       <c r="I59" s="37" t="n">
         <f aca="false">IF($B59="","",$I$55+SUM($H$57:$H59))</f>
-        <v>1309.03</v>
+        <v>519.03</v>
       </c>
       <c r="J59" s="38" t="str">
         <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3882,7 +3907,7 @@
       </c>
       <c r="I60" s="37" t="n">
         <f aca="false">IF($B60="","",$I$55+SUM($H$57:$H60))</f>
-        <v>1399.03</v>
+        <v>609.03</v>
       </c>
       <c r="J60" s="38" t="str">
         <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4101,7 +4126,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C67" s="40"/>
       <c r="D67" s="40"/>
@@ -4252,7 +4277,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="41" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C74" s="42"/>
       <c r="D74" s="42"/>
@@ -4274,7 +4299,7 @@
       </c>
       <c r="I74" s="44" t="n">
         <f aca="false">$I$55+SUM($H$57:$H$73)</f>
-        <v>1399.03</v>
+        <v>609.03</v>
       </c>
       <c r="J74" s="45" t="str">
         <f aca="false">IF($I$74&lt;0,"SHORTFALL",IF($I$74&lt;$E$7,"TIGHT","OK"))</f>
@@ -4295,12 +4320,12 @@
       <c r="E76" s="30"/>
       <c r="F76" s="30"/>
       <c r="G76" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H76" s="30"/>
       <c r="I76" s="32" t="n">
         <f aca="false">$I$74</f>
-        <v>1399.03</v>
+        <v>609.03</v>
       </c>
       <c r="J76" s="30"/>
       <c r="K76" s="26" t="str">
@@ -4310,31 +4335,31 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G77" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H77" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I77" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J77" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4365,7 +4390,7 @@
       </c>
       <c r="I78" s="37" t="n">
         <f aca="false">IF($B78="","",$I$76+SUM($H$78:$H78))</f>
-        <v>2189.03</v>
+        <v>1399.03</v>
       </c>
       <c r="J78" s="38" t="str">
         <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4400,7 +4425,7 @@
       </c>
       <c r="I79" s="37" t="n">
         <f aca="false">IF($B79="","",$I$76+SUM($H$78:$H79))</f>
-        <v>2039.03</v>
+        <v>1249.03</v>
       </c>
       <c r="J79" s="38" t="str">
         <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4435,7 +4460,7 @@
       </c>
       <c r="I80" s="37" t="n">
         <f aca="false">IF($B80="","",$I$76+SUM($H$78:$H80))</f>
-        <v>1689.03</v>
+        <v>899.03</v>
       </c>
       <c r="J80" s="38" t="str">
         <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4470,7 +4495,7 @@
       </c>
       <c r="I81" s="37" t="n">
         <f aca="false">IF($B81="","",$I$76+SUM($H$78:$H81))</f>
-        <v>1545.66</v>
+        <v>755.66</v>
       </c>
       <c r="J81" s="38" t="str">
         <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4505,7 +4530,7 @@
       </c>
       <c r="I82" s="37" t="n">
         <f aca="false">IF($B82="","",$I$76+SUM($H$78:$H82))</f>
-        <v>1635.66</v>
+        <v>845.66</v>
       </c>
       <c r="J82" s="38" t="str">
         <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4689,7 +4714,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C88" s="40"/>
       <c r="D88" s="40"/>
@@ -4840,7 +4865,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="41" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C95" s="42"/>
       <c r="D95" s="42"/>
@@ -4862,7 +4887,7 @@
       </c>
       <c r="I95" s="44" t="n">
         <f aca="false">$I$76+SUM($H$78:$H$94)</f>
-        <v>1635.66</v>
+        <v>845.66</v>
       </c>
       <c r="J95" s="45" t="str">
         <f aca="false">IF($I$95&lt;0,"SHORTFALL",IF($I$95&lt;$E$7,"TIGHT","OK"))</f>
@@ -4883,12 +4908,12 @@
       <c r="E97" s="30"/>
       <c r="F97" s="30"/>
       <c r="G97" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H97" s="30"/>
       <c r="I97" s="32" t="n">
         <f aca="false">$I$95</f>
-        <v>1635.66</v>
+        <v>845.66</v>
       </c>
       <c r="J97" s="30"/>
       <c r="K97" s="26" t="str">
@@ -4898,31 +4923,31 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E98" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F98" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G98" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H98" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I98" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J98" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4953,7 +4978,7 @@
       </c>
       <c r="I99" s="37" t="n">
         <f aca="false">IF($B99="","",$I$97+SUM($H$99:$H99))</f>
-        <v>2425.66</v>
+        <v>1635.66</v>
       </c>
       <c r="J99" s="38" t="str">
         <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4988,7 +5013,7 @@
       </c>
       <c r="I100" s="37" t="n">
         <f aca="false">IF($B100="","",$I$97+SUM($H$99:$H100))</f>
-        <v>2404.56</v>
+        <v>1614.56</v>
       </c>
       <c r="J100" s="38" t="str">
         <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5023,7 +5048,7 @@
       </c>
       <c r="I101" s="37" t="n">
         <f aca="false">IF($B101="","",$I$97+SUM($H$99:$H101))</f>
-        <v>2384.56</v>
+        <v>1594.56</v>
       </c>
       <c r="J101" s="38" t="str">
         <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5058,7 +5083,7 @@
       </c>
       <c r="I102" s="37" t="n">
         <f aca="false">IF($B102="","",$I$97+SUM($H$99:$H102))</f>
-        <v>2374.56</v>
+        <v>1584.56</v>
       </c>
       <c r="J102" s="38" t="str">
         <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5093,7 +5118,7 @@
       </c>
       <c r="I103" s="37" t="n">
         <f aca="false">IF($B103="","",$I$97+SUM($H$99:$H103))</f>
-        <v>2369.57</v>
+        <v>1579.57</v>
       </c>
       <c r="J103" s="38" t="str">
         <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5128,7 +5153,7 @@
       </c>
       <c r="I104" s="37" t="n">
         <f aca="false">IF($B104="","",$I$97+SUM($H$99:$H104))</f>
-        <v>1869.57</v>
+        <v>1079.57</v>
       </c>
       <c r="J104" s="38" t="str">
         <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5163,7 +5188,7 @@
       </c>
       <c r="I105" s="37" t="n">
         <f aca="false">IF($B105="","",$I$97+SUM($H$99:$H105))</f>
-        <v>1959.57</v>
+        <v>1169.57</v>
       </c>
       <c r="J105" s="38" t="str">
         <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5198,7 +5223,7 @@
       </c>
       <c r="I106" s="37" t="n">
         <f aca="false">IF($B106="","",$I$97+SUM($H$99:$H106))</f>
-        <v>1796.07</v>
+        <v>1006.07</v>
       </c>
       <c r="J106" s="38" t="str">
         <f aca="true">IF($B106="","",IF($F106&lt;&gt;"","PAID",IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5277,7 +5302,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C109" s="40"/>
       <c r="D109" s="40"/>
@@ -5428,7 +5453,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="41" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C116" s="42"/>
       <c r="D116" s="42"/>
@@ -5450,7 +5475,7 @@
       </c>
       <c r="I116" s="44" t="n">
         <f aca="false">$I$97+SUM($H$99:$H$115)</f>
-        <v>1796.07</v>
+        <v>1006.07</v>
       </c>
       <c r="J116" s="45" t="str">
         <f aca="false">IF($I$116&lt;0,"SHORTFALL",IF($I$116&lt;$E$7,"TIGHT","OK"))</f>
@@ -5471,12 +5496,12 @@
       <c r="E118" s="30"/>
       <c r="F118" s="30"/>
       <c r="G118" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H118" s="30"/>
       <c r="I118" s="32" t="n">
         <f aca="false">$I$116</f>
-        <v>1796.07</v>
+        <v>1006.07</v>
       </c>
       <c r="J118" s="30"/>
       <c r="K118" s="26" t="str">
@@ -5486,31 +5511,31 @@
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C119" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D119" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E119" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F119" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G119" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H119" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I119" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J119" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5541,7 +5566,7 @@
       </c>
       <c r="I120" s="37" t="n">
         <f aca="false">IF($B120="","",$I$118+SUM($H$120:$H120))</f>
-        <v>2586.07</v>
+        <v>1796.07</v>
       </c>
       <c r="J120" s="38" t="str">
         <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5576,7 +5601,7 @@
       </c>
       <c r="I121" s="37" t="n">
         <f aca="false">IF($B121="","",$I$118+SUM($H$120:$H121))</f>
-        <v>2583.08</v>
+        <v>1793.08</v>
       </c>
       <c r="J121" s="38" t="str">
         <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5611,7 +5636,7 @@
       </c>
       <c r="I122" s="37" t="n">
         <f aca="false">IF($B122="","",$I$118+SUM($H$120:$H122))</f>
-        <v>2233.08</v>
+        <v>1443.08</v>
       </c>
       <c r="J122" s="38" t="str">
         <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5646,7 +5671,7 @@
       </c>
       <c r="I123" s="37" t="n">
         <f aca="false">IF($B123="","",$I$118+SUM($H$120:$H123))</f>
-        <v>2323.08</v>
+        <v>1533.08</v>
       </c>
       <c r="J123" s="38" t="str">
         <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5681,7 +5706,7 @@
       </c>
       <c r="I124" s="37" t="n">
         <f aca="false">IF($B124="","",$I$118+SUM($H$120:$H124))</f>
-        <v>2151.98</v>
+        <v>1361.98</v>
       </c>
       <c r="J124" s="38" t="str">
         <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5716,7 +5741,7 @@
       </c>
       <c r="I125" s="37" t="n">
         <f aca="false">IF($B125="","",$I$118+SUM($H$120:$H125))</f>
-        <v>2106.98</v>
+        <v>1316.98</v>
       </c>
       <c r="J125" s="38" t="str">
         <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5865,7 +5890,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C130" s="40"/>
       <c r="D130" s="40"/>
@@ -6016,7 +6041,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="41" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C137" s="42"/>
       <c r="D137" s="42"/>
@@ -6038,7 +6063,7 @@
       </c>
       <c r="I137" s="44" t="n">
         <f aca="false">$I$118+SUM($H$120:$H$136)</f>
-        <v>2106.98</v>
+        <v>1316.98</v>
       </c>
       <c r="J137" s="45" t="str">
         <f aca="false">IF($I$137&lt;0,"SHORTFALL",IF($I$137&lt;$E$7,"TIGHT","OK"))</f>
@@ -6059,12 +6084,12 @@
       <c r="E139" s="30"/>
       <c r="F139" s="30"/>
       <c r="G139" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H139" s="30"/>
       <c r="I139" s="32" t="n">
         <f aca="false">$I$137</f>
-        <v>2106.98</v>
+        <v>1316.98</v>
       </c>
       <c r="J139" s="30"/>
       <c r="K139" s="26" t="str">
@@ -6074,31 +6099,31 @@
     </row>
     <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C140" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D140" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E140" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F140" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G140" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H140" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I140" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J140" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6129,7 +6154,7 @@
       </c>
       <c r="I141" s="37" t="n">
         <f aca="false">IF($B141="","",$I$139+SUM($H$141:$H141))</f>
-        <v>2896.98</v>
+        <v>2106.98</v>
       </c>
       <c r="J141" s="38" t="str">
         <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6164,7 +6189,7 @@
       </c>
       <c r="I142" s="37" t="n">
         <f aca="false">IF($B142="","",$I$139+SUM($H$141:$H142))</f>
-        <v>2879.99</v>
+        <v>2089.99</v>
       </c>
       <c r="J142" s="38" t="str">
         <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6199,7 +6224,7 @@
       </c>
       <c r="I143" s="37" t="n">
         <f aca="false">IF($B143="","",$I$139+SUM($H$141:$H143))</f>
-        <v>2969.99</v>
+        <v>2179.99</v>
       </c>
       <c r="J143" s="38" t="str">
         <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6453,7 +6478,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C151" s="40"/>
       <c r="D151" s="40"/>
@@ -6604,7 +6629,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="41" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C158" s="42"/>
       <c r="D158" s="42"/>
@@ -6626,7 +6651,7 @@
       </c>
       <c r="I158" s="44" t="n">
         <f aca="false">$I$139+SUM($H$141:$H$157)</f>
-        <v>2969.99</v>
+        <v>2179.99</v>
       </c>
       <c r="J158" s="45" t="str">
         <f aca="false">IF($I$158&lt;0,"SHORTFALL",IF($I$158&lt;$E$7,"TIGHT","OK"))</f>
@@ -6647,12 +6672,12 @@
       <c r="E160" s="30"/>
       <c r="F160" s="30"/>
       <c r="G160" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H160" s="30"/>
       <c r="I160" s="32" t="n">
         <f aca="false">$I$158</f>
-        <v>2969.99</v>
+        <v>2179.99</v>
       </c>
       <c r="J160" s="30"/>
       <c r="K160" s="26" t="str">
@@ -6662,31 +6687,31 @@
     </row>
     <row r="161" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E161" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F161" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G161" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H161" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I161" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J161" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6717,7 +6742,7 @@
       </c>
       <c r="I162" s="37" t="n">
         <f aca="false">IF($B162="","",$I$160+SUM($H$162:$H162))</f>
-        <v>3759.99</v>
+        <v>2969.99</v>
       </c>
       <c r="J162" s="38" t="str">
         <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6752,7 +6777,7 @@
       </c>
       <c r="I163" s="37" t="n">
         <f aca="false">IF($B163="","",$I$160+SUM($H$162:$H163))</f>
-        <v>3746.29</v>
+        <v>2956.29</v>
       </c>
       <c r="J163" s="38" t="str">
         <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6787,7 +6812,7 @@
       </c>
       <c r="I164" s="37" t="n">
         <f aca="false">IF($B164="","",$I$160+SUM($H$162:$H164))</f>
-        <v>3702.42</v>
+        <v>2912.42</v>
       </c>
       <c r="J164" s="38" t="str">
         <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6822,7 +6847,7 @@
       </c>
       <c r="I165" s="37" t="n">
         <f aca="false">IF($B165="","",$I$160+SUM($H$162:$H165))</f>
-        <v>3792.42</v>
+        <v>3002.42</v>
       </c>
       <c r="J165" s="38" t="str">
         <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6857,7 +6882,7 @@
       </c>
       <c r="I166" s="37" t="n">
         <f aca="false">IF($B166="","",$I$160+SUM($H$162:$H166))</f>
-        <v>3442.42</v>
+        <v>2652.42</v>
       </c>
       <c r="J166" s="38" t="str">
         <f aca="true">IF($B166="","",IF($F166&lt;&gt;"","PAID",IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6892,7 +6917,7 @@
       </c>
       <c r="I167" s="37" t="n">
         <f aca="false">IF($B167="","",$I$160+SUM($H$162:$H167))</f>
-        <v>3292.42</v>
+        <v>2502.42</v>
       </c>
       <c r="J167" s="38" t="str">
         <f aca="true">IF($B167="","",IF($F167&lt;&gt;"","PAID",IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6927,7 +6952,7 @@
       </c>
       <c r="I168" s="37" t="n">
         <f aca="false">IF($B168="","",$I$160+SUM($H$162:$H168))</f>
-        <v>3149.05</v>
+        <v>2359.05</v>
       </c>
       <c r="J168" s="38" t="str">
         <f aca="true">IF($B168="","",IF($F168&lt;&gt;"","PAID",IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7041,7 +7066,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C172" s="40"/>
       <c r="D172" s="40"/>
@@ -7192,7 +7217,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="41" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C179" s="42"/>
       <c r="D179" s="42"/>
@@ -7214,7 +7239,7 @@
       </c>
       <c r="I179" s="44" t="n">
         <f aca="false">$I$160+SUM($H$162:$H$178)</f>
-        <v>3149.05</v>
+        <v>2359.05</v>
       </c>
       <c r="J179" s="45" t="str">
         <f aca="false">IF($I$179&lt;0,"SHORTFALL",IF($I$179&lt;$E$7,"TIGHT","OK"))</f>
@@ -7235,12 +7260,12 @@
       <c r="E181" s="30"/>
       <c r="F181" s="30"/>
       <c r="G181" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H181" s="30"/>
       <c r="I181" s="32" t="n">
         <f aca="false">$I$179</f>
-        <v>3149.05</v>
+        <v>2359.05</v>
       </c>
       <c r="J181" s="30"/>
       <c r="K181" s="26" t="str">
@@ -7250,31 +7275,31 @@
     </row>
     <row r="182" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C182" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D182" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E182" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F182" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G182" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H182" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I182" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J182" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7305,7 +7330,7 @@
       </c>
       <c r="I183" s="37" t="n">
         <f aca="false">IF($B183="","",$I$181+SUM($H$183:$H183))</f>
-        <v>3939.05</v>
+        <v>3149.05</v>
       </c>
       <c r="J183" s="38" t="str">
         <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7340,7 +7365,7 @@
       </c>
       <c r="I184" s="37" t="n">
         <f aca="false">IF($B184="","",$I$181+SUM($H$183:$H184))</f>
-        <v>3917.95</v>
+        <v>3127.95</v>
       </c>
       <c r="J184" s="38" t="str">
         <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7375,7 +7400,7 @@
       </c>
       <c r="I185" s="37" t="n">
         <f aca="false">IF($B185="","",$I$181+SUM($H$183:$H185))</f>
-        <v>3897.95</v>
+        <v>3107.95</v>
       </c>
       <c r="J185" s="38" t="str">
         <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7410,7 +7435,7 @@
       </c>
       <c r="I186" s="37" t="n">
         <f aca="false">IF($B186="","",$I$181+SUM($H$183:$H186))</f>
-        <v>3887.95</v>
+        <v>3097.95</v>
       </c>
       <c r="J186" s="38" t="str">
         <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7445,7 +7470,7 @@
       </c>
       <c r="I187" s="37" t="n">
         <f aca="false">IF($B187="","",$I$181+SUM($H$183:$H187))</f>
-        <v>3977.95</v>
+        <v>3187.95</v>
       </c>
       <c r="J187" s="38" t="str">
         <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7480,7 +7505,7 @@
       </c>
       <c r="I188" s="37" t="n">
         <f aca="false">IF($B188="","",$I$181+SUM($H$183:$H188))</f>
-        <v>3972.96</v>
+        <v>3182.96</v>
       </c>
       <c r="J188" s="38" t="str">
         <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7515,7 +7540,7 @@
       </c>
       <c r="I189" s="37" t="n">
         <f aca="false">IF($B189="","",$I$181+SUM($H$183:$H189))</f>
-        <v>3472.96</v>
+        <v>2682.96</v>
       </c>
       <c r="J189" s="38" t="str">
         <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7629,7 +7654,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B193" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C193" s="40"/>
       <c r="D193" s="40"/>
@@ -7780,7 +7805,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B200" s="41" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C200" s="42"/>
       <c r="D200" s="42"/>
@@ -7802,7 +7827,7 @@
       </c>
       <c r="I200" s="44" t="n">
         <f aca="false">$I$181+SUM($H$183:$H$199)</f>
-        <v>3472.96</v>
+        <v>2682.96</v>
       </c>
       <c r="J200" s="45" t="str">
         <f aca="false">IF($I$200&lt;0,"SHORTFALL",IF($I$200&lt;$E$7,"TIGHT","OK"))</f>
@@ -7823,12 +7848,12 @@
       <c r="E202" s="30"/>
       <c r="F202" s="30"/>
       <c r="G202" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H202" s="30"/>
       <c r="I202" s="32" t="n">
         <f aca="false">$I$200</f>
-        <v>3472.96</v>
+        <v>2682.96</v>
       </c>
       <c r="J202" s="30"/>
       <c r="K202" s="26" t="str">
@@ -7838,31 +7863,31 @@
     </row>
     <row r="203" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C203" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D203" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E203" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F203" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G203" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H203" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I203" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J203" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7893,7 +7918,7 @@
       </c>
       <c r="I204" s="37" t="n">
         <f aca="false">IF($B204="","",$I$202+SUM($H$204:$H204))</f>
-        <v>4262.96</v>
+        <v>3472.96</v>
       </c>
       <c r="J204" s="38" t="str">
         <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7928,7 +7953,7 @@
       </c>
       <c r="I205" s="37" t="n">
         <f aca="false">IF($B205="","",$I$202+SUM($H$204:$H205))</f>
-        <v>4099.46</v>
+        <v>3309.46</v>
       </c>
       <c r="J205" s="38" t="str">
         <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7963,7 +7988,7 @@
       </c>
       <c r="I206" s="37" t="n">
         <f aca="false">IF($B206="","",$I$202+SUM($H$204:$H206))</f>
-        <v>4096.47</v>
+        <v>3306.47</v>
       </c>
       <c r="J206" s="38" t="str">
         <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7998,7 +8023,7 @@
       </c>
       <c r="I207" s="37" t="n">
         <f aca="false">IF($B207="","",$I$202+SUM($H$204:$H207))</f>
-        <v>4186.47</v>
+        <v>3396.47</v>
       </c>
       <c r="J207" s="38" t="str">
         <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8033,7 +8058,7 @@
       </c>
       <c r="I208" s="37" t="n">
         <f aca="false">IF($B208="","",$I$202+SUM($H$204:$H208))</f>
-        <v>3836.47</v>
+        <v>3046.47</v>
       </c>
       <c r="J208" s="38" t="str">
         <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8217,7 +8242,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C214" s="40"/>
       <c r="D214" s="40"/>
@@ -8368,7 +8393,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B221" s="41" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C221" s="42"/>
       <c r="D221" s="42"/>
@@ -8390,7 +8415,7 @@
       </c>
       <c r="I221" s="44" t="n">
         <f aca="false">$I$202+SUM($H$204:$H$220)</f>
-        <v>3836.47</v>
+        <v>3046.47</v>
       </c>
       <c r="J221" s="45" t="str">
         <f aca="false">IF($I$221&lt;0,"SHORTFALL",IF($I$221&lt;$E$7,"TIGHT","OK"))</f>
@@ -8411,12 +8436,12 @@
       <c r="E223" s="30"/>
       <c r="F223" s="30"/>
       <c r="G223" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H223" s="30"/>
       <c r="I223" s="32" t="n">
         <f aca="false">$I$221</f>
-        <v>3836.47</v>
+        <v>3046.47</v>
       </c>
       <c r="J223" s="30"/>
       <c r="K223" s="26" t="str">
@@ -8426,31 +8451,31 @@
     </row>
     <row r="224" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B224" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C224" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D224" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E224" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F224" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G224" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H224" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I224" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J224" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8481,7 +8506,7 @@
       </c>
       <c r="I225" s="37" t="n">
         <f aca="false">IF($B225="","",$I$223+SUM($H$225:$H225))</f>
-        <v>4626.47</v>
+        <v>3836.47</v>
       </c>
       <c r="J225" s="38" t="str">
         <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8516,7 +8541,7 @@
       </c>
       <c r="I226" s="37" t="n">
         <f aca="false">IF($B226="","",$I$223+SUM($H$225:$H226))</f>
-        <v>4455.37</v>
+        <v>3665.37</v>
       </c>
       <c r="J226" s="38" t="str">
         <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8551,7 +8576,7 @@
       </c>
       <c r="I227" s="37" t="n">
         <f aca="false">IF($B227="","",$I$223+SUM($H$225:$H227))</f>
-        <v>4410.37</v>
+        <v>3620.37</v>
       </c>
       <c r="J227" s="38" t="str">
         <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8586,7 +8611,7 @@
       </c>
       <c r="I228" s="37" t="n">
         <f aca="false">IF($B228="","",$I$223+SUM($H$225:$H228))</f>
-        <v>4393.38</v>
+        <v>3603.38</v>
       </c>
       <c r="J228" s="38" t="str">
         <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8621,7 +8646,7 @@
       </c>
       <c r="I229" s="37" t="n">
         <f aca="false">IF($B229="","",$I$223+SUM($H$225:$H229))</f>
-        <v>4483.38</v>
+        <v>3693.38</v>
       </c>
       <c r="J229" s="38" t="str">
         <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8805,7 +8830,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C235" s="40"/>
       <c r="D235" s="40"/>
@@ -8956,7 +8981,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="41" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C242" s="42"/>
       <c r="D242" s="42"/>
@@ -8978,7 +9003,7 @@
       </c>
       <c r="I242" s="44" t="n">
         <f aca="false">$I$223+SUM($H$225:$H$241)</f>
-        <v>4483.38</v>
+        <v>3693.38</v>
       </c>
       <c r="J242" s="45" t="str">
         <f aca="false">IF($I$242&lt;0,"SHORTFALL",IF($I$242&lt;$E$7,"TIGHT","OK"))</f>
@@ -8999,12 +9024,12 @@
       <c r="E244" s="30"/>
       <c r="F244" s="30"/>
       <c r="G244" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H244" s="30"/>
       <c r="I244" s="32" t="n">
         <f aca="false">$I$242</f>
-        <v>4483.38</v>
+        <v>3693.38</v>
       </c>
       <c r="J244" s="30"/>
       <c r="K244" s="26" t="str">
@@ -9014,31 +9039,31 @@
     </row>
     <row r="245" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B245" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C245" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D245" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E245" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F245" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G245" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H245" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I245" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J245" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9069,7 +9094,7 @@
       </c>
       <c r="I246" s="37" t="n">
         <f aca="false">IF($B246="","",$I$244+SUM($H$246:$H246))</f>
-        <v>5273.38</v>
+        <v>4483.38</v>
       </c>
       <c r="J246" s="38" t="str">
         <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9104,7 +9129,7 @@
       </c>
       <c r="I247" s="37" t="n">
         <f aca="false">IF($B247="","",$I$244+SUM($H$246:$H247))</f>
-        <v>5259.68</v>
+        <v>4469.68</v>
       </c>
       <c r="J247" s="38" t="str">
         <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9139,7 +9164,7 @@
       </c>
       <c r="I248" s="37" t="n">
         <f aca="false">IF($B248="","",$I$244+SUM($H$246:$H248))</f>
-        <v>5215.81</v>
+        <v>4425.81</v>
       </c>
       <c r="J248" s="38" t="str">
         <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9174,7 +9199,7 @@
       </c>
       <c r="I249" s="37" t="n">
         <f aca="false">IF($B249="","",$I$244+SUM($H$246:$H249))</f>
-        <v>5305.81</v>
+        <v>4515.81</v>
       </c>
       <c r="J249" s="38" t="str">
         <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9393,7 +9418,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B256" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C256" s="40"/>
       <c r="D256" s="40"/>
@@ -9544,7 +9569,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B263" s="41" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C263" s="42"/>
       <c r="D263" s="42"/>
@@ -9566,7 +9591,7 @@
       </c>
       <c r="I263" s="44" t="n">
         <f aca="false">$I$244+SUM($H$246:$H$262)</f>
-        <v>5305.81</v>
+        <v>4515.81</v>
       </c>
       <c r="J263" s="45" t="str">
         <f aca="false">IF($I$263&lt;0,"SHORTFALL",IF($I$263&lt;$E$7,"TIGHT","OK"))</f>
@@ -9587,12 +9612,12 @@
       <c r="E265" s="30"/>
       <c r="F265" s="30"/>
       <c r="G265" s="31" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="H265" s="30"/>
       <c r="I265" s="32" t="n">
         <f aca="false">$I$263</f>
-        <v>5305.81</v>
+        <v>4515.81</v>
       </c>
       <c r="J265" s="30"/>
       <c r="K265" s="26" t="str">
@@ -9602,31 +9627,31 @@
     </row>
     <row r="266" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="33" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C266" s="33" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D266" s="33" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E266" s="33" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F266" s="33" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G266" s="33" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="H266" s="33" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="I266" s="33" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J266" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9657,7 +9682,7 @@
       </c>
       <c r="I267" s="37" t="n">
         <f aca="false">IF($B267="","",$I$265+SUM($H$267:$H267))</f>
-        <v>6095.81</v>
+        <v>5305.81</v>
       </c>
       <c r="J267" s="38" t="str">
         <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9692,7 +9717,7 @@
       </c>
       <c r="I268" s="37" t="n">
         <f aca="false">IF($B268="","",$I$265+SUM($H$267:$H268))</f>
-        <v>5745.81</v>
+        <v>4955.81</v>
       </c>
       <c r="J268" s="38" t="str">
         <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9727,7 +9752,7 @@
       </c>
       <c r="I269" s="37" t="n">
         <f aca="false">IF($B269="","",$I$265+SUM($H$267:$H269))</f>
-        <v>5595.81</v>
+        <v>4805.81</v>
       </c>
       <c r="J269" s="38" t="str">
         <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9762,7 +9787,7 @@
       </c>
       <c r="I270" s="37" t="n">
         <f aca="false">IF($B270="","",$I$265+SUM($H$267:$H270))</f>
-        <v>5452.44</v>
+        <v>4662.44</v>
       </c>
       <c r="J270" s="38" t="str">
         <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9797,7 +9822,7 @@
       </c>
       <c r="I271" s="37" t="n">
         <f aca="false">IF($B271="","",$I$265+SUM($H$267:$H271))</f>
-        <v>5542.44</v>
+        <v>4752.44</v>
       </c>
       <c r="J271" s="38" t="str">
         <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9832,7 +9857,7 @@
       </c>
       <c r="I272" s="37" t="n">
         <f aca="false">IF($B272="","",$I$265+SUM($H$267:$H272))</f>
-        <v>5521.34</v>
+        <v>4731.34</v>
       </c>
       <c r="J272" s="38" t="str">
         <f aca="true">IF($B272="","",IF($F272&lt;&gt;"","PAID",IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9867,7 +9892,7 @@
       </c>
       <c r="I273" s="37" t="n">
         <f aca="false">IF($B273="","",$I$265+SUM($H$267:$H273))</f>
-        <v>5501.34</v>
+        <v>4711.34</v>
       </c>
       <c r="J273" s="38" t="str">
         <f aca="true">IF($B273="","",IF($F273&lt;&gt;"","PAID",IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9902,7 +9927,7 @@
       </c>
       <c r="I274" s="37" t="n">
         <f aca="false">IF($B274="","",$I$265+SUM($H$267:$H274))</f>
-        <v>5491.34</v>
+        <v>4701.34</v>
       </c>
       <c r="J274" s="38" t="str">
         <f aca="true">IF($B274="","",IF($F274&lt;&gt;"","PAID",IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9981,7 +10006,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="39" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C277" s="40"/>
       <c r="D277" s="40"/>
@@ -10132,7 +10157,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B284" s="41" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C284" s="42"/>
       <c r="D284" s="42"/>
@@ -10154,7 +10179,7 @@
       </c>
       <c r="I284" s="44" t="n">
         <f aca="false">$I$265+SUM($H$267:$H$283)</f>
-        <v>5491.34</v>
+        <v>4701.34</v>
       </c>
       <c r="J284" s="45" t="str">
         <f aca="false">IF($I$284&lt;0,"SHORTFALL",IF($I$284&lt;$E$7,"TIGHT","OK"))</f>
@@ -10219,28 +10244,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="46" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="46"/>
       <c r="E4" s="47" t="n">
         <f aca="false">MIN($I$13:$I$25)</f>
-        <v>279.69</v>
+        <v>-510.31</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="46" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C5" s="46"/>
       <c r="D5" s="46"/>
@@ -10255,13 +10280,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="46" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C6" s="46"/>
       <c r="D6" s="46"/>
       <c r="E6" s="48" t="str">
         <f aca="false">IF(MIN($K$13:$K$25)=999,"None — you stay above zero all 13 weeks","Week "&amp;MIN($K$13:$K$25)&amp;"  ("&amp;TEXT(INDEX($C$13:$C$25,MATCH(MIN($K$13:$K$25),$B$13:$B$25,0)),"mmm d, yyyy")&amp;")")</f>
-        <v>None — you stay above zero all 13 weeks</v>
+        <v>Week 1  (Aug 7, 2026)</v>
       </c>
       <c r="F6" s="48"/>
       <c r="G6" s="48"/>
@@ -10270,18 +10295,18 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="46" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C7" s="46"/>
       <c r="D7" s="46"/>
       <c r="E7" s="49" t="n">
         <f aca="false">SUM($E$13:$E$25)</f>
-        <v>11440</v>
+        <v>10650</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="46" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C8" s="46"/>
       <c r="D8" s="46"/>
@@ -10292,56 +10317,56 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="46" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C9" s="46"/>
       <c r="D9" s="46"/>
       <c r="E9" s="47" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5420.17</v>
+        <v>4630.17</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="46" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C10" s="46"/>
       <c r="D10" s="46"/>
       <c r="E10" s="47" t="n">
         <f aca="false">$I$25</f>
-        <v>5491.34</v>
+        <v>4701.34</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10358,7 +10383,7 @@
       </c>
       <c r="E13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Income",'Cash Flow'!$G$15:$G$24)</f>
-        <v>880</v>
+        <v>90</v>
       </c>
       <c r="F13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Expense",'Cash Flow'!$G$15:$G$24)</f>
@@ -10370,19 +10395,19 @@
       </c>
       <c r="H13" s="53" t="n">
         <f aca="false">$E13-$F13-$G13</f>
-        <v>208.52</v>
+        <v>-581.48</v>
       </c>
       <c r="I13" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$32</f>
-        <v>279.69</v>
+        <v>-510.31</v>
       </c>
       <c r="J13" s="54" t="str">
         <f aca="false">IF($I13&lt;0,"SHORTFALL",IF($I13&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
-        <v>OK</v>
+        <v>SHORTFALL</v>
       </c>
       <c r="K13" s="27" t="n">
         <f aca="false">IF($I13&lt;0,$B13,999)</f>
-        <v>999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10395,7 +10420,7 @@
       </c>
       <c r="D14" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$34</f>
-        <v>279.69</v>
+        <v>-510.31</v>
       </c>
       <c r="E14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$36:$D$45,"Income",'Cash Flow'!$G$36:$G$45)</f>
@@ -10415,15 +10440,15 @@
       </c>
       <c r="I14" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$53</f>
-        <v>576.6</v>
+        <v>-213.4</v>
       </c>
       <c r="J14" s="59" t="str">
         <f aca="false">IF($I14&lt;0,"SHORTFALL",IF($I14&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
-        <v>OK</v>
+        <v>SHORTFALL</v>
       </c>
       <c r="K14" s="27" t="n">
         <f aca="false">IF($I14&lt;0,$B14,999)</f>
-        <v>999</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10436,7 +10461,7 @@
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$55</f>
-        <v>576.6</v>
+        <v>-213.4</v>
       </c>
       <c r="E15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$57:$D$66,"Income",'Cash Flow'!$G$57:$G$66)</f>
@@ -10456,7 +10481,7 @@
       </c>
       <c r="I15" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$74</f>
-        <v>1399.03</v>
+        <v>609.03</v>
       </c>
       <c r="J15" s="54" t="str">
         <f aca="false">IF($I15&lt;0,"SHORTFALL",IF($I15&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10477,7 +10502,7 @@
       </c>
       <c r="D16" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$76</f>
-        <v>1399.03</v>
+        <v>609.03</v>
       </c>
       <c r="E16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$78:$D$87,"Income",'Cash Flow'!$G$78:$G$87)</f>
@@ -10497,7 +10522,7 @@
       </c>
       <c r="I16" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$95</f>
-        <v>1635.66</v>
+        <v>845.66</v>
       </c>
       <c r="J16" s="59" t="str">
         <f aca="false">IF($I16&lt;0,"SHORTFALL",IF($I16&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10518,7 +10543,7 @@
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$97</f>
-        <v>1635.66</v>
+        <v>845.66</v>
       </c>
       <c r="E17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$99:$D$108,"Income",'Cash Flow'!$G$99:$G$108)</f>
@@ -10538,7 +10563,7 @@
       </c>
       <c r="I17" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$116</f>
-        <v>1796.07</v>
+        <v>1006.07</v>
       </c>
       <c r="J17" s="54" t="str">
         <f aca="false">IF($I17&lt;0,"SHORTFALL",IF($I17&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10559,7 +10584,7 @@
       </c>
       <c r="D18" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$118</f>
-        <v>1796.07</v>
+        <v>1006.07</v>
       </c>
       <c r="E18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$120:$D$129,"Income",'Cash Flow'!$G$120:$G$129)</f>
@@ -10579,7 +10604,7 @@
       </c>
       <c r="I18" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$137</f>
-        <v>2106.98</v>
+        <v>1316.98</v>
       </c>
       <c r="J18" s="59" t="str">
         <f aca="false">IF($I18&lt;0,"SHORTFALL",IF($I18&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10600,7 +10625,7 @@
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$139</f>
-        <v>2106.98</v>
+        <v>1316.98</v>
       </c>
       <c r="E19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$141:$D$150,"Income",'Cash Flow'!$G$141:$G$150)</f>
@@ -10620,7 +10645,7 @@
       </c>
       <c r="I19" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$158</f>
-        <v>2969.99</v>
+        <v>2179.99</v>
       </c>
       <c r="J19" s="54" t="str">
         <f aca="false">IF($I19&lt;0,"SHORTFALL",IF($I19&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10641,7 +10666,7 @@
       </c>
       <c r="D20" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$160</f>
-        <v>2969.99</v>
+        <v>2179.99</v>
       </c>
       <c r="E20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$162:$D$171,"Income",'Cash Flow'!$G$162:$G$171)</f>
@@ -10661,7 +10686,7 @@
       </c>
       <c r="I20" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$179</f>
-        <v>3149.05</v>
+        <v>2359.05</v>
       </c>
       <c r="J20" s="59" t="str">
         <f aca="false">IF($I20&lt;0,"SHORTFALL",IF($I20&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10682,7 +10707,7 @@
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$181</f>
-        <v>3149.05</v>
+        <v>2359.05</v>
       </c>
       <c r="E21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$183:$D$192,"Income",'Cash Flow'!$G$183:$G$192)</f>
@@ -10702,7 +10727,7 @@
       </c>
       <c r="I21" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$200</f>
-        <v>3472.96</v>
+        <v>2682.96</v>
       </c>
       <c r="J21" s="54" t="str">
         <f aca="false">IF($I21&lt;0,"SHORTFALL",IF($I21&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10723,7 +10748,7 @@
       </c>
       <c r="D22" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$202</f>
-        <v>3472.96</v>
+        <v>2682.96</v>
       </c>
       <c r="E22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$204:$D$213,"Income",'Cash Flow'!$G$204:$G$213)</f>
@@ -10743,7 +10768,7 @@
       </c>
       <c r="I22" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$221</f>
-        <v>3836.47</v>
+        <v>3046.47</v>
       </c>
       <c r="J22" s="59" t="str">
         <f aca="false">IF($I22&lt;0,"SHORTFALL",IF($I22&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10764,7 +10789,7 @@
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$223</f>
-        <v>3836.47</v>
+        <v>3046.47</v>
       </c>
       <c r="E23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$225:$D$234,"Income",'Cash Flow'!$G$225:$G$234)</f>
@@ -10784,7 +10809,7 @@
       </c>
       <c r="I23" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$242</f>
-        <v>4483.38</v>
+        <v>3693.38</v>
       </c>
       <c r="J23" s="54" t="str">
         <f aca="false">IF($I23&lt;0,"SHORTFALL",IF($I23&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10805,7 +10830,7 @@
       </c>
       <c r="D24" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$244</f>
-        <v>4483.38</v>
+        <v>3693.38</v>
       </c>
       <c r="E24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$246:$D$255,"Income",'Cash Flow'!$G$246:$G$255)</f>
@@ -10825,7 +10850,7 @@
       </c>
       <c r="I24" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$263</f>
-        <v>5305.81</v>
+        <v>4515.81</v>
       </c>
       <c r="J24" s="59" t="str">
         <f aca="false">IF($I24&lt;0,"SHORTFALL",IF($I24&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10846,7 +10871,7 @@
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$265</f>
-        <v>5305.81</v>
+        <v>4515.81</v>
       </c>
       <c r="E25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$267:$D$276,"Income",'Cash Flow'!$G$267:$G$276)</f>
@@ -10866,7 +10891,7 @@
       </c>
       <c r="I25" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$284</f>
-        <v>5491.34</v>
+        <v>4701.34</v>
       </c>
       <c r="J25" s="54" t="str">
         <f aca="false">IF($I25&lt;0,"SHORTFALL",IF($I25&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10879,10 +10904,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="45" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C26" s="60" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D26" s="61" t="n">
         <f aca="false">$D$13</f>
@@ -10890,7 +10915,7 @@
       </c>
       <c r="E26" s="43" t="n">
         <f aca="false">SUM($E$13:$E$25)</f>
-        <v>11440</v>
+        <v>10650</v>
       </c>
       <c r="F26" s="43" t="n">
         <f aca="false">SUM($F$13:$F$25)</f>
@@ -10902,17 +10927,17 @@
       </c>
       <c r="H26" s="61" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5420.17</v>
+        <v>4630.17</v>
       </c>
       <c r="I26" s="61" t="n">
         <f aca="false">$I$25</f>
-        <v>5491.34</v>
+        <v>4701.34</v>
       </c>
       <c r="J26" s="42"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="62" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C28" s="62"/>
       <c r="D28" s="62"/>
@@ -10982,47 +11007,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="63" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="64" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E3" s="64" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F3" s="64" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G3" s="64" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H3" s="64" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="I3" s="64" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J3" s="64" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K3" s="64" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11046,27 +11071,27 @@
       </c>
       <c r="F4" s="68" t="n">
         <f aca="false">IF($C4="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*0,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*0,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,0),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$5="One Time",IF(1=1,Recurring!$F$5,""),""))))))</f>
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="G4" s="68" t="n">
         <f aca="false">IF($F4="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F4,2)=6,$F4-1,IF(WEEKDAY($F4,2)=7,$F4-2,$F4)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F4,2)=6,$F4+2,IF(WEEKDAY($F4,2)=7,$F4+1,$F4)),$F4)))</f>
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="H4" s="69" t="n">
         <f aca="false">IF($G4="",0,IF(AND($G4&gt;='Cash Flow'!$E$6,$G4&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I4" s="69" t="n">
         <f aca="false">IF($H4=1,INT(($G4-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J4" s="66" t="str">
+        <v>1</v>
+      </c>
+      <c r="J4" s="66" t="n">
         <f aca="false">IF($H4=1,$G4*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K4" s="66" t="str">
+        <v>462460004</v>
+      </c>
+      <c r="K4" s="66" t="n">
         <f aca="false">IF($H4=1,$I4*1000+COUNTIFS($I$4:$I$483,$I4,$J$4:$J$483,"&lt;"&amp;$J4)+1,"")</f>
-        <v/>
+        <v>1004</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11090,11 +11115,11 @@
       </c>
       <c r="F5" s="68" t="n">
         <f aca="false">IF($C5="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*1,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*1,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,1),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$5="One Time",IF(2=1,Recurring!$F$5,""),""))))))</f>
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="G5" s="68" t="n">
         <f aca="false">IF($F5="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F5,2)=6,$F5-1,IF(WEEKDAY($F5,2)=7,$F5-2,$F5)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F5,2)=6,$F5+2,IF(WEEKDAY($F5,2)=7,$F5+1,$F5)),$F5)))</f>
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="H5" s="69" t="n">
         <f aca="false">IF($G5="",0,IF(AND($G5&gt;='Cash Flow'!$E$6,$G5&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11102,15 +11127,15 @@
       </c>
       <c r="I5" s="69" t="n">
         <f aca="false">IF($H5=1,INT(($G5-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J5" s="66" t="n">
         <f aca="false">IF($H5=1,$G5*10000+ROW(),"")</f>
-        <v>462460005</v>
+        <v>462530005</v>
       </c>
       <c r="K5" s="66" t="n">
         <f aca="false">IF($H5=1,$I5*1000+COUNTIFS($I$4:$I$483,$I5,$J$4:$J$483,"&lt;"&amp;$J5)+1,"")</f>
-        <v>1005</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11134,11 +11159,11 @@
       </c>
       <c r="F6" s="68" t="n">
         <f aca="false">IF($C6="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*2,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*2,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,2),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$5="One Time",IF(3=1,Recurring!$F$5,""),""))))))</f>
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="G6" s="68" t="n">
         <f aca="false">IF($F6="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F6,2)=6,$F6-1,IF(WEEKDAY($F6,2)=7,$F6-2,$F6)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F6,2)=6,$F6+2,IF(WEEKDAY($F6,2)=7,$F6+1,$F6)),$F6)))</f>
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="H6" s="69" t="n">
         <f aca="false">IF($G6="",0,IF(AND($G6&gt;='Cash Flow'!$E$6,$G6&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11146,15 +11171,15 @@
       </c>
       <c r="I6" s="69" t="n">
         <f aca="false">IF($H6=1,INT(($G6-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J6" s="66" t="n">
         <f aca="false">IF($H6=1,$G6*10000+ROW(),"")</f>
-        <v>462530006</v>
+        <v>462600006</v>
       </c>
       <c r="K6" s="66" t="n">
         <f aca="false">IF($H6=1,$I6*1000+COUNTIFS($I$4:$I$483,$I6,$J$4:$J$483,"&lt;"&amp;$J6)+1,"")</f>
-        <v>2006</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11178,11 +11203,11 @@
       </c>
       <c r="F7" s="68" t="n">
         <f aca="false">IF($C7="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*3,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*3,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,3),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$5="One Time",IF(4=1,Recurring!$F$5,""),""))))))</f>
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="G7" s="68" t="n">
         <f aca="false">IF($F7="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F7,2)=6,$F7-1,IF(WEEKDAY($F7,2)=7,$F7-2,$F7)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F7,2)=6,$F7+2,IF(WEEKDAY($F7,2)=7,$F7+1,$F7)),$F7)))</f>
-        <v>46260</v>
+        <v>46267</v>
       </c>
       <c r="H7" s="69" t="n">
         <f aca="false">IF($G7="",0,IF(AND($G7&gt;='Cash Flow'!$E$6,$G7&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11190,15 +11215,15 @@
       </c>
       <c r="I7" s="69" t="n">
         <f aca="false">IF($H7=1,INT(($G7-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" s="66" t="n">
         <f aca="false">IF($H7=1,$G7*10000+ROW(),"")</f>
-        <v>462600007</v>
+        <v>462670007</v>
       </c>
       <c r="K7" s="66" t="n">
         <f aca="false">IF($H7=1,$I7*1000+COUNTIFS($I$4:$I$483,$I7,$J$4:$J$483,"&lt;"&amp;$J7)+1,"")</f>
-        <v>3004</v>
+        <v>4005</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11222,11 +11247,11 @@
       </c>
       <c r="F8" s="68" t="n">
         <f aca="false">IF($C8="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*4,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*4,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,4),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$5="One Time",IF(5=1,Recurring!$F$5,""),""))))))</f>
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="G8" s="68" t="n">
         <f aca="false">IF($F8="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F8,2)=6,$F8-1,IF(WEEKDAY($F8,2)=7,$F8-2,$F8)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F8,2)=6,$F8+2,IF(WEEKDAY($F8,2)=7,$F8+1,$F8)),$F8)))</f>
-        <v>46267</v>
+        <v>46274</v>
       </c>
       <c r="H8" s="69" t="n">
         <f aca="false">IF($G8="",0,IF(AND($G8&gt;='Cash Flow'!$E$6,$G8&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11234,15 +11259,15 @@
       </c>
       <c r="I8" s="69" t="n">
         <f aca="false">IF($H8=1,INT(($G8-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" s="66" t="n">
         <f aca="false">IF($H8=1,$G8*10000+ROW(),"")</f>
-        <v>462670008</v>
+        <v>462740008</v>
       </c>
       <c r="K8" s="66" t="n">
         <f aca="false">IF($H8=1,$I8*1000+COUNTIFS($I$4:$I$483,$I8,$J$4:$J$483,"&lt;"&amp;$J8)+1,"")</f>
-        <v>4005</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11266,11 +11291,11 @@
       </c>
       <c r="F9" s="68" t="n">
         <f aca="false">IF($C9="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*5,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*5,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,5),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$5="One Time",IF(6=1,Recurring!$F$5,""),""))))))</f>
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="G9" s="68" t="n">
         <f aca="false">IF($F9="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F9,2)=6,$F9-1,IF(WEEKDAY($F9,2)=7,$F9-2,$F9)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F9,2)=6,$F9+2,IF(WEEKDAY($F9,2)=7,$F9+1,$F9)),$F9)))</f>
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="H9" s="69" t="n">
         <f aca="false">IF($G9="",0,IF(AND($G9&gt;='Cash Flow'!$E$6,$G9&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11278,15 +11303,15 @@
       </c>
       <c r="I9" s="69" t="n">
         <f aca="false">IF($H9=1,INT(($G9-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J9" s="66" t="n">
         <f aca="false">IF($H9=1,$G9*10000+ROW(),"")</f>
-        <v>462740009</v>
+        <v>462810009</v>
       </c>
       <c r="K9" s="66" t="n">
         <f aca="false">IF($H9=1,$I9*1000+COUNTIFS($I$4:$I$483,$I9,$J$4:$J$483,"&lt;"&amp;$J9)+1,"")</f>
-        <v>5007</v>
+        <v>6004</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11310,11 +11335,11 @@
       </c>
       <c r="F10" s="68" t="n">
         <f aca="false">IF($C10="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*6,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*6,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,6),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$5="One Time",IF(7=1,Recurring!$F$5,""),""))))))</f>
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="G10" s="68" t="n">
         <f aca="false">IF($F10="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F10,2)=6,$F10-1,IF(WEEKDAY($F10,2)=7,$F10-2,$F10)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F10,2)=6,$F10+2,IF(WEEKDAY($F10,2)=7,$F10+1,$F10)),$F10)))</f>
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="H10" s="69" t="n">
         <f aca="false">IF($G10="",0,IF(AND($G10&gt;='Cash Flow'!$E$6,$G10&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11322,15 +11347,15 @@
       </c>
       <c r="I10" s="69" t="n">
         <f aca="false">IF($H10=1,INT(($G10-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="66" t="n">
         <f aca="false">IF($H10=1,$G10*10000+ROW(),"")</f>
-        <v>462810010</v>
+        <v>462880010</v>
       </c>
       <c r="K10" s="66" t="n">
         <f aca="false">IF($H10=1,$I10*1000+COUNTIFS($I$4:$I$483,$I10,$J$4:$J$483,"&lt;"&amp;$J10)+1,"")</f>
-        <v>6004</v>
+        <v>7003</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11354,11 +11379,11 @@
       </c>
       <c r="F11" s="68" t="n">
         <f aca="false">IF($C11="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*7,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*7,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,7),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$5="One Time",IF(8=1,Recurring!$F$5,""),""))))))</f>
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="G11" s="68" t="n">
         <f aca="false">IF($F11="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F11,2)=6,$F11-1,IF(WEEKDAY($F11,2)=7,$F11-2,$F11)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F11,2)=6,$F11+2,IF(WEEKDAY($F11,2)=7,$F11+1,$F11)),$F11)))</f>
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="H11" s="69" t="n">
         <f aca="false">IF($G11="",0,IF(AND($G11&gt;='Cash Flow'!$E$6,$G11&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11366,15 +11391,15 @@
       </c>
       <c r="I11" s="69" t="n">
         <f aca="false">IF($H11=1,INT(($G11-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="66" t="n">
         <f aca="false">IF($H11=1,$G11*10000+ROW(),"")</f>
-        <v>462880011</v>
+        <v>462950011</v>
       </c>
       <c r="K11" s="66" t="n">
         <f aca="false">IF($H11=1,$I11*1000+COUNTIFS($I$4:$I$483,$I11,$J$4:$J$483,"&lt;"&amp;$J11)+1,"")</f>
-        <v>7003</v>
+        <v>8004</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11398,11 +11423,11 @@
       </c>
       <c r="F12" s="68" t="n">
         <f aca="false">IF($C12="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*8,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*8,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,8),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$5="One Time",IF(9=1,Recurring!$F$5,""),""))))))</f>
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="G12" s="68" t="n">
         <f aca="false">IF($F12="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F12,2)=6,$F12-1,IF(WEEKDAY($F12,2)=7,$F12-2,$F12)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F12,2)=6,$F12+2,IF(WEEKDAY($F12,2)=7,$F12+1,$F12)),$F12)))</f>
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="H12" s="69" t="n">
         <f aca="false">IF($G12="",0,IF(AND($G12&gt;='Cash Flow'!$E$6,$G12&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11410,15 +11435,15 @@
       </c>
       <c r="I12" s="69" t="n">
         <f aca="false">IF($H12=1,INT(($G12-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J12" s="66" t="n">
         <f aca="false">IF($H12=1,$G12*10000+ROW(),"")</f>
-        <v>462950012</v>
+        <v>463020012</v>
       </c>
       <c r="K12" s="66" t="n">
         <f aca="false">IF($H12=1,$I12*1000+COUNTIFS($I$4:$I$483,$I12,$J$4:$J$483,"&lt;"&amp;$J12)+1,"")</f>
-        <v>8004</v>
+        <v>9005</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11442,11 +11467,11 @@
       </c>
       <c r="F13" s="68" t="n">
         <f aca="false">IF($C13="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*9,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*9,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,9),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$5="One Time",IF(10=1,Recurring!$F$5,""),""))))))</f>
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="G13" s="68" t="n">
         <f aca="false">IF($F13="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F13,2)=6,$F13-1,IF(WEEKDAY($F13,2)=7,$F13-2,$F13)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F13,2)=6,$F13+2,IF(WEEKDAY($F13,2)=7,$F13+1,$F13)),$F13)))</f>
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="H13" s="69" t="n">
         <f aca="false">IF($G13="",0,IF(AND($G13&gt;='Cash Flow'!$E$6,$G13&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11454,15 +11479,15 @@
       </c>
       <c r="I13" s="69" t="n">
         <f aca="false">IF($H13=1,INT(($G13-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" s="66" t="n">
         <f aca="false">IF($H13=1,$G13*10000+ROW(),"")</f>
-        <v>463020013</v>
+        <v>463090013</v>
       </c>
       <c r="K13" s="66" t="n">
         <f aca="false">IF($H13=1,$I13*1000+COUNTIFS($I$4:$I$483,$I13,$J$4:$J$483,"&lt;"&amp;$J13)+1,"")</f>
-        <v>9005</v>
+        <v>10004</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11486,11 +11511,11 @@
       </c>
       <c r="F14" s="68" t="n">
         <f aca="false">IF($C14="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*10,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*10,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,10),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$5="One Time",IF(11=1,Recurring!$F$5,""),""))))))</f>
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="G14" s="68" t="n">
         <f aca="false">IF($F14="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F14,2)=6,$F14-1,IF(WEEKDAY($F14,2)=7,$F14-2,$F14)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F14,2)=6,$F14+2,IF(WEEKDAY($F14,2)=7,$F14+1,$F14)),$F14)))</f>
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="H14" s="69" t="n">
         <f aca="false">IF($G14="",0,IF(AND($G14&gt;='Cash Flow'!$E$6,$G14&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11498,15 +11523,15 @@
       </c>
       <c r="I14" s="69" t="n">
         <f aca="false">IF($H14=1,INT(($G14-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J14" s="66" t="n">
         <f aca="false">IF($H14=1,$G14*10000+ROW(),"")</f>
-        <v>463090014</v>
+        <v>463160014</v>
       </c>
       <c r="K14" s="66" t="n">
         <f aca="false">IF($H14=1,$I14*1000+COUNTIFS($I$4:$I$483,$I14,$J$4:$J$483,"&lt;"&amp;$J14)+1,"")</f>
-        <v>10004</v>
+        <v>11005</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11530,11 +11555,11 @@
       </c>
       <c r="F15" s="68" t="n">
         <f aca="false">IF($C15="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*11,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*11,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,11),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$5="One Time",IF(12=1,Recurring!$F$5,""),""))))))</f>
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="G15" s="68" t="n">
         <f aca="false">IF($F15="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F15,2)=6,$F15-1,IF(WEEKDAY($F15,2)=7,$F15-2,$F15)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F15,2)=6,$F15+2,IF(WEEKDAY($F15,2)=7,$F15+1,$F15)),$F15)))</f>
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="H15" s="69" t="n">
         <f aca="false">IF($G15="",0,IF(AND($G15&gt;='Cash Flow'!$E$6,$G15&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11542,15 +11567,15 @@
       </c>
       <c r="I15" s="69" t="n">
         <f aca="false">IF($H15=1,INT(($G15-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="66" t="n">
         <f aca="false">IF($H15=1,$G15*10000+ROW(),"")</f>
-        <v>463160015</v>
+        <v>463230015</v>
       </c>
       <c r="K15" s="66" t="n">
         <f aca="false">IF($H15=1,$I15*1000+COUNTIFS($I$4:$I$483,$I15,$J$4:$J$483,"&lt;"&amp;$J15)+1,"")</f>
-        <v>11005</v>
+        <v>12004</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11574,11 +11599,11 @@
       </c>
       <c r="F16" s="68" t="n">
         <f aca="false">IF($C16="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*12,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*12,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,12),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$5="One Time",IF(13=1,Recurring!$F$5,""),""))))))</f>
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="G16" s="68" t="n">
         <f aca="false">IF($F16="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F16,2)=6,$F16-1,IF(WEEKDAY($F16,2)=7,$F16-2,$F16)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F16,2)=6,$F16+2,IF(WEEKDAY($F16,2)=7,$F16+1,$F16)),$F16)))</f>
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="H16" s="69" t="n">
         <f aca="false">IF($G16="",0,IF(AND($G16&gt;='Cash Flow'!$E$6,$G16&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11586,15 +11611,15 @@
       </c>
       <c r="I16" s="69" t="n">
         <f aca="false">IF($H16=1,INT(($G16-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="66" t="n">
         <f aca="false">IF($H16=1,$G16*10000+ROW(),"")</f>
-        <v>463230016</v>
+        <v>463300016</v>
       </c>
       <c r="K16" s="66" t="n">
         <f aca="false">IF($H16=1,$I16*1000+COUNTIFS($I$4:$I$483,$I16,$J$4:$J$483,"&lt;"&amp;$J16)+1,"")</f>
-        <v>12004</v>
+        <v>13005</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11618,27 +11643,27 @@
       </c>
       <c r="F17" s="68" t="n">
         <f aca="false">IF($C17="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*13,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*13,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,13),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$5="One Time",IF(14=1,Recurring!$F$5,""),""))))))</f>
-        <v>46330</v>
+        <v>46337</v>
       </c>
       <c r="G17" s="68" t="n">
         <f aca="false">IF($F17="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F17,2)=6,$F17-1,IF(WEEKDAY($F17,2)=7,$F17-2,$F17)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F17,2)=6,$F17+2,IF(WEEKDAY($F17,2)=7,$F17+1,$F17)),$F17)))</f>
-        <v>46330</v>
+        <v>46337</v>
       </c>
       <c r="H17" s="69" t="n">
         <f aca="false">IF($G17="",0,IF(AND($G17&gt;='Cash Flow'!$E$6,$G17&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I17" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="69" t="str">
         <f aca="false">IF($H17=1,INT(($G17-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J17" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J17" s="66" t="str">
         <f aca="false">IF($H17=1,$G17*10000+ROW(),"")</f>
-        <v>463300017</v>
-      </c>
-      <c r="K17" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K17" s="66" t="str">
         <f aca="false">IF($H17=1,$I17*1000+COUNTIFS($I$4:$I$483,$I17,$J$4:$J$483,"&lt;"&amp;$J17)+1,"")</f>
-        <v>13005</v>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11662,11 +11687,11 @@
       </c>
       <c r="F18" s="68" t="n">
         <f aca="false">IF($C18="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*14,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*14,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,14),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$5="One Time",IF(15=1,Recurring!$F$5,""),""))))))</f>
-        <v>46337</v>
+        <v>46344</v>
       </c>
       <c r="G18" s="68" t="n">
         <f aca="false">IF($F18="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F18,2)=6,$F18-1,IF(WEEKDAY($F18,2)=7,$F18-2,$F18)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F18,2)=6,$F18+2,IF(WEEKDAY($F18,2)=7,$F18+1,$F18)),$F18)))</f>
-        <v>46337</v>
+        <v>46344</v>
       </c>
       <c r="H18" s="69" t="n">
         <f aca="false">IF($G18="",0,IF(AND($G18&gt;='Cash Flow'!$E$6,$G18&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11706,11 +11731,11 @@
       </c>
       <c r="F19" s="68" t="n">
         <f aca="false">IF($C19="","",IF(Recurring!$E$5="Weekly",Recurring!$F$5+7*15,IF(Recurring!$E$5="Every 2 Weeks",Recurring!$F$5+14*15,IF(Recurring!$E$5="Monthly",EDATE(Recurring!$F$5,15),IF(Recurring!$E$5="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$5,INT((IF(DAY(Recurring!$F$5)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$5="One Time",IF(16=1,Recurring!$F$5,""),""))))))</f>
-        <v>46344</v>
+        <v>46351</v>
       </c>
       <c r="G19" s="68" t="n">
         <f aca="false">IF($F19="","",IF(Recurring!$G$5="Move Before",IF(WEEKDAY($F19,2)=6,$F19-1,IF(WEEKDAY($F19,2)=7,$F19-2,$F19)),IF(Recurring!$G$5="Move After",IF(WEEKDAY($F19,2)=6,$F19+2,IF(WEEKDAY($F19,2)=7,$F19+1,$F19)),$F19)))</f>
-        <v>46344</v>
+        <v>46351</v>
       </c>
       <c r="H19" s="69" t="n">
         <f aca="false">IF($G19="",0,IF(AND($G19&gt;='Cash Flow'!$E$6,$G19&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11750,11 +11775,11 @@
       </c>
       <c r="F20" s="68" t="n">
         <f aca="false">IF($C20="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*0,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*0,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,0),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$6="One Time",IF(1=1,Recurring!$F$6,""),""))))))</f>
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="G20" s="68" t="n">
         <f aca="false">IF($F20="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F20,2)=6,$F20-1,IF(WEEKDAY($F20,2)=7,$F20-2,$F20)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F20,2)=6,$F20+2,IF(WEEKDAY($F20,2)=7,$F20+1,$F20)),$F20)))</f>
-        <v>46241</v>
+        <v>46248</v>
       </c>
       <c r="H20" s="69" t="n">
         <f aca="false">IF($G20="",0,IF(AND($G20&gt;='Cash Flow'!$E$6,$G20&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11762,15 +11787,15 @@
       </c>
       <c r="I20" s="69" t="n">
         <f aca="false">IF($H20=1,INT(($G20-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="66" t="n">
         <f aca="false">IF($H20=1,$G20*10000+ROW(),"")</f>
-        <v>462410020</v>
+        <v>462480020</v>
       </c>
       <c r="K20" s="66" t="n">
         <f aca="false">IF($H20=1,$I20*1000+COUNTIFS($I$4:$I$483,$I20,$J$4:$J$483,"&lt;"&amp;$J20)+1,"")</f>
-        <v>1001</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11794,11 +11819,11 @@
       </c>
       <c r="F21" s="68" t="n">
         <f aca="false">IF($C21="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*1,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*1,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,1),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$6="One Time",IF(2=1,Recurring!$F$6,""),""))))))</f>
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="G21" s="68" t="n">
         <f aca="false">IF($F21="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F21,2)=6,$F21-1,IF(WEEKDAY($F21,2)=7,$F21-2,$F21)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F21,2)=6,$F21+2,IF(WEEKDAY($F21,2)=7,$F21+1,$F21)),$F21)))</f>
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="H21" s="69" t="n">
         <f aca="false">IF($G21="",0,IF(AND($G21&gt;='Cash Flow'!$E$6,$G21&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11806,15 +11831,15 @@
       </c>
       <c r="I21" s="69" t="n">
         <f aca="false">IF($H21=1,INT(($G21-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="66" t="n">
         <f aca="false">IF($H21=1,$G21*10000+ROW(),"")</f>
-        <v>462480021</v>
+        <v>462550021</v>
       </c>
       <c r="K21" s="66" t="n">
         <f aca="false">IF($H21=1,$I21*1000+COUNTIFS($I$4:$I$483,$I21,$J$4:$J$483,"&lt;"&amp;$J21)+1,"")</f>
-        <v>2001</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11838,11 +11863,11 @@
       </c>
       <c r="F22" s="68" t="n">
         <f aca="false">IF($C22="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*2,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*2,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,2),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$6="One Time",IF(3=1,Recurring!$F$6,""),""))))))</f>
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="G22" s="68" t="n">
         <f aca="false">IF($F22="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F22,2)=6,$F22-1,IF(WEEKDAY($F22,2)=7,$F22-2,$F22)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F22,2)=6,$F22+2,IF(WEEKDAY($F22,2)=7,$F22+1,$F22)),$F22)))</f>
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="H22" s="69" t="n">
         <f aca="false">IF($G22="",0,IF(AND($G22&gt;='Cash Flow'!$E$6,$G22&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11850,15 +11875,15 @@
       </c>
       <c r="I22" s="69" t="n">
         <f aca="false">IF($H22=1,INT(($G22-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="66" t="n">
         <f aca="false">IF($H22=1,$G22*10000+ROW(),"")</f>
-        <v>462550022</v>
+        <v>462620022</v>
       </c>
       <c r="K22" s="66" t="n">
         <f aca="false">IF($H22=1,$I22*1000+COUNTIFS($I$4:$I$483,$I22,$J$4:$J$483,"&lt;"&amp;$J22)+1,"")</f>
-        <v>3001</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11882,11 +11907,11 @@
       </c>
       <c r="F23" s="68" t="n">
         <f aca="false">IF($C23="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*3,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*3,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,3),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$6="One Time",IF(4=1,Recurring!$F$6,""),""))))))</f>
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="G23" s="68" t="n">
         <f aca="false">IF($F23="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F23,2)=6,$F23-1,IF(WEEKDAY($F23,2)=7,$F23-2,$F23)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F23,2)=6,$F23+2,IF(WEEKDAY($F23,2)=7,$F23+1,$F23)),$F23)))</f>
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="H23" s="69" t="n">
         <f aca="false">IF($G23="",0,IF(AND($G23&gt;='Cash Flow'!$E$6,$G23&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11894,15 +11919,15 @@
       </c>
       <c r="I23" s="69" t="n">
         <f aca="false">IF($H23=1,INT(($G23-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="66" t="n">
         <f aca="false">IF($H23=1,$G23*10000+ROW(),"")</f>
-        <v>462620023</v>
+        <v>462690023</v>
       </c>
       <c r="K23" s="66" t="n">
         <f aca="false">IF($H23=1,$I23*1000+COUNTIFS($I$4:$I$483,$I23,$J$4:$J$483,"&lt;"&amp;$J23)+1,"")</f>
-        <v>4001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11926,11 +11951,11 @@
       </c>
       <c r="F24" s="68" t="n">
         <f aca="false">IF($C24="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*4,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*4,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,4),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$6="One Time",IF(5=1,Recurring!$F$6,""),""))))))</f>
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="G24" s="68" t="n">
         <f aca="false">IF($F24="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F24,2)=6,$F24-1,IF(WEEKDAY($F24,2)=7,$F24-2,$F24)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F24,2)=6,$F24+2,IF(WEEKDAY($F24,2)=7,$F24+1,$F24)),$F24)))</f>
-        <v>46269</v>
+        <v>46276</v>
       </c>
       <c r="H24" s="69" t="n">
         <f aca="false">IF($G24="",0,IF(AND($G24&gt;='Cash Flow'!$E$6,$G24&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11938,15 +11963,15 @@
       </c>
       <c r="I24" s="69" t="n">
         <f aca="false">IF($H24=1,INT(($G24-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" s="66" t="n">
         <f aca="false">IF($H24=1,$G24*10000+ROW(),"")</f>
-        <v>462690024</v>
+        <v>462760024</v>
       </c>
       <c r="K24" s="66" t="n">
         <f aca="false">IF($H24=1,$I24*1000+COUNTIFS($I$4:$I$483,$I24,$J$4:$J$483,"&lt;"&amp;$J24)+1,"")</f>
-        <v>5001</v>
+        <v>6001</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11970,11 +11995,11 @@
       </c>
       <c r="F25" s="68" t="n">
         <f aca="false">IF($C25="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*5,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*5,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,5),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$6="One Time",IF(6=1,Recurring!$F$6,""),""))))))</f>
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="G25" s="68" t="n">
         <f aca="false">IF($F25="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F25,2)=6,$F25-1,IF(WEEKDAY($F25,2)=7,$F25-2,$F25)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F25,2)=6,$F25+2,IF(WEEKDAY($F25,2)=7,$F25+1,$F25)),$F25)))</f>
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="H25" s="69" t="n">
         <f aca="false">IF($G25="",0,IF(AND($G25&gt;='Cash Flow'!$E$6,$G25&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -11982,15 +12007,15 @@
       </c>
       <c r="I25" s="69" t="n">
         <f aca="false">IF($H25=1,INT(($G25-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J25" s="66" t="n">
         <f aca="false">IF($H25=1,$G25*10000+ROW(),"")</f>
-        <v>462760025</v>
+        <v>462830025</v>
       </c>
       <c r="K25" s="66" t="n">
         <f aca="false">IF($H25=1,$I25*1000+COUNTIFS($I$4:$I$483,$I25,$J$4:$J$483,"&lt;"&amp;$J25)+1,"")</f>
-        <v>6001</v>
+        <v>7001</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12014,11 +12039,11 @@
       </c>
       <c r="F26" s="68" t="n">
         <f aca="false">IF($C26="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*6,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*6,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,6),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$6="One Time",IF(7=1,Recurring!$F$6,""),""))))))</f>
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="G26" s="68" t="n">
         <f aca="false">IF($F26="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F26,2)=6,$F26-1,IF(WEEKDAY($F26,2)=7,$F26-2,$F26)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F26,2)=6,$F26+2,IF(WEEKDAY($F26,2)=7,$F26+1,$F26)),$F26)))</f>
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="H26" s="69" t="n">
         <f aca="false">IF($G26="",0,IF(AND($G26&gt;='Cash Flow'!$E$6,$G26&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12026,15 +12051,15 @@
       </c>
       <c r="I26" s="69" t="n">
         <f aca="false">IF($H26=1,INT(($G26-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="66" t="n">
         <f aca="false">IF($H26=1,$G26*10000+ROW(),"")</f>
-        <v>462830026</v>
+        <v>462900026</v>
       </c>
       <c r="K26" s="66" t="n">
         <f aca="false">IF($H26=1,$I26*1000+COUNTIFS($I$4:$I$483,$I26,$J$4:$J$483,"&lt;"&amp;$J26)+1,"")</f>
-        <v>7001</v>
+        <v>8001</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12058,11 +12083,11 @@
       </c>
       <c r="F27" s="68" t="n">
         <f aca="false">IF($C27="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*7,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*7,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,7),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$6="One Time",IF(8=1,Recurring!$F$6,""),""))))))</f>
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="G27" s="68" t="n">
         <f aca="false">IF($F27="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F27,2)=6,$F27-1,IF(WEEKDAY($F27,2)=7,$F27-2,$F27)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F27,2)=6,$F27+2,IF(WEEKDAY($F27,2)=7,$F27+1,$F27)),$F27)))</f>
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="H27" s="69" t="n">
         <f aca="false">IF($G27="",0,IF(AND($G27&gt;='Cash Flow'!$E$6,$G27&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12070,15 +12095,15 @@
       </c>
       <c r="I27" s="69" t="n">
         <f aca="false">IF($H27=1,INT(($G27-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="66" t="n">
         <f aca="false">IF($H27=1,$G27*10000+ROW(),"")</f>
-        <v>462900027</v>
+        <v>462970027</v>
       </c>
       <c r="K27" s="66" t="n">
         <f aca="false">IF($H27=1,$I27*1000+COUNTIFS($I$4:$I$483,$I27,$J$4:$J$483,"&lt;"&amp;$J27)+1,"")</f>
-        <v>8001</v>
+        <v>9001</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12102,11 +12127,11 @@
       </c>
       <c r="F28" s="68" t="n">
         <f aca="false">IF($C28="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*8,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*8,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,8),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$6="One Time",IF(9=1,Recurring!$F$6,""),""))))))</f>
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="G28" s="68" t="n">
         <f aca="false">IF($F28="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F28,2)=6,$F28-1,IF(WEEKDAY($F28,2)=7,$F28-2,$F28)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F28,2)=6,$F28+2,IF(WEEKDAY($F28,2)=7,$F28+1,$F28)),$F28)))</f>
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="H28" s="69" t="n">
         <f aca="false">IF($G28="",0,IF(AND($G28&gt;='Cash Flow'!$E$6,$G28&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12114,15 +12139,15 @@
       </c>
       <c r="I28" s="69" t="n">
         <f aca="false">IF($H28=1,INT(($G28-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="66" t="n">
         <f aca="false">IF($H28=1,$G28*10000+ROW(),"")</f>
-        <v>462970028</v>
+        <v>463040028</v>
       </c>
       <c r="K28" s="66" t="n">
         <f aca="false">IF($H28=1,$I28*1000+COUNTIFS($I$4:$I$483,$I28,$J$4:$J$483,"&lt;"&amp;$J28)+1,"")</f>
-        <v>9001</v>
+        <v>10001</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12146,11 +12171,11 @@
       </c>
       <c r="F29" s="68" t="n">
         <f aca="false">IF($C29="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*9,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*9,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,9),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$6="One Time",IF(10=1,Recurring!$F$6,""),""))))))</f>
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="G29" s="68" t="n">
         <f aca="false">IF($F29="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F29,2)=6,$F29-1,IF(WEEKDAY($F29,2)=7,$F29-2,$F29)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F29,2)=6,$F29+2,IF(WEEKDAY($F29,2)=7,$F29+1,$F29)),$F29)))</f>
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="H29" s="69" t="n">
         <f aca="false">IF($G29="",0,IF(AND($G29&gt;='Cash Flow'!$E$6,$G29&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12158,15 +12183,15 @@
       </c>
       <c r="I29" s="69" t="n">
         <f aca="false">IF($H29=1,INT(($G29-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J29" s="66" t="n">
         <f aca="false">IF($H29=1,$G29*10000+ROW(),"")</f>
-        <v>463040029</v>
+        <v>463110029</v>
       </c>
       <c r="K29" s="66" t="n">
         <f aca="false">IF($H29=1,$I29*1000+COUNTIFS($I$4:$I$483,$I29,$J$4:$J$483,"&lt;"&amp;$J29)+1,"")</f>
-        <v>10001</v>
+        <v>11001</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12190,11 +12215,11 @@
       </c>
       <c r="F30" s="68" t="n">
         <f aca="false">IF($C30="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*10,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*10,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,10),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$6="One Time",IF(11=1,Recurring!$F$6,""),""))))))</f>
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="G30" s="68" t="n">
         <f aca="false">IF($F30="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F30,2)=6,$F30-1,IF(WEEKDAY($F30,2)=7,$F30-2,$F30)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F30,2)=6,$F30+2,IF(WEEKDAY($F30,2)=7,$F30+1,$F30)),$F30)))</f>
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="H30" s="69" t="n">
         <f aca="false">IF($G30="",0,IF(AND($G30&gt;='Cash Flow'!$E$6,$G30&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12202,15 +12227,15 @@
       </c>
       <c r="I30" s="69" t="n">
         <f aca="false">IF($H30=1,INT(($G30-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J30" s="66" t="n">
         <f aca="false">IF($H30=1,$G30*10000+ROW(),"")</f>
-        <v>463110030</v>
+        <v>463180030</v>
       </c>
       <c r="K30" s="66" t="n">
         <f aca="false">IF($H30=1,$I30*1000+COUNTIFS($I$4:$I$483,$I30,$J$4:$J$483,"&lt;"&amp;$J30)+1,"")</f>
-        <v>11001</v>
+        <v>12001</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12234,11 +12259,11 @@
       </c>
       <c r="F31" s="68" t="n">
         <f aca="false">IF($C31="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*11,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*11,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,11),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$6="One Time",IF(12=1,Recurring!$F$6,""),""))))))</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="G31" s="68" t="n">
         <f aca="false">IF($F31="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F31,2)=6,$F31-1,IF(WEEKDAY($F31,2)=7,$F31-2,$F31)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F31,2)=6,$F31+2,IF(WEEKDAY($F31,2)=7,$F31+1,$F31)),$F31)))</f>
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="H31" s="69" t="n">
         <f aca="false">IF($G31="",0,IF(AND($G31&gt;='Cash Flow'!$E$6,$G31&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12246,15 +12271,15 @@
       </c>
       <c r="I31" s="69" t="n">
         <f aca="false">IF($H31=1,INT(($G31-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J31" s="66" t="n">
         <f aca="false">IF($H31=1,$G31*10000+ROW(),"")</f>
-        <v>463180031</v>
+        <v>463250031</v>
       </c>
       <c r="K31" s="66" t="n">
         <f aca="false">IF($H31=1,$I31*1000+COUNTIFS($I$4:$I$483,$I31,$J$4:$J$483,"&lt;"&amp;$J31)+1,"")</f>
-        <v>12001</v>
+        <v>13001</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12278,27 +12303,27 @@
       </c>
       <c r="F32" s="68" t="n">
         <f aca="false">IF($C32="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*12,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*12,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,12),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$6="One Time",IF(13=1,Recurring!$F$6,""),""))))))</f>
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="G32" s="68" t="n">
         <f aca="false">IF($F32="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F32,2)=6,$F32-1,IF(WEEKDAY($F32,2)=7,$F32-2,$F32)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F32,2)=6,$F32+2,IF(WEEKDAY($F32,2)=7,$F32+1,$F32)),$F32)))</f>
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="H32" s="69" t="n">
         <f aca="false">IF($G32="",0,IF(AND($G32&gt;='Cash Flow'!$E$6,$G32&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I32" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="69" t="str">
         <f aca="false">IF($H32=1,INT(($G32-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J32" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J32" s="66" t="str">
         <f aca="false">IF($H32=1,$G32*10000+ROW(),"")</f>
-        <v>463250032</v>
-      </c>
-      <c r="K32" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K32" s="66" t="str">
         <f aca="false">IF($H32=1,$I32*1000+COUNTIFS($I$4:$I$483,$I32,$J$4:$J$483,"&lt;"&amp;$J32)+1,"")</f>
-        <v>13001</v>
+        <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12322,11 +12347,11 @@
       </c>
       <c r="F33" s="68" t="n">
         <f aca="false">IF($C33="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*13,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*13,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,13),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$6="One Time",IF(14=1,Recurring!$F$6,""),""))))))</f>
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="G33" s="68" t="n">
         <f aca="false">IF($F33="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F33,2)=6,$F33-1,IF(WEEKDAY($F33,2)=7,$F33-2,$F33)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F33,2)=6,$F33+2,IF(WEEKDAY($F33,2)=7,$F33+1,$F33)),$F33)))</f>
-        <v>46332</v>
+        <v>46339</v>
       </c>
       <c r="H33" s="69" t="n">
         <f aca="false">IF($G33="",0,IF(AND($G33&gt;='Cash Flow'!$E$6,$G33&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12366,11 +12391,11 @@
       </c>
       <c r="F34" s="68" t="n">
         <f aca="false">IF($C34="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*14,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*14,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,14),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$6="One Time",IF(15=1,Recurring!$F$6,""),""))))))</f>
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="G34" s="68" t="n">
         <f aca="false">IF($F34="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F34,2)=6,$F34-1,IF(WEEKDAY($F34,2)=7,$F34-2,$F34)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F34,2)=6,$F34+2,IF(WEEKDAY($F34,2)=7,$F34+1,$F34)),$F34)))</f>
-        <v>46339</v>
+        <v>46346</v>
       </c>
       <c r="H34" s="69" t="n">
         <f aca="false">IF($G34="",0,IF(AND($G34&gt;='Cash Flow'!$E$6,$G34&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12410,11 +12435,11 @@
       </c>
       <c r="F35" s="68" t="n">
         <f aca="false">IF($C35="","",IF(Recurring!$E$6="Weekly",Recurring!$F$6+7*15,IF(Recurring!$E$6="Every 2 Weeks",Recurring!$F$6+14*15,IF(Recurring!$E$6="Monthly",EDATE(Recurring!$F$6,15),IF(Recurring!$E$6="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$6,INT((IF(DAY(Recurring!$F$6)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$6="One Time",IF(16=1,Recurring!$F$6,""),""))))))</f>
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="G35" s="68" t="n">
         <f aca="false">IF($F35="","",IF(Recurring!$G$6="Move Before",IF(WEEKDAY($F35,2)=6,$F35-1,IF(WEEKDAY($F35,2)=7,$F35-2,$F35)),IF(Recurring!$G$6="Move After",IF(WEEKDAY($F35,2)=6,$F35+2,IF(WEEKDAY($F35,2)=7,$F35+1,$F35)),$F35)))</f>
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="H35" s="69" t="n">
         <f aca="false">IF($G35="",0,IF(AND($G35&gt;='Cash Flow'!$E$6,$G35&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12454,27 +12479,27 @@
       </c>
       <c r="F36" s="68" t="n">
         <f aca="false">IF($C36="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*0,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*0,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,0),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$7="One Time",IF(1=1,Recurring!$F$7,""),""))))))</f>
-        <v>46238</v>
+        <v>46269</v>
       </c>
       <c r="G36" s="68" t="n">
         <f aca="false">IF($F36="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F36,2)=6,$F36-1,IF(WEEKDAY($F36,2)=7,$F36-2,$F36)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F36,2)=6,$F36+2,IF(WEEKDAY($F36,2)=7,$F36+1,$F36)),$F36)))</f>
-        <v>46238</v>
+        <v>46269</v>
       </c>
       <c r="H36" s="69" t="n">
         <f aca="false">IF($G36="",0,IF(AND($G36&gt;='Cash Flow'!$E$6,$G36&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I36" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I36" s="69" t="n">
         <f aca="false">IF($H36=1,INT(($G36-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J36" s="66" t="str">
+        <v>5</v>
+      </c>
+      <c r="J36" s="66" t="n">
         <f aca="false">IF($H36=1,$G36*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="66" t="str">
+        <v>462690036</v>
+      </c>
+      <c r="K36" s="66" t="n">
         <f aca="false">IF($H36=1,$I36*1000+COUNTIFS($I$4:$I$483,$I36,$J$4:$J$483,"&lt;"&amp;$J36)+1,"")</f>
-        <v/>
+        <v>5002</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12498,11 +12523,11 @@
       </c>
       <c r="F37" s="68" t="n">
         <f aca="false">IF($C37="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*1,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*1,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,1),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$7="One Time",IF(2=1,Recurring!$F$7,""),""))))))</f>
-        <v>46269</v>
+        <v>46299</v>
       </c>
       <c r="G37" s="68" t="n">
         <f aca="false">IF($F37="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F37,2)=6,$F37-1,IF(WEEKDAY($F37,2)=7,$F37-2,$F37)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F37,2)=6,$F37+2,IF(WEEKDAY($F37,2)=7,$F37+1,$F37)),$F37)))</f>
-        <v>46269</v>
+        <v>46299</v>
       </c>
       <c r="H37" s="69" t="n">
         <f aca="false">IF($G37="",0,IF(AND($G37&gt;='Cash Flow'!$E$6,$G37&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12510,15 +12535,15 @@
       </c>
       <c r="I37" s="69" t="n">
         <f aca="false">IF($H37=1,INT(($G37-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J37" s="66" t="n">
         <f aca="false">IF($H37=1,$G37*10000+ROW(),"")</f>
-        <v>462690037</v>
+        <v>462990037</v>
       </c>
       <c r="K37" s="66" t="n">
         <f aca="false">IF($H37=1,$I37*1000+COUNTIFS($I$4:$I$483,$I37,$J$4:$J$483,"&lt;"&amp;$J37)+1,"")</f>
-        <v>5002</v>
+        <v>9002</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12542,11 +12567,11 @@
       </c>
       <c r="F38" s="68" t="n">
         <f aca="false">IF($C38="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*2,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*2,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,2),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$7="One Time",IF(3=1,Recurring!$F$7,""),""))))))</f>
-        <v>46299</v>
+        <v>46330</v>
       </c>
       <c r="G38" s="68" t="n">
         <f aca="false">IF($F38="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F38,2)=6,$F38-1,IF(WEEKDAY($F38,2)=7,$F38-2,$F38)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F38,2)=6,$F38+2,IF(WEEKDAY($F38,2)=7,$F38+1,$F38)),$F38)))</f>
-        <v>46299</v>
+        <v>46330</v>
       </c>
       <c r="H38" s="69" t="n">
         <f aca="false">IF($G38="",0,IF(AND($G38&gt;='Cash Flow'!$E$6,$G38&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12554,15 +12579,15 @@
       </c>
       <c r="I38" s="69" t="n">
         <f aca="false">IF($H38=1,INT(($G38-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J38" s="66" t="n">
         <f aca="false">IF($H38=1,$G38*10000+ROW(),"")</f>
-        <v>462990038</v>
+        <v>463300038</v>
       </c>
       <c r="K38" s="66" t="n">
         <f aca="false">IF($H38=1,$I38*1000+COUNTIFS($I$4:$I$483,$I38,$J$4:$J$483,"&lt;"&amp;$J38)+1,"")</f>
-        <v>9002</v>
+        <v>13006</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12586,27 +12611,27 @@
       </c>
       <c r="F39" s="68" t="n">
         <f aca="false">IF($C39="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*3,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*3,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,3),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$7="One Time",IF(4=1,Recurring!$F$7,""),""))))))</f>
-        <v>46330</v>
+        <v>46360</v>
       </c>
       <c r="G39" s="68" t="n">
         <f aca="false">IF($F39="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F39,2)=6,$F39-1,IF(WEEKDAY($F39,2)=7,$F39-2,$F39)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F39,2)=6,$F39+2,IF(WEEKDAY($F39,2)=7,$F39+1,$F39)),$F39)))</f>
-        <v>46330</v>
+        <v>46360</v>
       </c>
       <c r="H39" s="69" t="n">
         <f aca="false">IF($G39="",0,IF(AND($G39&gt;='Cash Flow'!$E$6,$G39&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I39" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="69" t="str">
         <f aca="false">IF($H39=1,INT(($G39-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J39" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J39" s="66" t="str">
         <f aca="false">IF($H39=1,$G39*10000+ROW(),"")</f>
-        <v>463300039</v>
-      </c>
-      <c r="K39" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K39" s="66" t="str">
         <f aca="false">IF($H39=1,$I39*1000+COUNTIFS($I$4:$I$483,$I39,$J$4:$J$483,"&lt;"&amp;$J39)+1,"")</f>
-        <v>13006</v>
+        <v/>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12630,11 +12655,11 @@
       </c>
       <c r="F40" s="68" t="n">
         <f aca="false">IF($C40="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*4,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*4,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,4),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$7="One Time",IF(5=1,Recurring!$F$7,""),""))))))</f>
-        <v>46360</v>
+        <v>46391</v>
       </c>
       <c r="G40" s="68" t="n">
         <f aca="false">IF($F40="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F40,2)=6,$F40-1,IF(WEEKDAY($F40,2)=7,$F40-2,$F40)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F40,2)=6,$F40+2,IF(WEEKDAY($F40,2)=7,$F40+1,$F40)),$F40)))</f>
-        <v>46360</v>
+        <v>46391</v>
       </c>
       <c r="H40" s="69" t="n">
         <f aca="false">IF($G40="",0,IF(AND($G40&gt;='Cash Flow'!$E$6,$G40&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12674,11 +12699,11 @@
       </c>
       <c r="F41" s="68" t="n">
         <f aca="false">IF($C41="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*5,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*5,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,5),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$7="One Time",IF(6=1,Recurring!$F$7,""),""))))))</f>
-        <v>46391</v>
+        <v>46422</v>
       </c>
       <c r="G41" s="68" t="n">
         <f aca="false">IF($F41="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F41,2)=6,$F41-1,IF(WEEKDAY($F41,2)=7,$F41-2,$F41)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F41,2)=6,$F41+2,IF(WEEKDAY($F41,2)=7,$F41+1,$F41)),$F41)))</f>
-        <v>46391</v>
+        <v>46422</v>
       </c>
       <c r="H41" s="69" t="n">
         <f aca="false">IF($G41="",0,IF(AND($G41&gt;='Cash Flow'!$E$6,$G41&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12718,11 +12743,11 @@
       </c>
       <c r="F42" s="68" t="n">
         <f aca="false">IF($C42="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*6,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*6,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,6),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$7="One Time",IF(7=1,Recurring!$F$7,""),""))))))</f>
-        <v>46422</v>
+        <v>46450</v>
       </c>
       <c r="G42" s="68" t="n">
         <f aca="false">IF($F42="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F42,2)=6,$F42-1,IF(WEEKDAY($F42,2)=7,$F42-2,$F42)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F42,2)=6,$F42+2,IF(WEEKDAY($F42,2)=7,$F42+1,$F42)),$F42)))</f>
-        <v>46422</v>
+        <v>46450</v>
       </c>
       <c r="H42" s="69" t="n">
         <f aca="false">IF($G42="",0,IF(AND($G42&gt;='Cash Flow'!$E$6,$G42&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12762,11 +12787,11 @@
       </c>
       <c r="F43" s="68" t="n">
         <f aca="false">IF($C43="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*7,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*7,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,7),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$7="One Time",IF(8=1,Recurring!$F$7,""),""))))))</f>
-        <v>46450</v>
+        <v>46481</v>
       </c>
       <c r="G43" s="68" t="n">
         <f aca="false">IF($F43="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F43,2)=6,$F43-1,IF(WEEKDAY($F43,2)=7,$F43-2,$F43)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F43,2)=6,$F43+2,IF(WEEKDAY($F43,2)=7,$F43+1,$F43)),$F43)))</f>
-        <v>46450</v>
+        <v>46481</v>
       </c>
       <c r="H43" s="69" t="n">
         <f aca="false">IF($G43="",0,IF(AND($G43&gt;='Cash Flow'!$E$6,$G43&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12806,11 +12831,11 @@
       </c>
       <c r="F44" s="68" t="n">
         <f aca="false">IF($C44="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*8,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*8,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,8),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$7="One Time",IF(9=1,Recurring!$F$7,""),""))))))</f>
-        <v>46481</v>
+        <v>46511</v>
       </c>
       <c r="G44" s="68" t="n">
         <f aca="false">IF($F44="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F44,2)=6,$F44-1,IF(WEEKDAY($F44,2)=7,$F44-2,$F44)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F44,2)=6,$F44+2,IF(WEEKDAY($F44,2)=7,$F44+1,$F44)),$F44)))</f>
-        <v>46481</v>
+        <v>46511</v>
       </c>
       <c r="H44" s="69" t="n">
         <f aca="false">IF($G44="",0,IF(AND($G44&gt;='Cash Flow'!$E$6,$G44&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12850,11 +12875,11 @@
       </c>
       <c r="F45" s="68" t="n">
         <f aca="false">IF($C45="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*9,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*9,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,9),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$7="One Time",IF(10=1,Recurring!$F$7,""),""))))))</f>
-        <v>46511</v>
+        <v>46542</v>
       </c>
       <c r="G45" s="68" t="n">
         <f aca="false">IF($F45="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F45,2)=6,$F45-1,IF(WEEKDAY($F45,2)=7,$F45-2,$F45)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F45,2)=6,$F45+2,IF(WEEKDAY($F45,2)=7,$F45+1,$F45)),$F45)))</f>
-        <v>46511</v>
+        <v>46542</v>
       </c>
       <c r="H45" s="69" t="n">
         <f aca="false">IF($G45="",0,IF(AND($G45&gt;='Cash Flow'!$E$6,$G45&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12894,11 +12919,11 @@
       </c>
       <c r="F46" s="68" t="n">
         <f aca="false">IF($C46="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*10,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*10,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,10),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$7="One Time",IF(11=1,Recurring!$F$7,""),""))))))</f>
-        <v>46542</v>
+        <v>46572</v>
       </c>
       <c r="G46" s="68" t="n">
         <f aca="false">IF($F46="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F46,2)=6,$F46-1,IF(WEEKDAY($F46,2)=7,$F46-2,$F46)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F46,2)=6,$F46+2,IF(WEEKDAY($F46,2)=7,$F46+1,$F46)),$F46)))</f>
-        <v>46542</v>
+        <v>46572</v>
       </c>
       <c r="H46" s="69" t="n">
         <f aca="false">IF($G46="",0,IF(AND($G46&gt;='Cash Flow'!$E$6,$G46&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12938,11 +12963,11 @@
       </c>
       <c r="F47" s="68" t="n">
         <f aca="false">IF($C47="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*11,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*11,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,11),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$7="One Time",IF(12=1,Recurring!$F$7,""),""))))))</f>
-        <v>46572</v>
+        <v>46603</v>
       </c>
       <c r="G47" s="68" t="n">
         <f aca="false">IF($F47="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F47,2)=6,$F47-1,IF(WEEKDAY($F47,2)=7,$F47-2,$F47)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F47,2)=6,$F47+2,IF(WEEKDAY($F47,2)=7,$F47+1,$F47)),$F47)))</f>
-        <v>46572</v>
+        <v>46603</v>
       </c>
       <c r="H47" s="69" t="n">
         <f aca="false">IF($G47="",0,IF(AND($G47&gt;='Cash Flow'!$E$6,$G47&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -12982,11 +13007,11 @@
       </c>
       <c r="F48" s="68" t="n">
         <f aca="false">IF($C48="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*12,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*12,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,12),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$7="One Time",IF(13=1,Recurring!$F$7,""),""))))))</f>
-        <v>46603</v>
+        <v>46634</v>
       </c>
       <c r="G48" s="68" t="n">
         <f aca="false">IF($F48="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F48,2)=6,$F48-1,IF(WEEKDAY($F48,2)=7,$F48-2,$F48)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F48,2)=6,$F48+2,IF(WEEKDAY($F48,2)=7,$F48+1,$F48)),$F48)))</f>
-        <v>46603</v>
+        <v>46634</v>
       </c>
       <c r="H48" s="69" t="n">
         <f aca="false">IF($G48="",0,IF(AND($G48&gt;='Cash Flow'!$E$6,$G48&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13026,11 +13051,11 @@
       </c>
       <c r="F49" s="68" t="n">
         <f aca="false">IF($C49="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*13,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*13,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,13),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$7="One Time",IF(14=1,Recurring!$F$7,""),""))))))</f>
-        <v>46634</v>
+        <v>46664</v>
       </c>
       <c r="G49" s="68" t="n">
         <f aca="false">IF($F49="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F49,2)=6,$F49-1,IF(WEEKDAY($F49,2)=7,$F49-2,$F49)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F49,2)=6,$F49+2,IF(WEEKDAY($F49,2)=7,$F49+1,$F49)),$F49)))</f>
-        <v>46634</v>
+        <v>46664</v>
       </c>
       <c r="H49" s="69" t="n">
         <f aca="false">IF($G49="",0,IF(AND($G49&gt;='Cash Flow'!$E$6,$G49&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13070,11 +13095,11 @@
       </c>
       <c r="F50" s="68" t="n">
         <f aca="false">IF($C50="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*14,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*14,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,14),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$7="One Time",IF(15=1,Recurring!$F$7,""),""))))))</f>
-        <v>46664</v>
+        <v>46695</v>
       </c>
       <c r="G50" s="68" t="n">
         <f aca="false">IF($F50="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F50,2)=6,$F50-1,IF(WEEKDAY($F50,2)=7,$F50-2,$F50)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F50,2)=6,$F50+2,IF(WEEKDAY($F50,2)=7,$F50+1,$F50)),$F50)))</f>
-        <v>46664</v>
+        <v>46695</v>
       </c>
       <c r="H50" s="69" t="n">
         <f aca="false">IF($G50="",0,IF(AND($G50&gt;='Cash Flow'!$E$6,$G50&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13114,11 +13139,11 @@
       </c>
       <c r="F51" s="68" t="n">
         <f aca="false">IF($C51="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*15,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*15,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,15),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$7="One Time",IF(16=1,Recurring!$F$7,""),""))))))</f>
-        <v>46695</v>
+        <v>46725</v>
       </c>
       <c r="G51" s="68" t="n">
         <f aca="false">IF($F51="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F51,2)=6,$F51-1,IF(WEEKDAY($F51,2)=7,$F51-2,$F51)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F51,2)=6,$F51+2,IF(WEEKDAY($F51,2)=7,$F51+1,$F51)),$F51)))</f>
-        <v>46695</v>
+        <v>46725</v>
       </c>
       <c r="H51" s="69" t="n">
         <f aca="false">IF($G51="",0,IF(AND($G51&gt;='Cash Flow'!$E$6,$G51&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13158,27 +13183,27 @@
       </c>
       <c r="F52" s="68" t="n">
         <f aca="false">IF($C52="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*0,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*0,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,0),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$8="One Time",IF(1=1,Recurring!$F$8,""),""))))))</f>
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="G52" s="68" t="n">
         <f aca="false">IF($F52="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F52,2)=6,$F52-1,IF(WEEKDAY($F52,2)=7,$F52-2,$F52)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F52,2)=6,$F52+2,IF(WEEKDAY($F52,2)=7,$F52+1,$F52)),$F52)))</f>
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="H52" s="69" t="n">
         <f aca="false">IF($G52="",0,IF(AND($G52&gt;='Cash Flow'!$E$6,$G52&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I52" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I52" s="69" t="n">
         <f aca="false">IF($H52=1,INT(($G52-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="66" t="str">
+        <v>5</v>
+      </c>
+      <c r="J52" s="66" t="n">
         <f aca="false">IF($H52=1,$G52*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="66" t="str">
+        <v>462700052</v>
+      </c>
+      <c r="K52" s="66" t="n">
         <f aca="false">IF($H52=1,$I52*1000+COUNTIFS($I$4:$I$483,$I52,$J$4:$J$483,"&lt;"&amp;$J52)+1,"")</f>
-        <v/>
+        <v>5003</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13202,11 +13227,11 @@
       </c>
       <c r="F53" s="68" t="n">
         <f aca="false">IF($C53="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*1,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*1,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,1),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$8="One Time",IF(2=1,Recurring!$F$8,""),""))))))</f>
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="G53" s="68" t="n">
         <f aca="false">IF($F53="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F53,2)=6,$F53-1,IF(WEEKDAY($F53,2)=7,$F53-2,$F53)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F53,2)=6,$F53+2,IF(WEEKDAY($F53,2)=7,$F53+1,$F53)),$F53)))</f>
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="H53" s="69" t="n">
         <f aca="false">IF($G53="",0,IF(AND($G53&gt;='Cash Flow'!$E$6,$G53&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13214,15 +13239,15 @@
       </c>
       <c r="I53" s="69" t="n">
         <f aca="false">IF($H53=1,INT(($G53-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J53" s="66" t="n">
         <f aca="false">IF($H53=1,$G53*10000+ROW(),"")</f>
-        <v>462700053</v>
+        <v>463000053</v>
       </c>
       <c r="K53" s="66" t="n">
         <f aca="false">IF($H53=1,$I53*1000+COUNTIFS($I$4:$I$483,$I53,$J$4:$J$483,"&lt;"&amp;$J53)+1,"")</f>
-        <v>5003</v>
+        <v>9003</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13246,11 +13271,11 @@
       </c>
       <c r="F54" s="68" t="n">
         <f aca="false">IF($C54="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*2,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*2,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,2),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$8="One Time",IF(3=1,Recurring!$F$8,""),""))))))</f>
-        <v>46300</v>
+        <v>46331</v>
       </c>
       <c r="G54" s="68" t="n">
         <f aca="false">IF($F54="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F54,2)=6,$F54-1,IF(WEEKDAY($F54,2)=7,$F54-2,$F54)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F54,2)=6,$F54+2,IF(WEEKDAY($F54,2)=7,$F54+1,$F54)),$F54)))</f>
-        <v>46300</v>
+        <v>46331</v>
       </c>
       <c r="H54" s="69" t="n">
         <f aca="false">IF($G54="",0,IF(AND($G54&gt;='Cash Flow'!$E$6,$G54&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13258,15 +13283,15 @@
       </c>
       <c r="I54" s="69" t="n">
         <f aca="false">IF($H54=1,INT(($G54-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J54" s="66" t="n">
         <f aca="false">IF($H54=1,$G54*10000+ROW(),"")</f>
-        <v>463000054</v>
+        <v>463310054</v>
       </c>
       <c r="K54" s="66" t="n">
         <f aca="false">IF($H54=1,$I54*1000+COUNTIFS($I$4:$I$483,$I54,$J$4:$J$483,"&lt;"&amp;$J54)+1,"")</f>
-        <v>9003</v>
+        <v>13007</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13290,27 +13315,27 @@
       </c>
       <c r="F55" s="68" t="n">
         <f aca="false">IF($C55="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*3,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*3,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,3),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$8="One Time",IF(4=1,Recurring!$F$8,""),""))))))</f>
-        <v>46331</v>
+        <v>46361</v>
       </c>
       <c r="G55" s="68" t="n">
         <f aca="false">IF($F55="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F55,2)=6,$F55-1,IF(WEEKDAY($F55,2)=7,$F55-2,$F55)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F55,2)=6,$F55+2,IF(WEEKDAY($F55,2)=7,$F55+1,$F55)),$F55)))</f>
-        <v>46331</v>
+        <v>46361</v>
       </c>
       <c r="H55" s="69" t="n">
         <f aca="false">IF($G55="",0,IF(AND($G55&gt;='Cash Flow'!$E$6,$G55&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I55" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="69" t="str">
         <f aca="false">IF($H55=1,INT(($G55-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J55" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J55" s="66" t="str">
         <f aca="false">IF($H55=1,$G55*10000+ROW(),"")</f>
-        <v>463310055</v>
-      </c>
-      <c r="K55" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K55" s="66" t="str">
         <f aca="false">IF($H55=1,$I55*1000+COUNTIFS($I$4:$I$483,$I55,$J$4:$J$483,"&lt;"&amp;$J55)+1,"")</f>
-        <v>13007</v>
+        <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13334,11 +13359,11 @@
       </c>
       <c r="F56" s="68" t="n">
         <f aca="false">IF($C56="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*4,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*4,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,4),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$8="One Time",IF(5=1,Recurring!$F$8,""),""))))))</f>
-        <v>46361</v>
+        <v>46392</v>
       </c>
       <c r="G56" s="68" t="n">
         <f aca="false">IF($F56="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F56,2)=6,$F56-1,IF(WEEKDAY($F56,2)=7,$F56-2,$F56)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F56,2)=6,$F56+2,IF(WEEKDAY($F56,2)=7,$F56+1,$F56)),$F56)))</f>
-        <v>46361</v>
+        <v>46392</v>
       </c>
       <c r="H56" s="69" t="n">
         <f aca="false">IF($G56="",0,IF(AND($G56&gt;='Cash Flow'!$E$6,$G56&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13378,11 +13403,11 @@
       </c>
       <c r="F57" s="68" t="n">
         <f aca="false">IF($C57="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*5,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*5,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,5),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$8="One Time",IF(6=1,Recurring!$F$8,""),""))))))</f>
-        <v>46392</v>
+        <v>46423</v>
       </c>
       <c r="G57" s="68" t="n">
         <f aca="false">IF($F57="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F57,2)=6,$F57-1,IF(WEEKDAY($F57,2)=7,$F57-2,$F57)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F57,2)=6,$F57+2,IF(WEEKDAY($F57,2)=7,$F57+1,$F57)),$F57)))</f>
-        <v>46392</v>
+        <v>46423</v>
       </c>
       <c r="H57" s="69" t="n">
         <f aca="false">IF($G57="",0,IF(AND($G57&gt;='Cash Flow'!$E$6,$G57&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13422,11 +13447,11 @@
       </c>
       <c r="F58" s="68" t="n">
         <f aca="false">IF($C58="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*6,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*6,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,6),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$8="One Time",IF(7=1,Recurring!$F$8,""),""))))))</f>
-        <v>46423</v>
+        <v>46451</v>
       </c>
       <c r="G58" s="68" t="n">
         <f aca="false">IF($F58="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F58,2)=6,$F58-1,IF(WEEKDAY($F58,2)=7,$F58-2,$F58)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F58,2)=6,$F58+2,IF(WEEKDAY($F58,2)=7,$F58+1,$F58)),$F58)))</f>
-        <v>46423</v>
+        <v>46451</v>
       </c>
       <c r="H58" s="69" t="n">
         <f aca="false">IF($G58="",0,IF(AND($G58&gt;='Cash Flow'!$E$6,$G58&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13466,11 +13491,11 @@
       </c>
       <c r="F59" s="68" t="n">
         <f aca="false">IF($C59="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*7,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*7,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,7),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$8="One Time",IF(8=1,Recurring!$F$8,""),""))))))</f>
-        <v>46451</v>
+        <v>46482</v>
       </c>
       <c r="G59" s="68" t="n">
         <f aca="false">IF($F59="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F59,2)=6,$F59-1,IF(WEEKDAY($F59,2)=7,$F59-2,$F59)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F59,2)=6,$F59+2,IF(WEEKDAY($F59,2)=7,$F59+1,$F59)),$F59)))</f>
-        <v>46451</v>
+        <v>46482</v>
       </c>
       <c r="H59" s="69" t="n">
         <f aca="false">IF($G59="",0,IF(AND($G59&gt;='Cash Flow'!$E$6,$G59&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13510,11 +13535,11 @@
       </c>
       <c r="F60" s="68" t="n">
         <f aca="false">IF($C60="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*8,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*8,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,8),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$8="One Time",IF(9=1,Recurring!$F$8,""),""))))))</f>
-        <v>46482</v>
+        <v>46512</v>
       </c>
       <c r="G60" s="68" t="n">
         <f aca="false">IF($F60="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F60,2)=6,$F60-1,IF(WEEKDAY($F60,2)=7,$F60-2,$F60)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F60,2)=6,$F60+2,IF(WEEKDAY($F60,2)=7,$F60+1,$F60)),$F60)))</f>
-        <v>46482</v>
+        <v>46512</v>
       </c>
       <c r="H60" s="69" t="n">
         <f aca="false">IF($G60="",0,IF(AND($G60&gt;='Cash Flow'!$E$6,$G60&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13554,11 +13579,11 @@
       </c>
       <c r="F61" s="68" t="n">
         <f aca="false">IF($C61="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*9,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*9,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,9),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$8="One Time",IF(10=1,Recurring!$F$8,""),""))))))</f>
-        <v>46512</v>
+        <v>46543</v>
       </c>
       <c r="G61" s="68" t="n">
         <f aca="false">IF($F61="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F61,2)=6,$F61-1,IF(WEEKDAY($F61,2)=7,$F61-2,$F61)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F61,2)=6,$F61+2,IF(WEEKDAY($F61,2)=7,$F61+1,$F61)),$F61)))</f>
-        <v>46512</v>
+        <v>46543</v>
       </c>
       <c r="H61" s="69" t="n">
         <f aca="false">IF($G61="",0,IF(AND($G61&gt;='Cash Flow'!$E$6,$G61&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13598,11 +13623,11 @@
       </c>
       <c r="F62" s="68" t="n">
         <f aca="false">IF($C62="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*10,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*10,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,10),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$8="One Time",IF(11=1,Recurring!$F$8,""),""))))))</f>
-        <v>46543</v>
+        <v>46573</v>
       </c>
       <c r="G62" s="68" t="n">
         <f aca="false">IF($F62="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F62,2)=6,$F62-1,IF(WEEKDAY($F62,2)=7,$F62-2,$F62)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F62,2)=6,$F62+2,IF(WEEKDAY($F62,2)=7,$F62+1,$F62)),$F62)))</f>
-        <v>46543</v>
+        <v>46573</v>
       </c>
       <c r="H62" s="69" t="n">
         <f aca="false">IF($G62="",0,IF(AND($G62&gt;='Cash Flow'!$E$6,$G62&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13642,11 +13667,11 @@
       </c>
       <c r="F63" s="68" t="n">
         <f aca="false">IF($C63="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*11,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*11,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,11),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$8="One Time",IF(12=1,Recurring!$F$8,""),""))))))</f>
-        <v>46573</v>
+        <v>46604</v>
       </c>
       <c r="G63" s="68" t="n">
         <f aca="false">IF($F63="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F63,2)=6,$F63-1,IF(WEEKDAY($F63,2)=7,$F63-2,$F63)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F63,2)=6,$F63+2,IF(WEEKDAY($F63,2)=7,$F63+1,$F63)),$F63)))</f>
-        <v>46573</v>
+        <v>46604</v>
       </c>
       <c r="H63" s="69" t="n">
         <f aca="false">IF($G63="",0,IF(AND($G63&gt;='Cash Flow'!$E$6,$G63&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13686,11 +13711,11 @@
       </c>
       <c r="F64" s="68" t="n">
         <f aca="false">IF($C64="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*12,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*12,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,12),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$8="One Time",IF(13=1,Recurring!$F$8,""),""))))))</f>
-        <v>46604</v>
+        <v>46635</v>
       </c>
       <c r="G64" s="68" t="n">
         <f aca="false">IF($F64="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F64,2)=6,$F64-1,IF(WEEKDAY($F64,2)=7,$F64-2,$F64)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F64,2)=6,$F64+2,IF(WEEKDAY($F64,2)=7,$F64+1,$F64)),$F64)))</f>
-        <v>46604</v>
+        <v>46635</v>
       </c>
       <c r="H64" s="69" t="n">
         <f aca="false">IF($G64="",0,IF(AND($G64&gt;='Cash Flow'!$E$6,$G64&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13730,11 +13755,11 @@
       </c>
       <c r="F65" s="68" t="n">
         <f aca="false">IF($C65="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*13,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*13,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,13),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$8="One Time",IF(14=1,Recurring!$F$8,""),""))))))</f>
-        <v>46635</v>
+        <v>46665</v>
       </c>
       <c r="G65" s="68" t="n">
         <f aca="false">IF($F65="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F65,2)=6,$F65-1,IF(WEEKDAY($F65,2)=7,$F65-2,$F65)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F65,2)=6,$F65+2,IF(WEEKDAY($F65,2)=7,$F65+1,$F65)),$F65)))</f>
-        <v>46635</v>
+        <v>46665</v>
       </c>
       <c r="H65" s="69" t="n">
         <f aca="false">IF($G65="",0,IF(AND($G65&gt;='Cash Flow'!$E$6,$G65&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13774,11 +13799,11 @@
       </c>
       <c r="F66" s="68" t="n">
         <f aca="false">IF($C66="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*14,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*14,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,14),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$8="One Time",IF(15=1,Recurring!$F$8,""),""))))))</f>
-        <v>46665</v>
+        <v>46696</v>
       </c>
       <c r="G66" s="68" t="n">
         <f aca="false">IF($F66="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F66,2)=6,$F66-1,IF(WEEKDAY($F66,2)=7,$F66-2,$F66)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F66,2)=6,$F66+2,IF(WEEKDAY($F66,2)=7,$F66+1,$F66)),$F66)))</f>
-        <v>46665</v>
+        <v>46696</v>
       </c>
       <c r="H66" s="69" t="n">
         <f aca="false">IF($G66="",0,IF(AND($G66&gt;='Cash Flow'!$E$6,$G66&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13818,11 +13843,11 @@
       </c>
       <c r="F67" s="68" t="n">
         <f aca="false">IF($C67="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*15,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*15,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,15),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$8="One Time",IF(16=1,Recurring!$F$8,""),""))))))</f>
-        <v>46696</v>
+        <v>46726</v>
       </c>
       <c r="G67" s="68" t="n">
         <f aca="false">IF($F67="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F67,2)=6,$F67-1,IF(WEEKDAY($F67,2)=7,$F67-2,$F67)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F67,2)=6,$F67+2,IF(WEEKDAY($F67,2)=7,$F67+1,$F67)),$F67)))</f>
-        <v>46696</v>
+        <v>46726</v>
       </c>
       <c r="H67" s="69" t="n">
         <f aca="false">IF($G67="",0,IF(AND($G67&gt;='Cash Flow'!$E$6,$G67&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13862,27 +13887,27 @@
       </c>
       <c r="F68" s="68" t="n">
         <f aca="false">IF($C68="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*0,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*0,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,0),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$9="One Time",IF(1=1,Recurring!$F$9,""),""))))))</f>
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="G68" s="68" t="n">
         <f aca="false">IF($F68="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F68,2)=6,$F68-1,IF(WEEKDAY($F68,2)=7,$F68-2,$F68)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F68,2)=6,$F68+2,IF(WEEKDAY($F68,2)=7,$F68+1,$F68)),$F68)))</f>
-        <v>46239</v>
+        <v>46270</v>
       </c>
       <c r="H68" s="69" t="n">
         <f aca="false">IF($G68="",0,IF(AND($G68&gt;='Cash Flow'!$E$6,$G68&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I68" s="69" t="str">
+        <v>1</v>
+      </c>
+      <c r="I68" s="69" t="n">
         <f aca="false">IF($H68=1,INT(($G68-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J68" s="66" t="str">
+        <v>5</v>
+      </c>
+      <c r="J68" s="66" t="n">
         <f aca="false">IF($H68=1,$G68*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K68" s="66" t="str">
+        <v>462700068</v>
+      </c>
+      <c r="K68" s="66" t="n">
         <f aca="false">IF($H68=1,$I68*1000+COUNTIFS($I$4:$I$483,$I68,$J$4:$J$483,"&lt;"&amp;$J68)+1,"")</f>
-        <v/>
+        <v>5004</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13906,11 +13931,11 @@
       </c>
       <c r="F69" s="68" t="n">
         <f aca="false">IF($C69="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*1,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*1,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,1),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$9="One Time",IF(2=1,Recurring!$F$9,""),""))))))</f>
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="G69" s="68" t="n">
         <f aca="false">IF($F69="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F69,2)=6,$F69-1,IF(WEEKDAY($F69,2)=7,$F69-2,$F69)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F69,2)=6,$F69+2,IF(WEEKDAY($F69,2)=7,$F69+1,$F69)),$F69)))</f>
-        <v>46270</v>
+        <v>46300</v>
       </c>
       <c r="H69" s="69" t="n">
         <f aca="false">IF($G69="",0,IF(AND($G69&gt;='Cash Flow'!$E$6,$G69&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13918,15 +13943,15 @@
       </c>
       <c r="I69" s="69" t="n">
         <f aca="false">IF($H69=1,INT(($G69-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J69" s="66" t="n">
         <f aca="false">IF($H69=1,$G69*10000+ROW(),"")</f>
-        <v>462700069</v>
+        <v>463000069</v>
       </c>
       <c r="K69" s="66" t="n">
         <f aca="false">IF($H69=1,$I69*1000+COUNTIFS($I$4:$I$483,$I69,$J$4:$J$483,"&lt;"&amp;$J69)+1,"")</f>
-        <v>5004</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13950,11 +13975,11 @@
       </c>
       <c r="F70" s="68" t="n">
         <f aca="false">IF($C70="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*2,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*2,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,2),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$9="One Time",IF(3=1,Recurring!$F$9,""),""))))))</f>
-        <v>46300</v>
+        <v>46331</v>
       </c>
       <c r="G70" s="68" t="n">
         <f aca="false">IF($F70="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F70,2)=6,$F70-1,IF(WEEKDAY($F70,2)=7,$F70-2,$F70)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F70,2)=6,$F70+2,IF(WEEKDAY($F70,2)=7,$F70+1,$F70)),$F70)))</f>
-        <v>46300</v>
+        <v>46331</v>
       </c>
       <c r="H70" s="69" t="n">
         <f aca="false">IF($G70="",0,IF(AND($G70&gt;='Cash Flow'!$E$6,$G70&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -13962,15 +13987,15 @@
       </c>
       <c r="I70" s="69" t="n">
         <f aca="false">IF($H70=1,INT(($G70-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J70" s="66" t="n">
         <f aca="false">IF($H70=1,$G70*10000+ROW(),"")</f>
-        <v>463000070</v>
+        <v>463310070</v>
       </c>
       <c r="K70" s="66" t="n">
         <f aca="false">IF($H70=1,$I70*1000+COUNTIFS($I$4:$I$483,$I70,$J$4:$J$483,"&lt;"&amp;$J70)+1,"")</f>
-        <v>9004</v>
+        <v>13008</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13994,27 +14019,27 @@
       </c>
       <c r="F71" s="68" t="n">
         <f aca="false">IF($C71="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*3,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*3,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,3),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$9="One Time",IF(4=1,Recurring!$F$9,""),""))))))</f>
-        <v>46331</v>
+        <v>46361</v>
       </c>
       <c r="G71" s="68" t="n">
         <f aca="false">IF($F71="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F71,2)=6,$F71-1,IF(WEEKDAY($F71,2)=7,$F71-2,$F71)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F71,2)=6,$F71+2,IF(WEEKDAY($F71,2)=7,$F71+1,$F71)),$F71)))</f>
-        <v>46331</v>
+        <v>46361</v>
       </c>
       <c r="H71" s="69" t="n">
         <f aca="false">IF($G71="",0,IF(AND($G71&gt;='Cash Flow'!$E$6,$G71&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I71" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="69" t="str">
         <f aca="false">IF($H71=1,INT(($G71-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
-      </c>
-      <c r="J71" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J71" s="66" t="str">
         <f aca="false">IF($H71=1,$G71*10000+ROW(),"")</f>
-        <v>463310071</v>
-      </c>
-      <c r="K71" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K71" s="66" t="str">
         <f aca="false">IF($H71=1,$I71*1000+COUNTIFS($I$4:$I$483,$I71,$J$4:$J$483,"&lt;"&amp;$J71)+1,"")</f>
-        <v>13008</v>
+        <v/>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14038,11 +14063,11 @@
       </c>
       <c r="F72" s="68" t="n">
         <f aca="false">IF($C72="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*4,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*4,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,4),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$9="One Time",IF(5=1,Recurring!$F$9,""),""))))))</f>
-        <v>46361</v>
+        <v>46392</v>
       </c>
       <c r="G72" s="68" t="n">
         <f aca="false">IF($F72="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F72,2)=6,$F72-1,IF(WEEKDAY($F72,2)=7,$F72-2,$F72)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F72,2)=6,$F72+2,IF(WEEKDAY($F72,2)=7,$F72+1,$F72)),$F72)))</f>
-        <v>46361</v>
+        <v>46392</v>
       </c>
       <c r="H72" s="69" t="n">
         <f aca="false">IF($G72="",0,IF(AND($G72&gt;='Cash Flow'!$E$6,$G72&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14082,11 +14107,11 @@
       </c>
       <c r="F73" s="68" t="n">
         <f aca="false">IF($C73="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*5,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*5,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,5),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$9="One Time",IF(6=1,Recurring!$F$9,""),""))))))</f>
-        <v>46392</v>
+        <v>46423</v>
       </c>
       <c r="G73" s="68" t="n">
         <f aca="false">IF($F73="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F73,2)=6,$F73-1,IF(WEEKDAY($F73,2)=7,$F73-2,$F73)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F73,2)=6,$F73+2,IF(WEEKDAY($F73,2)=7,$F73+1,$F73)),$F73)))</f>
-        <v>46392</v>
+        <v>46423</v>
       </c>
       <c r="H73" s="69" t="n">
         <f aca="false">IF($G73="",0,IF(AND($G73&gt;='Cash Flow'!$E$6,$G73&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14126,11 +14151,11 @@
       </c>
       <c r="F74" s="68" t="n">
         <f aca="false">IF($C74="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*6,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*6,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,6),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$9="One Time",IF(7=1,Recurring!$F$9,""),""))))))</f>
-        <v>46423</v>
+        <v>46451</v>
       </c>
       <c r="G74" s="68" t="n">
         <f aca="false">IF($F74="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F74,2)=6,$F74-1,IF(WEEKDAY($F74,2)=7,$F74-2,$F74)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F74,2)=6,$F74+2,IF(WEEKDAY($F74,2)=7,$F74+1,$F74)),$F74)))</f>
-        <v>46423</v>
+        <v>46451</v>
       </c>
       <c r="H74" s="69" t="n">
         <f aca="false">IF($G74="",0,IF(AND($G74&gt;='Cash Flow'!$E$6,$G74&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14170,11 +14195,11 @@
       </c>
       <c r="F75" s="68" t="n">
         <f aca="false">IF($C75="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*7,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*7,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,7),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$9="One Time",IF(8=1,Recurring!$F$9,""),""))))))</f>
-        <v>46451</v>
+        <v>46482</v>
       </c>
       <c r="G75" s="68" t="n">
         <f aca="false">IF($F75="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F75,2)=6,$F75-1,IF(WEEKDAY($F75,2)=7,$F75-2,$F75)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F75,2)=6,$F75+2,IF(WEEKDAY($F75,2)=7,$F75+1,$F75)),$F75)))</f>
-        <v>46451</v>
+        <v>46482</v>
       </c>
       <c r="H75" s="69" t="n">
         <f aca="false">IF($G75="",0,IF(AND($G75&gt;='Cash Flow'!$E$6,$G75&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14214,11 +14239,11 @@
       </c>
       <c r="F76" s="68" t="n">
         <f aca="false">IF($C76="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*8,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*8,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,8),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$9="One Time",IF(9=1,Recurring!$F$9,""),""))))))</f>
-        <v>46482</v>
+        <v>46512</v>
       </c>
       <c r="G76" s="68" t="n">
         <f aca="false">IF($F76="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F76,2)=6,$F76-1,IF(WEEKDAY($F76,2)=7,$F76-2,$F76)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F76,2)=6,$F76+2,IF(WEEKDAY($F76,2)=7,$F76+1,$F76)),$F76)))</f>
-        <v>46482</v>
+        <v>46512</v>
       </c>
       <c r="H76" s="69" t="n">
         <f aca="false">IF($G76="",0,IF(AND($G76&gt;='Cash Flow'!$E$6,$G76&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14258,11 +14283,11 @@
       </c>
       <c r="F77" s="68" t="n">
         <f aca="false">IF($C77="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*9,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*9,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,9),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$9="One Time",IF(10=1,Recurring!$F$9,""),""))))))</f>
-        <v>46512</v>
+        <v>46543</v>
       </c>
       <c r="G77" s="68" t="n">
         <f aca="false">IF($F77="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F77,2)=6,$F77-1,IF(WEEKDAY($F77,2)=7,$F77-2,$F77)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F77,2)=6,$F77+2,IF(WEEKDAY($F77,2)=7,$F77+1,$F77)),$F77)))</f>
-        <v>46512</v>
+        <v>46543</v>
       </c>
       <c r="H77" s="69" t="n">
         <f aca="false">IF($G77="",0,IF(AND($G77&gt;='Cash Flow'!$E$6,$G77&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14302,11 +14327,11 @@
       </c>
       <c r="F78" s="68" t="n">
         <f aca="false">IF($C78="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*10,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*10,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,10),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$9="One Time",IF(11=1,Recurring!$F$9,""),""))))))</f>
-        <v>46543</v>
+        <v>46573</v>
       </c>
       <c r="G78" s="68" t="n">
         <f aca="false">IF($F78="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F78,2)=6,$F78-1,IF(WEEKDAY($F78,2)=7,$F78-2,$F78)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F78,2)=6,$F78+2,IF(WEEKDAY($F78,2)=7,$F78+1,$F78)),$F78)))</f>
-        <v>46543</v>
+        <v>46573</v>
       </c>
       <c r="H78" s="69" t="n">
         <f aca="false">IF($G78="",0,IF(AND($G78&gt;='Cash Flow'!$E$6,$G78&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14346,11 +14371,11 @@
       </c>
       <c r="F79" s="68" t="n">
         <f aca="false">IF($C79="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*11,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*11,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,11),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$9="One Time",IF(12=1,Recurring!$F$9,""),""))))))</f>
-        <v>46573</v>
+        <v>46604</v>
       </c>
       <c r="G79" s="68" t="n">
         <f aca="false">IF($F79="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F79,2)=6,$F79-1,IF(WEEKDAY($F79,2)=7,$F79-2,$F79)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F79,2)=6,$F79+2,IF(WEEKDAY($F79,2)=7,$F79+1,$F79)),$F79)))</f>
-        <v>46573</v>
+        <v>46604</v>
       </c>
       <c r="H79" s="69" t="n">
         <f aca="false">IF($G79="",0,IF(AND($G79&gt;='Cash Flow'!$E$6,$G79&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14390,11 +14415,11 @@
       </c>
       <c r="F80" s="68" t="n">
         <f aca="false">IF($C80="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*12,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*12,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,12),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$9="One Time",IF(13=1,Recurring!$F$9,""),""))))))</f>
-        <v>46604</v>
+        <v>46635</v>
       </c>
       <c r="G80" s="68" t="n">
         <f aca="false">IF($F80="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F80,2)=6,$F80-1,IF(WEEKDAY($F80,2)=7,$F80-2,$F80)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F80,2)=6,$F80+2,IF(WEEKDAY($F80,2)=7,$F80+1,$F80)),$F80)))</f>
-        <v>46604</v>
+        <v>46635</v>
       </c>
       <c r="H80" s="69" t="n">
         <f aca="false">IF($G80="",0,IF(AND($G80&gt;='Cash Flow'!$E$6,$G80&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14434,11 +14459,11 @@
       </c>
       <c r="F81" s="68" t="n">
         <f aca="false">IF($C81="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*13,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*13,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,13),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$9="One Time",IF(14=1,Recurring!$F$9,""),""))))))</f>
-        <v>46635</v>
+        <v>46665</v>
       </c>
       <c r="G81" s="68" t="n">
         <f aca="false">IF($F81="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F81,2)=6,$F81-1,IF(WEEKDAY($F81,2)=7,$F81-2,$F81)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F81,2)=6,$F81+2,IF(WEEKDAY($F81,2)=7,$F81+1,$F81)),$F81)))</f>
-        <v>46635</v>
+        <v>46665</v>
       </c>
       <c r="H81" s="69" t="n">
         <f aca="false">IF($G81="",0,IF(AND($G81&gt;='Cash Flow'!$E$6,$G81&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14478,11 +14503,11 @@
       </c>
       <c r="F82" s="68" t="n">
         <f aca="false">IF($C82="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*14,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*14,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,14),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$9="One Time",IF(15=1,Recurring!$F$9,""),""))))))</f>
-        <v>46665</v>
+        <v>46696</v>
       </c>
       <c r="G82" s="68" t="n">
         <f aca="false">IF($F82="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F82,2)=6,$F82-1,IF(WEEKDAY($F82,2)=7,$F82-2,$F82)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F82,2)=6,$F82+2,IF(WEEKDAY($F82,2)=7,$F82+1,$F82)),$F82)))</f>
-        <v>46665</v>
+        <v>46696</v>
       </c>
       <c r="H82" s="69" t="n">
         <f aca="false">IF($G82="",0,IF(AND($G82&gt;='Cash Flow'!$E$6,$G82&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14522,11 +14547,11 @@
       </c>
       <c r="F83" s="68" t="n">
         <f aca="false">IF($C83="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*15,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*15,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,15),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$9="One Time",IF(16=1,Recurring!$F$9,""),""))))))</f>
-        <v>46696</v>
+        <v>46726</v>
       </c>
       <c r="G83" s="68" t="n">
         <f aca="false">IF($F83="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F83,2)=6,$F83-1,IF(WEEKDAY($F83,2)=7,$F83-2,$F83)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F83,2)=6,$F83+2,IF(WEEKDAY($F83,2)=7,$F83+1,$F83)),$F83)))</f>
-        <v>46696</v>
+        <v>46726</v>
       </c>
       <c r="H83" s="69" t="n">
         <f aca="false">IF($G83="",0,IF(AND($G83&gt;='Cash Flow'!$E$6,$G83&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14586,7 +14611,7 @@
       </c>
       <c r="K84" s="66" t="n">
         <f aca="false">IF($H84=1,$I84*1000+COUNTIFS($I$4:$I$483,$I84,$J$4:$J$483,"&lt;"&amp;$J84)+1,"")</f>
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15290,7 +15315,7 @@
       </c>
       <c r="K100" s="66" t="n">
         <f aca="false">IF($H100=1,$I100*1000+COUNTIFS($I$4:$I$483,$I100,$J$4:$J$483,"&lt;"&amp;$J100)+1,"")</f>
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15994,7 +16019,7 @@
       </c>
       <c r="K116" s="66" t="n">
         <f aca="false">IF($H116=1,$I116*1000+COUNTIFS($I$4:$I$483,$I116,$J$4:$J$483,"&lt;"&amp;$J116)+1,"")</f>
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16698,7 +16723,7 @@
       </c>
       <c r="K132" s="66" t="n">
         <f aca="false">IF($H132=1,$I132*1000+COUNTIFS($I$4:$I$483,$I132,$J$4:$J$483,"&lt;"&amp;$J132)+1,"")</f>
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -189,7 +189,7 @@
     <t xml:space="preserve">Amounts are entered as positive numbers. The Type column (Income or Expense) decides the sign, so a $90 paycheck is Type = Income, amount 90.</t>
   </si>
   <si>
-    <t xml:space="preserve">The sheet opens on Fri Aug 7, 2026 with $71.17 already in hand. The Aug 7 Compunnel paycheck had already landed by then, so its Next Due Date is Aug 14 — the first one still to come. Bruno's, Apple: Claude, OpenAI and Obsidian were rolled forward for the same reason. Google One ($4.99) and Upstart ($500) are still shown as due on Aug 7; if those already came out of the account, roll them forward to Sep 7 too.</t>
+    <t xml:space="preserve">The sheet opens on Fri Aug 7, 2026 with $71.17 already in hand. Everything that had already moved by that morning was rolled forward to its next occurrence, so the projection never counts the same money twice: the Compunnel paycheck (now Aug 14), Upstart and Google One (now Sep 7), and Bruno's, Apple: Claude, OpenAI and Obsidian. Confirmed with the user on Aug 7, 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">Progressive Insurance ($143.37) was cut off at the bottom of the third screenshot, so its due date is set to Aug 31, 2026. Correct it on the Recurring tab if that is wrong.</t>
@@ -1886,7 +1886,7 @@
         <v>42</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>72</v>
@@ -1916,7 +1916,7 @@
         <v>42</v>
       </c>
       <c r="F11" s="17" t="n">
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="G11" s="15" t="s">
         <v>72</v>
@@ -2601,11 +2601,11 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Google One</v>
+        <v>Central Maine Power Co.</v>
       </c>
       <c r="C15" s="34" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$G$4:$G$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="D15" s="35" t="str">
         <f aca="false">IF($B15="","",INDEX(Schedule!$D$4:$D$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
@@ -2613,20 +2613,20 @@
       </c>
       <c r="E15" s="36" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$E$4:$E$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>4.99</v>
+        <v>163.5</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="36" t="n">
         <f aca="false">IF($B15="","",IF($F15&lt;&gt;"",$F15,$E15))</f>
-        <v>4.99</v>
+        <v>163.5</v>
       </c>
       <c r="H15" s="36" t="n">
         <f aca="false">IF($B15="",0,IF($D15="Income",$G15,-$G15))</f>
-        <v>-4.99</v>
+        <v>-163.5</v>
       </c>
       <c r="I15" s="37" t="n">
         <f aca="false">IF($B15="","",$I$13+SUM($H$15:$H15))</f>
-        <v>66.18</v>
+        <v>-92.33</v>
       </c>
       <c r="J15" s="38" t="str">
         <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2636,32 +2636,32 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Upstart (loan)</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$G$4:$G$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="D16" s="35" t="str">
         <f aca="false">IF($B16="","",INDEX(Schedule!$D$4:$D$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E16" s="36" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$E$4:$E$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="36" t="n">
         <f aca="false">IF($B16="","",IF($F16&lt;&gt;"",$F16,$E16))</f>
-        <v>500</v>
+        <v>90</v>
       </c>
       <c r="H16" s="36" t="n">
         <f aca="false">IF($B16="",0,IF($D16="Income",$G16,-$G16))</f>
-        <v>-500</v>
+        <v>90</v>
       </c>
       <c r="I16" s="37" t="n">
         <f aca="false">IF($B16="","",$I$13+SUM($H$15:$H16))</f>
-        <v>-433.82</v>
+        <v>-2.33</v>
       </c>
       <c r="J16" s="38" t="str">
         <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2671,11 +2671,11 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C17" s="34" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$G$4:$G$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="D17" s="35" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$D$4:$D$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
@@ -2683,20 +2683,20 @@
       </c>
       <c r="E17" s="36" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$E$4:$E$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>2.99</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="36" t="n">
         <f aca="false">IF($B17="","",IF($F17&lt;&gt;"",$F17,$E17))</f>
-        <v>163.5</v>
+        <v>2.99</v>
       </c>
       <c r="H17" s="36" t="n">
         <f aca="false">IF($B17="",0,IF($D17="Income",$G17,-$G17))</f>
-        <v>-163.5</v>
+        <v>-2.99</v>
       </c>
       <c r="I17" s="37" t="n">
         <f aca="false">IF($B17="","",$I$13+SUM($H$15:$H17))</f>
-        <v>-597.32</v>
+        <v>-5.31999999999999</v>
       </c>
       <c r="J17" s="38" t="str">
         <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2706,71 +2706,71 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
-      </c>
-      <c r="C18" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C18" s="34" t="str">
         <f aca="false">IF($B18="","",INDEX(Schedule!$G$4:$G$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>46246</v>
+        <v/>
       </c>
       <c r="D18" s="35" t="str">
         <f aca="false">IF($B18="","",INDEX(Schedule!$D$4:$D$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
-      </c>
-      <c r="E18" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E18" s="36" t="str">
         <f aca="false">IF($B18="","",INDEX(Schedule!$E$4:$E$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="F18" s="16"/>
-      <c r="G18" s="36" t="n">
+      <c r="G18" s="36" t="str">
         <f aca="false">IF($B18="","",IF($F18&lt;&gt;"",$F18,$E18))</f>
-        <v>90</v>
+        <v/>
       </c>
       <c r="H18" s="36" t="n">
         <f aca="false">IF($B18="",0,IF($D18="Income",$G18,-$G18))</f>
-        <v>90</v>
-      </c>
-      <c r="I18" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="37" t="str">
         <f aca="false">IF($B18="","",$I$13+SUM($H$15:$H18))</f>
-        <v>-507.32</v>
+        <v/>
       </c>
       <c r="J18" s="38" t="str">
         <f aca="true">IF($B18="","",IF($F18&lt;&gt;"","PAID",IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="9" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
-      </c>
-      <c r="C19" s="34" t="n">
+        <v/>
+      </c>
+      <c r="C19" s="34" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$G$4:$G$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>46247</v>
+        <v/>
       </c>
       <c r="D19" s="35" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$D$4:$D$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E19" s="36" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="36" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$E$4:$E$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="F19" s="16"/>
-      <c r="G19" s="36" t="n">
+      <c r="G19" s="36" t="str">
         <f aca="false">IF($B19="","",IF($F19&lt;&gt;"",$F19,$E19))</f>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="H19" s="36" t="n">
         <f aca="false">IF($B19="",0,IF($D19="Income",$G19,-$G19))</f>
-        <v>-2.99</v>
-      </c>
-      <c r="I19" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="37" t="str">
         <f aca="false">IF($B19="","",$I$13+SUM($H$15:$H19))</f>
-        <v>-510.31</v>
+        <v/>
       </c>
       <c r="J19" s="38" t="str">
         <f aca="true">IF($B19="","",IF($F19&lt;&gt;"","PAID",IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3107,7 +3107,7 @@
       <c r="D32" s="42"/>
       <c r="E32" s="43" t="n">
         <f aca="false">SUM($E$15:$E$31)</f>
-        <v>761.48</v>
+        <v>256.49</v>
       </c>
       <c r="F32" s="43" t="n">
         <f aca="false">SUM($F$15:$F$24)</f>
@@ -3115,15 +3115,15 @@
       </c>
       <c r="G32" s="43" t="n">
         <f aca="false">SUM($G$15:$G$31)</f>
-        <v>761.48</v>
+        <v>256.49</v>
       </c>
       <c r="H32" s="43" t="n">
         <f aca="false">SUM($H$15:$H$31)</f>
-        <v>-581.48</v>
+        <v>-76.49</v>
       </c>
       <c r="I32" s="44" t="n">
         <f aca="false">$I$13+SUM($H$15:$H$31)</f>
-        <v>-510.31</v>
+        <v>-5.31999999999999</v>
       </c>
       <c r="J32" s="45" t="str">
         <f aca="false">IF($I$32&lt;0,"SHORTFALL",IF($I$32&lt;$E$7,"TIGHT","OK"))</f>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="K32" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$15:$D$31,"Income",$G$15:$G$31),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$15:$D$31,"Expense",$G$15:$G$31),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$32,"$#,##0.00")</f>
-        <v>Income $90.00   less expenses $671.48   =  net -$581.48</v>
+        <v>Income $90.00   less expenses $166.49   =  net -$76.49</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3149,7 +3149,7 @@
       <c r="H34" s="30"/>
       <c r="I34" s="32" t="n">
         <f aca="false">$I$32</f>
-        <v>-510.31</v>
+        <v>-5.31999999999999</v>
       </c>
       <c r="J34" s="30"/>
       <c r="K34" s="26" t="str">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="I36" s="37" t="n">
         <f aca="false">IF($B36="","",$I$34+SUM($H$36:$H36))</f>
-        <v>279.69</v>
+        <v>784.68</v>
       </c>
       <c r="J36" s="38" t="str">
         <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3249,7 +3249,7 @@
       </c>
       <c r="I37" s="37" t="n">
         <f aca="false">IF($B37="","",$I$34+SUM($H$36:$H37))</f>
-        <v>-70.31</v>
+        <v>434.68</v>
       </c>
       <c r="J37" s="38" t="str">
         <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3284,7 +3284,7 @@
       </c>
       <c r="I38" s="37" t="n">
         <f aca="false">IF($B38="","",$I$34+SUM($H$36:$H38))</f>
-        <v>-241.41</v>
+        <v>263.58</v>
       </c>
       <c r="J38" s="38" t="str">
         <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I39" s="37" t="n">
         <f aca="false">IF($B39="","",$I$34+SUM($H$36:$H39))</f>
-        <v>-286.41</v>
+        <v>218.58</v>
       </c>
       <c r="J39" s="38" t="str">
         <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="I40" s="37" t="n">
         <f aca="false">IF($B40="","",$I$34+SUM($H$36:$H40))</f>
-        <v>-303.4</v>
+        <v>201.59</v>
       </c>
       <c r="J40" s="38" t="str">
         <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="I41" s="37" t="n">
         <f aca="false">IF($B41="","",$I$34+SUM($H$36:$H41))</f>
-        <v>-213.4</v>
+        <v>291.59</v>
       </c>
       <c r="J41" s="38" t="str">
         <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3711,11 +3711,11 @@
       </c>
       <c r="I53" s="44" t="n">
         <f aca="false">$I$34+SUM($H$36:$H$52)</f>
-        <v>-213.4</v>
+        <v>291.59</v>
       </c>
       <c r="J53" s="45" t="str">
         <f aca="false">IF($I$53&lt;0,"SHORTFALL",IF($I$53&lt;$E$7,"TIGHT","OK"))</f>
-        <v>SHORTFALL</v>
+        <v>OK</v>
       </c>
       <c r="K53" s="23" t="str">
         <f aca="false">"Income "&amp;TEXT(SUMIF($D$36:$D$52,"Income",$G$36:$G$52),"$#,##0.00")&amp;"   less expenses "&amp;TEXT(SUMIF($D$36:$D$52,"Expense",$G$36:$G$52),"$#,##0.00")&amp;"   =  net "&amp;TEXT($H$53,"$#,##0.00")</f>
@@ -3737,7 +3737,7 @@
       <c r="H55" s="30"/>
       <c r="I55" s="32" t="n">
         <f aca="false">$I$53</f>
-        <v>-213.4</v>
+        <v>291.59</v>
       </c>
       <c r="J55" s="30"/>
       <c r="K55" s="26" t="str">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="I57" s="37" t="n">
         <f aca="false">IF($B57="","",$I$55+SUM($H$57:$H57))</f>
-        <v>576.6</v>
+        <v>1081.59</v>
       </c>
       <c r="J57" s="38" t="str">
         <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3837,7 +3837,7 @@
       </c>
       <c r="I58" s="37" t="n">
         <f aca="false">IF($B58="","",$I$55+SUM($H$57:$H58))</f>
-        <v>562.9</v>
+        <v>1067.89</v>
       </c>
       <c r="J58" s="38" t="str">
         <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="I59" s="37" t="n">
         <f aca="false">IF($B59="","",$I$55+SUM($H$57:$H59))</f>
-        <v>519.03</v>
+        <v>1024.02</v>
       </c>
       <c r="J59" s="38" t="str">
         <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="I60" s="37" t="n">
         <f aca="false">IF($B60="","",$I$55+SUM($H$57:$H60))</f>
-        <v>609.03</v>
+        <v>1114.02</v>
       </c>
       <c r="J60" s="38" t="str">
         <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="I74" s="44" t="n">
         <f aca="false">$I$55+SUM($H$57:$H$73)</f>
-        <v>609.03</v>
+        <v>1114.02</v>
       </c>
       <c r="J74" s="45" t="str">
         <f aca="false">IF($I$74&lt;0,"SHORTFALL",IF($I$74&lt;$E$7,"TIGHT","OK"))</f>
@@ -4325,7 +4325,7 @@
       <c r="H76" s="30"/>
       <c r="I76" s="32" t="n">
         <f aca="false">$I$74</f>
-        <v>609.03</v>
+        <v>1114.02</v>
       </c>
       <c r="J76" s="30"/>
       <c r="K76" s="26" t="str">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="I78" s="37" t="n">
         <f aca="false">IF($B78="","",$I$76+SUM($H$78:$H78))</f>
-        <v>1399.03</v>
+        <v>1904.02</v>
       </c>
       <c r="J78" s="38" t="str">
         <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4425,7 +4425,7 @@
       </c>
       <c r="I79" s="37" t="n">
         <f aca="false">IF($B79="","",$I$76+SUM($H$78:$H79))</f>
-        <v>1249.03</v>
+        <v>1754.02</v>
       </c>
       <c r="J79" s="38" t="str">
         <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="I80" s="37" t="n">
         <f aca="false">IF($B80="","",$I$76+SUM($H$78:$H80))</f>
-        <v>899.03</v>
+        <v>1404.02</v>
       </c>
       <c r="J80" s="38" t="str">
         <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="I81" s="37" t="n">
         <f aca="false">IF($B81="","",$I$76+SUM($H$78:$H81))</f>
-        <v>755.66</v>
+        <v>1260.65</v>
       </c>
       <c r="J81" s="38" t="str">
         <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4530,7 +4530,7 @@
       </c>
       <c r="I82" s="37" t="n">
         <f aca="false">IF($B82="","",$I$76+SUM($H$78:$H82))</f>
-        <v>845.66</v>
+        <v>1350.65</v>
       </c>
       <c r="J82" s="38" t="str">
         <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4887,7 +4887,7 @@
       </c>
       <c r="I95" s="44" t="n">
         <f aca="false">$I$76+SUM($H$78:$H$94)</f>
-        <v>845.66</v>
+        <v>1350.65</v>
       </c>
       <c r="J95" s="45" t="str">
         <f aca="false">IF($I$95&lt;0,"SHORTFALL",IF($I$95&lt;$E$7,"TIGHT","OK"))</f>
@@ -4913,7 +4913,7 @@
       <c r="H97" s="30"/>
       <c r="I97" s="32" t="n">
         <f aca="false">$I$95</f>
-        <v>845.66</v>
+        <v>1350.65</v>
       </c>
       <c r="J97" s="30"/>
       <c r="K97" s="26" t="str">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="I99" s="37" t="n">
         <f aca="false">IF($B99="","",$I$97+SUM($H$99:$H99))</f>
-        <v>1635.66</v>
+        <v>2140.65</v>
       </c>
       <c r="J99" s="38" t="str">
         <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5013,7 +5013,7 @@
       </c>
       <c r="I100" s="37" t="n">
         <f aca="false">IF($B100="","",$I$97+SUM($H$99:$H100))</f>
-        <v>1614.56</v>
+        <v>2119.55</v>
       </c>
       <c r="J100" s="38" t="str">
         <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="I101" s="37" t="n">
         <f aca="false">IF($B101="","",$I$97+SUM($H$99:$H101))</f>
-        <v>1594.56</v>
+        <v>2099.55</v>
       </c>
       <c r="J101" s="38" t="str">
         <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="I102" s="37" t="n">
         <f aca="false">IF($B102="","",$I$97+SUM($H$99:$H102))</f>
-        <v>1584.56</v>
+        <v>2089.55</v>
       </c>
       <c r="J102" s="38" t="str">
         <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="I103" s="37" t="n">
         <f aca="false">IF($B103="","",$I$97+SUM($H$99:$H103))</f>
-        <v>1579.57</v>
+        <v>2084.56</v>
       </c>
       <c r="J103" s="38" t="str">
         <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="I104" s="37" t="n">
         <f aca="false">IF($B104="","",$I$97+SUM($H$99:$H104))</f>
-        <v>1079.57</v>
+        <v>1584.56</v>
       </c>
       <c r="J104" s="38" t="str">
         <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="I105" s="37" t="n">
         <f aca="false">IF($B105="","",$I$97+SUM($H$99:$H105))</f>
-        <v>1169.57</v>
+        <v>1674.56</v>
       </c>
       <c r="J105" s="38" t="str">
         <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I106" s="37" t="n">
         <f aca="false">IF($B106="","",$I$97+SUM($H$99:$H106))</f>
-        <v>1006.07</v>
+        <v>1511.06</v>
       </c>
       <c r="J106" s="38" t="str">
         <f aca="true">IF($B106="","",IF($F106&lt;&gt;"","PAID",IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="I116" s="44" t="n">
         <f aca="false">$I$97+SUM($H$99:$H$115)</f>
-        <v>1006.07</v>
+        <v>1511.06</v>
       </c>
       <c r="J116" s="45" t="str">
         <f aca="false">IF($I$116&lt;0,"SHORTFALL",IF($I$116&lt;$E$7,"TIGHT","OK"))</f>
@@ -5501,7 +5501,7 @@
       <c r="H118" s="30"/>
       <c r="I118" s="32" t="n">
         <f aca="false">$I$116</f>
-        <v>1006.07</v>
+        <v>1511.06</v>
       </c>
       <c r="J118" s="30"/>
       <c r="K118" s="26" t="str">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="I120" s="37" t="n">
         <f aca="false">IF($B120="","",$I$118+SUM($H$120:$H120))</f>
-        <v>1796.07</v>
+        <v>2301.06</v>
       </c>
       <c r="J120" s="38" t="str">
         <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="I121" s="37" t="n">
         <f aca="false">IF($B121="","",$I$118+SUM($H$120:$H121))</f>
-        <v>1793.08</v>
+        <v>2298.07</v>
       </c>
       <c r="J121" s="38" t="str">
         <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5636,7 +5636,7 @@
       </c>
       <c r="I122" s="37" t="n">
         <f aca="false">IF($B122="","",$I$118+SUM($H$120:$H122))</f>
-        <v>1443.08</v>
+        <v>1948.07</v>
       </c>
       <c r="J122" s="38" t="str">
         <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="I123" s="37" t="n">
         <f aca="false">IF($B123="","",$I$118+SUM($H$120:$H123))</f>
-        <v>1533.08</v>
+        <v>2038.07</v>
       </c>
       <c r="J123" s="38" t="str">
         <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5706,7 +5706,7 @@
       </c>
       <c r="I124" s="37" t="n">
         <f aca="false">IF($B124="","",$I$118+SUM($H$120:$H124))</f>
-        <v>1361.98</v>
+        <v>1866.97</v>
       </c>
       <c r="J124" s="38" t="str">
         <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="I125" s="37" t="n">
         <f aca="false">IF($B125="","",$I$118+SUM($H$120:$H125))</f>
-        <v>1316.98</v>
+        <v>1821.97</v>
       </c>
       <c r="J125" s="38" t="str">
         <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6063,7 +6063,7 @@
       </c>
       <c r="I137" s="44" t="n">
         <f aca="false">$I$118+SUM($H$120:$H$136)</f>
-        <v>1316.98</v>
+        <v>1821.97</v>
       </c>
       <c r="J137" s="45" t="str">
         <f aca="false">IF($I$137&lt;0,"SHORTFALL",IF($I$137&lt;$E$7,"TIGHT","OK"))</f>
@@ -6089,7 +6089,7 @@
       <c r="H139" s="30"/>
       <c r="I139" s="32" t="n">
         <f aca="false">$I$137</f>
-        <v>1316.98</v>
+        <v>1821.97</v>
       </c>
       <c r="J139" s="30"/>
       <c r="K139" s="26" t="str">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="I141" s="37" t="n">
         <f aca="false">IF($B141="","",$I$139+SUM($H$141:$H141))</f>
-        <v>2106.98</v>
+        <v>2611.97</v>
       </c>
       <c r="J141" s="38" t="str">
         <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="I142" s="37" t="n">
         <f aca="false">IF($B142="","",$I$139+SUM($H$141:$H142))</f>
-        <v>2089.99</v>
+        <v>2594.98</v>
       </c>
       <c r="J142" s="38" t="str">
         <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6224,7 +6224,7 @@
       </c>
       <c r="I143" s="37" t="n">
         <f aca="false">IF($B143="","",$I$139+SUM($H$141:$H143))</f>
-        <v>2179.99</v>
+        <v>2684.98</v>
       </c>
       <c r="J143" s="38" t="str">
         <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="I158" s="44" t="n">
         <f aca="false">$I$139+SUM($H$141:$H$157)</f>
-        <v>2179.99</v>
+        <v>2684.98</v>
       </c>
       <c r="J158" s="45" t="str">
         <f aca="false">IF($I$158&lt;0,"SHORTFALL",IF($I$158&lt;$E$7,"TIGHT","OK"))</f>
@@ -6677,7 +6677,7 @@
       <c r="H160" s="30"/>
       <c r="I160" s="32" t="n">
         <f aca="false">$I$158</f>
-        <v>2179.99</v>
+        <v>2684.98</v>
       </c>
       <c r="J160" s="30"/>
       <c r="K160" s="26" t="str">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="I162" s="37" t="n">
         <f aca="false">IF($B162="","",$I$160+SUM($H$162:$H162))</f>
-        <v>2969.99</v>
+        <v>3474.98</v>
       </c>
       <c r="J162" s="38" t="str">
         <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="I163" s="37" t="n">
         <f aca="false">IF($B163="","",$I$160+SUM($H$162:$H163))</f>
-        <v>2956.29</v>
+        <v>3461.28</v>
       </c>
       <c r="J163" s="38" t="str">
         <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6812,7 +6812,7 @@
       </c>
       <c r="I164" s="37" t="n">
         <f aca="false">IF($B164="","",$I$160+SUM($H$162:$H164))</f>
-        <v>2912.42</v>
+        <v>3417.41</v>
       </c>
       <c r="J164" s="38" t="str">
         <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="I165" s="37" t="n">
         <f aca="false">IF($B165="","",$I$160+SUM($H$162:$H165))</f>
-        <v>3002.42</v>
+        <v>3507.41</v>
       </c>
       <c r="J165" s="38" t="str">
         <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="I166" s="37" t="n">
         <f aca="false">IF($B166="","",$I$160+SUM($H$162:$H166))</f>
-        <v>2652.42</v>
+        <v>3157.41</v>
       </c>
       <c r="J166" s="38" t="str">
         <f aca="true">IF($B166="","",IF($F166&lt;&gt;"","PAID",IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="I167" s="37" t="n">
         <f aca="false">IF($B167="","",$I$160+SUM($H$162:$H167))</f>
-        <v>2502.42</v>
+        <v>3007.41</v>
       </c>
       <c r="J167" s="38" t="str">
         <f aca="true">IF($B167="","",IF($F167&lt;&gt;"","PAID",IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="I168" s="37" t="n">
         <f aca="false">IF($B168="","",$I$160+SUM($H$162:$H168))</f>
-        <v>2359.05</v>
+        <v>2864.04</v>
       </c>
       <c r="J168" s="38" t="str">
         <f aca="true">IF($B168="","",IF($F168&lt;&gt;"","PAID",IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="I179" s="44" t="n">
         <f aca="false">$I$160+SUM($H$162:$H$178)</f>
-        <v>2359.05</v>
+        <v>2864.04</v>
       </c>
       <c r="J179" s="45" t="str">
         <f aca="false">IF($I$179&lt;0,"SHORTFALL",IF($I$179&lt;$E$7,"TIGHT","OK"))</f>
@@ -7265,7 +7265,7 @@
       <c r="H181" s="30"/>
       <c r="I181" s="32" t="n">
         <f aca="false">$I$179</f>
-        <v>2359.05</v>
+        <v>2864.04</v>
       </c>
       <c r="J181" s="30"/>
       <c r="K181" s="26" t="str">
@@ -7330,7 +7330,7 @@
       </c>
       <c r="I183" s="37" t="n">
         <f aca="false">IF($B183="","",$I$181+SUM($H$183:$H183))</f>
-        <v>3149.05</v>
+        <v>3654.04</v>
       </c>
       <c r="J183" s="38" t="str">
         <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="I184" s="37" t="n">
         <f aca="false">IF($B184="","",$I$181+SUM($H$183:$H184))</f>
-        <v>3127.95</v>
+        <v>3632.94</v>
       </c>
       <c r="J184" s="38" t="str">
         <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="I185" s="37" t="n">
         <f aca="false">IF($B185="","",$I$181+SUM($H$183:$H185))</f>
-        <v>3107.95</v>
+        <v>3612.94</v>
       </c>
       <c r="J185" s="38" t="str">
         <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7435,7 +7435,7 @@
       </c>
       <c r="I186" s="37" t="n">
         <f aca="false">IF($B186="","",$I$181+SUM($H$183:$H186))</f>
-        <v>3097.95</v>
+        <v>3602.94</v>
       </c>
       <c r="J186" s="38" t="str">
         <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="I187" s="37" t="n">
         <f aca="false">IF($B187="","",$I$181+SUM($H$183:$H187))</f>
-        <v>3187.95</v>
+        <v>3692.94</v>
       </c>
       <c r="J187" s="38" t="str">
         <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7505,7 +7505,7 @@
       </c>
       <c r="I188" s="37" t="n">
         <f aca="false">IF($B188="","",$I$181+SUM($H$183:$H188))</f>
-        <v>3182.96</v>
+        <v>3687.95</v>
       </c>
       <c r="J188" s="38" t="str">
         <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="I189" s="37" t="n">
         <f aca="false">IF($B189="","",$I$181+SUM($H$183:$H189))</f>
-        <v>2682.96</v>
+        <v>3187.95</v>
       </c>
       <c r="J189" s="38" t="str">
         <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="I200" s="44" t="n">
         <f aca="false">$I$181+SUM($H$183:$H$199)</f>
-        <v>2682.96</v>
+        <v>3187.95</v>
       </c>
       <c r="J200" s="45" t="str">
         <f aca="false">IF($I$200&lt;0,"SHORTFALL",IF($I$200&lt;$E$7,"TIGHT","OK"))</f>
@@ -7853,7 +7853,7 @@
       <c r="H202" s="30"/>
       <c r="I202" s="32" t="n">
         <f aca="false">$I$200</f>
-        <v>2682.96</v>
+        <v>3187.95</v>
       </c>
       <c r="J202" s="30"/>
       <c r="K202" s="26" t="str">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="I204" s="37" t="n">
         <f aca="false">IF($B204="","",$I$202+SUM($H$204:$H204))</f>
-        <v>3472.96</v>
+        <v>3977.95</v>
       </c>
       <c r="J204" s="38" t="str">
         <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7953,7 +7953,7 @@
       </c>
       <c r="I205" s="37" t="n">
         <f aca="false">IF($B205="","",$I$202+SUM($H$204:$H205))</f>
-        <v>3309.46</v>
+        <v>3814.45</v>
       </c>
       <c r="J205" s="38" t="str">
         <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="I206" s="37" t="n">
         <f aca="false">IF($B206="","",$I$202+SUM($H$204:$H206))</f>
-        <v>3306.47</v>
+        <v>3811.46</v>
       </c>
       <c r="J206" s="38" t="str">
         <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="I207" s="37" t="n">
         <f aca="false">IF($B207="","",$I$202+SUM($H$204:$H207))</f>
-        <v>3396.47</v>
+        <v>3901.46</v>
       </c>
       <c r="J207" s="38" t="str">
         <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8058,7 +8058,7 @@
       </c>
       <c r="I208" s="37" t="n">
         <f aca="false">IF($B208="","",$I$202+SUM($H$204:$H208))</f>
-        <v>3046.47</v>
+        <v>3551.46</v>
       </c>
       <c r="J208" s="38" t="str">
         <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="I221" s="44" t="n">
         <f aca="false">$I$202+SUM($H$204:$H$220)</f>
-        <v>3046.47</v>
+        <v>3551.46</v>
       </c>
       <c r="J221" s="45" t="str">
         <f aca="false">IF($I$221&lt;0,"SHORTFALL",IF($I$221&lt;$E$7,"TIGHT","OK"))</f>
@@ -8441,7 +8441,7 @@
       <c r="H223" s="30"/>
       <c r="I223" s="32" t="n">
         <f aca="false">$I$221</f>
-        <v>3046.47</v>
+        <v>3551.46</v>
       </c>
       <c r="J223" s="30"/>
       <c r="K223" s="26" t="str">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="I225" s="37" t="n">
         <f aca="false">IF($B225="","",$I$223+SUM($H$225:$H225))</f>
-        <v>3836.47</v>
+        <v>4341.46</v>
       </c>
       <c r="J225" s="38" t="str">
         <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I226" s="37" t="n">
         <f aca="false">IF($B226="","",$I$223+SUM($H$225:$H226))</f>
-        <v>3665.37</v>
+        <v>4170.36</v>
       </c>
       <c r="J226" s="38" t="str">
         <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="I227" s="37" t="n">
         <f aca="false">IF($B227="","",$I$223+SUM($H$225:$H227))</f>
-        <v>3620.37</v>
+        <v>4125.36</v>
       </c>
       <c r="J227" s="38" t="str">
         <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="I228" s="37" t="n">
         <f aca="false">IF($B228="","",$I$223+SUM($H$225:$H228))</f>
-        <v>3603.38</v>
+        <v>4108.37</v>
       </c>
       <c r="J228" s="38" t="str">
         <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="I229" s="37" t="n">
         <f aca="false">IF($B229="","",$I$223+SUM($H$225:$H229))</f>
-        <v>3693.38</v>
+        <v>4198.37</v>
       </c>
       <c r="J229" s="38" t="str">
         <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="I242" s="44" t="n">
         <f aca="false">$I$223+SUM($H$225:$H$241)</f>
-        <v>3693.38</v>
+        <v>4198.37</v>
       </c>
       <c r="J242" s="45" t="str">
         <f aca="false">IF($I$242&lt;0,"SHORTFALL",IF($I$242&lt;$E$7,"TIGHT","OK"))</f>
@@ -9029,7 +9029,7 @@
       <c r="H244" s="30"/>
       <c r="I244" s="32" t="n">
         <f aca="false">$I$242</f>
-        <v>3693.38</v>
+        <v>4198.37</v>
       </c>
       <c r="J244" s="30"/>
       <c r="K244" s="26" t="str">
@@ -9094,7 +9094,7 @@
       </c>
       <c r="I246" s="37" t="n">
         <f aca="false">IF($B246="","",$I$244+SUM($H$246:$H246))</f>
-        <v>4483.38</v>
+        <v>4988.37</v>
       </c>
       <c r="J246" s="38" t="str">
         <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9129,7 +9129,7 @@
       </c>
       <c r="I247" s="37" t="n">
         <f aca="false">IF($B247="","",$I$244+SUM($H$246:$H247))</f>
-        <v>4469.68</v>
+        <v>4974.67</v>
       </c>
       <c r="J247" s="38" t="str">
         <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9164,7 +9164,7 @@
       </c>
       <c r="I248" s="37" t="n">
         <f aca="false">IF($B248="","",$I$244+SUM($H$246:$H248))</f>
-        <v>4425.81</v>
+        <v>4930.8</v>
       </c>
       <c r="J248" s="38" t="str">
         <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9199,7 +9199,7 @@
       </c>
       <c r="I249" s="37" t="n">
         <f aca="false">IF($B249="","",$I$244+SUM($H$246:$H249))</f>
-        <v>4515.81</v>
+        <v>5020.8</v>
       </c>
       <c r="J249" s="38" t="str">
         <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9591,7 +9591,7 @@
       </c>
       <c r="I263" s="44" t="n">
         <f aca="false">$I$244+SUM($H$246:$H$262)</f>
-        <v>4515.81</v>
+        <v>5020.8</v>
       </c>
       <c r="J263" s="45" t="str">
         <f aca="false">IF($I$263&lt;0,"SHORTFALL",IF($I$263&lt;$E$7,"TIGHT","OK"))</f>
@@ -9617,7 +9617,7 @@
       <c r="H265" s="30"/>
       <c r="I265" s="32" t="n">
         <f aca="false">$I$263</f>
-        <v>4515.81</v>
+        <v>5020.8</v>
       </c>
       <c r="J265" s="30"/>
       <c r="K265" s="26" t="str">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="I267" s="37" t="n">
         <f aca="false">IF($B267="","",$I$265+SUM($H$267:$H267))</f>
-        <v>5305.81</v>
+        <v>5810.8</v>
       </c>
       <c r="J267" s="38" t="str">
         <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9717,7 +9717,7 @@
       </c>
       <c r="I268" s="37" t="n">
         <f aca="false">IF($B268="","",$I$265+SUM($H$267:$H268))</f>
-        <v>4955.81</v>
+        <v>5460.8</v>
       </c>
       <c r="J268" s="38" t="str">
         <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="I269" s="37" t="n">
         <f aca="false">IF($B269="","",$I$265+SUM($H$267:$H269))</f>
-        <v>4805.81</v>
+        <v>5310.8</v>
       </c>
       <c r="J269" s="38" t="str">
         <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="I270" s="37" t="n">
         <f aca="false">IF($B270="","",$I$265+SUM($H$267:$H270))</f>
-        <v>4662.44</v>
+        <v>5167.43</v>
       </c>
       <c r="J270" s="38" t="str">
         <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9822,7 +9822,7 @@
       </c>
       <c r="I271" s="37" t="n">
         <f aca="false">IF($B271="","",$I$265+SUM($H$267:$H271))</f>
-        <v>4752.44</v>
+        <v>5257.43</v>
       </c>
       <c r="J271" s="38" t="str">
         <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9857,7 +9857,7 @@
       </c>
       <c r="I272" s="37" t="n">
         <f aca="false">IF($B272="","",$I$265+SUM($H$267:$H272))</f>
-        <v>4731.34</v>
+        <v>5236.33</v>
       </c>
       <c r="J272" s="38" t="str">
         <f aca="true">IF($B272="","",IF($F272&lt;&gt;"","PAID",IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="I273" s="37" t="n">
         <f aca="false">IF($B273="","",$I$265+SUM($H$267:$H273))</f>
-        <v>4711.34</v>
+        <v>5216.33</v>
       </c>
       <c r="J273" s="38" t="str">
         <f aca="true">IF($B273="","",IF($F273&lt;&gt;"","PAID",IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="I274" s="37" t="n">
         <f aca="false">IF($B274="","",$I$265+SUM($H$267:$H274))</f>
-        <v>4701.34</v>
+        <v>5206.33</v>
       </c>
       <c r="J274" s="38" t="str">
         <f aca="true">IF($B274="","",IF($F274&lt;&gt;"","PAID",IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="I284" s="44" t="n">
         <f aca="false">$I$265+SUM($H$267:$H$283)</f>
-        <v>4701.34</v>
+        <v>5206.33</v>
       </c>
       <c r="J284" s="45" t="str">
         <f aca="false">IF($I$284&lt;0,"SHORTFALL",IF($I$284&lt;$E$7,"TIGHT","OK"))</f>
@@ -10260,7 +10260,7 @@
       <c r="D4" s="46"/>
       <c r="E4" s="47" t="n">
         <f aca="false">MIN($I$13:$I$25)</f>
-        <v>-510.31</v>
+        <v>-5.31999999999999</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10312,7 +10312,7 @@
       <c r="D8" s="46"/>
       <c r="E8" s="49" t="n">
         <f aca="false">SUM($F$13:$F$25)+SUM($G$13:$G$25)</f>
-        <v>6019.83</v>
+        <v>5514.84</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10323,7 +10323,7 @@
       <c r="D9" s="46"/>
       <c r="E9" s="47" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>4630.17</v>
+        <v>5135.16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10334,7 +10334,7 @@
       <c r="D10" s="46"/>
       <c r="E10" s="47" t="n">
         <f aca="false">$I$25</f>
-        <v>4701.34</v>
+        <v>5206.33</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="F13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$15:$D$24,"Expense",'Cash Flow'!$G$15:$G$24)</f>
-        <v>671.48</v>
+        <v>166.49</v>
       </c>
       <c r="G13" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$26:$D$31,"Expense",'Cash Flow'!$G$26:$G$31)</f>
@@ -10395,11 +10395,11 @@
       </c>
       <c r="H13" s="53" t="n">
         <f aca="false">$E13-$F13-$G13</f>
-        <v>-581.48</v>
+        <v>-76.49</v>
       </c>
       <c r="I13" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$32</f>
-        <v>-510.31</v>
+        <v>-5.31999999999999</v>
       </c>
       <c r="J13" s="54" t="str">
         <f aca="false">IF($I13&lt;0,"SHORTFALL",IF($I13&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10420,7 +10420,7 @@
       </c>
       <c r="D14" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$34</f>
-        <v>-510.31</v>
+        <v>-5.31999999999999</v>
       </c>
       <c r="E14" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$36:$D$45,"Income",'Cash Flow'!$G$36:$G$45)</f>
@@ -10440,15 +10440,15 @@
       </c>
       <c r="I14" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$53</f>
-        <v>-213.4</v>
+        <v>291.59</v>
       </c>
       <c r="J14" s="59" t="str">
         <f aca="false">IF($I14&lt;0,"SHORTFALL",IF($I14&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
-        <v>SHORTFALL</v>
+        <v>OK</v>
       </c>
       <c r="K14" s="27" t="n">
         <f aca="false">IF($I14&lt;0,$B14,999)</f>
-        <v>2</v>
+        <v>999</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$55</f>
-        <v>-213.4</v>
+        <v>291.59</v>
       </c>
       <c r="E15" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$57:$D$66,"Income",'Cash Flow'!$G$57:$G$66)</f>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="I15" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$74</f>
-        <v>609.03</v>
+        <v>1114.02</v>
       </c>
       <c r="J15" s="54" t="str">
         <f aca="false">IF($I15&lt;0,"SHORTFALL",IF($I15&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="D16" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$76</f>
-        <v>609.03</v>
+        <v>1114.02</v>
       </c>
       <c r="E16" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$78:$D$87,"Income",'Cash Flow'!$G$78:$G$87)</f>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="I16" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$95</f>
-        <v>845.66</v>
+        <v>1350.65</v>
       </c>
       <c r="J16" s="59" t="str">
         <f aca="false">IF($I16&lt;0,"SHORTFALL",IF($I16&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10543,7 +10543,7 @@
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$97</f>
-        <v>845.66</v>
+        <v>1350.65</v>
       </c>
       <c r="E17" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$99:$D$108,"Income",'Cash Flow'!$G$99:$G$108)</f>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="I17" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$116</f>
-        <v>1006.07</v>
+        <v>1511.06</v>
       </c>
       <c r="J17" s="54" t="str">
         <f aca="false">IF($I17&lt;0,"SHORTFALL",IF($I17&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="D18" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$118</f>
-        <v>1006.07</v>
+        <v>1511.06</v>
       </c>
       <c r="E18" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$120:$D$129,"Income",'Cash Flow'!$G$120:$G$129)</f>
@@ -10604,7 +10604,7 @@
       </c>
       <c r="I18" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$137</f>
-        <v>1316.98</v>
+        <v>1821.97</v>
       </c>
       <c r="J18" s="59" t="str">
         <f aca="false">IF($I18&lt;0,"SHORTFALL",IF($I18&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10625,7 +10625,7 @@
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$139</f>
-        <v>1316.98</v>
+        <v>1821.97</v>
       </c>
       <c r="E19" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$141:$D$150,"Income",'Cash Flow'!$G$141:$G$150)</f>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="I19" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$158</f>
-        <v>2179.99</v>
+        <v>2684.98</v>
       </c>
       <c r="J19" s="54" t="str">
         <f aca="false">IF($I19&lt;0,"SHORTFALL",IF($I19&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D20" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$160</f>
-        <v>2179.99</v>
+        <v>2684.98</v>
       </c>
       <c r="E20" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$162:$D$171,"Income",'Cash Flow'!$G$162:$G$171)</f>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="I20" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$179</f>
-        <v>2359.05</v>
+        <v>2864.04</v>
       </c>
       <c r="J20" s="59" t="str">
         <f aca="false">IF($I20&lt;0,"SHORTFALL",IF($I20&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$181</f>
-        <v>2359.05</v>
+        <v>2864.04</v>
       </c>
       <c r="E21" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$183:$D$192,"Income",'Cash Flow'!$G$183:$G$192)</f>
@@ -10727,7 +10727,7 @@
       </c>
       <c r="I21" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$200</f>
-        <v>2682.96</v>
+        <v>3187.95</v>
       </c>
       <c r="J21" s="54" t="str">
         <f aca="false">IF($I21&lt;0,"SHORTFALL",IF($I21&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10748,7 +10748,7 @@
       </c>
       <c r="D22" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$202</f>
-        <v>2682.96</v>
+        <v>3187.95</v>
       </c>
       <c r="E22" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$204:$D$213,"Income",'Cash Flow'!$G$204:$G$213)</f>
@@ -10768,7 +10768,7 @@
       </c>
       <c r="I22" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$221</f>
-        <v>3046.47</v>
+        <v>3551.46</v>
       </c>
       <c r="J22" s="59" t="str">
         <f aca="false">IF($I22&lt;0,"SHORTFALL",IF($I22&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$223</f>
-        <v>3046.47</v>
+        <v>3551.46</v>
       </c>
       <c r="E23" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$225:$D$234,"Income",'Cash Flow'!$G$225:$G$234)</f>
@@ -10809,7 +10809,7 @@
       </c>
       <c r="I23" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$242</f>
-        <v>3693.38</v>
+        <v>4198.37</v>
       </c>
       <c r="J23" s="54" t="str">
         <f aca="false">IF($I23&lt;0,"SHORTFALL",IF($I23&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10830,7 +10830,7 @@
       </c>
       <c r="D24" s="56" t="n">
         <f aca="false">'Cash Flow'!$I$244</f>
-        <v>3693.38</v>
+        <v>4198.37</v>
       </c>
       <c r="E24" s="57" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$246:$D$255,"Income",'Cash Flow'!$G$246:$G$255)</f>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="I24" s="58" t="n">
         <f aca="false">'Cash Flow'!$I$263</f>
-        <v>4515.81</v>
+        <v>5020.8</v>
       </c>
       <c r="J24" s="59" t="str">
         <f aca="false">IF($I24&lt;0,"SHORTFALL",IF($I24&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">'Cash Flow'!$I$265</f>
-        <v>4515.81</v>
+        <v>5020.8</v>
       </c>
       <c r="E25" s="52" t="n">
         <f aca="false">SUMIF('Cash Flow'!$D$267:$D$276,"Income",'Cash Flow'!$G$267:$G$276)</f>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="I25" s="53" t="n">
         <f aca="false">'Cash Flow'!$I$284</f>
-        <v>4701.34</v>
+        <v>5206.33</v>
       </c>
       <c r="J25" s="54" t="str">
         <f aca="false">IF($I25&lt;0,"SHORTFALL",IF($I25&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10919,7 +10919,7 @@
       </c>
       <c r="F26" s="43" t="n">
         <f aca="false">SUM($F$13:$F$25)</f>
-        <v>6019.83</v>
+        <v>5514.84</v>
       </c>
       <c r="G26" s="43" t="n">
         <f aca="false">SUM($G$13:$G$25)</f>
@@ -10927,11 +10927,11 @@
       </c>
       <c r="H26" s="61" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>4630.17</v>
+        <v>5135.16</v>
       </c>
       <c r="I26" s="61" t="n">
         <f aca="false">$I$25</f>
-        <v>4701.34</v>
+        <v>5206.33</v>
       </c>
       <c r="J26" s="42"/>
     </row>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="K4" s="66" t="n">
         <f aca="false">IF($H4=1,$I4*1000+COUNTIFS($I$4:$I$483,$I4,$J$4:$J$483,"&lt;"&amp;$J4)+1,"")</f>
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14591,11 +14591,11 @@
       </c>
       <c r="F84" s="68" t="n">
         <f aca="false">IF($C84="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*0,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*0,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,0),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$10="One Time",IF(1=1,Recurring!$F$10,""),""))))))</f>
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="G84" s="68" t="n">
         <f aca="false">IF($F84="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F84,2)=6,$F84-1,IF(WEEKDAY($F84,2)=7,$F84-2,$F84)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F84,2)=6,$F84+2,IF(WEEKDAY($F84,2)=7,$F84+1,$F84)),$F84)))</f>
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="H84" s="69" t="n">
         <f aca="false">IF($G84="",0,IF(AND($G84&gt;='Cash Flow'!$E$6,$G84&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14603,15 +14603,15 @@
       </c>
       <c r="I84" s="69" t="n">
         <f aca="false">IF($H84=1,INT(($G84-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J84" s="66" t="n">
         <f aca="false">IF($H84=1,$G84*10000+ROW(),"")</f>
-        <v>462410084</v>
+        <v>462720084</v>
       </c>
       <c r="K84" s="66" t="n">
         <f aca="false">IF($H84=1,$I84*1000+COUNTIFS($I$4:$I$483,$I84,$J$4:$J$483,"&lt;"&amp;$J84)+1,"")</f>
-        <v>1001</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14635,11 +14635,11 @@
       </c>
       <c r="F85" s="68" t="n">
         <f aca="false">IF($C85="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*1,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*1,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,1),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$10="One Time",IF(2=1,Recurring!$F$10,""),""))))))</f>
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="G85" s="68" t="n">
         <f aca="false">IF($F85="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F85,2)=6,$F85-1,IF(WEEKDAY($F85,2)=7,$F85-2,$F85)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F85,2)=6,$F85+2,IF(WEEKDAY($F85,2)=7,$F85+1,$F85)),$F85)))</f>
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="H85" s="69" t="n">
         <f aca="false">IF($G85="",0,IF(AND($G85&gt;='Cash Flow'!$E$6,$G85&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14647,15 +14647,15 @@
       </c>
       <c r="I85" s="69" t="n">
         <f aca="false">IF($H85=1,INT(($G85-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J85" s="66" t="n">
         <f aca="false">IF($H85=1,$G85*10000+ROW(),"")</f>
-        <v>462720085</v>
+        <v>463020085</v>
       </c>
       <c r="K85" s="66" t="n">
         <f aca="false">IF($H85=1,$I85*1000+COUNTIFS($I$4:$I$483,$I85,$J$4:$J$483,"&lt;"&amp;$J85)+1,"")</f>
-        <v>5005</v>
+        <v>9006</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14679,27 +14679,27 @@
       </c>
       <c r="F86" s="68" t="n">
         <f aca="false">IF($C86="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*2,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*2,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,2),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$10="One Time",IF(3=1,Recurring!$F$10,""),""))))))</f>
-        <v>46302</v>
+        <v>46333</v>
       </c>
       <c r="G86" s="68" t="n">
         <f aca="false">IF($F86="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F86,2)=6,$F86-1,IF(WEEKDAY($F86,2)=7,$F86-2,$F86)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F86,2)=6,$F86+2,IF(WEEKDAY($F86,2)=7,$F86+1,$F86)),$F86)))</f>
-        <v>46302</v>
+        <v>46333</v>
       </c>
       <c r="H86" s="69" t="n">
         <f aca="false">IF($G86="",0,IF(AND($G86&gt;='Cash Flow'!$E$6,$G86&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I86" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="69" t="str">
         <f aca="false">IF($H86=1,INT(($G86-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
-      </c>
-      <c r="J86" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J86" s="66" t="str">
         <f aca="false">IF($H86=1,$G86*10000+ROW(),"")</f>
-        <v>463020086</v>
-      </c>
-      <c r="K86" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K86" s="66" t="str">
         <f aca="false">IF($H86=1,$I86*1000+COUNTIFS($I$4:$I$483,$I86,$J$4:$J$483,"&lt;"&amp;$J86)+1,"")</f>
-        <v>9006</v>
+        <v/>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14723,11 +14723,11 @@
       </c>
       <c r="F87" s="68" t="n">
         <f aca="false">IF($C87="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*3,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*3,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,3),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$10="One Time",IF(4=1,Recurring!$F$10,""),""))))))</f>
-        <v>46333</v>
+        <v>46363</v>
       </c>
       <c r="G87" s="68" t="n">
         <f aca="false">IF($F87="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F87,2)=6,$F87-1,IF(WEEKDAY($F87,2)=7,$F87-2,$F87)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F87,2)=6,$F87+2,IF(WEEKDAY($F87,2)=7,$F87+1,$F87)),$F87)))</f>
-        <v>46333</v>
+        <v>46363</v>
       </c>
       <c r="H87" s="69" t="n">
         <f aca="false">IF($G87="",0,IF(AND($G87&gt;='Cash Flow'!$E$6,$G87&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14767,11 +14767,11 @@
       </c>
       <c r="F88" s="68" t="n">
         <f aca="false">IF($C88="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*4,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*4,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,4),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$10="One Time",IF(5=1,Recurring!$F$10,""),""))))))</f>
-        <v>46363</v>
+        <v>46394</v>
       </c>
       <c r="G88" s="68" t="n">
         <f aca="false">IF($F88="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F88,2)=6,$F88-1,IF(WEEKDAY($F88,2)=7,$F88-2,$F88)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F88,2)=6,$F88+2,IF(WEEKDAY($F88,2)=7,$F88+1,$F88)),$F88)))</f>
-        <v>46363</v>
+        <v>46394</v>
       </c>
       <c r="H88" s="69" t="n">
         <f aca="false">IF($G88="",0,IF(AND($G88&gt;='Cash Flow'!$E$6,$G88&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14811,11 +14811,11 @@
       </c>
       <c r="F89" s="68" t="n">
         <f aca="false">IF($C89="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*5,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*5,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,5),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$10="One Time",IF(6=1,Recurring!$F$10,""),""))))))</f>
-        <v>46394</v>
+        <v>46425</v>
       </c>
       <c r="G89" s="68" t="n">
         <f aca="false">IF($F89="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F89,2)=6,$F89-1,IF(WEEKDAY($F89,2)=7,$F89-2,$F89)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F89,2)=6,$F89+2,IF(WEEKDAY($F89,2)=7,$F89+1,$F89)),$F89)))</f>
-        <v>46394</v>
+        <v>46425</v>
       </c>
       <c r="H89" s="69" t="n">
         <f aca="false">IF($G89="",0,IF(AND($G89&gt;='Cash Flow'!$E$6,$G89&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14855,11 +14855,11 @@
       </c>
       <c r="F90" s="68" t="n">
         <f aca="false">IF($C90="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*6,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*6,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,6),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$10="One Time",IF(7=1,Recurring!$F$10,""),""))))))</f>
-        <v>46425</v>
+        <v>46453</v>
       </c>
       <c r="G90" s="68" t="n">
         <f aca="false">IF($F90="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F90,2)=6,$F90-1,IF(WEEKDAY($F90,2)=7,$F90-2,$F90)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F90,2)=6,$F90+2,IF(WEEKDAY($F90,2)=7,$F90+1,$F90)),$F90)))</f>
-        <v>46425</v>
+        <v>46453</v>
       </c>
       <c r="H90" s="69" t="n">
         <f aca="false">IF($G90="",0,IF(AND($G90&gt;='Cash Flow'!$E$6,$G90&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14899,11 +14899,11 @@
       </c>
       <c r="F91" s="68" t="n">
         <f aca="false">IF($C91="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*7,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*7,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,7),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$10="One Time",IF(8=1,Recurring!$F$10,""),""))))))</f>
-        <v>46453</v>
+        <v>46484</v>
       </c>
       <c r="G91" s="68" t="n">
         <f aca="false">IF($F91="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F91,2)=6,$F91-1,IF(WEEKDAY($F91,2)=7,$F91-2,$F91)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F91,2)=6,$F91+2,IF(WEEKDAY($F91,2)=7,$F91+1,$F91)),$F91)))</f>
-        <v>46453</v>
+        <v>46484</v>
       </c>
       <c r="H91" s="69" t="n">
         <f aca="false">IF($G91="",0,IF(AND($G91&gt;='Cash Flow'!$E$6,$G91&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14943,11 +14943,11 @@
       </c>
       <c r="F92" s="68" t="n">
         <f aca="false">IF($C92="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*8,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*8,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,8),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$10="One Time",IF(9=1,Recurring!$F$10,""),""))))))</f>
-        <v>46484</v>
+        <v>46514</v>
       </c>
       <c r="G92" s="68" t="n">
         <f aca="false">IF($F92="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F92,2)=6,$F92-1,IF(WEEKDAY($F92,2)=7,$F92-2,$F92)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F92,2)=6,$F92+2,IF(WEEKDAY($F92,2)=7,$F92+1,$F92)),$F92)))</f>
-        <v>46484</v>
+        <v>46514</v>
       </c>
       <c r="H92" s="69" t="n">
         <f aca="false">IF($G92="",0,IF(AND($G92&gt;='Cash Flow'!$E$6,$G92&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -14987,11 +14987,11 @@
       </c>
       <c r="F93" s="68" t="n">
         <f aca="false">IF($C93="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*9,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*9,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,9),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$10="One Time",IF(10=1,Recurring!$F$10,""),""))))))</f>
-        <v>46514</v>
+        <v>46545</v>
       </c>
       <c r="G93" s="68" t="n">
         <f aca="false">IF($F93="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F93,2)=6,$F93-1,IF(WEEKDAY($F93,2)=7,$F93-2,$F93)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F93,2)=6,$F93+2,IF(WEEKDAY($F93,2)=7,$F93+1,$F93)),$F93)))</f>
-        <v>46514</v>
+        <v>46545</v>
       </c>
       <c r="H93" s="69" t="n">
         <f aca="false">IF($G93="",0,IF(AND($G93&gt;='Cash Flow'!$E$6,$G93&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15031,11 +15031,11 @@
       </c>
       <c r="F94" s="68" t="n">
         <f aca="false">IF($C94="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*10,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*10,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,10),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$10="One Time",IF(11=1,Recurring!$F$10,""),""))))))</f>
-        <v>46545</v>
+        <v>46575</v>
       </c>
       <c r="G94" s="68" t="n">
         <f aca="false">IF($F94="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F94,2)=6,$F94-1,IF(WEEKDAY($F94,2)=7,$F94-2,$F94)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F94,2)=6,$F94+2,IF(WEEKDAY($F94,2)=7,$F94+1,$F94)),$F94)))</f>
-        <v>46545</v>
+        <v>46575</v>
       </c>
       <c r="H94" s="69" t="n">
         <f aca="false">IF($G94="",0,IF(AND($G94&gt;='Cash Flow'!$E$6,$G94&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15075,11 +15075,11 @@
       </c>
       <c r="F95" s="68" t="n">
         <f aca="false">IF($C95="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*11,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*11,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,11),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$10="One Time",IF(12=1,Recurring!$F$10,""),""))))))</f>
-        <v>46575</v>
+        <v>46606</v>
       </c>
       <c r="G95" s="68" t="n">
         <f aca="false">IF($F95="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F95,2)=6,$F95-1,IF(WEEKDAY($F95,2)=7,$F95-2,$F95)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F95,2)=6,$F95+2,IF(WEEKDAY($F95,2)=7,$F95+1,$F95)),$F95)))</f>
-        <v>46575</v>
+        <v>46606</v>
       </c>
       <c r="H95" s="69" t="n">
         <f aca="false">IF($G95="",0,IF(AND($G95&gt;='Cash Flow'!$E$6,$G95&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15119,11 +15119,11 @@
       </c>
       <c r="F96" s="68" t="n">
         <f aca="false">IF($C96="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*12,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*12,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,12),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$10="One Time",IF(13=1,Recurring!$F$10,""),""))))))</f>
-        <v>46606</v>
+        <v>46637</v>
       </c>
       <c r="G96" s="68" t="n">
         <f aca="false">IF($F96="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F96,2)=6,$F96-1,IF(WEEKDAY($F96,2)=7,$F96-2,$F96)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F96,2)=6,$F96+2,IF(WEEKDAY($F96,2)=7,$F96+1,$F96)),$F96)))</f>
-        <v>46606</v>
+        <v>46637</v>
       </c>
       <c r="H96" s="69" t="n">
         <f aca="false">IF($G96="",0,IF(AND($G96&gt;='Cash Flow'!$E$6,$G96&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15163,11 +15163,11 @@
       </c>
       <c r="F97" s="68" t="n">
         <f aca="false">IF($C97="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*13,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*13,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,13),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$10="One Time",IF(14=1,Recurring!$F$10,""),""))))))</f>
-        <v>46637</v>
+        <v>46667</v>
       </c>
       <c r="G97" s="68" t="n">
         <f aca="false">IF($F97="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F97,2)=6,$F97-1,IF(WEEKDAY($F97,2)=7,$F97-2,$F97)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F97,2)=6,$F97+2,IF(WEEKDAY($F97,2)=7,$F97+1,$F97)),$F97)))</f>
-        <v>46637</v>
+        <v>46667</v>
       </c>
       <c r="H97" s="69" t="n">
         <f aca="false">IF($G97="",0,IF(AND($G97&gt;='Cash Flow'!$E$6,$G97&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15207,11 +15207,11 @@
       </c>
       <c r="F98" s="68" t="n">
         <f aca="false">IF($C98="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*14,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*14,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,14),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$10="One Time",IF(15=1,Recurring!$F$10,""),""))))))</f>
-        <v>46667</v>
+        <v>46698</v>
       </c>
       <c r="G98" s="68" t="n">
         <f aca="false">IF($F98="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F98,2)=6,$F98-1,IF(WEEKDAY($F98,2)=7,$F98-2,$F98)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F98,2)=6,$F98+2,IF(WEEKDAY($F98,2)=7,$F98+1,$F98)),$F98)))</f>
-        <v>46667</v>
+        <v>46698</v>
       </c>
       <c r="H98" s="69" t="n">
         <f aca="false">IF($G98="",0,IF(AND($G98&gt;='Cash Flow'!$E$6,$G98&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15251,11 +15251,11 @@
       </c>
       <c r="F99" s="68" t="n">
         <f aca="false">IF($C99="","",IF(Recurring!$E$10="Weekly",Recurring!$F$10+7*15,IF(Recurring!$E$10="Every 2 Weeks",Recurring!$F$10+14*15,IF(Recurring!$E$10="Monthly",EDATE(Recurring!$F$10,15),IF(Recurring!$E$10="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$10,INT((IF(DAY(Recurring!$F$10)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$10="One Time",IF(16=1,Recurring!$F$10,""),""))))))</f>
-        <v>46698</v>
+        <v>46728</v>
       </c>
       <c r="G99" s="68" t="n">
         <f aca="false">IF($F99="","",IF(Recurring!$G$10="Move Before",IF(WEEKDAY($F99,2)=6,$F99-1,IF(WEEKDAY($F99,2)=7,$F99-2,$F99)),IF(Recurring!$G$10="Move After",IF(WEEKDAY($F99,2)=6,$F99+2,IF(WEEKDAY($F99,2)=7,$F99+1,$F99)),$F99)))</f>
-        <v>46698</v>
+        <v>46728</v>
       </c>
       <c r="H99" s="69" t="n">
         <f aca="false">IF($G99="",0,IF(AND($G99&gt;='Cash Flow'!$E$6,$G99&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15295,11 +15295,11 @@
       </c>
       <c r="F100" s="68" t="n">
         <f aca="false">IF($C100="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*0,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*0,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,0),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$11="One Time",IF(1=1,Recurring!$F$11,""),""))))))</f>
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="G100" s="68" t="n">
         <f aca="false">IF($F100="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F100,2)=6,$F100-1,IF(WEEKDAY($F100,2)=7,$F100-2,$F100)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F100,2)=6,$F100+2,IF(WEEKDAY($F100,2)=7,$F100+1,$F100)),$F100)))</f>
-        <v>46241</v>
+        <v>46272</v>
       </c>
       <c r="H100" s="69" t="n">
         <f aca="false">IF($G100="",0,IF(AND($G100&gt;='Cash Flow'!$E$6,$G100&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15307,15 +15307,15 @@
       </c>
       <c r="I100" s="69" t="n">
         <f aca="false">IF($H100=1,INT(($G100-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J100" s="66" t="n">
         <f aca="false">IF($H100=1,$G100*10000+ROW(),"")</f>
-        <v>462410100</v>
+        <v>462720100</v>
       </c>
       <c r="K100" s="66" t="n">
         <f aca="false">IF($H100=1,$I100*1000+COUNTIFS($I$4:$I$483,$I100,$J$4:$J$483,"&lt;"&amp;$J100)+1,"")</f>
-        <v>1002</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15339,11 +15339,11 @@
       </c>
       <c r="F101" s="68" t="n">
         <f aca="false">IF($C101="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*1,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*1,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,1),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$11="One Time",IF(2=1,Recurring!$F$11,""),""))))))</f>
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="G101" s="68" t="n">
         <f aca="false">IF($F101="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F101,2)=6,$F101-1,IF(WEEKDAY($F101,2)=7,$F101-2,$F101)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F101,2)=6,$F101+2,IF(WEEKDAY($F101,2)=7,$F101+1,$F101)),$F101)))</f>
-        <v>46272</v>
+        <v>46302</v>
       </c>
       <c r="H101" s="69" t="n">
         <f aca="false">IF($G101="",0,IF(AND($G101&gt;='Cash Flow'!$E$6,$G101&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15351,15 +15351,15 @@
       </c>
       <c r="I101" s="69" t="n">
         <f aca="false">IF($H101=1,INT(($G101-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J101" s="66" t="n">
         <f aca="false">IF($H101=1,$G101*10000+ROW(),"")</f>
-        <v>462720101</v>
+        <v>463020101</v>
       </c>
       <c r="K101" s="66" t="n">
         <f aca="false">IF($H101=1,$I101*1000+COUNTIFS($I$4:$I$483,$I101,$J$4:$J$483,"&lt;"&amp;$J101)+1,"")</f>
-        <v>5006</v>
+        <v>9007</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15383,27 +15383,27 @@
       </c>
       <c r="F102" s="68" t="n">
         <f aca="false">IF($C102="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*2,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*2,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,2),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$11="One Time",IF(3=1,Recurring!$F$11,""),""))))))</f>
-        <v>46302</v>
+        <v>46333</v>
       </c>
       <c r="G102" s="68" t="n">
         <f aca="false">IF($F102="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F102,2)=6,$F102-1,IF(WEEKDAY($F102,2)=7,$F102-2,$F102)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F102,2)=6,$F102+2,IF(WEEKDAY($F102,2)=7,$F102+1,$F102)),$F102)))</f>
-        <v>46302</v>
+        <v>46333</v>
       </c>
       <c r="H102" s="69" t="n">
         <f aca="false">IF($G102="",0,IF(AND($G102&gt;='Cash Flow'!$E$6,$G102&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I102" s="69" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="69" t="str">
         <f aca="false">IF($H102=1,INT(($G102-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
-      </c>
-      <c r="J102" s="66" t="n">
+        <v/>
+      </c>
+      <c r="J102" s="66" t="str">
         <f aca="false">IF($H102=1,$G102*10000+ROW(),"")</f>
-        <v>463020102</v>
-      </c>
-      <c r="K102" s="66" t="n">
+        <v/>
+      </c>
+      <c r="K102" s="66" t="str">
         <f aca="false">IF($H102=1,$I102*1000+COUNTIFS($I$4:$I$483,$I102,$J$4:$J$483,"&lt;"&amp;$J102)+1,"")</f>
-        <v>9007</v>
+        <v/>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15427,11 +15427,11 @@
       </c>
       <c r="F103" s="68" t="n">
         <f aca="false">IF($C103="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*3,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*3,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,3),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$11="One Time",IF(4=1,Recurring!$F$11,""),""))))))</f>
-        <v>46333</v>
+        <v>46363</v>
       </c>
       <c r="G103" s="68" t="n">
         <f aca="false">IF($F103="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F103,2)=6,$F103-1,IF(WEEKDAY($F103,2)=7,$F103-2,$F103)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F103,2)=6,$F103+2,IF(WEEKDAY($F103,2)=7,$F103+1,$F103)),$F103)))</f>
-        <v>46333</v>
+        <v>46363</v>
       </c>
       <c r="H103" s="69" t="n">
         <f aca="false">IF($G103="",0,IF(AND($G103&gt;='Cash Flow'!$E$6,$G103&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15471,11 +15471,11 @@
       </c>
       <c r="F104" s="68" t="n">
         <f aca="false">IF($C104="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*4,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*4,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,4),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$11="One Time",IF(5=1,Recurring!$F$11,""),""))))))</f>
-        <v>46363</v>
+        <v>46394</v>
       </c>
       <c r="G104" s="68" t="n">
         <f aca="false">IF($F104="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F104,2)=6,$F104-1,IF(WEEKDAY($F104,2)=7,$F104-2,$F104)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F104,2)=6,$F104+2,IF(WEEKDAY($F104,2)=7,$F104+1,$F104)),$F104)))</f>
-        <v>46363</v>
+        <v>46394</v>
       </c>
       <c r="H104" s="69" t="n">
         <f aca="false">IF($G104="",0,IF(AND($G104&gt;='Cash Flow'!$E$6,$G104&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15515,11 +15515,11 @@
       </c>
       <c r="F105" s="68" t="n">
         <f aca="false">IF($C105="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*5,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*5,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,5),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$11="One Time",IF(6=1,Recurring!$F$11,""),""))))))</f>
-        <v>46394</v>
+        <v>46425</v>
       </c>
       <c r="G105" s="68" t="n">
         <f aca="false">IF($F105="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F105,2)=6,$F105-1,IF(WEEKDAY($F105,2)=7,$F105-2,$F105)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F105,2)=6,$F105+2,IF(WEEKDAY($F105,2)=7,$F105+1,$F105)),$F105)))</f>
-        <v>46394</v>
+        <v>46425</v>
       </c>
       <c r="H105" s="69" t="n">
         <f aca="false">IF($G105="",0,IF(AND($G105&gt;='Cash Flow'!$E$6,$G105&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15559,11 +15559,11 @@
       </c>
       <c r="F106" s="68" t="n">
         <f aca="false">IF($C106="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*6,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*6,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,6),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$11="One Time",IF(7=1,Recurring!$F$11,""),""))))))</f>
-        <v>46425</v>
+        <v>46453</v>
       </c>
       <c r="G106" s="68" t="n">
         <f aca="false">IF($F106="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F106,2)=6,$F106-1,IF(WEEKDAY($F106,2)=7,$F106-2,$F106)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F106,2)=6,$F106+2,IF(WEEKDAY($F106,2)=7,$F106+1,$F106)),$F106)))</f>
-        <v>46425</v>
+        <v>46453</v>
       </c>
       <c r="H106" s="69" t="n">
         <f aca="false">IF($G106="",0,IF(AND($G106&gt;='Cash Flow'!$E$6,$G106&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15603,11 +15603,11 @@
       </c>
       <c r="F107" s="68" t="n">
         <f aca="false">IF($C107="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*7,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*7,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,7),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$11="One Time",IF(8=1,Recurring!$F$11,""),""))))))</f>
-        <v>46453</v>
+        <v>46484</v>
       </c>
       <c r="G107" s="68" t="n">
         <f aca="false">IF($F107="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F107,2)=6,$F107-1,IF(WEEKDAY($F107,2)=7,$F107-2,$F107)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F107,2)=6,$F107+2,IF(WEEKDAY($F107,2)=7,$F107+1,$F107)),$F107)))</f>
-        <v>46453</v>
+        <v>46484</v>
       </c>
       <c r="H107" s="69" t="n">
         <f aca="false">IF($G107="",0,IF(AND($G107&gt;='Cash Flow'!$E$6,$G107&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15647,11 +15647,11 @@
       </c>
       <c r="F108" s="68" t="n">
         <f aca="false">IF($C108="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*8,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*8,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,8),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$11="One Time",IF(9=1,Recurring!$F$11,""),""))))))</f>
-        <v>46484</v>
+        <v>46514</v>
       </c>
       <c r="G108" s="68" t="n">
         <f aca="false">IF($F108="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F108,2)=6,$F108-1,IF(WEEKDAY($F108,2)=7,$F108-2,$F108)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F108,2)=6,$F108+2,IF(WEEKDAY($F108,2)=7,$F108+1,$F108)),$F108)))</f>
-        <v>46484</v>
+        <v>46514</v>
       </c>
       <c r="H108" s="69" t="n">
         <f aca="false">IF($G108="",0,IF(AND($G108&gt;='Cash Flow'!$E$6,$G108&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15691,11 +15691,11 @@
       </c>
       <c r="F109" s="68" t="n">
         <f aca="false">IF($C109="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*9,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*9,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,9),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$11="One Time",IF(10=1,Recurring!$F$11,""),""))))))</f>
-        <v>46514</v>
+        <v>46545</v>
       </c>
       <c r="G109" s="68" t="n">
         <f aca="false">IF($F109="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F109,2)=6,$F109-1,IF(WEEKDAY($F109,2)=7,$F109-2,$F109)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F109,2)=6,$F109+2,IF(WEEKDAY($F109,2)=7,$F109+1,$F109)),$F109)))</f>
-        <v>46514</v>
+        <v>46545</v>
       </c>
       <c r="H109" s="69" t="n">
         <f aca="false">IF($G109="",0,IF(AND($G109&gt;='Cash Flow'!$E$6,$G109&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15735,11 +15735,11 @@
       </c>
       <c r="F110" s="68" t="n">
         <f aca="false">IF($C110="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*10,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*10,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,10),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$11="One Time",IF(11=1,Recurring!$F$11,""),""))))))</f>
-        <v>46545</v>
+        <v>46575</v>
       </c>
       <c r="G110" s="68" t="n">
         <f aca="false">IF($F110="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F110,2)=6,$F110-1,IF(WEEKDAY($F110,2)=7,$F110-2,$F110)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F110,2)=6,$F110+2,IF(WEEKDAY($F110,2)=7,$F110+1,$F110)),$F110)))</f>
-        <v>46545</v>
+        <v>46575</v>
       </c>
       <c r="H110" s="69" t="n">
         <f aca="false">IF($G110="",0,IF(AND($G110&gt;='Cash Flow'!$E$6,$G110&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15779,11 +15779,11 @@
       </c>
       <c r="F111" s="68" t="n">
         <f aca="false">IF($C111="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*11,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*11,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,11),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$11="One Time",IF(12=1,Recurring!$F$11,""),""))))))</f>
-        <v>46575</v>
+        <v>46606</v>
       </c>
       <c r="G111" s="68" t="n">
         <f aca="false">IF($F111="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F111,2)=6,$F111-1,IF(WEEKDAY($F111,2)=7,$F111-2,$F111)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F111,2)=6,$F111+2,IF(WEEKDAY($F111,2)=7,$F111+1,$F111)),$F111)))</f>
-        <v>46575</v>
+        <v>46606</v>
       </c>
       <c r="H111" s="69" t="n">
         <f aca="false">IF($G111="",0,IF(AND($G111&gt;='Cash Flow'!$E$6,$G111&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15823,11 +15823,11 @@
       </c>
       <c r="F112" s="68" t="n">
         <f aca="false">IF($C112="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*12,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*12,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,12),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$11="One Time",IF(13=1,Recurring!$F$11,""),""))))))</f>
-        <v>46606</v>
+        <v>46637</v>
       </c>
       <c r="G112" s="68" t="n">
         <f aca="false">IF($F112="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F112,2)=6,$F112-1,IF(WEEKDAY($F112,2)=7,$F112-2,$F112)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F112,2)=6,$F112+2,IF(WEEKDAY($F112,2)=7,$F112+1,$F112)),$F112)))</f>
-        <v>46606</v>
+        <v>46637</v>
       </c>
       <c r="H112" s="69" t="n">
         <f aca="false">IF($G112="",0,IF(AND($G112&gt;='Cash Flow'!$E$6,$G112&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15867,11 +15867,11 @@
       </c>
       <c r="F113" s="68" t="n">
         <f aca="false">IF($C113="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*13,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*13,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,13),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$11="One Time",IF(14=1,Recurring!$F$11,""),""))))))</f>
-        <v>46637</v>
+        <v>46667</v>
       </c>
       <c r="G113" s="68" t="n">
         <f aca="false">IF($F113="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F113,2)=6,$F113-1,IF(WEEKDAY($F113,2)=7,$F113-2,$F113)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F113,2)=6,$F113+2,IF(WEEKDAY($F113,2)=7,$F113+1,$F113)),$F113)))</f>
-        <v>46637</v>
+        <v>46667</v>
       </c>
       <c r="H113" s="69" t="n">
         <f aca="false">IF($G113="",0,IF(AND($G113&gt;='Cash Flow'!$E$6,$G113&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15911,11 +15911,11 @@
       </c>
       <c r="F114" s="68" t="n">
         <f aca="false">IF($C114="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*14,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*14,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,14),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$11="One Time",IF(15=1,Recurring!$F$11,""),""))))))</f>
-        <v>46667</v>
+        <v>46698</v>
       </c>
       <c r="G114" s="68" t="n">
         <f aca="false">IF($F114="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F114,2)=6,$F114-1,IF(WEEKDAY($F114,2)=7,$F114-2,$F114)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F114,2)=6,$F114+2,IF(WEEKDAY($F114,2)=7,$F114+1,$F114)),$F114)))</f>
-        <v>46667</v>
+        <v>46698</v>
       </c>
       <c r="H114" s="69" t="n">
         <f aca="false">IF($G114="",0,IF(AND($G114&gt;='Cash Flow'!$E$6,$G114&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15955,11 +15955,11 @@
       </c>
       <c r="F115" s="68" t="n">
         <f aca="false">IF($C115="","",IF(Recurring!$E$11="Weekly",Recurring!$F$11+7*15,IF(Recurring!$E$11="Every 2 Weeks",Recurring!$F$11+14*15,IF(Recurring!$E$11="Monthly",EDATE(Recurring!$F$11,15),IF(Recurring!$E$11="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$11,INT((IF(DAY(Recurring!$F$11)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$11="One Time",IF(16=1,Recurring!$F$11,""),""))))))</f>
-        <v>46698</v>
+        <v>46728</v>
       </c>
       <c r="G115" s="68" t="n">
         <f aca="false">IF($F115="","",IF(Recurring!$G$11="Move Before",IF(WEEKDAY($F115,2)=6,$F115-1,IF(WEEKDAY($F115,2)=7,$F115-2,$F115)),IF(Recurring!$G$11="Move After",IF(WEEKDAY($F115,2)=6,$F115+2,IF(WEEKDAY($F115,2)=7,$F115+1,$F115)),$F115)))</f>
-        <v>46698</v>
+        <v>46728</v>
       </c>
       <c r="H115" s="69" t="n">
         <f aca="false">IF($G115="",0,IF(AND($G115&gt;='Cash Flow'!$E$6,$G115&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="K116" s="66" t="n">
         <f aca="false">IF($H116=1,$I116*1000+COUNTIFS($I$4:$I$483,$I116,$J$4:$J$483,"&lt;"&amp;$J116)+1,"")</f>
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16723,7 +16723,7 @@
       </c>
       <c r="K132" s="66" t="n">
         <f aca="false">IF($H132=1,$I132*1000+COUNTIFS($I$4:$I$483,$I132,$J$4:$J$483,"&lt;"&amp;$J132)+1,"")</f>
-        <v>1005</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Cash Flow'!$A$1:$K$284</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$44</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$45</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Recurring!$A$1:$J$38</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Recurring!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$J$28</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="166">
   <si>
     <t xml:space="preserve">WEEKLY CASH FLOW SURVIVAL WORKSHEET</t>
   </si>
@@ -207,6 +207,9 @@
     <t xml:space="preserve">Progressive Insurance ($143.37) was cut off at the bottom of the third screenshot, so its due date is set to Aug 31, 2026. Correct it on the Recurring tab if that is wrong.</t>
   </si>
   <si>
+    <t xml:space="preserve">Central Maine Power: the $43.87 payment plan covers usage through August, so the $163.50 regular bill does not start until Sep 10, 2026. OPEN QUESTION: the $43.87 plan is still set to repeat every month from Aug 25. If the plan ends once the $163.50 billing resumes, set its Active to No or give it an end, or the sheet will charge you both from September onward.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Patrick Rombalski is 'Twice a Month' with Weekend Rule = Move Before, which is why the August payment lands on Fri Aug 14 rather than Sat Aug 15, matching your app.</t>
   </si>
   <si>
@@ -330,7 +333,7 @@
     <t xml:space="preserve">Microsoft</t>
   </si>
   <si>
-    <t xml:space="preserve">Central Maine Power: Property</t>
+    <t xml:space="preserve">Central Maine Power: Payment Plan</t>
   </si>
   <si>
     <t xml:space="preserve">Maine Revenue Services (2)</t>
@@ -1427,7 +1430,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:C44"/>
+  <dimension ref="B2:C45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1717,6 +1720,14 @@
       </c>
       <c r="C44" s="14" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1752,44 +1763,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1797,10 +1808,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>90</v>
@@ -1812,13 +1823,13 @@
         <v>46246</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -1827,10 +1838,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" s="23" t="n">
         <v>790</v>
@@ -1842,13 +1853,13 @@
         <v>46248</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J6" s="21"/>
     </row>
@@ -1857,10 +1868,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>21.1</v>
@@ -1872,13 +1883,13 @@
         <v>46269</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -1887,10 +1898,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="23" t="n">
         <v>20</v>
@@ -1902,13 +1913,13 @@
         <v>46270</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J8" s="21"/>
     </row>
@@ -1917,10 +1928,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>10</v>
@@ -1932,13 +1943,13 @@
         <v>46270</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1947,10 +1958,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D10" s="23" t="n">
         <v>4.99</v>
@@ -1962,13 +1973,13 @@
         <v>46272</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J10" s="21"/>
     </row>
@@ -1977,10 +1988,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>500</v>
@@ -1992,13 +2003,13 @@
         <v>46272</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -2007,10 +2018,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D12" s="23" t="n">
         <v>163.5</v>
@@ -2019,16 +2030,16 @@
         <v>46</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>46244</v>
+        <v>46275</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J12" s="21"/>
     </row>
@@ -2037,10 +2048,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>2.99</v>
@@ -2052,13 +2063,13 @@
         <v>46247</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -2067,10 +2078,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="23" t="n">
         <v>350</v>
@@ -2082,13 +2093,13 @@
         <v>46248</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" s="21"/>
     </row>
@@ -2097,10 +2108,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>171.1</v>
@@ -2112,13 +2123,13 @@
         <v>46250</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -2127,10 +2138,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D16" s="23" t="n">
         <v>45</v>
@@ -2142,13 +2153,13 @@
         <v>46250</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J16" s="21"/>
     </row>
@@ -2157,10 +2168,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>16.99</v>
@@ -2172,13 +2183,13 @@
         <v>46252</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2187,10 +2198,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D18" s="23" t="n">
         <v>13.7</v>
@@ -2202,13 +2213,13 @@
         <v>46259</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J18" s="21"/>
     </row>
@@ -2217,10 +2228,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>43.87</v>
@@ -2232,13 +2243,13 @@
         <v>46259</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -2247,10 +2258,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D20" s="23" t="n">
         <v>150</v>
@@ -2262,13 +2273,13 @@
         <v>46264</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J20" s="21"/>
     </row>
@@ -2277,10 +2288,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>143.37</v>
@@ -2292,13 +2303,13 @@
         <v>46265</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J21" s="6"/>
     </row>
@@ -2486,17 +2497,17 @@
     </row>
     <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="25" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -2563,17 +2574,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>71.17</v>
@@ -2581,7 +2592,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>46241</v>
@@ -2593,7 +2604,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>200</v>
@@ -2601,7 +2612,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="true">TODAY()</f>
@@ -2610,12 +2621,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2628,7 +2639,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="32"/>
       <c r="G13" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="34" t="n">
@@ -2643,19 +2654,19 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G14" s="36" t="s">
         <v>18</v>
@@ -2664,41 +2675,41 @@
         <v>20</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power Co.</v>
+        <v>Bruno's Restaurant (paycheck)</v>
       </c>
       <c r="C15" s="38" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$G$4:$G$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="D15" s="39" t="str">
         <f aca="false">IF($B15="","",INDEX(Schedule!$D$4:$D$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
+        <v>Income</v>
       </c>
       <c r="E15" s="40" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$E$4:$E$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>163.5</v>
+        <v>90</v>
       </c>
       <c r="F15" s="18"/>
-      <c r="G15" s="41" t="str">
+      <c r="G15" s="41" t="n">
         <f aca="false">IF($B15="","",IF($D15="Income",IF($F15&lt;&gt;"",$F15,$E15),""))</f>
-        <v/>
-      </c>
-      <c r="H15" s="42" t="n">
+        <v>90</v>
+      </c>
+      <c r="H15" s="42" t="str">
         <f aca="false">IF($B15="","",IF($D15="Income","",IF($F15&lt;&gt;"",$F15,$E15)))</f>
-        <v>163.5</v>
+        <v/>
       </c>
       <c r="I15" s="43" t="n">
         <f aca="false">IF($B15="","",$I$13+SUM($G$15:$G15)-SUM($H$15:$H15))</f>
-        <v>-92.33</v>
+        <v>161.17</v>
       </c>
       <c r="J15" s="44" t="str">
         <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2708,32 +2719,32 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Apple: iCloud</v>
       </c>
       <c r="C16" s="38" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$G$4:$G$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="D16" s="39" t="str">
         <f aca="false">IF($B16="","",INDEX(Schedule!$D$4:$D$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E16" s="40" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$E$4:$E$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>2.99</v>
       </c>
       <c r="F16" s="18"/>
-      <c r="G16" s="41" t="n">
+      <c r="G16" s="41" t="str">
         <f aca="false">IF($B16="","",IF($D16="Income",IF($F16&lt;&gt;"",$F16,$E16),""))</f>
-        <v>90</v>
-      </c>
-      <c r="H16" s="42" t="str">
+        <v/>
+      </c>
+      <c r="H16" s="42" t="n">
         <f aca="false">IF($B16="","",IF($D16="Income","",IF($F16&lt;&gt;"",$F16,$E16)))</f>
-        <v/>
+        <v>2.99</v>
       </c>
       <c r="I16" s="43" t="n">
         <f aca="false">IF($B16="","",$I$13+SUM($G$15:$G16)-SUM($H$15:$H16))</f>
-        <v>-2.32999999999998</v>
+        <v>158.18</v>
       </c>
       <c r="J16" s="44" t="str">
         <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -2743,36 +2754,36 @@
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="11" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
-      </c>
-      <c r="C17" s="38" t="n">
+        <v/>
+      </c>
+      <c r="C17" s="38" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$G$4:$G$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>46247</v>
+        <v/>
       </c>
       <c r="D17" s="39" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$D$4:$D$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>Expense</v>
-      </c>
-      <c r="E17" s="40" t="n">
+        <v/>
+      </c>
+      <c r="E17" s="40" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$E$4:$E$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="41" t="str">
         <f aca="false">IF($B17="","",IF($D17="Income",IF($F17&lt;&gt;"",$F17,$E17),""))</f>
         <v/>
       </c>
-      <c r="H17" s="42" t="n">
+      <c r="H17" s="42" t="str">
         <f aca="false">IF($B17="","",IF($D17="Income","",IF($F17&lt;&gt;"",$F17,$E17)))</f>
-        <v>2.99</v>
-      </c>
-      <c r="I17" s="43" t="n">
+        <v/>
+      </c>
+      <c r="I17" s="43" t="str">
         <f aca="false">IF($B17="","",$I$13+SUM($G$15:$G17)-SUM($H$15:$H17))</f>
-        <v>-5.31999999999999</v>
+        <v/>
       </c>
       <c r="J17" s="44" t="str">
         <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3022,7 +3033,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C25" s="46"/>
       <c r="D25" s="46"/>
@@ -3155,7 +3166,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C32" s="48"/>
       <c r="D32" s="48"/>
@@ -3167,19 +3178,19 @@
       </c>
       <c r="H32" s="49" t="n">
         <f aca="false">SUM($H$15:$H$31)</f>
-        <v>166.49</v>
+        <v>2.99</v>
       </c>
       <c r="I32" s="50" t="n">
         <f aca="false">$I$13+$G$32-$H$32</f>
-        <v>-5.31999999999999</v>
+        <v>158.18</v>
       </c>
       <c r="J32" s="51" t="str">
         <f aca="false">IF($I$32&lt;0,"SHORTFALL",IF($I$32&lt;$E$7,"TIGHT","OK"))</f>
-        <v>SHORTFALL</v>
+        <v>TIGHT</v>
       </c>
       <c r="K32" s="25" t="str">
         <f aca="false">"In "&amp;TEXT($G$32,"$#,##0.00")&amp;"   less out "&amp;TEXT($H$32,"$#,##0.00")&amp;"   =  net "&amp;TEXT($G$32-$H$32,"$#,##0.00;-$#,##0.00")</f>
-        <v>In $90.00   less out $166.49   =  net -$76.49</v>
+        <v>In $90.00   less out $2.99   =  net $87.01</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3192,12 +3203,12 @@
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
       <c r="G34" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" s="32"/>
       <c r="I34" s="34" t="n">
         <f aca="false">$I$32</f>
-        <v>-5.31999999999999</v>
+        <v>158.18</v>
       </c>
       <c r="J34" s="32"/>
       <c r="K34" s="28" t="str">
@@ -3207,19 +3218,19 @@
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G35" s="36" t="s">
         <v>18</v>
@@ -3228,10 +3239,10 @@
         <v>20</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3262,7 +3273,7 @@
       </c>
       <c r="I36" s="43" t="n">
         <f aca="false">IF($B36="","",$I$34+SUM($G$36:$G36)-SUM($H$36:$H36))</f>
-        <v>784.68</v>
+        <v>948.18</v>
       </c>
       <c r="J36" s="44" t="str">
         <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3297,7 +3308,7 @@
       </c>
       <c r="I37" s="43" t="n">
         <f aca="false">IF($B37="","",$I$34+SUM($G$36:$G37)-SUM($H$36:$H37))</f>
-        <v>434.68</v>
+        <v>598.18</v>
       </c>
       <c r="J37" s="44" t="str">
         <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3332,7 +3343,7 @@
       </c>
       <c r="I38" s="43" t="n">
         <f aca="false">IF($B38="","",$I$34+SUM($G$36:$G38)-SUM($H$36:$H38))</f>
-        <v>263.58</v>
+        <v>427.08</v>
       </c>
       <c r="J38" s="44" t="str">
         <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3367,7 +3378,7 @@
       </c>
       <c r="I39" s="43" t="n">
         <f aca="false">IF($B39="","",$I$34+SUM($G$36:$G39)-SUM($H$36:$H39))</f>
-        <v>218.58</v>
+        <v>382.08</v>
       </c>
       <c r="J39" s="44" t="str">
         <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3402,7 +3413,7 @@
       </c>
       <c r="I40" s="43" t="n">
         <f aca="false">IF($B40="","",$I$34+SUM($G$36:$G40)-SUM($H$36:$H40))</f>
-        <v>201.59</v>
+        <v>365.09</v>
       </c>
       <c r="J40" s="44" t="str">
         <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3437,7 +3448,7 @@
       </c>
       <c r="I41" s="43" t="n">
         <f aca="false">IF($B41="","",$I$34+SUM($G$36:$G41)-SUM($H$36:$H41))</f>
-        <v>291.59</v>
+        <v>455.09</v>
       </c>
       <c r="J41" s="44" t="str">
         <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3586,7 +3597,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C46" s="46"/>
       <c r="D46" s="46"/>
@@ -3719,7 +3730,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="47" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C53" s="48"/>
       <c r="D53" s="48"/>
@@ -3735,7 +3746,7 @@
       </c>
       <c r="I53" s="50" t="n">
         <f aca="false">$I$34+$G$53-$H$53</f>
-        <v>291.59</v>
+        <v>455.09</v>
       </c>
       <c r="J53" s="51" t="str">
         <f aca="false">IF($I$53&lt;0,"SHORTFALL",IF($I$53&lt;$E$7,"TIGHT","OK"))</f>
@@ -3756,12 +3767,12 @@
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
       <c r="G55" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H55" s="32"/>
       <c r="I55" s="34" t="n">
         <f aca="false">$I$53</f>
-        <v>291.59</v>
+        <v>455.09</v>
       </c>
       <c r="J55" s="32"/>
       <c r="K55" s="28" t="str">
@@ -3771,19 +3782,19 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G56" s="36" t="s">
         <v>18</v>
@@ -3792,10 +3803,10 @@
         <v>20</v>
       </c>
       <c r="I56" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J56" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3826,7 +3837,7 @@
       </c>
       <c r="I57" s="43" t="n">
         <f aca="false">IF($B57="","",$I$55+SUM($G$57:$G57)-SUM($H$57:$H57))</f>
-        <v>1081.59</v>
+        <v>1245.09</v>
       </c>
       <c r="J57" s="44" t="str">
         <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3861,7 +3872,7 @@
       </c>
       <c r="I58" s="43" t="n">
         <f aca="false">IF($B58="","",$I$55+SUM($G$57:$G58)-SUM($H$57:$H58))</f>
-        <v>1067.89</v>
+        <v>1231.39</v>
       </c>
       <c r="J58" s="44" t="str">
         <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3871,7 +3882,7 @@
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="11" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(3003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="C59" s="38" t="n">
         <f aca="false">IF($B59="","",INDEX(Schedule!$G$4:$G$483,MATCH(3003,Schedule!$K$4:$K$483,0)))</f>
@@ -3896,7 +3907,7 @@
       </c>
       <c r="I59" s="43" t="n">
         <f aca="false">IF($B59="","",$I$55+SUM($G$57:$G59)-SUM($H$57:$H59))</f>
-        <v>1024.02</v>
+        <v>1187.52</v>
       </c>
       <c r="J59" s="44" t="str">
         <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3931,7 +3942,7 @@
       </c>
       <c r="I60" s="43" t="n">
         <f aca="false">IF($B60="","",$I$55+SUM($G$57:$G60)-SUM($H$57:$H60))</f>
-        <v>1114.02</v>
+        <v>1277.52</v>
       </c>
       <c r="J60" s="44" t="str">
         <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4150,7 +4161,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C67" s="46"/>
       <c r="D67" s="46"/>
@@ -4283,7 +4294,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="47" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C74" s="48"/>
       <c r="D74" s="48"/>
@@ -4299,7 +4310,7 @@
       </c>
       <c r="I74" s="50" t="n">
         <f aca="false">$I$55+$G$74-$H$74</f>
-        <v>1114.02</v>
+        <v>1277.52</v>
       </c>
       <c r="J74" s="51" t="str">
         <f aca="false">IF($I$74&lt;0,"SHORTFALL",IF($I$74&lt;$E$7,"TIGHT","OK"))</f>
@@ -4320,12 +4331,12 @@
       <c r="E76" s="32"/>
       <c r="F76" s="32"/>
       <c r="G76" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="34" t="n">
         <f aca="false">$I$74</f>
-        <v>1114.02</v>
+        <v>1277.52</v>
       </c>
       <c r="J76" s="32"/>
       <c r="K76" s="28" t="str">
@@ -4335,19 +4346,19 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D77" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G77" s="36" t="s">
         <v>18</v>
@@ -4356,10 +4367,10 @@
         <v>20</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J77" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4390,7 +4401,7 @@
       </c>
       <c r="I78" s="43" t="n">
         <f aca="false">IF($B78="","",$I$76+SUM($G$78:$G78)-SUM($H$78:$H78))</f>
-        <v>1904.02</v>
+        <v>2067.52</v>
       </c>
       <c r="J78" s="44" t="str">
         <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4425,7 +4436,7 @@
       </c>
       <c r="I79" s="43" t="n">
         <f aca="false">IF($B79="","",$I$76+SUM($G$78:$G79)-SUM($H$78:$H79))</f>
-        <v>1754.02</v>
+        <v>1917.52</v>
       </c>
       <c r="J79" s="44" t="str">
         <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4460,7 +4471,7 @@
       </c>
       <c r="I80" s="43" t="n">
         <f aca="false">IF($B80="","",$I$76+SUM($G$78:$G80)-SUM($H$78:$H80))</f>
-        <v>1404.02</v>
+        <v>1567.52</v>
       </c>
       <c r="J80" s="44" t="str">
         <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4495,7 +4506,7 @@
       </c>
       <c r="I81" s="43" t="n">
         <f aca="false">IF($B81="","",$I$76+SUM($G$78:$G81)-SUM($H$78:$H81))</f>
-        <v>1260.65</v>
+        <v>1424.15</v>
       </c>
       <c r="J81" s="44" t="str">
         <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4530,7 +4541,7 @@
       </c>
       <c r="I82" s="43" t="n">
         <f aca="false">IF($B82="","",$I$76+SUM($G$78:$G82)-SUM($H$78:$H82))</f>
-        <v>1350.65</v>
+        <v>1514.15</v>
       </c>
       <c r="J82" s="44" t="str">
         <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4714,7 +4725,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C88" s="46"/>
       <c r="D88" s="46"/>
@@ -4847,7 +4858,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C95" s="48"/>
       <c r="D95" s="48"/>
@@ -4863,7 +4874,7 @@
       </c>
       <c r="I95" s="50" t="n">
         <f aca="false">$I$76+$G$95-$H$95</f>
-        <v>1350.65</v>
+        <v>1514.15</v>
       </c>
       <c r="J95" s="51" t="str">
         <f aca="false">IF($I$95&lt;0,"SHORTFALL",IF($I$95&lt;$E$7,"TIGHT","OK"))</f>
@@ -4884,12 +4895,12 @@
       <c r="E97" s="32"/>
       <c r="F97" s="32"/>
       <c r="G97" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="34" t="n">
         <f aca="false">$I$95</f>
-        <v>1350.65</v>
+        <v>1514.15</v>
       </c>
       <c r="J97" s="32"/>
       <c r="K97" s="28" t="str">
@@ -4899,19 +4910,19 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G98" s="36" t="s">
         <v>18</v>
@@ -4920,10 +4931,10 @@
         <v>20</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4954,7 +4965,7 @@
       </c>
       <c r="I99" s="43" t="n">
         <f aca="false">IF($B99="","",$I$97+SUM($G$99:$G99)-SUM($H$99:$H99))</f>
-        <v>2140.65</v>
+        <v>2304.15</v>
       </c>
       <c r="J99" s="44" t="str">
         <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4989,7 +5000,7 @@
       </c>
       <c r="I100" s="43" t="n">
         <f aca="false">IF($B100="","",$I$97+SUM($G$99:$G100)-SUM($H$99:$H100))</f>
-        <v>2119.55</v>
+        <v>2283.05</v>
       </c>
       <c r="J100" s="44" t="str">
         <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5024,7 +5035,7 @@
       </c>
       <c r="I101" s="43" t="n">
         <f aca="false">IF($B101="","",$I$97+SUM($G$99:$G101)-SUM($H$99:$H101))</f>
-        <v>2099.55</v>
+        <v>2263.05</v>
       </c>
       <c r="J101" s="44" t="str">
         <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5059,7 +5070,7 @@
       </c>
       <c r="I102" s="43" t="n">
         <f aca="false">IF($B102="","",$I$97+SUM($G$99:$G102)-SUM($H$99:$H102))</f>
-        <v>2089.55</v>
+        <v>2253.05</v>
       </c>
       <c r="J102" s="44" t="str">
         <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5094,7 +5105,7 @@
       </c>
       <c r="I103" s="43" t="n">
         <f aca="false">IF($B103="","",$I$97+SUM($G$99:$G103)-SUM($H$99:$H103))</f>
-        <v>2084.56</v>
+        <v>2248.06</v>
       </c>
       <c r="J103" s="44" t="str">
         <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5129,7 +5140,7 @@
       </c>
       <c r="I104" s="43" t="n">
         <f aca="false">IF($B104="","",$I$97+SUM($G$99:$G104)-SUM($H$99:$H104))</f>
-        <v>1584.56</v>
+        <v>1748.06</v>
       </c>
       <c r="J104" s="44" t="str">
         <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5164,7 +5175,7 @@
       </c>
       <c r="I105" s="43" t="n">
         <f aca="false">IF($B105="","",$I$97+SUM($G$99:$G105)-SUM($H$99:$H105))</f>
-        <v>1674.56</v>
+        <v>1838.06</v>
       </c>
       <c r="J105" s="44" t="str">
         <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5199,7 +5210,7 @@
       </c>
       <c r="I106" s="43" t="n">
         <f aca="false">IF($B106="","",$I$97+SUM($G$99:$G106)-SUM($H$99:$H106))</f>
-        <v>1511.06</v>
+        <v>1674.56</v>
       </c>
       <c r="J106" s="44" t="str">
         <f aca="true">IF($B106="","",IF($F106&lt;&gt;"","PAID",IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5278,7 +5289,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C109" s="46"/>
       <c r="D109" s="46"/>
@@ -5411,7 +5422,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="47" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C116" s="48"/>
       <c r="D116" s="48"/>
@@ -5427,7 +5438,7 @@
       </c>
       <c r="I116" s="50" t="n">
         <f aca="false">$I$97+$G$116-$H$116</f>
-        <v>1511.06</v>
+        <v>1674.56</v>
       </c>
       <c r="J116" s="51" t="str">
         <f aca="false">IF($I$116&lt;0,"SHORTFALL",IF($I$116&lt;$E$7,"TIGHT","OK"))</f>
@@ -5448,12 +5459,12 @@
       <c r="E118" s="32"/>
       <c r="F118" s="32"/>
       <c r="G118" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="34" t="n">
         <f aca="false">$I$116</f>
-        <v>1511.06</v>
+        <v>1674.56</v>
       </c>
       <c r="J118" s="32"/>
       <c r="K118" s="28" t="str">
@@ -5463,19 +5474,19 @@
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F119" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G119" s="36" t="s">
         <v>18</v>
@@ -5484,10 +5495,10 @@
         <v>20</v>
       </c>
       <c r="I119" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J119" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5518,7 +5529,7 @@
       </c>
       <c r="I120" s="43" t="n">
         <f aca="false">IF($B120="","",$I$118+SUM($G$120:$G120)-SUM($H$120:$H120))</f>
-        <v>2301.06</v>
+        <v>2464.56</v>
       </c>
       <c r="J120" s="44" t="str">
         <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5553,7 +5564,7 @@
       </c>
       <c r="I121" s="43" t="n">
         <f aca="false">IF($B121="","",$I$118+SUM($G$120:$G121)-SUM($H$120:$H121))</f>
-        <v>2298.07</v>
+        <v>2461.57</v>
       </c>
       <c r="J121" s="44" t="str">
         <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5588,7 +5599,7 @@
       </c>
       <c r="I122" s="43" t="n">
         <f aca="false">IF($B122="","",$I$118+SUM($G$120:$G122)-SUM($H$120:$H122))</f>
-        <v>1948.07</v>
+        <v>2111.57</v>
       </c>
       <c r="J122" s="44" t="str">
         <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5623,7 +5634,7 @@
       </c>
       <c r="I123" s="43" t="n">
         <f aca="false">IF($B123="","",$I$118+SUM($G$120:$G123)-SUM($H$120:$H123))</f>
-        <v>2038.07</v>
+        <v>2201.57</v>
       </c>
       <c r="J123" s="44" t="str">
         <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5658,7 +5669,7 @@
       </c>
       <c r="I124" s="43" t="n">
         <f aca="false">IF($B124="","",$I$118+SUM($G$120:$G124)-SUM($H$120:$H124))</f>
-        <v>1866.97</v>
+        <v>2030.47</v>
       </c>
       <c r="J124" s="44" t="str">
         <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5693,7 +5704,7 @@
       </c>
       <c r="I125" s="43" t="n">
         <f aca="false">IF($B125="","",$I$118+SUM($G$120:$G125)-SUM($H$120:$H125))</f>
-        <v>1821.97</v>
+        <v>1985.47</v>
       </c>
       <c r="J125" s="44" t="str">
         <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5842,7 +5853,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C130" s="46"/>
       <c r="D130" s="46"/>
@@ -5975,7 +5986,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="47" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C137" s="48"/>
       <c r="D137" s="48"/>
@@ -5991,7 +6002,7 @@
       </c>
       <c r="I137" s="50" t="n">
         <f aca="false">$I$118+$G$137-$H$137</f>
-        <v>1821.97</v>
+        <v>1985.47</v>
       </c>
       <c r="J137" s="51" t="str">
         <f aca="false">IF($I$137&lt;0,"SHORTFALL",IF($I$137&lt;$E$7,"TIGHT","OK"))</f>
@@ -6012,12 +6023,12 @@
       <c r="E139" s="32"/>
       <c r="F139" s="32"/>
       <c r="G139" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="34" t="n">
         <f aca="false">$I$137</f>
-        <v>1821.97</v>
+        <v>1985.47</v>
       </c>
       <c r="J139" s="32"/>
       <c r="K139" s="28" t="str">
@@ -6027,19 +6038,19 @@
     </row>
     <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C140" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E140" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F140" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G140" s="36" t="s">
         <v>18</v>
@@ -6048,10 +6059,10 @@
         <v>20</v>
       </c>
       <c r="I140" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J140" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6082,7 +6093,7 @@
       </c>
       <c r="I141" s="43" t="n">
         <f aca="false">IF($B141="","",$I$139+SUM($G$141:$G141)-SUM($H$141:$H141))</f>
-        <v>2611.97</v>
+        <v>2775.47</v>
       </c>
       <c r="J141" s="44" t="str">
         <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6117,7 +6128,7 @@
       </c>
       <c r="I142" s="43" t="n">
         <f aca="false">IF($B142="","",$I$139+SUM($G$141:$G142)-SUM($H$141:$H142))</f>
-        <v>2594.98</v>
+        <v>2758.48</v>
       </c>
       <c r="J142" s="44" t="str">
         <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6152,7 +6163,7 @@
       </c>
       <c r="I143" s="43" t="n">
         <f aca="false">IF($B143="","",$I$139+SUM($G$141:$G143)-SUM($H$141:$H143))</f>
-        <v>2684.98</v>
+        <v>2848.48</v>
       </c>
       <c r="J143" s="44" t="str">
         <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6406,7 +6417,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C151" s="46"/>
       <c r="D151" s="46"/>
@@ -6539,7 +6550,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C158" s="48"/>
       <c r="D158" s="48"/>
@@ -6555,7 +6566,7 @@
       </c>
       <c r="I158" s="50" t="n">
         <f aca="false">$I$139+$G$158-$H$158</f>
-        <v>2684.98</v>
+        <v>2848.48</v>
       </c>
       <c r="J158" s="51" t="str">
         <f aca="false">IF($I$158&lt;0,"SHORTFALL",IF($I$158&lt;$E$7,"TIGHT","OK"))</f>
@@ -6576,12 +6587,12 @@
       <c r="E160" s="32"/>
       <c r="F160" s="32"/>
       <c r="G160" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="34" t="n">
         <f aca="false">$I$158</f>
-        <v>2684.98</v>
+        <v>2848.48</v>
       </c>
       <c r="J160" s="32"/>
       <c r="K160" s="28" t="str">
@@ -6591,19 +6602,19 @@
     </row>
     <row r="161" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E161" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F161" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G161" s="36" t="s">
         <v>18</v>
@@ -6612,10 +6623,10 @@
         <v>20</v>
       </c>
       <c r="I161" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J161" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6646,7 +6657,7 @@
       </c>
       <c r="I162" s="43" t="n">
         <f aca="false">IF($B162="","",$I$160+SUM($G$162:$G162)-SUM($H$162:$H162))</f>
-        <v>3474.98</v>
+        <v>3638.48</v>
       </c>
       <c r="J162" s="44" t="str">
         <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6681,7 +6692,7 @@
       </c>
       <c r="I163" s="43" t="n">
         <f aca="false">IF($B163="","",$I$160+SUM($G$162:$G163)-SUM($H$162:$H163))</f>
-        <v>3461.28</v>
+        <v>3624.78</v>
       </c>
       <c r="J163" s="44" t="str">
         <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6691,7 +6702,7 @@
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B164" s="11" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(8003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="C164" s="38" t="n">
         <f aca="false">IF($B164="","",INDEX(Schedule!$G$4:$G$483,MATCH(8003,Schedule!$K$4:$K$483,0)))</f>
@@ -6716,7 +6727,7 @@
       </c>
       <c r="I164" s="43" t="n">
         <f aca="false">IF($B164="","",$I$160+SUM($G$162:$G164)-SUM($H$162:$H164))</f>
-        <v>3417.41</v>
+        <v>3580.91</v>
       </c>
       <c r="J164" s="44" t="str">
         <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6751,7 +6762,7 @@
       </c>
       <c r="I165" s="43" t="n">
         <f aca="false">IF($B165="","",$I$160+SUM($G$162:$G165)-SUM($H$162:$H165))</f>
-        <v>3507.41</v>
+        <v>3670.91</v>
       </c>
       <c r="J165" s="44" t="str">
         <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6786,7 +6797,7 @@
       </c>
       <c r="I166" s="43" t="n">
         <f aca="false">IF($B166="","",$I$160+SUM($G$162:$G166)-SUM($H$162:$H166))</f>
-        <v>3157.41</v>
+        <v>3320.91</v>
       </c>
       <c r="J166" s="44" t="str">
         <f aca="true">IF($B166="","",IF($F166&lt;&gt;"","PAID",IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6821,7 +6832,7 @@
       </c>
       <c r="I167" s="43" t="n">
         <f aca="false">IF($B167="","",$I$160+SUM($G$162:$G167)-SUM($H$162:$H167))</f>
-        <v>3007.41</v>
+        <v>3170.91</v>
       </c>
       <c r="J167" s="44" t="str">
         <f aca="true">IF($B167="","",IF($F167&lt;&gt;"","PAID",IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6856,7 +6867,7 @@
       </c>
       <c r="I168" s="43" t="n">
         <f aca="false">IF($B168="","",$I$160+SUM($G$162:$G168)-SUM($H$162:$H168))</f>
-        <v>2864.04</v>
+        <v>3027.54</v>
       </c>
       <c r="J168" s="44" t="str">
         <f aca="true">IF($B168="","",IF($F168&lt;&gt;"","PAID",IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6970,7 +6981,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C172" s="46"/>
       <c r="D172" s="46"/>
@@ -7103,7 +7114,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="47" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C179" s="48"/>
       <c r="D179" s="48"/>
@@ -7119,7 +7130,7 @@
       </c>
       <c r="I179" s="50" t="n">
         <f aca="false">$I$160+$G$179-$H$179</f>
-        <v>2864.04</v>
+        <v>3027.54</v>
       </c>
       <c r="J179" s="51" t="str">
         <f aca="false">IF($I$179&lt;0,"SHORTFALL",IF($I$179&lt;$E$7,"TIGHT","OK"))</f>
@@ -7140,12 +7151,12 @@
       <c r="E181" s="32"/>
       <c r="F181" s="32"/>
       <c r="G181" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H181" s="32"/>
       <c r="I181" s="34" t="n">
         <f aca="false">$I$179</f>
-        <v>2864.04</v>
+        <v>3027.54</v>
       </c>
       <c r="J181" s="32"/>
       <c r="K181" s="28" t="str">
@@ -7155,19 +7166,19 @@
     </row>
     <row r="182" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C182" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E182" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F182" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G182" s="36" t="s">
         <v>18</v>
@@ -7176,10 +7187,10 @@
         <v>20</v>
       </c>
       <c r="I182" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J182" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7210,7 +7221,7 @@
       </c>
       <c r="I183" s="43" t="n">
         <f aca="false">IF($B183="","",$I$181+SUM($G$183:$G183)-SUM($H$183:$H183))</f>
-        <v>3654.04</v>
+        <v>3817.54</v>
       </c>
       <c r="J183" s="44" t="str">
         <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7245,7 +7256,7 @@
       </c>
       <c r="I184" s="43" t="n">
         <f aca="false">IF($B184="","",$I$181+SUM($G$183:$G184)-SUM($H$183:$H184))</f>
-        <v>3632.94</v>
+        <v>3796.44</v>
       </c>
       <c r="J184" s="44" t="str">
         <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7280,7 +7291,7 @@
       </c>
       <c r="I185" s="43" t="n">
         <f aca="false">IF($B185="","",$I$181+SUM($G$183:$G185)-SUM($H$183:$H185))</f>
-        <v>3612.94</v>
+        <v>3776.44</v>
       </c>
       <c r="J185" s="44" t="str">
         <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7315,7 +7326,7 @@
       </c>
       <c r="I186" s="43" t="n">
         <f aca="false">IF($B186="","",$I$181+SUM($G$183:$G186)-SUM($H$183:$H186))</f>
-        <v>3602.94</v>
+        <v>3766.44</v>
       </c>
       <c r="J186" s="44" t="str">
         <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7350,7 +7361,7 @@
       </c>
       <c r="I187" s="43" t="n">
         <f aca="false">IF($B187="","",$I$181+SUM($G$183:$G187)-SUM($H$183:$H187))</f>
-        <v>3692.94</v>
+        <v>3856.44</v>
       </c>
       <c r="J187" s="44" t="str">
         <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7385,7 +7396,7 @@
       </c>
       <c r="I188" s="43" t="n">
         <f aca="false">IF($B188="","",$I$181+SUM($G$183:$G188)-SUM($H$183:$H188))</f>
-        <v>3687.95</v>
+        <v>3851.45</v>
       </c>
       <c r="J188" s="44" t="str">
         <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7420,7 +7431,7 @@
       </c>
       <c r="I189" s="43" t="n">
         <f aca="false">IF($B189="","",$I$181+SUM($G$183:$G189)-SUM($H$183:$H189))</f>
-        <v>3187.95</v>
+        <v>3351.45</v>
       </c>
       <c r="J189" s="44" t="str">
         <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7534,7 +7545,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B193" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C193" s="46"/>
       <c r="D193" s="46"/>
@@ -7667,7 +7678,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B200" s="47" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C200" s="48"/>
       <c r="D200" s="48"/>
@@ -7683,7 +7694,7 @@
       </c>
       <c r="I200" s="50" t="n">
         <f aca="false">$I$181+$G$200-$H$200</f>
-        <v>3187.95</v>
+        <v>3351.45</v>
       </c>
       <c r="J200" s="51" t="str">
         <f aca="false">IF($I$200&lt;0,"SHORTFALL",IF($I$200&lt;$E$7,"TIGHT","OK"))</f>
@@ -7704,12 +7715,12 @@
       <c r="E202" s="32"/>
       <c r="F202" s="32"/>
       <c r="G202" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H202" s="32"/>
       <c r="I202" s="34" t="n">
         <f aca="false">$I$200</f>
-        <v>3187.95</v>
+        <v>3351.45</v>
       </c>
       <c r="J202" s="32"/>
       <c r="K202" s="28" t="str">
@@ -7719,19 +7730,19 @@
     </row>
     <row r="203" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C203" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D203" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E203" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F203" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G203" s="36" t="s">
         <v>18</v>
@@ -7740,10 +7751,10 @@
         <v>20</v>
       </c>
       <c r="I203" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J203" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7774,7 +7785,7 @@
       </c>
       <c r="I204" s="43" t="n">
         <f aca="false">IF($B204="","",$I$202+SUM($G$204:$G204)-SUM($H$204:$H204))</f>
-        <v>3977.95</v>
+        <v>4141.45</v>
       </c>
       <c r="J204" s="44" t="str">
         <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7809,7 +7820,7 @@
       </c>
       <c r="I205" s="43" t="n">
         <f aca="false">IF($B205="","",$I$202+SUM($G$204:$G205)-SUM($H$204:$H205))</f>
-        <v>3814.45</v>
+        <v>3977.95</v>
       </c>
       <c r="J205" s="44" t="str">
         <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7844,7 +7855,7 @@
       </c>
       <c r="I206" s="43" t="n">
         <f aca="false">IF($B206="","",$I$202+SUM($G$204:$G206)-SUM($H$204:$H206))</f>
-        <v>3811.46</v>
+        <v>3974.96</v>
       </c>
       <c r="J206" s="44" t="str">
         <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7879,7 +7890,7 @@
       </c>
       <c r="I207" s="43" t="n">
         <f aca="false">IF($B207="","",$I$202+SUM($G$204:$G207)-SUM($H$204:$H207))</f>
-        <v>3901.46</v>
+        <v>4064.96</v>
       </c>
       <c r="J207" s="44" t="str">
         <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7914,7 +7925,7 @@
       </c>
       <c r="I208" s="43" t="n">
         <f aca="false">IF($B208="","",$I$202+SUM($G$204:$G208)-SUM($H$204:$H208))</f>
-        <v>3551.46</v>
+        <v>3714.96</v>
       </c>
       <c r="J208" s="44" t="str">
         <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8098,7 +8109,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C214" s="46"/>
       <c r="D214" s="46"/>
@@ -8231,7 +8242,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B221" s="47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C221" s="48"/>
       <c r="D221" s="48"/>
@@ -8247,7 +8258,7 @@
       </c>
       <c r="I221" s="50" t="n">
         <f aca="false">$I$202+$G$221-$H$221</f>
-        <v>3551.46</v>
+        <v>3714.96</v>
       </c>
       <c r="J221" s="51" t="str">
         <f aca="false">IF($I$221&lt;0,"SHORTFALL",IF($I$221&lt;$E$7,"TIGHT","OK"))</f>
@@ -8268,12 +8279,12 @@
       <c r="E223" s="32"/>
       <c r="F223" s="32"/>
       <c r="G223" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H223" s="32"/>
       <c r="I223" s="34" t="n">
         <f aca="false">$I$221</f>
-        <v>3551.46</v>
+        <v>3714.96</v>
       </c>
       <c r="J223" s="32"/>
       <c r="K223" s="28" t="str">
@@ -8283,19 +8294,19 @@
     </row>
     <row r="224" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B224" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E224" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F224" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G224" s="36" t="s">
         <v>18</v>
@@ -8304,10 +8315,10 @@
         <v>20</v>
       </c>
       <c r="I224" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J224" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8338,7 +8349,7 @@
       </c>
       <c r="I225" s="43" t="n">
         <f aca="false">IF($B225="","",$I$223+SUM($G$225:$G225)-SUM($H$225:$H225))</f>
-        <v>4341.46</v>
+        <v>4504.96</v>
       </c>
       <c r="J225" s="44" t="str">
         <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8373,7 +8384,7 @@
       </c>
       <c r="I226" s="43" t="n">
         <f aca="false">IF($B226="","",$I$223+SUM($G$225:$G226)-SUM($H$225:$H226))</f>
-        <v>4170.36</v>
+        <v>4333.86</v>
       </c>
       <c r="J226" s="44" t="str">
         <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8408,7 +8419,7 @@
       </c>
       <c r="I227" s="43" t="n">
         <f aca="false">IF($B227="","",$I$223+SUM($G$225:$G227)-SUM($H$225:$H227))</f>
-        <v>4125.36</v>
+        <v>4288.86</v>
       </c>
       <c r="J227" s="44" t="str">
         <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8443,7 +8454,7 @@
       </c>
       <c r="I228" s="43" t="n">
         <f aca="false">IF($B228="","",$I$223+SUM($G$225:$G228)-SUM($H$225:$H228))</f>
-        <v>4108.37</v>
+        <v>4271.87</v>
       </c>
       <c r="J228" s="44" t="str">
         <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8478,7 +8489,7 @@
       </c>
       <c r="I229" s="43" t="n">
         <f aca="false">IF($B229="","",$I$223+SUM($G$225:$G229)-SUM($H$225:$H229))</f>
-        <v>4198.37</v>
+        <v>4361.87</v>
       </c>
       <c r="J229" s="44" t="str">
         <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8662,7 +8673,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C235" s="46"/>
       <c r="D235" s="46"/>
@@ -8795,7 +8806,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="47" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C242" s="48"/>
       <c r="D242" s="48"/>
@@ -8811,7 +8822,7 @@
       </c>
       <c r="I242" s="50" t="n">
         <f aca="false">$I$223+$G$242-$H$242</f>
-        <v>4198.37</v>
+        <v>4361.87</v>
       </c>
       <c r="J242" s="51" t="str">
         <f aca="false">IF($I$242&lt;0,"SHORTFALL",IF($I$242&lt;$E$7,"TIGHT","OK"))</f>
@@ -8832,12 +8843,12 @@
       <c r="E244" s="32"/>
       <c r="F244" s="32"/>
       <c r="G244" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H244" s="32"/>
       <c r="I244" s="34" t="n">
         <f aca="false">$I$242</f>
-        <v>4198.37</v>
+        <v>4361.87</v>
       </c>
       <c r="J244" s="32"/>
       <c r="K244" s="28" t="str">
@@ -8847,19 +8858,19 @@
     </row>
     <row r="245" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B245" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C245" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D245" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E245" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F245" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G245" s="36" t="s">
         <v>18</v>
@@ -8868,10 +8879,10 @@
         <v>20</v>
       </c>
       <c r="I245" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J245" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8902,7 +8913,7 @@
       </c>
       <c r="I246" s="43" t="n">
         <f aca="false">IF($B246="","",$I$244+SUM($G$246:$G246)-SUM($H$246:$H246))</f>
-        <v>4988.37</v>
+        <v>5151.87</v>
       </c>
       <c r="J246" s="44" t="str">
         <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8937,7 +8948,7 @@
       </c>
       <c r="I247" s="43" t="n">
         <f aca="false">IF($B247="","",$I$244+SUM($G$246:$G247)-SUM($H$246:$H247))</f>
-        <v>4974.67</v>
+        <v>5138.17</v>
       </c>
       <c r="J247" s="44" t="str">
         <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8947,7 +8958,7 @@
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B248" s="11" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(12003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="C248" s="38" t="n">
         <f aca="false">IF($B248="","",INDEX(Schedule!$G$4:$G$483,MATCH(12003,Schedule!$K$4:$K$483,0)))</f>
@@ -8972,7 +8983,7 @@
       </c>
       <c r="I248" s="43" t="n">
         <f aca="false">IF($B248="","",$I$244+SUM($G$246:$G248)-SUM($H$246:$H248))</f>
-        <v>4930.8</v>
+        <v>5094.3</v>
       </c>
       <c r="J248" s="44" t="str">
         <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9007,7 +9018,7 @@
       </c>
       <c r="I249" s="43" t="n">
         <f aca="false">IF($B249="","",$I$244+SUM($G$246:$G249)-SUM($H$246:$H249))</f>
-        <v>5020.8</v>
+        <v>5184.3</v>
       </c>
       <c r="J249" s="44" t="str">
         <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9226,7 +9237,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B256" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C256" s="46"/>
       <c r="D256" s="46"/>
@@ -9359,7 +9370,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B263" s="47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C263" s="48"/>
       <c r="D263" s="48"/>
@@ -9375,7 +9386,7 @@
       </c>
       <c r="I263" s="50" t="n">
         <f aca="false">$I$244+$G$263-$H$263</f>
-        <v>5020.8</v>
+        <v>5184.3</v>
       </c>
       <c r="J263" s="51" t="str">
         <f aca="false">IF($I$263&lt;0,"SHORTFALL",IF($I$263&lt;$E$7,"TIGHT","OK"))</f>
@@ -9396,12 +9407,12 @@
       <c r="E265" s="32"/>
       <c r="F265" s="32"/>
       <c r="G265" s="33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H265" s="32"/>
       <c r="I265" s="34" t="n">
         <f aca="false">$I$263</f>
-        <v>5020.8</v>
+        <v>5184.3</v>
       </c>
       <c r="J265" s="32"/>
       <c r="K265" s="28" t="str">
@@ -9411,19 +9422,19 @@
     </row>
     <row r="266" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E266" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F266" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G266" s="36" t="s">
         <v>18</v>
@@ -9432,10 +9443,10 @@
         <v>20</v>
       </c>
       <c r="I266" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J266" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9466,7 +9477,7 @@
       </c>
       <c r="I267" s="43" t="n">
         <f aca="false">IF($B267="","",$I$265+SUM($G$267:$G267)-SUM($H$267:$H267))</f>
-        <v>5810.8</v>
+        <v>5974.3</v>
       </c>
       <c r="J267" s="44" t="str">
         <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9501,7 +9512,7 @@
       </c>
       <c r="I268" s="43" t="n">
         <f aca="false">IF($B268="","",$I$265+SUM($G$267:$G268)-SUM($H$267:$H268))</f>
-        <v>5460.8</v>
+        <v>5624.3</v>
       </c>
       <c r="J268" s="44" t="str">
         <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9536,7 +9547,7 @@
       </c>
       <c r="I269" s="43" t="n">
         <f aca="false">IF($B269="","",$I$265+SUM($G$267:$G269)-SUM($H$267:$H269))</f>
-        <v>5310.8</v>
+        <v>5474.3</v>
       </c>
       <c r="J269" s="44" t="str">
         <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9571,7 +9582,7 @@
       </c>
       <c r="I270" s="43" t="n">
         <f aca="false">IF($B270="","",$I$265+SUM($G$267:$G270)-SUM($H$267:$H270))</f>
-        <v>5167.43</v>
+        <v>5330.93</v>
       </c>
       <c r="J270" s="44" t="str">
         <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9606,7 +9617,7 @@
       </c>
       <c r="I271" s="43" t="n">
         <f aca="false">IF($B271="","",$I$265+SUM($G$267:$G271)-SUM($H$267:$H271))</f>
-        <v>5257.43</v>
+        <v>5420.93</v>
       </c>
       <c r="J271" s="44" t="str">
         <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9641,7 +9652,7 @@
       </c>
       <c r="I272" s="43" t="n">
         <f aca="false">IF($B272="","",$I$265+SUM($G$267:$G272)-SUM($H$267:$H272))</f>
-        <v>5236.33</v>
+        <v>5399.83</v>
       </c>
       <c r="J272" s="44" t="str">
         <f aca="true">IF($B272="","",IF($F272&lt;&gt;"","PAID",IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9676,7 +9687,7 @@
       </c>
       <c r="I273" s="43" t="n">
         <f aca="false">IF($B273="","",$I$265+SUM($G$267:$G273)-SUM($H$267:$H273))</f>
-        <v>5216.33</v>
+        <v>5379.83</v>
       </c>
       <c r="J273" s="44" t="str">
         <f aca="true">IF($B273="","",IF($F273&lt;&gt;"","PAID",IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9711,7 +9722,7 @@
       </c>
       <c r="I274" s="43" t="n">
         <f aca="false">IF($B274="","",$I$265+SUM($G$267:$G274)-SUM($H$267:$H274))</f>
-        <v>5206.33</v>
+        <v>5369.83</v>
       </c>
       <c r="J274" s="44" t="str">
         <f aca="true">IF($B274="","",IF($F274&lt;&gt;"","PAID",IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9790,7 +9801,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="45" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C277" s="46"/>
       <c r="D277" s="46"/>
@@ -9923,7 +9934,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B284" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C284" s="48"/>
       <c r="D284" s="48"/>
@@ -9939,7 +9950,7 @@
       </c>
       <c r="I284" s="50" t="n">
         <f aca="false">$I$265+$G$284-$H$284</f>
-        <v>5206.33</v>
+        <v>5369.83</v>
       </c>
       <c r="J284" s="51" t="str">
         <f aca="false">IF($I$284&lt;0,"SHORTFALL",IF($I$284&lt;$E$7,"TIGHT","OK"))</f>
@@ -10004,28 +10015,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="52" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
       <c r="E4" s="53" t="n">
         <f aca="false">MIN($I$13:$I$25)</f>
-        <v>-5.31999999999999</v>
+        <v>158.18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="52"/>
       <c r="D5" s="52"/>
@@ -10040,13 +10051,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="52" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C6" s="52"/>
       <c r="D6" s="52"/>
       <c r="E6" s="54" t="str">
         <f aca="false">IF(MIN($K$13:$K$25)=999,"None — you stay above zero all 13 weeks","Week "&amp;MIN($K$13:$K$25)&amp;"  ("&amp;TEXT(INDEX($C$13:$C$25,MATCH(MIN($K$13:$K$25),$B$13:$B$25,0)),"mmm d, yyyy")&amp;")")</f>
-        <v>Week 1  (Aug 7, 2026)</v>
+        <v>None — you stay above zero all 13 weeks</v>
       </c>
       <c r="F6" s="54"/>
       <c r="G6" s="54"/>
@@ -10055,7 +10066,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="52" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="52"/>
       <c r="D7" s="52"/>
@@ -10066,67 +10077,67 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="52" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C8" s="52"/>
       <c r="D8" s="52"/>
       <c r="E8" s="55" t="n">
         <f aca="false">SUM($F$13:$F$25)+SUM($G$13:$G$25)</f>
-        <v>5514.84</v>
+        <v>5351.34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="52" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="52"/>
       <c r="E9" s="53" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5135.16</v>
+        <v>5298.66</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="52" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C10" s="52"/>
       <c r="D10" s="52"/>
       <c r="E10" s="53" t="n">
         <f aca="false">$I$25</f>
-        <v>5206.33</v>
+        <v>5369.83</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10147,7 +10158,7 @@
       </c>
       <c r="F13" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$H$15:$H$24)</f>
-        <v>166.49</v>
+        <v>2.99</v>
       </c>
       <c r="G13" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$H$26:$H$31)</f>
@@ -10155,19 +10166,19 @@
       </c>
       <c r="H13" s="59" t="n">
         <f aca="false">$E13-$F13-$G13</f>
-        <v>-76.49</v>
+        <v>87.01</v>
       </c>
       <c r="I13" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$32</f>
-        <v>-5.31999999999999</v>
+        <v>158.18</v>
       </c>
       <c r="J13" s="60" t="str">
         <f aca="false">IF($I13&lt;0,"SHORTFALL",IF($I13&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
-        <v>SHORTFALL</v>
+        <v>TIGHT</v>
       </c>
       <c r="K13" s="29" t="n">
         <f aca="false">IF($I13&lt;0,$B13,999)</f>
-        <v>1</v>
+        <v>999</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10180,7 +10191,7 @@
       </c>
       <c r="D14" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$34</f>
-        <v>-5.31999999999999</v>
+        <v>158.18</v>
       </c>
       <c r="E14" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$36:$G$52)</f>
@@ -10200,7 +10211,7 @@
       </c>
       <c r="I14" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$53</f>
-        <v>291.59</v>
+        <v>455.09</v>
       </c>
       <c r="J14" s="65" t="str">
         <f aca="false">IF($I14&lt;0,"SHORTFALL",IF($I14&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10221,7 +10232,7 @@
       </c>
       <c r="D15" s="57" t="n">
         <f aca="false">'Cash Flow'!$I$55</f>
-        <v>291.59</v>
+        <v>455.09</v>
       </c>
       <c r="E15" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$G$57:$G$73)</f>
@@ -10241,7 +10252,7 @@
       </c>
       <c r="I15" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$74</f>
-        <v>1114.02</v>
+        <v>1277.52</v>
       </c>
       <c r="J15" s="60" t="str">
         <f aca="false">IF($I15&lt;0,"SHORTFALL",IF($I15&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10262,7 +10273,7 @@
       </c>
       <c r="D16" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$76</f>
-        <v>1114.02</v>
+        <v>1277.52</v>
       </c>
       <c r="E16" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$78:$G$94)</f>
@@ -10282,7 +10293,7 @@
       </c>
       <c r="I16" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$95</f>
-        <v>1350.65</v>
+        <v>1514.15</v>
       </c>
       <c r="J16" s="65" t="str">
         <f aca="false">IF($I16&lt;0,"SHORTFALL",IF($I16&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10303,7 +10314,7 @@
       </c>
       <c r="D17" s="57" t="n">
         <f aca="false">'Cash Flow'!$I$97</f>
-        <v>1350.65</v>
+        <v>1514.15</v>
       </c>
       <c r="E17" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$G$99:$G$115)</f>
@@ -10323,7 +10334,7 @@
       </c>
       <c r="I17" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$116</f>
-        <v>1511.06</v>
+        <v>1674.56</v>
       </c>
       <c r="J17" s="60" t="str">
         <f aca="false">IF($I17&lt;0,"SHORTFALL",IF($I17&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10344,7 +10355,7 @@
       </c>
       <c r="D18" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$118</f>
-        <v>1511.06</v>
+        <v>1674.56</v>
       </c>
       <c r="E18" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$120:$G$136)</f>
@@ -10364,7 +10375,7 @@
       </c>
       <c r="I18" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$137</f>
-        <v>1821.97</v>
+        <v>1985.47</v>
       </c>
       <c r="J18" s="65" t="str">
         <f aca="false">IF($I18&lt;0,"SHORTFALL",IF($I18&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10385,7 +10396,7 @@
       </c>
       <c r="D19" s="57" t="n">
         <f aca="false">'Cash Flow'!$I$139</f>
-        <v>1821.97</v>
+        <v>1985.47</v>
       </c>
       <c r="E19" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$G$141:$G$157)</f>
@@ -10405,7 +10416,7 @@
       </c>
       <c r="I19" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$158</f>
-        <v>2684.98</v>
+        <v>2848.48</v>
       </c>
       <c r="J19" s="60" t="str">
         <f aca="false">IF($I19&lt;0,"SHORTFALL",IF($I19&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10426,7 +10437,7 @@
       </c>
       <c r="D20" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$160</f>
-        <v>2684.98</v>
+        <v>2848.48</v>
       </c>
       <c r="E20" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$162:$G$178)</f>
@@ -10446,7 +10457,7 @@
       </c>
       <c r="I20" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$179</f>
-        <v>2864.04</v>
+        <v>3027.54</v>
       </c>
       <c r="J20" s="65" t="str">
         <f aca="false">IF($I20&lt;0,"SHORTFALL",IF($I20&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10467,7 +10478,7 @@
       </c>
       <c r="D21" s="57" t="n">
         <f aca="false">'Cash Flow'!$I$181</f>
-        <v>2864.04</v>
+        <v>3027.54</v>
       </c>
       <c r="E21" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$G$183:$G$199)</f>
@@ -10487,7 +10498,7 @@
       </c>
       <c r="I21" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$200</f>
-        <v>3187.95</v>
+        <v>3351.45</v>
       </c>
       <c r="J21" s="60" t="str">
         <f aca="false">IF($I21&lt;0,"SHORTFALL",IF($I21&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10508,7 +10519,7 @@
       </c>
       <c r="D22" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$202</f>
-        <v>3187.95</v>
+        <v>3351.45</v>
       </c>
       <c r="E22" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$204:$G$220)</f>
@@ -10528,7 +10539,7 @@
       </c>
       <c r="I22" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$221</f>
-        <v>3551.46</v>
+        <v>3714.96</v>
       </c>
       <c r="J22" s="65" t="str">
         <f aca="false">IF($I22&lt;0,"SHORTFALL",IF($I22&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10549,7 +10560,7 @@
       </c>
       <c r="D23" s="57" t="n">
         <f aca="false">'Cash Flow'!$I$223</f>
-        <v>3551.46</v>
+        <v>3714.96</v>
       </c>
       <c r="E23" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$G$225:$G$241)</f>
@@ -10569,7 +10580,7 @@
       </c>
       <c r="I23" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$242</f>
-        <v>4198.37</v>
+        <v>4361.87</v>
       </c>
       <c r="J23" s="60" t="str">
         <f aca="false">IF($I23&lt;0,"SHORTFALL",IF($I23&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10590,7 +10601,7 @@
       </c>
       <c r="D24" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$244</f>
-        <v>4198.37</v>
+        <v>4361.87</v>
       </c>
       <c r="E24" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$246:$G$262)</f>
@@ -10610,7 +10621,7 @@
       </c>
       <c r="I24" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$263</f>
-        <v>5020.8</v>
+        <v>5184.3</v>
       </c>
       <c r="J24" s="65" t="str">
         <f aca="false">IF($I24&lt;0,"SHORTFALL",IF($I24&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10631,7 +10642,7 @@
       </c>
       <c r="D25" s="57" t="n">
         <f aca="false">'Cash Flow'!$I$265</f>
-        <v>5020.8</v>
+        <v>5184.3</v>
       </c>
       <c r="E25" s="58" t="n">
         <f aca="false">SUM('Cash Flow'!$G$267:$G$283)</f>
@@ -10651,7 +10662,7 @@
       </c>
       <c r="I25" s="59" t="n">
         <f aca="false">'Cash Flow'!$I$284</f>
-        <v>5206.33</v>
+        <v>5369.83</v>
       </c>
       <c r="J25" s="60" t="str">
         <f aca="false">IF($I25&lt;0,"SHORTFALL",IF($I25&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10664,10 +10675,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="51" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C26" s="66" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D26" s="67" t="n">
         <f aca="false">$D$13</f>
@@ -10679,7 +10690,7 @@
       </c>
       <c r="F26" s="49" t="n">
         <f aca="false">SUM($F$13:$F$25)</f>
-        <v>5514.84</v>
+        <v>5351.34</v>
       </c>
       <c r="G26" s="49" t="n">
         <f aca="false">SUM($G$13:$G$25)</f>
@@ -10687,17 +10698,17 @@
       </c>
       <c r="H26" s="67" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5135.16</v>
+        <v>5298.66</v>
       </c>
       <c r="I26" s="67" t="n">
         <f aca="false">$I$25</f>
-        <v>5206.33</v>
+        <v>5369.83</v>
       </c>
       <c r="J26" s="48"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="68" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C28" s="68"/>
       <c r="D28" s="68"/>
@@ -10767,47 +10778,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="69" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="70" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C3" s="70" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D3" s="70" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="70" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F3" s="70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G3" s="70" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H3" s="70" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I3" s="70" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J3" s="70" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K3" s="70" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10851,7 +10862,7 @@
       </c>
       <c r="K4" s="72" t="n">
         <f aca="false">IF($H4=1,$I4*1000+COUNTIFS($I$4:$I$483,$I4,$J$4:$J$483,"&lt;"&amp;$J4)+1,"")</f>
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15759,11 +15770,11 @@
       </c>
       <c r="F116" s="74" t="n">
         <f aca="false">IF($C116="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*0,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*0,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,0),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$12="One Time",IF(1=1,Recurring!$F$12,""),""))))))</f>
-        <v>46244</v>
+        <v>46275</v>
       </c>
       <c r="G116" s="74" t="n">
         <f aca="false">IF($F116="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F116,2)=6,$F116-1,IF(WEEKDAY($F116,2)=7,$F116-2,$F116)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F116,2)=6,$F116+2,IF(WEEKDAY($F116,2)=7,$F116+1,$F116)),$F116)))</f>
-        <v>46244</v>
+        <v>46275</v>
       </c>
       <c r="H116" s="75" t="n">
         <f aca="false">IF($G116="",0,IF(AND($G116&gt;='Cash Flow'!$E$6,$G116&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15771,15 +15782,15 @@
       </c>
       <c r="I116" s="75" t="n">
         <f aca="false">IF($H116=1,INT(($G116-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J116" s="72" t="n">
         <f aca="false">IF($H116=1,$G116*10000+ROW(),"")</f>
-        <v>462440116</v>
+        <v>462750116</v>
       </c>
       <c r="K116" s="72" t="n">
         <f aca="false">IF($H116=1,$I116*1000+COUNTIFS($I$4:$I$483,$I116,$J$4:$J$483,"&lt;"&amp;$J116)+1,"")</f>
-        <v>1001</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15803,11 +15814,11 @@
       </c>
       <c r="F117" s="74" t="n">
         <f aca="false">IF($C117="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*1,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*1,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,1),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$12="One Time",IF(2=1,Recurring!$F$12,""),""))))))</f>
-        <v>46275</v>
+        <v>46305</v>
       </c>
       <c r="G117" s="74" t="n">
         <f aca="false">IF($F117="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F117,2)=6,$F117-1,IF(WEEKDAY($F117,2)=7,$F117-2,$F117)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F117,2)=6,$F117+2,IF(WEEKDAY($F117,2)=7,$F117+1,$F117)),$F117)))</f>
-        <v>46275</v>
+        <v>46305</v>
       </c>
       <c r="H117" s="75" t="n">
         <f aca="false">IF($G117="",0,IF(AND($G117&gt;='Cash Flow'!$E$6,$G117&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15815,15 +15826,15 @@
       </c>
       <c r="I117" s="75" t="n">
         <f aca="false">IF($H117=1,INT(($G117-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J117" s="72" t="n">
         <f aca="false">IF($H117=1,$G117*10000+ROW(),"")</f>
-        <v>462750117</v>
+        <v>463050117</v>
       </c>
       <c r="K117" s="72" t="n">
         <f aca="false">IF($H117=1,$I117*1000+COUNTIFS($I$4:$I$483,$I117,$J$4:$J$483,"&lt;"&amp;$J117)+1,"")</f>
-        <v>5008</v>
+        <v>10002</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15847,27 +15858,27 @@
       </c>
       <c r="F118" s="74" t="n">
         <f aca="false">IF($C118="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*2,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*2,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,2),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$12="One Time",IF(3=1,Recurring!$F$12,""),""))))))</f>
-        <v>46305</v>
+        <v>46336</v>
       </c>
       <c r="G118" s="74" t="n">
         <f aca="false">IF($F118="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F118,2)=6,$F118-1,IF(WEEKDAY($F118,2)=7,$F118-2,$F118)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F118,2)=6,$F118+2,IF(WEEKDAY($F118,2)=7,$F118+1,$F118)),$F118)))</f>
-        <v>46305</v>
+        <v>46336</v>
       </c>
       <c r="H118" s="75" t="n">
         <f aca="false">IF($G118="",0,IF(AND($G118&gt;='Cash Flow'!$E$6,$G118&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="I118" s="75" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="75" t="str">
         <f aca="false">IF($H118=1,INT(($G118-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>10</v>
-      </c>
-      <c r="J118" s="72" t="n">
+        <v/>
+      </c>
+      <c r="J118" s="72" t="str">
         <f aca="false">IF($H118=1,$G118*10000+ROW(),"")</f>
-        <v>463050118</v>
-      </c>
-      <c r="K118" s="72" t="n">
+        <v/>
+      </c>
+      <c r="K118" s="72" t="str">
         <f aca="false">IF($H118=1,$I118*1000+COUNTIFS($I$4:$I$483,$I118,$J$4:$J$483,"&lt;"&amp;$J118)+1,"")</f>
-        <v>10002</v>
+        <v/>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15891,11 +15902,11 @@
       </c>
       <c r="F119" s="74" t="n">
         <f aca="false">IF($C119="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*3,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*3,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,3),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$12="One Time",IF(4=1,Recurring!$F$12,""),""))))))</f>
-        <v>46336</v>
+        <v>46366</v>
       </c>
       <c r="G119" s="74" t="n">
         <f aca="false">IF($F119="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F119,2)=6,$F119-1,IF(WEEKDAY($F119,2)=7,$F119-2,$F119)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F119,2)=6,$F119+2,IF(WEEKDAY($F119,2)=7,$F119+1,$F119)),$F119)))</f>
-        <v>46336</v>
+        <v>46366</v>
       </c>
       <c r="H119" s="75" t="n">
         <f aca="false">IF($G119="",0,IF(AND($G119&gt;='Cash Flow'!$E$6,$G119&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15935,11 +15946,11 @@
       </c>
       <c r="F120" s="74" t="n">
         <f aca="false">IF($C120="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*4,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*4,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,4),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$12="One Time",IF(5=1,Recurring!$F$12,""),""))))))</f>
-        <v>46366</v>
+        <v>46397</v>
       </c>
       <c r="G120" s="74" t="n">
         <f aca="false">IF($F120="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F120,2)=6,$F120-1,IF(WEEKDAY($F120,2)=7,$F120-2,$F120)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F120,2)=6,$F120+2,IF(WEEKDAY($F120,2)=7,$F120+1,$F120)),$F120)))</f>
-        <v>46366</v>
+        <v>46397</v>
       </c>
       <c r="H120" s="75" t="n">
         <f aca="false">IF($G120="",0,IF(AND($G120&gt;='Cash Flow'!$E$6,$G120&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -15979,11 +15990,11 @@
       </c>
       <c r="F121" s="74" t="n">
         <f aca="false">IF($C121="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*5,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*5,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,5),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$12="One Time",IF(6=1,Recurring!$F$12,""),""))))))</f>
-        <v>46397</v>
+        <v>46428</v>
       </c>
       <c r="G121" s="74" t="n">
         <f aca="false">IF($F121="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F121,2)=6,$F121-1,IF(WEEKDAY($F121,2)=7,$F121-2,$F121)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F121,2)=6,$F121+2,IF(WEEKDAY($F121,2)=7,$F121+1,$F121)),$F121)))</f>
-        <v>46397</v>
+        <v>46428</v>
       </c>
       <c r="H121" s="75" t="n">
         <f aca="false">IF($G121="",0,IF(AND($G121&gt;='Cash Flow'!$E$6,$G121&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16023,11 +16034,11 @@
       </c>
       <c r="F122" s="74" t="n">
         <f aca="false">IF($C122="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*6,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*6,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,6),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$12="One Time",IF(7=1,Recurring!$F$12,""),""))))))</f>
-        <v>46428</v>
+        <v>46456</v>
       </c>
       <c r="G122" s="74" t="n">
         <f aca="false">IF($F122="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F122,2)=6,$F122-1,IF(WEEKDAY($F122,2)=7,$F122-2,$F122)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F122,2)=6,$F122+2,IF(WEEKDAY($F122,2)=7,$F122+1,$F122)),$F122)))</f>
-        <v>46428</v>
+        <v>46456</v>
       </c>
       <c r="H122" s="75" t="n">
         <f aca="false">IF($G122="",0,IF(AND($G122&gt;='Cash Flow'!$E$6,$G122&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16067,11 +16078,11 @@
       </c>
       <c r="F123" s="74" t="n">
         <f aca="false">IF($C123="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*7,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*7,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,7),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$12="One Time",IF(8=1,Recurring!$F$12,""),""))))))</f>
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="G123" s="74" t="n">
         <f aca="false">IF($F123="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F123,2)=6,$F123-1,IF(WEEKDAY($F123,2)=7,$F123-2,$F123)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F123,2)=6,$F123+2,IF(WEEKDAY($F123,2)=7,$F123+1,$F123)),$F123)))</f>
-        <v>46456</v>
+        <v>46487</v>
       </c>
       <c r="H123" s="75" t="n">
         <f aca="false">IF($G123="",0,IF(AND($G123&gt;='Cash Flow'!$E$6,$G123&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16111,11 +16122,11 @@
       </c>
       <c r="F124" s="74" t="n">
         <f aca="false">IF($C124="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*8,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*8,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,8),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$12="One Time",IF(9=1,Recurring!$F$12,""),""))))))</f>
-        <v>46487</v>
+        <v>46517</v>
       </c>
       <c r="G124" s="74" t="n">
         <f aca="false">IF($F124="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F124,2)=6,$F124-1,IF(WEEKDAY($F124,2)=7,$F124-2,$F124)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F124,2)=6,$F124+2,IF(WEEKDAY($F124,2)=7,$F124+1,$F124)),$F124)))</f>
-        <v>46487</v>
+        <v>46517</v>
       </c>
       <c r="H124" s="75" t="n">
         <f aca="false">IF($G124="",0,IF(AND($G124&gt;='Cash Flow'!$E$6,$G124&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16155,11 +16166,11 @@
       </c>
       <c r="F125" s="74" t="n">
         <f aca="false">IF($C125="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*9,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*9,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,9),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$12="One Time",IF(10=1,Recurring!$F$12,""),""))))))</f>
-        <v>46517</v>
+        <v>46548</v>
       </c>
       <c r="G125" s="74" t="n">
         <f aca="false">IF($F125="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F125,2)=6,$F125-1,IF(WEEKDAY($F125,2)=7,$F125-2,$F125)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F125,2)=6,$F125+2,IF(WEEKDAY($F125,2)=7,$F125+1,$F125)),$F125)))</f>
-        <v>46517</v>
+        <v>46548</v>
       </c>
       <c r="H125" s="75" t="n">
         <f aca="false">IF($G125="",0,IF(AND($G125&gt;='Cash Flow'!$E$6,$G125&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16199,11 +16210,11 @@
       </c>
       <c r="F126" s="74" t="n">
         <f aca="false">IF($C126="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*10,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*10,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,10),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$12="One Time",IF(11=1,Recurring!$F$12,""),""))))))</f>
-        <v>46548</v>
+        <v>46578</v>
       </c>
       <c r="G126" s="74" t="n">
         <f aca="false">IF($F126="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F126,2)=6,$F126-1,IF(WEEKDAY($F126,2)=7,$F126-2,$F126)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F126,2)=6,$F126+2,IF(WEEKDAY($F126,2)=7,$F126+1,$F126)),$F126)))</f>
-        <v>46548</v>
+        <v>46578</v>
       </c>
       <c r="H126" s="75" t="n">
         <f aca="false">IF($G126="",0,IF(AND($G126&gt;='Cash Flow'!$E$6,$G126&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16243,11 +16254,11 @@
       </c>
       <c r="F127" s="74" t="n">
         <f aca="false">IF($C127="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*11,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*11,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,11),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$12="One Time",IF(12=1,Recurring!$F$12,""),""))))))</f>
-        <v>46578</v>
+        <v>46609</v>
       </c>
       <c r="G127" s="74" t="n">
         <f aca="false">IF($F127="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F127,2)=6,$F127-1,IF(WEEKDAY($F127,2)=7,$F127-2,$F127)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F127,2)=6,$F127+2,IF(WEEKDAY($F127,2)=7,$F127+1,$F127)),$F127)))</f>
-        <v>46578</v>
+        <v>46609</v>
       </c>
       <c r="H127" s="75" t="n">
         <f aca="false">IF($G127="",0,IF(AND($G127&gt;='Cash Flow'!$E$6,$G127&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16287,11 +16298,11 @@
       </c>
       <c r="F128" s="74" t="n">
         <f aca="false">IF($C128="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*12,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*12,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,12),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$12="One Time",IF(13=1,Recurring!$F$12,""),""))))))</f>
-        <v>46609</v>
+        <v>46640</v>
       </c>
       <c r="G128" s="74" t="n">
         <f aca="false">IF($F128="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F128,2)=6,$F128-1,IF(WEEKDAY($F128,2)=7,$F128-2,$F128)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F128,2)=6,$F128+2,IF(WEEKDAY($F128,2)=7,$F128+1,$F128)),$F128)))</f>
-        <v>46609</v>
+        <v>46640</v>
       </c>
       <c r="H128" s="75" t="n">
         <f aca="false">IF($G128="",0,IF(AND($G128&gt;='Cash Flow'!$E$6,$G128&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16331,11 +16342,11 @@
       </c>
       <c r="F129" s="74" t="n">
         <f aca="false">IF($C129="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*13,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*13,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,13),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$12="One Time",IF(14=1,Recurring!$F$12,""),""))))))</f>
-        <v>46640</v>
+        <v>46670</v>
       </c>
       <c r="G129" s="74" t="n">
         <f aca="false">IF($F129="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F129,2)=6,$F129-1,IF(WEEKDAY($F129,2)=7,$F129-2,$F129)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F129,2)=6,$F129+2,IF(WEEKDAY($F129,2)=7,$F129+1,$F129)),$F129)))</f>
-        <v>46640</v>
+        <v>46670</v>
       </c>
       <c r="H129" s="75" t="n">
         <f aca="false">IF($G129="",0,IF(AND($G129&gt;='Cash Flow'!$E$6,$G129&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16375,11 +16386,11 @@
       </c>
       <c r="F130" s="74" t="n">
         <f aca="false">IF($C130="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*14,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*14,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,14),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$12="One Time",IF(15=1,Recurring!$F$12,""),""))))))</f>
-        <v>46670</v>
+        <v>46701</v>
       </c>
       <c r="G130" s="74" t="n">
         <f aca="false">IF($F130="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F130,2)=6,$F130-1,IF(WEEKDAY($F130,2)=7,$F130-2,$F130)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F130,2)=6,$F130+2,IF(WEEKDAY($F130,2)=7,$F130+1,$F130)),$F130)))</f>
-        <v>46670</v>
+        <v>46701</v>
       </c>
       <c r="H130" s="75" t="n">
         <f aca="false">IF($G130="",0,IF(AND($G130&gt;='Cash Flow'!$E$6,$G130&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16419,11 +16430,11 @@
       </c>
       <c r="F131" s="74" t="n">
         <f aca="false">IF($C131="","",IF(Recurring!$E$12="Weekly",Recurring!$F$12+7*15,IF(Recurring!$E$12="Every 2 Weeks",Recurring!$F$12+14*15,IF(Recurring!$E$12="Monthly",EDATE(Recurring!$F$12,15),IF(Recurring!$E$12="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$12,INT((IF(DAY(Recurring!$F$12)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$12="One Time",IF(16=1,Recurring!$F$12,""),""))))))</f>
-        <v>46701</v>
+        <v>46731</v>
       </c>
       <c r="G131" s="74" t="n">
         <f aca="false">IF($F131="","",IF(Recurring!$G$12="Move Before",IF(WEEKDAY($F131,2)=6,$F131-1,IF(WEEKDAY($F131,2)=7,$F131-2,$F131)),IF(Recurring!$G$12="Move After",IF(WEEKDAY($F131,2)=6,$F131+2,IF(WEEKDAY($F131,2)=7,$F131+1,$F131)),$F131)))</f>
-        <v>46701</v>
+        <v>46731</v>
       </c>
       <c r="H131" s="75" t="n">
         <f aca="false">IF($G131="",0,IF(AND($G131&gt;='Cash Flow'!$E$6,$G131&lt;'Cash Flow'!$E$6+91),1,0))</f>
@@ -16483,7 +16494,7 @@
       </c>
       <c r="K132" s="72" t="n">
         <f aca="false">IF($H132=1,$I132*1000+COUNTIFS($I$4:$I$483,$I132,$J$4:$J$483,"&lt;"&amp;$J132)+1,"")</f>
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -20675,7 +20686,7 @@
       </c>
       <c r="C228" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D228" s="72" t="str">
         <f aca="false">IF($C228="","",Recurring!$C$19)</f>
@@ -20719,7 +20730,7 @@
       </c>
       <c r="C229" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D229" s="72" t="str">
         <f aca="false">IF($C229="","",Recurring!$C$19)</f>
@@ -20763,7 +20774,7 @@
       </c>
       <c r="C230" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D230" s="72" t="str">
         <f aca="false">IF($C230="","",Recurring!$C$19)</f>
@@ -20807,7 +20818,7 @@
       </c>
       <c r="C231" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D231" s="72" t="str">
         <f aca="false">IF($C231="","",Recurring!$C$19)</f>
@@ -20851,7 +20862,7 @@
       </c>
       <c r="C232" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D232" s="72" t="str">
         <f aca="false">IF($C232="","",Recurring!$C$19)</f>
@@ -20895,7 +20906,7 @@
       </c>
       <c r="C233" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D233" s="72" t="str">
         <f aca="false">IF($C233="","",Recurring!$C$19)</f>
@@ -20939,7 +20950,7 @@
       </c>
       <c r="C234" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D234" s="72" t="str">
         <f aca="false">IF($C234="","",Recurring!$C$19)</f>
@@ -20983,7 +20994,7 @@
       </c>
       <c r="C235" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D235" s="72" t="str">
         <f aca="false">IF($C235="","",Recurring!$C$19)</f>
@@ -21027,7 +21038,7 @@
       </c>
       <c r="C236" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D236" s="72" t="str">
         <f aca="false">IF($C236="","",Recurring!$C$19)</f>
@@ -21071,7 +21082,7 @@
       </c>
       <c r="C237" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D237" s="72" t="str">
         <f aca="false">IF($C237="","",Recurring!$C$19)</f>
@@ -21115,7 +21126,7 @@
       </c>
       <c r="C238" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D238" s="72" t="str">
         <f aca="false">IF($C238="","",Recurring!$C$19)</f>
@@ -21159,7 +21170,7 @@
       </c>
       <c r="C239" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D239" s="72" t="str">
         <f aca="false">IF($C239="","",Recurring!$C$19)</f>
@@ -21203,7 +21214,7 @@
       </c>
       <c r="C240" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D240" s="72" t="str">
         <f aca="false">IF($C240="","",Recurring!$C$19)</f>
@@ -21247,7 +21258,7 @@
       </c>
       <c r="C241" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D241" s="72" t="str">
         <f aca="false">IF($C241="","",Recurring!$C$19)</f>
@@ -21291,7 +21302,7 @@
       </c>
       <c r="C242" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D242" s="72" t="str">
         <f aca="false">IF($C242="","",Recurring!$C$19)</f>
@@ -21335,7 +21346,7 @@
       </c>
       <c r="C243" s="72" t="str">
         <f aca="false">IF(OR(Recurring!$B$19="",Recurring!$H$19&lt;&gt;"Yes",Recurring!$D$19=""),"",Recurring!$B$19)</f>
-        <v>Central Maine Power: Property</v>
+        <v>Central Maine Power: Payment Plan</v>
       </c>
       <c r="D243" s="72" t="str">
         <f aca="false">IF($C243="","",Recurring!$C$19)</f>

--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Cash Flow'!$A$1:$K$284</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$45</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$46</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Recurring!$A$1:$J$38</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Recurring!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$J$28</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="167">
   <si>
     <t xml:space="preserve">WEEKLY CASH FLOW SURVIVAL WORKSHEET</t>
   </si>
@@ -201,7 +201,10 @@
     <t xml:space="preserve">Amounts are entered as positive numbers. The Type column (Income or Expense) decides the sign, so a $90 paycheck is Type = Income, amount 90.</t>
   </si>
   <si>
-    <t xml:space="preserve">The sheet opens on Fri Aug 7, 2026 with $71.17 already in hand. Everything that had already moved by that morning was rolled forward to its next occurrence, so the projection never counts the same money twice: the Compunnel paycheck (now Aug 14), Upstart and Google One (now Sep 7), and Bruno's, Apple: Claude, OpenAI and Obsidian. Confirmed with the user on Aug 7, 2026.</t>
+    <t xml:space="preserve">Next Due Date means the next occurrence you have NOT paid yet. If that date is already behind you the transaction still appears, in Week 1, marked PAST DUE — an unpaid bill never drops off this sheet just because its date has passed. Only roll a date forward once the money has actually moved.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The sheet opens on Fri Aug 7, 2026 with $71.17 already in hand. Confirmed as already settled and therefore rolled forward: the Compunnel paycheck (now Aug 14), Upstart and Google One (now Sep 7), Bruno's (Aug 12), and the $163.50 Central Maine Power bill (now Sep 10, covered by the payment plan through August). Apple: Claude, OpenAI and Obsidian keep their Aug 4 and Aug 5 dates because they are still unpaid.</t>
   </si>
   <si>
     <t xml:space="preserve">Progressive Insurance ($143.37) was cut off at the bottom of the third screenshot, so its due date is set to Aug 31, 2026. Correct it on the Recurring tab if that is wrong.</t>
@@ -345,7 +348,7 @@
     <t xml:space="preserve">Insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Next Due Date = the next time it happens on or after your cash flow start date. Set Active to No to park a transaction without deleting it.</t>
+    <t xml:space="preserve">Next Due Date = the next occurrence you have NOT paid yet. A date already in the past is fine — it appears in Week 1 marked PAST DUE and stays there until you deal with it. Only move a date forward once the money has actually moved. Set Active to No to park a transaction without deleting it.</t>
   </si>
   <si>
     <t xml:space="preserve">Weekend Rule shifts a due date that lands on a Saturday or Sunday: Move Before = the Friday, Move After = the Monday, None = leave it alone.</t>
@@ -1459,7 +1462,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:C45"/>
+  <dimension ref="B2:C46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1757,6 +1760,14 @@
       </c>
       <c r="C45" s="14" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1792,44 +1803,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1837,10 +1848,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>90</v>
@@ -1852,13 +1863,13 @@
         <v>46246</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -1867,10 +1878,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="23" t="n">
         <v>790</v>
@@ -1882,13 +1893,13 @@
         <v>46248</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J6" s="21"/>
     </row>
@@ -1897,10 +1908,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>21.1</v>
@@ -1909,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>46269</v>
+        <v>46238</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -1927,10 +1938,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D8" s="23" t="n">
         <v>20</v>
@@ -1939,16 +1950,16 @@
         <v>46</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="21"/>
     </row>
@@ -1957,10 +1968,10 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>10</v>
@@ -1969,16 +1980,16 @@
         <v>46</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1987,10 +1998,10 @@
         <v>6</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D10" s="23" t="n">
         <v>4.99</v>
@@ -2002,13 +2013,13 @@
         <v>46272</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J10" s="21"/>
     </row>
@@ -2017,10 +2028,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>500</v>
@@ -2032,13 +2043,13 @@
         <v>46272</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -2047,10 +2058,10 @@
         <v>8</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D12" s="23" t="n">
         <v>163.5</v>
@@ -2062,13 +2073,13 @@
         <v>46275</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J12" s="21"/>
     </row>
@@ -2077,10 +2088,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>2.99</v>
@@ -2092,13 +2103,13 @@
         <v>46247</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -2107,10 +2118,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" s="23" t="n">
         <v>350</v>
@@ -2122,13 +2133,13 @@
         <v>46248</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" s="21"/>
     </row>
@@ -2137,10 +2148,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>171.1</v>
@@ -2152,13 +2163,13 @@
         <v>46250</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -2167,10 +2178,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D16" s="23" t="n">
         <v>45</v>
@@ -2182,13 +2193,13 @@
         <v>46250</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J16" s="21"/>
     </row>
@@ -2197,10 +2208,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>16.99</v>
@@ -2212,13 +2223,13 @@
         <v>46252</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2227,10 +2238,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D18" s="23" t="n">
         <v>13.7</v>
@@ -2242,13 +2253,13 @@
         <v>46259</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J18" s="21"/>
     </row>
@@ -2257,10 +2268,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>43.87</v>
@@ -2272,13 +2283,13 @@
         <v>46259</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -2287,10 +2298,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="23" t="n">
         <v>150</v>
@@ -2302,13 +2313,13 @@
         <v>46264</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J20" s="21"/>
     </row>
@@ -2317,10 +2328,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>143.37</v>
@@ -2332,13 +2343,13 @@
         <v>46265</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J21" s="6"/>
     </row>
@@ -2524,19 +2535,19 @@
       <c r="I34" s="21"/>
       <c r="J34" s="21"/>
     </row>
-    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="14" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="25" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2603,17 +2614,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>71.17</v>
@@ -2621,7 +2632,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>46241</v>
@@ -2633,7 +2644,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>200</v>
@@ -2641,7 +2652,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="true">TODAY()</f>
@@ -2650,12 +2661,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2668,7 +2679,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="32"/>
       <c r="G13" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="34" t="n">
@@ -2683,19 +2694,19 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G14" s="36" t="s">
         <v>18</v>
@@ -2704,55 +2715,55 @@
         <v>20</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="38" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1001,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Bruno's Restaurant (paycheck)</v>
+        <v>Apple: Claude</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$G$4:$G$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="D15" s="40" t="str">
         <f aca="false">IF($B15="","",INDEX(Schedule!$D$4:$D$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>Income</v>
+        <v>Expense</v>
       </c>
       <c r="E15" s="41" t="n">
         <f aca="false">IF($B15="","",INDEX(Schedule!$E$4:$E$483,MATCH(1001,Schedule!$K$4:$K$483,0)))</f>
-        <v>90</v>
+        <v>21.1</v>
       </c>
       <c r="F15" s="42"/>
-      <c r="G15" s="43" t="n">
+      <c r="G15" s="43" t="str">
         <f aca="false">IF($B15="","",IF($D15="Income",IF($F15&lt;&gt;"",$F15,$E15),""))</f>
-        <v>90</v>
-      </c>
-      <c r="H15" s="44" t="str">
+        <v/>
+      </c>
+      <c r="H15" s="44" t="n">
         <f aca="false">IF($B15="","",IF($D15="Income","",IF($F15&lt;&gt;"",$F15,$E15)))</f>
-        <v/>
+        <v>21.1</v>
       </c>
       <c r="I15" s="45" t="n">
         <f aca="false">IF($B15="","",$I$13+SUM($G$15:$G15)-SUM($H$15:$H15))</f>
-        <v>161.17</v>
+        <v>50.07</v>
       </c>
       <c r="J15" s="46" t="str">
         <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="38" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1002,Schedule!$K$4:$K$483,0)),"")</f>
-        <v>Apple: iCloud</v>
+        <v>OpenAI</v>
       </c>
       <c r="C16" s="39" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$G$4:$G$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>46247</v>
+        <v>46239</v>
       </c>
       <c r="D16" s="40" t="str">
         <f aca="false">IF($B16="","",INDEX(Schedule!$D$4:$D$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
@@ -2760,7 +2771,7 @@
       </c>
       <c r="E16" s="41" t="n">
         <f aca="false">IF($B16="","",INDEX(Schedule!$E$4:$E$483,MATCH(1002,Schedule!$K$4:$K$483,0)))</f>
-        <v>2.99</v>
+        <v>20</v>
       </c>
       <c r="F16" s="42"/>
       <c r="G16" s="43" t="str">
@@ -2769,120 +2780,120 @@
       </c>
       <c r="H16" s="44" t="n">
         <f aca="false">IF($B16="","",IF($D16="Income","",IF($F16&lt;&gt;"",$F16,$E16)))</f>
-        <v>2.99</v>
+        <v>20</v>
       </c>
       <c r="I16" s="45" t="n">
         <f aca="false">IF($B16="","",$I$13+SUM($G$15:$G16)-SUM($H$15:$H16))</f>
-        <v>158.18</v>
+        <v>30.07</v>
       </c>
       <c r="J16" s="46" t="str">
         <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v>DUE</v>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="38" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1003,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C17" s="39" t="str">
+        <v>Obsidian</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$G$4:$G$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46239</v>
       </c>
       <c r="D17" s="40" t="str">
         <f aca="false">IF($B17="","",INDEX(Schedule!$D$4:$D$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E17" s="41" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E17" s="41" t="n">
         <f aca="false">IF($B17="","",INDEX(Schedule!$E$4:$E$483,MATCH(1003,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F17" s="42"/>
       <c r="G17" s="43" t="str">
         <f aca="false">IF($B17="","",IF($D17="Income",IF($F17&lt;&gt;"",$F17,$E17),""))</f>
         <v/>
       </c>
-      <c r="H17" s="44" t="str">
+      <c r="H17" s="44" t="n">
         <f aca="false">IF($B17="","",IF($D17="Income","",IF($F17&lt;&gt;"",$F17,$E17)))</f>
-        <v/>
-      </c>
-      <c r="I17" s="45" t="str">
+        <v>10</v>
+      </c>
+      <c r="I17" s="45" t="n">
         <f aca="false">IF($B17="","",$I$13+SUM($G$15:$G17)-SUM($H$15:$H17))</f>
-        <v/>
+        <v>20.07</v>
       </c>
       <c r="J17" s="46" t="str">
         <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>PAST DUE</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="38" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1004,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C18" s="39" t="str">
+        <v>Bruno's Restaurant (paycheck)</v>
+      </c>
+      <c r="C18" s="39" t="n">
         <f aca="false">IF($B18="","",INDEX(Schedule!$G$4:$G$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46246</v>
       </c>
       <c r="D18" s="40" t="str">
         <f aca="false">IF($B18="","",INDEX(Schedule!$D$4:$D$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E18" s="41" t="str">
+        <v>Income</v>
+      </c>
+      <c r="E18" s="41" t="n">
         <f aca="false">IF($B18="","",INDEX(Schedule!$E$4:$E$483,MATCH(1004,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="F18" s="42"/>
-      <c r="G18" s="43" t="str">
+      <c r="G18" s="43" t="n">
         <f aca="false">IF($B18="","",IF($D18="Income",IF($F18&lt;&gt;"",$F18,$E18),""))</f>
-        <v/>
+        <v>90</v>
       </c>
       <c r="H18" s="44" t="str">
         <f aca="false">IF($B18="","",IF($D18="Income","",IF($F18&lt;&gt;"",$F18,$E18)))</f>
         <v/>
       </c>
-      <c r="I18" s="45" t="str">
+      <c r="I18" s="45" t="n">
         <f aca="false">IF($B18="","",$I$13+SUM($G$15:$G18)-SUM($H$15:$H18))</f>
-        <v/>
+        <v>110.07</v>
       </c>
       <c r="J18" s="46" t="str">
         <f aca="true">IF($B18="","",IF($F18&lt;&gt;"","PAID",IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>DUE</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="38" t="str">
         <f aca="false">IFERROR(INDEX(Schedule!$C$4:$C$483,MATCH(1005,Schedule!$K$4:$K$483,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C19" s="39" t="str">
+        <v>Apple: iCloud</v>
+      </c>
+      <c r="C19" s="39" t="n">
         <f aca="false">IF($B19="","",INDEX(Schedule!$G$4:$G$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>46247</v>
       </c>
       <c r="D19" s="40" t="str">
         <f aca="false">IF($B19="","",INDEX(Schedule!$D$4:$D$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
-      </c>
-      <c r="E19" s="41" t="str">
+        <v>Expense</v>
+      </c>
+      <c r="E19" s="41" t="n">
         <f aca="false">IF($B19="","",INDEX(Schedule!$E$4:$E$483,MATCH(1005,Schedule!$K$4:$K$483,0)))</f>
-        <v/>
+        <v>2.99</v>
       </c>
       <c r="F19" s="42"/>
       <c r="G19" s="43" t="str">
         <f aca="false">IF($B19="","",IF($D19="Income",IF($F19&lt;&gt;"",$F19,$E19),""))</f>
         <v/>
       </c>
-      <c r="H19" s="44" t="str">
+      <c r="H19" s="44" t="n">
         <f aca="false">IF($B19="","",IF($D19="Income","",IF($F19&lt;&gt;"",$F19,$E19)))</f>
-        <v/>
-      </c>
-      <c r="I19" s="45" t="str">
+        <v>2.99</v>
+      </c>
+      <c r="I19" s="45" t="n">
         <f aca="false">IF($B19="","",$I$13+SUM($G$15:$G19)-SUM($H$15:$H19))</f>
-        <v/>
+        <v>107.08</v>
       </c>
       <c r="J19" s="46" t="str">
         <f aca="true">IF($B19="","",IF($F19&lt;&gt;"","PAID",IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
-        <v/>
+        <v>DUE</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3062,7 +3073,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="48"/>
@@ -3195,7 +3206,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
@@ -3207,11 +3218,11 @@
       </c>
       <c r="H32" s="54" t="n">
         <f aca="false">SUM($H$15:$H$31)</f>
-        <v>2.99</v>
+        <v>54.09</v>
       </c>
       <c r="I32" s="55" t="n">
         <f aca="false">$I$13+$G$32-$H$32</f>
-        <v>158.18</v>
+        <v>107.08</v>
       </c>
       <c r="J32" s="56" t="str">
         <f aca="false">IF($I$32&lt;0,"SHORTFALL",IF($I$32&lt;$E$7,"TIGHT","OK"))</f>
@@ -3219,7 +3230,7 @@
       </c>
       <c r="K32" s="25" t="str">
         <f aca="false">"In "&amp;TEXT($G$32,"$#,##0.00")&amp;"   less out "&amp;TEXT($H$32,"$#,##0.00")&amp;"   =  net "&amp;TEXT($G$32-$H$32,"$#,##0.00;-$#,##0.00")</f>
-        <v>In $90.00   less out $2.99   =  net $87.01</v>
+        <v>In $90.00   less out $54.09   =  net $35.91</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3232,12 +3243,12 @@
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
       <c r="G34" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="32"/>
       <c r="I34" s="34" t="n">
         <f aca="false">$I$32</f>
-        <v>158.18</v>
+        <v>107.08</v>
       </c>
       <c r="J34" s="32"/>
       <c r="K34" s="28" t="str">
@@ -3247,19 +3258,19 @@
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G35" s="36" t="s">
         <v>18</v>
@@ -3268,10 +3279,10 @@
         <v>20</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3302,7 +3313,7 @@
       </c>
       <c r="I36" s="45" t="n">
         <f aca="false">IF($B36="","",$I$34+SUM($G$36:$G36)-SUM($H$36:$H36))</f>
-        <v>948.18</v>
+        <v>897.08</v>
       </c>
       <c r="J36" s="46" t="str">
         <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3337,7 +3348,7 @@
       </c>
       <c r="I37" s="45" t="n">
         <f aca="false">IF($B37="","",$I$34+SUM($G$36:$G37)-SUM($H$36:$H37))</f>
-        <v>598.18</v>
+        <v>547.08</v>
       </c>
       <c r="J37" s="46" t="str">
         <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3372,7 +3383,7 @@
       </c>
       <c r="I38" s="45" t="n">
         <f aca="false">IF($B38="","",$I$34+SUM($G$36:$G38)-SUM($H$36:$H38))</f>
-        <v>427.08</v>
+        <v>375.98</v>
       </c>
       <c r="J38" s="46" t="str">
         <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3407,7 +3418,7 @@
       </c>
       <c r="I39" s="45" t="n">
         <f aca="false">IF($B39="","",$I$34+SUM($G$36:$G39)-SUM($H$36:$H39))</f>
-        <v>382.08</v>
+        <v>330.98</v>
       </c>
       <c r="J39" s="46" t="str">
         <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3442,7 +3453,7 @@
       </c>
       <c r="I40" s="45" t="n">
         <f aca="false">IF($B40="","",$I$34+SUM($G$36:$G40)-SUM($H$36:$H40))</f>
-        <v>365.09</v>
+        <v>313.99</v>
       </c>
       <c r="J40" s="46" t="str">
         <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3477,7 +3488,7 @@
       </c>
       <c r="I41" s="45" t="n">
         <f aca="false">IF($B41="","",$I$34+SUM($G$36:$G41)-SUM($H$36:$H41))</f>
-        <v>455.09</v>
+        <v>403.99</v>
       </c>
       <c r="J41" s="46" t="str">
         <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3626,7 +3637,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C46" s="48"/>
       <c r="D46" s="48"/>
@@ -3759,7 +3770,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="52" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="53"/>
@@ -3775,7 +3786,7 @@
       </c>
       <c r="I53" s="55" t="n">
         <f aca="false">$I$34+$G$53-$H$53</f>
-        <v>455.09</v>
+        <v>403.99</v>
       </c>
       <c r="J53" s="56" t="str">
         <f aca="false">IF($I$53&lt;0,"SHORTFALL",IF($I$53&lt;$E$7,"TIGHT","OK"))</f>
@@ -3796,12 +3807,12 @@
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
       <c r="G55" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H55" s="32"/>
       <c r="I55" s="34" t="n">
         <f aca="false">$I$53</f>
-        <v>455.09</v>
+        <v>403.99</v>
       </c>
       <c r="J55" s="32"/>
       <c r="K55" s="28" t="str">
@@ -3811,19 +3822,19 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G56" s="36" t="s">
         <v>18</v>
@@ -3832,10 +3843,10 @@
         <v>20</v>
       </c>
       <c r="I56" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J56" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3866,7 +3877,7 @@
       </c>
       <c r="I57" s="45" t="n">
         <f aca="false">IF($B57="","",$I$55+SUM($G$57:$G57)-SUM($H$57:$H57))</f>
-        <v>1245.09</v>
+        <v>1193.99</v>
       </c>
       <c r="J57" s="46" t="str">
         <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3901,7 +3912,7 @@
       </c>
       <c r="I58" s="45" t="n">
         <f aca="false">IF($B58="","",$I$55+SUM($G$57:$G58)-SUM($H$57:$H58))</f>
-        <v>1231.39</v>
+        <v>1180.29</v>
       </c>
       <c r="J58" s="46" t="str">
         <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3936,7 +3947,7 @@
       </c>
       <c r="I59" s="45" t="n">
         <f aca="false">IF($B59="","",$I$55+SUM($G$57:$G59)-SUM($H$57:$H59))</f>
-        <v>1187.52</v>
+        <v>1136.42</v>
       </c>
       <c r="J59" s="46" t="str">
         <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -3971,7 +3982,7 @@
       </c>
       <c r="I60" s="45" t="n">
         <f aca="false">IF($B60="","",$I$55+SUM($G$57:$G60)-SUM($H$57:$H60))</f>
-        <v>1277.52</v>
+        <v>1226.42</v>
       </c>
       <c r="J60" s="46" t="str">
         <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4190,7 +4201,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C67" s="48"/>
       <c r="D67" s="48"/>
@@ -4323,7 +4334,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="52" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C74" s="53"/>
       <c r="D74" s="53"/>
@@ -4339,7 +4350,7 @@
       </c>
       <c r="I74" s="55" t="n">
         <f aca="false">$I$55+$G$74-$H$74</f>
-        <v>1277.52</v>
+        <v>1226.42</v>
       </c>
       <c r="J74" s="56" t="str">
         <f aca="false">IF($I$74&lt;0,"SHORTFALL",IF($I$74&lt;$E$7,"TIGHT","OK"))</f>
@@ -4360,12 +4371,12 @@
       <c r="E76" s="32"/>
       <c r="F76" s="32"/>
       <c r="G76" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="34" t="n">
         <f aca="false">$I$74</f>
-        <v>1277.52</v>
+        <v>1226.42</v>
       </c>
       <c r="J76" s="32"/>
       <c r="K76" s="28" t="str">
@@ -4375,19 +4386,19 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D77" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G77" s="36" t="s">
         <v>18</v>
@@ -4396,10 +4407,10 @@
         <v>20</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J77" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4430,7 +4441,7 @@
       </c>
       <c r="I78" s="45" t="n">
         <f aca="false">IF($B78="","",$I$76+SUM($G$78:$G78)-SUM($H$78:$H78))</f>
-        <v>2067.52</v>
+        <v>2016.42</v>
       </c>
       <c r="J78" s="46" t="str">
         <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4465,7 +4476,7 @@
       </c>
       <c r="I79" s="45" t="n">
         <f aca="false">IF($B79="","",$I$76+SUM($G$78:$G79)-SUM($H$78:$H79))</f>
-        <v>1917.52</v>
+        <v>1866.42</v>
       </c>
       <c r="J79" s="46" t="str">
         <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4500,7 +4511,7 @@
       </c>
       <c r="I80" s="45" t="n">
         <f aca="false">IF($B80="","",$I$76+SUM($G$78:$G80)-SUM($H$78:$H80))</f>
-        <v>1567.52</v>
+        <v>1516.42</v>
       </c>
       <c r="J80" s="46" t="str">
         <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4535,7 +4546,7 @@
       </c>
       <c r="I81" s="45" t="n">
         <f aca="false">IF($B81="","",$I$76+SUM($G$78:$G81)-SUM($H$78:$H81))</f>
-        <v>1424.15</v>
+        <v>1373.05</v>
       </c>
       <c r="J81" s="46" t="str">
         <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4570,7 +4581,7 @@
       </c>
       <c r="I82" s="45" t="n">
         <f aca="false">IF($B82="","",$I$76+SUM($G$78:$G82)-SUM($H$78:$H82))</f>
-        <v>1514.15</v>
+        <v>1463.05</v>
       </c>
       <c r="J82" s="46" t="str">
         <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -4754,7 +4765,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C88" s="48"/>
       <c r="D88" s="48"/>
@@ -4887,7 +4898,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="52" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C95" s="53"/>
       <c r="D95" s="53"/>
@@ -4903,7 +4914,7 @@
       </c>
       <c r="I95" s="55" t="n">
         <f aca="false">$I$76+$G$95-$H$95</f>
-        <v>1514.15</v>
+        <v>1463.05</v>
       </c>
       <c r="J95" s="56" t="str">
         <f aca="false">IF($I$95&lt;0,"SHORTFALL",IF($I$95&lt;$E$7,"TIGHT","OK"))</f>
@@ -4924,12 +4935,12 @@
       <c r="E97" s="32"/>
       <c r="F97" s="32"/>
       <c r="G97" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="34" t="n">
         <f aca="false">$I$95</f>
-        <v>1514.15</v>
+        <v>1463.05</v>
       </c>
       <c r="J97" s="32"/>
       <c r="K97" s="28" t="str">
@@ -4939,19 +4950,19 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G98" s="36" t="s">
         <v>18</v>
@@ -4960,10 +4971,10 @@
         <v>20</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4994,7 +5005,7 @@
       </c>
       <c r="I99" s="45" t="n">
         <f aca="false">IF($B99="","",$I$97+SUM($G$99:$G99)-SUM($H$99:$H99))</f>
-        <v>2304.15</v>
+        <v>2253.05</v>
       </c>
       <c r="J99" s="46" t="str">
         <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5029,7 +5040,7 @@
       </c>
       <c r="I100" s="45" t="n">
         <f aca="false">IF($B100="","",$I$97+SUM($G$99:$G100)-SUM($H$99:$H100))</f>
-        <v>2283.05</v>
+        <v>2231.95</v>
       </c>
       <c r="J100" s="46" t="str">
         <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5064,7 +5075,7 @@
       </c>
       <c r="I101" s="45" t="n">
         <f aca="false">IF($B101="","",$I$97+SUM($G$99:$G101)-SUM($H$99:$H101))</f>
-        <v>2263.05</v>
+        <v>2211.95</v>
       </c>
       <c r="J101" s="46" t="str">
         <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5099,7 +5110,7 @@
       </c>
       <c r="I102" s="45" t="n">
         <f aca="false">IF($B102="","",$I$97+SUM($G$99:$G102)-SUM($H$99:$H102))</f>
-        <v>2253.05</v>
+        <v>2201.95</v>
       </c>
       <c r="J102" s="46" t="str">
         <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5134,7 +5145,7 @@
       </c>
       <c r="I103" s="45" t="n">
         <f aca="false">IF($B103="","",$I$97+SUM($G$99:$G103)-SUM($H$99:$H103))</f>
-        <v>2248.06</v>
+        <v>2196.96</v>
       </c>
       <c r="J103" s="46" t="str">
         <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5169,7 +5180,7 @@
       </c>
       <c r="I104" s="45" t="n">
         <f aca="false">IF($B104="","",$I$97+SUM($G$99:$G104)-SUM($H$99:$H104))</f>
-        <v>1748.06</v>
+        <v>1696.96</v>
       </c>
       <c r="J104" s="46" t="str">
         <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5204,7 +5215,7 @@
       </c>
       <c r="I105" s="45" t="n">
         <f aca="false">IF($B105="","",$I$97+SUM($G$99:$G105)-SUM($H$99:$H105))</f>
-        <v>1838.06</v>
+        <v>1786.96</v>
       </c>
       <c r="J105" s="46" t="str">
         <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5239,7 +5250,7 @@
       </c>
       <c r="I106" s="45" t="n">
         <f aca="false">IF($B106="","",$I$97+SUM($G$99:$G106)-SUM($H$99:$H106))</f>
-        <v>1674.56</v>
+        <v>1623.46</v>
       </c>
       <c r="J106" s="46" t="str">
         <f aca="true">IF($B106="","",IF($F106&lt;&gt;"","PAID",IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5318,7 +5329,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C109" s="48"/>
       <c r="D109" s="48"/>
@@ -5451,7 +5462,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="52" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C116" s="53"/>
       <c r="D116" s="53"/>
@@ -5467,7 +5478,7 @@
       </c>
       <c r="I116" s="55" t="n">
         <f aca="false">$I$97+$G$116-$H$116</f>
-        <v>1674.56</v>
+        <v>1623.46</v>
       </c>
       <c r="J116" s="56" t="str">
         <f aca="false">IF($I$116&lt;0,"SHORTFALL",IF($I$116&lt;$E$7,"TIGHT","OK"))</f>
@@ -5488,12 +5499,12 @@
       <c r="E118" s="32"/>
       <c r="F118" s="32"/>
       <c r="G118" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="34" t="n">
         <f aca="false">$I$116</f>
-        <v>1674.56</v>
+        <v>1623.46</v>
       </c>
       <c r="J118" s="32"/>
       <c r="K118" s="28" t="str">
@@ -5503,19 +5514,19 @@
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F119" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G119" s="36" t="s">
         <v>18</v>
@@ -5524,10 +5535,10 @@
         <v>20</v>
       </c>
       <c r="I119" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J119" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5558,7 +5569,7 @@
       </c>
       <c r="I120" s="45" t="n">
         <f aca="false">IF($B120="","",$I$118+SUM($G$120:$G120)-SUM($H$120:$H120))</f>
-        <v>2464.56</v>
+        <v>2413.46</v>
       </c>
       <c r="J120" s="46" t="str">
         <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5593,7 +5604,7 @@
       </c>
       <c r="I121" s="45" t="n">
         <f aca="false">IF($B121="","",$I$118+SUM($G$120:$G121)-SUM($H$120:$H121))</f>
-        <v>2461.57</v>
+        <v>2410.47</v>
       </c>
       <c r="J121" s="46" t="str">
         <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5628,7 +5639,7 @@
       </c>
       <c r="I122" s="45" t="n">
         <f aca="false">IF($B122="","",$I$118+SUM($G$120:$G122)-SUM($H$120:$H122))</f>
-        <v>2111.57</v>
+        <v>2060.47</v>
       </c>
       <c r="J122" s="46" t="str">
         <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5663,7 +5674,7 @@
       </c>
       <c r="I123" s="45" t="n">
         <f aca="false">IF($B123="","",$I$118+SUM($G$120:$G123)-SUM($H$120:$H123))</f>
-        <v>2201.57</v>
+        <v>2150.47</v>
       </c>
       <c r="J123" s="46" t="str">
         <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5698,7 +5709,7 @@
       </c>
       <c r="I124" s="45" t="n">
         <f aca="false">IF($B124="","",$I$118+SUM($G$120:$G124)-SUM($H$120:$H124))</f>
-        <v>2030.47</v>
+        <v>1979.37</v>
       </c>
       <c r="J124" s="46" t="str">
         <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5733,7 +5744,7 @@
       </c>
       <c r="I125" s="45" t="n">
         <f aca="false">IF($B125="","",$I$118+SUM($G$120:$G125)-SUM($H$120:$H125))</f>
-        <v>1985.47</v>
+        <v>1934.37</v>
       </c>
       <c r="J125" s="46" t="str">
         <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -5882,7 +5893,7 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C130" s="48"/>
       <c r="D130" s="48"/>
@@ -6015,7 +6026,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="52" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C137" s="53"/>
       <c r="D137" s="53"/>
@@ -6031,7 +6042,7 @@
       </c>
       <c r="I137" s="55" t="n">
         <f aca="false">$I$118+$G$137-$H$137</f>
-        <v>1985.47</v>
+        <v>1934.37</v>
       </c>
       <c r="J137" s="56" t="str">
         <f aca="false">IF($I$137&lt;0,"SHORTFALL",IF($I$137&lt;$E$7,"TIGHT","OK"))</f>
@@ -6052,12 +6063,12 @@
       <c r="E139" s="32"/>
       <c r="F139" s="32"/>
       <c r="G139" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="34" t="n">
         <f aca="false">$I$137</f>
-        <v>1985.47</v>
+        <v>1934.37</v>
       </c>
       <c r="J139" s="32"/>
       <c r="K139" s="28" t="str">
@@ -6067,19 +6078,19 @@
     </row>
     <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C140" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E140" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F140" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G140" s="36" t="s">
         <v>18</v>
@@ -6088,10 +6099,10 @@
         <v>20</v>
       </c>
       <c r="I140" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J140" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6122,7 +6133,7 @@
       </c>
       <c r="I141" s="45" t="n">
         <f aca="false">IF($B141="","",$I$139+SUM($G$141:$G141)-SUM($H$141:$H141))</f>
-        <v>2775.47</v>
+        <v>2724.37</v>
       </c>
       <c r="J141" s="46" t="str">
         <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6157,7 +6168,7 @@
       </c>
       <c r="I142" s="45" t="n">
         <f aca="false">IF($B142="","",$I$139+SUM($G$141:$G142)-SUM($H$141:$H142))</f>
-        <v>2758.48</v>
+        <v>2707.38</v>
       </c>
       <c r="J142" s="46" t="str">
         <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6192,7 +6203,7 @@
       </c>
       <c r="I143" s="45" t="n">
         <f aca="false">IF($B143="","",$I$139+SUM($G$141:$G143)-SUM($H$141:$H143))</f>
-        <v>2848.48</v>
+        <v>2797.38</v>
       </c>
       <c r="J143" s="46" t="str">
         <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6446,7 +6457,7 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C151" s="48"/>
       <c r="D151" s="48"/>
@@ -6579,7 +6590,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="52" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C158" s="53"/>
       <c r="D158" s="53"/>
@@ -6595,7 +6606,7 @@
       </c>
       <c r="I158" s="55" t="n">
         <f aca="false">$I$139+$G$158-$H$158</f>
-        <v>2848.48</v>
+        <v>2797.38</v>
       </c>
       <c r="J158" s="56" t="str">
         <f aca="false">IF($I$158&lt;0,"SHORTFALL",IF($I$158&lt;$E$7,"TIGHT","OK"))</f>
@@ -6616,12 +6627,12 @@
       <c r="E160" s="32"/>
       <c r="F160" s="32"/>
       <c r="G160" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="34" t="n">
         <f aca="false">$I$158</f>
-        <v>2848.48</v>
+        <v>2797.38</v>
       </c>
       <c r="J160" s="32"/>
       <c r="K160" s="28" t="str">
@@ -6631,19 +6642,19 @@
     </row>
     <row r="161" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E161" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F161" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G161" s="36" t="s">
         <v>18</v>
@@ -6652,10 +6663,10 @@
         <v>20</v>
       </c>
       <c r="I161" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J161" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6686,7 +6697,7 @@
       </c>
       <c r="I162" s="45" t="n">
         <f aca="false">IF($B162="","",$I$160+SUM($G$162:$G162)-SUM($H$162:$H162))</f>
-        <v>3638.48</v>
+        <v>3587.38</v>
       </c>
       <c r="J162" s="46" t="str">
         <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6721,7 +6732,7 @@
       </c>
       <c r="I163" s="45" t="n">
         <f aca="false">IF($B163="","",$I$160+SUM($G$162:$G163)-SUM($H$162:$H163))</f>
-        <v>3624.78</v>
+        <v>3573.68</v>
       </c>
       <c r="J163" s="46" t="str">
         <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6756,7 +6767,7 @@
       </c>
       <c r="I164" s="45" t="n">
         <f aca="false">IF($B164="","",$I$160+SUM($G$162:$G164)-SUM($H$162:$H164))</f>
-        <v>3580.91</v>
+        <v>3529.81</v>
       </c>
       <c r="J164" s="46" t="str">
         <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6791,7 +6802,7 @@
       </c>
       <c r="I165" s="45" t="n">
         <f aca="false">IF($B165="","",$I$160+SUM($G$162:$G165)-SUM($H$162:$H165))</f>
-        <v>3670.91</v>
+        <v>3619.81</v>
       </c>
       <c r="J165" s="46" t="str">
         <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6826,7 +6837,7 @@
       </c>
       <c r="I166" s="45" t="n">
         <f aca="false">IF($B166="","",$I$160+SUM($G$162:$G166)-SUM($H$162:$H166))</f>
-        <v>3320.91</v>
+        <v>3269.81</v>
       </c>
       <c r="J166" s="46" t="str">
         <f aca="true">IF($B166="","",IF($F166&lt;&gt;"","PAID",IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6861,7 +6872,7 @@
       </c>
       <c r="I167" s="45" t="n">
         <f aca="false">IF($B167="","",$I$160+SUM($G$162:$G167)-SUM($H$162:$H167))</f>
-        <v>3170.91</v>
+        <v>3119.81</v>
       </c>
       <c r="J167" s="46" t="str">
         <f aca="true">IF($B167="","",IF($F167&lt;&gt;"","PAID",IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -6896,7 +6907,7 @@
       </c>
       <c r="I168" s="45" t="n">
         <f aca="false">IF($B168="","",$I$160+SUM($G$162:$G168)-SUM($H$162:$H168))</f>
-        <v>3027.54</v>
+        <v>2976.44</v>
       </c>
       <c r="J168" s="46" t="str">
         <f aca="true">IF($B168="","",IF($F168&lt;&gt;"","PAID",IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7010,7 +7021,7 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C172" s="48"/>
       <c r="D172" s="48"/>
@@ -7143,7 +7154,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="52" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C179" s="53"/>
       <c r="D179" s="53"/>
@@ -7159,7 +7170,7 @@
       </c>
       <c r="I179" s="55" t="n">
         <f aca="false">$I$160+$G$179-$H$179</f>
-        <v>3027.54</v>
+        <v>2976.44</v>
       </c>
       <c r="J179" s="56" t="str">
         <f aca="false">IF($I$179&lt;0,"SHORTFALL",IF($I$179&lt;$E$7,"TIGHT","OK"))</f>
@@ -7180,12 +7191,12 @@
       <c r="E181" s="32"/>
       <c r="F181" s="32"/>
       <c r="G181" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H181" s="32"/>
       <c r="I181" s="34" t="n">
         <f aca="false">$I$179</f>
-        <v>3027.54</v>
+        <v>2976.44</v>
       </c>
       <c r="J181" s="32"/>
       <c r="K181" s="28" t="str">
@@ -7195,19 +7206,19 @@
     </row>
     <row r="182" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C182" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E182" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F182" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G182" s="36" t="s">
         <v>18</v>
@@ -7216,10 +7227,10 @@
         <v>20</v>
       </c>
       <c r="I182" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J182" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7250,7 +7261,7 @@
       </c>
       <c r="I183" s="45" t="n">
         <f aca="false">IF($B183="","",$I$181+SUM($G$183:$G183)-SUM($H$183:$H183))</f>
-        <v>3817.54</v>
+        <v>3766.44</v>
       </c>
       <c r="J183" s="46" t="str">
         <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7285,7 +7296,7 @@
       </c>
       <c r="I184" s="45" t="n">
         <f aca="false">IF($B184="","",$I$181+SUM($G$183:$G184)-SUM($H$183:$H184))</f>
-        <v>3796.44</v>
+        <v>3745.34</v>
       </c>
       <c r="J184" s="46" t="str">
         <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7320,7 +7331,7 @@
       </c>
       <c r="I185" s="45" t="n">
         <f aca="false">IF($B185="","",$I$181+SUM($G$183:$G185)-SUM($H$183:$H185))</f>
-        <v>3776.44</v>
+        <v>3725.34</v>
       </c>
       <c r="J185" s="46" t="str">
         <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7355,7 +7366,7 @@
       </c>
       <c r="I186" s="45" t="n">
         <f aca="false">IF($B186="","",$I$181+SUM($G$183:$G186)-SUM($H$183:$H186))</f>
-        <v>3766.44</v>
+        <v>3715.34</v>
       </c>
       <c r="J186" s="46" t="str">
         <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7390,7 +7401,7 @@
       </c>
       <c r="I187" s="45" t="n">
         <f aca="false">IF($B187="","",$I$181+SUM($G$183:$G187)-SUM($H$183:$H187))</f>
-        <v>3856.44</v>
+        <v>3805.34</v>
       </c>
       <c r="J187" s="46" t="str">
         <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7425,7 +7436,7 @@
       </c>
       <c r="I188" s="45" t="n">
         <f aca="false">IF($B188="","",$I$181+SUM($G$183:$G188)-SUM($H$183:$H188))</f>
-        <v>3851.45</v>
+        <v>3800.35</v>
       </c>
       <c r="J188" s="46" t="str">
         <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7460,7 +7471,7 @@
       </c>
       <c r="I189" s="45" t="n">
         <f aca="false">IF($B189="","",$I$181+SUM($G$183:$G189)-SUM($H$183:$H189))</f>
-        <v>3351.45</v>
+        <v>3300.35</v>
       </c>
       <c r="J189" s="46" t="str">
         <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7574,7 +7585,7 @@
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B193" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C193" s="48"/>
       <c r="D193" s="48"/>
@@ -7707,7 +7718,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B200" s="52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C200" s="53"/>
       <c r="D200" s="53"/>
@@ -7723,7 +7734,7 @@
       </c>
       <c r="I200" s="55" t="n">
         <f aca="false">$I$181+$G$200-$H$200</f>
-        <v>3351.45</v>
+        <v>3300.35</v>
       </c>
       <c r="J200" s="56" t="str">
         <f aca="false">IF($I$200&lt;0,"SHORTFALL",IF($I$200&lt;$E$7,"TIGHT","OK"))</f>
@@ -7744,12 +7755,12 @@
       <c r="E202" s="32"/>
       <c r="F202" s="32"/>
       <c r="G202" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H202" s="32"/>
       <c r="I202" s="34" t="n">
         <f aca="false">$I$200</f>
-        <v>3351.45</v>
+        <v>3300.35</v>
       </c>
       <c r="J202" s="32"/>
       <c r="K202" s="28" t="str">
@@ -7759,19 +7770,19 @@
     </row>
     <row r="203" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C203" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D203" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E203" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F203" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G203" s="36" t="s">
         <v>18</v>
@@ -7780,10 +7791,10 @@
         <v>20</v>
       </c>
       <c r="I203" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J203" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7814,7 +7825,7 @@
       </c>
       <c r="I204" s="45" t="n">
         <f aca="false">IF($B204="","",$I$202+SUM($G$204:$G204)-SUM($H$204:$H204))</f>
-        <v>4141.45</v>
+        <v>4090.35</v>
       </c>
       <c r="J204" s="46" t="str">
         <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7849,7 +7860,7 @@
       </c>
       <c r="I205" s="45" t="n">
         <f aca="false">IF($B205="","",$I$202+SUM($G$204:$G205)-SUM($H$204:$H205))</f>
-        <v>3977.95</v>
+        <v>3926.85</v>
       </c>
       <c r="J205" s="46" t="str">
         <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7884,7 +7895,7 @@
       </c>
       <c r="I206" s="45" t="n">
         <f aca="false">IF($B206="","",$I$202+SUM($G$204:$G206)-SUM($H$204:$H206))</f>
-        <v>3974.96</v>
+        <v>3923.86</v>
       </c>
       <c r="J206" s="46" t="str">
         <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7919,7 +7930,7 @@
       </c>
       <c r="I207" s="45" t="n">
         <f aca="false">IF($B207="","",$I$202+SUM($G$204:$G207)-SUM($H$204:$H207))</f>
-        <v>4064.96</v>
+        <v>4013.86</v>
       </c>
       <c r="J207" s="46" t="str">
         <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -7954,7 +7965,7 @@
       </c>
       <c r="I208" s="45" t="n">
         <f aca="false">IF($B208="","",$I$202+SUM($G$204:$G208)-SUM($H$204:$H208))</f>
-        <v>3714.96</v>
+        <v>3663.86</v>
       </c>
       <c r="J208" s="46" t="str">
         <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8138,7 +8149,7 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C214" s="48"/>
       <c r="D214" s="48"/>
@@ -8271,7 +8282,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B221" s="52" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C221" s="53"/>
       <c r="D221" s="53"/>
@@ -8287,7 +8298,7 @@
       </c>
       <c r="I221" s="55" t="n">
         <f aca="false">$I$202+$G$221-$H$221</f>
-        <v>3714.96</v>
+        <v>3663.86</v>
       </c>
       <c r="J221" s="56" t="str">
         <f aca="false">IF($I$221&lt;0,"SHORTFALL",IF($I$221&lt;$E$7,"TIGHT","OK"))</f>
@@ -8308,12 +8319,12 @@
       <c r="E223" s="32"/>
       <c r="F223" s="32"/>
       <c r="G223" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H223" s="32"/>
       <c r="I223" s="34" t="n">
         <f aca="false">$I$221</f>
-        <v>3714.96</v>
+        <v>3663.86</v>
       </c>
       <c r="J223" s="32"/>
       <c r="K223" s="28" t="str">
@@ -8323,19 +8334,19 @@
     </row>
     <row r="224" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B224" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E224" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F224" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G224" s="36" t="s">
         <v>18</v>
@@ -8344,10 +8355,10 @@
         <v>20</v>
       </c>
       <c r="I224" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J224" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8378,7 +8389,7 @@
       </c>
       <c r="I225" s="45" t="n">
         <f aca="false">IF($B225="","",$I$223+SUM($G$225:$G225)-SUM($H$225:$H225))</f>
-        <v>4504.96</v>
+        <v>4453.86</v>
       </c>
       <c r="J225" s="46" t="str">
         <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8413,7 +8424,7 @@
       </c>
       <c r="I226" s="45" t="n">
         <f aca="false">IF($B226="","",$I$223+SUM($G$225:$G226)-SUM($H$225:$H226))</f>
-        <v>4333.86</v>
+        <v>4282.76</v>
       </c>
       <c r="J226" s="46" t="str">
         <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8448,7 +8459,7 @@
       </c>
       <c r="I227" s="45" t="n">
         <f aca="false">IF($B227="","",$I$223+SUM($G$225:$G227)-SUM($H$225:$H227))</f>
-        <v>4288.86</v>
+        <v>4237.76</v>
       </c>
       <c r="J227" s="46" t="str">
         <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8483,7 +8494,7 @@
       </c>
       <c r="I228" s="45" t="n">
         <f aca="false">IF($B228="","",$I$223+SUM($G$225:$G228)-SUM($H$225:$H228))</f>
-        <v>4271.87</v>
+        <v>4220.77</v>
       </c>
       <c r="J228" s="46" t="str">
         <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8518,7 +8529,7 @@
       </c>
       <c r="I229" s="45" t="n">
         <f aca="false">IF($B229="","",$I$223+SUM($G$225:$G229)-SUM($H$225:$H229))</f>
-        <v>4361.87</v>
+        <v>4310.77</v>
       </c>
       <c r="J229" s="46" t="str">
         <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8702,7 +8713,7 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C235" s="48"/>
       <c r="D235" s="48"/>
@@ -8835,7 +8846,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C242" s="53"/>
       <c r="D242" s="53"/>
@@ -8851,7 +8862,7 @@
       </c>
       <c r="I242" s="55" t="n">
         <f aca="false">$I$223+$G$242-$H$242</f>
-        <v>4361.87</v>
+        <v>4310.77</v>
       </c>
       <c r="J242" s="56" t="str">
         <f aca="false">IF($I$242&lt;0,"SHORTFALL",IF($I$242&lt;$E$7,"TIGHT","OK"))</f>
@@ -8872,12 +8883,12 @@
       <c r="E244" s="32"/>
       <c r="F244" s="32"/>
       <c r="G244" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H244" s="32"/>
       <c r="I244" s="34" t="n">
         <f aca="false">$I$242</f>
-        <v>4361.87</v>
+        <v>4310.77</v>
       </c>
       <c r="J244" s="32"/>
       <c r="K244" s="28" t="str">
@@ -8887,19 +8898,19 @@
     </row>
     <row r="245" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B245" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C245" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D245" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E245" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F245" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G245" s="36" t="s">
         <v>18</v>
@@ -8908,10 +8919,10 @@
         <v>20</v>
       </c>
       <c r="I245" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J245" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8942,7 +8953,7 @@
       </c>
       <c r="I246" s="45" t="n">
         <f aca="false">IF($B246="","",$I$244+SUM($G$246:$G246)-SUM($H$246:$H246))</f>
-        <v>5151.87</v>
+        <v>5100.77</v>
       </c>
       <c r="J246" s="46" t="str">
         <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -8977,7 +8988,7 @@
       </c>
       <c r="I247" s="45" t="n">
         <f aca="false">IF($B247="","",$I$244+SUM($G$246:$G247)-SUM($H$246:$H247))</f>
-        <v>5138.17</v>
+        <v>5087.07</v>
       </c>
       <c r="J247" s="46" t="str">
         <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9012,7 +9023,7 @@
       </c>
       <c r="I248" s="45" t="n">
         <f aca="false">IF($B248="","",$I$244+SUM($G$246:$G248)-SUM($H$246:$H248))</f>
-        <v>5094.3</v>
+        <v>5043.2</v>
       </c>
       <c r="J248" s="46" t="str">
         <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9047,7 +9058,7 @@
       </c>
       <c r="I249" s="45" t="n">
         <f aca="false">IF($B249="","",$I$244+SUM($G$246:$G249)-SUM($H$246:$H249))</f>
-        <v>5184.3</v>
+        <v>5133.2</v>
       </c>
       <c r="J249" s="46" t="str">
         <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9266,7 +9277,7 @@
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B256" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C256" s="48"/>
       <c r="D256" s="48"/>
@@ -9399,7 +9410,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B263" s="52" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C263" s="53"/>
       <c r="D263" s="53"/>
@@ -9415,7 +9426,7 @@
       </c>
       <c r="I263" s="55" t="n">
         <f aca="false">$I$244+$G$263-$H$263</f>
-        <v>5184.3</v>
+        <v>5133.2</v>
       </c>
       <c r="J263" s="56" t="str">
         <f aca="false">IF($I$263&lt;0,"SHORTFALL",IF($I$263&lt;$E$7,"TIGHT","OK"))</f>
@@ -9436,12 +9447,12 @@
       <c r="E265" s="32"/>
       <c r="F265" s="32"/>
       <c r="G265" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H265" s="32"/>
       <c r="I265" s="34" t="n">
         <f aca="false">$I$263</f>
-        <v>5184.3</v>
+        <v>5133.2</v>
       </c>
       <c r="J265" s="32"/>
       <c r="K265" s="28" t="str">
@@ -9451,19 +9462,19 @@
     </row>
     <row r="266" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E266" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F266" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G266" s="36" t="s">
         <v>18</v>
@@ -9472,10 +9483,10 @@
         <v>20</v>
       </c>
       <c r="I266" s="35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J266" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9506,7 +9517,7 @@
       </c>
       <c r="I267" s="45" t="n">
         <f aca="false">IF($B267="","",$I$265+SUM($G$267:$G267)-SUM($H$267:$H267))</f>
-        <v>5974.3</v>
+        <v>5923.2</v>
       </c>
       <c r="J267" s="46" t="str">
         <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9541,7 +9552,7 @@
       </c>
       <c r="I268" s="45" t="n">
         <f aca="false">IF($B268="","",$I$265+SUM($G$267:$G268)-SUM($H$267:$H268))</f>
-        <v>5624.3</v>
+        <v>5573.2</v>
       </c>
       <c r="J268" s="46" t="str">
         <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9576,7 +9587,7 @@
       </c>
       <c r="I269" s="45" t="n">
         <f aca="false">IF($B269="","",$I$265+SUM($G$267:$G269)-SUM($H$267:$H269))</f>
-        <v>5474.3</v>
+        <v>5423.2</v>
       </c>
       <c r="J269" s="46" t="str">
         <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9611,7 +9622,7 @@
       </c>
       <c r="I270" s="45" t="n">
         <f aca="false">IF($B270="","",$I$265+SUM($G$267:$G270)-SUM($H$267:$H270))</f>
-        <v>5330.93</v>
+        <v>5279.83</v>
       </c>
       <c r="J270" s="46" t="str">
         <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9646,7 +9657,7 @@
       </c>
       <c r="I271" s="45" t="n">
         <f aca="false">IF($B271="","",$I$265+SUM($G$267:$G271)-SUM($H$267:$H271))</f>
-        <v>5420.93</v>
+        <v>5369.83</v>
       </c>
       <c r="J271" s="46" t="str">
         <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9681,7 +9692,7 @@
       </c>
       <c r="I272" s="45" t="n">
         <f aca="false">IF($B272="","",$I$265+SUM($G$267:$G272)-SUM($H$267:$H272))</f>
-        <v>5399.83</v>
+        <v>5348.73</v>
       </c>
       <c r="J272" s="46" t="str">
         <f aca="true">IF($B272="","",IF($F272&lt;&gt;"","PAID",IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9716,7 +9727,7 @@
       </c>
       <c r="I273" s="45" t="n">
         <f aca="false">IF($B273="","",$I$265+SUM($G$267:$G273)-SUM($H$267:$H273))</f>
-        <v>5379.83</v>
+        <v>5328.73</v>
       </c>
       <c r="J273" s="46" t="str">
         <f aca="true">IF($B273="","",IF($F273&lt;&gt;"","PAID",IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9751,7 +9762,7 @@
       </c>
       <c r="I274" s="45" t="n">
         <f aca="false">IF($B274="","",$I$265+SUM($G$267:$G274)-SUM($H$267:$H274))</f>
-        <v>5369.83</v>
+        <v>5318.73</v>
       </c>
       <c r="J274" s="46" t="str">
         <f aca="true">IF($B274="","",IF($F274&lt;&gt;"","PAID",IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
@@ -9830,7 +9841,7 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="47" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C277" s="48"/>
       <c r="D277" s="48"/>
@@ -9963,7 +9974,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B284" s="52" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C284" s="53"/>
       <c r="D284" s="53"/>
@@ -9979,7 +9990,7 @@
       </c>
       <c r="I284" s="55" t="n">
         <f aca="false">$I$265+$G$284-$H$284</f>
-        <v>5369.83</v>
+        <v>5318.73</v>
       </c>
       <c r="J284" s="56" t="str">
         <f aca="false">IF($I$284&lt;0,"SHORTFALL",IF($I$284&lt;$E$7,"TIGHT","OK"))</f>
@@ -10049,28 +10060,28 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="57" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="57"/>
       <c r="D4" s="57"/>
       <c r="E4" s="58" t="n">
         <f aca="false">MIN($I$13:$I$25)</f>
-        <v>158.18</v>
+        <v>107.08</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="57" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="57"/>
@@ -10085,7 +10096,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="57" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="57"/>
@@ -10100,7 +10111,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="57" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
@@ -10111,67 +10122,67 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="57" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="57"/>
       <c r="E8" s="60" t="n">
         <f aca="false">SUM($F$13:$F$25)+SUM($G$13:$G$25)</f>
-        <v>5351.34</v>
+        <v>5402.44</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
       <c r="E9" s="58" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5298.66</v>
+        <v>5247.56</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="57" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="57"/>
       <c r="E10" s="58" t="n">
         <f aca="false">$I$25</f>
-        <v>5369.83</v>
+        <v>5318.73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10192,7 +10203,7 @@
       </c>
       <c r="F13" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$H$15:$H$24)</f>
-        <v>2.99</v>
+        <v>54.09</v>
       </c>
       <c r="G13" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$H$26:$H$31)</f>
@@ -10200,11 +10211,11 @@
       </c>
       <c r="H13" s="64" t="n">
         <f aca="false">$E13-$F13-$G13</f>
-        <v>87.01</v>
+        <v>35.91</v>
       </c>
       <c r="I13" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$32</f>
-        <v>158.18</v>
+        <v>107.08</v>
       </c>
       <c r="J13" s="65" t="str">
         <f aca="false">IF($I13&lt;0,"SHORTFALL",IF($I13&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10225,7 +10236,7 @@
       </c>
       <c r="D14" s="67" t="n">
         <f aca="false">'Cash Flow'!$I$34</f>
-        <v>158.18</v>
+        <v>107.08</v>
       </c>
       <c r="E14" s="68" t="n">
         <f aca="false">SUM('Cash Flow'!$G$36:$G$52)</f>
@@ -10245,7 +10256,7 @@
       </c>
       <c r="I14" s="69" t="n">
         <f aca="false">'Cash Flow'!$I$53</f>
-        <v>455.09</v>
+        <v>403.99</v>
       </c>
       <c r="J14" s="70" t="str">
         <f aca="false">IF($I14&lt;0,"SHORTFALL",IF($I14&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10266,7 +10277,7 @@
       </c>
       <c r="D15" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$55</f>
-        <v>455.09</v>
+        <v>403.99</v>
       </c>
       <c r="E15" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$57:$G$73)</f>
@@ -10286,7 +10297,7 @@
       </c>
       <c r="I15" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$74</f>
-        <v>1277.52</v>
+        <v>1226.42</v>
       </c>
       <c r="J15" s="65" t="str">
         <f aca="false">IF($I15&lt;0,"SHORTFALL",IF($I15&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10307,7 +10318,7 @@
       </c>
       <c r="D16" s="67" t="n">
         <f aca="false">'Cash Flow'!$I$76</f>
-        <v>1277.52</v>
+        <v>1226.42</v>
       </c>
       <c r="E16" s="68" t="n">
         <f aca="false">SUM('Cash Flow'!$G$78:$G$94)</f>
@@ -10327,7 +10338,7 @@
       </c>
       <c r="I16" s="69" t="n">
         <f aca="false">'Cash Flow'!$I$95</f>
-        <v>1514.15</v>
+        <v>1463.05</v>
       </c>
       <c r="J16" s="70" t="str">
         <f aca="false">IF($I16&lt;0,"SHORTFALL",IF($I16&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10348,7 +10359,7 @@
       </c>
       <c r="D17" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$97</f>
-        <v>1514.15</v>
+        <v>1463.05</v>
       </c>
       <c r="E17" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$99:$G$115)</f>
@@ -10368,7 +10379,7 @@
       </c>
       <c r="I17" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$116</f>
-        <v>1674.56</v>
+        <v>1623.46</v>
       </c>
       <c r="J17" s="65" t="str">
         <f aca="false">IF($I17&lt;0,"SHORTFALL",IF($I17&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10389,7 +10400,7 @@
       </c>
       <c r="D18" s="67" t="n">
         <f aca="false">'Cash Flow'!$I$118</f>
-        <v>1674.56</v>
+        <v>1623.46</v>
       </c>
       <c r="E18" s="68" t="n">
         <f aca="false">SUM('Cash Flow'!$G$120:$G$136)</f>
@@ -10409,7 +10420,7 @@
       </c>
       <c r="I18" s="69" t="n">
         <f aca="false">'Cash Flow'!$I$137</f>
-        <v>1985.47</v>
+        <v>1934.37</v>
       </c>
       <c r="J18" s="70" t="str">
         <f aca="false">IF($I18&lt;0,"SHORTFALL",IF($I18&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10430,7 +10441,7 @@
       </c>
       <c r="D19" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$139</f>
-        <v>1985.47</v>
+        <v>1934.37</v>
       </c>
       <c r="E19" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$141:$G$157)</f>
@@ -10450,7 +10461,7 @@
       </c>
       <c r="I19" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$158</f>
-        <v>2848.48</v>
+        <v>2797.38</v>
       </c>
       <c r="J19" s="65" t="str">
         <f aca="false">IF($I19&lt;0,"SHORTFALL",IF($I19&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10471,7 +10482,7 @@
       </c>
       <c r="D20" s="67" t="n">
         <f aca="false">'Cash Flow'!$I$160</f>
-        <v>2848.48</v>
+        <v>2797.38</v>
       </c>
       <c r="E20" s="68" t="n">
         <f aca="false">SUM('Cash Flow'!$G$162:$G$178)</f>
@@ -10491,7 +10502,7 @@
       </c>
       <c r="I20" s="69" t="n">
         <f aca="false">'Cash Flow'!$I$179</f>
-        <v>3027.54</v>
+        <v>2976.44</v>
       </c>
       <c r="J20" s="70" t="str">
         <f aca="false">IF($I20&lt;0,"SHORTFALL",IF($I20&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10512,7 +10523,7 @@
       </c>
       <c r="D21" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$181</f>
-        <v>3027.54</v>
+        <v>2976.44</v>
       </c>
       <c r="E21" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$183:$G$199)</f>
@@ -10532,7 +10543,7 @@
       </c>
       <c r="I21" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$200</f>
-        <v>3351.45</v>
+        <v>3300.35</v>
       </c>
       <c r="J21" s="65" t="str">
         <f aca="false">IF($I21&lt;0,"SHORTFALL",IF($I21&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10553,7 +10564,7 @@
       </c>
       <c r="D22" s="67" t="n">
         <f aca="false">'Cash Flow'!$I$202</f>
-        <v>3351.45</v>
+        <v>3300.35</v>
       </c>
       <c r="E22" s="68" t="n">
         <f aca="false">SUM('Cash Flow'!$G$204:$G$220)</f>
@@ -10573,7 +10584,7 @@
       </c>
       <c r="I22" s="69" t="n">
         <f aca="false">'Cash Flow'!$I$221</f>
-        <v>3714.96</v>
+        <v>3663.86</v>
       </c>
       <c r="J22" s="70" t="str">
         <f aca="false">IF($I22&lt;0,"SHORTFALL",IF($I22&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10594,7 +10605,7 @@
       </c>
       <c r="D23" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$223</f>
-        <v>3714.96</v>
+        <v>3663.86</v>
       </c>
       <c r="E23" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$225:$G$241)</f>
@@ -10614,7 +10625,7 @@
       </c>
       <c r="I23" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$242</f>
-        <v>4361.87</v>
+        <v>4310.77</v>
       </c>
       <c r="J23" s="65" t="str">
         <f aca="false">IF($I23&lt;0,"SHORTFALL",IF($I23&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10635,7 +10646,7 @@
       </c>
       <c r="D24" s="67" t="n">
         <f aca="false">'Cash Flow'!$I$244</f>
-        <v>4361.87</v>
+        <v>4310.77</v>
       </c>
       <c r="E24" s="68" t="n">
         <f aca="false">SUM('Cash Flow'!$G$246:$G$262)</f>
@@ -10655,7 +10666,7 @@
       </c>
       <c r="I24" s="69" t="n">
         <f aca="false">'Cash Flow'!$I$263</f>
-        <v>5184.3</v>
+        <v>5133.2</v>
       </c>
       <c r="J24" s="70" t="str">
         <f aca="false">IF($I24&lt;0,"SHORTFALL",IF($I24&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10676,7 +10687,7 @@
       </c>
       <c r="D25" s="62" t="n">
         <f aca="false">'Cash Flow'!$I$265</f>
-        <v>5184.3</v>
+        <v>5133.2</v>
       </c>
       <c r="E25" s="63" t="n">
         <f aca="false">SUM('Cash Flow'!$G$267:$G$283)</f>
@@ -10696,7 +10707,7 @@
       </c>
       <c r="I25" s="64" t="n">
         <f aca="false">'Cash Flow'!$I$284</f>
-        <v>5369.83</v>
+        <v>5318.73</v>
       </c>
       <c r="J25" s="65" t="str">
         <f aca="false">IF($I25&lt;0,"SHORTFALL",IF($I25&lt;'Cash Flow'!$E$7,"TIGHT","OK"))</f>
@@ -10709,10 +10720,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C26" s="71" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D26" s="72" t="n">
         <f aca="false">$D$13</f>
@@ -10724,7 +10735,7 @@
       </c>
       <c r="F26" s="54" t="n">
         <f aca="false">SUM($F$13:$F$25)</f>
-        <v>5351.34</v>
+        <v>5402.44</v>
       </c>
       <c r="G26" s="54" t="n">
         <f aca="false">SUM($G$13:$G$25)</f>
@@ -10732,17 +10743,17 @@
       </c>
       <c r="H26" s="72" t="n">
         <f aca="false">SUM($H$13:$H$25)</f>
-        <v>5298.66</v>
+        <v>5247.56</v>
       </c>
       <c r="I26" s="72" t="n">
         <f aca="false">$I$25</f>
-        <v>5369.83</v>
+        <v>5318.73</v>
       </c>
       <c r="J26" s="53"/>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="73" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C28" s="73"/>
       <c r="D28" s="73"/>
@@ -10812,47 +10823,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="74" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D3" s="75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E3" s="75" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" s="75" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G3" s="75" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H3" s="75" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I3" s="75" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J3" s="75" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K3" s="75" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10883,11 +10894,11 @@
         <v>46246</v>
       </c>
       <c r="H4" s="78" t="n">
-        <f aca="false">IF($G4="",0,IF(AND($G4&gt;='Cash Flow'!$E$6,$G4&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G4="",0,IF(AND($G4&gt;='Cash Flow'!$E$6-90,$G4&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I4" s="78" t="n">
-        <f aca="false">IF($H4=1,INT(($G4-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H4=1,MAX(1,INT(($G4-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>1</v>
       </c>
       <c r="J4" s="38" t="n">
@@ -10896,7 +10907,7 @@
       </c>
       <c r="K4" s="38" t="n">
         <f aca="false">IF($H4=1,$I4*1000+COUNTIFS($I$4:$I$483,$I4,$J$4:$J$483,"&lt;"&amp;$J4)+1,"")</f>
-        <v>1001</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10931,7 +10942,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="78" t="n">
-        <f aca="false">IF($H5=1,INT(($G5-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H5=1,MAX(1,INT(($G5-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>2</v>
       </c>
       <c r="J5" s="38" t="n">
@@ -10975,7 +10986,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="78" t="n">
-        <f aca="false">IF($H6=1,INT(($G6-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H6=1,MAX(1,INT(($G6-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>3</v>
       </c>
       <c r="J6" s="38" t="n">
@@ -11019,7 +11030,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="78" t="n">
-        <f aca="false">IF($H7=1,INT(($G7-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H7=1,MAX(1,INT(($G7-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>4</v>
       </c>
       <c r="J7" s="38" t="n">
@@ -11063,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="78" t="n">
-        <f aca="false">IF($H8=1,INT(($G8-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H8=1,MAX(1,INT(($G8-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>5</v>
       </c>
       <c r="J8" s="38" t="n">
@@ -11107,7 +11118,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="78" t="n">
-        <f aca="false">IF($H9=1,INT(($G9-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H9=1,MAX(1,INT(($G9-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>6</v>
       </c>
       <c r="J9" s="38" t="n">
@@ -11151,7 +11162,7 @@
         <v>1</v>
       </c>
       <c r="I10" s="78" t="n">
-        <f aca="false">IF($H10=1,INT(($G10-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H10=1,MAX(1,INT(($G10-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>7</v>
       </c>
       <c r="J10" s="38" t="n">
@@ -11195,7 +11206,7 @@
         <v>1</v>
       </c>
       <c r="I11" s="78" t="n">
-        <f aca="false">IF($H11=1,INT(($G11-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H11=1,MAX(1,INT(($G11-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J11" s="38" t="n">
@@ -11239,7 +11250,7 @@
         <v>1</v>
       </c>
       <c r="I12" s="78" t="n">
-        <f aca="false">IF($H12=1,INT(($G12-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H12=1,MAX(1,INT(($G12-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>9</v>
       </c>
       <c r="J12" s="38" t="n">
@@ -11283,7 +11294,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="78" t="n">
-        <f aca="false">IF($H13=1,INT(($G13-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H13=1,MAX(1,INT(($G13-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>10</v>
       </c>
       <c r="J13" s="38" t="n">
@@ -11327,7 +11338,7 @@
         <v>1</v>
       </c>
       <c r="I14" s="78" t="n">
-        <f aca="false">IF($H14=1,INT(($G14-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H14=1,MAX(1,INT(($G14-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>11</v>
       </c>
       <c r="J14" s="38" t="n">
@@ -11371,7 +11382,7 @@
         <v>1</v>
       </c>
       <c r="I15" s="78" t="n">
-        <f aca="false">IF($H15=1,INT(($G15-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H15=1,MAX(1,INT(($G15-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>12</v>
       </c>
       <c r="J15" s="38" t="n">
@@ -11415,7 +11426,7 @@
         <v>1</v>
       </c>
       <c r="I16" s="78" t="n">
-        <f aca="false">IF($H16=1,INT(($G16-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H16=1,MAX(1,INT(($G16-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>13</v>
       </c>
       <c r="J16" s="38" t="n">
@@ -11459,7 +11470,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="78" t="str">
-        <f aca="false">IF($H17=1,INT(($G17-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H17=1,MAX(1,INT(($G17-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J17" s="38" t="str">
@@ -11503,7 +11514,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="78" t="str">
-        <f aca="false">IF($H18=1,INT(($G18-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H18=1,MAX(1,INT(($G18-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J18" s="38" t="str">
@@ -11547,7 +11558,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="78" t="str">
-        <f aca="false">IF($H19=1,INT(($G19-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H19=1,MAX(1,INT(($G19-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J19" s="38" t="str">
@@ -11587,11 +11598,11 @@
         <v>46248</v>
       </c>
       <c r="H20" s="78" t="n">
-        <f aca="false">IF($G20="",0,IF(AND($G20&gt;='Cash Flow'!$E$6,$G20&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G20="",0,IF(AND($G20&gt;='Cash Flow'!$E$6-90,$G20&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I20" s="78" t="n">
-        <f aca="false">IF($H20=1,INT(($G20-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H20=1,MAX(1,INT(($G20-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>2</v>
       </c>
       <c r="J20" s="38" t="n">
@@ -11635,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="I21" s="78" t="n">
-        <f aca="false">IF($H21=1,INT(($G21-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H21=1,MAX(1,INT(($G21-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>3</v>
       </c>
       <c r="J21" s="38" t="n">
@@ -11679,7 +11690,7 @@
         <v>1</v>
       </c>
       <c r="I22" s="78" t="n">
-        <f aca="false">IF($H22=1,INT(($G22-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H22=1,MAX(1,INT(($G22-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>4</v>
       </c>
       <c r="J22" s="38" t="n">
@@ -11723,7 +11734,7 @@
         <v>1</v>
       </c>
       <c r="I23" s="78" t="n">
-        <f aca="false">IF($H23=1,INT(($G23-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H23=1,MAX(1,INT(($G23-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>5</v>
       </c>
       <c r="J23" s="38" t="n">
@@ -11767,7 +11778,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="78" t="n">
-        <f aca="false">IF($H24=1,INT(($G24-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H24=1,MAX(1,INT(($G24-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>6</v>
       </c>
       <c r="J24" s="38" t="n">
@@ -11811,7 +11822,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="78" t="n">
-        <f aca="false">IF($H25=1,INT(($G25-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H25=1,MAX(1,INT(($G25-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>7</v>
       </c>
       <c r="J25" s="38" t="n">
@@ -11855,7 +11866,7 @@
         <v>1</v>
       </c>
       <c r="I26" s="78" t="n">
-        <f aca="false">IF($H26=1,INT(($G26-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H26=1,MAX(1,INT(($G26-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J26" s="38" t="n">
@@ -11899,7 +11910,7 @@
         <v>1</v>
       </c>
       <c r="I27" s="78" t="n">
-        <f aca="false">IF($H27=1,INT(($G27-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H27=1,MAX(1,INT(($G27-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>9</v>
       </c>
       <c r="J27" s="38" t="n">
@@ -11943,7 +11954,7 @@
         <v>1</v>
       </c>
       <c r="I28" s="78" t="n">
-        <f aca="false">IF($H28=1,INT(($G28-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H28=1,MAX(1,INT(($G28-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>10</v>
       </c>
       <c r="J28" s="38" t="n">
@@ -11987,7 +11998,7 @@
         <v>1</v>
       </c>
       <c r="I29" s="78" t="n">
-        <f aca="false">IF($H29=1,INT(($G29-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H29=1,MAX(1,INT(($G29-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>11</v>
       </c>
       <c r="J29" s="38" t="n">
@@ -12031,7 +12042,7 @@
         <v>1</v>
       </c>
       <c r="I30" s="78" t="n">
-        <f aca="false">IF($H30=1,INT(($G30-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H30=1,MAX(1,INT(($G30-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>12</v>
       </c>
       <c r="J30" s="38" t="n">
@@ -12075,7 +12086,7 @@
         <v>1</v>
       </c>
       <c r="I31" s="78" t="n">
-        <f aca="false">IF($H31=1,INT(($G31-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H31=1,MAX(1,INT(($G31-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>13</v>
       </c>
       <c r="J31" s="38" t="n">
@@ -12119,7 +12130,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="78" t="str">
-        <f aca="false">IF($H32=1,INT(($G32-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H32=1,MAX(1,INT(($G32-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J32" s="38" t="str">
@@ -12163,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="78" t="str">
-        <f aca="false">IF($H33=1,INT(($G33-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H33=1,MAX(1,INT(($G33-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J33" s="38" t="str">
@@ -12207,7 +12218,7 @@
         <v>0</v>
       </c>
       <c r="I34" s="78" t="str">
-        <f aca="false">IF($H34=1,INT(($G34-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H34=1,MAX(1,INT(($G34-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J34" s="38" t="str">
@@ -12251,7 +12262,7 @@
         <v>0</v>
       </c>
       <c r="I35" s="78" t="str">
-        <f aca="false">IF($H35=1,INT(($G35-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H35=1,MAX(1,INT(($G35-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J35" s="38" t="str">
@@ -12284,27 +12295,27 @@
       </c>
       <c r="F36" s="77" t="n">
         <f aca="false">IF($C36="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*0,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*0,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,0),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$7="One Time",IF(1=1,Recurring!$F$7,""),""))))))</f>
-        <v>46269</v>
+        <v>46238</v>
       </c>
       <c r="G36" s="77" t="n">
         <f aca="false">IF($F36="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F36,2)=6,$F36-1,IF(WEEKDAY($F36,2)=7,$F36-2,$F36)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F36,2)=6,$F36+2,IF(WEEKDAY($F36,2)=7,$F36+1,$F36)),$F36)))</f>
-        <v>46269</v>
+        <v>46238</v>
       </c>
       <c r="H36" s="78" t="n">
-        <f aca="false">IF($G36="",0,IF(AND($G36&gt;='Cash Flow'!$E$6,$G36&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G36="",0,IF(AND($G36&gt;='Cash Flow'!$E$6-90,$G36&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I36" s="78" t="n">
-        <f aca="false">IF($H36=1,INT(($G36-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <f aca="false">IF($H36=1,MAX(1,INT(($G36-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>1</v>
       </c>
       <c r="J36" s="38" t="n">
         <f aca="false">IF($H36=1,$G36*10000+ROW(),"")</f>
-        <v>462690036</v>
+        <v>462380036</v>
       </c>
       <c r="K36" s="38" t="n">
         <f aca="false">IF($H36=1,$I36*1000+COUNTIFS($I$4:$I$483,$I36,$J$4:$J$483,"&lt;"&amp;$J36)+1,"")</f>
-        <v>5002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12328,27 +12339,27 @@
       </c>
       <c r="F37" s="77" t="n">
         <f aca="false">IF($C37="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*1,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*1,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,1),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$7="One Time",IF(2=1,Recurring!$F$7,""),""))))))</f>
-        <v>46299</v>
+        <v>46269</v>
       </c>
       <c r="G37" s="77" t="n">
         <f aca="false">IF($F37="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F37,2)=6,$F37-1,IF(WEEKDAY($F37,2)=7,$F37-2,$F37)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F37,2)=6,$F37+2,IF(WEEKDAY($F37,2)=7,$F37+1,$F37)),$F37)))</f>
-        <v>46299</v>
+        <v>46269</v>
       </c>
       <c r="H37" s="78" t="n">
         <f aca="false">IF($G37="",0,IF(AND($G37&gt;='Cash Flow'!$E$6,$G37&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I37" s="78" t="n">
-        <f aca="false">IF($H37=1,INT(($G37-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <f aca="false">IF($H37=1,MAX(1,INT(($G37-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>5</v>
       </c>
       <c r="J37" s="38" t="n">
         <f aca="false">IF($H37=1,$G37*10000+ROW(),"")</f>
-        <v>462990037</v>
+        <v>462690037</v>
       </c>
       <c r="K37" s="38" t="n">
         <f aca="false">IF($H37=1,$I37*1000+COUNTIFS($I$4:$I$483,$I37,$J$4:$J$483,"&lt;"&amp;$J37)+1,"")</f>
-        <v>9002</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12372,27 +12383,27 @@
       </c>
       <c r="F38" s="77" t="n">
         <f aca="false">IF($C38="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*2,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*2,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,2),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$7="One Time",IF(3=1,Recurring!$F$7,""),""))))))</f>
-        <v>46330</v>
+        <v>46299</v>
       </c>
       <c r="G38" s="77" t="n">
         <f aca="false">IF($F38="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F38,2)=6,$F38-1,IF(WEEKDAY($F38,2)=7,$F38-2,$F38)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F38,2)=6,$F38+2,IF(WEEKDAY($F38,2)=7,$F38+1,$F38)),$F38)))</f>
-        <v>46330</v>
+        <v>46299</v>
       </c>
       <c r="H38" s="78" t="n">
         <f aca="false">IF($G38="",0,IF(AND($G38&gt;='Cash Flow'!$E$6,$G38&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I38" s="78" t="n">
-        <f aca="false">IF($H38=1,INT(($G38-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <f aca="false">IF($H38=1,MAX(1,INT(($G38-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>9</v>
       </c>
       <c r="J38" s="38" t="n">
         <f aca="false">IF($H38=1,$G38*10000+ROW(),"")</f>
-        <v>463300038</v>
+        <v>462990038</v>
       </c>
       <c r="K38" s="38" t="n">
         <f aca="false">IF($H38=1,$I38*1000+COUNTIFS($I$4:$I$483,$I38,$J$4:$J$483,"&lt;"&amp;$J38)+1,"")</f>
-        <v>13006</v>
+        <v>9002</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12416,27 +12427,27 @@
       </c>
       <c r="F39" s="77" t="n">
         <f aca="false">IF($C39="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*3,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*3,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,3),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$7="One Time",IF(4=1,Recurring!$F$7,""),""))))))</f>
-        <v>46360</v>
+        <v>46330</v>
       </c>
       <c r="G39" s="77" t="n">
         <f aca="false">IF($F39="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F39,2)=6,$F39-1,IF(WEEKDAY($F39,2)=7,$F39-2,$F39)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F39,2)=6,$F39+2,IF(WEEKDAY($F39,2)=7,$F39+1,$F39)),$F39)))</f>
-        <v>46360</v>
+        <v>46330</v>
       </c>
       <c r="H39" s="78" t="n">
         <f aca="false">IF($G39="",0,IF(AND($G39&gt;='Cash Flow'!$E$6,$G39&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="78" t="str">
-        <f aca="false">IF($H39=1,INT(($G39-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J39" s="38" t="str">
+        <v>1</v>
+      </c>
+      <c r="I39" s="78" t="n">
+        <f aca="false">IF($H39=1,MAX(1,INT(($G39-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J39" s="38" t="n">
         <f aca="false">IF($H39=1,$G39*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="38" t="str">
+        <v>463300039</v>
+      </c>
+      <c r="K39" s="38" t="n">
         <f aca="false">IF($H39=1,$I39*1000+COUNTIFS($I$4:$I$483,$I39,$J$4:$J$483,"&lt;"&amp;$J39)+1,"")</f>
-        <v/>
+        <v>13006</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12460,18 +12471,18 @@
       </c>
       <c r="F40" s="77" t="n">
         <f aca="false">IF($C40="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*4,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*4,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,4),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$7="One Time",IF(5=1,Recurring!$F$7,""),""))))))</f>
-        <v>46391</v>
+        <v>46360</v>
       </c>
       <c r="G40" s="77" t="n">
         <f aca="false">IF($F40="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F40,2)=6,$F40-1,IF(WEEKDAY($F40,2)=7,$F40-2,$F40)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F40,2)=6,$F40+2,IF(WEEKDAY($F40,2)=7,$F40+1,$F40)),$F40)))</f>
-        <v>46391</v>
+        <v>46360</v>
       </c>
       <c r="H40" s="78" t="n">
         <f aca="false">IF($G40="",0,IF(AND($G40&gt;='Cash Flow'!$E$6,$G40&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I40" s="78" t="str">
-        <f aca="false">IF($H40=1,INT(($G40-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H40=1,MAX(1,INT(($G40-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J40" s="38" t="str">
@@ -12504,18 +12515,18 @@
       </c>
       <c r="F41" s="77" t="n">
         <f aca="false">IF($C41="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*5,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*5,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,5),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$7="One Time",IF(6=1,Recurring!$F$7,""),""))))))</f>
-        <v>46422</v>
+        <v>46391</v>
       </c>
       <c r="G41" s="77" t="n">
         <f aca="false">IF($F41="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F41,2)=6,$F41-1,IF(WEEKDAY($F41,2)=7,$F41-2,$F41)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F41,2)=6,$F41+2,IF(WEEKDAY($F41,2)=7,$F41+1,$F41)),$F41)))</f>
-        <v>46422</v>
+        <v>46391</v>
       </c>
       <c r="H41" s="78" t="n">
         <f aca="false">IF($G41="",0,IF(AND($G41&gt;='Cash Flow'!$E$6,$G41&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I41" s="78" t="str">
-        <f aca="false">IF($H41=1,INT(($G41-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H41=1,MAX(1,INT(($G41-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J41" s="38" t="str">
@@ -12548,18 +12559,18 @@
       </c>
       <c r="F42" s="77" t="n">
         <f aca="false">IF($C42="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*6,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*6,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,6),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$7="One Time",IF(7=1,Recurring!$F$7,""),""))))))</f>
-        <v>46450</v>
+        <v>46422</v>
       </c>
       <c r="G42" s="77" t="n">
         <f aca="false">IF($F42="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F42,2)=6,$F42-1,IF(WEEKDAY($F42,2)=7,$F42-2,$F42)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F42,2)=6,$F42+2,IF(WEEKDAY($F42,2)=7,$F42+1,$F42)),$F42)))</f>
-        <v>46450</v>
+        <v>46422</v>
       </c>
       <c r="H42" s="78" t="n">
         <f aca="false">IF($G42="",0,IF(AND($G42&gt;='Cash Flow'!$E$6,$G42&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I42" s="78" t="str">
-        <f aca="false">IF($H42=1,INT(($G42-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H42=1,MAX(1,INT(($G42-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J42" s="38" t="str">
@@ -12592,18 +12603,18 @@
       </c>
       <c r="F43" s="77" t="n">
         <f aca="false">IF($C43="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*7,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*7,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,7),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$7="One Time",IF(8=1,Recurring!$F$7,""),""))))))</f>
-        <v>46481</v>
+        <v>46450</v>
       </c>
       <c r="G43" s="77" t="n">
         <f aca="false">IF($F43="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F43,2)=6,$F43-1,IF(WEEKDAY($F43,2)=7,$F43-2,$F43)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F43,2)=6,$F43+2,IF(WEEKDAY($F43,2)=7,$F43+1,$F43)),$F43)))</f>
-        <v>46481</v>
+        <v>46450</v>
       </c>
       <c r="H43" s="78" t="n">
         <f aca="false">IF($G43="",0,IF(AND($G43&gt;='Cash Flow'!$E$6,$G43&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I43" s="78" t="str">
-        <f aca="false">IF($H43=1,INT(($G43-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H43=1,MAX(1,INT(($G43-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J43" s="38" t="str">
@@ -12636,18 +12647,18 @@
       </c>
       <c r="F44" s="77" t="n">
         <f aca="false">IF($C44="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*8,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*8,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,8),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$7="One Time",IF(9=1,Recurring!$F$7,""),""))))))</f>
-        <v>46511</v>
+        <v>46481</v>
       </c>
       <c r="G44" s="77" t="n">
         <f aca="false">IF($F44="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F44,2)=6,$F44-1,IF(WEEKDAY($F44,2)=7,$F44-2,$F44)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F44,2)=6,$F44+2,IF(WEEKDAY($F44,2)=7,$F44+1,$F44)),$F44)))</f>
-        <v>46511</v>
+        <v>46481</v>
       </c>
       <c r="H44" s="78" t="n">
         <f aca="false">IF($G44="",0,IF(AND($G44&gt;='Cash Flow'!$E$6,$G44&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I44" s="78" t="str">
-        <f aca="false">IF($H44=1,INT(($G44-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H44=1,MAX(1,INT(($G44-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J44" s="38" t="str">
@@ -12680,18 +12691,18 @@
       </c>
       <c r="F45" s="77" t="n">
         <f aca="false">IF($C45="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*9,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*9,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,9),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$7="One Time",IF(10=1,Recurring!$F$7,""),""))))))</f>
-        <v>46542</v>
+        <v>46511</v>
       </c>
       <c r="G45" s="77" t="n">
         <f aca="false">IF($F45="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F45,2)=6,$F45-1,IF(WEEKDAY($F45,2)=7,$F45-2,$F45)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F45,2)=6,$F45+2,IF(WEEKDAY($F45,2)=7,$F45+1,$F45)),$F45)))</f>
-        <v>46542</v>
+        <v>46511</v>
       </c>
       <c r="H45" s="78" t="n">
         <f aca="false">IF($G45="",0,IF(AND($G45&gt;='Cash Flow'!$E$6,$G45&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I45" s="78" t="str">
-        <f aca="false">IF($H45=1,INT(($G45-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H45=1,MAX(1,INT(($G45-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J45" s="38" t="str">
@@ -12724,18 +12735,18 @@
       </c>
       <c r="F46" s="77" t="n">
         <f aca="false">IF($C46="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*10,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*10,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,10),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$7="One Time",IF(11=1,Recurring!$F$7,""),""))))))</f>
-        <v>46572</v>
+        <v>46542</v>
       </c>
       <c r="G46" s="77" t="n">
         <f aca="false">IF($F46="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F46,2)=6,$F46-1,IF(WEEKDAY($F46,2)=7,$F46-2,$F46)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F46,2)=6,$F46+2,IF(WEEKDAY($F46,2)=7,$F46+1,$F46)),$F46)))</f>
-        <v>46572</v>
+        <v>46542</v>
       </c>
       <c r="H46" s="78" t="n">
         <f aca="false">IF($G46="",0,IF(AND($G46&gt;='Cash Flow'!$E$6,$G46&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I46" s="78" t="str">
-        <f aca="false">IF($H46=1,INT(($G46-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H46=1,MAX(1,INT(($G46-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J46" s="38" t="str">
@@ -12768,18 +12779,18 @@
       </c>
       <c r="F47" s="77" t="n">
         <f aca="false">IF($C47="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*11,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*11,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,11),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$7="One Time",IF(12=1,Recurring!$F$7,""),""))))))</f>
-        <v>46603</v>
+        <v>46572</v>
       </c>
       <c r="G47" s="77" t="n">
         <f aca="false">IF($F47="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F47,2)=6,$F47-1,IF(WEEKDAY($F47,2)=7,$F47-2,$F47)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F47,2)=6,$F47+2,IF(WEEKDAY($F47,2)=7,$F47+1,$F47)),$F47)))</f>
-        <v>46603</v>
+        <v>46572</v>
       </c>
       <c r="H47" s="78" t="n">
         <f aca="false">IF($G47="",0,IF(AND($G47&gt;='Cash Flow'!$E$6,$G47&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I47" s="78" t="str">
-        <f aca="false">IF($H47=1,INT(($G47-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H47=1,MAX(1,INT(($G47-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J47" s="38" t="str">
@@ -12812,18 +12823,18 @@
       </c>
       <c r="F48" s="77" t="n">
         <f aca="false">IF($C48="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*12,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*12,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,12),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$7="One Time",IF(13=1,Recurring!$F$7,""),""))))))</f>
-        <v>46634</v>
+        <v>46603</v>
       </c>
       <c r="G48" s="77" t="n">
         <f aca="false">IF($F48="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F48,2)=6,$F48-1,IF(WEEKDAY($F48,2)=7,$F48-2,$F48)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F48,2)=6,$F48+2,IF(WEEKDAY($F48,2)=7,$F48+1,$F48)),$F48)))</f>
-        <v>46634</v>
+        <v>46603</v>
       </c>
       <c r="H48" s="78" t="n">
         <f aca="false">IF($G48="",0,IF(AND($G48&gt;='Cash Flow'!$E$6,$G48&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I48" s="78" t="str">
-        <f aca="false">IF($H48=1,INT(($G48-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H48=1,MAX(1,INT(($G48-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J48" s="38" t="str">
@@ -12856,18 +12867,18 @@
       </c>
       <c r="F49" s="77" t="n">
         <f aca="false">IF($C49="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*13,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*13,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,13),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$7="One Time",IF(14=1,Recurring!$F$7,""),""))))))</f>
-        <v>46664</v>
+        <v>46634</v>
       </c>
       <c r="G49" s="77" t="n">
         <f aca="false">IF($F49="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F49,2)=6,$F49-1,IF(WEEKDAY($F49,2)=7,$F49-2,$F49)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F49,2)=6,$F49+2,IF(WEEKDAY($F49,2)=7,$F49+1,$F49)),$F49)))</f>
-        <v>46664</v>
+        <v>46634</v>
       </c>
       <c r="H49" s="78" t="n">
         <f aca="false">IF($G49="",0,IF(AND($G49&gt;='Cash Flow'!$E$6,$G49&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I49" s="78" t="str">
-        <f aca="false">IF($H49=1,INT(($G49-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H49=1,MAX(1,INT(($G49-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J49" s="38" t="str">
@@ -12900,18 +12911,18 @@
       </c>
       <c r="F50" s="77" t="n">
         <f aca="false">IF($C50="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*14,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*14,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,14),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$7="One Time",IF(15=1,Recurring!$F$7,""),""))))))</f>
-        <v>46695</v>
+        <v>46664</v>
       </c>
       <c r="G50" s="77" t="n">
         <f aca="false">IF($F50="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F50,2)=6,$F50-1,IF(WEEKDAY($F50,2)=7,$F50-2,$F50)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F50,2)=6,$F50+2,IF(WEEKDAY($F50,2)=7,$F50+1,$F50)),$F50)))</f>
-        <v>46695</v>
+        <v>46664</v>
       </c>
       <c r="H50" s="78" t="n">
         <f aca="false">IF($G50="",0,IF(AND($G50&gt;='Cash Flow'!$E$6,$G50&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I50" s="78" t="str">
-        <f aca="false">IF($H50=1,INT(($G50-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H50=1,MAX(1,INT(($G50-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J50" s="38" t="str">
@@ -12944,18 +12955,18 @@
       </c>
       <c r="F51" s="77" t="n">
         <f aca="false">IF($C51="","",IF(Recurring!$E$7="Weekly",Recurring!$F$7+7*15,IF(Recurring!$E$7="Every 2 Weeks",Recurring!$F$7+14*15,IF(Recurring!$E$7="Monthly",EDATE(Recurring!$F$7,15),IF(Recurring!$E$7="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$7,INT((IF(DAY(Recurring!$F$7)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$7="One Time",IF(16=1,Recurring!$F$7,""),""))))))</f>
-        <v>46725</v>
+        <v>46695</v>
       </c>
       <c r="G51" s="77" t="n">
         <f aca="false">IF($F51="","",IF(Recurring!$G$7="Move Before",IF(WEEKDAY($F51,2)=6,$F51-1,IF(WEEKDAY($F51,2)=7,$F51-2,$F51)),IF(Recurring!$G$7="Move After",IF(WEEKDAY($F51,2)=6,$F51+2,IF(WEEKDAY($F51,2)=7,$F51+1,$F51)),$F51)))</f>
-        <v>46725</v>
+        <v>46695</v>
       </c>
       <c r="H51" s="78" t="n">
         <f aca="false">IF($G51="",0,IF(AND($G51&gt;='Cash Flow'!$E$6,$G51&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I51" s="78" t="str">
-        <f aca="false">IF($H51=1,INT(($G51-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H51=1,MAX(1,INT(($G51-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J51" s="38" t="str">
@@ -12988,27 +12999,27 @@
       </c>
       <c r="F52" s="77" t="n">
         <f aca="false">IF($C52="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*0,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*0,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,0),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$8="One Time",IF(1=1,Recurring!$F$8,""),""))))))</f>
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="G52" s="77" t="n">
         <f aca="false">IF($F52="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F52,2)=6,$F52-1,IF(WEEKDAY($F52,2)=7,$F52-2,$F52)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F52,2)=6,$F52+2,IF(WEEKDAY($F52,2)=7,$F52+1,$F52)),$F52)))</f>
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="H52" s="78" t="n">
-        <f aca="false">IF($G52="",0,IF(AND($G52&gt;='Cash Flow'!$E$6,$G52&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G52="",0,IF(AND($G52&gt;='Cash Flow'!$E$6-90,$G52&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I52" s="78" t="n">
-        <f aca="false">IF($H52=1,INT(($G52-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <f aca="false">IF($H52=1,MAX(1,INT(($G52-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>1</v>
       </c>
       <c r="J52" s="38" t="n">
         <f aca="false">IF($H52=1,$G52*10000+ROW(),"")</f>
-        <v>462700052</v>
+        <v>462390052</v>
       </c>
       <c r="K52" s="38" t="n">
         <f aca="false">IF($H52=1,$I52*1000+COUNTIFS($I$4:$I$483,$I52,$J$4:$J$483,"&lt;"&amp;$J52)+1,"")</f>
-        <v>5003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13032,27 +13043,27 @@
       </c>
       <c r="F53" s="77" t="n">
         <f aca="false">IF($C53="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*1,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*1,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,1),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$8="One Time",IF(2=1,Recurring!$F$8,""),""))))))</f>
-        <v>46300</v>
+        <v>46270</v>
       </c>
       <c r="G53" s="77" t="n">
         <f aca="false">IF($F53="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F53,2)=6,$F53-1,IF(WEEKDAY($F53,2)=7,$F53-2,$F53)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F53,2)=6,$F53+2,IF(WEEKDAY($F53,2)=7,$F53+1,$F53)),$F53)))</f>
-        <v>46300</v>
+        <v>46270</v>
       </c>
       <c r="H53" s="78" t="n">
         <f aca="false">IF($G53="",0,IF(AND($G53&gt;='Cash Flow'!$E$6,$G53&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I53" s="78" t="n">
-        <f aca="false">IF($H53=1,INT(($G53-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <f aca="false">IF($H53=1,MAX(1,INT(($G53-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>5</v>
       </c>
       <c r="J53" s="38" t="n">
         <f aca="false">IF($H53=1,$G53*10000+ROW(),"")</f>
-        <v>463000053</v>
+        <v>462700053</v>
       </c>
       <c r="K53" s="38" t="n">
         <f aca="false">IF($H53=1,$I53*1000+COUNTIFS($I$4:$I$483,$I53,$J$4:$J$483,"&lt;"&amp;$J53)+1,"")</f>
-        <v>9003</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13076,27 +13087,27 @@
       </c>
       <c r="F54" s="77" t="n">
         <f aca="false">IF($C54="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*2,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*2,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,2),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$8="One Time",IF(3=1,Recurring!$F$8,""),""))))))</f>
-        <v>46331</v>
+        <v>46300</v>
       </c>
       <c r="G54" s="77" t="n">
         <f aca="false">IF($F54="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F54,2)=6,$F54-1,IF(WEEKDAY($F54,2)=7,$F54-2,$F54)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F54,2)=6,$F54+2,IF(WEEKDAY($F54,2)=7,$F54+1,$F54)),$F54)))</f>
-        <v>46331</v>
+        <v>46300</v>
       </c>
       <c r="H54" s="78" t="n">
         <f aca="false">IF($G54="",0,IF(AND($G54&gt;='Cash Flow'!$E$6,$G54&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I54" s="78" t="n">
-        <f aca="false">IF($H54=1,INT(($G54-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <f aca="false">IF($H54=1,MAX(1,INT(($G54-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>9</v>
       </c>
       <c r="J54" s="38" t="n">
         <f aca="false">IF($H54=1,$G54*10000+ROW(),"")</f>
-        <v>463310054</v>
+        <v>463000054</v>
       </c>
       <c r="K54" s="38" t="n">
         <f aca="false">IF($H54=1,$I54*1000+COUNTIFS($I$4:$I$483,$I54,$J$4:$J$483,"&lt;"&amp;$J54)+1,"")</f>
-        <v>13007</v>
+        <v>9003</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13120,27 +13131,27 @@
       </c>
       <c r="F55" s="77" t="n">
         <f aca="false">IF($C55="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*3,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*3,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,3),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$8="One Time",IF(4=1,Recurring!$F$8,""),""))))))</f>
-        <v>46361</v>
+        <v>46331</v>
       </c>
       <c r="G55" s="77" t="n">
         <f aca="false">IF($F55="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F55,2)=6,$F55-1,IF(WEEKDAY($F55,2)=7,$F55-2,$F55)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F55,2)=6,$F55+2,IF(WEEKDAY($F55,2)=7,$F55+1,$F55)),$F55)))</f>
-        <v>46361</v>
+        <v>46331</v>
       </c>
       <c r="H55" s="78" t="n">
         <f aca="false">IF($G55="",0,IF(AND($G55&gt;='Cash Flow'!$E$6,$G55&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I55" s="78" t="str">
-        <f aca="false">IF($H55=1,INT(($G55-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J55" s="38" t="str">
+        <v>1</v>
+      </c>
+      <c r="I55" s="78" t="n">
+        <f aca="false">IF($H55=1,MAX(1,INT(($G55-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J55" s="38" t="n">
         <f aca="false">IF($H55=1,$G55*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K55" s="38" t="str">
+        <v>463310055</v>
+      </c>
+      <c r="K55" s="38" t="n">
         <f aca="false">IF($H55=1,$I55*1000+COUNTIFS($I$4:$I$483,$I55,$J$4:$J$483,"&lt;"&amp;$J55)+1,"")</f>
-        <v/>
+        <v>13007</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13164,18 +13175,18 @@
       </c>
       <c r="F56" s="77" t="n">
         <f aca="false">IF($C56="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*4,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*4,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,4),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$8="One Time",IF(5=1,Recurring!$F$8,""),""))))))</f>
-        <v>46392</v>
+        <v>46361</v>
       </c>
       <c r="G56" s="77" t="n">
         <f aca="false">IF($F56="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F56,2)=6,$F56-1,IF(WEEKDAY($F56,2)=7,$F56-2,$F56)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F56,2)=6,$F56+2,IF(WEEKDAY($F56,2)=7,$F56+1,$F56)),$F56)))</f>
-        <v>46392</v>
+        <v>46361</v>
       </c>
       <c r="H56" s="78" t="n">
         <f aca="false">IF($G56="",0,IF(AND($G56&gt;='Cash Flow'!$E$6,$G56&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I56" s="78" t="str">
-        <f aca="false">IF($H56=1,INT(($G56-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H56=1,MAX(1,INT(($G56-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J56" s="38" t="str">
@@ -13208,18 +13219,18 @@
       </c>
       <c r="F57" s="77" t="n">
         <f aca="false">IF($C57="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*5,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*5,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,5),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$8="One Time",IF(6=1,Recurring!$F$8,""),""))))))</f>
-        <v>46423</v>
+        <v>46392</v>
       </c>
       <c r="G57" s="77" t="n">
         <f aca="false">IF($F57="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F57,2)=6,$F57-1,IF(WEEKDAY($F57,2)=7,$F57-2,$F57)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F57,2)=6,$F57+2,IF(WEEKDAY($F57,2)=7,$F57+1,$F57)),$F57)))</f>
-        <v>46423</v>
+        <v>46392</v>
       </c>
       <c r="H57" s="78" t="n">
         <f aca="false">IF($G57="",0,IF(AND($G57&gt;='Cash Flow'!$E$6,$G57&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I57" s="78" t="str">
-        <f aca="false">IF($H57=1,INT(($G57-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H57=1,MAX(1,INT(($G57-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J57" s="38" t="str">
@@ -13252,18 +13263,18 @@
       </c>
       <c r="F58" s="77" t="n">
         <f aca="false">IF($C58="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*6,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*6,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,6),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$8="One Time",IF(7=1,Recurring!$F$8,""),""))))))</f>
-        <v>46451</v>
+        <v>46423</v>
       </c>
       <c r="G58" s="77" t="n">
         <f aca="false">IF($F58="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F58,2)=6,$F58-1,IF(WEEKDAY($F58,2)=7,$F58-2,$F58)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F58,2)=6,$F58+2,IF(WEEKDAY($F58,2)=7,$F58+1,$F58)),$F58)))</f>
-        <v>46451</v>
+        <v>46423</v>
       </c>
       <c r="H58" s="78" t="n">
         <f aca="false">IF($G58="",0,IF(AND($G58&gt;='Cash Flow'!$E$6,$G58&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I58" s="78" t="str">
-        <f aca="false">IF($H58=1,INT(($G58-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H58=1,MAX(1,INT(($G58-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J58" s="38" t="str">
@@ -13296,18 +13307,18 @@
       </c>
       <c r="F59" s="77" t="n">
         <f aca="false">IF($C59="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*7,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*7,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,7),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$8="One Time",IF(8=1,Recurring!$F$8,""),""))))))</f>
-        <v>46482</v>
+        <v>46451</v>
       </c>
       <c r="G59" s="77" t="n">
         <f aca="false">IF($F59="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F59,2)=6,$F59-1,IF(WEEKDAY($F59,2)=7,$F59-2,$F59)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F59,2)=6,$F59+2,IF(WEEKDAY($F59,2)=7,$F59+1,$F59)),$F59)))</f>
-        <v>46482</v>
+        <v>46451</v>
       </c>
       <c r="H59" s="78" t="n">
         <f aca="false">IF($G59="",0,IF(AND($G59&gt;='Cash Flow'!$E$6,$G59&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I59" s="78" t="str">
-        <f aca="false">IF($H59=1,INT(($G59-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H59=1,MAX(1,INT(($G59-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J59" s="38" t="str">
@@ -13340,18 +13351,18 @@
       </c>
       <c r="F60" s="77" t="n">
         <f aca="false">IF($C60="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*8,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*8,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,8),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$8="One Time",IF(9=1,Recurring!$F$8,""),""))))))</f>
-        <v>46512</v>
+        <v>46482</v>
       </c>
       <c r="G60" s="77" t="n">
         <f aca="false">IF($F60="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F60,2)=6,$F60-1,IF(WEEKDAY($F60,2)=7,$F60-2,$F60)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F60,2)=6,$F60+2,IF(WEEKDAY($F60,2)=7,$F60+1,$F60)),$F60)))</f>
-        <v>46512</v>
+        <v>46482</v>
       </c>
       <c r="H60" s="78" t="n">
         <f aca="false">IF($G60="",0,IF(AND($G60&gt;='Cash Flow'!$E$6,$G60&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I60" s="78" t="str">
-        <f aca="false">IF($H60=1,INT(($G60-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H60=1,MAX(1,INT(($G60-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J60" s="38" t="str">
@@ -13384,18 +13395,18 @@
       </c>
       <c r="F61" s="77" t="n">
         <f aca="false">IF($C61="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*9,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*9,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,9),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$8="One Time",IF(10=1,Recurring!$F$8,""),""))))))</f>
-        <v>46543</v>
+        <v>46512</v>
       </c>
       <c r="G61" s="77" t="n">
         <f aca="false">IF($F61="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F61,2)=6,$F61-1,IF(WEEKDAY($F61,2)=7,$F61-2,$F61)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F61,2)=6,$F61+2,IF(WEEKDAY($F61,2)=7,$F61+1,$F61)),$F61)))</f>
-        <v>46543</v>
+        <v>46512</v>
       </c>
       <c r="H61" s="78" t="n">
         <f aca="false">IF($G61="",0,IF(AND($G61&gt;='Cash Flow'!$E$6,$G61&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I61" s="78" t="str">
-        <f aca="false">IF($H61=1,INT(($G61-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H61=1,MAX(1,INT(($G61-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J61" s="38" t="str">
@@ -13428,18 +13439,18 @@
       </c>
       <c r="F62" s="77" t="n">
         <f aca="false">IF($C62="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*10,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*10,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,10),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$8="One Time",IF(11=1,Recurring!$F$8,""),""))))))</f>
-        <v>46573</v>
+        <v>46543</v>
       </c>
       <c r="G62" s="77" t="n">
         <f aca="false">IF($F62="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F62,2)=6,$F62-1,IF(WEEKDAY($F62,2)=7,$F62-2,$F62)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F62,2)=6,$F62+2,IF(WEEKDAY($F62,2)=7,$F62+1,$F62)),$F62)))</f>
-        <v>46573</v>
+        <v>46543</v>
       </c>
       <c r="H62" s="78" t="n">
         <f aca="false">IF($G62="",0,IF(AND($G62&gt;='Cash Flow'!$E$6,$G62&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I62" s="78" t="str">
-        <f aca="false">IF($H62=1,INT(($G62-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H62=1,MAX(1,INT(($G62-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J62" s="38" t="str">
@@ -13472,18 +13483,18 @@
       </c>
       <c r="F63" s="77" t="n">
         <f aca="false">IF($C63="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*11,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*11,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,11),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$8="One Time",IF(12=1,Recurring!$F$8,""),""))))))</f>
-        <v>46604</v>
+        <v>46573</v>
       </c>
       <c r="G63" s="77" t="n">
         <f aca="false">IF($F63="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F63,2)=6,$F63-1,IF(WEEKDAY($F63,2)=7,$F63-2,$F63)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F63,2)=6,$F63+2,IF(WEEKDAY($F63,2)=7,$F63+1,$F63)),$F63)))</f>
-        <v>46604</v>
+        <v>46573</v>
       </c>
       <c r="H63" s="78" t="n">
         <f aca="false">IF($G63="",0,IF(AND($G63&gt;='Cash Flow'!$E$6,$G63&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I63" s="78" t="str">
-        <f aca="false">IF($H63=1,INT(($G63-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H63=1,MAX(1,INT(($G63-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J63" s="38" t="str">
@@ -13516,18 +13527,18 @@
       </c>
       <c r="F64" s="77" t="n">
         <f aca="false">IF($C64="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*12,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*12,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,12),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$8="One Time",IF(13=1,Recurring!$F$8,""),""))))))</f>
-        <v>46635</v>
+        <v>46604</v>
       </c>
       <c r="G64" s="77" t="n">
         <f aca="false">IF($F64="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F64,2)=6,$F64-1,IF(WEEKDAY($F64,2)=7,$F64-2,$F64)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F64,2)=6,$F64+2,IF(WEEKDAY($F64,2)=7,$F64+1,$F64)),$F64)))</f>
-        <v>46635</v>
+        <v>46604</v>
       </c>
       <c r="H64" s="78" t="n">
         <f aca="false">IF($G64="",0,IF(AND($G64&gt;='Cash Flow'!$E$6,$G64&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I64" s="78" t="str">
-        <f aca="false">IF($H64=1,INT(($G64-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H64=1,MAX(1,INT(($G64-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J64" s="38" t="str">
@@ -13560,18 +13571,18 @@
       </c>
       <c r="F65" s="77" t="n">
         <f aca="false">IF($C65="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*13,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*13,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,13),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$8="One Time",IF(14=1,Recurring!$F$8,""),""))))))</f>
-        <v>46665</v>
+        <v>46635</v>
       </c>
       <c r="G65" s="77" t="n">
         <f aca="false">IF($F65="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F65,2)=6,$F65-1,IF(WEEKDAY($F65,2)=7,$F65-2,$F65)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F65,2)=6,$F65+2,IF(WEEKDAY($F65,2)=7,$F65+1,$F65)),$F65)))</f>
-        <v>46665</v>
+        <v>46635</v>
       </c>
       <c r="H65" s="78" t="n">
         <f aca="false">IF($G65="",0,IF(AND($G65&gt;='Cash Flow'!$E$6,$G65&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I65" s="78" t="str">
-        <f aca="false">IF($H65=1,INT(($G65-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H65=1,MAX(1,INT(($G65-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J65" s="38" t="str">
@@ -13604,18 +13615,18 @@
       </c>
       <c r="F66" s="77" t="n">
         <f aca="false">IF($C66="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*14,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*14,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,14),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$8="One Time",IF(15=1,Recurring!$F$8,""),""))))))</f>
-        <v>46696</v>
+        <v>46665</v>
       </c>
       <c r="G66" s="77" t="n">
         <f aca="false">IF($F66="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F66,2)=6,$F66-1,IF(WEEKDAY($F66,2)=7,$F66-2,$F66)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F66,2)=6,$F66+2,IF(WEEKDAY($F66,2)=7,$F66+1,$F66)),$F66)))</f>
-        <v>46696</v>
+        <v>46665</v>
       </c>
       <c r="H66" s="78" t="n">
         <f aca="false">IF($G66="",0,IF(AND($G66&gt;='Cash Flow'!$E$6,$G66&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I66" s="78" t="str">
-        <f aca="false">IF($H66=1,INT(($G66-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H66=1,MAX(1,INT(($G66-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J66" s="38" t="str">
@@ -13648,18 +13659,18 @@
       </c>
       <c r="F67" s="77" t="n">
         <f aca="false">IF($C67="","",IF(Recurring!$E$8="Weekly",Recurring!$F$8+7*15,IF(Recurring!$E$8="Every 2 Weeks",Recurring!$F$8+14*15,IF(Recurring!$E$8="Monthly",EDATE(Recurring!$F$8,15),IF(Recurring!$E$8="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$8,INT((IF(DAY(Recurring!$F$8)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$8="One Time",IF(16=1,Recurring!$F$8,""),""))))))</f>
-        <v>46726</v>
+        <v>46696</v>
       </c>
       <c r="G67" s="77" t="n">
         <f aca="false">IF($F67="","",IF(Recurring!$G$8="Move Before",IF(WEEKDAY($F67,2)=6,$F67-1,IF(WEEKDAY($F67,2)=7,$F67-2,$F67)),IF(Recurring!$G$8="Move After",IF(WEEKDAY($F67,2)=6,$F67+2,IF(WEEKDAY($F67,2)=7,$F67+1,$F67)),$F67)))</f>
-        <v>46726</v>
+        <v>46696</v>
       </c>
       <c r="H67" s="78" t="n">
         <f aca="false">IF($G67="",0,IF(AND($G67&gt;='Cash Flow'!$E$6,$G67&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I67" s="78" t="str">
-        <f aca="false">IF($H67=1,INT(($G67-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H67=1,MAX(1,INT(($G67-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J67" s="38" t="str">
@@ -13692,27 +13703,27 @@
       </c>
       <c r="F68" s="77" t="n">
         <f aca="false">IF($C68="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*0,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*0,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,0),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+0)/2))),15)),IF(Recurring!$E$9="One Time",IF(1=1,Recurring!$F$9,""),""))))))</f>
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="G68" s="77" t="n">
         <f aca="false">IF($F68="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F68,2)=6,$F68-1,IF(WEEKDAY($F68,2)=7,$F68-2,$F68)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F68,2)=6,$F68+2,IF(WEEKDAY($F68,2)=7,$F68+1,$F68)),$F68)))</f>
-        <v>46270</v>
+        <v>46239</v>
       </c>
       <c r="H68" s="78" t="n">
-        <f aca="false">IF($G68="",0,IF(AND($G68&gt;='Cash Flow'!$E$6,$G68&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G68="",0,IF(AND($G68&gt;='Cash Flow'!$E$6-90,$G68&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I68" s="78" t="n">
-        <f aca="false">IF($H68=1,INT(($G68-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>5</v>
+        <f aca="false">IF($H68=1,MAX(1,INT(($G68-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>1</v>
       </c>
       <c r="J68" s="38" t="n">
         <f aca="false">IF($H68=1,$G68*10000+ROW(),"")</f>
-        <v>462700068</v>
+        <v>462390068</v>
       </c>
       <c r="K68" s="38" t="n">
         <f aca="false">IF($H68=1,$I68*1000+COUNTIFS($I$4:$I$483,$I68,$J$4:$J$483,"&lt;"&amp;$J68)+1,"")</f>
-        <v>5004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13736,27 +13747,27 @@
       </c>
       <c r="F69" s="77" t="n">
         <f aca="false">IF($C69="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*1,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*1,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,1),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+1)/2))),15)),IF(Recurring!$E$9="One Time",IF(2=1,Recurring!$F$9,""),""))))))</f>
-        <v>46300</v>
+        <v>46270</v>
       </c>
       <c r="G69" s="77" t="n">
         <f aca="false">IF($F69="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F69,2)=6,$F69-1,IF(WEEKDAY($F69,2)=7,$F69-2,$F69)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F69,2)=6,$F69+2,IF(WEEKDAY($F69,2)=7,$F69+1,$F69)),$F69)))</f>
-        <v>46300</v>
+        <v>46270</v>
       </c>
       <c r="H69" s="78" t="n">
         <f aca="false">IF($G69="",0,IF(AND($G69&gt;='Cash Flow'!$E$6,$G69&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I69" s="78" t="n">
-        <f aca="false">IF($H69=1,INT(($G69-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>9</v>
+        <f aca="false">IF($H69=1,MAX(1,INT(($G69-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>5</v>
       </c>
       <c r="J69" s="38" t="n">
         <f aca="false">IF($H69=1,$G69*10000+ROW(),"")</f>
-        <v>463000069</v>
+        <v>462700069</v>
       </c>
       <c r="K69" s="38" t="n">
         <f aca="false">IF($H69=1,$I69*1000+COUNTIFS($I$4:$I$483,$I69,$J$4:$J$483,"&lt;"&amp;$J69)+1,"")</f>
-        <v>9004</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13780,27 +13791,27 @@
       </c>
       <c r="F70" s="77" t="n">
         <f aca="false">IF($C70="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*2,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*2,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,2),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+2)/2))),15)),IF(Recurring!$E$9="One Time",IF(3=1,Recurring!$F$9,""),""))))))</f>
-        <v>46331</v>
+        <v>46300</v>
       </c>
       <c r="G70" s="77" t="n">
         <f aca="false">IF($F70="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F70,2)=6,$F70-1,IF(WEEKDAY($F70,2)=7,$F70-2,$F70)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F70,2)=6,$F70+2,IF(WEEKDAY($F70,2)=7,$F70+1,$F70)),$F70)))</f>
-        <v>46331</v>
+        <v>46300</v>
       </c>
       <c r="H70" s="78" t="n">
         <f aca="false">IF($G70="",0,IF(AND($G70&gt;='Cash Flow'!$E$6,$G70&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I70" s="78" t="n">
-        <f aca="false">IF($H70=1,INT(($G70-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v>13</v>
+        <f aca="false">IF($H70=1,MAX(1,INT(($G70-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>9</v>
       </c>
       <c r="J70" s="38" t="n">
         <f aca="false">IF($H70=1,$G70*10000+ROW(),"")</f>
-        <v>463310070</v>
+        <v>463000070</v>
       </c>
       <c r="K70" s="38" t="n">
         <f aca="false">IF($H70=1,$I70*1000+COUNTIFS($I$4:$I$483,$I70,$J$4:$J$483,"&lt;"&amp;$J70)+1,"")</f>
-        <v>13008</v>
+        <v>9004</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13824,27 +13835,27 @@
       </c>
       <c r="F71" s="77" t="n">
         <f aca="false">IF($C71="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*3,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*3,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,3),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+3)/2))),15)),IF(Recurring!$E$9="One Time",IF(4=1,Recurring!$F$9,""),""))))))</f>
-        <v>46361</v>
+        <v>46331</v>
       </c>
       <c r="G71" s="77" t="n">
         <f aca="false">IF($F71="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F71,2)=6,$F71-1,IF(WEEKDAY($F71,2)=7,$F71-2,$F71)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F71,2)=6,$F71+2,IF(WEEKDAY($F71,2)=7,$F71+1,$F71)),$F71)))</f>
-        <v>46361</v>
+        <v>46331</v>
       </c>
       <c r="H71" s="78" t="n">
         <f aca="false">IF($G71="",0,IF(AND($G71&gt;='Cash Flow'!$E$6,$G71&lt;'Cash Flow'!$E$6+91),1,0))</f>
-        <v>0</v>
-      </c>
-      <c r="I71" s="78" t="str">
-        <f aca="false">IF($H71=1,INT(($G71-'Cash Flow'!$E$6)/7)+1,"")</f>
-        <v/>
-      </c>
-      <c r="J71" s="38" t="str">
+        <v>1</v>
+      </c>
+      <c r="I71" s="78" t="n">
+        <f aca="false">IF($H71=1,MAX(1,INT(($G71-'Cash Flow'!$E$6)/7)+1),"")</f>
+        <v>13</v>
+      </c>
+      <c r="J71" s="38" t="n">
         <f aca="false">IF($H71=1,$G71*10000+ROW(),"")</f>
-        <v/>
-      </c>
-      <c r="K71" s="38" t="str">
+        <v>463310071</v>
+      </c>
+      <c r="K71" s="38" t="n">
         <f aca="false">IF($H71=1,$I71*1000+COUNTIFS($I$4:$I$483,$I71,$J$4:$J$483,"&lt;"&amp;$J71)+1,"")</f>
-        <v/>
+        <v>13008</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13868,18 +13879,18 @@
       </c>
       <c r="F72" s="77" t="n">
         <f aca="false">IF($C72="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*4,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*4,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,4),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+4)/2))),15)),IF(Recurring!$E$9="One Time",IF(5=1,Recurring!$F$9,""),""))))))</f>
-        <v>46392</v>
+        <v>46361</v>
       </c>
       <c r="G72" s="77" t="n">
         <f aca="false">IF($F72="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F72,2)=6,$F72-1,IF(WEEKDAY($F72,2)=7,$F72-2,$F72)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F72,2)=6,$F72+2,IF(WEEKDAY($F72,2)=7,$F72+1,$F72)),$F72)))</f>
-        <v>46392</v>
+        <v>46361</v>
       </c>
       <c r="H72" s="78" t="n">
         <f aca="false">IF($G72="",0,IF(AND($G72&gt;='Cash Flow'!$E$6,$G72&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I72" s="78" t="str">
-        <f aca="false">IF($H72=1,INT(($G72-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H72=1,MAX(1,INT(($G72-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J72" s="38" t="str">
@@ -13912,18 +13923,18 @@
       </c>
       <c r="F73" s="77" t="n">
         <f aca="false">IF($C73="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*5,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*5,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,5),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+5)/2))),15)),IF(Recurring!$E$9="One Time",IF(6=1,Recurring!$F$9,""),""))))))</f>
-        <v>46423</v>
+        <v>46392</v>
       </c>
       <c r="G73" s="77" t="n">
         <f aca="false">IF($F73="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F73,2)=6,$F73-1,IF(WEEKDAY($F73,2)=7,$F73-2,$F73)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F73,2)=6,$F73+2,IF(WEEKDAY($F73,2)=7,$F73+1,$F73)),$F73)))</f>
-        <v>46423</v>
+        <v>46392</v>
       </c>
       <c r="H73" s="78" t="n">
         <f aca="false">IF($G73="",0,IF(AND($G73&gt;='Cash Flow'!$E$6,$G73&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I73" s="78" t="str">
-        <f aca="false">IF($H73=1,INT(($G73-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H73=1,MAX(1,INT(($G73-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J73" s="38" t="str">
@@ -13956,18 +13967,18 @@
       </c>
       <c r="F74" s="77" t="n">
         <f aca="false">IF($C74="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*6,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*6,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,6),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+6)/2))),15)),IF(Recurring!$E$9="One Time",IF(7=1,Recurring!$F$9,""),""))))))</f>
-        <v>46451</v>
+        <v>46423</v>
       </c>
       <c r="G74" s="77" t="n">
         <f aca="false">IF($F74="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F74,2)=6,$F74-1,IF(WEEKDAY($F74,2)=7,$F74-2,$F74)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F74,2)=6,$F74+2,IF(WEEKDAY($F74,2)=7,$F74+1,$F74)),$F74)))</f>
-        <v>46451</v>
+        <v>46423</v>
       </c>
       <c r="H74" s="78" t="n">
         <f aca="false">IF($G74="",0,IF(AND($G74&gt;='Cash Flow'!$E$6,$G74&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I74" s="78" t="str">
-        <f aca="false">IF($H74=1,INT(($G74-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H74=1,MAX(1,INT(($G74-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J74" s="38" t="str">
@@ -14000,18 +14011,18 @@
       </c>
       <c r="F75" s="77" t="n">
         <f aca="false">IF($C75="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*7,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*7,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,7),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+7)/2))),15)),IF(Recurring!$E$9="One Time",IF(8=1,Recurring!$F$9,""),""))))))</f>
-        <v>46482</v>
+        <v>46451</v>
       </c>
       <c r="G75" s="77" t="n">
         <f aca="false">IF($F75="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F75,2)=6,$F75-1,IF(WEEKDAY($F75,2)=7,$F75-2,$F75)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F75,2)=6,$F75+2,IF(WEEKDAY($F75,2)=7,$F75+1,$F75)),$F75)))</f>
-        <v>46482</v>
+        <v>46451</v>
       </c>
       <c r="H75" s="78" t="n">
         <f aca="false">IF($G75="",0,IF(AND($G75&gt;='Cash Flow'!$E$6,$G75&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I75" s="78" t="str">
-        <f aca="false">IF($H75=1,INT(($G75-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H75=1,MAX(1,INT(($G75-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J75" s="38" t="str">
@@ -14044,18 +14055,18 @@
       </c>
       <c r="F76" s="77" t="n">
         <f aca="false">IF($C76="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*8,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*8,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,8),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+8)/2))),15)),IF(Recurring!$E$9="One Time",IF(9=1,Recurring!$F$9,""),""))))))</f>
-        <v>46512</v>
+        <v>46482</v>
       </c>
       <c r="G76" s="77" t="n">
         <f aca="false">IF($F76="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F76,2)=6,$F76-1,IF(WEEKDAY($F76,2)=7,$F76-2,$F76)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F76,2)=6,$F76+2,IF(WEEKDAY($F76,2)=7,$F76+1,$F76)),$F76)))</f>
-        <v>46512</v>
+        <v>46482</v>
       </c>
       <c r="H76" s="78" t="n">
         <f aca="false">IF($G76="",0,IF(AND($G76&gt;='Cash Flow'!$E$6,$G76&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I76" s="78" t="str">
-        <f aca="false">IF($H76=1,INT(($G76-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H76=1,MAX(1,INT(($G76-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J76" s="38" t="str">
@@ -14088,18 +14099,18 @@
       </c>
       <c r="F77" s="77" t="n">
         <f aca="false">IF($C77="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*9,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*9,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,9),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+9)/2))),15)),IF(Recurring!$E$9="One Time",IF(10=1,Recurring!$F$9,""),""))))))</f>
-        <v>46543</v>
+        <v>46512</v>
       </c>
       <c r="G77" s="77" t="n">
         <f aca="false">IF($F77="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F77,2)=6,$F77-1,IF(WEEKDAY($F77,2)=7,$F77-2,$F77)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F77,2)=6,$F77+2,IF(WEEKDAY($F77,2)=7,$F77+1,$F77)),$F77)))</f>
-        <v>46543</v>
+        <v>46512</v>
       </c>
       <c r="H77" s="78" t="n">
         <f aca="false">IF($G77="",0,IF(AND($G77&gt;='Cash Flow'!$E$6,$G77&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I77" s="78" t="str">
-        <f aca="false">IF($H77=1,INT(($G77-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H77=1,MAX(1,INT(($G77-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J77" s="38" t="str">
@@ -14132,18 +14143,18 @@
       </c>
       <c r="F78" s="77" t="n">
         <f aca="false">IF($C78="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*10,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*10,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,10),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+10)/2))),15)),IF(Recurring!$E$9="One Time",IF(11=1,Recurring!$F$9,""),""))))))</f>
-        <v>46573</v>
+        <v>46543</v>
       </c>
       <c r="G78" s="77" t="n">
         <f aca="false">IF($F78="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F78,2)=6,$F78-1,IF(WEEKDAY($F78,2)=7,$F78-2,$F78)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F78,2)=6,$F78+2,IF(WEEKDAY($F78,2)=7,$F78+1,$F78)),$F78)))</f>
-        <v>46573</v>
+        <v>46543</v>
       </c>
       <c r="H78" s="78" t="n">
         <f aca="false">IF($G78="",0,IF(AND($G78&gt;='Cash Flow'!$E$6,$G78&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I78" s="78" t="str">
-        <f aca="false">IF($H78=1,INT(($G78-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H78=1,MAX(1,INT(($G78-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J78" s="38" t="str">
@@ -14176,18 +14187,18 @@
       </c>
       <c r="F79" s="77" t="n">
         <f aca="false">IF($C79="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*11,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*11,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,11),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+11)/2))),15)),IF(Recurring!$E$9="One Time",IF(12=1,Recurring!$F$9,""),""))))))</f>
-        <v>46604</v>
+        <v>46573</v>
       </c>
       <c r="G79" s="77" t="n">
         <f aca="false">IF($F79="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F79,2)=6,$F79-1,IF(WEEKDAY($F79,2)=7,$F79-2,$F79)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F79,2)=6,$F79+2,IF(WEEKDAY($F79,2)=7,$F79+1,$F79)),$F79)))</f>
-        <v>46604</v>
+        <v>46573</v>
       </c>
       <c r="H79" s="78" t="n">
         <f aca="false">IF($G79="",0,IF(AND($G79&gt;='Cash Flow'!$E$6,$G79&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I79" s="78" t="str">
-        <f aca="false">IF($H79=1,INT(($G79-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H79=1,MAX(1,INT(($G79-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J79" s="38" t="str">
@@ -14220,18 +14231,18 @@
       </c>
       <c r="F80" s="77" t="n">
         <f aca="false">IF($C80="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*12,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*12,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,12),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+12)/2))),15)),IF(Recurring!$E$9="One Time",IF(13=1,Recurring!$F$9,""),""))))))</f>
-        <v>46635</v>
+        <v>46604</v>
       </c>
       <c r="G80" s="77" t="n">
         <f aca="false">IF($F80="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F80,2)=6,$F80-1,IF(WEEKDAY($F80,2)=7,$F80-2,$F80)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F80,2)=6,$F80+2,IF(WEEKDAY($F80,2)=7,$F80+1,$F80)),$F80)))</f>
-        <v>46635</v>
+        <v>46604</v>
       </c>
       <c r="H80" s="78" t="n">
         <f aca="false">IF($G80="",0,IF(AND($G80&gt;='Cash Flow'!$E$6,$G80&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I80" s="78" t="str">
-        <f aca="false">IF($H80=1,INT(($G80-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H80=1,MAX(1,INT(($G80-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J80" s="38" t="str">
@@ -14264,18 +14275,18 @@
       </c>
       <c r="F81" s="77" t="n">
         <f aca="false">IF($C81="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*13,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*13,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,13),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+13)/2))),15)),IF(Recurring!$E$9="One Time",IF(14=1,Recurring!$F$9,""),""))))))</f>
-        <v>46665</v>
+        <v>46635</v>
       </c>
       <c r="G81" s="77" t="n">
         <f aca="false">IF($F81="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F81,2)=6,$F81-1,IF(WEEKDAY($F81,2)=7,$F81-2,$F81)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F81,2)=6,$F81+2,IF(WEEKDAY($F81,2)=7,$F81+1,$F81)),$F81)))</f>
-        <v>46665</v>
+        <v>46635</v>
       </c>
       <c r="H81" s="78" t="n">
         <f aca="false">IF($G81="",0,IF(AND($G81&gt;='Cash Flow'!$E$6,$G81&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I81" s="78" t="str">
-        <f aca="false">IF($H81=1,INT(($G81-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H81=1,MAX(1,INT(($G81-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J81" s="38" t="str">
@@ -14308,18 +14319,18 @@
       </c>
       <c r="F82" s="77" t="n">
         <f aca="false">IF($C82="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*14,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*14,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,14),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+14)/2))),15)),IF(Recurring!$E$9="One Time",IF(15=1,Recurring!$F$9,""),""))))))</f>
-        <v>46696</v>
+        <v>46665</v>
       </c>
       <c r="G82" s="77" t="n">
         <f aca="false">IF($F82="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F82,2)=6,$F82-1,IF(WEEKDAY($F82,2)=7,$F82-2,$F82)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F82,2)=6,$F82+2,IF(WEEKDAY($F82,2)=7,$F82+1,$F82)),$F82)))</f>
-        <v>46696</v>
+        <v>46665</v>
       </c>
       <c r="H82" s="78" t="n">
         <f aca="false">IF($G82="",0,IF(AND($G82&gt;='Cash Flow'!$E$6,$G82&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I82" s="78" t="str">
-        <f aca="false">IF($H82=1,INT(($G82-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H82=1,MAX(1,INT(($G82-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J82" s="38" t="str">
@@ -14352,18 +14363,18 @@
       </c>
       <c r="F83" s="77" t="n">
         <f aca="false">IF($C83="","",IF(Recurring!$E$9="Weekly",Recurring!$F$9+7*15,IF(Recurring!$E$9="Every 2 Weeks",Recurring!$F$9+14*15,IF(Recurring!$E$9="Monthly",EDATE(Recurring!$F$9,15),IF(Recurring!$E$9="Twice a Month",IF(MOD((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15),2)=1,EOMONTH(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15)/2)),DATE(YEAR(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15)/2))),MONTH(EDATE(Recurring!$F$9,INT((IF(DAY(Recurring!$F$9)&lt;=20,0,1)+15)/2))),15)),IF(Recurring!$E$9="One Time",IF(16=1,Recurring!$F$9,""),""))))))</f>
-        <v>46726</v>
+        <v>46696</v>
       </c>
       <c r="G83" s="77" t="n">
         <f aca="false">IF($F83="","",IF(Recurring!$G$9="Move Before",IF(WEEKDAY($F83,2)=6,$F83-1,IF(WEEKDAY($F83,2)=7,$F83-2,$F83)),IF(Recurring!$G$9="Move After",IF(WEEKDAY($F83,2)=6,$F83+2,IF(WEEKDAY($F83,2)=7,$F83+1,$F83)),$F83)))</f>
-        <v>46726</v>
+        <v>46696</v>
       </c>
       <c r="H83" s="78" t="n">
         <f aca="false">IF($G83="",0,IF(AND($G83&gt;='Cash Flow'!$E$6,$G83&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I83" s="78" t="str">
-        <f aca="false">IF($H83=1,INT(($G83-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H83=1,MAX(1,INT(($G83-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J83" s="38" t="str">
@@ -14403,11 +14414,11 @@
         <v>46272</v>
       </c>
       <c r="H84" s="78" t="n">
-        <f aca="false">IF($G84="",0,IF(AND($G84&gt;='Cash Flow'!$E$6,$G84&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G84="",0,IF(AND($G84&gt;='Cash Flow'!$E$6-90,$G84&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I84" s="78" t="n">
-        <f aca="false">IF($H84=1,INT(($G84-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H84=1,MAX(1,INT(($G84-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>5</v>
       </c>
       <c r="J84" s="38" t="n">
@@ -14451,7 +14462,7 @@
         <v>1</v>
       </c>
       <c r="I85" s="78" t="n">
-        <f aca="false">IF($H85=1,INT(($G85-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H85=1,MAX(1,INT(($G85-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>9</v>
       </c>
       <c r="J85" s="38" t="n">
@@ -14495,7 +14506,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="78" t="str">
-        <f aca="false">IF($H86=1,INT(($G86-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H86=1,MAX(1,INT(($G86-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J86" s="38" t="str">
@@ -14539,7 +14550,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="78" t="str">
-        <f aca="false">IF($H87=1,INT(($G87-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H87=1,MAX(1,INT(($G87-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J87" s="38" t="str">
@@ -14583,7 +14594,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="78" t="str">
-        <f aca="false">IF($H88=1,INT(($G88-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H88=1,MAX(1,INT(($G88-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J88" s="38" t="str">
@@ -14627,7 +14638,7 @@
         <v>0</v>
       </c>
       <c r="I89" s="78" t="str">
-        <f aca="false">IF($H89=1,INT(($G89-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H89=1,MAX(1,INT(($G89-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J89" s="38" t="str">
@@ -14671,7 +14682,7 @@
         <v>0</v>
       </c>
       <c r="I90" s="78" t="str">
-        <f aca="false">IF($H90=1,INT(($G90-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H90=1,MAX(1,INT(($G90-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J90" s="38" t="str">
@@ -14715,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="78" t="str">
-        <f aca="false">IF($H91=1,INT(($G91-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H91=1,MAX(1,INT(($G91-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J91" s="38" t="str">
@@ -14759,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="78" t="str">
-        <f aca="false">IF($H92=1,INT(($G92-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H92=1,MAX(1,INT(($G92-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J92" s="38" t="str">
@@ -14803,7 +14814,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="78" t="str">
-        <f aca="false">IF($H93=1,INT(($G93-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H93=1,MAX(1,INT(($G93-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J93" s="38" t="str">
@@ -14847,7 +14858,7 @@
         <v>0</v>
       </c>
       <c r="I94" s="78" t="str">
-        <f aca="false">IF($H94=1,INT(($G94-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H94=1,MAX(1,INT(($G94-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J94" s="38" t="str">
@@ -14891,7 +14902,7 @@
         <v>0</v>
       </c>
       <c r="I95" s="78" t="str">
-        <f aca="false">IF($H95=1,INT(($G95-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H95=1,MAX(1,INT(($G95-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J95" s="38" t="str">
@@ -14935,7 +14946,7 @@
         <v>0</v>
       </c>
       <c r="I96" s="78" t="str">
-        <f aca="false">IF($H96=1,INT(($G96-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H96=1,MAX(1,INT(($G96-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J96" s="38" t="str">
@@ -14979,7 +14990,7 @@
         <v>0</v>
       </c>
       <c r="I97" s="78" t="str">
-        <f aca="false">IF($H97=1,INT(($G97-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H97=1,MAX(1,INT(($G97-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J97" s="38" t="str">
@@ -15023,7 +15034,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="78" t="str">
-        <f aca="false">IF($H98=1,INT(($G98-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H98=1,MAX(1,INT(($G98-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J98" s="38" t="str">
@@ -15067,7 +15078,7 @@
         <v>0</v>
       </c>
       <c r="I99" s="78" t="str">
-        <f aca="false">IF($H99=1,INT(($G99-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H99=1,MAX(1,INT(($G99-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J99" s="38" t="str">
@@ -15107,11 +15118,11 @@
         <v>46272</v>
       </c>
       <c r="H100" s="78" t="n">
-        <f aca="false">IF($G100="",0,IF(AND($G100&gt;='Cash Flow'!$E$6,$G100&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G100="",0,IF(AND($G100&gt;='Cash Flow'!$E$6-90,$G100&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I100" s="78" t="n">
-        <f aca="false">IF($H100=1,INT(($G100-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H100=1,MAX(1,INT(($G100-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>5</v>
       </c>
       <c r="J100" s="38" t="n">
@@ -15155,7 +15166,7 @@
         <v>1</v>
       </c>
       <c r="I101" s="78" t="n">
-        <f aca="false">IF($H101=1,INT(($G101-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H101=1,MAX(1,INT(($G101-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>9</v>
       </c>
       <c r="J101" s="38" t="n">
@@ -15199,7 +15210,7 @@
         <v>0</v>
       </c>
       <c r="I102" s="78" t="str">
-        <f aca="false">IF($H102=1,INT(($G102-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H102=1,MAX(1,INT(($G102-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J102" s="38" t="str">
@@ -15243,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="I103" s="78" t="str">
-        <f aca="false">IF($H103=1,INT(($G103-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H103=1,MAX(1,INT(($G103-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J103" s="38" t="str">
@@ -15287,7 +15298,7 @@
         <v>0</v>
       </c>
       <c r="I104" s="78" t="str">
-        <f aca="false">IF($H104=1,INT(($G104-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H104=1,MAX(1,INT(($G104-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J104" s="38" t="str">
@@ -15331,7 +15342,7 @@
         <v>0</v>
       </c>
       <c r="I105" s="78" t="str">
-        <f aca="false">IF($H105=1,INT(($G105-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H105=1,MAX(1,INT(($G105-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J105" s="38" t="str">
@@ -15375,7 +15386,7 @@
         <v>0</v>
       </c>
       <c r="I106" s="78" t="str">
-        <f aca="false">IF($H106=1,INT(($G106-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H106=1,MAX(1,INT(($G106-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J106" s="38" t="str">
@@ -15419,7 +15430,7 @@
         <v>0</v>
       </c>
       <c r="I107" s="78" t="str">
-        <f aca="false">IF($H107=1,INT(($G107-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H107=1,MAX(1,INT(($G107-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J107" s="38" t="str">
@@ -15463,7 +15474,7 @@
         <v>0</v>
       </c>
       <c r="I108" s="78" t="str">
-        <f aca="false">IF($H108=1,INT(($G108-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H108=1,MAX(1,INT(($G108-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J108" s="38" t="str">
@@ -15507,7 +15518,7 @@
         <v>0</v>
       </c>
       <c r="I109" s="78" t="str">
-        <f aca="false">IF($H109=1,INT(($G109-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H109=1,MAX(1,INT(($G109-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J109" s="38" t="str">
@@ -15551,7 +15562,7 @@
         <v>0</v>
       </c>
       <c r="I110" s="78" t="str">
-        <f aca="false">IF($H110=1,INT(($G110-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H110=1,MAX(1,INT(($G110-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J110" s="38" t="str">
@@ -15595,7 +15606,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="78" t="str">
-        <f aca="false">IF($H111=1,INT(($G111-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H111=1,MAX(1,INT(($G111-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J111" s="38" t="str">
@@ -15639,7 +15650,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="78" t="str">
-        <f aca="false">IF($H112=1,INT(($G112-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H112=1,MAX(1,INT(($G112-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J112" s="38" t="str">
@@ -15683,7 +15694,7 @@
         <v>0</v>
       </c>
       <c r="I113" s="78" t="str">
-        <f aca="false">IF($H113=1,INT(($G113-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H113=1,MAX(1,INT(($G113-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J113" s="38" t="str">
@@ -15727,7 +15738,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="78" t="str">
-        <f aca="false">IF($H114=1,INT(($G114-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H114=1,MAX(1,INT(($G114-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J114" s="38" t="str">
@@ -15771,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="78" t="str">
-        <f aca="false">IF($H115=1,INT(($G115-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H115=1,MAX(1,INT(($G115-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J115" s="38" t="str">
@@ -15811,11 +15822,11 @@
         <v>46275</v>
       </c>
       <c r="H116" s="78" t="n">
-        <f aca="false">IF($G116="",0,IF(AND($G116&gt;='Cash Flow'!$E$6,$G116&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G116="",0,IF(AND($G116&gt;='Cash Flow'!$E$6-90,$G116&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I116" s="78" t="n">
-        <f aca="false">IF($H116=1,INT(($G116-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H116=1,MAX(1,INT(($G116-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>5</v>
       </c>
       <c r="J116" s="38" t="n">
@@ -15859,7 +15870,7 @@
         <v>1</v>
       </c>
       <c r="I117" s="78" t="n">
-        <f aca="false">IF($H117=1,INT(($G117-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H117=1,MAX(1,INT(($G117-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>10</v>
       </c>
       <c r="J117" s="38" t="n">
@@ -15903,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="I118" s="78" t="str">
-        <f aca="false">IF($H118=1,INT(($G118-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H118=1,MAX(1,INT(($G118-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J118" s="38" t="str">
@@ -15947,7 +15958,7 @@
         <v>0</v>
       </c>
       <c r="I119" s="78" t="str">
-        <f aca="false">IF($H119=1,INT(($G119-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H119=1,MAX(1,INT(($G119-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J119" s="38" t="str">
@@ -15991,7 +16002,7 @@
         <v>0</v>
       </c>
       <c r="I120" s="78" t="str">
-        <f aca="false">IF($H120=1,INT(($G120-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H120=1,MAX(1,INT(($G120-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J120" s="38" t="str">
@@ -16035,7 +16046,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="78" t="str">
-        <f aca="false">IF($H121=1,INT(($G121-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H121=1,MAX(1,INT(($G121-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J121" s="38" t="str">
@@ -16079,7 +16090,7 @@
         <v>0</v>
       </c>
       <c r="I122" s="78" t="str">
-        <f aca="false">IF($H122=1,INT(($G122-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H122=1,MAX(1,INT(($G122-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J122" s="38" t="str">
@@ -16123,7 +16134,7 @@
         <v>0</v>
       </c>
       <c r="I123" s="78" t="str">
-        <f aca="false">IF($H123=1,INT(($G123-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H123=1,MAX(1,INT(($G123-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J123" s="38" t="str">
@@ -16167,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="I124" s="78" t="str">
-        <f aca="false">IF($H124=1,INT(($G124-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H124=1,MAX(1,INT(($G124-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J124" s="38" t="str">
@@ -16211,7 +16222,7 @@
         <v>0</v>
       </c>
       <c r="I125" s="78" t="str">
-        <f aca="false">IF($H125=1,INT(($G125-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H125=1,MAX(1,INT(($G125-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J125" s="38" t="str">
@@ -16255,7 +16266,7 @@
         <v>0</v>
       </c>
       <c r="I126" s="78" t="str">
-        <f aca="false">IF($H126=1,INT(($G126-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H126=1,MAX(1,INT(($G126-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J126" s="38" t="str">
@@ -16299,7 +16310,7 @@
         <v>0</v>
       </c>
       <c r="I127" s="78" t="str">
-        <f aca="false">IF($H127=1,INT(($G127-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H127=1,MAX(1,INT(($G127-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J127" s="38" t="str">
@@ -16343,7 +16354,7 @@
         <v>0</v>
       </c>
       <c r="I128" s="78" t="str">
-        <f aca="false">IF($H128=1,INT(($G128-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H128=1,MAX(1,INT(($G128-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J128" s="38" t="str">
@@ -16387,7 +16398,7 @@
         <v>0</v>
       </c>
       <c r="I129" s="78" t="str">
-        <f aca="false">IF($H129=1,INT(($G129-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H129=1,MAX(1,INT(($G129-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J129" s="38" t="str">
@@ -16431,7 +16442,7 @@
         <v>0</v>
       </c>
       <c r="I130" s="78" t="str">
-        <f aca="false">IF($H130=1,INT(($G130-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H130=1,MAX(1,INT(($G130-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J130" s="38" t="str">
@@ -16475,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="I131" s="78" t="str">
-        <f aca="false">IF($H131=1,INT(($G131-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H131=1,MAX(1,INT(($G131-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J131" s="38" t="str">
@@ -16515,11 +16526,11 @@
         <v>46247</v>
       </c>
       <c r="H132" s="78" t="n">
-        <f aca="false">IF($G132="",0,IF(AND($G132&gt;='Cash Flow'!$E$6,$G132&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G132="",0,IF(AND($G132&gt;='Cash Flow'!$E$6-90,$G132&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I132" s="78" t="n">
-        <f aca="false">IF($H132=1,INT(($G132-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H132=1,MAX(1,INT(($G132-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>1</v>
       </c>
       <c r="J132" s="38" t="n">
@@ -16528,7 +16539,7 @@
       </c>
       <c r="K132" s="38" t="n">
         <f aca="false">IF($H132=1,$I132*1000+COUNTIFS($I$4:$I$483,$I132,$J$4:$J$483,"&lt;"&amp;$J132)+1,"")</f>
-        <v>1002</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16563,7 +16574,7 @@
         <v>1</v>
       </c>
       <c r="I133" s="78" t="n">
-        <f aca="false">IF($H133=1,INT(($G133-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H133=1,MAX(1,INT(($G133-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>6</v>
       </c>
       <c r="J133" s="38" t="n">
@@ -16607,7 +16618,7 @@
         <v>1</v>
       </c>
       <c r="I134" s="78" t="n">
-        <f aca="false">IF($H134=1,INT(($G134-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H134=1,MAX(1,INT(($G134-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>10</v>
       </c>
       <c r="J134" s="38" t="n">
@@ -16651,7 +16662,7 @@
         <v>0</v>
       </c>
       <c r="I135" s="78" t="str">
-        <f aca="false">IF($H135=1,INT(($G135-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H135=1,MAX(1,INT(($G135-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J135" s="38" t="str">
@@ -16695,7 +16706,7 @@
         <v>0</v>
       </c>
       <c r="I136" s="78" t="str">
-        <f aca="false">IF($H136=1,INT(($G136-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H136=1,MAX(1,INT(($G136-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J136" s="38" t="str">
@@ -16739,7 +16750,7 @@
         <v>0</v>
       </c>
       <c r="I137" s="78" t="str">
-        <f aca="false">IF($H137=1,INT(($G137-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H137=1,MAX(1,INT(($G137-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J137" s="38" t="str">
@@ -16783,7 +16794,7 @@
         <v>0</v>
       </c>
       <c r="I138" s="78" t="str">
-        <f aca="false">IF($H138=1,INT(($G138-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H138=1,MAX(1,INT(($G138-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J138" s="38" t="str">
@@ -16827,7 +16838,7 @@
         <v>0</v>
       </c>
       <c r="I139" s="78" t="str">
-        <f aca="false">IF($H139=1,INT(($G139-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H139=1,MAX(1,INT(($G139-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J139" s="38" t="str">
@@ -16871,7 +16882,7 @@
         <v>0</v>
       </c>
       <c r="I140" s="78" t="str">
-        <f aca="false">IF($H140=1,INT(($G140-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H140=1,MAX(1,INT(($G140-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J140" s="38" t="str">
@@ -16915,7 +16926,7 @@
         <v>0</v>
       </c>
       <c r="I141" s="78" t="str">
-        <f aca="false">IF($H141=1,INT(($G141-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H141=1,MAX(1,INT(($G141-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J141" s="38" t="str">
@@ -16959,7 +16970,7 @@
         <v>0</v>
       </c>
       <c r="I142" s="78" t="str">
-        <f aca="false">IF($H142=1,INT(($G142-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H142=1,MAX(1,INT(($G142-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J142" s="38" t="str">
@@ -17003,7 +17014,7 @@
         <v>0</v>
       </c>
       <c r="I143" s="78" t="str">
-        <f aca="false">IF($H143=1,INT(($G143-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H143=1,MAX(1,INT(($G143-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J143" s="38" t="str">
@@ -17047,7 +17058,7 @@
         <v>0</v>
       </c>
       <c r="I144" s="78" t="str">
-        <f aca="false">IF($H144=1,INT(($G144-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H144=1,MAX(1,INT(($G144-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J144" s="38" t="str">
@@ -17091,7 +17102,7 @@
         <v>0</v>
       </c>
       <c r="I145" s="78" t="str">
-        <f aca="false">IF($H145=1,INT(($G145-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H145=1,MAX(1,INT(($G145-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J145" s="38" t="str">
@@ -17135,7 +17146,7 @@
         <v>0</v>
       </c>
       <c r="I146" s="78" t="str">
-        <f aca="false">IF($H146=1,INT(($G146-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H146=1,MAX(1,INT(($G146-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J146" s="38" t="str">
@@ -17179,7 +17190,7 @@
         <v>0</v>
       </c>
       <c r="I147" s="78" t="str">
-        <f aca="false">IF($H147=1,INT(($G147-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H147=1,MAX(1,INT(($G147-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J147" s="38" t="str">
@@ -17219,11 +17230,11 @@
         <v>46248</v>
       </c>
       <c r="H148" s="78" t="n">
-        <f aca="false">IF($G148="",0,IF(AND($G148&gt;='Cash Flow'!$E$6,$G148&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G148="",0,IF(AND($G148&gt;='Cash Flow'!$E$6-90,$G148&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I148" s="78" t="n">
-        <f aca="false">IF($H148=1,INT(($G148-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H148=1,MAX(1,INT(($G148-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>2</v>
       </c>
       <c r="J148" s="38" t="n">
@@ -17267,7 +17278,7 @@
         <v>1</v>
       </c>
       <c r="I149" s="78" t="n">
-        <f aca="false">IF($H149=1,INT(($G149-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H149=1,MAX(1,INT(($G149-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>4</v>
       </c>
       <c r="J149" s="38" t="n">
@@ -17311,7 +17322,7 @@
         <v>1</v>
       </c>
       <c r="I150" s="78" t="n">
-        <f aca="false">IF($H150=1,INT(($G150-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H150=1,MAX(1,INT(($G150-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>6</v>
       </c>
       <c r="J150" s="38" t="n">
@@ -17355,7 +17366,7 @@
         <v>1</v>
       </c>
       <c r="I151" s="78" t="n">
-        <f aca="false">IF($H151=1,INT(($G151-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H151=1,MAX(1,INT(($G151-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J151" s="38" t="n">
@@ -17399,7 +17410,7 @@
         <v>1</v>
       </c>
       <c r="I152" s="78" t="n">
-        <f aca="false">IF($H152=1,INT(($G152-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H152=1,MAX(1,INT(($G152-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>10</v>
       </c>
       <c r="J152" s="38" t="n">
@@ -17443,7 +17454,7 @@
         <v>1</v>
       </c>
       <c r="I153" s="78" t="n">
-        <f aca="false">IF($H153=1,INT(($G153-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H153=1,MAX(1,INT(($G153-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>13</v>
       </c>
       <c r="J153" s="38" t="n">
@@ -17487,7 +17498,7 @@
         <v>0</v>
       </c>
       <c r="I154" s="78" t="str">
-        <f aca="false">IF($H154=1,INT(($G154-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H154=1,MAX(1,INT(($G154-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J154" s="38" t="str">
@@ -17531,7 +17542,7 @@
         <v>0</v>
       </c>
       <c r="I155" s="78" t="str">
-        <f aca="false">IF($H155=1,INT(($G155-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H155=1,MAX(1,INT(($G155-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J155" s="38" t="str">
@@ -17575,7 +17586,7 @@
         <v>0</v>
       </c>
       <c r="I156" s="78" t="str">
-        <f aca="false">IF($H156=1,INT(($G156-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H156=1,MAX(1,INT(($G156-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J156" s="38" t="str">
@@ -17619,7 +17630,7 @@
         <v>0</v>
       </c>
       <c r="I157" s="78" t="str">
-        <f aca="false">IF($H157=1,INT(($G157-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H157=1,MAX(1,INT(($G157-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J157" s="38" t="str">
@@ -17663,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="I158" s="78" t="str">
-        <f aca="false">IF($H158=1,INT(($G158-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H158=1,MAX(1,INT(($G158-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J158" s="38" t="str">
@@ -17707,7 +17718,7 @@
         <v>0</v>
       </c>
       <c r="I159" s="78" t="str">
-        <f aca="false">IF($H159=1,INT(($G159-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H159=1,MAX(1,INT(($G159-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J159" s="38" t="str">
@@ -17751,7 +17762,7 @@
         <v>0</v>
       </c>
       <c r="I160" s="78" t="str">
-        <f aca="false">IF($H160=1,INT(($G160-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H160=1,MAX(1,INT(($G160-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J160" s="38" t="str">
@@ -17795,7 +17806,7 @@
         <v>0</v>
       </c>
       <c r="I161" s="78" t="str">
-        <f aca="false">IF($H161=1,INT(($G161-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H161=1,MAX(1,INT(($G161-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J161" s="38" t="str">
@@ -17839,7 +17850,7 @@
         <v>0</v>
       </c>
       <c r="I162" s="78" t="str">
-        <f aca="false">IF($H162=1,INT(($G162-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H162=1,MAX(1,INT(($G162-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J162" s="38" t="str">
@@ -17883,7 +17894,7 @@
         <v>0</v>
       </c>
       <c r="I163" s="78" t="str">
-        <f aca="false">IF($H163=1,INT(($G163-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H163=1,MAX(1,INT(($G163-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J163" s="38" t="str">
@@ -17923,11 +17934,11 @@
         <v>46250</v>
       </c>
       <c r="H164" s="78" t="n">
-        <f aca="false">IF($G164="",0,IF(AND($G164&gt;='Cash Flow'!$E$6,$G164&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G164="",0,IF(AND($G164&gt;='Cash Flow'!$E$6-90,$G164&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I164" s="78" t="n">
-        <f aca="false">IF($H164=1,INT(($G164-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H164=1,MAX(1,INT(($G164-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>2</v>
       </c>
       <c r="J164" s="38" t="n">
@@ -17971,7 +17982,7 @@
         <v>1</v>
       </c>
       <c r="I165" s="78" t="n">
-        <f aca="false">IF($H165=1,INT(($G165-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H165=1,MAX(1,INT(($G165-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>6</v>
       </c>
       <c r="J165" s="38" t="n">
@@ -18015,7 +18026,7 @@
         <v>1</v>
       </c>
       <c r="I166" s="78" t="n">
-        <f aca="false">IF($H166=1,INT(($G166-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H166=1,MAX(1,INT(($G166-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>11</v>
       </c>
       <c r="J166" s="38" t="n">
@@ -18059,7 +18070,7 @@
         <v>0</v>
       </c>
       <c r="I167" s="78" t="str">
-        <f aca="false">IF($H167=1,INT(($G167-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H167=1,MAX(1,INT(($G167-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J167" s="38" t="str">
@@ -18103,7 +18114,7 @@
         <v>0</v>
       </c>
       <c r="I168" s="78" t="str">
-        <f aca="false">IF($H168=1,INT(($G168-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H168=1,MAX(1,INT(($G168-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J168" s="38" t="str">
@@ -18147,7 +18158,7 @@
         <v>0</v>
       </c>
       <c r="I169" s="78" t="str">
-        <f aca="false">IF($H169=1,INT(($G169-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H169=1,MAX(1,INT(($G169-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J169" s="38" t="str">
@@ -18191,7 +18202,7 @@
         <v>0</v>
       </c>
       <c r="I170" s="78" t="str">
-        <f aca="false">IF($H170=1,INT(($G170-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H170=1,MAX(1,INT(($G170-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J170" s="38" t="str">
@@ -18235,7 +18246,7 @@
         <v>0</v>
       </c>
       <c r="I171" s="78" t="str">
-        <f aca="false">IF($H171=1,INT(($G171-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H171=1,MAX(1,INT(($G171-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J171" s="38" t="str">
@@ -18279,7 +18290,7 @@
         <v>0</v>
       </c>
       <c r="I172" s="78" t="str">
-        <f aca="false">IF($H172=1,INT(($G172-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H172=1,MAX(1,INT(($G172-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J172" s="38" t="str">
@@ -18323,7 +18334,7 @@
         <v>0</v>
       </c>
       <c r="I173" s="78" t="str">
-        <f aca="false">IF($H173=1,INT(($G173-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H173=1,MAX(1,INT(($G173-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J173" s="38" t="str">
@@ -18367,7 +18378,7 @@
         <v>0</v>
       </c>
       <c r="I174" s="78" t="str">
-        <f aca="false">IF($H174=1,INT(($G174-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H174=1,MAX(1,INT(($G174-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J174" s="38" t="str">
@@ -18411,7 +18422,7 @@
         <v>0</v>
       </c>
       <c r="I175" s="78" t="str">
-        <f aca="false">IF($H175=1,INT(($G175-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H175=1,MAX(1,INT(($G175-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J175" s="38" t="str">
@@ -18455,7 +18466,7 @@
         <v>0</v>
       </c>
       <c r="I176" s="78" t="str">
-        <f aca="false">IF($H176=1,INT(($G176-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H176=1,MAX(1,INT(($G176-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J176" s="38" t="str">
@@ -18499,7 +18510,7 @@
         <v>0</v>
       </c>
       <c r="I177" s="78" t="str">
-        <f aca="false">IF($H177=1,INT(($G177-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H177=1,MAX(1,INT(($G177-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J177" s="38" t="str">
@@ -18543,7 +18554,7 @@
         <v>0</v>
       </c>
       <c r="I178" s="78" t="str">
-        <f aca="false">IF($H178=1,INT(($G178-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H178=1,MAX(1,INT(($G178-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J178" s="38" t="str">
@@ -18587,7 +18598,7 @@
         <v>0</v>
       </c>
       <c r="I179" s="78" t="str">
-        <f aca="false">IF($H179=1,INT(($G179-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H179=1,MAX(1,INT(($G179-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J179" s="38" t="str">
@@ -18627,11 +18638,11 @@
         <v>46250</v>
       </c>
       <c r="H180" s="78" t="n">
-        <f aca="false">IF($G180="",0,IF(AND($G180&gt;='Cash Flow'!$E$6,$G180&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G180="",0,IF(AND($G180&gt;='Cash Flow'!$E$6-90,$G180&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I180" s="78" t="n">
-        <f aca="false">IF($H180=1,INT(($G180-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H180=1,MAX(1,INT(($G180-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>2</v>
       </c>
       <c r="J180" s="38" t="n">
@@ -18675,7 +18686,7 @@
         <v>1</v>
       </c>
       <c r="I181" s="78" t="n">
-        <f aca="false">IF($H181=1,INT(($G181-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H181=1,MAX(1,INT(($G181-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>6</v>
       </c>
       <c r="J181" s="38" t="n">
@@ -18719,7 +18730,7 @@
         <v>1</v>
       </c>
       <c r="I182" s="78" t="n">
-        <f aca="false">IF($H182=1,INT(($G182-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H182=1,MAX(1,INT(($G182-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>11</v>
       </c>
       <c r="J182" s="38" t="n">
@@ -18763,7 +18774,7 @@
         <v>0</v>
       </c>
       <c r="I183" s="78" t="str">
-        <f aca="false">IF($H183=1,INT(($G183-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H183=1,MAX(1,INT(($G183-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J183" s="38" t="str">
@@ -18807,7 +18818,7 @@
         <v>0</v>
       </c>
       <c r="I184" s="78" t="str">
-        <f aca="false">IF($H184=1,INT(($G184-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H184=1,MAX(1,INT(($G184-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J184" s="38" t="str">
@@ -18851,7 +18862,7 @@
         <v>0</v>
       </c>
       <c r="I185" s="78" t="str">
-        <f aca="false">IF($H185=1,INT(($G185-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H185=1,MAX(1,INT(($G185-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J185" s="38" t="str">
@@ -18895,7 +18906,7 @@
         <v>0</v>
       </c>
       <c r="I186" s="78" t="str">
-        <f aca="false">IF($H186=1,INT(($G186-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H186=1,MAX(1,INT(($G186-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J186" s="38" t="str">
@@ -18939,7 +18950,7 @@
         <v>0</v>
       </c>
       <c r="I187" s="78" t="str">
-        <f aca="false">IF($H187=1,INT(($G187-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H187=1,MAX(1,INT(($G187-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J187" s="38" t="str">
@@ -18983,7 +18994,7 @@
         <v>0</v>
       </c>
       <c r="I188" s="78" t="str">
-        <f aca="false">IF($H188=1,INT(($G188-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H188=1,MAX(1,INT(($G188-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J188" s="38" t="str">
@@ -19027,7 +19038,7 @@
         <v>0</v>
       </c>
       <c r="I189" s="78" t="str">
-        <f aca="false">IF($H189=1,INT(($G189-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H189=1,MAX(1,INT(($G189-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J189" s="38" t="str">
@@ -19071,7 +19082,7 @@
         <v>0</v>
       </c>
       <c r="I190" s="78" t="str">
-        <f aca="false">IF($H190=1,INT(($G190-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H190=1,MAX(1,INT(($G190-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J190" s="38" t="str">
@@ -19115,7 +19126,7 @@
         <v>0</v>
       </c>
       <c r="I191" s="78" t="str">
-        <f aca="false">IF($H191=1,INT(($G191-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H191=1,MAX(1,INT(($G191-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J191" s="38" t="str">
@@ -19159,7 +19170,7 @@
         <v>0</v>
       </c>
       <c r="I192" s="78" t="str">
-        <f aca="false">IF($H192=1,INT(($G192-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H192=1,MAX(1,INT(($G192-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J192" s="38" t="str">
@@ -19203,7 +19214,7 @@
         <v>0</v>
       </c>
       <c r="I193" s="78" t="str">
-        <f aca="false">IF($H193=1,INT(($G193-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H193=1,MAX(1,INT(($G193-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J193" s="38" t="str">
@@ -19247,7 +19258,7 @@
         <v>0</v>
       </c>
       <c r="I194" s="78" t="str">
-        <f aca="false">IF($H194=1,INT(($G194-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H194=1,MAX(1,INT(($G194-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J194" s="38" t="str">
@@ -19291,7 +19302,7 @@
         <v>0</v>
       </c>
       <c r="I195" s="78" t="str">
-        <f aca="false">IF($H195=1,INT(($G195-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H195=1,MAX(1,INT(($G195-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J195" s="38" t="str">
@@ -19331,11 +19342,11 @@
         <v>46252</v>
       </c>
       <c r="H196" s="78" t="n">
-        <f aca="false">IF($G196="",0,IF(AND($G196&gt;='Cash Flow'!$E$6,$G196&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G196="",0,IF(AND($G196&gt;='Cash Flow'!$E$6-90,$G196&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I196" s="78" t="n">
-        <f aca="false">IF($H196=1,INT(($G196-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H196=1,MAX(1,INT(($G196-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>2</v>
       </c>
       <c r="J196" s="38" t="n">
@@ -19379,7 +19390,7 @@
         <v>1</v>
       </c>
       <c r="I197" s="78" t="n">
-        <f aca="false">IF($H197=1,INT(($G197-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H197=1,MAX(1,INT(($G197-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>7</v>
       </c>
       <c r="J197" s="38" t="n">
@@ -19423,7 +19434,7 @@
         <v>1</v>
       </c>
       <c r="I198" s="78" t="n">
-        <f aca="false">IF($H198=1,INT(($G198-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H198=1,MAX(1,INT(($G198-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>11</v>
       </c>
       <c r="J198" s="38" t="n">
@@ -19467,7 +19478,7 @@
         <v>0</v>
       </c>
       <c r="I199" s="78" t="str">
-        <f aca="false">IF($H199=1,INT(($G199-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H199=1,MAX(1,INT(($G199-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J199" s="38" t="str">
@@ -19511,7 +19522,7 @@
         <v>0</v>
       </c>
       <c r="I200" s="78" t="str">
-        <f aca="false">IF($H200=1,INT(($G200-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H200=1,MAX(1,INT(($G200-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J200" s="38" t="str">
@@ -19555,7 +19566,7 @@
         <v>0</v>
       </c>
       <c r="I201" s="78" t="str">
-        <f aca="false">IF($H201=1,INT(($G201-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H201=1,MAX(1,INT(($G201-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J201" s="38" t="str">
@@ -19599,7 +19610,7 @@
         <v>0</v>
       </c>
       <c r="I202" s="78" t="str">
-        <f aca="false">IF($H202=1,INT(($G202-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H202=1,MAX(1,INT(($G202-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J202" s="38" t="str">
@@ -19643,7 +19654,7 @@
         <v>0</v>
       </c>
       <c r="I203" s="78" t="str">
-        <f aca="false">IF($H203=1,INT(($G203-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H203=1,MAX(1,INT(($G203-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J203" s="38" t="str">
@@ -19687,7 +19698,7 @@
         <v>0</v>
       </c>
       <c r="I204" s="78" t="str">
-        <f aca="false">IF($H204=1,INT(($G204-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H204=1,MAX(1,INT(($G204-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J204" s="38" t="str">
@@ -19731,7 +19742,7 @@
         <v>0</v>
       </c>
       <c r="I205" s="78" t="str">
-        <f aca="false">IF($H205=1,INT(($G205-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H205=1,MAX(1,INT(($G205-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J205" s="38" t="str">
@@ -19775,7 +19786,7 @@
         <v>0</v>
       </c>
       <c r="I206" s="78" t="str">
-        <f aca="false">IF($H206=1,INT(($G206-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H206=1,MAX(1,INT(($G206-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J206" s="38" t="str">
@@ -19819,7 +19830,7 @@
         <v>0</v>
       </c>
       <c r="I207" s="78" t="str">
-        <f aca="false">IF($H207=1,INT(($G207-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H207=1,MAX(1,INT(($G207-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J207" s="38" t="str">
@@ -19863,7 +19874,7 @@
         <v>0</v>
       </c>
       <c r="I208" s="78" t="str">
-        <f aca="false">IF($H208=1,INT(($G208-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H208=1,MAX(1,INT(($G208-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J208" s="38" t="str">
@@ -19907,7 +19918,7 @@
         <v>0</v>
       </c>
       <c r="I209" s="78" t="str">
-        <f aca="false">IF($H209=1,INT(($G209-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H209=1,MAX(1,INT(($G209-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J209" s="38" t="str">
@@ -19951,7 +19962,7 @@
         <v>0</v>
       </c>
       <c r="I210" s="78" t="str">
-        <f aca="false">IF($H210=1,INT(($G210-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H210=1,MAX(1,INT(($G210-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J210" s="38" t="str">
@@ -19995,7 +20006,7 @@
         <v>0</v>
       </c>
       <c r="I211" s="78" t="str">
-        <f aca="false">IF($H211=1,INT(($G211-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H211=1,MAX(1,INT(($G211-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J211" s="38" t="str">
@@ -20035,11 +20046,11 @@
         <v>46259</v>
       </c>
       <c r="H212" s="78" t="n">
-        <f aca="false">IF($G212="",0,IF(AND($G212&gt;='Cash Flow'!$E$6,$G212&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G212="",0,IF(AND($G212&gt;='Cash Flow'!$E$6-90,$G212&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I212" s="78" t="n">
-        <f aca="false">IF($H212=1,INT(($G212-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H212=1,MAX(1,INT(($G212-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>3</v>
       </c>
       <c r="J212" s="38" t="n">
@@ -20083,7 +20094,7 @@
         <v>1</v>
       </c>
       <c r="I213" s="78" t="n">
-        <f aca="false">IF($H213=1,INT(($G213-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H213=1,MAX(1,INT(($G213-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J213" s="38" t="n">
@@ -20127,7 +20138,7 @@
         <v>1</v>
       </c>
       <c r="I214" s="78" t="n">
-        <f aca="false">IF($H214=1,INT(($G214-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H214=1,MAX(1,INT(($G214-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>12</v>
       </c>
       <c r="J214" s="38" t="n">
@@ -20171,7 +20182,7 @@
         <v>0</v>
       </c>
       <c r="I215" s="78" t="str">
-        <f aca="false">IF($H215=1,INT(($G215-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H215=1,MAX(1,INT(($G215-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J215" s="38" t="str">
@@ -20215,7 +20226,7 @@
         <v>0</v>
       </c>
       <c r="I216" s="78" t="str">
-        <f aca="false">IF($H216=1,INT(($G216-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H216=1,MAX(1,INT(($G216-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J216" s="38" t="str">
@@ -20259,7 +20270,7 @@
         <v>0</v>
       </c>
       <c r="I217" s="78" t="str">
-        <f aca="false">IF($H217=1,INT(($G217-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H217=1,MAX(1,INT(($G217-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J217" s="38" t="str">
@@ -20303,7 +20314,7 @@
         <v>0</v>
       </c>
       <c r="I218" s="78" t="str">
-        <f aca="false">IF($H218=1,INT(($G218-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H218=1,MAX(1,INT(($G218-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J218" s="38" t="str">
@@ -20347,7 +20358,7 @@
         <v>0</v>
       </c>
       <c r="I219" s="78" t="str">
-        <f aca="false">IF($H219=1,INT(($G219-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H219=1,MAX(1,INT(($G219-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J219" s="38" t="str">
@@ -20391,7 +20402,7 @@
         <v>0</v>
       </c>
       <c r="I220" s="78" t="str">
-        <f aca="false">IF($H220=1,INT(($G220-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H220=1,MAX(1,INT(($G220-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J220" s="38" t="str">
@@ -20435,7 +20446,7 @@
         <v>0</v>
       </c>
       <c r="I221" s="78" t="str">
-        <f aca="false">IF($H221=1,INT(($G221-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H221=1,MAX(1,INT(($G221-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J221" s="38" t="str">
@@ -20479,7 +20490,7 @@
         <v>0</v>
       </c>
       <c r="I222" s="78" t="str">
-        <f aca="false">IF($H222=1,INT(($G222-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H222=1,MAX(1,INT(($G222-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J222" s="38" t="str">
@@ -20523,7 +20534,7 @@
         <v>0</v>
       </c>
       <c r="I223" s="78" t="str">
-        <f aca="false">IF($H223=1,INT(($G223-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H223=1,MAX(1,INT(($G223-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J223" s="38" t="str">
@@ -20567,7 +20578,7 @@
         <v>0</v>
       </c>
       <c r="I224" s="78" t="str">
-        <f aca="false">IF($H224=1,INT(($G224-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H224=1,MAX(1,INT(($G224-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J224" s="38" t="str">
@@ -20611,7 +20622,7 @@
         <v>0</v>
       </c>
       <c r="I225" s="78" t="str">
-        <f aca="false">IF($H225=1,INT(($G225-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H225=1,MAX(1,INT(($G225-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J225" s="38" t="str">
@@ -20655,7 +20666,7 @@
         <v>0</v>
       </c>
       <c r="I226" s="78" t="str">
-        <f aca="false">IF($H226=1,INT(($G226-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H226=1,MAX(1,INT(($G226-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J226" s="38" t="str">
@@ -20699,7 +20710,7 @@
         <v>0</v>
       </c>
       <c r="I227" s="78" t="str">
-        <f aca="false">IF($H227=1,INT(($G227-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H227=1,MAX(1,INT(($G227-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J227" s="38" t="str">
@@ -20739,11 +20750,11 @@
         <v>46259</v>
       </c>
       <c r="H228" s="78" t="n">
-        <f aca="false">IF($G228="",0,IF(AND($G228&gt;='Cash Flow'!$E$6,$G228&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G228="",0,IF(AND($G228&gt;='Cash Flow'!$E$6-90,$G228&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I228" s="78" t="n">
-        <f aca="false">IF($H228=1,INT(($G228-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H228=1,MAX(1,INT(($G228-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>3</v>
       </c>
       <c r="J228" s="38" t="n">
@@ -20787,7 +20798,7 @@
         <v>1</v>
       </c>
       <c r="I229" s="78" t="n">
-        <f aca="false">IF($H229=1,INT(($G229-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H229=1,MAX(1,INT(($G229-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J229" s="38" t="n">
@@ -20831,7 +20842,7 @@
         <v>1</v>
       </c>
       <c r="I230" s="78" t="n">
-        <f aca="false">IF($H230=1,INT(($G230-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H230=1,MAX(1,INT(($G230-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>12</v>
       </c>
       <c r="J230" s="38" t="n">
@@ -20875,7 +20886,7 @@
         <v>0</v>
       </c>
       <c r="I231" s="78" t="str">
-        <f aca="false">IF($H231=1,INT(($G231-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H231=1,MAX(1,INT(($G231-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J231" s="38" t="str">
@@ -20919,7 +20930,7 @@
         <v>0</v>
       </c>
       <c r="I232" s="78" t="str">
-        <f aca="false">IF($H232=1,INT(($G232-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H232=1,MAX(1,INT(($G232-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J232" s="38" t="str">
@@ -20963,7 +20974,7 @@
         <v>0</v>
       </c>
       <c r="I233" s="78" t="str">
-        <f aca="false">IF($H233=1,INT(($G233-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H233=1,MAX(1,INT(($G233-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J233" s="38" t="str">
@@ -21007,7 +21018,7 @@
         <v>0</v>
       </c>
       <c r="I234" s="78" t="str">
-        <f aca="false">IF($H234=1,INT(($G234-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H234=1,MAX(1,INT(($G234-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J234" s="38" t="str">
@@ -21051,7 +21062,7 @@
         <v>0</v>
       </c>
       <c r="I235" s="78" t="str">
-        <f aca="false">IF($H235=1,INT(($G235-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H235=1,MAX(1,INT(($G235-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J235" s="38" t="str">
@@ -21095,7 +21106,7 @@
         <v>0</v>
       </c>
       <c r="I236" s="78" t="str">
-        <f aca="false">IF($H236=1,INT(($G236-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H236=1,MAX(1,INT(($G236-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J236" s="38" t="str">
@@ -21139,7 +21150,7 @@
         <v>0</v>
       </c>
       <c r="I237" s="78" t="str">
-        <f aca="false">IF($H237=1,INT(($G237-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H237=1,MAX(1,INT(($G237-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J237" s="38" t="str">
@@ -21183,7 +21194,7 @@
         <v>0</v>
       </c>
       <c r="I238" s="78" t="str">
-        <f aca="false">IF($H238=1,INT(($G238-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H238=1,MAX(1,INT(($G238-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J238" s="38" t="str">
@@ -21227,7 +21238,7 @@
         <v>0</v>
       </c>
       <c r="I239" s="78" t="str">
-        <f aca="false">IF($H239=1,INT(($G239-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H239=1,MAX(1,INT(($G239-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J239" s="38" t="str">
@@ -21271,7 +21282,7 @@
         <v>0</v>
       </c>
       <c r="I240" s="78" t="str">
-        <f aca="false">IF($H240=1,INT(($G240-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H240=1,MAX(1,INT(($G240-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J240" s="38" t="str">
@@ -21315,7 +21326,7 @@
         <v>0</v>
       </c>
       <c r="I241" s="78" t="str">
-        <f aca="false">IF($H241=1,INT(($G241-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H241=1,MAX(1,INT(($G241-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J241" s="38" t="str">
@@ -21359,7 +21370,7 @@
         <v>0</v>
       </c>
       <c r="I242" s="78" t="str">
-        <f aca="false">IF($H242=1,INT(($G242-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H242=1,MAX(1,INT(($G242-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J242" s="38" t="str">
@@ -21403,7 +21414,7 @@
         <v>0</v>
       </c>
       <c r="I243" s="78" t="str">
-        <f aca="false">IF($H243=1,INT(($G243-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H243=1,MAX(1,INT(($G243-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J243" s="38" t="str">
@@ -21443,11 +21454,11 @@
         <v>46264</v>
       </c>
       <c r="H244" s="78" t="n">
-        <f aca="false">IF($G244="",0,IF(AND($G244&gt;='Cash Flow'!$E$6,$G244&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G244="",0,IF(AND($G244&gt;='Cash Flow'!$E$6-90,$G244&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I244" s="78" t="n">
-        <f aca="false">IF($H244=1,INT(($G244-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H244=1,MAX(1,INT(($G244-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>4</v>
       </c>
       <c r="J244" s="38" t="n">
@@ -21491,7 +21502,7 @@
         <v>1</v>
       </c>
       <c r="I245" s="78" t="n">
-        <f aca="false">IF($H245=1,INT(($G245-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H245=1,MAX(1,INT(($G245-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J245" s="38" t="n">
@@ -21535,7 +21546,7 @@
         <v>1</v>
       </c>
       <c r="I246" s="78" t="n">
-        <f aca="false">IF($H246=1,INT(($G246-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H246=1,MAX(1,INT(($G246-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>13</v>
       </c>
       <c r="J246" s="38" t="n">
@@ -21579,7 +21590,7 @@
         <v>0</v>
       </c>
       <c r="I247" s="78" t="str">
-        <f aca="false">IF($H247=1,INT(($G247-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H247=1,MAX(1,INT(($G247-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J247" s="38" t="str">
@@ -21623,7 +21634,7 @@
         <v>0</v>
       </c>
       <c r="I248" s="78" t="str">
-        <f aca="false">IF($H248=1,INT(($G248-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H248=1,MAX(1,INT(($G248-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J248" s="38" t="str">
@@ -21667,7 +21678,7 @@
         <v>0</v>
       </c>
       <c r="I249" s="78" t="str">
-        <f aca="false">IF($H249=1,INT(($G249-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H249=1,MAX(1,INT(($G249-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J249" s="38" t="str">
@@ -21711,7 +21722,7 @@
         <v>0</v>
       </c>
       <c r="I250" s="78" t="str">
-        <f aca="false">IF($H250=1,INT(($G250-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H250=1,MAX(1,INT(($G250-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J250" s="38" t="str">
@@ -21755,7 +21766,7 @@
         <v>0</v>
       </c>
       <c r="I251" s="78" t="str">
-        <f aca="false">IF($H251=1,INT(($G251-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H251=1,MAX(1,INT(($G251-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J251" s="38" t="str">
@@ -21799,7 +21810,7 @@
         <v>0</v>
       </c>
       <c r="I252" s="78" t="str">
-        <f aca="false">IF($H252=1,INT(($G252-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H252=1,MAX(1,INT(($G252-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J252" s="38" t="str">
@@ -21843,7 +21854,7 @@
         <v>0</v>
       </c>
       <c r="I253" s="78" t="str">
-        <f aca="false">IF($H253=1,INT(($G253-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H253=1,MAX(1,INT(($G253-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J253" s="38" t="str">
@@ -21887,7 +21898,7 @@
         <v>0</v>
       </c>
       <c r="I254" s="78" t="str">
-        <f aca="false">IF($H254=1,INT(($G254-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H254=1,MAX(1,INT(($G254-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J254" s="38" t="str">
@@ -21931,7 +21942,7 @@
         <v>0</v>
       </c>
       <c r="I255" s="78" t="str">
-        <f aca="false">IF($H255=1,INT(($G255-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H255=1,MAX(1,INT(($G255-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J255" s="38" t="str">
@@ -21975,7 +21986,7 @@
         <v>0</v>
       </c>
       <c r="I256" s="78" t="str">
-        <f aca="false">IF($H256=1,INT(($G256-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H256=1,MAX(1,INT(($G256-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J256" s="38" t="str">
@@ -22019,7 +22030,7 @@
         <v>0</v>
       </c>
       <c r="I257" s="78" t="str">
-        <f aca="false">IF($H257=1,INT(($G257-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H257=1,MAX(1,INT(($G257-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J257" s="38" t="str">
@@ -22063,7 +22074,7 @@
         <v>0</v>
       </c>
       <c r="I258" s="78" t="str">
-        <f aca="false">IF($H258=1,INT(($G258-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H258=1,MAX(1,INT(($G258-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J258" s="38" t="str">
@@ -22107,7 +22118,7 @@
         <v>0</v>
       </c>
       <c r="I259" s="78" t="str">
-        <f aca="false">IF($H259=1,INT(($G259-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H259=1,MAX(1,INT(($G259-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J259" s="38" t="str">
@@ -22147,11 +22158,11 @@
         <v>46265</v>
       </c>
       <c r="H260" s="78" t="n">
-        <f aca="false">IF($G260="",0,IF(AND($G260&gt;='Cash Flow'!$E$6,$G260&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G260="",0,IF(AND($G260&gt;='Cash Flow'!$E$6-90,$G260&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>1</v>
       </c>
       <c r="I260" s="78" t="n">
-        <f aca="false">IF($H260=1,INT(($G260-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H260=1,MAX(1,INT(($G260-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>4</v>
       </c>
       <c r="J260" s="38" t="n">
@@ -22195,7 +22206,7 @@
         <v>1</v>
       </c>
       <c r="I261" s="78" t="n">
-        <f aca="false">IF($H261=1,INT(($G261-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H261=1,MAX(1,INT(($G261-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>8</v>
       </c>
       <c r="J261" s="38" t="n">
@@ -22239,7 +22250,7 @@
         <v>1</v>
       </c>
       <c r="I262" s="78" t="n">
-        <f aca="false">IF($H262=1,INT(($G262-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H262=1,MAX(1,INT(($G262-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v>13</v>
       </c>
       <c r="J262" s="38" t="n">
@@ -22283,7 +22294,7 @@
         <v>0</v>
       </c>
       <c r="I263" s="78" t="str">
-        <f aca="false">IF($H263=1,INT(($G263-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H263=1,MAX(1,INT(($G263-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J263" s="38" t="str">
@@ -22327,7 +22338,7 @@
         <v>0</v>
       </c>
       <c r="I264" s="78" t="str">
-        <f aca="false">IF($H264=1,INT(($G264-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H264=1,MAX(1,INT(($G264-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J264" s="38" t="str">
@@ -22371,7 +22382,7 @@
         <v>0</v>
       </c>
       <c r="I265" s="78" t="str">
-        <f aca="false">IF($H265=1,INT(($G265-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H265=1,MAX(1,INT(($G265-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J265" s="38" t="str">
@@ -22415,7 +22426,7 @@
         <v>0</v>
       </c>
       <c r="I266" s="78" t="str">
-        <f aca="false">IF($H266=1,INT(($G266-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H266=1,MAX(1,INT(($G266-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J266" s="38" t="str">
@@ -22459,7 +22470,7 @@
         <v>0</v>
       </c>
       <c r="I267" s="78" t="str">
-        <f aca="false">IF($H267=1,INT(($G267-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H267=1,MAX(1,INT(($G267-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J267" s="38" t="str">
@@ -22503,7 +22514,7 @@
         <v>0</v>
       </c>
       <c r="I268" s="78" t="str">
-        <f aca="false">IF($H268=1,INT(($G268-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H268=1,MAX(1,INT(($G268-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J268" s="38" t="str">
@@ -22547,7 +22558,7 @@
         <v>0</v>
       </c>
       <c r="I269" s="78" t="str">
-        <f aca="false">IF($H269=1,INT(($G269-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H269=1,MAX(1,INT(($G269-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J269" s="38" t="str">
@@ -22591,7 +22602,7 @@
         <v>0</v>
       </c>
       <c r="I270" s="78" t="str">
-        <f aca="false">IF($H270=1,INT(($G270-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H270=1,MAX(1,INT(($G270-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J270" s="38" t="str">
@@ -22635,7 +22646,7 @@
         <v>0</v>
       </c>
       <c r="I271" s="78" t="str">
-        <f aca="false">IF($H271=1,INT(($G271-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H271=1,MAX(1,INT(($G271-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J271" s="38" t="str">
@@ -22679,7 +22690,7 @@
         <v>0</v>
       </c>
       <c r="I272" s="78" t="str">
-        <f aca="false">IF($H272=1,INT(($G272-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H272=1,MAX(1,INT(($G272-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J272" s="38" t="str">
@@ -22723,7 +22734,7 @@
         <v>0</v>
       </c>
       <c r="I273" s="78" t="str">
-        <f aca="false">IF($H273=1,INT(($G273-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H273=1,MAX(1,INT(($G273-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J273" s="38" t="str">
@@ -22767,7 +22778,7 @@
         <v>0</v>
       </c>
       <c r="I274" s="78" t="str">
-        <f aca="false">IF($H274=1,INT(($G274-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H274=1,MAX(1,INT(($G274-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J274" s="38" t="str">
@@ -22811,7 +22822,7 @@
         <v>0</v>
       </c>
       <c r="I275" s="78" t="str">
-        <f aca="false">IF($H275=1,INT(($G275-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H275=1,MAX(1,INT(($G275-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J275" s="38" t="str">
@@ -22851,11 +22862,11 @@
         <v/>
       </c>
       <c r="H276" s="78" t="n">
-        <f aca="false">IF($G276="",0,IF(AND($G276&gt;='Cash Flow'!$E$6,$G276&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G276="",0,IF(AND($G276&gt;='Cash Flow'!$E$6-90,$G276&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I276" s="78" t="str">
-        <f aca="false">IF($H276=1,INT(($G276-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H276=1,MAX(1,INT(($G276-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J276" s="38" t="str">
@@ -22899,7 +22910,7 @@
         <v>0</v>
       </c>
       <c r="I277" s="78" t="str">
-        <f aca="false">IF($H277=1,INT(($G277-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H277=1,MAX(1,INT(($G277-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J277" s="38" t="str">
@@ -22943,7 +22954,7 @@
         <v>0</v>
       </c>
       <c r="I278" s="78" t="str">
-        <f aca="false">IF($H278=1,INT(($G278-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H278=1,MAX(1,INT(($G278-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J278" s="38" t="str">
@@ -22987,7 +22998,7 @@
         <v>0</v>
       </c>
       <c r="I279" s="78" t="str">
-        <f aca="false">IF($H279=1,INT(($G279-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H279=1,MAX(1,INT(($G279-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J279" s="38" t="str">
@@ -23031,7 +23042,7 @@
         <v>0</v>
       </c>
       <c r="I280" s="78" t="str">
-        <f aca="false">IF($H280=1,INT(($G280-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H280=1,MAX(1,INT(($G280-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J280" s="38" t="str">
@@ -23075,7 +23086,7 @@
         <v>0</v>
       </c>
       <c r="I281" s="78" t="str">
-        <f aca="false">IF($H281=1,INT(($G281-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H281=1,MAX(1,INT(($G281-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J281" s="38" t="str">
@@ -23119,7 +23130,7 @@
         <v>0</v>
       </c>
       <c r="I282" s="78" t="str">
-        <f aca="false">IF($H282=1,INT(($G282-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H282=1,MAX(1,INT(($G282-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J282" s="38" t="str">
@@ -23163,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="I283" s="78" t="str">
-        <f aca="false">IF($H283=1,INT(($G283-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H283=1,MAX(1,INT(($G283-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J283" s="38" t="str">
@@ -23207,7 +23218,7 @@
         <v>0</v>
       </c>
       <c r="I284" s="78" t="str">
-        <f aca="false">IF($H284=1,INT(($G284-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H284=1,MAX(1,INT(($G284-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J284" s="38" t="str">
@@ -23251,7 +23262,7 @@
         <v>0</v>
       </c>
       <c r="I285" s="78" t="str">
-        <f aca="false">IF($H285=1,INT(($G285-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H285=1,MAX(1,INT(($G285-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J285" s="38" t="str">
@@ -23295,7 +23306,7 @@
         <v>0</v>
       </c>
       <c r="I286" s="78" t="str">
-        <f aca="false">IF($H286=1,INT(($G286-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H286=1,MAX(1,INT(($G286-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J286" s="38" t="str">
@@ -23339,7 +23350,7 @@
         <v>0</v>
       </c>
       <c r="I287" s="78" t="str">
-        <f aca="false">IF($H287=1,INT(($G287-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H287=1,MAX(1,INT(($G287-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J287" s="38" t="str">
@@ -23383,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="I288" s="78" t="str">
-        <f aca="false">IF($H288=1,INT(($G288-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H288=1,MAX(1,INT(($G288-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J288" s="38" t="str">
@@ -23427,7 +23438,7 @@
         <v>0</v>
       </c>
       <c r="I289" s="78" t="str">
-        <f aca="false">IF($H289=1,INT(($G289-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H289=1,MAX(1,INT(($G289-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J289" s="38" t="str">
@@ -23471,7 +23482,7 @@
         <v>0</v>
       </c>
       <c r="I290" s="78" t="str">
-        <f aca="false">IF($H290=1,INT(($G290-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H290=1,MAX(1,INT(($G290-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J290" s="38" t="str">
@@ -23515,7 +23526,7 @@
         <v>0</v>
       </c>
       <c r="I291" s="78" t="str">
-        <f aca="false">IF($H291=1,INT(($G291-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H291=1,MAX(1,INT(($G291-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J291" s="38" t="str">
@@ -23555,11 +23566,11 @@
         <v/>
       </c>
       <c r="H292" s="78" t="n">
-        <f aca="false">IF($G292="",0,IF(AND($G292&gt;='Cash Flow'!$E$6,$G292&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G292="",0,IF(AND($G292&gt;='Cash Flow'!$E$6-90,$G292&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I292" s="78" t="str">
-        <f aca="false">IF($H292=1,INT(($G292-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H292=1,MAX(1,INT(($G292-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J292" s="38" t="str">
@@ -23603,7 +23614,7 @@
         <v>0</v>
       </c>
       <c r="I293" s="78" t="str">
-        <f aca="false">IF($H293=1,INT(($G293-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H293=1,MAX(1,INT(($G293-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J293" s="38" t="str">
@@ -23647,7 +23658,7 @@
         <v>0</v>
       </c>
       <c r="I294" s="78" t="str">
-        <f aca="false">IF($H294=1,INT(($G294-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H294=1,MAX(1,INT(($G294-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J294" s="38" t="str">
@@ -23691,7 +23702,7 @@
         <v>0</v>
       </c>
       <c r="I295" s="78" t="str">
-        <f aca="false">IF($H295=1,INT(($G295-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H295=1,MAX(1,INT(($G295-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J295" s="38" t="str">
@@ -23735,7 +23746,7 @@
         <v>0</v>
       </c>
       <c r="I296" s="78" t="str">
-        <f aca="false">IF($H296=1,INT(($G296-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H296=1,MAX(1,INT(($G296-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J296" s="38" t="str">
@@ -23779,7 +23790,7 @@
         <v>0</v>
       </c>
       <c r="I297" s="78" t="str">
-        <f aca="false">IF($H297=1,INT(($G297-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H297=1,MAX(1,INT(($G297-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J297" s="38" t="str">
@@ -23823,7 +23834,7 @@
         <v>0</v>
       </c>
       <c r="I298" s="78" t="str">
-        <f aca="false">IF($H298=1,INT(($G298-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H298=1,MAX(1,INT(($G298-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J298" s="38" t="str">
@@ -23867,7 +23878,7 @@
         <v>0</v>
       </c>
       <c r="I299" s="78" t="str">
-        <f aca="false">IF($H299=1,INT(($G299-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H299=1,MAX(1,INT(($G299-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J299" s="38" t="str">
@@ -23911,7 +23922,7 @@
         <v>0</v>
       </c>
       <c r="I300" s="78" t="str">
-        <f aca="false">IF($H300=1,INT(($G300-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H300=1,MAX(1,INT(($G300-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J300" s="38" t="str">
@@ -23955,7 +23966,7 @@
         <v>0</v>
       </c>
       <c r="I301" s="78" t="str">
-        <f aca="false">IF($H301=1,INT(($G301-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H301=1,MAX(1,INT(($G301-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J301" s="38" t="str">
@@ -23999,7 +24010,7 @@
         <v>0</v>
       </c>
       <c r="I302" s="78" t="str">
-        <f aca="false">IF($H302=1,INT(($G302-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H302=1,MAX(1,INT(($G302-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J302" s="38" t="str">
@@ -24043,7 +24054,7 @@
         <v>0</v>
       </c>
       <c r="I303" s="78" t="str">
-        <f aca="false">IF($H303=1,INT(($G303-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H303=1,MAX(1,INT(($G303-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J303" s="38" t="str">
@@ -24087,7 +24098,7 @@
         <v>0</v>
       </c>
       <c r="I304" s="78" t="str">
-        <f aca="false">IF($H304=1,INT(($G304-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H304=1,MAX(1,INT(($G304-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J304" s="38" t="str">
@@ -24131,7 +24142,7 @@
         <v>0</v>
       </c>
       <c r="I305" s="78" t="str">
-        <f aca="false">IF($H305=1,INT(($G305-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H305=1,MAX(1,INT(($G305-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J305" s="38" t="str">
@@ -24175,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="I306" s="78" t="str">
-        <f aca="false">IF($H306=1,INT(($G306-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H306=1,MAX(1,INT(($G306-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J306" s="38" t="str">
@@ -24219,7 +24230,7 @@
         <v>0</v>
       </c>
       <c r="I307" s="78" t="str">
-        <f aca="false">IF($H307=1,INT(($G307-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H307=1,MAX(1,INT(($G307-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J307" s="38" t="str">
@@ -24259,11 +24270,11 @@
         <v/>
       </c>
       <c r="H308" s="78" t="n">
-        <f aca="false">IF($G308="",0,IF(AND($G308&gt;='Cash Flow'!$E$6,$G308&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G308="",0,IF(AND($G308&gt;='Cash Flow'!$E$6-90,$G308&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I308" s="78" t="str">
-        <f aca="false">IF($H308=1,INT(($G308-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H308=1,MAX(1,INT(($G308-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J308" s="38" t="str">
@@ -24307,7 +24318,7 @@
         <v>0</v>
       </c>
       <c r="I309" s="78" t="str">
-        <f aca="false">IF($H309=1,INT(($G309-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H309=1,MAX(1,INT(($G309-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J309" s="38" t="str">
@@ -24351,7 +24362,7 @@
         <v>0</v>
       </c>
       <c r="I310" s="78" t="str">
-        <f aca="false">IF($H310=1,INT(($G310-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H310=1,MAX(1,INT(($G310-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J310" s="38" t="str">
@@ -24395,7 +24406,7 @@
         <v>0</v>
       </c>
       <c r="I311" s="78" t="str">
-        <f aca="false">IF($H311=1,INT(($G311-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H311=1,MAX(1,INT(($G311-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J311" s="38" t="str">
@@ -24439,7 +24450,7 @@
         <v>0</v>
       </c>
       <c r="I312" s="78" t="str">
-        <f aca="false">IF($H312=1,INT(($G312-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H312=1,MAX(1,INT(($G312-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J312" s="38" t="str">
@@ -24483,7 +24494,7 @@
         <v>0</v>
       </c>
       <c r="I313" s="78" t="str">
-        <f aca="false">IF($H313=1,INT(($G313-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H313=1,MAX(1,INT(($G313-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J313" s="38" t="str">
@@ -24527,7 +24538,7 @@
         <v>0</v>
       </c>
       <c r="I314" s="78" t="str">
-        <f aca="false">IF($H314=1,INT(($G314-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H314=1,MAX(1,INT(($G314-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J314" s="38" t="str">
@@ -24571,7 +24582,7 @@
         <v>0</v>
       </c>
       <c r="I315" s="78" t="str">
-        <f aca="false">IF($H315=1,INT(($G315-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H315=1,MAX(1,INT(($G315-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J315" s="38" t="str">
@@ -24615,7 +24626,7 @@
         <v>0</v>
       </c>
       <c r="I316" s="78" t="str">
-        <f aca="false">IF($H316=1,INT(($G316-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H316=1,MAX(1,INT(($G316-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J316" s="38" t="str">
@@ -24659,7 +24670,7 @@
         <v>0</v>
       </c>
       <c r="I317" s="78" t="str">
-        <f aca="false">IF($H317=1,INT(($G317-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H317=1,MAX(1,INT(($G317-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J317" s="38" t="str">
@@ -24703,7 +24714,7 @@
         <v>0</v>
       </c>
       <c r="I318" s="78" t="str">
-        <f aca="false">IF($H318=1,INT(($G318-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H318=1,MAX(1,INT(($G318-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J318" s="38" t="str">
@@ -24747,7 +24758,7 @@
         <v>0</v>
       </c>
       <c r="I319" s="78" t="str">
-        <f aca="false">IF($H319=1,INT(($G319-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H319=1,MAX(1,INT(($G319-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J319" s="38" t="str">
@@ -24791,7 +24802,7 @@
         <v>0</v>
       </c>
       <c r="I320" s="78" t="str">
-        <f aca="false">IF($H320=1,INT(($G320-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H320=1,MAX(1,INT(($G320-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J320" s="38" t="str">
@@ -24835,7 +24846,7 @@
         <v>0</v>
       </c>
       <c r="I321" s="78" t="str">
-        <f aca="false">IF($H321=1,INT(($G321-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H321=1,MAX(1,INT(($G321-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J321" s="38" t="str">
@@ -24879,7 +24890,7 @@
         <v>0</v>
       </c>
       <c r="I322" s="78" t="str">
-        <f aca="false">IF($H322=1,INT(($G322-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H322=1,MAX(1,INT(($G322-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J322" s="38" t="str">
@@ -24923,7 +24934,7 @@
         <v>0</v>
       </c>
       <c r="I323" s="78" t="str">
-        <f aca="false">IF($H323=1,INT(($G323-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H323=1,MAX(1,INT(($G323-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J323" s="38" t="str">
@@ -24963,11 +24974,11 @@
         <v/>
       </c>
       <c r="H324" s="78" t="n">
-        <f aca="false">IF($G324="",0,IF(AND($G324&gt;='Cash Flow'!$E$6,$G324&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G324="",0,IF(AND($G324&gt;='Cash Flow'!$E$6-90,$G324&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I324" s="78" t="str">
-        <f aca="false">IF($H324=1,INT(($G324-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H324=1,MAX(1,INT(($G324-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J324" s="38" t="str">
@@ -25011,7 +25022,7 @@
         <v>0</v>
       </c>
       <c r="I325" s="78" t="str">
-        <f aca="false">IF($H325=1,INT(($G325-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H325=1,MAX(1,INT(($G325-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J325" s="38" t="str">
@@ -25055,7 +25066,7 @@
         <v>0</v>
       </c>
       <c r="I326" s="78" t="str">
-        <f aca="false">IF($H326=1,INT(($G326-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H326=1,MAX(1,INT(($G326-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J326" s="38" t="str">
@@ -25099,7 +25110,7 @@
         <v>0</v>
       </c>
       <c r="I327" s="78" t="str">
-        <f aca="false">IF($H327=1,INT(($G327-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H327=1,MAX(1,INT(($G327-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J327" s="38" t="str">
@@ -25143,7 +25154,7 @@
         <v>0</v>
       </c>
       <c r="I328" s="78" t="str">
-        <f aca="false">IF($H328=1,INT(($G328-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H328=1,MAX(1,INT(($G328-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J328" s="38" t="str">
@@ -25187,7 +25198,7 @@
         <v>0</v>
       </c>
       <c r="I329" s="78" t="str">
-        <f aca="false">IF($H329=1,INT(($G329-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H329=1,MAX(1,INT(($G329-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J329" s="38" t="str">
@@ -25231,7 +25242,7 @@
         <v>0</v>
       </c>
       <c r="I330" s="78" t="str">
-        <f aca="false">IF($H330=1,INT(($G330-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H330=1,MAX(1,INT(($G330-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J330" s="38" t="str">
@@ -25275,7 +25286,7 @@
         <v>0</v>
       </c>
       <c r="I331" s="78" t="str">
-        <f aca="false">IF($H331=1,INT(($G331-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H331=1,MAX(1,INT(($G331-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J331" s="38" t="str">
@@ -25319,7 +25330,7 @@
         <v>0</v>
       </c>
       <c r="I332" s="78" t="str">
-        <f aca="false">IF($H332=1,INT(($G332-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H332=1,MAX(1,INT(($G332-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J332" s="38" t="str">
@@ -25363,7 +25374,7 @@
         <v>0</v>
       </c>
       <c r="I333" s="78" t="str">
-        <f aca="false">IF($H333=1,INT(($G333-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H333=1,MAX(1,INT(($G333-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J333" s="38" t="str">
@@ -25407,7 +25418,7 @@
         <v>0</v>
       </c>
       <c r="I334" s="78" t="str">
-        <f aca="false">IF($H334=1,INT(($G334-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H334=1,MAX(1,INT(($G334-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J334" s="38" t="str">
@@ -25451,7 +25462,7 @@
         <v>0</v>
       </c>
       <c r="I335" s="78" t="str">
-        <f aca="false">IF($H335=1,INT(($G335-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H335=1,MAX(1,INT(($G335-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J335" s="38" t="str">
@@ -25495,7 +25506,7 @@
         <v>0</v>
       </c>
       <c r="I336" s="78" t="str">
-        <f aca="false">IF($H336=1,INT(($G336-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H336=1,MAX(1,INT(($G336-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J336" s="38" t="str">
@@ -25539,7 +25550,7 @@
         <v>0</v>
       </c>
       <c r="I337" s="78" t="str">
-        <f aca="false">IF($H337=1,INT(($G337-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H337=1,MAX(1,INT(($G337-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J337" s="38" t="str">
@@ -25583,7 +25594,7 @@
         <v>0</v>
       </c>
       <c r="I338" s="78" t="str">
-        <f aca="false">IF($H338=1,INT(($G338-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H338=1,MAX(1,INT(($G338-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J338" s="38" t="str">
@@ -25627,7 +25638,7 @@
         <v>0</v>
       </c>
       <c r="I339" s="78" t="str">
-        <f aca="false">IF($H339=1,INT(($G339-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H339=1,MAX(1,INT(($G339-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J339" s="38" t="str">
@@ -25667,11 +25678,11 @@
         <v/>
       </c>
       <c r="H340" s="78" t="n">
-        <f aca="false">IF($G340="",0,IF(AND($G340&gt;='Cash Flow'!$E$6,$G340&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G340="",0,IF(AND($G340&gt;='Cash Flow'!$E$6-90,$G340&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I340" s="78" t="str">
-        <f aca="false">IF($H340=1,INT(($G340-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H340=1,MAX(1,INT(($G340-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J340" s="38" t="str">
@@ -25715,7 +25726,7 @@
         <v>0</v>
       </c>
       <c r="I341" s="78" t="str">
-        <f aca="false">IF($H341=1,INT(($G341-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H341=1,MAX(1,INT(($G341-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J341" s="38" t="str">
@@ -25759,7 +25770,7 @@
         <v>0</v>
       </c>
       <c r="I342" s="78" t="str">
-        <f aca="false">IF($H342=1,INT(($G342-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H342=1,MAX(1,INT(($G342-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J342" s="38" t="str">
@@ -25803,7 +25814,7 @@
         <v>0</v>
       </c>
       <c r="I343" s="78" t="str">
-        <f aca="false">IF($H343=1,INT(($G343-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H343=1,MAX(1,INT(($G343-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J343" s="38" t="str">
@@ -25847,7 +25858,7 @@
         <v>0</v>
       </c>
       <c r="I344" s="78" t="str">
-        <f aca="false">IF($H344=1,INT(($G344-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H344=1,MAX(1,INT(($G344-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J344" s="38" t="str">
@@ -25891,7 +25902,7 @@
         <v>0</v>
       </c>
       <c r="I345" s="78" t="str">
-        <f aca="false">IF($H345=1,INT(($G345-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H345=1,MAX(1,INT(($G345-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J345" s="38" t="str">
@@ -25935,7 +25946,7 @@
         <v>0</v>
       </c>
       <c r="I346" s="78" t="str">
-        <f aca="false">IF($H346=1,INT(($G346-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H346=1,MAX(1,INT(($G346-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J346" s="38" t="str">
@@ -25979,7 +25990,7 @@
         <v>0</v>
       </c>
       <c r="I347" s="78" t="str">
-        <f aca="false">IF($H347=1,INT(($G347-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H347=1,MAX(1,INT(($G347-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J347" s="38" t="str">
@@ -26023,7 +26034,7 @@
         <v>0</v>
       </c>
       <c r="I348" s="78" t="str">
-        <f aca="false">IF($H348=1,INT(($G348-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H348=1,MAX(1,INT(($G348-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J348" s="38" t="str">
@@ -26067,7 +26078,7 @@
         <v>0</v>
       </c>
       <c r="I349" s="78" t="str">
-        <f aca="false">IF($H349=1,INT(($G349-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H349=1,MAX(1,INT(($G349-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J349" s="38" t="str">
@@ -26111,7 +26122,7 @@
         <v>0</v>
       </c>
       <c r="I350" s="78" t="str">
-        <f aca="false">IF($H350=1,INT(($G350-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H350=1,MAX(1,INT(($G350-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J350" s="38" t="str">
@@ -26155,7 +26166,7 @@
         <v>0</v>
       </c>
       <c r="I351" s="78" t="str">
-        <f aca="false">IF($H351=1,INT(($G351-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H351=1,MAX(1,INT(($G351-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J351" s="38" t="str">
@@ -26199,7 +26210,7 @@
         <v>0</v>
       </c>
       <c r="I352" s="78" t="str">
-        <f aca="false">IF($H352=1,INT(($G352-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H352=1,MAX(1,INT(($G352-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J352" s="38" t="str">
@@ -26243,7 +26254,7 @@
         <v>0</v>
       </c>
       <c r="I353" s="78" t="str">
-        <f aca="false">IF($H353=1,INT(($G353-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H353=1,MAX(1,INT(($G353-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J353" s="38" t="str">
@@ -26287,7 +26298,7 @@
         <v>0</v>
       </c>
       <c r="I354" s="78" t="str">
-        <f aca="false">IF($H354=1,INT(($G354-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H354=1,MAX(1,INT(($G354-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J354" s="38" t="str">
@@ -26331,7 +26342,7 @@
         <v>0</v>
       </c>
       <c r="I355" s="78" t="str">
-        <f aca="false">IF($H355=1,INT(($G355-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H355=1,MAX(1,INT(($G355-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J355" s="38" t="str">
@@ -26371,11 +26382,11 @@
         <v/>
       </c>
       <c r="H356" s="78" t="n">
-        <f aca="false">IF($G356="",0,IF(AND($G356&gt;='Cash Flow'!$E$6,$G356&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G356="",0,IF(AND($G356&gt;='Cash Flow'!$E$6-90,$G356&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I356" s="78" t="str">
-        <f aca="false">IF($H356=1,INT(($G356-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H356=1,MAX(1,INT(($G356-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J356" s="38" t="str">
@@ -26419,7 +26430,7 @@
         <v>0</v>
       </c>
       <c r="I357" s="78" t="str">
-        <f aca="false">IF($H357=1,INT(($G357-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H357=1,MAX(1,INT(($G357-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J357" s="38" t="str">
@@ -26463,7 +26474,7 @@
         <v>0</v>
       </c>
       <c r="I358" s="78" t="str">
-        <f aca="false">IF($H358=1,INT(($G358-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H358=1,MAX(1,INT(($G358-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J358" s="38" t="str">
@@ -26507,7 +26518,7 @@
         <v>0</v>
       </c>
       <c r="I359" s="78" t="str">
-        <f aca="false">IF($H359=1,INT(($G359-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H359=1,MAX(1,INT(($G359-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J359" s="38" t="str">
@@ -26551,7 +26562,7 @@
         <v>0</v>
       </c>
       <c r="I360" s="78" t="str">
-        <f aca="false">IF($H360=1,INT(($G360-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H360=1,MAX(1,INT(($G360-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J360" s="38" t="str">
@@ -26595,7 +26606,7 @@
         <v>0</v>
       </c>
       <c r="I361" s="78" t="str">
-        <f aca="false">IF($H361=1,INT(($G361-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H361=1,MAX(1,INT(($G361-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J361" s="38" t="str">
@@ -26639,7 +26650,7 @@
         <v>0</v>
       </c>
       <c r="I362" s="78" t="str">
-        <f aca="false">IF($H362=1,INT(($G362-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H362=1,MAX(1,INT(($G362-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J362" s="38" t="str">
@@ -26683,7 +26694,7 @@
         <v>0</v>
       </c>
       <c r="I363" s="78" t="str">
-        <f aca="false">IF($H363=1,INT(($G363-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H363=1,MAX(1,INT(($G363-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J363" s="38" t="str">
@@ -26727,7 +26738,7 @@
         <v>0</v>
       </c>
       <c r="I364" s="78" t="str">
-        <f aca="false">IF($H364=1,INT(($G364-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H364=1,MAX(1,INT(($G364-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J364" s="38" t="str">
@@ -26771,7 +26782,7 @@
         <v>0</v>
       </c>
       <c r="I365" s="78" t="str">
-        <f aca="false">IF($H365=1,INT(($G365-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H365=1,MAX(1,INT(($G365-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J365" s="38" t="str">
@@ -26815,7 +26826,7 @@
         <v>0</v>
       </c>
       <c r="I366" s="78" t="str">
-        <f aca="false">IF($H366=1,INT(($G366-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H366=1,MAX(1,INT(($G366-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J366" s="38" t="str">
@@ -26859,7 +26870,7 @@
         <v>0</v>
       </c>
       <c r="I367" s="78" t="str">
-        <f aca="false">IF($H367=1,INT(($G367-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H367=1,MAX(1,INT(($G367-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J367" s="38" t="str">
@@ -26903,7 +26914,7 @@
         <v>0</v>
       </c>
       <c r="I368" s="78" t="str">
-        <f aca="false">IF($H368=1,INT(($G368-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H368=1,MAX(1,INT(($G368-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J368" s="38" t="str">
@@ -26947,7 +26958,7 @@
         <v>0</v>
       </c>
       <c r="I369" s="78" t="str">
-        <f aca="false">IF($H369=1,INT(($G369-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H369=1,MAX(1,INT(($G369-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J369" s="38" t="str">
@@ -26991,7 +27002,7 @@
         <v>0</v>
       </c>
       <c r="I370" s="78" t="str">
-        <f aca="false">IF($H370=1,INT(($G370-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H370=1,MAX(1,INT(($G370-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J370" s="38" t="str">
@@ -27035,7 +27046,7 @@
         <v>0</v>
       </c>
       <c r="I371" s="78" t="str">
-        <f aca="false">IF($H371=1,INT(($G371-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H371=1,MAX(1,INT(($G371-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J371" s="38" t="str">
@@ -27075,11 +27086,11 @@
         <v/>
       </c>
       <c r="H372" s="78" t="n">
-        <f aca="false">IF($G372="",0,IF(AND($G372&gt;='Cash Flow'!$E$6,$G372&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G372="",0,IF(AND($G372&gt;='Cash Flow'!$E$6-90,$G372&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I372" s="78" t="str">
-        <f aca="false">IF($H372=1,INT(($G372-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H372=1,MAX(1,INT(($G372-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J372" s="38" t="str">
@@ -27123,7 +27134,7 @@
         <v>0</v>
       </c>
       <c r="I373" s="78" t="str">
-        <f aca="false">IF($H373=1,INT(($G373-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H373=1,MAX(1,INT(($G373-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J373" s="38" t="str">
@@ -27167,7 +27178,7 @@
         <v>0</v>
       </c>
       <c r="I374" s="78" t="str">
-        <f aca="false">IF($H374=1,INT(($G374-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H374=1,MAX(1,INT(($G374-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J374" s="38" t="str">
@@ -27211,7 +27222,7 @@
         <v>0</v>
       </c>
       <c r="I375" s="78" t="str">
-        <f aca="false">IF($H375=1,INT(($G375-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H375=1,MAX(1,INT(($G375-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J375" s="38" t="str">
@@ -27255,7 +27266,7 @@
         <v>0</v>
       </c>
       <c r="I376" s="78" t="str">
-        <f aca="false">IF($H376=1,INT(($G376-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H376=1,MAX(1,INT(($G376-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J376" s="38" t="str">
@@ -27299,7 +27310,7 @@
         <v>0</v>
       </c>
       <c r="I377" s="78" t="str">
-        <f aca="false">IF($H377=1,INT(($G377-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H377=1,MAX(1,INT(($G377-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J377" s="38" t="str">
@@ -27343,7 +27354,7 @@
         <v>0</v>
       </c>
       <c r="I378" s="78" t="str">
-        <f aca="false">IF($H378=1,INT(($G378-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H378=1,MAX(1,INT(($G378-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J378" s="38" t="str">
@@ -27387,7 +27398,7 @@
         <v>0</v>
       </c>
       <c r="I379" s="78" t="str">
-        <f aca="false">IF($H379=1,INT(($G379-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H379=1,MAX(1,INT(($G379-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J379" s="38" t="str">
@@ -27431,7 +27442,7 @@
         <v>0</v>
       </c>
       <c r="I380" s="78" t="str">
-        <f aca="false">IF($H380=1,INT(($G380-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H380=1,MAX(1,INT(($G380-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J380" s="38" t="str">
@@ -27475,7 +27486,7 @@
         <v>0</v>
       </c>
       <c r="I381" s="78" t="str">
-        <f aca="false">IF($H381=1,INT(($G381-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H381=1,MAX(1,INT(($G381-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J381" s="38" t="str">
@@ -27519,7 +27530,7 @@
         <v>0</v>
       </c>
       <c r="I382" s="78" t="str">
-        <f aca="false">IF($H382=1,INT(($G382-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H382=1,MAX(1,INT(($G382-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J382" s="38" t="str">
@@ -27563,7 +27574,7 @@
         <v>0</v>
       </c>
       <c r="I383" s="78" t="str">
-        <f aca="false">IF($H383=1,INT(($G383-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H383=1,MAX(1,INT(($G383-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J383" s="38" t="str">
@@ -27607,7 +27618,7 @@
         <v>0</v>
       </c>
       <c r="I384" s="78" t="str">
-        <f aca="false">IF($H384=1,INT(($G384-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H384=1,MAX(1,INT(($G384-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J384" s="38" t="str">
@@ -27651,7 +27662,7 @@
         <v>0</v>
       </c>
       <c r="I385" s="78" t="str">
-        <f aca="false">IF($H385=1,INT(($G385-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H385=1,MAX(1,INT(($G385-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J385" s="38" t="str">
@@ -27695,7 +27706,7 @@
         <v>0</v>
       </c>
       <c r="I386" s="78" t="str">
-        <f aca="false">IF($H386=1,INT(($G386-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H386=1,MAX(1,INT(($G386-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J386" s="38" t="str">
@@ -27739,7 +27750,7 @@
         <v>0</v>
       </c>
       <c r="I387" s="78" t="str">
-        <f aca="false">IF($H387=1,INT(($G387-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H387=1,MAX(1,INT(($G387-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J387" s="38" t="str">
@@ -27779,11 +27790,11 @@
         <v/>
       </c>
       <c r="H388" s="78" t="n">
-        <f aca="false">IF($G388="",0,IF(AND($G388&gt;='Cash Flow'!$E$6,$G388&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G388="",0,IF(AND($G388&gt;='Cash Flow'!$E$6-90,$G388&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I388" s="78" t="str">
-        <f aca="false">IF($H388=1,INT(($G388-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H388=1,MAX(1,INT(($G388-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J388" s="38" t="str">
@@ -27827,7 +27838,7 @@
         <v>0</v>
       </c>
       <c r="I389" s="78" t="str">
-        <f aca="false">IF($H389=1,INT(($G389-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H389=1,MAX(1,INT(($G389-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J389" s="38" t="str">
@@ -27871,7 +27882,7 @@
         <v>0</v>
       </c>
       <c r="I390" s="78" t="str">
-        <f aca="false">IF($H390=1,INT(($G390-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H390=1,MAX(1,INT(($G390-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J390" s="38" t="str">
@@ -27915,7 +27926,7 @@
         <v>0</v>
       </c>
       <c r="I391" s="78" t="str">
-        <f aca="false">IF($H391=1,INT(($G391-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H391=1,MAX(1,INT(($G391-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J391" s="38" t="str">
@@ -27959,7 +27970,7 @@
         <v>0</v>
       </c>
       <c r="I392" s="78" t="str">
-        <f aca="false">IF($H392=1,INT(($G392-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H392=1,MAX(1,INT(($G392-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J392" s="38" t="str">
@@ -28003,7 +28014,7 @@
         <v>0</v>
       </c>
       <c r="I393" s="78" t="str">
-        <f aca="false">IF($H393=1,INT(($G393-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H393=1,MAX(1,INT(($G393-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J393" s="38" t="str">
@@ -28047,7 +28058,7 @@
         <v>0</v>
       </c>
       <c r="I394" s="78" t="str">
-        <f aca="false">IF($H394=1,INT(($G394-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H394=1,MAX(1,INT(($G394-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J394" s="38" t="str">
@@ -28091,7 +28102,7 @@
         <v>0</v>
       </c>
       <c r="I395" s="78" t="str">
-        <f aca="false">IF($H395=1,INT(($G395-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H395=1,MAX(1,INT(($G395-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J395" s="38" t="str">
@@ -28135,7 +28146,7 @@
         <v>0</v>
       </c>
       <c r="I396" s="78" t="str">
-        <f aca="false">IF($H396=1,INT(($G396-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H396=1,MAX(1,INT(($G396-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J396" s="38" t="str">
@@ -28179,7 +28190,7 @@
         <v>0</v>
       </c>
       <c r="I397" s="78" t="str">
-        <f aca="false">IF($H397=1,INT(($G397-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H397=1,MAX(1,INT(($G397-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J397" s="38" t="str">
@@ -28223,7 +28234,7 @@
         <v>0</v>
       </c>
       <c r="I398" s="78" t="str">
-        <f aca="false">IF($H398=1,INT(($G398-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H398=1,MAX(1,INT(($G398-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J398" s="38" t="str">
@@ -28267,7 +28278,7 @@
         <v>0</v>
       </c>
       <c r="I399" s="78" t="str">
-        <f aca="false">IF($H399=1,INT(($G399-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H399=1,MAX(1,INT(($G399-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J399" s="38" t="str">
@@ -28311,7 +28322,7 @@
         <v>0</v>
       </c>
       <c r="I400" s="78" t="str">
-        <f aca="false">IF($H400=1,INT(($G400-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H400=1,MAX(1,INT(($G400-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J400" s="38" t="str">
@@ -28355,7 +28366,7 @@
         <v>0</v>
       </c>
       <c r="I401" s="78" t="str">
-        <f aca="false">IF($H401=1,INT(($G401-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H401=1,MAX(1,INT(($G401-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J401" s="38" t="str">
@@ -28399,7 +28410,7 @@
         <v>0</v>
       </c>
       <c r="I402" s="78" t="str">
-        <f aca="false">IF($H402=1,INT(($G402-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H402=1,MAX(1,INT(($G402-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J402" s="38" t="str">
@@ -28443,7 +28454,7 @@
         <v>0</v>
       </c>
       <c r="I403" s="78" t="str">
-        <f aca="false">IF($H403=1,INT(($G403-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H403=1,MAX(1,INT(($G403-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J403" s="38" t="str">
@@ -28483,11 +28494,11 @@
         <v/>
       </c>
       <c r="H404" s="78" t="n">
-        <f aca="false">IF($G404="",0,IF(AND($G404&gt;='Cash Flow'!$E$6,$G404&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G404="",0,IF(AND($G404&gt;='Cash Flow'!$E$6-90,$G404&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I404" s="78" t="str">
-        <f aca="false">IF($H404=1,INT(($G404-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H404=1,MAX(1,INT(($G404-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J404" s="38" t="str">
@@ -28531,7 +28542,7 @@
         <v>0</v>
       </c>
       <c r="I405" s="78" t="str">
-        <f aca="false">IF($H405=1,INT(($G405-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H405=1,MAX(1,INT(($G405-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J405" s="38" t="str">
@@ -28575,7 +28586,7 @@
         <v>0</v>
       </c>
       <c r="I406" s="78" t="str">
-        <f aca="false">IF($H406=1,INT(($G406-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H406=1,MAX(1,INT(($G406-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J406" s="38" t="str">
@@ -28619,7 +28630,7 @@
         <v>0</v>
       </c>
       <c r="I407" s="78" t="str">
-        <f aca="false">IF($H407=1,INT(($G407-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H407=1,MAX(1,INT(($G407-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J407" s="38" t="str">
@@ -28663,7 +28674,7 @@
         <v>0</v>
       </c>
       <c r="I408" s="78" t="str">
-        <f aca="false">IF($H408=1,INT(($G408-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H408=1,MAX(1,INT(($G408-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J408" s="38" t="str">
@@ -28707,7 +28718,7 @@
         <v>0</v>
       </c>
       <c r="I409" s="78" t="str">
-        <f aca="false">IF($H409=1,INT(($G409-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H409=1,MAX(1,INT(($G409-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J409" s="38" t="str">
@@ -28751,7 +28762,7 @@
         <v>0</v>
       </c>
       <c r="I410" s="78" t="str">
-        <f aca="false">IF($H410=1,INT(($G410-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H410=1,MAX(1,INT(($G410-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J410" s="38" t="str">
@@ -28795,7 +28806,7 @@
         <v>0</v>
       </c>
       <c r="I411" s="78" t="str">
-        <f aca="false">IF($H411=1,INT(($G411-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H411=1,MAX(1,INT(($G411-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J411" s="38" t="str">
@@ -28839,7 +28850,7 @@
         <v>0</v>
       </c>
       <c r="I412" s="78" t="str">
-        <f aca="false">IF($H412=1,INT(($G412-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H412=1,MAX(1,INT(($G412-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J412" s="38" t="str">
@@ -28883,7 +28894,7 @@
         <v>0</v>
       </c>
       <c r="I413" s="78" t="str">
-        <f aca="false">IF($H413=1,INT(($G413-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H413=1,MAX(1,INT(($G413-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J413" s="38" t="str">
@@ -28927,7 +28938,7 @@
         <v>0</v>
       </c>
       <c r="I414" s="78" t="str">
-        <f aca="false">IF($H414=1,INT(($G414-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H414=1,MAX(1,INT(($G414-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J414" s="38" t="str">
@@ -28971,7 +28982,7 @@
         <v>0</v>
       </c>
       <c r="I415" s="78" t="str">
-        <f aca="false">IF($H415=1,INT(($G415-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H415=1,MAX(1,INT(($G415-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J415" s="38" t="str">
@@ -29015,7 +29026,7 @@
         <v>0</v>
       </c>
       <c r="I416" s="78" t="str">
-        <f aca="false">IF($H416=1,INT(($G416-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H416=1,MAX(1,INT(($G416-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J416" s="38" t="str">
@@ -29059,7 +29070,7 @@
         <v>0</v>
       </c>
       <c r="I417" s="78" t="str">
-        <f aca="false">IF($H417=1,INT(($G417-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H417=1,MAX(1,INT(($G417-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J417" s="38" t="str">
@@ -29103,7 +29114,7 @@
         <v>0</v>
       </c>
       <c r="I418" s="78" t="str">
-        <f aca="false">IF($H418=1,INT(($G418-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H418=1,MAX(1,INT(($G418-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J418" s="38" t="str">
@@ -29147,7 +29158,7 @@
         <v>0</v>
       </c>
       <c r="I419" s="78" t="str">
-        <f aca="false">IF($H419=1,INT(($G419-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H419=1,MAX(1,INT(($G419-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J419" s="38" t="str">
@@ -29187,11 +29198,11 @@
         <v/>
       </c>
       <c r="H420" s="78" t="n">
-        <f aca="false">IF($G420="",0,IF(AND($G420&gt;='Cash Flow'!$E$6,$G420&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G420="",0,IF(AND($G420&gt;='Cash Flow'!$E$6-90,$G420&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I420" s="78" t="str">
-        <f aca="false">IF($H420=1,INT(($G420-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H420=1,MAX(1,INT(($G420-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J420" s="38" t="str">
@@ -29235,7 +29246,7 @@
         <v>0</v>
       </c>
       <c r="I421" s="78" t="str">
-        <f aca="false">IF($H421=1,INT(($G421-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H421=1,MAX(1,INT(($G421-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J421" s="38" t="str">
@@ -29279,7 +29290,7 @@
         <v>0</v>
       </c>
       <c r="I422" s="78" t="str">
-        <f aca="false">IF($H422=1,INT(($G422-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H422=1,MAX(1,INT(($G422-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J422" s="38" t="str">
@@ -29323,7 +29334,7 @@
         <v>0</v>
       </c>
       <c r="I423" s="78" t="str">
-        <f aca="false">IF($H423=1,INT(($G423-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H423=1,MAX(1,INT(($G423-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J423" s="38" t="str">
@@ -29367,7 +29378,7 @@
         <v>0</v>
       </c>
       <c r="I424" s="78" t="str">
-        <f aca="false">IF($H424=1,INT(($G424-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H424=1,MAX(1,INT(($G424-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J424" s="38" t="str">
@@ -29411,7 +29422,7 @@
         <v>0</v>
       </c>
       <c r="I425" s="78" t="str">
-        <f aca="false">IF($H425=1,INT(($G425-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H425=1,MAX(1,INT(($G425-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J425" s="38" t="str">
@@ -29455,7 +29466,7 @@
         <v>0</v>
       </c>
       <c r="I426" s="78" t="str">
-        <f aca="false">IF($H426=1,INT(($G426-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H426=1,MAX(1,INT(($G426-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J426" s="38" t="str">
@@ -29499,7 +29510,7 @@
         <v>0</v>
       </c>
       <c r="I427" s="78" t="str">
-        <f aca="false">IF($H427=1,INT(($G427-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H427=1,MAX(1,INT(($G427-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J427" s="38" t="str">
@@ -29543,7 +29554,7 @@
         <v>0</v>
       </c>
       <c r="I428" s="78" t="str">
-        <f aca="false">IF($H428=1,INT(($G428-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H428=1,MAX(1,INT(($G428-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J428" s="38" t="str">
@@ -29587,7 +29598,7 @@
         <v>0</v>
       </c>
       <c r="I429" s="78" t="str">
-        <f aca="false">IF($H429=1,INT(($G429-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H429=1,MAX(1,INT(($G429-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J429" s="38" t="str">
@@ -29631,7 +29642,7 @@
         <v>0</v>
       </c>
       <c r="I430" s="78" t="str">
-        <f aca="false">IF($H430=1,INT(($G430-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H430=1,MAX(1,INT(($G430-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J430" s="38" t="str">
@@ -29675,7 +29686,7 @@
         <v>0</v>
       </c>
       <c r="I431" s="78" t="str">
-        <f aca="false">IF($H431=1,INT(($G431-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H431=1,MAX(1,INT(($G431-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J431" s="38" t="str">
@@ -29719,7 +29730,7 @@
         <v>0</v>
       </c>
       <c r="I432" s="78" t="str">
-        <f aca="false">IF($H432=1,INT(($G432-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H432=1,MAX(1,INT(($G432-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J432" s="38" t="str">
@@ -29763,7 +29774,7 @@
         <v>0</v>
       </c>
       <c r="I433" s="78" t="str">
-        <f aca="false">IF($H433=1,INT(($G433-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H433=1,MAX(1,INT(($G433-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J433" s="38" t="str">
@@ -29807,7 +29818,7 @@
         <v>0</v>
       </c>
       <c r="I434" s="78" t="str">
-        <f aca="false">IF($H434=1,INT(($G434-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H434=1,MAX(1,INT(($G434-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J434" s="38" t="str">
@@ -29851,7 +29862,7 @@
         <v>0</v>
       </c>
       <c r="I435" s="78" t="str">
-        <f aca="false">IF($H435=1,INT(($G435-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H435=1,MAX(1,INT(($G435-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J435" s="38" t="str">
@@ -29891,11 +29902,11 @@
         <v/>
       </c>
       <c r="H436" s="78" t="n">
-        <f aca="false">IF($G436="",0,IF(AND($G436&gt;='Cash Flow'!$E$6,$G436&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G436="",0,IF(AND($G436&gt;='Cash Flow'!$E$6-90,$G436&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I436" s="78" t="str">
-        <f aca="false">IF($H436=1,INT(($G436-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H436=1,MAX(1,INT(($G436-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J436" s="38" t="str">
@@ -29939,7 +29950,7 @@
         <v>0</v>
       </c>
       <c r="I437" s="78" t="str">
-        <f aca="false">IF($H437=1,INT(($G437-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H437=1,MAX(1,INT(($G437-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J437" s="38" t="str">
@@ -29983,7 +29994,7 @@
         <v>0</v>
       </c>
       <c r="I438" s="78" t="str">
-        <f aca="false">IF($H438=1,INT(($G438-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H438=1,MAX(1,INT(($G438-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J438" s="38" t="str">
@@ -30027,7 +30038,7 @@
         <v>0</v>
       </c>
       <c r="I439" s="78" t="str">
-        <f aca="false">IF($H439=1,INT(($G439-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H439=1,MAX(1,INT(($G439-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J439" s="38" t="str">
@@ -30071,7 +30082,7 @@
         <v>0</v>
       </c>
       <c r="I440" s="78" t="str">
-        <f aca="false">IF($H440=1,INT(($G440-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H440=1,MAX(1,INT(($G440-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J440" s="38" t="str">
@@ -30115,7 +30126,7 @@
         <v>0</v>
       </c>
       <c r="I441" s="78" t="str">
-        <f aca="false">IF($H441=1,INT(($G441-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H441=1,MAX(1,INT(($G441-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J441" s="38" t="str">
@@ -30159,7 +30170,7 @@
         <v>0</v>
       </c>
       <c r="I442" s="78" t="str">
-        <f aca="false">IF($H442=1,INT(($G442-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H442=1,MAX(1,INT(($G442-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J442" s="38" t="str">
@@ -30203,7 +30214,7 @@
         <v>0</v>
       </c>
       <c r="I443" s="78" t="str">
-        <f aca="false">IF($H443=1,INT(($G443-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H443=1,MAX(1,INT(($G443-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J443" s="38" t="str">
@@ -30247,7 +30258,7 @@
         <v>0</v>
       </c>
       <c r="I444" s="78" t="str">
-        <f aca="false">IF($H444=1,INT(($G444-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H444=1,MAX(1,INT(($G444-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J444" s="38" t="str">
@@ -30291,7 +30302,7 @@
         <v>0</v>
       </c>
       <c r="I445" s="78" t="str">
-        <f aca="false">IF($H445=1,INT(($G445-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H445=1,MAX(1,INT(($G445-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J445" s="38" t="str">
@@ -30335,7 +30346,7 @@
         <v>0</v>
       </c>
       <c r="I446" s="78" t="str">
-        <f aca="false">IF($H446=1,INT(($G446-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H446=1,MAX(1,INT(($G446-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J446" s="38" t="str">
@@ -30379,7 +30390,7 @@
         <v>0</v>
       </c>
       <c r="I447" s="78" t="str">
-        <f aca="false">IF($H447=1,INT(($G447-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H447=1,MAX(1,INT(($G447-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J447" s="38" t="str">
@@ -30423,7 +30434,7 @@
         <v>0</v>
       </c>
       <c r="I448" s="78" t="str">
-        <f aca="false">IF($H448=1,INT(($G448-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H448=1,MAX(1,INT(($G448-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J448" s="38" t="str">
@@ -30467,7 +30478,7 @@
         <v>0</v>
       </c>
       <c r="I449" s="78" t="str">
-        <f aca="false">IF($H449=1,INT(($G449-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H449=1,MAX(1,INT(($G449-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J449" s="38" t="str">
@@ -30511,7 +30522,7 @@
         <v>0</v>
       </c>
       <c r="I450" s="78" t="str">
-        <f aca="false">IF($H450=1,INT(($G450-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H450=1,MAX(1,INT(($G450-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J450" s="38" t="str">
@@ -30555,7 +30566,7 @@
         <v>0</v>
       </c>
       <c r="I451" s="78" t="str">
-        <f aca="false">IF($H451=1,INT(($G451-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H451=1,MAX(1,INT(($G451-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J451" s="38" t="str">
@@ -30595,11 +30606,11 @@
         <v/>
       </c>
       <c r="H452" s="78" t="n">
-        <f aca="false">IF($G452="",0,IF(AND($G452&gt;='Cash Flow'!$E$6,$G452&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G452="",0,IF(AND($G452&gt;='Cash Flow'!$E$6-90,$G452&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I452" s="78" t="str">
-        <f aca="false">IF($H452=1,INT(($G452-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H452=1,MAX(1,INT(($G452-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J452" s="38" t="str">
@@ -30643,7 +30654,7 @@
         <v>0</v>
       </c>
       <c r="I453" s="78" t="str">
-        <f aca="false">IF($H453=1,INT(($G453-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H453=1,MAX(1,INT(($G453-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J453" s="38" t="str">
@@ -30687,7 +30698,7 @@
         <v>0</v>
       </c>
       <c r="I454" s="78" t="str">
-        <f aca="false">IF($H454=1,INT(($G454-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H454=1,MAX(1,INT(($G454-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J454" s="38" t="str">
@@ -30731,7 +30742,7 @@
         <v>0</v>
       </c>
       <c r="I455" s="78" t="str">
-        <f aca="false">IF($H455=1,INT(($G455-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H455=1,MAX(1,INT(($G455-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J455" s="38" t="str">
@@ -30775,7 +30786,7 @@
         <v>0</v>
       </c>
       <c r="I456" s="78" t="str">
-        <f aca="false">IF($H456=1,INT(($G456-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H456=1,MAX(1,INT(($G456-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J456" s="38" t="str">
@@ -30819,7 +30830,7 @@
         <v>0</v>
       </c>
       <c r="I457" s="78" t="str">
-        <f aca="false">IF($H457=1,INT(($G457-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H457=1,MAX(1,INT(($G457-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J457" s="38" t="str">
@@ -30863,7 +30874,7 @@
         <v>0</v>
       </c>
       <c r="I458" s="78" t="str">
-        <f aca="false">IF($H458=1,INT(($G458-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H458=1,MAX(1,INT(($G458-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J458" s="38" t="str">
@@ -30907,7 +30918,7 @@
         <v>0</v>
       </c>
       <c r="I459" s="78" t="str">
-        <f aca="false">IF($H459=1,INT(($G459-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H459=1,MAX(1,INT(($G459-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J459" s="38" t="str">
@@ -30951,7 +30962,7 @@
         <v>0</v>
       </c>
       <c r="I460" s="78" t="str">
-        <f aca="false">IF($H460=1,INT(($G460-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H460=1,MAX(1,INT(($G460-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J460" s="38" t="str">
@@ -30995,7 +31006,7 @@
         <v>0</v>
       </c>
       <c r="I461" s="78" t="str">
-        <f aca="false">IF($H461=1,INT(($G461-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H461=1,MAX(1,INT(($G461-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J461" s="38" t="str">
@@ -31039,7 +31050,7 @@
         <v>0</v>
       </c>
       <c r="I462" s="78" t="str">
-        <f aca="false">IF($H462=1,INT(($G462-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H462=1,MAX(1,INT(($G462-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J462" s="38" t="str">
@@ -31083,7 +31094,7 @@
         <v>0</v>
       </c>
       <c r="I463" s="78" t="str">
-        <f aca="false">IF($H463=1,INT(($G463-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H463=1,MAX(1,INT(($G463-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J463" s="38" t="str">
@@ -31127,7 +31138,7 @@
         <v>0</v>
       </c>
       <c r="I464" s="78" t="str">
-        <f aca="false">IF($H464=1,INT(($G464-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H464=1,MAX(1,INT(($G464-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J464" s="38" t="str">
@@ -31171,7 +31182,7 @@
         <v>0</v>
       </c>
       <c r="I465" s="78" t="str">
-        <f aca="false">IF($H465=1,INT(($G465-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H465=1,MAX(1,INT(($G465-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J465" s="38" t="str">
@@ -31215,7 +31226,7 @@
         <v>0</v>
       </c>
       <c r="I466" s="78" t="str">
-        <f aca="false">IF($H466=1,INT(($G466-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H466=1,MAX(1,INT(($G466-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J466" s="38" t="str">
@@ -31259,7 +31270,7 @@
         <v>0</v>
       </c>
       <c r="I467" s="78" t="str">
-        <f aca="false">IF($H467=1,INT(($G467-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H467=1,MAX(1,INT(($G467-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J467" s="38" t="str">
@@ -31299,11 +31310,11 @@
         <v/>
       </c>
       <c r="H468" s="78" t="n">
-        <f aca="false">IF($G468="",0,IF(AND($G468&gt;='Cash Flow'!$E$6,$G468&lt;'Cash Flow'!$E$6+91),1,0))</f>
+        <f aca="false">IF($G468="",0,IF(AND($G468&gt;='Cash Flow'!$E$6-90,$G468&lt;'Cash Flow'!$E$6+91),1,0))</f>
         <v>0</v>
       </c>
       <c r="I468" s="78" t="str">
-        <f aca="false">IF($H468=1,INT(($G468-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H468=1,MAX(1,INT(($G468-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J468" s="38" t="str">
@@ -31347,7 +31358,7 @@
         <v>0</v>
       </c>
       <c r="I469" s="78" t="str">
-        <f aca="false">IF($H469=1,INT(($G469-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H469=1,MAX(1,INT(($G469-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J469" s="38" t="str">
@@ -31391,7 +31402,7 @@
         <v>0</v>
       </c>
       <c r="I470" s="78" t="str">
-        <f aca="false">IF($H470=1,INT(($G470-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H470=1,MAX(1,INT(($G470-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J470" s="38" t="str">
@@ -31435,7 +31446,7 @@
         <v>0</v>
       </c>
       <c r="I471" s="78" t="str">
-        <f aca="false">IF($H471=1,INT(($G471-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H471=1,MAX(1,INT(($G471-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J471" s="38" t="str">
@@ -31479,7 +31490,7 @@
         <v>0</v>
       </c>
       <c r="I472" s="78" t="str">
-        <f aca="false">IF($H472=1,INT(($G472-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H472=1,MAX(1,INT(($G472-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J472" s="38" t="str">
@@ -31523,7 +31534,7 @@
         <v>0</v>
       </c>
       <c r="I473" s="78" t="str">
-        <f aca="false">IF($H473=1,INT(($G473-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H473=1,MAX(1,INT(($G473-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J473" s="38" t="str">
@@ -31567,7 +31578,7 @@
         <v>0</v>
       </c>
       <c r="I474" s="78" t="str">
-        <f aca="false">IF($H474=1,INT(($G474-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H474=1,MAX(1,INT(($G474-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J474" s="38" t="str">
@@ -31611,7 +31622,7 @@
         <v>0</v>
       </c>
       <c r="I475" s="78" t="str">
-        <f aca="false">IF($H475=1,INT(($G475-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H475=1,MAX(1,INT(($G475-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J475" s="38" t="str">
@@ -31655,7 +31666,7 @@
         <v>0</v>
       </c>
       <c r="I476" s="78" t="str">
-        <f aca="false">IF($H476=1,INT(($G476-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H476=1,MAX(1,INT(($G476-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J476" s="38" t="str">
@@ -31699,7 +31710,7 @@
         <v>0</v>
       </c>
       <c r="I477" s="78" t="str">
-        <f aca="false">IF($H477=1,INT(($G477-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H477=1,MAX(1,INT(($G477-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J477" s="38" t="str">
@@ -31743,7 +31754,7 @@
         <v>0</v>
       </c>
       <c r="I478" s="78" t="str">
-        <f aca="false">IF($H478=1,INT(($G478-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H478=1,MAX(1,INT(($G478-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J478" s="38" t="str">
@@ -31787,7 +31798,7 @@
         <v>0</v>
       </c>
       <c r="I479" s="78" t="str">
-        <f aca="false">IF($H479=1,INT(($G479-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H479=1,MAX(1,INT(($G479-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J479" s="38" t="str">
@@ -31831,7 +31842,7 @@
         <v>0</v>
       </c>
       <c r="I480" s="78" t="str">
-        <f aca="false">IF($H480=1,INT(($G480-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H480=1,MAX(1,INT(($G480-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J480" s="38" t="str">
@@ -31875,7 +31886,7 @@
         <v>0</v>
       </c>
       <c r="I481" s="78" t="str">
-        <f aca="false">IF($H481=1,INT(($G481-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H481=1,MAX(1,INT(($G481-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J481" s="38" t="str">
@@ -31919,7 +31930,7 @@
         <v>0</v>
       </c>
       <c r="I482" s="78" t="str">
-        <f aca="false">IF($H482=1,INT(($G482-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H482=1,MAX(1,INT(($G482-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J482" s="38" t="str">
@@ -31963,7 +31974,7 @@
         <v>0</v>
       </c>
       <c r="I483" s="78" t="str">
-        <f aca="false">IF($H483=1,INT(($G483-'Cash Flow'!$E$6)/7)+1,"")</f>
+        <f aca="false">IF($H483=1,MAX(1,INT(($G483-'Cash Flow'!$E$6)/7)+1),"")</f>
         <v/>
       </c>
       <c r="J483" s="38" t="str">

--- a/Weekly_Cash_Flow_Survival.xlsx
+++ b/Weekly_Cash_Flow_Survival.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">'Cash Flow'!$A$1:$K$284</definedName>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$46</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instructions!$A$1:$C$48</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">Recurring!$A$1:$J$38</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">Recurring!$4:$4</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Summary!$A$1:$J$28</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="171">
   <si>
     <t xml:space="preserve">WEEKLY CASH FLOW SURVIVAL WORKSHEET</t>
   </si>
@@ -138,10 +138,22 @@
     <t xml:space="preserve">Type a description, date, Income or Expense, and an amount into any blank row in a week block. Nothing needs to exist on the Recurring tab first.</t>
   </si>
   <si>
+    <t xml:space="preserve">One week's amount is different</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is what the 'Amount Paid / Received' column is for, and it needs no formula touched at all. Working extra shifts and expecting $150 from Bruno's instead of $90? Type 150 into that row's Amount Paid / Received cell. MONEY IN, the running balance and the Summary all follow it, that row stays linked to the Recurring tab, and every other week keeps the usual $90. It works the same for a bill that comes in higher or lower than scheduled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADJUSTED vs PAID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A figure typed against a date still in the future reads ADJUSTED — you have revised what you expect, not recorded money that moved. Once the date arrives it reads PAID.</t>
+  </si>
+  <si>
     <t xml:space="preserve">To pay part of a bill</t>
   </si>
   <si>
-    <t xml:space="preserve">Leave the scheduled row alone and put what you actually paid in Amount Paid. That column is yours already and always wins over the scheduled figure.</t>
+    <t xml:space="preserve">Same column. Put what you actually paid in Amount Paid / Received; it always wins over the scheduled figure.</t>
   </si>
   <si>
     <t xml:space="preserve">To get the formula back</t>
@@ -393,7 +405,7 @@
     <t xml:space="preserve">Scheduled Amount</t>
   </si>
   <si>
-    <t xml:space="preserve">Amount Paid</t>
+    <t xml:space="preserve">Amount Paid / Received</t>
   </si>
   <si>
     <t xml:space="preserve">Running Balance</t>
@@ -1462,7 +1474,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B2:C46"/>
+  <dimension ref="B2:C48"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -1640,24 +1652,24 @@
         <v>40</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="3" t="s">
+    <row r="28" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="12" t="s">
+      <c r="C28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="5" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="12" t="s">
         <v>43</v>
       </c>
+      <c r="C29" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1685,89 +1697,105 @@
         <v>51</v>
       </c>
     </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="B36" s="12" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="C36" s="5" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>63</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1803,44 +1831,44 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1848,28 +1876,28 @@
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D5" s="18" t="n">
         <v>90</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F5" s="19" t="n">
         <v>46246</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -1878,28 +1906,28 @@
         <v>2</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>81</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>77</v>
       </c>
       <c r="D6" s="23" t="n">
         <v>790</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>46248</v>
       </c>
       <c r="G6" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J6" s="21"/>
     </row>
@@ -1908,28 +1936,28 @@
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>21.1</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F7" s="19" t="n">
         <v>46238</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -1938,28 +1966,28 @@
         <v>4</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D8" s="23" t="n">
         <v>20</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>46239</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J8" s="21"/>
     </row>
@@ -1968,28 +1996,28 @@
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D9" s="18" t="n">
         <v>10</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F9" s="19" t="n">
         <v>46239</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -1998,28 +2026,28 @@
         <v>6</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>83</v>
       </c>
       <c r="D10" s="23" t="n">
         <v>4.99</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>46272</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J10" s="21"/>
     </row>
@@ -2028,28 +2056,28 @@
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" s="18" t="n">
         <v>500</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F11" s="19" t="n">
         <v>46272</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J11" s="6"/>
     </row>
@@ -2058,28 +2086,28 @@
         <v>8</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D12" s="23" t="n">
         <v>163.5</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>46275</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J12" s="21"/>
     </row>
@@ -2088,28 +2116,28 @@
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>2.99</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F13" s="19" t="n">
         <v>46247</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -2118,28 +2146,28 @@
         <v>10</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D14" s="23" t="n">
         <v>350</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>46248</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="J14" s="21"/>
     </row>
@@ -2148,28 +2176,28 @@
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D15" s="18" t="n">
         <v>171.1</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F15" s="19" t="n">
         <v>46250</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -2178,28 +2206,28 @@
         <v>12</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D16" s="23" t="n">
         <v>45</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F16" s="24" t="n">
         <v>46250</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J16" s="21"/>
     </row>
@@ -2208,28 +2236,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D17" s="18" t="n">
         <v>16.99</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F17" s="19" t="n">
         <v>46252</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -2238,28 +2266,28 @@
         <v>14</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D18" s="23" t="n">
         <v>13.7</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F18" s="24" t="n">
         <v>46259</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I18" s="21" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J18" s="21"/>
     </row>
@@ -2268,28 +2296,28 @@
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D19" s="18" t="n">
         <v>43.87</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F19" s="19" t="n">
         <v>46259</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -2298,28 +2326,28 @@
         <v>16</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D20" s="23" t="n">
         <v>150</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F20" s="24" t="n">
         <v>46264</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I20" s="21" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J20" s="21"/>
     </row>
@@ -2328,28 +2356,28 @@
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>143.37</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F21" s="19" t="n">
         <v>46265</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="J21" s="6"/>
     </row>
@@ -2537,17 +2565,17 @@
     </row>
     <row r="36" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="25" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -2614,17 +2642,17 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="12" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E5" s="26" t="n">
         <v>71.17</v>
@@ -2632,7 +2660,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="12" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E6" s="27" t="n">
         <v>46241</v>
@@ -2644,7 +2672,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>200</v>
@@ -2652,7 +2680,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="29" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E8" s="30" t="n">
         <f aca="true">TODAY()</f>
@@ -2661,12 +2689,12 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="25" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2679,7 +2707,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="32"/>
       <c r="G13" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="34" t="n">
@@ -2694,19 +2722,19 @@
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G14" s="36" t="s">
         <v>18</v>
@@ -2715,10 +2743,10 @@
         <v>20</v>
       </c>
       <c r="I14" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J14" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2752,7 +2780,7 @@
         <v>50.07</v>
       </c>
       <c r="J15" s="46" t="str">
-        <f aca="true">IF($B15="","",IF($F15&lt;&gt;"","PAID",IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B15="","",IF($F15&lt;&gt;"",IF($C15&gt;TODAY(),"ADJUSTED","PAID"),IF($C15&lt;TODAY(),"PAST DUE",IF($C15&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>PAST DUE</v>
       </c>
     </row>
@@ -2787,7 +2815,7 @@
         <v>30.07</v>
       </c>
       <c r="J16" s="46" t="str">
-        <f aca="true">IF($B16="","",IF($F16&lt;&gt;"","PAID",IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B16="","",IF($F16&lt;&gt;"",IF($C16&gt;TODAY(),"ADJUSTED","PAID"),IF($C16&lt;TODAY(),"PAST DUE",IF($C16&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>PAST DUE</v>
       </c>
     </row>
@@ -2822,7 +2850,7 @@
         <v>20.07</v>
       </c>
       <c r="J17" s="46" t="str">
-        <f aca="true">IF($B17="","",IF($F17&lt;&gt;"","PAID",IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B17="","",IF($F17&lt;&gt;"",IF($C17&gt;TODAY(),"ADJUSTED","PAID"),IF($C17&lt;TODAY(),"PAST DUE",IF($C17&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>PAST DUE</v>
       </c>
     </row>
@@ -2857,7 +2885,7 @@
         <v>110.07</v>
       </c>
       <c r="J18" s="46" t="str">
-        <f aca="true">IF($B18="","",IF($F18&lt;&gt;"","PAID",IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B18="","",IF($F18&lt;&gt;"",IF($C18&gt;TODAY(),"ADJUSTED","PAID"),IF($C18&lt;TODAY(),"PAST DUE",IF($C18&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>DUE</v>
       </c>
     </row>
@@ -2892,7 +2920,7 @@
         <v>107.08</v>
       </c>
       <c r="J19" s="46" t="str">
-        <f aca="true">IF($B19="","",IF($F19&lt;&gt;"","PAID",IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B19="","",IF($F19&lt;&gt;"",IF($C19&gt;TODAY(),"ADJUSTED","PAID"),IF($C19&lt;TODAY(),"PAST DUE",IF($C19&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>DUE</v>
       </c>
     </row>
@@ -2927,7 +2955,7 @@
         <v/>
       </c>
       <c r="J20" s="46" t="str">
-        <f aca="true">IF($B20="","",IF($F20&lt;&gt;"","PAID",IF($C20&lt;TODAY(),"PAST DUE",IF($C20&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B20="","",IF($F20&lt;&gt;"",IF($C20&gt;TODAY(),"ADJUSTED","PAID"),IF($C20&lt;TODAY(),"PAST DUE",IF($C20&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -2962,7 +2990,7 @@
         <v/>
       </c>
       <c r="J21" s="46" t="str">
-        <f aca="true">IF($B21="","",IF($F21&lt;&gt;"","PAID",IF($C21&lt;TODAY(),"PAST DUE",IF($C21&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B21="","",IF($F21&lt;&gt;"",IF($C21&gt;TODAY(),"ADJUSTED","PAID"),IF($C21&lt;TODAY(),"PAST DUE",IF($C21&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -2997,7 +3025,7 @@
         <v/>
       </c>
       <c r="J22" s="46" t="str">
-        <f aca="true">IF($B22="","",IF($F22&lt;&gt;"","PAID",IF($C22&lt;TODAY(),"PAST DUE",IF($C22&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B22="","",IF($F22&lt;&gt;"",IF($C22&gt;TODAY(),"ADJUSTED","PAID"),IF($C22&lt;TODAY(),"PAST DUE",IF($C22&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -3032,7 +3060,7 @@
         <v/>
       </c>
       <c r="J23" s="46" t="str">
-        <f aca="true">IF($B23="","",IF($F23&lt;&gt;"","PAID",IF($C23&lt;TODAY(),"PAST DUE",IF($C23&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B23="","",IF($F23&lt;&gt;"",IF($C23&gt;TODAY(),"ADJUSTED","PAID"),IF($C23&lt;TODAY(),"PAST DUE",IF($C23&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -3067,13 +3095,13 @@
         <v/>
       </c>
       <c r="J24" s="46" t="str">
-        <f aca="true">IF($B24="","",IF($F24&lt;&gt;"","PAID",IF($C24&lt;TODAY(),"PAST DUE",IF($C24&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B24="","",IF($F24&lt;&gt;"",IF($C24&gt;TODAY(),"ADJUSTED","PAID"),IF($C24&lt;TODAY(),"PAST DUE",IF($C24&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="48"/>
@@ -3206,7 +3234,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="52" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
@@ -3243,7 +3271,7 @@
       <c r="E34" s="32"/>
       <c r="F34" s="32"/>
       <c r="G34" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H34" s="32"/>
       <c r="I34" s="34" t="n">
@@ -3258,19 +3286,19 @@
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D35" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E35" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F35" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G35" s="36" t="s">
         <v>18</v>
@@ -3279,10 +3307,10 @@
         <v>20</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J35" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3316,7 +3344,7 @@
         <v>897.08</v>
       </c>
       <c r="J36" s="46" t="str">
-        <f aca="true">IF($B36="","",IF($F36&lt;&gt;"","PAID",IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B36="","",IF($F36&lt;&gt;"",IF($C36&gt;TODAY(),"ADJUSTED","PAID"),IF($C36&lt;TODAY(),"PAST DUE",IF($C36&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>DUE</v>
       </c>
     </row>
@@ -3351,7 +3379,7 @@
         <v>547.08</v>
       </c>
       <c r="J37" s="46" t="str">
-        <f aca="true">IF($B37="","",IF($F37&lt;&gt;"","PAID",IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B37="","",IF($F37&lt;&gt;"",IF($C37&gt;TODAY(),"ADJUSTED","PAID"),IF($C37&lt;TODAY(),"PAST DUE",IF($C37&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>DUE</v>
       </c>
     </row>
@@ -3386,7 +3414,7 @@
         <v>375.98</v>
       </c>
       <c r="J38" s="46" t="str">
-        <f aca="true">IF($B38="","",IF($F38&lt;&gt;"","PAID",IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B38="","",IF($F38&lt;&gt;"",IF($C38&gt;TODAY(),"ADJUSTED","PAID"),IF($C38&lt;TODAY(),"PAST DUE",IF($C38&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3421,7 +3449,7 @@
         <v>330.98</v>
       </c>
       <c r="J39" s="46" t="str">
-        <f aca="true">IF($B39="","",IF($F39&lt;&gt;"","PAID",IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B39="","",IF($F39&lt;&gt;"",IF($C39&gt;TODAY(),"ADJUSTED","PAID"),IF($C39&lt;TODAY(),"PAST DUE",IF($C39&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3456,7 +3484,7 @@
         <v>313.99</v>
       </c>
       <c r="J40" s="46" t="str">
-        <f aca="true">IF($B40="","",IF($F40&lt;&gt;"","PAID",IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B40="","",IF($F40&lt;&gt;"",IF($C40&gt;TODAY(),"ADJUSTED","PAID"),IF($C40&lt;TODAY(),"PAST DUE",IF($C40&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3491,7 +3519,7 @@
         <v>403.99</v>
       </c>
       <c r="J41" s="46" t="str">
-        <f aca="true">IF($B41="","",IF($F41&lt;&gt;"","PAID",IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B41="","",IF($F41&lt;&gt;"",IF($C41&gt;TODAY(),"ADJUSTED","PAID"),IF($C41&lt;TODAY(),"PAST DUE",IF($C41&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3526,7 +3554,7 @@
         <v/>
       </c>
       <c r="J42" s="46" t="str">
-        <f aca="true">IF($B42="","",IF($F42&lt;&gt;"","PAID",IF($C42&lt;TODAY(),"PAST DUE",IF($C42&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B42="","",IF($F42&lt;&gt;"",IF($C42&gt;TODAY(),"ADJUSTED","PAID"),IF($C42&lt;TODAY(),"PAST DUE",IF($C42&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -3561,7 +3589,7 @@
         <v/>
       </c>
       <c r="J43" s="46" t="str">
-        <f aca="true">IF($B43="","",IF($F43&lt;&gt;"","PAID",IF($C43&lt;TODAY(),"PAST DUE",IF($C43&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B43="","",IF($F43&lt;&gt;"",IF($C43&gt;TODAY(),"ADJUSTED","PAID"),IF($C43&lt;TODAY(),"PAST DUE",IF($C43&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -3596,7 +3624,7 @@
         <v/>
       </c>
       <c r="J44" s="46" t="str">
-        <f aca="true">IF($B44="","",IF($F44&lt;&gt;"","PAID",IF($C44&lt;TODAY(),"PAST DUE",IF($C44&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B44="","",IF($F44&lt;&gt;"",IF($C44&gt;TODAY(),"ADJUSTED","PAID"),IF($C44&lt;TODAY(),"PAST DUE",IF($C44&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -3631,13 +3659,13 @@
         <v/>
       </c>
       <c r="J45" s="46" t="str">
-        <f aca="true">IF($B45="","",IF($F45&lt;&gt;"","PAID",IF($C45&lt;TODAY(),"PAST DUE",IF($C45&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B45="","",IF($F45&lt;&gt;"",IF($C45&gt;TODAY(),"ADJUSTED","PAID"),IF($C45&lt;TODAY(),"PAST DUE",IF($C45&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C46" s="48"/>
       <c r="D46" s="48"/>
@@ -3770,7 +3798,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="52" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C53" s="53"/>
       <c r="D53" s="53"/>
@@ -3807,7 +3835,7 @@
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
       <c r="G55" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H55" s="32"/>
       <c r="I55" s="34" t="n">
@@ -3822,19 +3850,19 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E56" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G56" s="36" t="s">
         <v>18</v>
@@ -3843,10 +3871,10 @@
         <v>20</v>
       </c>
       <c r="I56" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J56" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3880,7 +3908,7 @@
         <v>1193.99</v>
       </c>
       <c r="J57" s="46" t="str">
-        <f aca="true">IF($B57="","",IF($F57&lt;&gt;"","PAID",IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B57="","",IF($F57&lt;&gt;"",IF($C57&gt;TODAY(),"ADJUSTED","PAID"),IF($C57&lt;TODAY(),"PAST DUE",IF($C57&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3915,7 +3943,7 @@
         <v>1180.29</v>
       </c>
       <c r="J58" s="46" t="str">
-        <f aca="true">IF($B58="","",IF($F58&lt;&gt;"","PAID",IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B58="","",IF($F58&lt;&gt;"",IF($C58&gt;TODAY(),"ADJUSTED","PAID"),IF($C58&lt;TODAY(),"PAST DUE",IF($C58&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3950,7 +3978,7 @@
         <v>1136.42</v>
       </c>
       <c r="J59" s="46" t="str">
-        <f aca="true">IF($B59="","",IF($F59&lt;&gt;"","PAID",IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B59="","",IF($F59&lt;&gt;"",IF($C59&gt;TODAY(),"ADJUSTED","PAID"),IF($C59&lt;TODAY(),"PAST DUE",IF($C59&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -3985,7 +4013,7 @@
         <v>1226.42</v>
       </c>
       <c r="J60" s="46" t="str">
-        <f aca="true">IF($B60="","",IF($F60&lt;&gt;"","PAID",IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B60="","",IF($F60&lt;&gt;"",IF($C60&gt;TODAY(),"ADJUSTED","PAID"),IF($C60&lt;TODAY(),"PAST DUE",IF($C60&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4020,7 +4048,7 @@
         <v/>
       </c>
       <c r="J61" s="46" t="str">
-        <f aca="true">IF($B61="","",IF($F61&lt;&gt;"","PAID",IF($C61&lt;TODAY(),"PAST DUE",IF($C61&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B61="","",IF($F61&lt;&gt;"",IF($C61&gt;TODAY(),"ADJUSTED","PAID"),IF($C61&lt;TODAY(),"PAST DUE",IF($C61&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4055,7 +4083,7 @@
         <v/>
       </c>
       <c r="J62" s="46" t="str">
-        <f aca="true">IF($B62="","",IF($F62&lt;&gt;"","PAID",IF($C62&lt;TODAY(),"PAST DUE",IF($C62&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B62="","",IF($F62&lt;&gt;"",IF($C62&gt;TODAY(),"ADJUSTED","PAID"),IF($C62&lt;TODAY(),"PAST DUE",IF($C62&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4090,7 +4118,7 @@
         <v/>
       </c>
       <c r="J63" s="46" t="str">
-        <f aca="true">IF($B63="","",IF($F63&lt;&gt;"","PAID",IF($C63&lt;TODAY(),"PAST DUE",IF($C63&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B63="","",IF($F63&lt;&gt;"",IF($C63&gt;TODAY(),"ADJUSTED","PAID"),IF($C63&lt;TODAY(),"PAST DUE",IF($C63&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4125,7 +4153,7 @@
         <v/>
       </c>
       <c r="J64" s="46" t="str">
-        <f aca="true">IF($B64="","",IF($F64&lt;&gt;"","PAID",IF($C64&lt;TODAY(),"PAST DUE",IF($C64&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B64="","",IF($F64&lt;&gt;"",IF($C64&gt;TODAY(),"ADJUSTED","PAID"),IF($C64&lt;TODAY(),"PAST DUE",IF($C64&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4160,7 +4188,7 @@
         <v/>
       </c>
       <c r="J65" s="46" t="str">
-        <f aca="true">IF($B65="","",IF($F65&lt;&gt;"","PAID",IF($C65&lt;TODAY(),"PAST DUE",IF($C65&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B65="","",IF($F65&lt;&gt;"",IF($C65&gt;TODAY(),"ADJUSTED","PAID"),IF($C65&lt;TODAY(),"PAST DUE",IF($C65&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4195,13 +4223,13 @@
         <v/>
       </c>
       <c r="J66" s="46" t="str">
-        <f aca="true">IF($B66="","",IF($F66&lt;&gt;"","PAID",IF($C66&lt;TODAY(),"PAST DUE",IF($C66&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B66="","",IF($F66&lt;&gt;"",IF($C66&gt;TODAY(),"ADJUSTED","PAID"),IF($C66&lt;TODAY(),"PAST DUE",IF($C66&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C67" s="48"/>
       <c r="D67" s="48"/>
@@ -4334,7 +4362,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="52" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C74" s="53"/>
       <c r="D74" s="53"/>
@@ -4371,7 +4399,7 @@
       <c r="E76" s="32"/>
       <c r="F76" s="32"/>
       <c r="G76" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H76" s="32"/>
       <c r="I76" s="34" t="n">
@@ -4386,19 +4414,19 @@
     </row>
     <row r="77" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C77" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D77" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E77" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F77" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G77" s="36" t="s">
         <v>18</v>
@@ -4407,10 +4435,10 @@
         <v>20</v>
       </c>
       <c r="I77" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J77" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4444,7 +4472,7 @@
         <v>2016.42</v>
       </c>
       <c r="J78" s="46" t="str">
-        <f aca="true">IF($B78="","",IF($F78&lt;&gt;"","PAID",IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B78="","",IF($F78&lt;&gt;"",IF($C78&gt;TODAY(),"ADJUSTED","PAID"),IF($C78&lt;TODAY(),"PAST DUE",IF($C78&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4479,7 +4507,7 @@
         <v>1866.42</v>
       </c>
       <c r="J79" s="46" t="str">
-        <f aca="true">IF($B79="","",IF($F79&lt;&gt;"","PAID",IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B79="","",IF($F79&lt;&gt;"",IF($C79&gt;TODAY(),"ADJUSTED","PAID"),IF($C79&lt;TODAY(),"PAST DUE",IF($C79&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4514,7 +4542,7 @@
         <v>1516.42</v>
       </c>
       <c r="J80" s="46" t="str">
-        <f aca="true">IF($B80="","",IF($F80&lt;&gt;"","PAID",IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B80="","",IF($F80&lt;&gt;"",IF($C80&gt;TODAY(),"ADJUSTED","PAID"),IF($C80&lt;TODAY(),"PAST DUE",IF($C80&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4549,7 +4577,7 @@
         <v>1373.05</v>
       </c>
       <c r="J81" s="46" t="str">
-        <f aca="true">IF($B81="","",IF($F81&lt;&gt;"","PAID",IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B81="","",IF($F81&lt;&gt;"",IF($C81&gt;TODAY(),"ADJUSTED","PAID"),IF($C81&lt;TODAY(),"PAST DUE",IF($C81&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4584,7 +4612,7 @@
         <v>1463.05</v>
       </c>
       <c r="J82" s="46" t="str">
-        <f aca="true">IF($B82="","",IF($F82&lt;&gt;"","PAID",IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B82="","",IF($F82&lt;&gt;"",IF($C82&gt;TODAY(),"ADJUSTED","PAID"),IF($C82&lt;TODAY(),"PAST DUE",IF($C82&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -4619,7 +4647,7 @@
         <v/>
       </c>
       <c r="J83" s="46" t="str">
-        <f aca="true">IF($B83="","",IF($F83&lt;&gt;"","PAID",IF($C83&lt;TODAY(),"PAST DUE",IF($C83&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B83="","",IF($F83&lt;&gt;"",IF($C83&gt;TODAY(),"ADJUSTED","PAID"),IF($C83&lt;TODAY(),"PAST DUE",IF($C83&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4654,7 +4682,7 @@
         <v/>
       </c>
       <c r="J84" s="46" t="str">
-        <f aca="true">IF($B84="","",IF($F84&lt;&gt;"","PAID",IF($C84&lt;TODAY(),"PAST DUE",IF($C84&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B84="","",IF($F84&lt;&gt;"",IF($C84&gt;TODAY(),"ADJUSTED","PAID"),IF($C84&lt;TODAY(),"PAST DUE",IF($C84&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4689,7 +4717,7 @@
         <v/>
       </c>
       <c r="J85" s="46" t="str">
-        <f aca="true">IF($B85="","",IF($F85&lt;&gt;"","PAID",IF($C85&lt;TODAY(),"PAST DUE",IF($C85&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B85="","",IF($F85&lt;&gt;"",IF($C85&gt;TODAY(),"ADJUSTED","PAID"),IF($C85&lt;TODAY(),"PAST DUE",IF($C85&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4724,7 +4752,7 @@
         <v/>
       </c>
       <c r="J86" s="46" t="str">
-        <f aca="true">IF($B86="","",IF($F86&lt;&gt;"","PAID",IF($C86&lt;TODAY(),"PAST DUE",IF($C86&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B86="","",IF($F86&lt;&gt;"",IF($C86&gt;TODAY(),"ADJUSTED","PAID"),IF($C86&lt;TODAY(),"PAST DUE",IF($C86&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -4759,13 +4787,13 @@
         <v/>
       </c>
       <c r="J87" s="46" t="str">
-        <f aca="true">IF($B87="","",IF($F87&lt;&gt;"","PAID",IF($C87&lt;TODAY(),"PAST DUE",IF($C87&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B87="","",IF($F87&lt;&gt;"",IF($C87&gt;TODAY(),"ADJUSTED","PAID"),IF($C87&lt;TODAY(),"PAST DUE",IF($C87&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C88" s="48"/>
       <c r="D88" s="48"/>
@@ -4898,7 +4926,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="52" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C95" s="53"/>
       <c r="D95" s="53"/>
@@ -4935,7 +4963,7 @@
       <c r="E97" s="32"/>
       <c r="F97" s="32"/>
       <c r="G97" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H97" s="32"/>
       <c r="I97" s="34" t="n">
@@ -4950,19 +4978,19 @@
     </row>
     <row r="98" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C98" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D98" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E98" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F98" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G98" s="36" t="s">
         <v>18</v>
@@ -4971,10 +4999,10 @@
         <v>20</v>
       </c>
       <c r="I98" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J98" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5008,7 +5036,7 @@
         <v>2253.05</v>
       </c>
       <c r="J99" s="46" t="str">
-        <f aca="true">IF($B99="","",IF($F99&lt;&gt;"","PAID",IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B99="","",IF($F99&lt;&gt;"",IF($C99&gt;TODAY(),"ADJUSTED","PAID"),IF($C99&lt;TODAY(),"PAST DUE",IF($C99&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5043,7 +5071,7 @@
         <v>2231.95</v>
       </c>
       <c r="J100" s="46" t="str">
-        <f aca="true">IF($B100="","",IF($F100&lt;&gt;"","PAID",IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B100="","",IF($F100&lt;&gt;"",IF($C100&gt;TODAY(),"ADJUSTED","PAID"),IF($C100&lt;TODAY(),"PAST DUE",IF($C100&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5078,7 +5106,7 @@
         <v>2211.95</v>
       </c>
       <c r="J101" s="46" t="str">
-        <f aca="true">IF($B101="","",IF($F101&lt;&gt;"","PAID",IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B101="","",IF($F101&lt;&gt;"",IF($C101&gt;TODAY(),"ADJUSTED","PAID"),IF($C101&lt;TODAY(),"PAST DUE",IF($C101&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5113,7 +5141,7 @@
         <v>2201.95</v>
       </c>
       <c r="J102" s="46" t="str">
-        <f aca="true">IF($B102="","",IF($F102&lt;&gt;"","PAID",IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B102="","",IF($F102&lt;&gt;"",IF($C102&gt;TODAY(),"ADJUSTED","PAID"),IF($C102&lt;TODAY(),"PAST DUE",IF($C102&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5148,7 +5176,7 @@
         <v>2196.96</v>
       </c>
       <c r="J103" s="46" t="str">
-        <f aca="true">IF($B103="","",IF($F103&lt;&gt;"","PAID",IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B103="","",IF($F103&lt;&gt;"",IF($C103&gt;TODAY(),"ADJUSTED","PAID"),IF($C103&lt;TODAY(),"PAST DUE",IF($C103&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5183,7 +5211,7 @@
         <v>1696.96</v>
       </c>
       <c r="J104" s="46" t="str">
-        <f aca="true">IF($B104="","",IF($F104&lt;&gt;"","PAID",IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B104="","",IF($F104&lt;&gt;"",IF($C104&gt;TODAY(),"ADJUSTED","PAID"),IF($C104&lt;TODAY(),"PAST DUE",IF($C104&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5218,7 +5246,7 @@
         <v>1786.96</v>
       </c>
       <c r="J105" s="46" t="str">
-        <f aca="true">IF($B105="","",IF($F105&lt;&gt;"","PAID",IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B105="","",IF($F105&lt;&gt;"",IF($C105&gt;TODAY(),"ADJUSTED","PAID"),IF($C105&lt;TODAY(),"PAST DUE",IF($C105&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5253,7 +5281,7 @@
         <v>1623.46</v>
       </c>
       <c r="J106" s="46" t="str">
-        <f aca="true">IF($B106="","",IF($F106&lt;&gt;"","PAID",IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B106="","",IF($F106&lt;&gt;"",IF($C106&gt;TODAY(),"ADJUSTED","PAID"),IF($C106&lt;TODAY(),"PAST DUE",IF($C106&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5288,7 +5316,7 @@
         <v/>
       </c>
       <c r="J107" s="46" t="str">
-        <f aca="true">IF($B107="","",IF($F107&lt;&gt;"","PAID",IF($C107&lt;TODAY(),"PAST DUE",IF($C107&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B107="","",IF($F107&lt;&gt;"",IF($C107&gt;TODAY(),"ADJUSTED","PAID"),IF($C107&lt;TODAY(),"PAST DUE",IF($C107&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -5323,13 +5351,13 @@
         <v/>
       </c>
       <c r="J108" s="46" t="str">
-        <f aca="true">IF($B108="","",IF($F108&lt;&gt;"","PAID",IF($C108&lt;TODAY(),"PAST DUE",IF($C108&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B108="","",IF($F108&lt;&gt;"",IF($C108&gt;TODAY(),"ADJUSTED","PAID"),IF($C108&lt;TODAY(),"PAST DUE",IF($C108&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C109" s="48"/>
       <c r="D109" s="48"/>
@@ -5462,7 +5490,7 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="52" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C116" s="53"/>
       <c r="D116" s="53"/>
@@ -5499,7 +5527,7 @@
       <c r="E118" s="32"/>
       <c r="F118" s="32"/>
       <c r="G118" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H118" s="32"/>
       <c r="I118" s="34" t="n">
@@ -5514,19 +5542,19 @@
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B119" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C119" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E119" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F119" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G119" s="36" t="s">
         <v>18</v>
@@ -5535,10 +5563,10 @@
         <v>20</v>
       </c>
       <c r="I119" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J119" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5572,7 +5600,7 @@
         <v>2413.46</v>
       </c>
       <c r="J120" s="46" t="str">
-        <f aca="true">IF($B120="","",IF($F120&lt;&gt;"","PAID",IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B120="","",IF($F120&lt;&gt;"",IF($C120&gt;TODAY(),"ADJUSTED","PAID"),IF($C120&lt;TODAY(),"PAST DUE",IF($C120&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5607,7 +5635,7 @@
         <v>2410.47</v>
       </c>
       <c r="J121" s="46" t="str">
-        <f aca="true">IF($B121="","",IF($F121&lt;&gt;"","PAID",IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B121="","",IF($F121&lt;&gt;"",IF($C121&gt;TODAY(),"ADJUSTED","PAID"),IF($C121&lt;TODAY(),"PAST DUE",IF($C121&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5642,7 +5670,7 @@
         <v>2060.47</v>
       </c>
       <c r="J122" s="46" t="str">
-        <f aca="true">IF($B122="","",IF($F122&lt;&gt;"","PAID",IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B122="","",IF($F122&lt;&gt;"",IF($C122&gt;TODAY(),"ADJUSTED","PAID"),IF($C122&lt;TODAY(),"PAST DUE",IF($C122&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5677,7 +5705,7 @@
         <v>2150.47</v>
       </c>
       <c r="J123" s="46" t="str">
-        <f aca="true">IF($B123="","",IF($F123&lt;&gt;"","PAID",IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B123="","",IF($F123&lt;&gt;"",IF($C123&gt;TODAY(),"ADJUSTED","PAID"),IF($C123&lt;TODAY(),"PAST DUE",IF($C123&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5712,7 +5740,7 @@
         <v>1979.37</v>
       </c>
       <c r="J124" s="46" t="str">
-        <f aca="true">IF($B124="","",IF($F124&lt;&gt;"","PAID",IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B124="","",IF($F124&lt;&gt;"",IF($C124&gt;TODAY(),"ADJUSTED","PAID"),IF($C124&lt;TODAY(),"PAST DUE",IF($C124&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5747,7 +5775,7 @@
         <v>1934.37</v>
       </c>
       <c r="J125" s="46" t="str">
-        <f aca="true">IF($B125="","",IF($F125&lt;&gt;"","PAID",IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B125="","",IF($F125&lt;&gt;"",IF($C125&gt;TODAY(),"ADJUSTED","PAID"),IF($C125&lt;TODAY(),"PAST DUE",IF($C125&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -5782,7 +5810,7 @@
         <v/>
       </c>
       <c r="J126" s="46" t="str">
-        <f aca="true">IF($B126="","",IF($F126&lt;&gt;"","PAID",IF($C126&lt;TODAY(),"PAST DUE",IF($C126&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B126="","",IF($F126&lt;&gt;"",IF($C126&gt;TODAY(),"ADJUSTED","PAID"),IF($C126&lt;TODAY(),"PAST DUE",IF($C126&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -5817,7 +5845,7 @@
         <v/>
       </c>
       <c r="J127" s="46" t="str">
-        <f aca="true">IF($B127="","",IF($F127&lt;&gt;"","PAID",IF($C127&lt;TODAY(),"PAST DUE",IF($C127&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B127="","",IF($F127&lt;&gt;"",IF($C127&gt;TODAY(),"ADJUSTED","PAID"),IF($C127&lt;TODAY(),"PAST DUE",IF($C127&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -5852,7 +5880,7 @@
         <v/>
       </c>
       <c r="J128" s="46" t="str">
-        <f aca="true">IF($B128="","",IF($F128&lt;&gt;"","PAID",IF($C128&lt;TODAY(),"PAST DUE",IF($C128&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B128="","",IF($F128&lt;&gt;"",IF($C128&gt;TODAY(),"ADJUSTED","PAID"),IF($C128&lt;TODAY(),"PAST DUE",IF($C128&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -5887,13 +5915,13 @@
         <v/>
       </c>
       <c r="J129" s="46" t="str">
-        <f aca="true">IF($B129="","",IF($F129&lt;&gt;"","PAID",IF($C129&lt;TODAY(),"PAST DUE",IF($C129&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B129="","",IF($F129&lt;&gt;"",IF($C129&gt;TODAY(),"ADJUSTED","PAID"),IF($C129&lt;TODAY(),"PAST DUE",IF($C129&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C130" s="48"/>
       <c r="D130" s="48"/>
@@ -6026,7 +6054,7 @@
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B137" s="52" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C137" s="53"/>
       <c r="D137" s="53"/>
@@ -6063,7 +6091,7 @@
       <c r="E139" s="32"/>
       <c r="F139" s="32"/>
       <c r="G139" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H139" s="32"/>
       <c r="I139" s="34" t="n">
@@ -6078,19 +6106,19 @@
     </row>
     <row r="140" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B140" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C140" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E140" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F140" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G140" s="36" t="s">
         <v>18</v>
@@ -6099,10 +6127,10 @@
         <v>20</v>
       </c>
       <c r="I140" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J140" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6136,7 +6164,7 @@
         <v>2724.37</v>
       </c>
       <c r="J141" s="46" t="str">
-        <f aca="true">IF($B141="","",IF($F141&lt;&gt;"","PAID",IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B141="","",IF($F141&lt;&gt;"",IF($C141&gt;TODAY(),"ADJUSTED","PAID"),IF($C141&lt;TODAY(),"PAST DUE",IF($C141&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6171,7 +6199,7 @@
         <v>2707.38</v>
       </c>
       <c r="J142" s="46" t="str">
-        <f aca="true">IF($B142="","",IF($F142&lt;&gt;"","PAID",IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B142="","",IF($F142&lt;&gt;"",IF($C142&gt;TODAY(),"ADJUSTED","PAID"),IF($C142&lt;TODAY(),"PAST DUE",IF($C142&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6206,7 +6234,7 @@
         <v>2797.38</v>
       </c>
       <c r="J143" s="46" t="str">
-        <f aca="true">IF($B143="","",IF($F143&lt;&gt;"","PAID",IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B143="","",IF($F143&lt;&gt;"",IF($C143&gt;TODAY(),"ADJUSTED","PAID"),IF($C143&lt;TODAY(),"PAST DUE",IF($C143&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6241,7 +6269,7 @@
         <v/>
       </c>
       <c r="J144" s="46" t="str">
-        <f aca="true">IF($B144="","",IF($F144&lt;&gt;"","PAID",IF($C144&lt;TODAY(),"PAST DUE",IF($C144&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B144="","",IF($F144&lt;&gt;"",IF($C144&gt;TODAY(),"ADJUSTED","PAID"),IF($C144&lt;TODAY(),"PAST DUE",IF($C144&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6276,7 +6304,7 @@
         <v/>
       </c>
       <c r="J145" s="46" t="str">
-        <f aca="true">IF($B145="","",IF($F145&lt;&gt;"","PAID",IF($C145&lt;TODAY(),"PAST DUE",IF($C145&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B145="","",IF($F145&lt;&gt;"",IF($C145&gt;TODAY(),"ADJUSTED","PAID"),IF($C145&lt;TODAY(),"PAST DUE",IF($C145&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6311,7 +6339,7 @@
         <v/>
       </c>
       <c r="J146" s="46" t="str">
-        <f aca="true">IF($B146="","",IF($F146&lt;&gt;"","PAID",IF($C146&lt;TODAY(),"PAST DUE",IF($C146&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B146="","",IF($F146&lt;&gt;"",IF($C146&gt;TODAY(),"ADJUSTED","PAID"),IF($C146&lt;TODAY(),"PAST DUE",IF($C146&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6346,7 +6374,7 @@
         <v/>
       </c>
       <c r="J147" s="46" t="str">
-        <f aca="true">IF($B147="","",IF($F147&lt;&gt;"","PAID",IF($C147&lt;TODAY(),"PAST DUE",IF($C147&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B147="","",IF($F147&lt;&gt;"",IF($C147&gt;TODAY(),"ADJUSTED","PAID"),IF($C147&lt;TODAY(),"PAST DUE",IF($C147&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6381,7 +6409,7 @@
         <v/>
       </c>
       <c r="J148" s="46" t="str">
-        <f aca="true">IF($B148="","",IF($F148&lt;&gt;"","PAID",IF($C148&lt;TODAY(),"PAST DUE",IF($C148&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B148="","",IF($F148&lt;&gt;"",IF($C148&gt;TODAY(),"ADJUSTED","PAID"),IF($C148&lt;TODAY(),"PAST DUE",IF($C148&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6416,7 +6444,7 @@
         <v/>
       </c>
       <c r="J149" s="46" t="str">
-        <f aca="true">IF($B149="","",IF($F149&lt;&gt;"","PAID",IF($C149&lt;TODAY(),"PAST DUE",IF($C149&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B149="","",IF($F149&lt;&gt;"",IF($C149&gt;TODAY(),"ADJUSTED","PAID"),IF($C149&lt;TODAY(),"PAST DUE",IF($C149&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6451,13 +6479,13 @@
         <v/>
       </c>
       <c r="J150" s="46" t="str">
-        <f aca="true">IF($B150="","",IF($F150&lt;&gt;"","PAID",IF($C150&lt;TODAY(),"PAST DUE",IF($C150&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B150="","",IF($F150&lt;&gt;"",IF($C150&gt;TODAY(),"ADJUSTED","PAID"),IF($C150&lt;TODAY(),"PAST DUE",IF($C150&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B151" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C151" s="48"/>
       <c r="D151" s="48"/>
@@ -6590,7 +6618,7 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B158" s="52" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C158" s="53"/>
       <c r="D158" s="53"/>
@@ -6627,7 +6655,7 @@
       <c r="E160" s="32"/>
       <c r="F160" s="32"/>
       <c r="G160" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H160" s="32"/>
       <c r="I160" s="34" t="n">
@@ -6642,19 +6670,19 @@
     </row>
     <row r="161" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B161" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C161" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E161" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F161" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G161" s="36" t="s">
         <v>18</v>
@@ -6663,10 +6691,10 @@
         <v>20</v>
       </c>
       <c r="I161" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J161" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6700,7 +6728,7 @@
         <v>3587.38</v>
       </c>
       <c r="J162" s="46" t="str">
-        <f aca="true">IF($B162="","",IF($F162&lt;&gt;"","PAID",IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B162="","",IF($F162&lt;&gt;"",IF($C162&gt;TODAY(),"ADJUSTED","PAID"),IF($C162&lt;TODAY(),"PAST DUE",IF($C162&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6735,7 +6763,7 @@
         <v>3573.68</v>
       </c>
       <c r="J163" s="46" t="str">
-        <f aca="true">IF($B163="","",IF($F163&lt;&gt;"","PAID",IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B163="","",IF($F163&lt;&gt;"",IF($C163&gt;TODAY(),"ADJUSTED","PAID"),IF($C163&lt;TODAY(),"PAST DUE",IF($C163&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6770,7 +6798,7 @@
         <v>3529.81</v>
       </c>
       <c r="J164" s="46" t="str">
-        <f aca="true">IF($B164="","",IF($F164&lt;&gt;"","PAID",IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B164="","",IF($F164&lt;&gt;"",IF($C164&gt;TODAY(),"ADJUSTED","PAID"),IF($C164&lt;TODAY(),"PAST DUE",IF($C164&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6805,7 +6833,7 @@
         <v>3619.81</v>
       </c>
       <c r="J165" s="46" t="str">
-        <f aca="true">IF($B165="","",IF($F165&lt;&gt;"","PAID",IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B165="","",IF($F165&lt;&gt;"",IF($C165&gt;TODAY(),"ADJUSTED","PAID"),IF($C165&lt;TODAY(),"PAST DUE",IF($C165&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6840,7 +6868,7 @@
         <v>3269.81</v>
       </c>
       <c r="J166" s="46" t="str">
-        <f aca="true">IF($B166="","",IF($F166&lt;&gt;"","PAID",IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B166="","",IF($F166&lt;&gt;"",IF($C166&gt;TODAY(),"ADJUSTED","PAID"),IF($C166&lt;TODAY(),"PAST DUE",IF($C166&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6875,7 +6903,7 @@
         <v>3119.81</v>
       </c>
       <c r="J167" s="46" t="str">
-        <f aca="true">IF($B167="","",IF($F167&lt;&gt;"","PAID",IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B167="","",IF($F167&lt;&gt;"",IF($C167&gt;TODAY(),"ADJUSTED","PAID"),IF($C167&lt;TODAY(),"PAST DUE",IF($C167&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6910,7 +6938,7 @@
         <v>2976.44</v>
       </c>
       <c r="J168" s="46" t="str">
-        <f aca="true">IF($B168="","",IF($F168&lt;&gt;"","PAID",IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B168="","",IF($F168&lt;&gt;"",IF($C168&gt;TODAY(),"ADJUSTED","PAID"),IF($C168&lt;TODAY(),"PAST DUE",IF($C168&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -6945,7 +6973,7 @@
         <v/>
       </c>
       <c r="J169" s="46" t="str">
-        <f aca="true">IF($B169="","",IF($F169&lt;&gt;"","PAID",IF($C169&lt;TODAY(),"PAST DUE",IF($C169&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B169="","",IF($F169&lt;&gt;"",IF($C169&gt;TODAY(),"ADJUSTED","PAID"),IF($C169&lt;TODAY(),"PAST DUE",IF($C169&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -6980,7 +7008,7 @@
         <v/>
       </c>
       <c r="J170" s="46" t="str">
-        <f aca="true">IF($B170="","",IF($F170&lt;&gt;"","PAID",IF($C170&lt;TODAY(),"PAST DUE",IF($C170&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B170="","",IF($F170&lt;&gt;"",IF($C170&gt;TODAY(),"ADJUSTED","PAID"),IF($C170&lt;TODAY(),"PAST DUE",IF($C170&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -7015,13 +7043,13 @@
         <v/>
       </c>
       <c r="J171" s="46" t="str">
-        <f aca="true">IF($B171="","",IF($F171&lt;&gt;"","PAID",IF($C171&lt;TODAY(),"PAST DUE",IF($C171&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B171="","",IF($F171&lt;&gt;"",IF($C171&gt;TODAY(),"ADJUSTED","PAID"),IF($C171&lt;TODAY(),"PAST DUE",IF($C171&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B172" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C172" s="48"/>
       <c r="D172" s="48"/>
@@ -7154,7 +7182,7 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B179" s="52" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C179" s="53"/>
       <c r="D179" s="53"/>
@@ -7191,7 +7219,7 @@
       <c r="E181" s="32"/>
       <c r="F181" s="32"/>
       <c r="G181" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H181" s="32"/>
       <c r="I181" s="34" t="n">
@@ -7206,19 +7234,19 @@
     </row>
     <row r="182" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B182" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C182" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E182" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F182" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G182" s="36" t="s">
         <v>18</v>
@@ -7227,10 +7255,10 @@
         <v>20</v>
       </c>
       <c r="I182" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J182" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7264,7 +7292,7 @@
         <v>3766.44</v>
       </c>
       <c r="J183" s="46" t="str">
-        <f aca="true">IF($B183="","",IF($F183&lt;&gt;"","PAID",IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B183="","",IF($F183&lt;&gt;"",IF($C183&gt;TODAY(),"ADJUSTED","PAID"),IF($C183&lt;TODAY(),"PAST DUE",IF($C183&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7299,7 +7327,7 @@
         <v>3745.34</v>
       </c>
       <c r="J184" s="46" t="str">
-        <f aca="true">IF($B184="","",IF($F184&lt;&gt;"","PAID",IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B184="","",IF($F184&lt;&gt;"",IF($C184&gt;TODAY(),"ADJUSTED","PAID"),IF($C184&lt;TODAY(),"PAST DUE",IF($C184&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7334,7 +7362,7 @@
         <v>3725.34</v>
       </c>
       <c r="J185" s="46" t="str">
-        <f aca="true">IF($B185="","",IF($F185&lt;&gt;"","PAID",IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B185="","",IF($F185&lt;&gt;"",IF($C185&gt;TODAY(),"ADJUSTED","PAID"),IF($C185&lt;TODAY(),"PAST DUE",IF($C185&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7369,7 +7397,7 @@
         <v>3715.34</v>
       </c>
       <c r="J186" s="46" t="str">
-        <f aca="true">IF($B186="","",IF($F186&lt;&gt;"","PAID",IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B186="","",IF($F186&lt;&gt;"",IF($C186&gt;TODAY(),"ADJUSTED","PAID"),IF($C186&lt;TODAY(),"PAST DUE",IF($C186&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7404,7 +7432,7 @@
         <v>3805.34</v>
       </c>
       <c r="J187" s="46" t="str">
-        <f aca="true">IF($B187="","",IF($F187&lt;&gt;"","PAID",IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B187="","",IF($F187&lt;&gt;"",IF($C187&gt;TODAY(),"ADJUSTED","PAID"),IF($C187&lt;TODAY(),"PAST DUE",IF($C187&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7439,7 +7467,7 @@
         <v>3800.35</v>
       </c>
       <c r="J188" s="46" t="str">
-        <f aca="true">IF($B188="","",IF($F188&lt;&gt;"","PAID",IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B188="","",IF($F188&lt;&gt;"",IF($C188&gt;TODAY(),"ADJUSTED","PAID"),IF($C188&lt;TODAY(),"PAST DUE",IF($C188&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7474,7 +7502,7 @@
         <v>3300.35</v>
       </c>
       <c r="J189" s="46" t="str">
-        <f aca="true">IF($B189="","",IF($F189&lt;&gt;"","PAID",IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B189="","",IF($F189&lt;&gt;"",IF($C189&gt;TODAY(),"ADJUSTED","PAID"),IF($C189&lt;TODAY(),"PAST DUE",IF($C189&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7509,7 +7537,7 @@
         <v/>
       </c>
       <c r="J190" s="46" t="str">
-        <f aca="true">IF($B190="","",IF($F190&lt;&gt;"","PAID",IF($C190&lt;TODAY(),"PAST DUE",IF($C190&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B190="","",IF($F190&lt;&gt;"",IF($C190&gt;TODAY(),"ADJUSTED","PAID"),IF($C190&lt;TODAY(),"PAST DUE",IF($C190&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -7544,7 +7572,7 @@
         <v/>
       </c>
       <c r="J191" s="46" t="str">
-        <f aca="true">IF($B191="","",IF($F191&lt;&gt;"","PAID",IF($C191&lt;TODAY(),"PAST DUE",IF($C191&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B191="","",IF($F191&lt;&gt;"",IF($C191&gt;TODAY(),"ADJUSTED","PAID"),IF($C191&lt;TODAY(),"PAST DUE",IF($C191&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -7579,13 +7607,13 @@
         <v/>
       </c>
       <c r="J192" s="46" t="str">
-        <f aca="true">IF($B192="","",IF($F192&lt;&gt;"","PAID",IF($C192&lt;TODAY(),"PAST DUE",IF($C192&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B192="","",IF($F192&lt;&gt;"",IF($C192&gt;TODAY(),"ADJUSTED","PAID"),IF($C192&lt;TODAY(),"PAST DUE",IF($C192&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B193" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C193" s="48"/>
       <c r="D193" s="48"/>
@@ -7718,7 +7746,7 @@
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B200" s="52" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C200" s="53"/>
       <c r="D200" s="53"/>
@@ -7755,7 +7783,7 @@
       <c r="E202" s="32"/>
       <c r="F202" s="32"/>
       <c r="G202" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H202" s="32"/>
       <c r="I202" s="34" t="n">
@@ -7770,19 +7798,19 @@
     </row>
     <row r="203" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B203" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C203" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D203" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E203" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F203" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G203" s="36" t="s">
         <v>18</v>
@@ -7791,10 +7819,10 @@
         <v>20</v>
       </c>
       <c r="I203" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J203" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7828,7 +7856,7 @@
         <v>4090.35</v>
       </c>
       <c r="J204" s="46" t="str">
-        <f aca="true">IF($B204="","",IF($F204&lt;&gt;"","PAID",IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B204="","",IF($F204&lt;&gt;"",IF($C204&gt;TODAY(),"ADJUSTED","PAID"),IF($C204&lt;TODAY(),"PAST DUE",IF($C204&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7863,7 +7891,7 @@
         <v>3926.85</v>
       </c>
       <c r="J205" s="46" t="str">
-        <f aca="true">IF($B205="","",IF($F205&lt;&gt;"","PAID",IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B205="","",IF($F205&lt;&gt;"",IF($C205&gt;TODAY(),"ADJUSTED","PAID"),IF($C205&lt;TODAY(),"PAST DUE",IF($C205&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7898,7 +7926,7 @@
         <v>3923.86</v>
       </c>
       <c r="J206" s="46" t="str">
-        <f aca="true">IF($B206="","",IF($F206&lt;&gt;"","PAID",IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B206="","",IF($F206&lt;&gt;"",IF($C206&gt;TODAY(),"ADJUSTED","PAID"),IF($C206&lt;TODAY(),"PAST DUE",IF($C206&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7933,7 +7961,7 @@
         <v>4013.86</v>
       </c>
       <c r="J207" s="46" t="str">
-        <f aca="true">IF($B207="","",IF($F207&lt;&gt;"","PAID",IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B207="","",IF($F207&lt;&gt;"",IF($C207&gt;TODAY(),"ADJUSTED","PAID"),IF($C207&lt;TODAY(),"PAST DUE",IF($C207&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -7968,7 +7996,7 @@
         <v>3663.86</v>
       </c>
       <c r="J208" s="46" t="str">
-        <f aca="true">IF($B208="","",IF($F208&lt;&gt;"","PAID",IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B208="","",IF($F208&lt;&gt;"",IF($C208&gt;TODAY(),"ADJUSTED","PAID"),IF($C208&lt;TODAY(),"PAST DUE",IF($C208&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8003,7 +8031,7 @@
         <v/>
       </c>
       <c r="J209" s="46" t="str">
-        <f aca="true">IF($B209="","",IF($F209&lt;&gt;"","PAID",IF($C209&lt;TODAY(),"PAST DUE",IF($C209&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B209="","",IF($F209&lt;&gt;"",IF($C209&gt;TODAY(),"ADJUSTED","PAID"),IF($C209&lt;TODAY(),"PAST DUE",IF($C209&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8038,7 +8066,7 @@
         <v/>
       </c>
       <c r="J210" s="46" t="str">
-        <f aca="true">IF($B210="","",IF($F210&lt;&gt;"","PAID",IF($C210&lt;TODAY(),"PAST DUE",IF($C210&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B210="","",IF($F210&lt;&gt;"",IF($C210&gt;TODAY(),"ADJUSTED","PAID"),IF($C210&lt;TODAY(),"PAST DUE",IF($C210&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8073,7 +8101,7 @@
         <v/>
       </c>
       <c r="J211" s="46" t="str">
-        <f aca="true">IF($B211="","",IF($F211&lt;&gt;"","PAID",IF($C211&lt;TODAY(),"PAST DUE",IF($C211&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B211="","",IF($F211&lt;&gt;"",IF($C211&gt;TODAY(),"ADJUSTED","PAID"),IF($C211&lt;TODAY(),"PAST DUE",IF($C211&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8108,7 +8136,7 @@
         <v/>
       </c>
       <c r="J212" s="46" t="str">
-        <f aca="true">IF($B212="","",IF($F212&lt;&gt;"","PAID",IF($C212&lt;TODAY(),"PAST DUE",IF($C212&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B212="","",IF($F212&lt;&gt;"",IF($C212&gt;TODAY(),"ADJUSTED","PAID"),IF($C212&lt;TODAY(),"PAST DUE",IF($C212&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8143,13 +8171,13 @@
         <v/>
       </c>
       <c r="J213" s="46" t="str">
-        <f aca="true">IF($B213="","",IF($F213&lt;&gt;"","PAID",IF($C213&lt;TODAY(),"PAST DUE",IF($C213&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B213="","",IF($F213&lt;&gt;"",IF($C213&gt;TODAY(),"ADJUSTED","PAID"),IF($C213&lt;TODAY(),"PAST DUE",IF($C213&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B214" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C214" s="48"/>
       <c r="D214" s="48"/>
@@ -8282,7 +8310,7 @@
     </row>
     <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B221" s="52" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C221" s="53"/>
       <c r="D221" s="53"/>
@@ -8319,7 +8347,7 @@
       <c r="E223" s="32"/>
       <c r="F223" s="32"/>
       <c r="G223" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H223" s="32"/>
       <c r="I223" s="34" t="n">
@@ -8334,19 +8362,19 @@
     </row>
     <row r="224" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B224" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C224" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D224" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E224" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F224" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G224" s="36" t="s">
         <v>18</v>
@@ -8355,10 +8383,10 @@
         <v>20</v>
       </c>
       <c r="I224" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J224" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8392,7 +8420,7 @@
         <v>4453.86</v>
       </c>
       <c r="J225" s="46" t="str">
-        <f aca="true">IF($B225="","",IF($F225&lt;&gt;"","PAID",IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B225="","",IF($F225&lt;&gt;"",IF($C225&gt;TODAY(),"ADJUSTED","PAID"),IF($C225&lt;TODAY(),"PAST DUE",IF($C225&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8427,7 +8455,7 @@
         <v>4282.76</v>
       </c>
       <c r="J226" s="46" t="str">
-        <f aca="true">IF($B226="","",IF($F226&lt;&gt;"","PAID",IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B226="","",IF($F226&lt;&gt;"",IF($C226&gt;TODAY(),"ADJUSTED","PAID"),IF($C226&lt;TODAY(),"PAST DUE",IF($C226&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8462,7 +8490,7 @@
         <v>4237.76</v>
       </c>
       <c r="J227" s="46" t="str">
-        <f aca="true">IF($B227="","",IF($F227&lt;&gt;"","PAID",IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B227="","",IF($F227&lt;&gt;"",IF($C227&gt;TODAY(),"ADJUSTED","PAID"),IF($C227&lt;TODAY(),"PAST DUE",IF($C227&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8497,7 +8525,7 @@
         <v>4220.77</v>
       </c>
       <c r="J228" s="46" t="str">
-        <f aca="true">IF($B228="","",IF($F228&lt;&gt;"","PAID",IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B228="","",IF($F228&lt;&gt;"",IF($C228&gt;TODAY(),"ADJUSTED","PAID"),IF($C228&lt;TODAY(),"PAST DUE",IF($C228&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8532,7 +8560,7 @@
         <v>4310.77</v>
       </c>
       <c r="J229" s="46" t="str">
-        <f aca="true">IF($B229="","",IF($F229&lt;&gt;"","PAID",IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B229="","",IF($F229&lt;&gt;"",IF($C229&gt;TODAY(),"ADJUSTED","PAID"),IF($C229&lt;TODAY(),"PAST DUE",IF($C229&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8567,7 +8595,7 @@
         <v/>
       </c>
       <c r="J230" s="46" t="str">
-        <f aca="true">IF($B230="","",IF($F230&lt;&gt;"","PAID",IF($C230&lt;TODAY(),"PAST DUE",IF($C230&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B230="","",IF($F230&lt;&gt;"",IF($C230&gt;TODAY(),"ADJUSTED","PAID"),IF($C230&lt;TODAY(),"PAST DUE",IF($C230&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8602,7 +8630,7 @@
         <v/>
       </c>
       <c r="J231" s="46" t="str">
-        <f aca="true">IF($B231="","",IF($F231&lt;&gt;"","PAID",IF($C231&lt;TODAY(),"PAST DUE",IF($C231&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B231="","",IF($F231&lt;&gt;"",IF($C231&gt;TODAY(),"ADJUSTED","PAID"),IF($C231&lt;TODAY(),"PAST DUE",IF($C231&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8637,7 +8665,7 @@
         <v/>
       </c>
       <c r="J232" s="46" t="str">
-        <f aca="true">IF($B232="","",IF($F232&lt;&gt;"","PAID",IF($C232&lt;TODAY(),"PAST DUE",IF($C232&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B232="","",IF($F232&lt;&gt;"",IF($C232&gt;TODAY(),"ADJUSTED","PAID"),IF($C232&lt;TODAY(),"PAST DUE",IF($C232&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8672,7 +8700,7 @@
         <v/>
       </c>
       <c r="J233" s="46" t="str">
-        <f aca="true">IF($B233="","",IF($F233&lt;&gt;"","PAID",IF($C233&lt;TODAY(),"PAST DUE",IF($C233&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B233="","",IF($F233&lt;&gt;"",IF($C233&gt;TODAY(),"ADJUSTED","PAID"),IF($C233&lt;TODAY(),"PAST DUE",IF($C233&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -8707,13 +8735,13 @@
         <v/>
       </c>
       <c r="J234" s="46" t="str">
-        <f aca="true">IF($B234="","",IF($F234&lt;&gt;"","PAID",IF($C234&lt;TODAY(),"PAST DUE",IF($C234&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B234="","",IF($F234&lt;&gt;"",IF($C234&gt;TODAY(),"ADJUSTED","PAID"),IF($C234&lt;TODAY(),"PAST DUE",IF($C234&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B235" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C235" s="48"/>
       <c r="D235" s="48"/>
@@ -8846,7 +8874,7 @@
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B242" s="52" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C242" s="53"/>
       <c r="D242" s="53"/>
@@ -8883,7 +8911,7 @@
       <c r="E244" s="32"/>
       <c r="F244" s="32"/>
       <c r="G244" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H244" s="32"/>
       <c r="I244" s="34" t="n">
@@ -8898,19 +8926,19 @@
     </row>
     <row r="245" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B245" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C245" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D245" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E245" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F245" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G245" s="36" t="s">
         <v>18</v>
@@ -8919,10 +8947,10 @@
         <v>20</v>
       </c>
       <c r="I245" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J245" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8956,7 +8984,7 @@
         <v>5100.77</v>
       </c>
       <c r="J246" s="46" t="str">
-        <f aca="true">IF($B246="","",IF($F246&lt;&gt;"","PAID",IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B246="","",IF($F246&lt;&gt;"",IF($C246&gt;TODAY(),"ADJUSTED","PAID"),IF($C246&lt;TODAY(),"PAST DUE",IF($C246&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -8991,7 +9019,7 @@
         <v>5087.07</v>
       </c>
       <c r="J247" s="46" t="str">
-        <f aca="true">IF($B247="","",IF($F247&lt;&gt;"","PAID",IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B247="","",IF($F247&lt;&gt;"",IF($C247&gt;TODAY(),"ADJUSTED","PAID"),IF($C247&lt;TODAY(),"PAST DUE",IF($C247&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9026,7 +9054,7 @@
         <v>5043.2</v>
       </c>
       <c r="J248" s="46" t="str">
-        <f aca="true">IF($B248="","",IF($F248&lt;&gt;"","PAID",IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B248="","",IF($F248&lt;&gt;"",IF($C248&gt;TODAY(),"ADJUSTED","PAID"),IF($C248&lt;TODAY(),"PAST DUE",IF($C248&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9061,7 +9089,7 @@
         <v>5133.2</v>
       </c>
       <c r="J249" s="46" t="str">
-        <f aca="true">IF($B249="","",IF($F249&lt;&gt;"","PAID",IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B249="","",IF($F249&lt;&gt;"",IF($C249&gt;TODAY(),"ADJUSTED","PAID"),IF($C249&lt;TODAY(),"PAST DUE",IF($C249&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9096,7 +9124,7 @@
         <v/>
       </c>
       <c r="J250" s="46" t="str">
-        <f aca="true">IF($B250="","",IF($F250&lt;&gt;"","PAID",IF($C250&lt;TODAY(),"PAST DUE",IF($C250&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B250="","",IF($F250&lt;&gt;"",IF($C250&gt;TODAY(),"ADJUSTED","PAID"),IF($C250&lt;TODAY(),"PAST DUE",IF($C250&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -9131,7 +9159,7 @@
         <v/>
       </c>
       <c r="J251" s="46" t="str">
-        <f aca="true">IF($B251="","",IF($F251&lt;&gt;"","PAID",IF($C251&lt;TODAY(),"PAST DUE",IF($C251&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B251="","",IF($F251&lt;&gt;"",IF($C251&gt;TODAY(),"ADJUSTED","PAID"),IF($C251&lt;TODAY(),"PAST DUE",IF($C251&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -9166,7 +9194,7 @@
         <v/>
       </c>
       <c r="J252" s="46" t="str">
-        <f aca="true">IF($B252="","",IF($F252&lt;&gt;"","PAID",IF($C252&lt;TODAY(),"PAST DUE",IF($C252&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B252="","",IF($F252&lt;&gt;"",IF($C252&gt;TODAY(),"ADJUSTED","PAID"),IF($C252&lt;TODAY(),"PAST DUE",IF($C252&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -9201,7 +9229,7 @@
         <v/>
       </c>
       <c r="J253" s="46" t="str">
-        <f aca="true">IF($B253="","",IF($F253&lt;&gt;"","PAID",IF($C253&lt;TODAY(),"PAST DUE",IF($C253&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B253="","",IF($F253&lt;&gt;"",IF($C253&gt;TODAY(),"ADJUSTED","PAID"),IF($C253&lt;TODAY(),"PAST DUE",IF($C253&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -9236,7 +9264,7 @@
         <v/>
       </c>
       <c r="J254" s="46" t="str">
-        <f aca="true">IF($B254="","",IF($F254&lt;&gt;"","PAID",IF($C254&lt;TODAY(),"PAST DUE",IF($C254&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B254="","",IF($F254&lt;&gt;"",IF($C254&gt;TODAY(),"ADJUSTED","PAID"),IF($C254&lt;TODAY(),"PAST DUE",IF($C254&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -9271,13 +9299,13 @@
         <v/>
       </c>
       <c r="J255" s="46" t="str">
-        <f aca="true">IF($B255="","",IF($F255&lt;&gt;"","PAID",IF($C255&lt;TODAY(),"PAST DUE",IF($C255&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B255="","",IF($F255&lt;&gt;"",IF($C255&gt;TODAY(),"ADJUSTED","PAID"),IF($C255&lt;TODAY(),"PAST DUE",IF($C255&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B256" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C256" s="48"/>
       <c r="D256" s="48"/>
@@ -9410,7 +9438,7 @@
     </row>
     <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B263" s="52" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C263" s="53"/>
       <c r="D263" s="53"/>
@@ -9447,7 +9475,7 @@
       <c r="E265" s="32"/>
       <c r="F265" s="32"/>
       <c r="G265" s="33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H265" s="32"/>
       <c r="I265" s="34" t="n">
@@ -9462,19 +9490,19 @@
     </row>
     <row r="266" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B266" s="35" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C266" s="35" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="D266" s="35" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E266" s="35" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F266" s="35" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G266" s="36" t="s">
         <v>18</v>
@@ -9483,10 +9511,10 @@
         <v>20</v>
       </c>
       <c r="I266" s="35" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J266" s="35" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9520,7 +9548,7 @@
         <v>5923.2</v>
       </c>
       <c r="J267" s="46" t="str">
-        <f aca="true">IF($B267="","",IF($F267&lt;&gt;"","PAID",IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B267="","",IF($F267&lt;&gt;"",IF($C267&gt;TODAY(),"ADJUSTED","PAID"),IF($C267&lt;TODAY(),"PAST DUE",IF($C267&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9555,7 +9583,7 @@
         <v>5573.2</v>
       </c>
       <c r="J268" s="46" t="str">
-        <f aca="true">IF($B268="","",IF($F268&lt;&gt;"","PAID",IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B268="","",IF($F268&lt;&gt;"",IF($C268&gt;TODAY(),"ADJUSTED","PAID"),IF($C268&lt;TODAY(),"PAST DUE",IF($C268&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9590,7 +9618,7 @@
         <v>5423.2</v>
       </c>
       <c r="J269" s="46" t="str">
-        <f aca="true">IF($B269="","",IF($F269&lt;&gt;"","PAID",IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B269="","",IF($F269&lt;&gt;"",IF($C269&gt;TODAY(),"ADJUSTED","PAID"),IF($C269&lt;TODAY(),"PAST DUE",IF($C269&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9625,7 +9653,7 @@
         <v>5279.83</v>
       </c>
       <c r="J270" s="46" t="str">
-        <f aca="true">IF($B270="","",IF($F270&lt;&gt;"","PAID",IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B270="","",IF($F270&lt;&gt;"",IF($C270&gt;TODAY(),"ADJUSTED","PAID"),IF($C270&lt;TODAY(),"PAST DUE",IF($C270&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9660,7 +9688,7 @@
         <v>5369.83</v>
       </c>
       <c r="J271" s="46" t="str">
-        <f aca="true">IF($B271="","",IF($F271&lt;&gt;"","PAID",IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B271="","",IF($F271&lt;&gt;"",IF($C271&gt;TODAY(),"ADJUSTED","PAID"),IF($C271&lt;TODAY(),"PAST DUE",IF($C271&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9695,7 +9723,7 @@
         <v>5348.73</v>
       </c>
       <c r="J272" s="46" t="str">
-        <f aca="true">IF($B272="","",IF($F272&lt;&gt;"","PAID",IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B272="","",IF($F272&lt;&gt;"",IF($C272&gt;TODAY(),"ADJUSTED","PAID"),IF($C272&lt;TODAY(),"PAST DUE",IF($C272&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9730,7 +9758,7 @@
         <v>5328.73</v>
       </c>
       <c r="J273" s="46" t="str">
-        <f aca="true">IF($B273="","",IF($F273&lt;&gt;"","PAID",IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B273="","",IF($F273&lt;&gt;"",IF($C273&gt;TODAY(),"ADJUSTED","PAID"),IF($C273&lt;TODAY(),"PAST DUE",IF($C273&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9765,7 +9793,7 @@
         <v>5318.73</v>
       </c>
       <c r="J274" s="46" t="str">
-        <f aca="true">IF($B274="","",IF($F274&lt;&gt;"","PAID",IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B274="","",IF($F274&lt;&gt;"",IF($C274&gt;TODAY(),"ADJUSTED","PAID"),IF($C274&lt;TODAY(),"PAST DUE",IF($C274&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v>Upcoming</v>
       </c>
     </row>
@@ -9800,7 +9828,7 @@
         <v/>
       </c>
       <c r="J275" s="46" t="str">
-        <f aca="true">IF($B275="","",IF($F275&lt;&gt;"","PAID",IF($C275&lt;TODAY(),"PAST DUE",IF($C275&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B275="","",IF($F275&lt;&gt;"",IF($C275&gt;TODAY(),"ADJUSTED","PAID"),IF($C275&lt;TODAY(),"PAST DUE",IF($C275&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
@@ -9835,13 +9863,13 @@
         <v/>
       </c>
       <c r="J276" s="46" t="str">
-        <f aca="true">IF($B276="","",IF($F276&lt;&gt;"","PAID",IF($C276&lt;TODAY(),"PAST DUE",IF($C276&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
+        <f aca="true">IF($B276="","",IF($F276&lt;&gt;"",IF($C276&gt;TODAY(),"ADJUSTED","PAID"),IF($C276&lt;TODAY(),"PAST DUE",IF($C276&lt;=TODAY()+7,"DUE","Upcoming"))))</f>
         <v/>
       </c>
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B277" s="47" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C277" s="48"/>
       <c r="D277" s="48"/>
@@ -9974,7 +10002,7 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B284" s="52" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C284" s="53"/>
       <c r="D284" s="53"/>
@@ -10060,17 +10088,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="57" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C4" s="57"/>
       <c r="D4" s="57"/>
@@ -10081,7 +10109,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="57" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="57"/>
@@ -10096,7 +10124,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="57" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C6" s="57"/>
       <c r="D6" s="57"/>
@@ -10111,7 +10139,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="57" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C7" s="57"/>
       <c r="D7" s="57"/>
@@ -10122,7 +10150,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="57" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C8" s="57"/>
       <c r="D8" s="57"/>
@@ -10133,7 +10161,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C9" s="57"/>
       <c r="D9" s="57"/>
@@ -10144,7 +10172,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="57" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C10" s="57"/>
       <c r="D10" s="57"/>
@@ -10155,34 +10183,34 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G12" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="I12" s="15" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10720,10 +10748,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="56" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C26" s="71" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D26" s="72" t="n">
         <f aca="false">$D$13</f>
@@ -10753,7 +10781,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="73" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C28" s="73"/>
       <c r="D28" s="73"/>
@@ -10823,47 +10851,47 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="74" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="75" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B3" s="75" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C3" s="75" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="D3" s="75" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E3" s="75" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F3" s="75" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G3" s="75" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H3" s="75" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="I3" s="75" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J3" s="75" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="K3" s="75" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
